--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C712"/>
+  <dimension ref="A1:C754"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -802,7443 +802,7905 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Select an option</v>
+        <v>No results</v>
       </c>
       <c r="B37" t="str">
-        <v>اختر خياراً</v>
+        <v>لا توجد نتائج</v>
       </c>
       <c r="C37" t="str">
-        <v>Izvēlieties opciju</v>
+        <v>Nav rezultātu</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Required</v>
+        <v>No results.</v>
       </c>
       <c r="B38" t="str">
-        <v>مطلوب</v>
+        <v>لا توجد نتائج.</v>
       </c>
       <c r="C38" t="str">
-        <v>Obligāts</v>
+        <v>Nav rezultātu.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Optional</v>
+        <v>Select an option</v>
       </c>
       <c r="B39" t="str">
-        <v>اختياري</v>
+        <v>اختر خياراً</v>
       </c>
       <c r="C39" t="str">
-        <v>Neobligāts</v>
+        <v>Izvēlieties opciju</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>View</v>
+        <v>Required</v>
       </c>
       <c r="B40" t="str">
-        <v>عرض</v>
+        <v>مطلوب</v>
       </c>
       <c r="C40" t="str">
-        <v>Skatīt</v>
+        <v>Obligāts</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Download</v>
+        <v>Optional</v>
       </c>
       <c r="B41" t="str">
-        <v>تحميل</v>
+        <v>اختياري</v>
       </c>
       <c r="C41" t="str">
-        <v>Lejupielādēt</v>
+        <v>Neobligāts</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Upload</v>
+        <v>View</v>
       </c>
       <c r="B42" t="str">
-        <v>رفع</v>
+        <v>عرض</v>
       </c>
       <c r="C42" t="str">
-        <v>Augšupielādēt</v>
+        <v>Skatīt</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Select</v>
+        <v>Download</v>
       </c>
       <c r="B43" t="str">
-        <v>اختيار</v>
+        <v>تحميل</v>
       </c>
       <c r="C43" t="str">
-        <v>Izvēlēties</v>
+        <v>Lejupielādēt</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Clear</v>
+        <v>Upload</v>
       </c>
       <c r="B44" t="str">
-        <v>مسح</v>
+        <v>رفع</v>
       </c>
       <c r="C44" t="str">
-        <v>Notīrīt</v>
+        <v>Augšupielādēt</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Reset</v>
+        <v>Select</v>
       </c>
       <c r="B45" t="str">
-        <v>إعادة تعيين</v>
+        <v>اختيار</v>
       </c>
       <c r="C45" t="str">
-        <v>Atiestatīt</v>
+        <v>Izvēlēties</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Apply</v>
+        <v>Clear</v>
       </c>
       <c r="B46" t="str">
-        <v>تطبيق</v>
+        <v>مسح</v>
       </c>
       <c r="C46" t="str">
-        <v>Lietot</v>
+        <v>Notīrīt</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Update</v>
+        <v>Reset</v>
       </c>
       <c r="B47" t="str">
-        <v>تحديث</v>
+        <v>إعادة تعيين</v>
       </c>
       <c r="C47" t="str">
-        <v>Atjaunināt</v>
+        <v>Atiestatīt</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Create</v>
+        <v>Apply</v>
       </c>
       <c r="B48" t="str">
-        <v>إنشاء</v>
+        <v>تطبيق</v>
       </c>
       <c r="C48" t="str">
-        <v>Izveidot</v>
+        <v>Lietot</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Remove</v>
+        <v>Update</v>
       </c>
       <c r="B49" t="str">
-        <v>إزالة</v>
+        <v>تحديث</v>
       </c>
       <c r="C49" t="str">
-        <v>Noņemt</v>
+        <v>Atjaunināt</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Continue</v>
+        <v>Create</v>
       </c>
       <c r="B50" t="str">
-        <v>متابعة</v>
+        <v>إنشاء</v>
       </c>
       <c r="C50" t="str">
-        <v>Turpināt</v>
+        <v>Izveidot</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Finish</v>
+        <v>Remove</v>
       </c>
       <c r="B51" t="str">
-        <v>إنهاء</v>
+        <v>إزالة</v>
       </c>
       <c r="C51" t="str">
-        <v>Pabeigt</v>
+        <v>Noņemt</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Done</v>
+        <v>Continue</v>
       </c>
       <c r="B52" t="str">
-        <v>تم</v>
+        <v>متابعة</v>
       </c>
       <c r="C52" t="str">
-        <v>Gatavs</v>
+        <v>Turpināt</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Error</v>
+        <v>Finish</v>
       </c>
       <c r="B53" t="str">
-        <v>خطأ</v>
+        <v>إنهاء</v>
       </c>
       <c r="C53" t="str">
-        <v>Kļūda</v>
+        <v>Pabeigt</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Success</v>
+        <v>Done</v>
       </c>
       <c r="B54" t="str">
-        <v>نجاح</v>
+        <v>تم</v>
       </c>
       <c r="C54" t="str">
-        <v>Veiksmīgi</v>
+        <v>Gatavs</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B55" t="str">
-        <v>تحذير</v>
+        <v>خطأ</v>
       </c>
       <c r="C55" t="str">
-        <v>Brīdinājums</v>
+        <v>Kļūda</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Info</v>
+        <v>Success</v>
       </c>
       <c r="B56" t="str">
-        <v>معلومات</v>
+        <v>نجاح</v>
       </c>
       <c r="C56" t="str">
-        <v>Informācija</v>
+        <v>Veiksmīgi</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading</v>
+        <v>Warning</v>
       </c>
       <c r="B57" t="str">
-        <v>تحميل</v>
+        <v>تحذير</v>
       </c>
       <c r="C57" t="str">
-        <v>Ielāde</v>
+        <v>Brīdinājums</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Please wait...</v>
+        <v>Info</v>
       </c>
       <c r="B58" t="str">
-        <v>يرجى الانتظار...</v>
+        <v>معلومات</v>
       </c>
       <c r="C58" t="str">
-        <v>Lūdzu, uzgaidiet...</v>
+        <v>Informācija</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>No items found</v>
+        <v>Loading</v>
       </c>
       <c r="B59" t="str">
-        <v>لم يتم العثور على عناصر</v>
+        <v>تحميل</v>
       </c>
       <c r="C59" t="str">
-        <v>Nav atrasts neviens vienums</v>
+        <v>Ielāde</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Are you sure?</v>
+        <v>Please wait...</v>
       </c>
       <c r="B60" t="str">
-        <v>هل أنت متأكد؟</v>
+        <v>يرجى الانتظار...</v>
       </c>
       <c r="C60" t="str">
-        <v>Vai esat pārliecināts?</v>
+        <v>Lūdzu, uzgaidiet...</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>This action cannot be undone.</v>
+        <v>No items found</v>
       </c>
       <c r="B61" t="str">
-        <v>لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>لم يتم العثور على عناصر</v>
       </c>
       <c r="C61" t="str">
-        <v>Šo darbību nevar atsaukt.</v>
+        <v>Nav atrasts neviens vienums</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Time</v>
+        <v>Are you sure?</v>
       </c>
       <c r="B62" t="str">
-        <v>الوقت</v>
+        <v>هل أنت متأكد؟</v>
       </c>
       <c r="C62" t="str">
-        <v>Laiks</v>
+        <v>Vai esat pārliecināts?</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Notifications</v>
+        <v>This action cannot be undone.</v>
       </c>
       <c r="B63" t="str">
-        <v>الإشعارات</v>
+        <v>لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C63" t="str">
-        <v>Paziņojumi</v>
+        <v>Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Mark all read</v>
+        <v>Time</v>
       </c>
       <c r="B64" t="str">
-        <v>تحديد الكل كمقروء</v>
+        <v>الوقت</v>
       </c>
       <c r="C64" t="str">
-        <v>Atzīmēt visus kā lasītus</v>
+        <v>Laiks</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>View all notifications</v>
+        <v>Notifications</v>
       </c>
       <c r="B65" t="str">
-        <v>عرض جميع الإشعارات</v>
+        <v>الإشعارات</v>
       </c>
       <c r="C65" t="str">
-        <v>Skatīt visus paziņojumus</v>
+        <v>Paziņojumi</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Evidence request due tomorrow</v>
+        <v>Mark all read</v>
       </c>
       <c r="B66" t="str">
-        <v>طلب الأدلة مستحق غداً</v>
+        <v>تحديد الكل كمقروء</v>
       </c>
       <c r="C66" t="str">
-        <v>Pierādījumu pieprasījums jāiesniedz rīt</v>
+        <v>Atzīmēt visus kā lasītus</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Risk assessment assigned</v>
+        <v>View all notifications</v>
       </c>
       <c r="B67" t="str">
-        <v>تم تعيين تقييم المخاطر</v>
+        <v>عرض جميع الإشعارات</v>
       </c>
       <c r="C67" t="str">
-        <v>Piešķirts riska novērtējums</v>
+        <v>Skatīt visus paziņojumus</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>New audit finding created</v>
+        <v>Evidence request due tomorrow</v>
       </c>
       <c r="B68" t="str">
-        <v>تم إنشاء اكتشاف تدقيق جديد</v>
+        <v>طلب الأدلة مستحق غداً</v>
       </c>
       <c r="C68" t="str">
-        <v>Izveidots jauns audita konstatējums</v>
+        <v>Pierādījumu pieprasījums jāiesniedz rīt</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2 hours ago</v>
+        <v>Risk assessment assigned</v>
       </c>
       <c r="B69" t="str">
-        <v>قبل ساعتين</v>
+        <v>تم تعيين تقييم المخاطر</v>
       </c>
       <c r="C69" t="str">
-        <v>Pirms 2 stundām</v>
+        <v>Piešķirts riska novērtējums</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Yesterday</v>
+        <v>New audit finding created</v>
       </c>
       <c r="B70" t="str">
-        <v>أمس</v>
+        <v>تم إنشاء اكتشاف تدقيق جديد</v>
       </c>
       <c r="C70" t="str">
-        <v>Vakar</v>
+        <v>Izveidots jauns audita konstatējums</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2 days ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="B71" t="str">
-        <v>قبل يومين</v>
+        <v>قبل ساعتين</v>
       </c>
       <c r="C71" t="str">
-        <v>Pirms 2 dienām</v>
+        <v>Pirms 2 stundām</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Profile</v>
+        <v>Yesterday</v>
       </c>
       <c r="B72" t="str">
-        <v>الملف الشخصي</v>
+        <v>أمس</v>
       </c>
       <c r="C72" t="str">
-        <v>Profils</v>
+        <v>Vakar</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Settings</v>
+        <v>2 days ago</v>
       </c>
       <c r="B73" t="str">
-        <v>الإعدادات</v>
+        <v>قبل يومين</v>
       </c>
       <c r="C73" t="str">
-        <v>Iestatījumi</v>
+        <v>Pirms 2 dienām</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Log out</v>
+        <v>Profile</v>
       </c>
       <c r="B74" t="str">
-        <v>تسجيل الخروج</v>
+        <v>الملف الشخصي</v>
       </c>
       <c r="C74" t="str">
-        <v>Iziet</v>
+        <v>Profils</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>User</v>
+        <v>Settings</v>
       </c>
       <c r="B75" t="str">
-        <v>المستخدم</v>
+        <v>الإعدادات</v>
       </c>
       <c r="C75" t="str">
-        <v>Lietotājs</v>
+        <v>Iestatījumi</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>GRC Platform</v>
+        <v>Log out</v>
       </c>
       <c r="B76" t="str">
-        <v>منصة الحوكمة والمخاطر والامتثال</v>
+        <v>تسجيل الخروج</v>
       </c>
       <c r="C76" t="str">
-        <v>GRC Platforma</v>
+        <v>Iziet</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>v2.0</v>
+        <v>User</v>
       </c>
       <c r="B77" t="str">
-        <v>الإصدار 2.0</v>
+        <v>المستخدم</v>
       </c>
       <c r="C77" t="str">
-        <v>v2.0</v>
+        <v>Lietotājs</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Dashboard</v>
+        <v>GRC Platform</v>
       </c>
       <c r="B78" t="str">
-        <v>لوحة التحكم</v>
+        <v>منصة الحوكمة والمخاطر والامتثال</v>
       </c>
       <c r="C78" t="str">
-        <v>Vadības panelis</v>
+        <v>GRC Platforma</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dashboard Overview</v>
+        <v>v2.0</v>
       </c>
       <c r="B79" t="str">
-        <v>نظرة عامة على لوحة التحكم</v>
+        <v>الإصدار 2.0</v>
       </c>
       <c r="C79" t="str">
-        <v>Vadības paneļa pārskats</v>
+        <v>v2.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Customer Accounts</v>
+        <v>Dashboard</v>
       </c>
       <c r="B80" t="str">
-        <v>حسابات العملاء</v>
+        <v>لوحة التحكم</v>
       </c>
       <c r="C80" t="str">
-        <v>Klientu konti</v>
+        <v>Vadības panelis</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Customer</v>
+        <v>Dashboard Overview</v>
       </c>
       <c r="B81" t="str">
-        <v>العميل</v>
+        <v>نظرة عامة على لوحة التحكم</v>
       </c>
       <c r="C81" t="str">
-        <v>Klients</v>
+        <v>Vadības paneļa pārskats</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Organization</v>
+        <v>Customer Accounts</v>
       </c>
       <c r="B82" t="str">
-        <v>المنظمة</v>
+        <v>حسابات العملاء</v>
       </c>
       <c r="C82" t="str">
-        <v>Organizācija</v>
+        <v>Klientu konti</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Organization Dashboard</v>
+        <v>Customer</v>
       </c>
       <c r="B83" t="str">
-        <v>لوحة تحكم المنظمة</v>
+        <v>العميل</v>
       </c>
       <c r="C83" t="str">
-        <v>Organizācijas vadības panelis</v>
+        <v>Klients</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Context</v>
+        <v>Organization</v>
       </c>
       <c r="B84" t="str">
-        <v>السياق</v>
+        <v>المنظمة</v>
       </c>
       <c r="C84" t="str">
-        <v>Konteksts</v>
+        <v>Organizācija</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Users</v>
+        <v>Organization Dashboard</v>
       </c>
       <c r="B85" t="str">
-        <v>المستخدمون</v>
+        <v>لوحة تحكم المنظمة</v>
       </c>
       <c r="C85" t="str">
-        <v>Lietotāji</v>
+        <v>Organizācijas vadības panelis</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Process</v>
+        <v>Context</v>
       </c>
       <c r="B86" t="str">
-        <v>العمليات</v>
+        <v>السياق</v>
       </c>
       <c r="C86" t="str">
-        <v>Process</v>
+        <v>Konteksts</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Organization Settings</v>
+        <v>Users</v>
       </c>
       <c r="B87" t="str">
-        <v>إعدادات المنظمة</v>
+        <v>المستخدمون</v>
       </c>
       <c r="C87" t="str">
-        <v>Organizācijas iestatījumi</v>
+        <v>Lietotāji</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Reports</v>
+        <v>Process</v>
       </c>
       <c r="B88" t="str">
-        <v>التقارير</v>
+        <v>العمليات</v>
       </c>
       <c r="C88" t="str">
-        <v>Atskaites</v>
+        <v>Process</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Compliance</v>
+        <v>Organization Settings</v>
       </c>
       <c r="B89" t="str">
-        <v>الامتثال</v>
+        <v>إعدادات المنظمة</v>
       </c>
       <c r="C89" t="str">
-        <v>Atbilstība</v>
+        <v>Organizācijas iestatījumi</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Frameworks</v>
+        <v>Reports</v>
       </c>
       <c r="B90" t="str">
-        <v>الأطر</v>
+        <v>التقارير</v>
       </c>
       <c r="C90" t="str">
-        <v>Ietvari</v>
+        <v>Atskaites</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Controls</v>
+        <v>Compliance</v>
       </c>
       <c r="B91" t="str">
-        <v>الضوابط</v>
+        <v>الامتثال</v>
       </c>
       <c r="C91" t="str">
-        <v>Kontroles</v>
+        <v>Atbilstība</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Governance</v>
+        <v>Frameworks</v>
       </c>
       <c r="B92" t="str">
-        <v>الحوكمة</v>
+        <v>الأطر</v>
       </c>
       <c r="C92" t="str">
-        <v>Pārvaldība</v>
+        <v>Ietvari</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Evidence</v>
+        <v>Controls</v>
       </c>
       <c r="B93" t="str">
-        <v>الأدلة</v>
+        <v>الضوابط</v>
       </c>
       <c r="C93" t="str">
-        <v>Pierādījumi</v>
+        <v>Kontroles</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Exception Management</v>
+        <v>Governance</v>
       </c>
       <c r="B94" t="str">
-        <v>إدارة الاستثناءات</v>
+        <v>الحوكمة</v>
       </c>
       <c r="C94" t="str">
-        <v>Izņēmumu pārvaldība</v>
+        <v>Pārvaldība</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>KPI</v>
+        <v>Evidence</v>
       </c>
       <c r="B95" t="str">
-        <v>مؤشرات الأداء</v>
+        <v>الأدلة</v>
       </c>
       <c r="C95" t="str">
-        <v>KPI</v>
+        <v>Pierādījumi</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Master Data</v>
+        <v>Exception Management</v>
       </c>
       <c r="B96" t="str">
-        <v>البيانات الرئيسية</v>
+        <v>إدارة الاستثناءات</v>
       </c>
       <c r="C96" t="str">
-        <v>Pamatdati</v>
+        <v>Izņēmumu pārvaldība</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Asset Management</v>
+        <v>KPI</v>
       </c>
       <c r="B97" t="str">
-        <v>إدارة الأصول</v>
+        <v>مؤشرات الأداء</v>
       </c>
       <c r="C97" t="str">
-        <v>Aktīvu pārvaldība</v>
+        <v>KPI</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Asset Inventory</v>
+        <v>Master Data</v>
       </c>
       <c r="B98" t="str">
-        <v>جرد الأصول</v>
+        <v>البيانات الرئيسية</v>
       </c>
       <c r="C98" t="str">
-        <v>Aktīvu inventārs</v>
+        <v>Pamatdati</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Asset Classification</v>
+        <v>Asset Management</v>
       </c>
       <c r="B99" t="str">
-        <v>تصنيف الأصول</v>
+        <v>إدارة الأصول</v>
       </c>
       <c r="C99" t="str">
-        <v>Aktīvu klasifikācija</v>
+        <v>Aktīvu pārvaldība</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Asset Settings</v>
+        <v>Asset Inventory</v>
       </c>
       <c r="B100" t="str">
-        <v>إعدادات الأصول</v>
+        <v>جرد الأصول</v>
       </c>
       <c r="C100" t="str">
-        <v>Aktīvu iestatījumi</v>
+        <v>Aktīvu inventārs</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Risk Management</v>
+        <v>Asset Classification</v>
       </c>
       <c r="B101" t="str">
-        <v>إدارة المخاطر</v>
+        <v>تصنيف الأصول</v>
       </c>
       <c r="C101" t="str">
-        <v>Risku pārvaldība</v>
+        <v>Aktīvu klasifikācija</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Risk Dashboard</v>
+        <v>Asset Settings</v>
       </c>
       <c r="B102" t="str">
-        <v>لوحة تحكم المخاطر</v>
+        <v>إعدادات الأصول</v>
       </c>
       <c r="C102" t="str">
-        <v>Risku vadības panelis</v>
+        <v>Aktīvu iestatījumi</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Risk Register</v>
+        <v>Risk Management</v>
       </c>
       <c r="B103" t="str">
-        <v>سجل المخاطر</v>
+        <v>إدارة المخاطر</v>
       </c>
       <c r="C103" t="str">
-        <v>Risku reģistrs</v>
+        <v>Risku pārvaldība</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Risk Assessment</v>
+        <v>Risk Dashboard</v>
       </c>
       <c r="B104" t="str">
-        <v>تقييم المخاطر</v>
+        <v>لوحة تحكم المخاطر</v>
       </c>
       <c r="C104" t="str">
-        <v>Riska novērtējums</v>
+        <v>Risku vadības panelis</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Risk Response Strategy</v>
+        <v>Risk Register</v>
       </c>
       <c r="B105" t="str">
-        <v>استراتيجية الاستجابة للمخاطر</v>
+        <v>سجل المخاطر</v>
       </c>
       <c r="C105" t="str">
-        <v>Risku reaģēšanas stratēģija</v>
+        <v>Risku reģistrs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Risk Control Matrix</v>
+        <v>Risk Assessment</v>
       </c>
       <c r="B106" t="str">
-        <v>مصفوفة التحكم في المخاطر</v>
+        <v>تقييم المخاطر</v>
       </c>
       <c r="C106" t="str">
-        <v>Risku kontroles matrica</v>
+        <v>Riska novērtējums</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Risk Settings</v>
+        <v>Risk Response Strategy</v>
       </c>
       <c r="B107" t="str">
-        <v>إعدادات المخاطر</v>
+        <v>استراتيجية الاستجابة للمخاطر</v>
       </c>
       <c r="C107" t="str">
-        <v>Risku iestatījumi</v>
+        <v>Risku reaģēšanas stratēģija</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Internal Audit</v>
+        <v>Risk Control Matrix</v>
       </c>
       <c r="B108" t="str">
-        <v>التدقيق الداخلي</v>
+        <v>مصفوفة التحكم في المخاطر</v>
       </c>
       <c r="C108" t="str">
-        <v>Iekšējais audits</v>
+        <v>Risku kontroles matrica</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Audit Universe</v>
+        <v>Risk Settings</v>
       </c>
       <c r="B109" t="str">
-        <v>نطاق التدقيق</v>
+        <v>إعدادات المخاطر</v>
       </c>
       <c r="C109" t="str">
-        <v>Audita telpa</v>
+        <v>Risku iestatījumi</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Risk Identification</v>
+        <v>Internal Audit</v>
       </c>
       <c r="B110" t="str">
-        <v>تحديد المخاطر</v>
+        <v>التدقيق الداخلي</v>
       </c>
       <c r="C110" t="str">
-        <v>Risku identificēšana</v>
+        <v>Iekšējais audits</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Audit Planning</v>
+        <v>Audit Universe</v>
       </c>
       <c r="B111" t="str">
-        <v>تخطيط التدقيق</v>
+        <v>نطاق التدقيق</v>
       </c>
       <c r="C111" t="str">
-        <v>Audita plānošana</v>
+        <v>Audita telpa</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>FieldWork</v>
+        <v>Risk Identification</v>
       </c>
       <c r="B112" t="str">
-        <v>العمل الميداني</v>
+        <v>تحديد المخاطر</v>
       </c>
       <c r="C112" t="str">
-        <v>Lauka darbs</v>
+        <v>Risku identificēšana</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Report</v>
+        <v>Audit Planning</v>
       </c>
       <c r="B113" t="str">
-        <v>التقرير</v>
+        <v>تخطيط التدقيق</v>
       </c>
       <c r="C113" t="str">
-        <v>Atskaite</v>
+        <v>Audita plānošana</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>CAPA Tracking</v>
+        <v>FieldWork</v>
       </c>
       <c r="B114" t="str">
-        <v>تتبع الإجراءات التصحيحية</v>
+        <v>العمل الميداني</v>
       </c>
       <c r="C114" t="str">
-        <v>CAPA izsekošana</v>
+        <v>Lauka darbs</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Document Library</v>
+        <v>Report</v>
       </c>
       <c r="B115" t="str">
-        <v>مكتبة المستندات</v>
+        <v>التقرير</v>
       </c>
       <c r="C115" t="str">
-        <v>Dokumentu bibliotēka</v>
+        <v>Atskaite</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Risk Universe</v>
+        <v>CAPA Tracking</v>
       </c>
       <c r="B116" t="str">
-        <v>نطاق المخاطر</v>
+        <v>تتبع الإجراءات التصحيحية</v>
       </c>
       <c r="C116" t="str">
-        <v>Risku telpa</v>
+        <v>CAPA izsekošana</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Log Out</v>
+        <v>Document Library</v>
       </c>
       <c r="B117" t="str">
-        <v>تسجيل الخروج</v>
+        <v>مكتبة المستندات</v>
       </c>
       <c r="C117" t="str">
-        <v>Iziet</v>
+        <v>Dokumentu bibliotēka</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Welcome Back !</v>
+        <v>Risk Universe</v>
       </c>
       <c r="B118" t="str">
-        <v>مرحباً بعودتك!</v>
+        <v>نطاق المخاطر</v>
       </c>
       <c r="C118" t="str">
-        <v>Laipni lūdzam atpakaļ!</v>
+        <v>Risku telpa</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Log into your account</v>
+        <v>Log Out</v>
       </c>
       <c r="B119" t="str">
-        <v>تسجيل الدخول إلى حسابك</v>
+        <v>تسجيل الخروج</v>
       </c>
       <c r="C119" t="str">
-        <v>Piesakieties savā kontā</v>
+        <v>Iziet</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Username</v>
+        <v>Welcome Back !</v>
       </c>
       <c r="B120" t="str">
-        <v>اسم المستخدم</v>
+        <v>مرحباً بعودتك!</v>
       </c>
       <c r="C120" t="str">
-        <v>Lietotājvārds</v>
+        <v>Laipni lūdzam atpakaļ!</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Enter your username</v>
+        <v>Log into your account</v>
       </c>
       <c r="B121" t="str">
-        <v>أدخل اسم المستخدم</v>
+        <v>تسجيل الدخول إلى حسابك</v>
       </c>
       <c r="C121" t="str">
-        <v>Ievadiet lietotājvārdu</v>
+        <v>Piesakieties savā kontā</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Passcode</v>
+        <v>Username</v>
       </c>
       <c r="B122" t="str">
-        <v>رمز المرور</v>
+        <v>اسم المستخدم</v>
       </c>
       <c r="C122" t="str">
-        <v>Parole</v>
+        <v>Lietotājvārds</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Password</v>
+        <v>Enter your username</v>
       </c>
       <c r="B123" t="str">
-        <v>كلمة المرور</v>
+        <v>أدخل اسم المستخدم</v>
       </c>
       <c r="C123" t="str">
-        <v>Parole</v>
+        <v>Ievadiet lietotājvārdu</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Remember me</v>
+        <v>Passcode</v>
       </c>
       <c r="B124" t="str">
-        <v>تذكرني</v>
+        <v>رمز المرور</v>
       </c>
       <c r="C124" t="str">
-        <v>Atcerēties mani</v>
+        <v>Parole</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Forgot passcode?</v>
+        <v>Password</v>
       </c>
       <c r="B125" t="str">
-        <v>نسيت رمز المرور؟</v>
+        <v>كلمة المرور</v>
       </c>
       <c r="C125" t="str">
-        <v>Aizmirsāt paroli?</v>
+        <v>Parole</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Logging in...</v>
+        <v>Remember me</v>
       </c>
       <c r="B126" t="str">
-        <v>جاري تسجيل الدخول...</v>
+        <v>تذكرني</v>
       </c>
       <c r="C126" t="str">
-        <v>Piesakās...</v>
+        <v>Atcerēties mani</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Login</v>
+        <v>Forgot passcode?</v>
       </c>
       <c r="B127" t="str">
-        <v>تسجيل الدخول</v>
+        <v>نسيت رمز المرور؟</v>
       </c>
       <c r="C127" t="str">
-        <v>Pieteikties</v>
+        <v>Aizmirsāt paroli?</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Invalid username or password</v>
+        <v>Logging in...</v>
       </c>
       <c r="B128" t="str">
-        <v>اسم المستخدم أو كلمة المرور غير صحيحة</v>
+        <v>جاري تسجيل الدخول...</v>
       </c>
       <c r="C128" t="str">
-        <v>Nepareizs lietotājvārds vai parole</v>
+        <v>Piesakās...</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>An error occurred. Please try again.</v>
+        <v>Login</v>
       </c>
       <c r="B129" t="str">
-        <v>حدث خطأ. يرجى المحاولة مرة أخرى.</v>
+        <v>تسجيل الدخول</v>
       </c>
       <c r="C129" t="str">
-        <v>Radās kļūda. Lūdzu, mēģiniet vēlreiz.</v>
+        <v>Pieteikties</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Access Denied</v>
+        <v>Invalid username or password</v>
       </c>
       <c r="B130" t="str">
-        <v>الوصول مرفوض</v>
+        <v>اسم المستخدم أو كلمة المرور غير صحيحة</v>
       </c>
       <c r="C130" t="str">
-        <v>Piekļuve liegta</v>
+        <v>Nepareizs lietotājvārds vai parole</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>You don't have permission to access this page.</v>
+        <v>An error occurred. Please try again.</v>
       </c>
       <c r="B131" t="str">
-        <v>ليس لديك صلاحية للوصول إلى هذه الصفحة.</v>
+        <v>حدث خطأ. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C131" t="str">
-        <v>Jums nav atļaujas piekļūt šai lapai.</v>
+        <v>Radās kļūda. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Go Back</v>
+        <v>Access Denied</v>
       </c>
       <c r="B132" t="str">
-        <v>العودة</v>
+        <v>الوصول مرفوض</v>
       </c>
       <c r="C132" t="str">
-        <v>Atgriezties</v>
+        <v>Piekļuve liegta</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Go to Dashboard</v>
+        <v>You don't have permission to access this page.</v>
       </c>
       <c r="B133" t="str">
-        <v>الذهاب إلى لوحة التحكم</v>
+        <v>ليس لديك صلاحية للوصول إلى هذه الصفحة.</v>
       </c>
       <c r="C133" t="str">
-        <v>Doties uz vadības paneli</v>
+        <v>Jums nav atļaujas piekļūt šai lapai.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>You don't have permission to view this content.</v>
+        <v>Go Back</v>
       </c>
       <c r="B134" t="str">
-        <v>ليس لديك صلاحية لعرض هذا المحتوى.</v>
+        <v>العودة</v>
       </c>
       <c r="C134" t="str">
-        <v>Jums nav atļaujas skatīt šo saturu.</v>
+        <v>Atgriezties</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Organization Profile</v>
+        <v>Go to Dashboard</v>
       </c>
       <c r="B135" t="str">
-        <v>الملف التعريفي للمنظمة</v>
+        <v>الذهاب إلى لوحة التحكم</v>
       </c>
       <c r="C135" t="str">
-        <v>Organizācijas profils</v>
+        <v>Doties uz vadības paneli</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Company Information</v>
+        <v>You don't have permission to view this content.</v>
       </c>
       <c r="B136" t="str">
-        <v>معلومات الشركة</v>
+        <v>ليس لديك صلاحية لعرض هذا المحتوى.</v>
       </c>
       <c r="C136" t="str">
-        <v>Uzņēmuma informācija</v>
+        <v>Jums nav atļaujas skatīt šo saturu.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Company Name</v>
+        <v>Organization Profile</v>
       </c>
       <c r="B137" t="str">
-        <v>اسم الشركة</v>
+        <v>الملف التعريفي للمنظمة</v>
       </c>
       <c r="C137" t="str">
-        <v>Uzņēmuma nosaukums</v>
+        <v>Organizācijas profils</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Email</v>
+        <v>Company Information</v>
       </c>
       <c r="B138" t="str">
-        <v>البريد الإلكتروني</v>
+        <v>معلومات الشركة</v>
       </c>
       <c r="C138" t="str">
-        <v>E-pasts</v>
+        <v>Uzņēmuma informācija</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Phone</v>
+        <v>Company Name</v>
       </c>
       <c r="B139" t="str">
-        <v>الهاتف</v>
+        <v>اسم الشركة</v>
       </c>
       <c r="C139" t="str">
-        <v>Tālrunis</v>
+        <v>Uzņēmuma nosaukums</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Website</v>
+        <v>Email</v>
       </c>
       <c r="B140" t="str">
-        <v>الموقع الإلكتروني</v>
+        <v>البريد الإلكتروني</v>
       </c>
       <c r="C140" t="str">
-        <v>Tīmekļa vietne</v>
+        <v>E-pasts</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Established Date</v>
+        <v>Phone</v>
       </c>
       <c r="B141" t="str">
-        <v>تاريخ التأسيس</v>
+        <v>الهاتف</v>
       </c>
       <c r="C141" t="str">
-        <v>Dibināšanas datums</v>
+        <v>Tālrunis</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Employee Count</v>
+        <v>Website</v>
       </c>
       <c r="B142" t="str">
-        <v>عدد الموظفين</v>
+        <v>الموقع الإلكتروني</v>
       </c>
       <c r="C142" t="str">
-        <v>Darbinieku skaits</v>
+        <v>Tīmekļa vietne</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Branch Count</v>
+        <v>Established Date</v>
       </c>
       <c r="B143" t="str">
-        <v>عدد الفروع</v>
+        <v>تاريخ التأسيس</v>
       </c>
       <c r="C143" t="str">
-        <v>Filiāļu skaits</v>
+        <v>Dibināšanas datums</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Head Office</v>
+        <v>Employee Count</v>
       </c>
       <c r="B144" t="str">
-        <v>المقر الرئيسي</v>
+        <v>عدد الموظفين</v>
       </c>
       <c r="C144" t="str">
-        <v>Galvenais birojs</v>
+        <v>Darbinieku skaits</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Location</v>
+        <v>Branch Count</v>
       </c>
       <c r="B145" t="str">
-        <v>الموقع</v>
+        <v>عدد الفروع</v>
       </c>
       <c r="C145" t="str">
-        <v>Atrašanās vieta</v>
+        <v>Filiāļu skaits</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Address</v>
+        <v>Head Office</v>
       </c>
       <c r="B146" t="str">
-        <v>العنوان</v>
+        <v>المقر الرئيسي</v>
       </c>
       <c r="C146" t="str">
-        <v>Adrese</v>
+        <v>Galvenais birojs</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Vision</v>
+        <v>Location</v>
       </c>
       <c r="B147" t="str">
-        <v>الرؤية</v>
+        <v>الموقع</v>
       </c>
       <c r="C147" t="str">
-        <v>Vīzija</v>
+        <v>Atrašanās vieta</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Mission</v>
+        <v>Address</v>
       </c>
       <c r="B148" t="str">
-        <v>الرسالة</v>
+        <v>العنوان</v>
       </c>
       <c r="C148" t="str">
-        <v>Misija</v>
+        <v>Adrese</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Values</v>
+        <v>Vision</v>
       </c>
       <c r="B149" t="str">
-        <v>القيم</v>
+        <v>الرؤية</v>
       </c>
       <c r="C149" t="str">
-        <v>Vērtības</v>
+        <v>Vīzija</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>CEO Message</v>
+        <v>Mission</v>
       </c>
       <c r="B150" t="str">
-        <v>رسالة الرئيس التنفيذي</v>
+        <v>الرسالة</v>
       </c>
       <c r="C150" t="str">
-        <v>Izpilddirektora vēstījums</v>
+        <v>Misija</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Social Media</v>
+        <v>Values</v>
       </c>
       <c r="B151" t="str">
-        <v>وسائل التواصل الاجتماعي</v>
+        <v>القيم</v>
       </c>
       <c r="C151" t="str">
-        <v>Sociālie mediji</v>
+        <v>Vērtības</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Facebook</v>
+        <v>CEO Message</v>
       </c>
       <c r="B152" t="str">
-        <v>فيسبوك</v>
+        <v>رسالة الرئيس التنفيذي</v>
       </c>
       <c r="C152" t="str">
-        <v>Facebook</v>
+        <v>Izpilddirektora vēstījums</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Twitter</v>
+        <v>Social Media</v>
       </c>
       <c r="B153" t="str">
-        <v>تويتر</v>
+        <v>وسائل التواصل الاجتماعي</v>
       </c>
       <c r="C153" t="str">
-        <v>Twitter</v>
+        <v>Sociālie mediji</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>LinkedIn</v>
+        <v>Facebook</v>
       </c>
       <c r="B154" t="str">
-        <v>لينكد إن</v>
+        <v>فيسبوك</v>
       </c>
       <c r="C154" t="str">
-        <v>LinkedIn</v>
+        <v>Facebook</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>YouTube</v>
+        <v>Twitter</v>
       </c>
       <c r="B155" t="str">
-        <v>يوتيوب</v>
+        <v>تويتر</v>
       </c>
       <c r="C155" t="str">
-        <v>YouTube</v>
+        <v>Twitter</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Departments</v>
+        <v>LinkedIn</v>
       </c>
       <c r="B156" t="str">
-        <v>الأقسام</v>
+        <v>لينكد إن</v>
       </c>
       <c r="C156" t="str">
-        <v>Nodaļas</v>
+        <v>LinkedIn</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Add Department</v>
+        <v>YouTube</v>
       </c>
       <c r="B157" t="str">
-        <v>إضافة قسم</v>
+        <v>يوتيوب</v>
       </c>
       <c r="C157" t="str">
-        <v>Pievienot nodaļu</v>
+        <v>YouTube</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Department Name</v>
+        <v>Departments</v>
       </c>
       <c r="B158" t="str">
-        <v>اسم القسم</v>
+        <v>الأقسام</v>
       </c>
       <c r="C158" t="str">
-        <v>Nodaļas nosaukums</v>
+        <v>Nodaļas</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Services</v>
+        <v>Add Department</v>
       </c>
       <c r="B159" t="str">
-        <v>الخدمات</v>
+        <v>إضافة قسم</v>
       </c>
       <c r="C159" t="str">
-        <v>Pakalpojumi</v>
+        <v>Pievienot nodaļu</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Add Service</v>
+        <v>Department Name</v>
       </c>
       <c r="B160" t="str">
-        <v>إضافة خدمة</v>
+        <v>اسم القسم</v>
       </c>
       <c r="C160" t="str">
-        <v>Pievienot pakalpojumu</v>
+        <v>Nodaļas nosaukums</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Service Title</v>
+        <v>Services</v>
       </c>
       <c r="B161" t="str">
-        <v>عنوان الخدمة</v>
+        <v>الخدمات</v>
       </c>
       <c r="C161" t="str">
-        <v>Pakalpojuma nosaukums</v>
+        <v>Pakalpojumi</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Service User</v>
+        <v>Add Service</v>
       </c>
       <c r="B162" t="str">
-        <v>مستخدم الخدمة</v>
+        <v>إضافة خدمة</v>
       </c>
       <c r="C162" t="str">
-        <v>Pakalpojuma lietotājs</v>
+        <v>Pievienot pakalpojumu</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Service Category</v>
+        <v>Service Title</v>
       </c>
       <c r="B163" t="str">
-        <v>فئة الخدمة</v>
+        <v>عنوان الخدمة</v>
       </c>
       <c r="C163" t="str">
-        <v>Pakalpojuma kategorija</v>
+        <v>Pakalpojuma nosaukums</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Service Item</v>
+        <v>Service User</v>
       </c>
       <c r="B164" t="str">
-        <v>عنصر الخدمة</v>
+        <v>مستخدم الخدمة</v>
       </c>
       <c r="C164" t="str">
-        <v>Pakalpojuma vienums</v>
+        <v>Pakalpojuma lietotājs</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Regulations</v>
+        <v>Service Category</v>
       </c>
       <c r="B165" t="str">
-        <v>اللوائح</v>
+        <v>فئة الخدمة</v>
       </c>
       <c r="C165" t="str">
-        <v>Noteikumi</v>
+        <v>Pakalpojuma kategorija</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Add Regulation</v>
+        <v>Service Item</v>
       </c>
       <c r="B166" t="str">
-        <v>إضافة لائحة</v>
+        <v>عنصر الخدمة</v>
       </c>
       <c r="C166" t="str">
-        <v>Pievienot noteikumus</v>
+        <v>Pakalpojuma vienums</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Regulation Name</v>
+        <v>Regulations</v>
       </c>
       <c r="B167" t="str">
-        <v>اسم اللائحة</v>
+        <v>اللوائح</v>
       </c>
       <c r="C167" t="str">
-        <v>Noteikumu nosaukums</v>
+        <v>Noteikumi</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Version</v>
+        <v>Add Regulation</v>
       </c>
       <c r="B168" t="str">
-        <v>الإصدار</v>
+        <v>إضافة لائحة</v>
       </c>
       <c r="C168" t="str">
-        <v>Versija</v>
+        <v>Pievienot noteikumus</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Scope</v>
+        <v>Regulation Name</v>
       </c>
       <c r="B169" t="str">
-        <v>النطاق</v>
+        <v>اسم اللائحة</v>
       </c>
       <c r="C169" t="str">
-        <v>Tvērums</v>
+        <v>Noteikumu nosaukums</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Branches</v>
+        <v>Version</v>
       </c>
       <c r="B170" t="str">
-        <v>الفروع</v>
+        <v>الإصدار</v>
       </c>
       <c r="C170" t="str">
-        <v>Filiāles</v>
+        <v>Versija</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Add Branch</v>
+        <v>Scope</v>
       </c>
       <c r="B171" t="str">
-        <v>إضافة فرع</v>
+        <v>النطاق</v>
       </c>
       <c r="C171" t="str">
-        <v>Pievienot filiāli</v>
+        <v>Tvērums</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Data Centers</v>
+        <v>Branches</v>
       </c>
       <c r="B172" t="str">
-        <v>مراكز البيانات</v>
+        <v>الفروع</v>
       </c>
       <c r="C172" t="str">
-        <v>Datu centri</v>
+        <v>Filiāles</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Add Data Center</v>
+        <v>Add Branch</v>
       </c>
       <c r="B173" t="str">
-        <v>إضافة مركز بيانات</v>
+        <v>إضافة فرع</v>
       </c>
       <c r="C173" t="str">
-        <v>Pievienot datu centru</v>
+        <v>Pievienot filiāli</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Location Type</v>
+        <v>Data Centers</v>
       </c>
       <c r="B174" t="str">
-        <v>نوع الموقع</v>
+        <v>مراكز البيانات</v>
       </c>
       <c r="C174" t="str">
-        <v>Atrašanās vietas tips</v>
+        <v>Datu centri</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Vendor</v>
+        <v>Add Data Center</v>
       </c>
       <c r="B175" t="str">
-        <v>المورد</v>
+        <v>إضافة مركز بيانات</v>
       </c>
       <c r="C175" t="str">
-        <v>Piegādātājs</v>
+        <v>Pievienot datu centru</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Cloud Providers</v>
+        <v>Location Type</v>
       </c>
       <c r="B176" t="str">
-        <v>مزودو الخدمات السحابية</v>
+        <v>نوع الموقع</v>
       </c>
       <c r="C176" t="str">
-        <v>Mākoņpakalpojumu sniedzēji</v>
+        <v>Atrašanās vietas tips</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Add Cloud Provider</v>
+        <v>Vendor</v>
       </c>
       <c r="B177" t="str">
-        <v>إضافة مزود سحابي</v>
+        <v>المورد</v>
       </c>
       <c r="C177" t="str">
-        <v>Pievienot mākoņpakalpojumu sniedzēju</v>
+        <v>Piegādātājs</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Provider Name</v>
+        <v>Cloud Providers</v>
       </c>
       <c r="B178" t="str">
-        <v>اسم المزود</v>
+        <v>مزودو الخدمات السحابية</v>
       </c>
       <c r="C178" t="str">
-        <v>Pakalpojuma sniedzēja nosaukums</v>
+        <v>Mākoņpakalpojumu sniedzēji</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Service Type</v>
+        <v>Add Cloud Provider</v>
       </c>
       <c r="B179" t="str">
-        <v>نوع الخدمة</v>
+        <v>إضافة مزود سحابي</v>
       </c>
       <c r="C179" t="str">
-        <v>Pakalpojuma tips</v>
+        <v>Pievienot mākoņpakalpojumu sniedzēju</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Org Chart</v>
+        <v>Provider Name</v>
       </c>
       <c r="B180" t="str">
-        <v>الهيكل التنظيمي</v>
+        <v>اسم المزود</v>
       </c>
       <c r="C180" t="str">
-        <v>Organizācijas struktūra</v>
+        <v>Pakalpojuma sniedzēja nosaukums</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>No Profile Created</v>
+        <v>Service Type</v>
       </c>
       <c r="B181" t="str">
-        <v>لم يتم إنشاء ملف تعريفي</v>
+        <v>نوع الخدمة</v>
       </c>
       <c r="C181" t="str">
-        <v>Profils nav izveidots</v>
+        <v>Pakalpojuma tips</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Create your organization profile to get started.</v>
+        <v>Org Chart</v>
       </c>
       <c r="B182" t="str">
-        <v>قم بإنشاء الملف التعريفي للمنظمة للبدء.</v>
+        <v>الهيكل التنظيمي</v>
       </c>
       <c r="C182" t="str">
-        <v>Izveidojiet organizācijas profilu, lai sāktu.</v>
+        <v>Organizācijas struktūra</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Create Profile</v>
+        <v>No Profile Created</v>
       </c>
       <c r="B183" t="str">
-        <v>إنشاء ملف تعريفي</v>
+        <v>لم يتم إنشاء ملف تعريفي</v>
       </c>
       <c r="C183" t="str">
-        <v>Izveidot profilu</v>
+        <v>Profils nav izveidots</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Organization Information</v>
+        <v>Create your organization profile to get started.</v>
       </c>
       <c r="B184" t="str">
-        <v>معلومات المنظمة</v>
+        <v>قم بإنشاء الملف التعريفي للمنظمة للبدء.</v>
       </c>
       <c r="C184" t="str">
-        <v>Organizācijas informācija</v>
+        <v>Izveidojiet organizācijas profilu, lai sāktu.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Organization Name</v>
+        <v>Create Profile</v>
       </c>
       <c r="B185" t="str">
-        <v>اسم المنظمة</v>
+        <v>إنشاء ملف تعريفي</v>
       </c>
       <c r="C185" t="str">
-        <v>Organizācijas nosaukums</v>
+        <v>Izveidot profilu</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Head Office Location</v>
+        <v>Organization Information</v>
       </c>
       <c r="B186" t="str">
-        <v>موقع المقر الرئيسي</v>
+        <v>معلومات المنظمة</v>
       </c>
       <c r="C186" t="str">
-        <v>Galvenā biroja atrašanās vieta</v>
+        <v>Organizācijas informācija</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Head Office Address</v>
+        <v>Organization Name</v>
       </c>
       <c r="B187" t="str">
-        <v>عنوان المقر الرئيسي</v>
+        <v>اسم المنظمة</v>
       </c>
       <c r="C187" t="str">
-        <v>Galvenā biroja adrese</v>
+        <v>Organizācijas nosaukums</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>No Services</v>
+        <v>Head Office Location</v>
       </c>
       <c r="B188" t="str">
-        <v>لا توجد خدمات</v>
+        <v>موقع المقر الرئيسي</v>
       </c>
       <c r="C188" t="str">
-        <v>Nav pakalpojumu</v>
+        <v>Galvenā biroja atrašanās vieta</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Add services your organization provides.</v>
+        <v>Head Office Address</v>
       </c>
       <c r="B189" t="str">
-        <v>أضف الخدمات التي تقدمها منظمتك.</v>
+        <v>عنوان المقر الرئيسي</v>
       </c>
       <c r="C189" t="str">
-        <v>Pievienojiet organizācijas sniegtos pakalpojumus.</v>
+        <v>Galvenā biroja adrese</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>No Regulations</v>
+        <v>No Services</v>
       </c>
       <c r="B190" t="str">
-        <v>لا توجد لوائح</v>
+        <v>لا توجد خدمات</v>
       </c>
       <c r="C190" t="str">
-        <v>Nav noteikumu</v>
+        <v>Nav pakalpojumu</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Add regulations that apply to your organization.</v>
+        <v>Add services your organization provides.</v>
       </c>
       <c r="B191" t="str">
-        <v>أضف اللوائح التي تنطبق على منظمتك.</v>
+        <v>أضف الخدمات التي تقدمها منظمتك.</v>
       </c>
       <c r="C191" t="str">
-        <v>Pievienojiet organizācijai piemērojamos noteikumus.</v>
+        <v>Pievienojiet organizācijas sniegtos pakalpojumus.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>No Departments</v>
+        <v>No Regulations</v>
       </c>
       <c r="B192" t="str">
-        <v>لا توجد أقسام</v>
+        <v>لا توجد لوائح</v>
       </c>
       <c r="C192" t="str">
-        <v>Nav nodaļu</v>
+        <v>Nav noteikumu</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Add departments to organize your team structure.</v>
+        <v>Add regulations that apply to your organization.</v>
       </c>
       <c r="B193" t="str">
-        <v>أضف أقسام لتنظيم هيكل فريقك.</v>
+        <v>أضف اللوائح التي تنطبق على منظمتك.</v>
       </c>
       <c r="C193" t="str">
-        <v>Pievienojiet nodaļas, lai organizētu komandas struktūru.</v>
+        <v>Pievienojiet organizācijai piemērojamos noteikumus.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Organization Structure</v>
+        <v>No Departments</v>
       </c>
       <c r="B194" t="str">
-        <v>الهيكل التنظيمي</v>
+        <v>لا توجد أقسام</v>
       </c>
       <c r="C194" t="str">
-        <v>Organizācijas struktūra</v>
+        <v>Nav nodaļu</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Edit Department</v>
+        <v>Add departments to organize your team structure.</v>
       </c>
       <c r="B195" t="str">
-        <v>تعديل القسم</v>
+        <v>أضف أقسام لتنظيم هيكل فريقك.</v>
       </c>
       <c r="C195" t="str">
-        <v>Rediģēt nodaļu</v>
+        <v>Pievienojiet nodaļas, lai organizētu komandas struktūru.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Delete Department</v>
+        <v>Organization Structure</v>
       </c>
       <c r="B196" t="str">
-        <v>حذف القسم</v>
+        <v>الهيكل التنظيمي</v>
       </c>
       <c r="C196" t="str">
-        <v>Dzēst nodaļu</v>
+        <v>Organizācijas struktūra</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Are you sure you want to delete this department?</v>
+        <v>Edit Department</v>
       </c>
       <c r="B197" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذا القسم؟</v>
+        <v>تعديل القسم</v>
       </c>
       <c r="C197" t="str">
-        <v>Vai tiešām vēlaties dzēst šo nodaļu?</v>
+        <v>Rediģēt nodaļu</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Edit Service</v>
+        <v>Delete Department</v>
       </c>
       <c r="B198" t="str">
-        <v>تعديل الخدمة</v>
+        <v>حذف القسم</v>
       </c>
       <c r="C198" t="str">
-        <v>Rediģēt pakalpojumu</v>
+        <v>Dzēst nodaļu</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Delete Service</v>
+        <v>Are you sure you want to delete this department?</v>
       </c>
       <c r="B199" t="str">
-        <v>حذف الخدمة</v>
+        <v>هل أنت متأكد أنك تريد حذف هذا القسم؟</v>
       </c>
       <c r="C199" t="str">
-        <v>Dzēst pakalpojumu</v>
+        <v>Vai tiešām vēlaties dzēst šo nodaļu?</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Are you sure you want to delete this service?</v>
+        <v>Edit Service</v>
       </c>
       <c r="B200" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه الخدمة؟</v>
+        <v>تعديل الخدمة</v>
       </c>
       <c r="C200" t="str">
-        <v>Vai tiešām vēlaties dzēst šo pakalpojumu?</v>
+        <v>Rediģēt pakalpojumu</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Edit Regulation</v>
+        <v>Delete Service</v>
       </c>
       <c r="B201" t="str">
-        <v>تعديل اللائحة</v>
+        <v>حذف الخدمة</v>
       </c>
       <c r="C201" t="str">
-        <v>Rediģēt noteikumus</v>
+        <v>Dzēst pakalpojumu</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Unsubscribe from Regulation</v>
+        <v>Are you sure you want to delete this service?</v>
       </c>
       <c r="B202" t="str">
-        <v>إلغاء الاشتراك من اللائحة</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه الخدمة؟</v>
       </c>
       <c r="C202" t="str">
-        <v>Atteikties no noteikumiem</v>
+        <v>Vai tiešām vēlaties dzēst šo pakalpojumu?</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Are you sure you want to unsubscribe from this regulation?</v>
+        <v>Edit Regulation</v>
       </c>
       <c r="B203" t="str">
-        <v>هل أنت متأكد أنك تريد إلغاء الاشتراك من هذه اللائحة؟</v>
+        <v>تعديل اللائحة</v>
       </c>
       <c r="C203" t="str">
-        <v>Vai tiešām vēlaties atteikties no šiem noteikumiem?</v>
+        <v>Rediģēt noteikumus</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Unsubscribe</v>
+        <v>Unsubscribe from Regulation</v>
       </c>
       <c r="B204" t="str">
-        <v>إلغاء الاشتراك</v>
+        <v>إلغاء الاشتراك من اللائحة</v>
       </c>
       <c r="C204" t="str">
-        <v>Atteikties</v>
+        <v>Atteikties no noteikumiem</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Add Service Category</v>
+        <v>Are you sure you want to unsubscribe from this regulation?</v>
       </c>
       <c r="B205" t="str">
-        <v>إضافة فئة خدمة</v>
+        <v>هل أنت متأكد أنك تريد إلغاء الاشتراك من هذه اللائحة؟</v>
       </c>
       <c r="C205" t="str">
-        <v>Pievienot pakalpojuma kategoriju</v>
+        <v>Vai tiešām vēlaties atteikties no šiem noteikumiem?</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Category Name</v>
+        <v>Unsubscribe</v>
       </c>
       <c r="B206" t="str">
-        <v>اسم الفئة</v>
+        <v>إلغاء الاشتراك</v>
       </c>
       <c r="C206" t="str">
-        <v>Kategorijas nosaukums</v>
+        <v>Atteikties</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Add Service Item</v>
+        <v>Add Service Category</v>
       </c>
       <c r="B207" t="str">
-        <v>إضافة عنصر خدمة</v>
+        <v>إضافة فئة خدمة</v>
       </c>
       <c r="C207" t="str">
-        <v>Pievienot pakalpojuma vienumu</v>
+        <v>Pievienot pakalpojuma kategoriju</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Item Name</v>
+        <v>Category Name</v>
       </c>
       <c r="B208" t="str">
-        <v>اسم العنصر</v>
+        <v>اسم الفئة</v>
       </c>
       <c r="C208" t="str">
-        <v>Vienuma nosaukums</v>
+        <v>Kategorijas nosaukums</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>User Type</v>
+        <v>Add Service Item</v>
       </c>
       <c r="B209" t="str">
-        <v>نوع المستخدم</v>
+        <v>إضافة عنصر خدمة</v>
       </c>
       <c r="C209" t="str">
-        <v>Lietotāja tips</v>
+        <v>Pievienot pakalpojuma vienumu</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Category</v>
+        <v>Item Name</v>
       </c>
       <c r="B210" t="str">
-        <v>الفئة</v>
+        <v>اسم العنصر</v>
       </c>
       <c r="C210" t="str">
-        <v>Kategorija</v>
+        <v>Vienuma nosaukums</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Item</v>
+        <v>User Type</v>
       </c>
       <c r="B211" t="str">
-        <v>العنصر</v>
+        <v>نوع المستخدم</v>
       </c>
       <c r="C211" t="str">
-        <v>Vienums</v>
+        <v>Lietotāja tips</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Internal</v>
+        <v>Category</v>
       </c>
       <c r="B212" t="str">
-        <v>داخلي</v>
+        <v>الفئة</v>
       </c>
       <c r="C212" t="str">
-        <v>Iekšējs</v>
+        <v>Kategorija</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>External</v>
+        <v>Item</v>
       </c>
       <c r="B213" t="str">
-        <v>خارجي</v>
+        <v>العنصر</v>
       </c>
       <c r="C213" t="str">
-        <v>Ārējs</v>
+        <v>Vienums</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Public</v>
+        <v>Internal</v>
       </c>
       <c r="B214" t="str">
-        <v>عام</v>
+        <v>داخلي</v>
       </c>
       <c r="C214" t="str">
-        <v>Publisks</v>
+        <v>Iekšējs</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>SA1 Date</v>
+        <v>External</v>
       </c>
       <c r="B215" t="str">
-        <v>تاريخ SA1</v>
+        <v>خارجي</v>
       </c>
       <c r="C215" t="str">
-        <v>SA1 datums</v>
+        <v>Ārējs</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>SA2 Date</v>
+        <v>Public</v>
       </c>
       <c r="B216" t="str">
-        <v>تاريخ SA2</v>
+        <v>عام</v>
       </c>
       <c r="C216" t="str">
-        <v>SA2 datums</v>
+        <v>Publisks</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Exclusion and Justification</v>
+        <v>SA1 Date</v>
       </c>
       <c r="B217" t="str">
-        <v>الاستثناء والتبرير</v>
+        <v>تاريخ SA1</v>
       </c>
       <c r="C217" t="str">
-        <v>Izslēgšana un pamatojums</v>
+        <v>SA1 datums</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Document</v>
+        <v>SA2 Date</v>
       </c>
       <c r="B218" t="str">
-        <v>المستند</v>
+        <v>تاريخ SA2</v>
       </c>
       <c r="C218" t="str">
-        <v>Dokuments</v>
+        <v>SA2 datums</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Certificate</v>
+        <v>Exclusion and Justification</v>
       </c>
       <c r="B219" t="str">
-        <v>الشهادة</v>
+        <v>الاستثناء والتبرير</v>
       </c>
       <c r="C219" t="str">
-        <v>Sertifikāts</v>
+        <v>Izslēgšana un pamatojums</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Click to upload document</v>
+        <v>Document</v>
       </c>
       <c r="B220" t="str">
-        <v>انقر لتحميل المستند</v>
+        <v>المستند</v>
       </c>
       <c r="C220" t="str">
-        <v>Noklikšķiniet, lai augšupielādētu dokumentu</v>
+        <v>Dokuments</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Click to upload certificate</v>
+        <v>Certificate</v>
       </c>
       <c r="B221" t="str">
-        <v>انقر لتحميل الشهادة</v>
+        <v>الشهادة</v>
       </c>
       <c r="C221" t="str">
-        <v>Noklikšķiniet, lai augšupielādētu sertifikātu</v>
+        <v>Sertifikāts</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Replace</v>
+        <v>Click to upload document</v>
       </c>
       <c r="B222" t="str">
-        <v>استبدال</v>
+        <v>انقر لتحميل المستند</v>
       </c>
       <c r="C222" t="str">
-        <v>Aizstāt</v>
+        <v>Noklikšķiniet, lai augšupielādētu dokumentu</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Compliance Status</v>
+        <v>Click to upload certificate</v>
       </c>
       <c r="B223" t="str">
-        <v>حالة الامتثال</v>
+        <v>انقر لتحميل الشهادة</v>
       </c>
       <c r="C223" t="str">
-        <v>Atbilstības statuss</v>
+        <v>Noklikšķiniet, lai augšupielādētu sertifikātu</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Subscribed</v>
+        <v>Replace</v>
       </c>
       <c r="B224" t="str">
-        <v>مشترك</v>
+        <v>استبدال</v>
       </c>
       <c r="C224" t="str">
-        <v>Abonēts</v>
+        <v>Aizstāt</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading profile...</v>
+        <v>Compliance Status</v>
       </c>
       <c r="B225" t="str">
-        <v>جاري تحميل الملف...</v>
+        <v>حالة الامتثال</v>
       </c>
       <c r="C225" t="str">
-        <v>Ielādē profilu...</v>
+        <v>Atbilstības statuss</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Company Info</v>
+        <v>Subscribed</v>
       </c>
       <c r="B226" t="str">
-        <v>معلومات الشركة</v>
+        <v>مشترك</v>
       </c>
       <c r="C226" t="str">
-        <v>Uzņēmuma info</v>
+        <v>Abonēts</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Organization Chart</v>
+        <v>Loading profile...</v>
       </c>
       <c r="B227" t="str">
-        <v>الهيكل التنظيمي</v>
+        <v>جاري تحميل الملف...</v>
       </c>
       <c r="C227" t="str">
-        <v>Organizācijas shēma</v>
+        <v>Ielādē profilu...</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>No Profile</v>
+        <v>Company Info</v>
       </c>
       <c r="B228" t="str">
-        <v>لا يوجد ملف تعريفي</v>
+        <v>معلومات الشركة</v>
       </c>
       <c r="C228" t="str">
-        <v>Nav profila</v>
+        <v>Uzņēmuma info</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Enter department name</v>
+        <v>Organization Chart</v>
       </c>
       <c r="B229" t="str">
-        <v>أدخل اسم القسم</v>
+        <v>الهيكل التنظيمي</v>
       </c>
       <c r="C229" t="str">
-        <v>Ievadiet nodaļas nosaukumu</v>
+        <v>Organizācijas shēma</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Enter service title</v>
+        <v>No Profile</v>
       </c>
       <c r="B230" t="str">
-        <v>أدخل عنوان الخدمة</v>
+        <v>لا يوجد ملف تعريفي</v>
       </c>
       <c r="C230" t="str">
-        <v>Ievadiet pakalpojuma nosaukumu</v>
+        <v>Nav profila</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Enter service description</v>
+        <v>Enter department name</v>
       </c>
       <c r="B231" t="str">
-        <v>أدخل وصف الخدمة</v>
+        <v>أدخل اسم القسم</v>
       </c>
       <c r="C231" t="str">
-        <v>Ievadiet pakalpojuma aprakstu</v>
+        <v>Ievadiet nodaļas nosaukumu</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Select category</v>
+        <v>Enter service title</v>
       </c>
       <c r="B232" t="str">
-        <v>اختر الفئة</v>
+        <v>أدخل عنوان الخدمة</v>
       </c>
       <c r="C232" t="str">
-        <v>Izvēlieties kategoriju</v>
+        <v>Ievadiet pakalpojuma nosaukumu</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Select item</v>
+        <v>Enter service description</v>
       </c>
       <c r="B233" t="str">
-        <v>اختر العنصر</v>
+        <v>أدخل وصف الخدمة</v>
       </c>
       <c r="C233" t="str">
-        <v>Izvēlieties vienumu</v>
+        <v>Ievadiet pakalpojuma aprakstu</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Enter category name</v>
+        <v>Select category</v>
       </c>
       <c r="B234" t="str">
-        <v>أدخل اسم الفئة</v>
+        <v>اختر الفئة</v>
       </c>
       <c r="C234" t="str">
-        <v>Ievadiet kategorijas nosaukumu</v>
+        <v>Izvēlieties kategoriju</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Enter item name</v>
+        <v>Select item</v>
       </c>
       <c r="B235" t="str">
-        <v>أدخل اسم العنصر</v>
+        <v>اختر العنصر</v>
       </c>
       <c r="C235" t="str">
-        <v>Ievadiet vienuma nosaukumu</v>
+        <v>Izvēlieties vienumu</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Enter regulation name</v>
+        <v>Enter category name</v>
       </c>
       <c r="B236" t="str">
-        <v>أدخل اسم اللائحة</v>
+        <v>أدخل اسم الفئة</v>
       </c>
       <c r="C236" t="str">
-        <v>Ievadiet noteikumu nosaukumu</v>
+        <v>Ievadiet kategorijas nosaukumu</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Enter version</v>
+        <v>Enter item name</v>
       </c>
       <c r="B237" t="str">
-        <v>أدخل الإصدار</v>
+        <v>أدخل اسم العنصر</v>
       </c>
       <c r="C237" t="str">
-        <v>Ievadiet versiju</v>
+        <v>Ievadiet vienuma nosaukumu</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Select SA1 date</v>
+        <v>Enter regulation name</v>
       </c>
       <c r="B238" t="str">
-        <v>اختر تاريخ SA1</v>
+        <v>أدخل اسم اللائحة</v>
       </c>
       <c r="C238" t="str">
-        <v>Izvēlieties SA1 datumu</v>
+        <v>Ievadiet noteikumu nosaukumu</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Select SA2 date</v>
+        <v>Enter version</v>
       </c>
       <c r="B239" t="str">
-        <v>اختر تاريخ SA2</v>
+        <v>أدخل الإصدار</v>
       </c>
       <c r="C239" t="str">
-        <v>Izvēlieties SA2 datumu</v>
+        <v>Ievadiet versiju</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Enter scope</v>
+        <v>Select SA1 date</v>
       </c>
       <c r="B240" t="str">
-        <v>أدخل النطاق</v>
+        <v>اختر تاريخ SA1</v>
       </c>
       <c r="C240" t="str">
-        <v>Ievadiet tvērumu</v>
+        <v>Izvēlieties SA1 datumu</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Enter exclusion and justification</v>
+        <v>Select SA2 date</v>
       </c>
       <c r="B241" t="str">
-        <v>أدخل الاستثناء والتبرير</v>
+        <v>اختر تاريخ SA2</v>
       </c>
       <c r="C241" t="str">
-        <v>Ievadiet izslēgšanu un pamatojumu</v>
+        <v>Izvēlieties SA2 datumu</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Search departments...</v>
+        <v>Enter scope</v>
       </c>
       <c r="B242" t="str">
-        <v>البحث في الأقسام...</v>
+        <v>أدخل النطاق</v>
       </c>
       <c r="C242" t="str">
-        <v>Meklēt nodaļas...</v>
+        <v>Ievadiet tvērumu</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Search regulations...</v>
+        <v>Enter exclusion and justification</v>
       </c>
       <c r="B243" t="str">
-        <v>البحث في اللوائح...</v>
+        <v>أدخل الاستثناء والتبرير</v>
       </c>
       <c r="C243" t="str">
-        <v>Meklēt noteikumus...</v>
+        <v>Ievadiet izslēgšanu un pamatojumu</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Are you sure you want to delete this department? This action cannot be undone.</v>
+        <v>Search departments...</v>
       </c>
       <c r="B244" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذا القسم؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>البحث في الأقسام...</v>
       </c>
       <c r="C244" t="str">
-        <v>Vai tiešām vēlaties dzēst šo nodaļu? Šo darbību nevar atsaukt.</v>
+        <v>Meklēt nodaļas...</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Are you sure you want to delete this service? This action cannot be undone.</v>
+        <v>Search regulations...</v>
       </c>
       <c r="B245" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه الخدمة؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>البحث في اللوائح...</v>
       </c>
       <c r="C245" t="str">
-        <v>Vai tiešām vēlaties dzēst šo pakalpojumu? Šo darbību nevar atsaukt.</v>
+        <v>Meklēt noteikumus...</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Are you sure you want to unsubscribe from this regulation? This action cannot be undone.</v>
+        <v>Are you sure you want to delete this department? This action cannot be undone.</v>
       </c>
       <c r="B246" t="str">
-        <v>هل أنت متأكد أنك تريد إلغاء الاشتراك من هذه اللائحة؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>هل أنت متأكد أنك تريد حذف هذا القسم؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C246" t="str">
-        <v>Vai tiešām vēlaties atteikties no šiem noteikumiem? Šo darbību nevar atsaukt.</v>
+        <v>Vai tiešām vēlaties dzēst šo nodaļu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Stakeholder</v>
+        <v>Are you sure you want to delete this service? This action cannot be undone.</v>
       </c>
       <c r="B247" t="str">
-        <v>صاحب المصلحة</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه الخدمة؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C247" t="str">
-        <v>Ieinteresētā puse</v>
+        <v>Vai tiešām vēlaties dzēst šo pakalpojumu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Stakeholders</v>
+        <v>Are you sure you want to unsubscribe from this regulation? This action cannot be undone.</v>
       </c>
       <c r="B248" t="str">
-        <v>أصحاب المصلحة</v>
+        <v>هل أنت متأكد أنك تريد إلغاء الاشتراك من هذه اللائحة؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C248" t="str">
-        <v>Ieinteresētās puses</v>
+        <v>Vai tiešām vēlaties atteikties no šiem noteikumiem? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Add Stakeholder</v>
+        <v>Stakeholder</v>
       </c>
       <c r="B249" t="str">
-        <v>إضافة صاحب مصلحة</v>
+        <v>صاحب المصلحة</v>
       </c>
       <c r="C249" t="str">
-        <v>Pievienot ieinteresēto pusi</v>
+        <v>Ieinteresētā puse</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Stakeholder Name</v>
+        <v>Stakeholders</v>
       </c>
       <c r="B250" t="str">
-        <v>اسم صاحب المصلحة</v>
+        <v>أصحاب المصلحة</v>
       </c>
       <c r="C250" t="str">
-        <v>Ieinteresētās puses nosaukums</v>
+        <v>Ieinteresētās puses</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Stakeholder Type</v>
+        <v>Add Stakeholder</v>
       </c>
       <c r="B251" t="str">
-        <v>نوع صاحب المصلحة</v>
+        <v>إضافة صاحب مصلحة</v>
       </c>
       <c r="C251" t="str">
-        <v>Ieinteresētās puses tips</v>
+        <v>Pievienot ieinteresēto pusi</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Third Party</v>
+        <v>Stakeholder Name</v>
       </c>
       <c r="B252" t="str">
-        <v>طرف ثالث</v>
+        <v>اسم صاحب المصلحة</v>
       </c>
       <c r="C252" t="str">
-        <v>Trešā puse</v>
+        <v>Ieinteresētās puses nosaukums</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Department</v>
+        <v>Stakeholder Type</v>
       </c>
       <c r="B253" t="str">
-        <v>القسم</v>
+        <v>نوع صاحب المصلحة</v>
       </c>
       <c r="C253" t="str">
-        <v>Nodaļa</v>
+        <v>Ieinteresētās puses tips</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Issues</v>
+        <v>Third Party</v>
       </c>
       <c r="B254" t="str">
-        <v>القضايا</v>
+        <v>طرف ثالث</v>
       </c>
       <c r="C254" t="str">
-        <v>Problēmas</v>
+        <v>Trešā puse</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Issue List</v>
+        <v>Department</v>
       </c>
       <c r="B255" t="str">
-        <v>قائمة القضايا</v>
+        <v>القسم</v>
       </c>
       <c r="C255" t="str">
-        <v>Problēmu saraksts</v>
+        <v>Nodaļa</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Add Issue</v>
+        <v>Issues</v>
       </c>
       <c r="B256" t="str">
-        <v>إضافة قضية</v>
+        <v>القضايا</v>
       </c>
       <c r="C256" t="str">
-        <v>Pievienot problēmu</v>
+        <v>Problēmas</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Issue Title</v>
+        <v>Issue List</v>
       </c>
       <c r="B257" t="str">
-        <v>عنوان القضية</v>
+        <v>قائمة القضايا</v>
       </c>
       <c r="C257" t="str">
-        <v>Problēmas nosaukums</v>
+        <v>Problēmu saraksts</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Domain</v>
+        <v>Add Issue</v>
       </c>
       <c r="B258" t="str">
-        <v>المجال</v>
+        <v>إضافة قضية</v>
       </c>
       <c r="C258" t="str">
-        <v>Domēns</v>
+        <v>Pievienot problēmu</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Issue Type</v>
+        <v>Issue Title</v>
       </c>
       <c r="B259" t="str">
-        <v>نوع القضية</v>
+        <v>عنوان القضية</v>
       </c>
       <c r="C259" t="str">
-        <v>Problēmas tips</v>
+        <v>Problēmas nosaukums</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Owner</v>
+        <v>Domain</v>
       </c>
       <c r="B260" t="str">
-        <v>المالك</v>
+        <v>المجال</v>
       </c>
       <c r="C260" t="str">
-        <v>Īpašnieks</v>
+        <v>Domēns</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Due Date</v>
+        <v>Issue Type</v>
       </c>
       <c r="B261" t="str">
-        <v>تاريخ الاستحقاق</v>
+        <v>نوع القضية</v>
       </c>
       <c r="C261" t="str">
-        <v>Izpildes termiņš</v>
+        <v>Problēmas tips</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Related Regulations</v>
+        <v>Owner</v>
       </c>
       <c r="B262" t="str">
-        <v>اللوائح ذات الصلة</v>
+        <v>المالك</v>
       </c>
       <c r="C262" t="str">
-        <v>Saistītie noteikumi</v>
+        <v>Īpašnieks</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Related Processes</v>
+        <v>Due Date</v>
       </c>
       <c r="B263" t="str">
-        <v>العمليات ذات الصلة</v>
+        <v>تاريخ الاستحقاق</v>
       </c>
       <c r="C263" t="str">
-        <v>Saistītie procesi</v>
+        <v>Izpildes termiņš</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Related Stakeholders</v>
+        <v>Related Regulations</v>
       </c>
       <c r="B264" t="str">
-        <v>أصحاب المصلحة ذوي الصلة</v>
+        <v>اللوائح ذات الصلة</v>
       </c>
       <c r="C264" t="str">
-        <v>Saistītās ieinteresētās puses</v>
+        <v>Saistītie noteikumi</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Needs &amp; Expectations</v>
+        <v>Related Processes</v>
       </c>
       <c r="B265" t="str">
-        <v>الاحتياجات والتوقعات</v>
+        <v>العمليات ذات الصلة</v>
       </c>
       <c r="C265" t="str">
-        <v>Vajadzības un gaidas</v>
+        <v>Saistītie procesi</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Preventive</v>
+        <v>Related Stakeholders</v>
       </c>
       <c r="B266" t="str">
-        <v>وقائي</v>
+        <v>أصحاب المصلحة ذوي الصلة</v>
       </c>
       <c r="C266" t="str">
-        <v>Preventīvs</v>
+        <v>Saistītās ieinteresētās puses</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Corrective</v>
+        <v>Needs &amp; Expectations</v>
       </c>
       <c r="B267" t="str">
-        <v>تصحيحي</v>
+        <v>الاحتياجات والتوقعات</v>
       </c>
       <c r="C267" t="str">
-        <v>Korektīvs</v>
+        <v>Vajadzības un gaidas</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Resolved</v>
+        <v>Preventive</v>
       </c>
       <c r="B268" t="str">
-        <v>تم الحل</v>
+        <v>وقائي</v>
       </c>
       <c r="C268" t="str">
-        <v>Atrisināts</v>
+        <v>Preventīvs</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Sent Back</v>
+        <v>Corrective</v>
       </c>
       <c r="B269" t="str">
-        <v>تم الإرجاع</v>
+        <v>تصحيحي</v>
       </c>
       <c r="C269" t="str">
-        <v>Nosūtīts atpakaļ</v>
+        <v>Korektīvs</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Add User</v>
+        <v>Resolved</v>
       </c>
       <c r="B270" t="str">
-        <v>إضافة مستخدم</v>
+        <v>تم الحل</v>
       </c>
       <c r="C270" t="str">
-        <v>Pievienot lietotāju</v>
+        <v>Atrisināts</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Full Name</v>
+        <v>Sent Back</v>
       </c>
       <c r="B271" t="str">
-        <v>الاسم الكامل</v>
+        <v>تم الإرجاع</v>
       </c>
       <c r="C271" t="str">
-        <v>Pilns vārds</v>
+        <v>Nosūtīts atpakaļ</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>First Name</v>
+        <v>Add User</v>
       </c>
       <c r="B272" t="str">
-        <v>الاسم الأول</v>
+        <v>إضافة مستخدم</v>
       </c>
       <c r="C272" t="str">
-        <v>Vārds</v>
+        <v>Pievienot lietotāju</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Last Name</v>
+        <v>Full Name</v>
       </c>
       <c r="B273" t="str">
-        <v>اسم العائلة</v>
+        <v>الاسم الكامل</v>
       </c>
       <c r="C273" t="str">
-        <v>Uzvārds</v>
+        <v>Pilns vārds</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Designation</v>
+        <v>First Name</v>
       </c>
       <c r="B274" t="str">
-        <v>المسمى الوظيفي</v>
+        <v>الاسم الأول</v>
       </c>
       <c r="C274" t="str">
-        <v>Amats</v>
+        <v>Vārds</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Function</v>
+        <v>Last Name</v>
       </c>
       <c r="B275" t="str">
-        <v>الوظيفة</v>
+        <v>اسم العائلة</v>
       </c>
       <c r="C275" t="str">
-        <v>Funkcija</v>
+        <v>Uzvārds</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Role</v>
+        <v>Designation</v>
       </c>
       <c r="B276" t="str">
-        <v>الدور</v>
+        <v>المسمى الوظيفي</v>
       </c>
       <c r="C276" t="str">
-        <v>Loma</v>
+        <v>Amats</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Roles</v>
+        <v>Function</v>
       </c>
       <c r="B277" t="str">
-        <v>الأدوار</v>
+        <v>الوظيفة</v>
       </c>
       <c r="C277" t="str">
-        <v>Lomas</v>
+        <v>Funkcija</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Is Active</v>
+        <v>Role</v>
       </c>
       <c r="B278" t="str">
-        <v>نشط</v>
+        <v>الدور</v>
       </c>
       <c r="C278" t="str">
-        <v>Ir aktīvs</v>
+        <v>Loma</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Is Blocked</v>
+        <v>Roles</v>
       </c>
       <c r="B279" t="str">
-        <v>محظور</v>
+        <v>الأدوار</v>
       </c>
       <c r="C279" t="str">
-        <v>Ir bloķēts</v>
+        <v>Lomas</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Last Login</v>
+        <v>Is Active</v>
       </c>
       <c r="B280" t="str">
-        <v>آخر تسجيل دخول</v>
+        <v>نشط</v>
       </c>
       <c r="C280" t="str">
-        <v>Pēdējā pieteikšanās</v>
+        <v>Ir aktīvs</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Created At</v>
+        <v>Is Blocked</v>
       </c>
       <c r="B281" t="str">
-        <v>تاريخ الإنشاء</v>
+        <v>محظور</v>
       </c>
       <c r="C281" t="str">
-        <v>Izveidots</v>
+        <v>Ir bloķēts</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Confirm Password</v>
+        <v>Last Login</v>
       </c>
       <c r="B282" t="str">
-        <v>تأكيد كلمة المرور</v>
+        <v>آخر تسجيل دخول</v>
       </c>
       <c r="C282" t="str">
-        <v>Apstiprināt paroli</v>
+        <v>Pēdējā pieteikšanās</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Change Password</v>
+        <v>Created At</v>
       </c>
       <c r="B283" t="str">
-        <v>تغيير كلمة المرور</v>
+        <v>تاريخ الإنشاء</v>
       </c>
       <c r="C283" t="str">
-        <v>Mainīt paroli</v>
+        <v>Izveidots</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Business</v>
+        <v>Confirm Password</v>
       </c>
       <c r="B284" t="str">
-        <v>الأعمال</v>
+        <v>تأكيد كلمة المرور</v>
       </c>
       <c r="C284" t="str">
-        <v>Bizness</v>
+        <v>Apstiprināt paroli</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Security</v>
+        <v>Change Password</v>
       </c>
       <c r="B285" t="str">
-        <v>الأمان</v>
+        <v>تغيير كلمة المرور</v>
       </c>
       <c r="C285" t="str">
-        <v>Drošība</v>
+        <v>Mainīt paroli</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Audit</v>
+        <v>Business</v>
       </c>
       <c r="B286" t="str">
-        <v>التدقيق</v>
+        <v>الأعمال</v>
       </c>
       <c r="C286" t="str">
-        <v>Audits</v>
+        <v>Bizness</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Account Overview</v>
+        <v>Security</v>
       </c>
       <c r="B287" t="str">
-        <v>نظرة عامة على الحساب</v>
+        <v>الأمان</v>
       </c>
       <c r="C287" t="str">
-        <v>Konta pārskats</v>
+        <v>Drošība</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>User Management</v>
+        <v>Audit</v>
       </c>
       <c r="B288" t="str">
-        <v>إدارة المستخدمين</v>
+        <v>التدقيق</v>
       </c>
       <c r="C288" t="str">
-        <v>Lietotāju pārvaldība</v>
+        <v>Audits</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>New Account</v>
+        <v>Account Overview</v>
       </c>
       <c r="B289" t="str">
-        <v>حساب جديد</v>
+        <v>نظرة عامة على الحساب</v>
       </c>
       <c r="C289" t="str">
-        <v>Jauns konts</v>
+        <v>Konta pārskats</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Edit Account</v>
+        <v>User Management</v>
       </c>
       <c r="B290" t="str">
-        <v>تعديل الحساب</v>
+        <v>إدارة المستخدمين</v>
       </c>
       <c r="C290" t="str">
-        <v>Rediģēt kontu</v>
+        <v>Lietotāju pārvaldība</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Import Users</v>
+        <v>New Account</v>
       </c>
       <c r="B291" t="str">
-        <v>استيراد المستخدمين</v>
+        <v>حساب جديد</v>
       </c>
       <c r="C291" t="str">
-        <v>Importēt lietotājus</v>
+        <v>Jauns konts</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Search by Department Name</v>
+        <v>Edit Account</v>
       </c>
       <c r="B292" t="str">
-        <v>البحث باسم القسم</v>
+        <v>تعديل الحساب</v>
       </c>
       <c r="C292" t="str">
-        <v>Meklēt pēc nodaļas nosaukuma</v>
+        <v>Rediģēt kontu</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Search user...</v>
+        <v>Import Users</v>
       </c>
       <c r="B293" t="str">
-        <v>البحث عن مستخدم...</v>
+        <v>استيراد المستخدمين</v>
       </c>
       <c r="C293" t="str">
-        <v>Meklēt lietotāju...</v>
+        <v>Importēt lietotājus</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>All Roles</v>
+        <v>Search by Department Name</v>
       </c>
       <c r="B294" t="str">
-        <v>جميع الأدوار</v>
+        <v>البحث باسم القسم</v>
       </c>
       <c r="C294" t="str">
-        <v>Visas lomas</v>
+        <v>Meklēt pēc nodaļas nosaukuma</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>All Departments</v>
+        <v>Search user...</v>
       </c>
       <c r="B295" t="str">
-        <v>جميع الأقسام</v>
+        <v>البحث عن مستخدم...</v>
       </c>
       <c r="C295" t="str">
-        <v>Visas nodaļas</v>
+        <v>Meklēt lietotāju...</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Account Credentials</v>
+        <v>All Roles</v>
       </c>
       <c r="B296" t="str">
-        <v>بيانات اعتماد الحساب</v>
+        <v>جميع الأدوار</v>
       </c>
       <c r="C296" t="str">
-        <v>Konta akreditācijas dati</v>
+        <v>Visas lomas</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Personal Information</v>
+        <v>All Departments</v>
       </c>
       <c r="B297" t="str">
-        <v>المعلومات الشخصية</v>
+        <v>جميع الأقسام</v>
       </c>
       <c r="C297" t="str">
-        <v>Personīgā informācija</v>
+        <v>Visas nodaļas</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Organization &amp; Role</v>
+        <v>Account Credentials</v>
       </c>
       <c r="B298" t="str">
-        <v>المنظمة والدور</v>
+        <v>بيانات اعتماد الحساب</v>
       </c>
       <c r="C298" t="str">
-        <v>Organizācija un loma</v>
+        <v>Konta akreditācijas dati</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Preferences</v>
+        <v>Personal Information</v>
       </c>
       <c r="B299" t="str">
-        <v>التفضيلات</v>
+        <v>المعلومات الشخصية</v>
       </c>
       <c r="C299" t="str">
-        <v>Preferences</v>
+        <v>Personīgā informācija</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Account Status</v>
+        <v>Organization &amp; Role</v>
       </c>
       <c r="B300" t="str">
-        <v>حالة الحساب</v>
+        <v>المنظمة والدور</v>
       </c>
       <c r="C300" t="str">
-        <v>Konta statuss</v>
+        <v>Organizācija un loma</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>User ID</v>
+        <v>Preferences</v>
       </c>
       <c r="B301" t="str">
-        <v>معرف المستخدم</v>
+        <v>التفضيلات</v>
       </c>
       <c r="C301" t="str">
-        <v>Lietotāja ID</v>
+        <v>Preferences</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>User Name</v>
+        <v>Account Status</v>
       </c>
       <c r="B302" t="str">
-        <v>اسم المستخدم</v>
+        <v>حالة الحساب</v>
       </c>
       <c r="C302" t="str">
-        <v>Lietotājvārds</v>
+        <v>Konta statuss</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Enter username</v>
+        <v>User ID</v>
       </c>
       <c r="B303" t="str">
-        <v>أدخل اسم المستخدم</v>
+        <v>معرف المستخدم</v>
       </c>
       <c r="C303" t="str">
-        <v>Ievadiet lietotājvārdu</v>
+        <v>Lietotāja ID</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Enter email</v>
+        <v>User Name</v>
       </c>
       <c r="B304" t="str">
-        <v>أدخل البريد الإلكتروني</v>
+        <v>اسم المستخدم</v>
       </c>
       <c r="C304" t="str">
-        <v>Ievadiet e-pastu</v>
+        <v>Lietotājvārds</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Enter password</v>
+        <v>Enter username</v>
       </c>
       <c r="B305" t="str">
-        <v>أدخل كلمة المرور</v>
+        <v>أدخل اسم المستخدم</v>
       </c>
       <c r="C305" t="str">
-        <v>Ievadiet paroli</v>
+        <v>Ievadiet lietotājvārdu</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Confirm password</v>
+        <v>Enter email</v>
       </c>
       <c r="B306" t="str">
-        <v>تأكيد كلمة المرور</v>
+        <v>أدخل البريد الإلكتروني</v>
       </c>
       <c r="C306" t="str">
-        <v>Apstipriniet paroli</v>
+        <v>Ievadiet e-pastu</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Enter first name</v>
+        <v>Enter password</v>
       </c>
       <c r="B307" t="str">
-        <v>أدخل الاسم الأول</v>
+        <v>أدخل كلمة المرور</v>
       </c>
       <c r="C307" t="str">
-        <v>Ievadiet vārdu</v>
+        <v>Ievadiet paroli</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Enter last name</v>
+        <v>Confirm password</v>
       </c>
       <c r="B308" t="str">
-        <v>أدخل اسم العائلة</v>
+        <v>تأكيد كلمة المرور</v>
       </c>
       <c r="C308" t="str">
-        <v>Ievadiet uzvārdu</v>
+        <v>Apstipriniet paroli</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Enter full name</v>
+        <v>Enter first name</v>
       </c>
       <c r="B309" t="str">
-        <v>أدخل الاسم الكامل</v>
+        <v>أدخل الاسم الأول</v>
       </c>
       <c r="C309" t="str">
-        <v>Ievadiet pilnu vārdu</v>
+        <v>Ievadiet vārdu</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Enter designation</v>
+        <v>Enter last name</v>
       </c>
       <c r="B310" t="str">
-        <v>أدخل المسمى الوظيفي</v>
+        <v>أدخل اسم العائلة</v>
       </c>
       <c r="C310" t="str">
-        <v>Ievadiet amatu</v>
+        <v>Ievadiet uzvārdu</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Select function</v>
+        <v>Enter full name</v>
       </c>
       <c r="B311" t="str">
-        <v>اختر الوظيفة</v>
+        <v>أدخل الاسم الكامل</v>
       </c>
       <c r="C311" t="str">
-        <v>Izvēlieties funkciju</v>
+        <v>Ievadiet pilnu vārdu</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Select function first</v>
+        <v>Enter designation</v>
       </c>
       <c r="B312" t="str">
-        <v>اختر الوظيفة أولاً</v>
+        <v>أدخل المسمى الوظيفي</v>
       </c>
       <c r="C312" t="str">
-        <v>Vispirms izvēlieties funkciju</v>
+        <v>Ievadiet amatu</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Please select a function first</v>
+        <v>Select function</v>
       </c>
       <c r="B313" t="str">
-        <v>يرجى اختيار الوظيفة أولاً</v>
+        <v>اختر الوظيفة</v>
       </c>
       <c r="C313" t="str">
-        <v>Lūdzu, vispirms izvēlieties funkciju</v>
+        <v>Izvēlieties funkciju</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Select role</v>
+        <v>Select function first</v>
       </c>
       <c r="B314" t="str">
-        <v>اختر الدور</v>
+        <v>اختر الوظيفة أولاً</v>
       </c>
       <c r="C314" t="str">
-        <v>Izvēlieties lomu</v>
+        <v>Vispirms izvēlieties funkciju</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select department</v>
+        <v>Please select a function first</v>
       </c>
       <c r="B315" t="str">
-        <v>اختر القسم</v>
+        <v>يرجى اختيار الوظيفة أولاً</v>
       </c>
       <c r="C315" t="str">
-        <v>Izvēlieties nodaļu</v>
+        <v>Lūdzu, vispirms izvēlieties funkciju</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Reporting Manager</v>
+        <v>Select role</v>
       </c>
       <c r="B316" t="str">
-        <v>المدير المباشر</v>
+        <v>اختر الدور</v>
       </c>
       <c r="C316" t="str">
-        <v>Ziņojošais vadītājs</v>
+        <v>Izvēlieties lomu</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Select reporting manager</v>
+        <v>Select department</v>
       </c>
       <c r="B317" t="str">
-        <v>اختر المدير المباشر</v>
+        <v>اختر القسم</v>
       </c>
       <c r="C317" t="str">
-        <v>Izvēlieties ziņojošo vadītāju</v>
+        <v>Izvēlieties nodaļu</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Language</v>
+        <v>Reporting Manager</v>
       </c>
       <c r="B318" t="str">
-        <v>اللغة</v>
+        <v>المدير المباشر</v>
       </c>
       <c r="C318" t="str">
-        <v>Valoda</v>
+        <v>Ziņojošais vadītājs</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Select language</v>
+        <v>Select reporting manager</v>
       </c>
       <c r="B319" t="str">
-        <v>اختر اللغة</v>
+        <v>اختر المدير المباشر</v>
       </c>
       <c r="C319" t="str">
-        <v>Izvēlieties valodu</v>
+        <v>Izvēlieties ziņojošo vadītāju</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Time Zone</v>
+        <v>Language</v>
       </c>
       <c r="B320" t="str">
-        <v>المنطقة الزمنية</v>
+        <v>اللغة</v>
       </c>
       <c r="C320" t="str">
-        <v>Laika zona</v>
+        <v>Valoda</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Select timezone</v>
+        <v>Select language</v>
       </c>
       <c r="B321" t="str">
-        <v>اختر المنطقة الزمنية</v>
+        <v>اختر اللغة</v>
       </c>
       <c r="C321" t="str">
-        <v>Izvēlieties laika zonu</v>
+        <v>Izvēlieties valodu</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blocked</v>
+        <v>Time Zone</v>
       </c>
       <c r="B322" t="str">
-        <v>محظور</v>
+        <v>المنطقة الزمنية</v>
       </c>
       <c r="C322" t="str">
-        <v>Bloķēts</v>
+        <v>Laika zona</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Is local user</v>
+        <v>Select timezone</v>
       </c>
       <c r="B323" t="str">
-        <v>مستخدم محلي</v>
+        <v>اختر المنطقة الزمنية</v>
       </c>
       <c r="C323" t="str">
-        <v>Ir vietējais lietotājs</v>
+        <v>Izvēlieties laika zonu</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>User Role</v>
+        <v>Blocked</v>
       </c>
       <c r="B324" t="str">
-        <v>دور المستخدم</v>
+        <v>محظور</v>
       </c>
       <c r="C324" t="str">
-        <v>Lietotāja loma</v>
+        <v>Bloķēts</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Select Designation</v>
+        <v>Is local user</v>
       </c>
       <c r="B325" t="str">
-        <v>اختر المسمى الوظيفي</v>
+        <v>مستخدم محلي</v>
       </c>
       <c r="C325" t="str">
-        <v>Izvēlieties amatu</v>
+        <v>Ir vietējais lietotājs</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Analyst</v>
+        <v>User Role</v>
       </c>
       <c r="B326" t="str">
-        <v>محلل</v>
+        <v>دور المستخدم</v>
       </c>
       <c r="C326" t="str">
-        <v>Analītiķis</v>
+        <v>Lietotāja loma</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Developer</v>
+        <v>Select Designation</v>
       </c>
       <c r="B327" t="str">
-        <v>مطور</v>
+        <v>اختر المسمى الوظيفي</v>
       </c>
       <c r="C327" t="str">
-        <v>Izstrādātājs</v>
+        <v>Izvēlieties amatu</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Financial Analyst</v>
+        <v>Analyst</v>
       </c>
       <c r="B328" t="str">
-        <v>محلل مالي</v>
+        <v>محلل</v>
       </c>
       <c r="C328" t="str">
-        <v>Finanšu analītiķis</v>
+        <v>Analītiķis</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>HR Manager</v>
+        <v>Developer</v>
       </c>
       <c r="B329" t="str">
-        <v>مدير الموارد البشرية</v>
+        <v>مطور</v>
       </c>
       <c r="C329" t="str">
-        <v>Personāla vadītājs</v>
+        <v>Izstrādātājs</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Manager</v>
+        <v>Financial Analyst</v>
       </c>
       <c r="B330" t="str">
-        <v>مدير</v>
+        <v>محلل مالي</v>
       </c>
       <c r="C330" t="str">
-        <v>Vadītājs</v>
+        <v>Finanšu analītiķis</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Marketing Specialist</v>
+        <v>HR Manager</v>
       </c>
       <c r="B331" t="str">
-        <v>أخصائي تسويق</v>
+        <v>مدير الموارد البشرية</v>
       </c>
       <c r="C331" t="str">
-        <v>Mārketinga speciālists</v>
+        <v>Personāla vadītājs</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Operations Executive</v>
+        <v>Manager</v>
       </c>
       <c r="B332" t="str">
-        <v>تنفيذي العمليات</v>
+        <v>مدير</v>
       </c>
       <c r="C332" t="str">
-        <v>Operāciju vadītājs</v>
+        <v>Vadītājs</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Senior Manager</v>
+        <v>Marketing Specialist</v>
       </c>
       <c r="B333" t="str">
-        <v>مدير أول</v>
+        <v>أخصائي تسويق</v>
       </c>
       <c r="C333" t="str">
-        <v>Vecākais vadītājs</v>
+        <v>Mārketinga speciālists</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Software Engineer</v>
+        <v>Operations Executive</v>
       </c>
       <c r="B334" t="str">
-        <v>مهندس برمجيات</v>
+        <v>تنفيذي العمليات</v>
       </c>
       <c r="C334" t="str">
-        <v>Programmatūras inženieris</v>
+        <v>Operāciju vadītājs</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Team Lead</v>
+        <v>Senior Manager</v>
       </c>
       <c r="B335" t="str">
-        <v>قائد الفريق</v>
+        <v>مدير أول</v>
       </c>
       <c r="C335" t="str">
-        <v>Komandas vadītājs</v>
+        <v>Vecākais vadītājs</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>View Details</v>
+        <v>Software Engineer</v>
       </c>
       <c r="B336" t="str">
-        <v>عرض التفاصيل</v>
+        <v>مهندس برمجيات</v>
       </c>
       <c r="C336" t="str">
-        <v>Skatīt detaļas</v>
+        <v>Programmatūras inženieris</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Reset Password</v>
+        <v>Team Lead</v>
       </c>
       <c r="B337" t="str">
-        <v>إعادة تعيين كلمة المرور</v>
+        <v>قائد الفريق</v>
       </c>
       <c r="C337" t="str">
-        <v>Atiestatīt paroli</v>
+        <v>Komandas vadītājs</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Deactivate</v>
+        <v>View Details</v>
       </c>
       <c r="B338" t="str">
-        <v>إلغاء التفعيل</v>
+        <v>عرض التفاصيل</v>
       </c>
       <c r="C338" t="str">
-        <v>Deaktivizēt</v>
+        <v>Skatīt detaļas</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Download Template</v>
+        <v>Reset Password</v>
       </c>
       <c r="B339" t="str">
-        <v>تحميل القالب</v>
+        <v>إعادة تعيين كلمة المرور</v>
       </c>
       <c r="C339" t="str">
-        <v>Lejupielādēt veidni</v>
+        <v>Atiestatīt paroli</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Importing...</v>
+        <v>Deactivate</v>
       </c>
       <c r="B340" t="str">
-        <v>جاري الاستيراد...</v>
+        <v>إلغاء التفعيل</v>
       </c>
       <c r="C340" t="str">
-        <v>Importē...</v>
+        <v>Deaktivizēt</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Changing...</v>
+        <v>Download Template</v>
       </c>
       <c r="B341" t="str">
-        <v>جاري التغيير...</v>
+        <v>تحميل القالب</v>
       </c>
       <c r="C341" t="str">
-        <v>Maina...</v>
+        <v>Lejupielādēt veidni</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>New Password</v>
+        <v>Importing...</v>
       </c>
       <c r="B342" t="str">
-        <v>كلمة المرور الجديدة</v>
+        <v>جاري الاستيراد...</v>
       </c>
       <c r="C342" t="str">
-        <v>Jaunā parole</v>
+        <v>Importē...</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Enter new password</v>
+        <v>Changing...</v>
       </c>
       <c r="B343" t="str">
-        <v>أدخل كلمة المرور الجديدة</v>
+        <v>جاري التغيير...</v>
       </c>
       <c r="C343" t="str">
-        <v>Ievadiet jauno paroli</v>
+        <v>Maina...</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Confirm new password</v>
+        <v>New Password</v>
       </c>
       <c r="B344" t="str">
-        <v>تأكيد كلمة المرور الجديدة</v>
+        <v>كلمة المرور الجديدة</v>
       </c>
       <c r="C344" t="str">
-        <v>Apstipriniet jauno paroli</v>
+        <v>Jaunā parole</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Enter a new password for</v>
+        <v>Enter new password</v>
       </c>
       <c r="B345" t="str">
-        <v>أدخل كلمة مرور جديدة لـ</v>
+        <v>أدخل كلمة المرور الجديدة</v>
       </c>
       <c r="C345" t="str">
-        <v>Ievadiet jaunu paroli lietotājam</v>
+        <v>Ievadiet jauno paroli</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>No users in this department</v>
+        <v>Confirm new password</v>
       </c>
       <c r="B346" t="str">
-        <v>لا يوجد مستخدمون في هذا القسم</v>
+        <v>تأكيد كلمة المرور الجديدة</v>
       </c>
       <c r="C346" t="str">
-        <v>Šajā nodaļā nav lietotāju</v>
+        <v>Apstipriniet jauno paroli</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>users</v>
+        <v>Enter a new password for</v>
       </c>
       <c r="B347" t="str">
-        <v>مستخدمون</v>
+        <v>أدخل كلمة مرور جديدة لـ</v>
       </c>
       <c r="C347" t="str">
-        <v>lietotāji</v>
+        <v>Ievadiet jaunu paroli lietotājam</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please fill in all required fields</v>
+        <v>No users in this department</v>
       </c>
       <c r="B348" t="str">
-        <v>يرجى ملء جميع الحقول المطلوبة</v>
+        <v>لا يوجد مستخدمون في هذا القسم</v>
       </c>
       <c r="C348" t="str">
-        <v>Lūdzu, aizpildiet visus obligātos laukus</v>
+        <v>Šajā nodaļā nav lietotāju</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Failed to create user</v>
+        <v>users</v>
       </c>
       <c r="B349" t="str">
-        <v>فشل في إنشاء المستخدم</v>
+        <v>مستخدمون</v>
       </c>
       <c r="C349" t="str">
-        <v>Neizdevās izveidot lietotāju</v>
+        <v>lietotāji</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Please enter a new password</v>
+        <v>Please fill in all required fields</v>
       </c>
       <c r="B350" t="str">
-        <v>يرجى إدخال كلمة مرور جديدة</v>
+        <v>يرجى ملء جميع الحقول المطلوبة</v>
       </c>
       <c r="C350" t="str">
-        <v>Lūdzu, ievadiet jaunu paroli</v>
+        <v>Lūdzu, aizpildiet visus obligātos laukus</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Password changed successfully</v>
+        <v>Failed to create user</v>
       </c>
       <c r="B351" t="str">
-        <v>تم تغيير كلمة المرور بنجاح</v>
+        <v>فشل في إنشاء المستخدم</v>
       </c>
       <c r="C351" t="str">
-        <v>Parole veiksmīgi nomainīta</v>
+        <v>Neizdevās izveidot lietotāju</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Failed to change password</v>
+        <v>Please enter a new password</v>
       </c>
       <c r="B352" t="str">
-        <v>فشل في تغيير كلمة المرور</v>
+        <v>يرجى إدخال كلمة مرور جديدة</v>
       </c>
       <c r="C352" t="str">
-        <v>Neizdevās nomainīt paroli</v>
+        <v>Lūdzu, ievadiet jaunu paroli</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Import completed:</v>
+        <v>Password changed successfully</v>
       </c>
       <c r="B353" t="str">
-        <v>اكتمل الاستيراد:</v>
+        <v>تم تغيير كلمة المرور بنجاح</v>
       </c>
       <c r="C353" t="str">
-        <v>Imports pabeigts:</v>
+        <v>Parole veiksmīgi nomainīta</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>users imported,</v>
+        <v>Failed to change password</v>
       </c>
       <c r="B354" t="str">
-        <v>مستخدم تم استيرادهم،</v>
+        <v>فشل في تغيير كلمة المرور</v>
       </c>
       <c r="C354" t="str">
-        <v>lietotāji importēti,</v>
+        <v>Neizdevās nomainīt paroli</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>errors</v>
+        <v>Import completed:</v>
       </c>
       <c r="B355" t="str">
-        <v>أخطاء</v>
+        <v>اكتمل الاستيراد:</v>
       </c>
       <c r="C355" t="str">
-        <v>kļūdas</v>
+        <v>Imports pabeigts:</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Failed to import users. Please check the file format.</v>
+        <v>users imported,</v>
       </c>
       <c r="B356" t="str">
-        <v>فشل في استيراد المستخدمين. يرجى التحقق من تنسيق الملف.</v>
+        <v>مستخدم تم استيرادهم،</v>
       </c>
       <c r="C356" t="str">
-        <v>Neizdevās importēt lietotājus. Lūdzu, pārbaudiet faila formātu.</v>
+        <v>lietotāji importēti,</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Designation Name</v>
+        <v>errors</v>
       </c>
       <c r="B357" t="str">
-        <v>اسم المسمى الوظيفي</v>
+        <v>أخطاء</v>
       </c>
       <c r="C357" t="str">
-        <v>Amata nosaukums</v>
+        <v>kļūdas</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Email ID</v>
+        <v>Failed to import users. Please check the file format.</v>
       </c>
       <c r="B358" t="str">
-        <v>معرف البريد الإلكتروني</v>
+        <v>فشل في استيراد المستخدمين. يرجى التحقق من تنسيق الملف.</v>
       </c>
       <c r="C358" t="str">
-        <v>E-pasta ID</v>
+        <v>Neizdevās importēt lietotājus. Lūdzu, pārbaudiet faila formātu.</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Add New</v>
+        <v>Designation Name</v>
       </c>
       <c r="B359" t="str">
-        <v>إضافة جديد</v>
+        <v>اسم المسمى الوظيفي</v>
       </c>
       <c r="C359" t="str">
-        <v>Pievienot jaunu</v>
+        <v>Amata nosaukums</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>File</v>
+        <v>Email ID</v>
       </c>
       <c r="B360" t="str">
-        <v>ملف</v>
+        <v>معرف البريد الإلكتروني</v>
       </c>
       <c r="C360" t="str">
-        <v>Fails</v>
+        <v>E-pasta ID</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Selected:</v>
+        <v>Add New</v>
       </c>
       <c r="B361" t="str">
-        <v>المحدد:</v>
+        <v>إضافة جديد</v>
       </c>
       <c r="C361" t="str">
-        <v>Izvēlēts:</v>
+        <v>Pievienot jaunu</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Search users...</v>
+        <v>File</v>
       </c>
       <c r="B362" t="str">
-        <v>البحث في المستخدمين...</v>
+        <v>ملف</v>
       </c>
       <c r="C362" t="str">
-        <v>Meklēt lietotājus...</v>
+        <v>Fails</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>English</v>
+        <v>Selected:</v>
       </c>
       <c r="B363" t="str">
-        <v>الإنجليزية</v>
+        <v>المحدد:</v>
       </c>
       <c r="C363" t="str">
-        <v>Angļu</v>
+        <v>Izvēlēts:</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Arabic</v>
+        <v>Search users...</v>
       </c>
       <c r="B364" t="str">
-        <v>العربية</v>
+        <v>البحث في المستخدمين...</v>
       </c>
       <c r="C364" t="str">
-        <v>Arābu</v>
+        <v>Meklēt lietotājus...</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Hindi</v>
+        <v>English</v>
       </c>
       <c r="B365" t="str">
-        <v>الهندية</v>
+        <v>الإنجليزية</v>
       </c>
       <c r="C365" t="str">
-        <v>Hindi</v>
+        <v>Angļu</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Latvian</v>
+        <v>Arabic</v>
       </c>
       <c r="B366" t="str">
-        <v>اللاتفية</v>
+        <v>العربية</v>
       </c>
       <c r="C366" t="str">
-        <v>Latviešu</v>
+        <v>Arābu</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Select...</v>
+        <v>Hindi</v>
       </c>
       <c r="B367" t="str">
-        <v>اختر...</v>
+        <v>الهندية</v>
       </c>
       <c r="C367" t="str">
-        <v>Izvēlieties...</v>
+        <v>Hindi</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Download the template file and fill in your data</v>
+        <v>Latvian</v>
       </c>
       <c r="B368" t="str">
-        <v>قم بتحميل ملف القالب وملء بياناتك</v>
+        <v>اللاتفية</v>
       </c>
       <c r="C368" t="str">
-        <v>Lejupielādējiet veidnes failu un aizpildiet savus datus</v>
+        <v>Latviešu</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Import users from a CSV file. The file should have columns: Username, Email, Password, First Name, Last Name, Full Name, Designation, Function, Role, Department, Language, Timezone.</v>
+        <v>Select...</v>
       </c>
       <c r="B369" t="str">
-        <v>استيراد المستخدمين من ملف CSV. يجب أن يحتوي الملف على أعمدة: اسم المستخدم، البريد الإلكتروني، كلمة المرور، الاسم الأول، اسم العائلة، الاسم الكامل، المسمى الوظيفي، الوظيفة، الدور، القسم، اللغة، المنطقة الزمنية.</v>
+        <v>اختر...</v>
       </c>
       <c r="C369" t="str">
-        <v>Importējiet lietotājus no CSV faila. Failam jābūt ar kolonnām: Lietotājvārds, E-pasts, Parole, Vārds, Uzvārds, Pilns vārds, Amats, Funkcija, Loma, Nodaļa, Valoda, Laika zona.</v>
+        <v>Izvēlieties...</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Processes</v>
+        <v>Download the template file and fill in your data</v>
       </c>
       <c r="B370" t="str">
-        <v>العمليات</v>
+        <v>قم بتحميل ملف القالب وملء بياناتك</v>
       </c>
       <c r="C370" t="str">
-        <v>Procesi</v>
+        <v>Lejupielādējiet veidnes failu un aizpildiet savus datus</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Add Process</v>
+        <v>Import users from a CSV file. The file should have columns: Username, Email, Password, First Name, Last Name, Full Name, Designation, Function, Role, Department, Language, Timezone.</v>
       </c>
       <c r="B371" t="str">
-        <v>إضافة عملية</v>
+        <v>استيراد المستخدمين من ملف CSV. يجب أن يحتوي الملف على أعمدة: اسم المستخدم، البريد الإلكتروني، كلمة المرور، الاسم الأول، اسم العائلة، الاسم الكامل، المسمى الوظيفي، الوظيفة، الدور، القسم، اللغة، المنطقة الزمنية.</v>
       </c>
       <c r="C371" t="str">
-        <v>Pievienot procesu</v>
+        <v>Importējiet lietotājus no CSV faila. Failam jābūt ar kolonnām: Lietotājvārds, E-pasts, Parole, Vārds, Uzvārds, Pilns vārds, Amats, Funkcija, Loma, Nodaļa, Valoda, Laika zona.</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Process Code</v>
+        <v>View Mode</v>
       </c>
       <c r="B372" t="str">
-        <v>رمز العملية</v>
+        <v>وضع العرض</v>
       </c>
       <c r="C372" t="str">
-        <v>Procesa kods</v>
+        <v>Skata režīms</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Process Name</v>
+        <v>Role-wise Chart</v>
       </c>
       <c r="B373" t="str">
-        <v>اسم العملية</v>
+        <v>مخطط حسب الدور</v>
       </c>
       <c r="C373" t="str">
-        <v>Procesa nosaukums</v>
+        <v>Lomu diagramma</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Process Owner</v>
+        <v>Department-wise Chart</v>
       </c>
       <c r="B374" t="str">
-        <v>مالك العملية</v>
+        <v>مخطط حسب القسم</v>
       </c>
       <c r="C374" t="str">
-        <v>Procesa īpašnieks</v>
+        <v>Nodaļu diagramma</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Process Type</v>
+        <v>Loading organization chart...</v>
       </c>
       <c r="B375" t="str">
-        <v>نوع العملية</v>
+        <v>جاري تحميل الهيكل التنظيمي...</v>
       </c>
       <c r="C375" t="str">
-        <v>Procesa tips</v>
+        <v>Ielādē organizācijas shēmu...</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Core</v>
+        <v>No users found. Add users and assign reporting managers to build the organization chart.</v>
       </c>
       <c r="B376" t="str">
-        <v>أساسي</v>
+        <v>لم يتم العثور على مستخدمين. أضف مستخدمين وعيّن مدراء للتقارير لبناء الهيكل التنظيمي.</v>
       </c>
       <c r="C376" t="str">
-        <v>Pamata</v>
+        <v>Nav atrasts neviens lietotājs. Pievienojiet lietotājus un piešķiriet vadītājus, lai izveidotu organizācijas shēmu.</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Support</v>
+        <v>No users found in</v>
       </c>
       <c r="B377" t="str">
-        <v>دعم</v>
+        <v>لم يتم العثور على مستخدمين في</v>
       </c>
       <c r="C377" t="str">
-        <v>Atbalsta</v>
+        <v>Nav atrasts neviens lietotājs</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Management</v>
+        <v>selected department</v>
       </c>
       <c r="B378" t="str">
-        <v>إدارة</v>
+        <v>القسم المحدد</v>
       </c>
       <c r="C378" t="str">
-        <v>Vadības</v>
+        <v>izvēlētajā nodaļā</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Frequency</v>
+        <v>Assign users to this department to see the hierarchy.</v>
       </c>
       <c r="B379" t="str">
-        <v>التكرار</v>
+        <v>عيّن مستخدمين لهذا القسم لرؤية التسلسل الهرمي.</v>
       </c>
       <c r="C379" t="str">
-        <v>Biežums</v>
+        <v>Piešķiriet lietotājus šai nodaļai, lai redzētu hierarhiju.</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Daily</v>
+        <v>Select a department to view its hierarchy.</v>
       </c>
       <c r="B380" t="str">
-        <v>يومي</v>
+        <v>حدد قسماً لعرض تسلسله الهرمي.</v>
       </c>
       <c r="C380" t="str">
-        <v>Ikdienas</v>
+        <v>Izvēlieties nodaļu, lai skatītu tās hierarhiju.</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Weekly</v>
+        <v>No organization hierarchy defined. Assign reporting managers to users to build the chart.</v>
       </c>
       <c r="B381" t="str">
-        <v>أسبوعي</v>
+        <v>لم يتم تحديد تسلسل هرمي للمنظمة. عيّن مدراء للتقارير للمستخدمين لبناء المخطط.</v>
       </c>
       <c r="C381" t="str">
-        <v>Iknedēļas</v>
+        <v>Nav definēta organizācijas hierarhija. Piešķiriet vadītājus lietotājiem, lai izveidotu shēmu.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Monthly</v>
+        <v>Processes</v>
       </c>
       <c r="B382" t="str">
-        <v>شهري</v>
+        <v>العمليات</v>
       </c>
       <c r="C382" t="str">
-        <v>Ikmēneša</v>
+        <v>Procesi</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Quarterly</v>
+        <v>Add Process</v>
       </c>
       <c r="B383" t="str">
-        <v>ربع سنوي</v>
+        <v>إضافة عملية</v>
       </c>
       <c r="C383" t="str">
-        <v>Ceturkšņa</v>
+        <v>Pievienot procesu</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Annually</v>
+        <v>Process Code</v>
       </c>
       <c r="B384" t="str">
-        <v>سنوي</v>
+        <v>رمز العملية</v>
       </c>
       <c r="C384" t="str">
-        <v>Ikgadējs</v>
+        <v>Procesa kods</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>As Needed</v>
+        <v>Process Name</v>
       </c>
       <c r="B385" t="str">
-        <v>حسب الحاجة</v>
+        <v>اسم العملية</v>
       </c>
       <c r="C385" t="str">
-        <v>Pēc vajadzības</v>
+        <v>Procesa nosaukums</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Responsible</v>
+        <v>Process Owner</v>
       </c>
       <c r="B386" t="str">
-        <v>المسؤول</v>
+        <v>مالك العملية</v>
       </c>
       <c r="C386" t="str">
-        <v>Atbildīgais</v>
+        <v>Procesa īpašnieks</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Accountable</v>
+        <v>Process Type</v>
       </c>
       <c r="B387" t="str">
-        <v>المحاسب</v>
+        <v>نوع العملية</v>
       </c>
       <c r="C387" t="str">
-        <v>Uzraugošais</v>
+        <v>Procesa tips</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Consulted</v>
+        <v>Core</v>
       </c>
       <c r="B388" t="str">
-        <v>المستشار</v>
+        <v>أساسي</v>
       </c>
       <c r="C388" t="str">
-        <v>Konsultējamais</v>
+        <v>Pamata</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Informed</v>
+        <v>Support</v>
       </c>
       <c r="B389" t="str">
-        <v>المُبلَّغ</v>
+        <v>دعم</v>
       </c>
       <c r="C389" t="str">
-        <v>Informējamais</v>
+        <v>Atbalsta</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Business Impact Analysis</v>
+        <v>Management</v>
       </c>
       <c r="B390" t="str">
-        <v>تحليل تأثير الأعمال</v>
+        <v>إدارة</v>
       </c>
       <c r="C390" t="str">
-        <v>Biznesa ietekmes analīze</v>
+        <v>Vadības</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Add BIA</v>
+        <v>Frequency</v>
       </c>
       <c r="B391" t="str">
-        <v>إضافة تحليل تأثير</v>
+        <v>التكرار</v>
       </c>
       <c r="C391" t="str">
-        <v>Pievienot BIA</v>
+        <v>Biežums</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Criticality</v>
+        <v>Daily</v>
       </c>
       <c r="B392" t="str">
-        <v>الأهمية</v>
+        <v>يومي</v>
       </c>
       <c r="C392" t="str">
-        <v>Kritiskums</v>
+        <v>Ikdienas</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Critical</v>
+        <v>Weekly</v>
       </c>
       <c r="B393" t="str">
-        <v>حرج</v>
+        <v>أسبوعي</v>
       </c>
       <c r="C393" t="str">
-        <v>Kritisks</v>
+        <v>Iknedēļas</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>High</v>
+        <v>Monthly</v>
       </c>
       <c r="B394" t="str">
-        <v>عالي</v>
+        <v>شهري</v>
       </c>
       <c r="C394" t="str">
-        <v>Augsts</v>
+        <v>Ikmēneša</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Medium</v>
+        <v>Quarterly</v>
       </c>
       <c r="B395" t="str">
-        <v>متوسط</v>
+        <v>ربع سنوي</v>
       </c>
       <c r="C395" t="str">
-        <v>Vidējs</v>
+        <v>Ceturkšņa</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Low</v>
+        <v>Annually</v>
       </c>
       <c r="B396" t="str">
-        <v>منخفض</v>
+        <v>سنوي</v>
       </c>
       <c r="C396" t="str">
-        <v>Zems</v>
+        <v>Ikgadējs</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>RTO (Recovery Time Objective)</v>
+        <v>As Needed</v>
       </c>
       <c r="B397" t="str">
-        <v>هدف وقت الاستعادة</v>
+        <v>حسب الحاجة</v>
       </c>
       <c r="C397" t="str">
-        <v>RTO (Atjaunošanas laika mērķis)</v>
+        <v>Pēc vajadzības</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>RPO (Recovery Point Objective)</v>
+        <v>Responsible</v>
       </c>
       <c r="B398" t="str">
-        <v>هدف نقطة الاستعادة</v>
+        <v>المسؤول</v>
       </c>
       <c r="C398" t="str">
-        <v>RPO (Atjaunošanas punkta mērķis)</v>
+        <v>Atbildīgais</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>MTPD (Maximum Tolerable Period of Disruption)</v>
+        <v>Accountable</v>
       </c>
       <c r="B399" t="str">
-        <v>أقصى فترة تعطل مقبولة</v>
+        <v>المحاسب</v>
       </c>
       <c r="C399" t="str">
-        <v>MTPD (Maksimālais pieļaujamais pārtraukuma periods)</v>
+        <v>Uzraugošais</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Dependencies</v>
+        <v>Consulted</v>
       </c>
       <c r="B400" t="str">
-        <v>التبعيات</v>
+        <v>المستشار</v>
       </c>
       <c r="C400" t="str">
-        <v>Atkarības</v>
+        <v>Konsultējamais</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Resources</v>
+        <v>Informed</v>
       </c>
       <c r="B401" t="str">
-        <v>الموارد</v>
+        <v>المُبلَّغ</v>
       </c>
       <c r="C401" t="str">
-        <v>Resursi</v>
+        <v>Informējamais</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Impact Analysis</v>
+        <v>Business Impact Analysis</v>
       </c>
       <c r="B402" t="str">
-        <v>تحليل التأثير</v>
+        <v>تحليل تأثير الأعمال</v>
       </c>
       <c r="C402" t="str">
-        <v>Ietekmes analīze</v>
+        <v>Biznesa ietekmes analīze</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Search by control code or name...</v>
+        <v>Add BIA</v>
       </c>
       <c r="B403" t="str">
-        <v>البحث برمز الضابطة أو الاسم...</v>
+        <v>إضافة تحليل تأثير</v>
       </c>
       <c r="C403" t="str">
-        <v>Meklēt pēc kontroles koda vai nosaukuma...</v>
+        <v>Pievienot BIA</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Integrated Framework</v>
+        <v>Criticality</v>
       </c>
       <c r="B404" t="str">
-        <v>الإطار المتكامل</v>
+        <v>الأهمية</v>
       </c>
       <c r="C404" t="str">
-        <v>Integrētais ietvars</v>
+        <v>Kritiskums</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>All Frameworks</v>
+        <v>Critical</v>
       </c>
       <c r="B405" t="str">
-        <v>جميع الأطر</v>
+        <v>حرج</v>
       </c>
       <c r="C405" t="str">
-        <v>Visi ietvari</v>
+        <v>Kritisks</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Delete All</v>
+        <v>High</v>
       </c>
       <c r="B406" t="str">
-        <v>حذف الكل</v>
+        <v>عالي</v>
       </c>
       <c r="C406" t="str">
-        <v>Dzēst visu</v>
+        <v>Augsts</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>New Control</v>
+        <v>Medium</v>
       </c>
       <c r="B407" t="str">
-        <v>ضابطة جديدة</v>
+        <v>متوسط</v>
       </c>
       <c r="C407" t="str">
-        <v>Jauna kontrole</v>
+        <v>Vidējs</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Control Name</v>
+        <v>Low</v>
       </c>
       <c r="B408" t="str">
-        <v>اسم الضابطة</v>
+        <v>منخفض</v>
       </c>
       <c r="C408" t="str">
-        <v>Kontroles nosaukums</v>
+        <v>Zems</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Control Code</v>
+        <v>RTO (Recovery Time Objective)</v>
       </c>
       <c r="B409" t="str">
-        <v>رمز الضابطة</v>
+        <v>هدف وقت الاستعادة</v>
       </c>
       <c r="C409" t="str">
-        <v>Kontroles kods</v>
+        <v>RTO (Atjaunošanas laika mērķis)</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Functional Grouping</v>
+        <v>RPO (Recovery Point Objective)</v>
       </c>
       <c r="B410" t="str">
-        <v>التجميع الوظيفي</v>
+        <v>هدف نقطة الاستعادة</v>
       </c>
       <c r="C410" t="str">
-        <v>Funkcionālā grupēšana</v>
+        <v>RPO (Atjaunošanas punkta mērķis)</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Assignee</v>
+        <v>MTPD (Maximum Tolerable Period of Disruption)</v>
       </c>
       <c r="B411" t="str">
-        <v>المسؤول</v>
+        <v>أقصى فترة تعطل مقبولة</v>
       </c>
       <c r="C411" t="str">
-        <v>Piešķirtais</v>
+        <v>MTPD (Maksimālais pieļaujamais pārtraukuma periods)</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Domain Name</v>
+        <v>Dependencies</v>
       </c>
       <c r="B412" t="str">
-        <v>اسم المجال</v>
+        <v>التبعيات</v>
       </c>
       <c r="C412" t="str">
-        <v>Domēna nosaukums</v>
+        <v>Atkarības</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>No controls found.</v>
+        <v>Resources</v>
       </c>
       <c r="B413" t="str">
-        <v>لم يتم العثور على ضوابط.</v>
+        <v>الموارد</v>
       </c>
       <c r="C413" t="str">
-        <v>Kontroles nav atrastas.</v>
+        <v>Resursi</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>No controls</v>
+        <v>Impact Analysis</v>
       </c>
       <c r="B414" t="str">
-        <v>لا توجد ضوابط</v>
+        <v>تحليل التأثير</v>
       </c>
       <c r="C414" t="str">
-        <v>Nav kontroles</v>
+        <v>Ietekmes analīze</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Govern</v>
+        <v>Search by control code or name...</v>
       </c>
       <c r="B415" t="str">
-        <v>الحوكمة</v>
+        <v>البحث برمز الضابطة أو الاسم...</v>
       </c>
       <c r="C415" t="str">
-        <v>Pārvaldīt</v>
+        <v>Meklēt pēc kontroles koda vai nosaukuma...</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Identify</v>
+        <v>Integrated Framework</v>
       </c>
       <c r="B416" t="str">
-        <v>تحديد</v>
+        <v>الإطار المتكامل</v>
       </c>
       <c r="C416" t="str">
-        <v>Identificēt</v>
+        <v>Integrētais ietvars</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Protect</v>
+        <v>All Frameworks</v>
       </c>
       <c r="B417" t="str">
-        <v>حماية</v>
+        <v>جميع الأطر</v>
       </c>
       <c r="C417" t="str">
-        <v>Aizsargāt</v>
+        <v>Visi ietvari</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Detect</v>
+        <v>Delete All</v>
       </c>
       <c r="B418" t="str">
-        <v>اكتشاف</v>
+        <v>حذف الكل</v>
       </c>
       <c r="C418" t="str">
-        <v>Atklāt</v>
+        <v>Dzēst visu</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Respond</v>
+        <v>New Control</v>
       </c>
       <c r="B419" t="str">
-        <v>استجابة</v>
+        <v>ضابطة جديدة</v>
       </c>
       <c r="C419" t="str">
-        <v>Reaģēt</v>
+        <v>Jauna kontrole</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Recover</v>
+        <v>Control Name</v>
       </c>
       <c r="B420" t="str">
-        <v>استعادة</v>
+        <v>اسم الضابطة</v>
       </c>
       <c r="C420" t="str">
-        <v>Atjaunot</v>
+        <v>Kontroles nosaukums</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>You don't have permission to access Controls.</v>
+        <v>Control Code</v>
       </c>
       <c r="B421" t="str">
-        <v>ليس لديك صلاحية للوصول إلى الضوابط.</v>
+        <v>رمز الضابطة</v>
       </c>
       <c r="C421" t="str">
-        <v>Jums nav atļaujas piekļūt kontrolēm.</v>
+        <v>Kontroles kods</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Policy</v>
+        <v>Functional Grouping</v>
       </c>
       <c r="B422" t="str">
-        <v>السياسة</v>
+        <v>التجميع الوظيفي</v>
       </c>
       <c r="C422" t="str">
-        <v>Politika</v>
+        <v>Funkcionālā grupēšana</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Standards</v>
+        <v>Assignee</v>
       </c>
       <c r="B423" t="str">
-        <v>المعايير</v>
+        <v>المسؤول</v>
       </c>
       <c r="C423" t="str">
-        <v>Standarti</v>
+        <v>Piešķirtais</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Procedures</v>
+        <v>Domain Name</v>
       </c>
       <c r="B424" t="str">
-        <v>الإجراءات</v>
+        <v>اسم المجال</v>
       </c>
       <c r="C424" t="str">
-        <v>Procedūras</v>
+        <v>Domēna nosaukums</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Search by policy name or code...</v>
+        <v>No controls found.</v>
       </c>
       <c r="B425" t="str">
-        <v>البحث باسم السياسة أو الرمز...</v>
+        <v>لم يتم العثور على ضوابط.</v>
       </c>
       <c r="C425" t="str">
-        <v>Meklēt pēc politikas nosaukuma vai koda...</v>
+        <v>Kontroles nav atrastas.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Search by standard name or code...</v>
+        <v>No controls</v>
       </c>
       <c r="B426" t="str">
-        <v>البحث باسم المعيار أو الرمز...</v>
+        <v>لا توجد ضوابط</v>
       </c>
       <c r="C426" t="str">
-        <v>Meklēt pēc standarta nosaukuma vai koda...</v>
+        <v>Nav kontroles</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Search by procedure name or code...</v>
+        <v>Govern</v>
       </c>
       <c r="B427" t="str">
-        <v>البحث باسم الإجراء أو الرمز...</v>
+        <v>الحوكمة</v>
       </c>
       <c r="C427" t="str">
-        <v>Meklēt pēc procedūras nosaukuma vai koda...</v>
+        <v>Pārvaldīt</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>New Governance</v>
+        <v>Identify</v>
       </c>
       <c r="B428" t="str">
-        <v>حوكمة جديدة</v>
+        <v>تحديد</v>
       </c>
       <c r="C428" t="str">
-        <v>Jauna pārvaldība</v>
+        <v>Identificēt</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Code</v>
+        <v>Protect</v>
       </c>
       <c r="B429" t="str">
-        <v>الرمز</v>
+        <v>حماية</v>
       </c>
       <c r="C429" t="str">
-        <v>Kods</v>
+        <v>Aizsargāt</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Approver</v>
+        <v>Detect</v>
       </c>
       <c r="B430" t="str">
-        <v>المعتمد</v>
+        <v>اكتشاف</v>
       </c>
       <c r="C430" t="str">
-        <v>Apstiprinātājs</v>
+        <v>Atklāt</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Action</v>
+        <v>Respond</v>
       </c>
       <c r="B431" t="str">
-        <v>الإجراء</v>
+        <v>استجابة</v>
       </c>
       <c r="C431" t="str">
-        <v>Darbība</v>
+        <v>Reaģēt</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No policys found</v>
+        <v>Recover</v>
       </c>
       <c r="B432" t="str">
-        <v>لم يتم العثور على سياسات</v>
+        <v>استعادة</v>
       </c>
       <c r="C432" t="str">
-        <v>Politikas nav atrastas</v>
+        <v>Atjaunot</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>No standards found</v>
+        <v>You don't have permission to access Controls.</v>
       </c>
       <c r="B433" t="str">
-        <v>لم يتم العثور على معايير</v>
+        <v>ليس لديك صلاحية للوصول إلى الضوابط.</v>
       </c>
       <c r="C433" t="str">
-        <v>Standarti nav atrasti</v>
+        <v>Jums nav atļaujas piekļūt kontrolēm.</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>No procedures found</v>
+        <v>Policy</v>
       </c>
       <c r="B434" t="str">
-        <v>لم يتم العثور على إجراءات</v>
+        <v>السياسة</v>
       </c>
       <c r="C434" t="str">
-        <v>Procedūras nav atrastas</v>
+        <v>Politika</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Compliant</v>
+        <v>Standards</v>
       </c>
       <c r="B435" t="str">
-        <v>متوافق</v>
+        <v>المعايير</v>
       </c>
       <c r="C435" t="str">
-        <v>Atbilstošs</v>
+        <v>Standarti</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Non Compliant</v>
+        <v>Procedures</v>
       </c>
       <c r="B436" t="str">
-        <v>غير متوافق</v>
+        <v>الإجراءات</v>
       </c>
       <c r="C436" t="str">
-        <v>Neatbilstošs</v>
+        <v>Procedūras</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Not Applicable</v>
+        <v>Search by policy name or code...</v>
       </c>
       <c r="B437" t="str">
-        <v>غير قابل للتطبيق</v>
+        <v>البحث باسم السياسة أو الرمز...</v>
       </c>
       <c r="C437" t="str">
-        <v>Nav piemērojams</v>
+        <v>Meklēt pēc politikas nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Needs Review</v>
+        <v>Search by standard name or code...</v>
       </c>
       <c r="B438" t="str">
-        <v>يحتاج مراجعة</v>
+        <v>البحث باسم المعيار أو الرمز...</v>
       </c>
       <c r="C438" t="str">
-        <v>Nepieciešama pārskatīšana</v>
+        <v>Meklēt pēc standarta nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not Uploaded</v>
+        <v>Search by procedure name or code...</v>
       </c>
       <c r="B439" t="str">
-        <v>لم يتم الرفع</v>
+        <v>البحث باسم الإجراء أو الرمز...</v>
       </c>
       <c r="C439" t="str">
-        <v>Nav augšupielādēts</v>
+        <v>Meklēt pēc procedūras nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Pending Approval</v>
+        <v>New Governance</v>
       </c>
       <c r="B440" t="str">
-        <v>في انتظار الموافقة</v>
+        <v>حوكمة جديدة</v>
       </c>
       <c r="C440" t="str">
-        <v>Gaida apstiprinājumu</v>
+        <v>Jauna pārvaldība</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Yearly</v>
+        <v>Code</v>
       </c>
       <c r="B441" t="str">
-        <v>سنوي</v>
+        <v>الرمز</v>
       </c>
       <c r="C441" t="str">
-        <v>Ikgadējs</v>
+        <v>Kods</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Half-yearly</v>
+        <v>Approver</v>
       </c>
       <c r="B442" t="str">
-        <v>نصف سنوي</v>
+        <v>المعتمد</v>
       </c>
       <c r="C442" t="str">
-        <v>Pusgada</v>
+        <v>Apstiprinātājs</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>New Governance - Step 1 of 3</v>
+        <v>Action</v>
       </c>
       <c r="B443" t="str">
-        <v>حوكمة جديدة - الخطوة 1 من 3</v>
+        <v>الإجراء</v>
       </c>
       <c r="C443" t="str">
-        <v>Jauna pārvaldība - 1. solis no 3</v>
+        <v>Darbība</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>New Governance - Step 2 of 3</v>
+        <v>No policys found</v>
       </c>
       <c r="B444" t="str">
-        <v>حوكمة جديدة - الخطوة 2 من 3</v>
+        <v>لم يتم العثور على سياسات</v>
       </c>
       <c r="C444" t="str">
-        <v>Jauna pārvaldība - 2. solis no 3</v>
+        <v>Politikas nav atrastas</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>New Governance - Step 3 of 3</v>
+        <v>No standards found</v>
       </c>
       <c r="B445" t="str">
-        <v>حوكمة جديدة - الخطوة 3 من 3</v>
+        <v>لم يتم العثور على معايير</v>
       </c>
       <c r="C445" t="str">
-        <v>Jauna pārvaldība - 3. solis no 3</v>
+        <v>Standarti nav atrasti</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Governance Name</v>
+        <v>No procedures found</v>
       </c>
       <c r="B446" t="str">
-        <v>اسم الحوكمة</v>
+        <v>لم يتم العثور على إجراءات</v>
       </c>
       <c r="C446" t="str">
-        <v>Pārvaldības nosaukums</v>
+        <v>Procedūras nav atrastas</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Enter governance name</v>
+        <v>Compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>أدخل اسم الحوكمة</v>
+        <v>متوافق</v>
       </c>
       <c r="C447" t="str">
-        <v>Ievadiet pārvaldības nosaukumu</v>
+        <v>Atbilstošs</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>You don't have permission to access Governance.</v>
+        <v>Non Compliant</v>
       </c>
       <c r="B448" t="str">
-        <v>ليس لديك صلاحية للوصول إلى الحوكمة.</v>
+        <v>غير متوافق</v>
       </c>
       <c r="C448" t="str">
-        <v>Jums nav atļaujas piekļūt pārvaldībai.</v>
+        <v>Neatbilstošs</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Standard</v>
+        <v>Not Applicable</v>
       </c>
       <c r="B449" t="str">
-        <v>المعيار</v>
+        <v>غير قابل للتطبيق</v>
       </c>
       <c r="C449" t="str">
-        <v>Standarts</v>
+        <v>Nav piemērojams</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Procedure</v>
+        <v>Needs Review</v>
       </c>
       <c r="B450" t="str">
-        <v>الإجراء</v>
+        <v>يحتاج مراجعة</v>
       </c>
       <c r="C450" t="str">
-        <v>Procedūra</v>
+        <v>Nepieciešama pārskatīšana</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Validated</v>
+        <v>Not Uploaded</v>
       </c>
       <c r="B451" t="str">
-        <v>تم التحقق</v>
+        <v>لم يتم الرفع</v>
       </c>
       <c r="C451" t="str">
-        <v>Validēts</v>
+        <v>Nav augšupielādēts</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Need Attention</v>
+        <v>Pending Approval</v>
       </c>
       <c r="B452" t="str">
-        <v>يحتاج انتباه</v>
+        <v>في انتظار الموافقة</v>
       </c>
       <c r="C452" t="str">
-        <v>Nepieciešama uzmanība</v>
+        <v>Gaida apstiprinājumu</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Risk ID</v>
+        <v>Yearly</v>
       </c>
       <c r="B453" t="str">
-        <v>معرف المخاطر</v>
+        <v>سنوي</v>
       </c>
       <c r="C453" t="str">
-        <v>Riska ID</v>
+        <v>Ikgadējs</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Risk Name</v>
+        <v>Half-yearly</v>
       </c>
       <c r="B454" t="str">
-        <v>اسم المخاطر</v>
+        <v>نصف سنوي</v>
       </c>
       <c r="C454" t="str">
-        <v>Riska nosaukums</v>
+        <v>Pusgada</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Risk Description</v>
+        <v>New Governance - Step 1 of 3</v>
       </c>
       <c r="B455" t="str">
-        <v>وصف المخاطر</v>
+        <v>حوكمة جديدة - الخطوة 1 من 3</v>
       </c>
       <c r="C455" t="str">
-        <v>Riska apraksts</v>
+        <v>Jauna pārvaldība - 1. solis no 3</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Risk Category</v>
+        <v>New Governance - Step 2 of 3</v>
       </c>
       <c r="B456" t="str">
-        <v>فئة المخاطر</v>
+        <v>حوكمة جديدة - الخطوة 2 من 3</v>
       </c>
       <c r="C456" t="str">
-        <v>Riska kategorija</v>
+        <v>Jauna pārvaldība - 2. solis no 3</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Risk Owner</v>
+        <v>New Governance - Step 3 of 3</v>
       </c>
       <c r="B457" t="str">
-        <v>مالك المخاطر</v>
+        <v>حوكمة جديدة - الخطوة 3 من 3</v>
       </c>
       <c r="C457" t="str">
-        <v>Riska īpašnieks</v>
+        <v>Jauna pārvaldība - 3. solis no 3</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Risk Rating</v>
+        <v>Governance Name</v>
       </c>
       <c r="B458" t="str">
-        <v>تصنيف المخاطر</v>
+        <v>اسم الحوكمة</v>
       </c>
       <c r="C458" t="str">
-        <v>Riska novērtējums</v>
+        <v>Pārvaldības nosaukums</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Risk Type</v>
+        <v>Enter governance name</v>
       </c>
       <c r="B459" t="str">
-        <v>نوع المخاطر</v>
+        <v>أدخل اسم الحوكمة</v>
       </c>
       <c r="C459" t="str">
-        <v>Riska tips</v>
+        <v>Ievadiet pārvaldības nosaukumu</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>You don't have permission to access Risk Register.</v>
+        <v>You don't have permission to access Governance.</v>
       </c>
       <c r="B460" t="str">
-        <v>ليس لديك صلاحية للوصول إلى سجل المخاطر.</v>
+        <v>ليس لديك صلاحية للوصول إلى الحوكمة.</v>
       </c>
       <c r="C460" t="str">
-        <v>Jums nav atļaujas piekļūt risku reģistram.</v>
+        <v>Jums nav atļaujas piekļūt pārvaldībai.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Failed to fetch fieldwork data</v>
+        <v>Standard</v>
       </c>
       <c r="B461" t="str">
-        <v>فشل في جلب بيانات العمل الميداني</v>
+        <v>المعيار</v>
       </c>
       <c r="C461" t="str">
-        <v>Neizdevās ielādēt lauka darba datus</v>
+        <v>Standarts</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Framework Created Successfully</v>
+        <v>Procedure</v>
       </c>
       <c r="B462" t="str">
-        <v>تم إنشاء الإطار بنجاح</v>
+        <v>الإجراء</v>
       </c>
       <c r="C462" t="str">
-        <v>Ietvars veiksmīgi izveidots</v>
+        <v>Procedūra</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Framework</v>
+        <v>Validated</v>
       </c>
       <c r="B463" t="str">
-        <v>الإطار</v>
+        <v>تم التحقق</v>
       </c>
       <c r="C463" t="str">
-        <v>Ietvars</v>
+        <v>Validēts</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Unknown</v>
+        <v>Need Attention</v>
       </c>
       <c r="B464" t="str">
-        <v>غير معروف</v>
+        <v>يحتاج انتباه</v>
       </c>
       <c r="C464" t="str">
-        <v>Nezināms</v>
+        <v>Nepieciešama uzmanība</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>is ready to use!</v>
+        <v>Risk ID</v>
       </c>
       <c r="B465" t="str">
-        <v>جاهز للاستخدام!</v>
+        <v>معرف المخاطر</v>
       </c>
       <c r="C465" t="str">
-        <v>ir gatavs lietošanai!</v>
+        <v>Riska ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Framework was created but couldn't retrieve result. Check dashboard.</v>
+        <v>Risk Name</v>
       </c>
       <c r="B466" t="str">
-        <v>تم إنشاء الإطار ولكن لم يتم استرجاع النتيجة. تحقق من لوحة التحكم.</v>
+        <v>اسم المخاطر</v>
       </c>
       <c r="C466" t="str">
-        <v>Ietvars izveidots, bet neizdevās iegūt rezultātu. Pārbaudiet vadības paneli.</v>
+        <v>Riska nosaukums</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Framework Generation Failed</v>
+        <v>Risk Description</v>
       </c>
       <c r="B467" t="str">
-        <v>فشل في إنشاء الإطار</v>
+        <v>وصف المخاطر</v>
       </c>
       <c r="C467" t="str">
-        <v>Ietvara izveide neizdevās</v>
+        <v>Riska apraksts</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Validation Error</v>
+        <v>Risk Category</v>
       </c>
       <c r="B468" t="str">
-        <v>خطأ في التحقق</v>
+        <v>فئة المخاطر</v>
       </c>
       <c r="C468" t="str">
-        <v>Validācijas kļūda</v>
+        <v>Riska kategorija</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Framework name is required</v>
+        <v>Risk Owner</v>
       </c>
       <c r="B469" t="str">
-        <v>اسم الإطار مطلوب</v>
+        <v>مالك المخاطر</v>
       </c>
       <c r="C469" t="str">
-        <v>Ietvara nosaukums ir obligāts</v>
+        <v>Riska īpašnieks</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Framework Already Exists</v>
+        <v>Risk Rating</v>
       </c>
       <c r="B470" t="str">
-        <v>الإطار موجود بالفعل</v>
+        <v>تصنيف المخاطر</v>
       </c>
       <c r="C470" t="str">
-        <v>Ietvars jau pastāv</v>
+        <v>Riska novērtējums</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>A framework named</v>
+        <v>Risk Type</v>
       </c>
       <c r="B471" t="str">
-        <v>إطار باسم</v>
+        <v>نوع المخاطر</v>
       </c>
       <c r="C471" t="str">
-        <v>Ietvars ar nosaukumu</v>
+        <v>Riska tips</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>already exists.</v>
+        <v>You don't have permission to access Risk Register.</v>
       </c>
       <c r="B472" t="str">
-        <v>موجود بالفعل.</v>
+        <v>ليس لديك صلاحية للوصول إلى سجل المخاطر.</v>
       </c>
       <c r="C472" t="str">
-        <v>jau pastāv.</v>
+        <v>Jums nav atļaujas piekļūt risku reģistram.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Failed to create framework</v>
+        <v>RiskRegister</v>
       </c>
       <c r="B473" t="str">
-        <v>فشل في إنشاء الإطار</v>
+        <v>سجل المخاطر</v>
       </c>
       <c r="C473" t="str">
-        <v>Neizdevās izveidot ietvaru</v>
+        <v>Risku reģistrs</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Framework Generation Started</v>
+        <v>Register</v>
       </c>
       <c r="B474" t="str">
-        <v>بدأ إنشاء الإطار</v>
+        <v>السجل</v>
       </c>
       <c r="C474" t="str">
-        <v>Ietvara izveide sākta</v>
+        <v>Reģistrs</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Polling Stopped</v>
+        <v>Total Risks</v>
       </c>
       <c r="B475" t="str">
-        <v>توقف الاستطلاع</v>
+        <v>إجمالي المخاطر</v>
       </c>
       <c r="C475" t="str">
-        <v>Aptauja apturēta</v>
+        <v>Kopējie riski</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>You can check the status manually from the dashboard.</v>
+        <v>Open Risks</v>
       </c>
       <c r="B476" t="str">
-        <v>يمكنك التحقق من الحالة يدوياً من لوحة التحكم.</v>
+        <v>المخاطر المفتوحة</v>
       </c>
       <c r="C476" t="str">
-        <v>Jūs varat manuāli pārbaudīt statusu vadības panelī.</v>
+        <v>Atvērtie riski</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Regulation</v>
+        <v>Closed Risks</v>
       </c>
       <c r="B477" t="str">
-        <v>اللائحة</v>
+        <v>المخاطر المغلقة</v>
       </c>
       <c r="C477" t="str">
-        <v>Regula</v>
+        <v>Slēgtie riski</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Additional details about the framework...</v>
+        <v>Search risks...</v>
       </c>
       <c r="B478" t="str">
-        <v>تفاصيل إضافية حول الإطار...</v>
+        <v>البحث في المخاطر...</v>
       </c>
       <c r="C478" t="str">
-        <v>Papildu informācija par ietvaru...</v>
+        <v>Meklēt riskus...</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Generate Framework</v>
+        <v>All Ratings</v>
       </c>
       <c r="B479" t="str">
-        <v>إنشاء الإطار</v>
+        <v>جميع التصنيفات</v>
       </c>
       <c r="C479" t="str">
-        <v>Ģenerēt ietvaru</v>
+        <v>Visi vērtējumi</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>QUEUED</v>
+        <v>Activity Log</v>
       </c>
       <c r="B480" t="str">
-        <v>في قائمة الانتظار</v>
+        <v>سجل النشاط</v>
       </c>
       <c r="C480" t="str">
-        <v>RINDĀ</v>
+        <v>Aktivitāšu žurnāls</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>PROCESSING</v>
+        <v>New Risk</v>
       </c>
       <c r="B481" t="str">
-        <v>قيد المعالجة</v>
+        <v>مخاطر جديدة</v>
       </c>
       <c r="C481" t="str">
-        <v>APSTRĀDĀ</v>
+        <v>Jauns risks</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>COMPLETED</v>
+        <v>Risk</v>
       </c>
       <c r="B482" t="str">
-        <v>مكتمل</v>
+        <v>المخاطر</v>
       </c>
       <c r="C482" t="str">
-        <v>PABEIGTS</v>
+        <v>Risks</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>FAILED</v>
+        <v>Activity</v>
       </c>
       <c r="B483" t="str">
-        <v>فشل</v>
+        <v>النشاط</v>
       </c>
       <c r="C483" t="str">
-        <v>NEIZDEVĀS</v>
+        <v>Aktivitāte</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>PENDING_RESULT</v>
+        <v>Actor</v>
       </c>
       <c r="B484" t="str">
-        <v>في انتظار النتيجة</v>
+        <v>الفاعل</v>
       </c>
       <c r="C484" t="str">
-        <v>GAIDA_REZULTĀTU</v>
+        <v>Dalībnieks</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Overall Compliance Status</v>
+        <v>activities</v>
       </c>
       <c r="B485" t="str">
-        <v>حالة الامتثال الشاملة</v>
+        <v>الأنشطة</v>
       </c>
       <c r="C485" t="str">
-        <v>Kopējais atbilstības statuss</v>
+        <v>aktivitātes</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Overall:</v>
+        <v>No activity log entries found</v>
       </c>
       <c r="B486" t="str">
-        <v>الإجمالي:</v>
+        <v>لم يتم العثور على إدخالات في سجل النشاط</v>
       </c>
       <c r="C486" t="str">
-        <v>Kopā:</v>
+        <v>Nav atrasti aktivitāšu žurnāla ieraksti</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Risks</v>
+        <v>Import Risks</v>
       </c>
       <c r="B487" t="str">
-        <v>المخاطر</v>
+        <v>استيراد المخاطر</v>
       </c>
       <c r="C487" t="str">
-        <v>Riski</v>
+        <v>Importēt riskus</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Exceptions</v>
+        <v>Upload a CSV file to import risks</v>
       </c>
       <c r="B488" t="str">
-        <v>الاستثناءات</v>
+        <v>ارفع ملف CSV لاستيراد المخاطر</v>
       </c>
       <c r="C488" t="str">
-        <v>Izņēmumi</v>
+        <v>Augšupielādējiet CSV failu, lai importētu riskus</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Risk Assessment Overview</v>
+        <v>Required columns:</v>
       </c>
       <c r="B489" t="str">
-        <v>نظرة عامة على تقييم المخاطر</v>
+        <v>الأعمدة المطلوبة:</v>
       </c>
       <c r="C489" t="str">
-        <v>Risku novērtējuma pārskats</v>
+        <v>Obligātās kolonnas:</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Closed</v>
+        <v>Risk name, Risk description, Risk category, Risk type</v>
       </c>
       <c r="B490" t="str">
-        <v>مغلق</v>
+        <v>اسم المخاطر، وصف المخاطر، فئة المخاطر، نوع المخاطر</v>
       </c>
       <c r="C490" t="str">
-        <v>Slēgts</v>
+        <v>Riska nosaukums, Riska apraksts, Riska kategorija, Riska tips</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Total</v>
+        <v>Click to select a file or drag and drop</v>
       </c>
       <c r="B491" t="str">
-        <v>الإجمالي</v>
+        <v>انقر لاختيار ملف أو اسحب وأفلت</v>
       </c>
       <c r="C491" t="str">
-        <v>Kopā</v>
+        <v>Noklikšķiniet, lai izvēlētos failu, vai velciet un nometiet</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Issue By Category</v>
+        <v>Select File</v>
       </c>
       <c r="B492" t="str">
-        <v>القضايا حسب الفئة</v>
+        <v>اختيار ملف</v>
       </c>
       <c r="C492" t="str">
-        <v>Problēmas pēc kategorijas</v>
+        <v>Izvēlēties failu</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Issue By Department</v>
+        <v>Confirmation</v>
       </c>
       <c r="B493" t="str">
-        <v>القضايا حسب القسم</v>
+        <v>تأكيد</v>
       </c>
       <c r="C493" t="str">
-        <v>Problēmas pēc nodaļas</v>
+        <v>Apstiprinājums</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Issue By Domain</v>
+        <v>Are you sure you want to delete this risk?</v>
       </c>
       <c r="B494" t="str">
-        <v>القضايا حسب المجال</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه المخاطر؟</v>
       </c>
       <c r="C494" t="str">
-        <v>Problēmas pēc domēna</v>
+        <v>Vai tiešām vēlaties dzēst šo risku?</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>items</v>
+        <v>Catastrophic</v>
       </c>
       <c r="B495" t="str">
-        <v>عناصر</v>
+        <v>كارثي</v>
       </c>
       <c r="C495" t="str">
-        <v>vienumi</v>
+        <v>Katastrofāls</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Evidence KPI</v>
+        <v>Very high</v>
       </c>
       <c r="B496" t="str">
-        <v>مؤشرات أداء الأدلة</v>
+        <v>عالي جداً</v>
       </c>
       <c r="C496" t="str">
-        <v>Pierādījumu KPI</v>
+        <v>Ļoti augsts</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Process KPI</v>
+        <v>Very Low</v>
       </c>
       <c r="B497" t="str">
-        <v>مؤشرات أداء العمليات</v>
+        <v>منخفض جداً</v>
       </c>
       <c r="C497" t="str">
-        <v>Procesu KPI</v>
+        <v>Ļoti zems</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Achieved</v>
+        <v>Low Risk</v>
       </c>
       <c r="B498" t="str">
-        <v>محقق</v>
+        <v>مخاطر منخفضة</v>
       </c>
       <c r="C498" t="str">
-        <v>Sasniegts</v>
+        <v>Zems risks</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Scheduled</v>
+        <v>Medium Risk</v>
       </c>
       <c r="B499" t="str">
-        <v>مجدول</v>
+        <v>مخاطر متوسطة</v>
       </c>
       <c r="C499" t="str">
-        <v>Ieplānots</v>
+        <v>Vidējs risks</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Missed</v>
+        <v>High Risk</v>
       </c>
       <c r="B500" t="str">
-        <v>فائت</v>
+        <v>مخاطر عالية</v>
       </c>
       <c r="C500" t="str">
-        <v>Nokavēts</v>
+        <v>Augsts risks</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Overdue</v>
+        <v>Critical Risk</v>
       </c>
       <c r="B501" t="str">
-        <v>متأخر</v>
+        <v>مخاطر حرجة</v>
       </c>
       <c r="C501" t="str">
-        <v>Nokavēts</v>
+        <v>Kritisks risks</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Governance Status</v>
+        <v>Failed to fetch fieldwork data</v>
       </c>
       <c r="B502" t="str">
-        <v>حالة الحوكمة</v>
+        <v>فشل في جلب بيانات العمل الميداني</v>
       </c>
       <c r="C502" t="str">
-        <v>Pārvaldības statuss</v>
+        <v>Neizdevās ielādēt lauka darba datus</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Exception Status</v>
+        <v>Framework Created Successfully</v>
       </c>
       <c r="B503" t="str">
-        <v>حالة الاستثناءات</v>
+        <v>تم إنشاء الإطار بنجاح</v>
       </c>
       <c r="C503" t="str">
-        <v>Izņēmumu statuss</v>
+        <v>Ietvars veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Authorized</v>
+        <v>Framework</v>
       </c>
       <c r="B504" t="str">
-        <v>مصرح</v>
+        <v>الإطار</v>
       </c>
       <c r="C504" t="str">
-        <v>Autorizēts</v>
+        <v>Ietvars</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Showing</v>
+        <v>Unknown</v>
       </c>
       <c r="B505" t="str">
-        <v>عرض</v>
+        <v>غير معروف</v>
       </c>
       <c r="C505" t="str">
-        <v>Rāda</v>
+        <v>Nezināms</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>to</v>
+        <v>is ready to use!</v>
       </c>
       <c r="B506" t="str">
-        <v>إلى</v>
+        <v>جاهز للاستخدام!</v>
       </c>
       <c r="C506" t="str">
-        <v>līdz</v>
+        <v>ir gatavs lietošanai!</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>of</v>
+        <v>Framework was created but couldn't retrieve result. Check dashboard.</v>
       </c>
       <c r="B507" t="str">
-        <v>من</v>
+        <v>تم إنشاء الإطار ولكن لم يتم استرجاع النتيجة. تحقق من لوحة التحكم.</v>
       </c>
       <c r="C507" t="str">
-        <v>no</v>
+        <v>Ietvars izveidots, bet neizdevās iegūt rezultātu. Pārbaudiet vadības paneli.</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>entries</v>
+        <v>Framework Generation Failed</v>
       </c>
       <c r="B508" t="str">
-        <v>إدخالات</v>
+        <v>فشل في إنشاء الإطار</v>
       </c>
       <c r="C508" t="str">
-        <v>ierakstiem</v>
+        <v>Ietvara izveide neizdevās</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>rows per page</v>
+        <v>Validation Error</v>
       </c>
       <c r="B509" t="str">
-        <v>صفوف في الصفحة</v>
+        <v>خطأ في التحقق</v>
       </c>
       <c r="C509" t="str">
-        <v>rindas lapā</v>
+        <v>Validācijas kļūda</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Page</v>
+        <v>Framework name is required</v>
       </c>
       <c r="B510" t="str">
-        <v>صفحة</v>
+        <v>اسم الإطار مطلوب</v>
       </c>
       <c r="C510" t="str">
-        <v>Lapa</v>
+        <v>Ietvara nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>First</v>
+        <v>Framework Already Exists</v>
       </c>
       <c r="B511" t="str">
-        <v>الأول</v>
+        <v>الإطار موجود بالفعل</v>
       </c>
       <c r="C511" t="str">
-        <v>Pirmā</v>
+        <v>Ietvars jau pastāv</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Last</v>
+        <v>A framework named</v>
       </c>
       <c r="B512" t="str">
-        <v>الأخير</v>
+        <v>إطار باسم</v>
       </c>
       <c r="C512" t="str">
-        <v>Pēdējā</v>
+        <v>Ietvars ar nosaukumu</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Go to page</v>
+        <v>already exists.</v>
       </c>
       <c r="B513" t="str">
-        <v>انتقل إلى الصفحة</v>
+        <v>موجود بالفعل.</v>
       </c>
       <c r="C513" t="str">
-        <v>Doties uz lapu</v>
+        <v>jau pastāv.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Search...</v>
+        <v>Failed to create framework</v>
       </c>
       <c r="B514" t="str">
-        <v>بحث...</v>
+        <v>فشل في إنشاء الإطار</v>
       </c>
       <c r="C514" t="str">
-        <v>Meklēt...</v>
+        <v>Neizdevās izveidot ietvaru</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>No data</v>
+        <v>Framework Generation Started</v>
       </c>
       <c r="B515" t="str">
-        <v>لا توجد بيانات</v>
+        <v>بدأ إنشاء الإطار</v>
       </c>
       <c r="C515" t="str">
-        <v>Nav datu</v>
+        <v>Ietvara izveide sākta</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Search By Name</v>
+        <v>Polling Stopped</v>
       </c>
       <c r="B516" t="str">
-        <v>البحث بالاسم</v>
+        <v>توقف الاستطلاع</v>
       </c>
       <c r="C516" t="str">
-        <v>Meklēt pēc nosaukuma</v>
+        <v>Aptauja apturēta</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Search By Control Code , Name</v>
+        <v>You can check the status manually from the dashboard.</v>
       </c>
       <c r="B517" t="str">
-        <v>البحث برمز الضابطة أو الاسم</v>
+        <v>يمكنك التحقق من الحالة يدوياً من لوحة التحكم.</v>
       </c>
       <c r="C517" t="str">
-        <v>Meklēt pēc kontroles koda, nosaukuma</v>
+        <v>Jūs varat manuāli pārbaudīt statusu vadības panelī.</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This field is required</v>
+        <v>Regulation</v>
       </c>
       <c r="B518" t="str">
-        <v>هذا الحقل مطلوب</v>
+        <v>اللائحة</v>
       </c>
       <c r="C518" t="str">
-        <v>Šis lauks ir obligāts</v>
+        <v>Regula</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Invalid email format</v>
+        <v>Additional details about the framework...</v>
       </c>
       <c r="B519" t="str">
-        <v>تنسيق البريد الإلكتروني غير صالح</v>
+        <v>تفاصيل إضافية حول الإطار...</v>
       </c>
       <c r="C519" t="str">
-        <v>Nederīgs e-pasta formāts</v>
+        <v>Papildu informācija par ietvaru...</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Password must be at least 8 characters</v>
+        <v>Generate Framework</v>
       </c>
       <c r="B520" t="str">
-        <v>يجب أن تكون كلمة المرور 8 أحرف على الأقل</v>
+        <v>إنشاء الإطار</v>
       </c>
       <c r="C520" t="str">
-        <v>Parolei jābūt vismaz 8 rakstzīmēm</v>
+        <v>Ģenerēt ietvaru</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Passwords do not match</v>
+        <v>QUEUED</v>
       </c>
       <c r="B521" t="str">
-        <v>كلمات المرور غير متطابقة</v>
+        <v>في قائمة الانتظار</v>
       </c>
       <c r="C521" t="str">
-        <v>Paroles nesakrīt</v>
+        <v>RINDĀ</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Please enter a valid value</v>
+        <v>PROCESSING</v>
       </c>
       <c r="B522" t="str">
-        <v>يرجى إدخال قيمة صالحة</v>
+        <v>قيد المعالجة</v>
       </c>
       <c r="C522" t="str">
-        <v>Lūdzu, ievadiet derīgu vērtību</v>
+        <v>APSTRĀDĀ</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Maximum length exceeded</v>
+        <v>COMPLETED</v>
       </c>
       <c r="B523" t="str">
-        <v>تم تجاوز الحد الأقصى للطول</v>
+        <v>مكتمل</v>
       </c>
       <c r="C523" t="str">
-        <v>Pārsniegts maksimālais garums</v>
+        <v>PABEIGTS</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Minimum length not met</v>
+        <v>FAILED</v>
       </c>
       <c r="B524" t="str">
-        <v>لم يتم تحقيق الحد الأدنى للطول</v>
+        <v>فشل</v>
       </c>
       <c r="C524" t="str">
-        <v>Nav sasniegts minimālais garums</v>
+        <v>NEIZDEVĀS</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>An error occurred</v>
+        <v>PENDING_RESULT</v>
       </c>
       <c r="B525" t="str">
-        <v>حدث خطأ</v>
+        <v>في انتظار النتيجة</v>
       </c>
       <c r="C525" t="str">
-        <v>Radās kļūda</v>
+        <v>GAIDA_REZULTĀTU</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Not found</v>
+        <v>Overall Compliance Status</v>
       </c>
       <c r="B526" t="str">
-        <v>غير موجود</v>
+        <v>حالة الامتثال الشاملة</v>
       </c>
       <c r="C526" t="str">
-        <v>Nav atrasts</v>
+        <v>Kopējais atbilstības statuss</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Unauthorized</v>
+        <v>Overall:</v>
       </c>
       <c r="B527" t="str">
-        <v>غير مصرح</v>
+        <v>الإجمالي:</v>
       </c>
       <c r="C527" t="str">
-        <v>Nav autorizēts</v>
+        <v>Kopā:</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Forbidden</v>
+        <v>Loading dashboard...</v>
       </c>
       <c r="B528" t="str">
-        <v>محظور</v>
+        <v>جاري تحميل لوحة التحكم...</v>
       </c>
       <c r="C528" t="str">
-        <v>Aizliegts</v>
+        <v>Ielādē vadības paneli...</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Network error</v>
+        <v>Risks</v>
       </c>
       <c r="B529" t="str">
-        <v>خطأ في الشبكة</v>
+        <v>المخاطر</v>
       </c>
       <c r="C529" t="str">
-        <v>Tīkla kļūda</v>
+        <v>Riski</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Server error</v>
+        <v>Exceptions</v>
       </c>
       <c r="B530" t="str">
-        <v>خطأ في الخادم</v>
+        <v>الاستثناءات</v>
       </c>
       <c r="C530" t="str">
-        <v>Servera kļūda</v>
+        <v>Izņēmumi</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Session expired</v>
+        <v>Risk Assessment Overview</v>
       </c>
       <c r="B531" t="str">
-        <v>انتهت صلاحية الجلسة</v>
+        <v>نظرة عامة على تقييم المخاطر</v>
       </c>
       <c r="C531" t="str">
-        <v>Sesija ir beigusies</v>
+        <v>Risku novērtējuma pārskats</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Please login again</v>
+        <v>Closed</v>
       </c>
       <c r="B532" t="str">
-        <v>يرجى تسجيل الدخول مرة أخرى</v>
+        <v>مغلق</v>
       </c>
       <c r="C532" t="str">
-        <v>Lūdzu, piesakieties vēlreiz</v>
+        <v>Slēgts</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Saved successfully</v>
+        <v>Total</v>
       </c>
       <c r="B533" t="str">
-        <v>تم الحفظ بنجاح</v>
+        <v>الإجمالي</v>
       </c>
       <c r="C533" t="str">
-        <v>Veiksmīgi saglabāts</v>
+        <v>Kopā</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Deleted successfully</v>
+        <v>Issue By Category</v>
       </c>
       <c r="B534" t="str">
-        <v>تم الحذف بنجاح</v>
+        <v>القضايا حسب الفئة</v>
       </c>
       <c r="C534" t="str">
-        <v>Veiksmīgi dzēsts</v>
+        <v>Problēmas pēc kategorijas</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Updated successfully</v>
+        <v>Issue By Department</v>
       </c>
       <c r="B535" t="str">
-        <v>تم التحديث بنجاح</v>
+        <v>القضايا حسب القسم</v>
       </c>
       <c r="C535" t="str">
-        <v>Veiksmīgi atjaunināts</v>
+        <v>Problēmas pēc nodaļas</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Created successfully</v>
+        <v>Issue By Domain</v>
       </c>
       <c r="B536" t="str">
-        <v>تم الإنشاء بنجاح</v>
+        <v>القضايا حسب المجال</v>
       </c>
       <c r="C536" t="str">
-        <v>Veiksmīgi izveidots</v>
+        <v>Problēmas pēc domēna</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Operation completed</v>
+        <v>items</v>
       </c>
       <c r="B537" t="str">
-        <v>تمت العملية</v>
+        <v>عناصر</v>
       </c>
       <c r="C537" t="str">
-        <v>Darbība pabeigta</v>
+        <v>vienumi</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Today</v>
+        <v>Evidence KPI</v>
       </c>
       <c r="B538" t="str">
-        <v>اليوم</v>
+        <v>مؤشرات أداء الأدلة</v>
       </c>
       <c r="C538" t="str">
-        <v>Šodien</v>
+        <v>Pierādījumu KPI</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Tomorrow</v>
+        <v>Process KPI</v>
       </c>
       <c r="B539" t="str">
-        <v>غداً</v>
+        <v>مؤشرات أداء العمليات</v>
       </c>
       <c r="C539" t="str">
-        <v>Rīt</v>
+        <v>Procesu KPI</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Select date</v>
+        <v>Achieved</v>
       </c>
       <c r="B540" t="str">
-        <v>اختر التاريخ</v>
+        <v>محقق</v>
       </c>
       <c r="C540" t="str">
-        <v>Izvēlieties datumu</v>
+        <v>Sasniegts</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Select time</v>
+        <v>Scheduled</v>
       </c>
       <c r="B541" t="str">
-        <v>اختر الوقت</v>
+        <v>مجدول</v>
       </c>
       <c r="C541" t="str">
-        <v>Izvēlieties laiku</v>
+        <v>Ieplānots</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>From</v>
+        <v>Missed</v>
       </c>
       <c r="B542" t="str">
-        <v>من</v>
+        <v>فائت</v>
       </c>
       <c r="C542" t="str">
-        <v>No</v>
+        <v>Nokavēts</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>To</v>
+        <v>Overdue</v>
       </c>
       <c r="B543" t="str">
-        <v>إلى</v>
+        <v>متأخر</v>
       </c>
       <c r="C543" t="str">
-        <v>Līdz</v>
+        <v>Nokavēts</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Start Date</v>
+        <v>Governance Status</v>
       </c>
       <c r="B544" t="str">
-        <v>تاريخ البداية</v>
+        <v>حالة الحوكمة</v>
       </c>
       <c r="C544" t="str">
-        <v>Sākuma datums</v>
+        <v>Pārvaldības statuss</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>End Date</v>
+        <v>Exception Status</v>
       </c>
       <c r="B545" t="str">
-        <v>تاريخ النهاية</v>
+        <v>حالة الاستثناءات</v>
       </c>
       <c r="C545" t="str">
-        <v>Beigu datums</v>
+        <v>Izņēmumu statuss</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Select file</v>
+        <v>Authorized</v>
       </c>
       <c r="B546" t="str">
-        <v>اختر ملف</v>
+        <v>مصرح</v>
       </c>
       <c r="C546" t="str">
-        <v>Izvēlieties failu</v>
+        <v>Autorizēts</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Select files</v>
+        <v>Showing</v>
       </c>
       <c r="B547" t="str">
-        <v>اختر ملفات</v>
+        <v>عرض</v>
       </c>
       <c r="C547" t="str">
-        <v>Izvēlieties failus</v>
+        <v>Rāda</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Drop files here</v>
+        <v>to</v>
       </c>
       <c r="B548" t="str">
-        <v>أسقط الملفات هنا</v>
+        <v>إلى</v>
       </c>
       <c r="C548" t="str">
-        <v>Nometiet failus šeit</v>
+        <v>līdz</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>or click to select</v>
+        <v>of</v>
       </c>
       <c r="B549" t="str">
-        <v>أو انقر للاختيار</v>
+        <v>من</v>
       </c>
       <c r="C549" t="str">
-        <v>vai noklikšķiniet, lai izvēlētos</v>
+        <v>no</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>File uploaded successfully</v>
+        <v>entries</v>
       </c>
       <c r="B550" t="str">
-        <v>تم رفع الملف بنجاح</v>
+        <v>إدخالات</v>
       </c>
       <c r="C550" t="str">
-        <v>Fails veiksmīgi augšupielādēts</v>
+        <v>ierakstiem</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Failed to upload file</v>
+        <v>rows per page</v>
       </c>
       <c r="B551" t="str">
-        <v>فشل في رفع الملف</v>
+        <v>صفوف في الصفحة</v>
       </c>
       <c r="C551" t="str">
-        <v>Neizdevās augšupielādēt failu</v>
+        <v>rindas lapā</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>File size too large</v>
+        <v>Page</v>
       </c>
       <c r="B552" t="str">
-        <v>حجم الملف كبير جداً</v>
+        <v>صفحة</v>
       </c>
       <c r="C552" t="str">
-        <v>Faila izmērs ir pārāk liels</v>
+        <v>Lapa</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Invalid file type</v>
+        <v>First</v>
       </c>
       <c r="B553" t="str">
-        <v>نوع الملف غير صالح</v>
+        <v>الأول</v>
       </c>
       <c r="C553" t="str">
-        <v>Nederīgs faila tips</v>
+        <v>Pirmā</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Edit Issue</v>
+        <v>Last</v>
       </c>
       <c r="B554" t="str">
-        <v>تعديل القضية</v>
+        <v>الأخير</v>
       </c>
       <c r="C554" t="str">
-        <v>Rediģēt problēmu</v>
+        <v>Pēdējā</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Enter issue title</v>
+        <v>Go to page</v>
       </c>
       <c r="B555" t="str">
-        <v>أدخل عنوان القضية</v>
+        <v>انتقل إلى الصفحة</v>
       </c>
       <c r="C555" t="str">
-        <v>Ievadiet problēmas nosaukumu</v>
+        <v>Doties uz lapu</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Select domain</v>
+        <v>Search...</v>
       </c>
       <c r="B556" t="str">
-        <v>اختر المجال</v>
+        <v>بحث...</v>
       </c>
       <c r="C556" t="str">
-        <v>Izvēlieties domēnu</v>
+        <v>Meklēt...</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Issue Owner</v>
+        <v>No data</v>
       </c>
       <c r="B557" t="str">
-        <v>مالك القضية</v>
+        <v>لا توجد بيانات</v>
       </c>
       <c r="C557" t="str">
-        <v>Problēmas īpašnieks</v>
+        <v>Nav datu</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Select owner</v>
+        <v>Search By Name</v>
       </c>
       <c r="B558" t="str">
-        <v>اختر المالك</v>
+        <v>البحث بالاسم</v>
       </c>
       <c r="C558" t="str">
-        <v>Izvēlieties īpašnieku</v>
+        <v>Meklēt pēc nosaukuma</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Select department first</v>
+        <v>Search By Control Code , Name</v>
       </c>
       <c r="B559" t="str">
-        <v>اختر القسم أولاً</v>
+        <v>البحث برمز الضابطة أو الاسم</v>
       </c>
       <c r="C559" t="str">
-        <v>Vispirms izvēlieties nodaļu</v>
+        <v>Meklēt pēc kontroles koda, nosaukuma</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Select type</v>
+        <v>This field is required</v>
       </c>
       <c r="B560" t="str">
-        <v>اختر النوع</v>
+        <v>هذا الحقل مطلوب</v>
       </c>
       <c r="C560" t="str">
-        <v>Izvēlieties tipu</v>
+        <v>Šis lauks ir obligāts</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Enter issue description</v>
+        <v>Invalid email format</v>
       </c>
       <c r="B561" t="str">
-        <v>أدخل وصف القضية</v>
+        <v>تنسيق البريد الإلكتروني غير صالح</v>
       </c>
       <c r="C561" t="str">
-        <v>Ievadiet problēmas aprakstu</v>
+        <v>Nederīgs e-pasta formāts</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>New Stakeholder</v>
+        <v>Password must be at least 8 characters</v>
       </c>
       <c r="B562" t="str">
-        <v>صاحب مصلحة جديد</v>
+        <v>يجب أن تكون كلمة المرور 8 أحرف على الأقل</v>
       </c>
       <c r="C562" t="str">
-        <v>Jauna ieinteresētā puse</v>
+        <v>Parolei jābūt vismaz 8 rakstzīmēm</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Edit Stakeholder</v>
+        <v>Passwords do not match</v>
       </c>
       <c r="B563" t="str">
-        <v>تعديل صاحب المصلحة</v>
+        <v>كلمات المرور غير متطابقة</v>
       </c>
       <c r="C563" t="str">
-        <v>Rediģēt ieinteresēto pusi</v>
+        <v>Paroles nesakrīt</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Search stakeholders...</v>
+        <v>Please enter a valid value</v>
       </c>
       <c r="B564" t="str">
-        <v>البحث في أصحاب المصلحة...</v>
+        <v>يرجى إدخال قيمة صالحة</v>
       </c>
       <c r="C564" t="str">
-        <v>Meklēt ieinteresētās puses...</v>
+        <v>Lūdzu, ievadiet derīgu vērtību</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Search issues...</v>
+        <v>Maximum length exceeded</v>
       </c>
       <c r="B565" t="str">
-        <v>البحث في القضايا...</v>
+        <v>تم تجاوز الحد الأقصى للطول</v>
       </c>
       <c r="C565" t="str">
-        <v>Meklēt problēmas...</v>
+        <v>Pārsniegts maksimālais garums</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>All Types</v>
+        <v>Minimum length not met</v>
       </c>
       <c r="B566" t="str">
-        <v>جميع الأنواع</v>
+        <v>لم يتم تحقيق الحد الأدنى للطول</v>
       </c>
       <c r="C566" t="str">
-        <v>Visi tipi</v>
+        <v>Nav sasniegts minimālais garums</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>All Status</v>
+        <v>An error occurred</v>
       </c>
       <c r="B567" t="str">
-        <v>جميع الحالات</v>
+        <v>حدث خطأ</v>
       </c>
       <c r="C567" t="str">
-        <v>Visi statusi</v>
+        <v>Radās kļūda</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>All Categories</v>
+        <v>Not found</v>
       </c>
       <c r="B568" t="str">
-        <v>جميع الفئات</v>
+        <v>غير موجود</v>
       </c>
       <c r="C568" t="str">
-        <v>Visas kategorijas</v>
+        <v>Nav atrasts</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>All Domains</v>
+        <v>Unauthorized</v>
       </c>
       <c r="B569" t="str">
-        <v>جميع المجالات</v>
+        <v>غير مصرح</v>
       </c>
       <c r="C569" t="str">
-        <v>Visi domēni</v>
+        <v>Nav autorizēts</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>No Issues Found</v>
+        <v>Forbidden</v>
       </c>
       <c r="B570" t="str">
-        <v>لم يتم العثور على قضايا</v>
+        <v>محظور</v>
       </c>
       <c r="C570" t="str">
-        <v>Problēmas nav atrastas</v>
+        <v>Aizliegts</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Try adjusting your filters to find issues.</v>
+        <v>Network error</v>
       </c>
       <c r="B571" t="str">
-        <v>حاول تعديل الفلاتر للعثور على القضايا.</v>
+        <v>خطأ في الشبكة</v>
       </c>
       <c r="C571" t="str">
-        <v>Mēģiniet pielāgot filtrus, lai atrastu problēmas.</v>
+        <v>Tīkla kļūda</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Create your first issue to get started.</v>
+        <v>Server error</v>
       </c>
       <c r="B572" t="str">
-        <v>أنشئ أول قضية للبدء.</v>
+        <v>خطأ في الخادم</v>
       </c>
       <c r="C572" t="str">
-        <v>Izveidojiet savu pirmo problēmu, lai sāktu.</v>
+        <v>Servera kļūda</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Create Action</v>
+        <v>Session expired</v>
       </c>
       <c r="B573" t="str">
-        <v>إنشاء إجراء</v>
+        <v>انتهت صلاحية الجلسة</v>
       </c>
       <c r="C573" t="str">
-        <v>Izveidot darbību</v>
+        <v>Sesija ir beigusies</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>View Actions</v>
+        <v>Please login again</v>
       </c>
       <c r="B574" t="str">
-        <v>عرض الإجراءات</v>
+        <v>يرجى تسجيل الدخول مرة أخرى</v>
       </c>
       <c r="C574" t="str">
-        <v>Skatīt darbības</v>
+        <v>Lūdzu, piesakieties vēlreiz</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Review Actions</v>
+        <v>Saved successfully</v>
       </c>
       <c r="B575" t="str">
-        <v>مراجعة الإجراءات</v>
+        <v>تم الحفظ بنجاح</v>
       </c>
       <c r="C575" t="str">
-        <v>Pārskatīt darbības</v>
+        <v>Veiksmīgi saglabāts</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Select stakeholder</v>
+        <v>Deleted successfully</v>
       </c>
       <c r="B576" t="str">
-        <v>اختر صاحب المصلحة</v>
+        <v>تم الحذف بنجاح</v>
       </c>
       <c r="C576" t="str">
-        <v>Izvēlieties ieinteresēto pusi</v>
+        <v>Veiksmīgi dzēsts</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Need and Expectation</v>
+        <v>Updated successfully</v>
       </c>
       <c r="B577" t="str">
-        <v>الاحتياجات والتوقعات</v>
+        <v>تم التحديث بنجاح</v>
       </c>
       <c r="C577" t="str">
-        <v>Vajadzība un gaidījums</v>
+        <v>Veiksmīgi atjaunināts</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Select need/expectation</v>
+        <v>Created successfully</v>
       </c>
       <c r="B578" t="str">
-        <v>اختر الاحتياج/التوقع</v>
+        <v>تم الإنشاء بنجاح</v>
       </c>
       <c r="C578" t="str">
-        <v>Izvēlieties vajadzību/gaidījumu</v>
+        <v>Veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Stakeholder Needs and Expectations</v>
+        <v>Operation completed</v>
       </c>
       <c r="B579" t="str">
-        <v>احتياجات وتوقعات أصحاب المصلحة</v>
+        <v>تمت العملية</v>
       </c>
       <c r="C579" t="str">
-        <v>Ieinteresēto pušu vajadzības un gaidījumi</v>
+        <v>Darbība pabeigta</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Add New Domain</v>
+        <v>Today</v>
       </c>
       <c r="B580" t="str">
-        <v>إضافة مجال جديد</v>
+        <v>اليوم</v>
       </c>
       <c r="C580" t="str">
-        <v>Pievienot jaunu domēnu</v>
+        <v>Šodien</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Enter domain name</v>
+        <v>Tomorrow</v>
       </c>
       <c r="B581" t="str">
-        <v>أدخل اسم المجال</v>
+        <v>غداً</v>
       </c>
       <c r="C581" t="str">
-        <v>Ievadiet domēna nosaukumu</v>
+        <v>Rīt</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Add New Category</v>
+        <v>Select date</v>
       </c>
       <c r="B582" t="str">
-        <v>إضافة فئة جديدة</v>
+        <v>اختر التاريخ</v>
       </c>
       <c r="C582" t="str">
-        <v>Pievienot jaunu kategoriju</v>
+        <v>Izvēlieties datumu</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Add New Issue Type</v>
+        <v>Select time</v>
       </c>
       <c r="B583" t="str">
-        <v>إضافة نوع قضية جديد</v>
+        <v>اختر الوقت</v>
       </c>
       <c r="C583" t="str">
-        <v>Pievienot jaunu problēmas tipu</v>
+        <v>Izvēlieties laiku</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Issue Type Name</v>
+        <v>From</v>
       </c>
       <c r="B584" t="str">
-        <v>اسم نوع القضية</v>
+        <v>من</v>
       </c>
       <c r="C584" t="str">
-        <v>Problēmas tipa nosaukums</v>
+        <v>No</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Enter issue type name</v>
+        <v>To</v>
       </c>
       <c r="B585" t="str">
-        <v>أدخل اسم نوع القضية</v>
+        <v>إلى</v>
       </c>
       <c r="C585" t="str">
-        <v>Ievadiet problēmas tipa nosaukumu</v>
+        <v>Līdz</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Link Process</v>
+        <v>Start Date</v>
       </c>
       <c r="B586" t="str">
-        <v>ربط العملية</v>
+        <v>تاريخ البداية</v>
       </c>
       <c r="C586" t="str">
-        <v>Saistīt procesu</v>
+        <v>Sākuma datums</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>No processes found</v>
+        <v>End Date</v>
       </c>
       <c r="B587" t="str">
-        <v>لم يتم العثور على عمليات</v>
+        <v>تاريخ النهاية</v>
       </c>
       <c r="C587" t="str">
-        <v>Procesi nav atrasti</v>
+        <v>Beigu datums</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Add New Need/Expectation</v>
+        <v>Select file</v>
       </c>
       <c r="B588" t="str">
-        <v>إضافة احتياج/توقع جديد</v>
+        <v>اختر ملف</v>
       </c>
       <c r="C588" t="str">
-        <v>Pievienot jaunu vajadzību/gaidījumu</v>
+        <v>Izvēlieties failu</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Need/Expectation</v>
+        <v>Select files</v>
       </c>
       <c r="B589" t="str">
-        <v>الاحتياج/التوقع</v>
+        <v>اختر ملفات</v>
       </c>
       <c r="C589" t="str">
-        <v>Vajadzība/Gaidījums</v>
+        <v>Izvēlieties failus</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Enter need/expectation</v>
+        <v>Drop files here</v>
       </c>
       <c r="B590" t="str">
-        <v>أدخل الاحتياج/التوقع</v>
+        <v>أسقط الملفات هنا</v>
       </c>
       <c r="C590" t="str">
-        <v>Ievadiet vajadzību/gaidījumu</v>
+        <v>Nometiet failus šeit</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Enter a new need or expectation type.</v>
+        <v>or click to select</v>
       </c>
       <c r="B591" t="str">
-        <v>أدخل نوع احتياج أو توقع جديد.</v>
+        <v>أو انقر للاختيار</v>
       </c>
       <c r="C591" t="str">
-        <v>Ievadiet jaunu vajadzības vai gaidījumu tipu.</v>
+        <v>vai noklikšķiniet, lai izvēlētos</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Title is required</v>
+        <v>File uploaded successfully</v>
       </c>
       <c r="B592" t="str">
-        <v>العنوان مطلوب</v>
+        <v>تم رفع الملف بنجاح</v>
       </c>
       <c r="C592" t="str">
-        <v>Nosaukums ir obligāts</v>
+        <v>Fails veiksmīgi augšupielādēts</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Issue created successfully</v>
+        <v>Failed to upload file</v>
       </c>
       <c r="B593" t="str">
-        <v>تم إنشاء القضية بنجاح</v>
+        <v>فشل في رفع الملف</v>
       </c>
       <c r="C593" t="str">
-        <v>Problēma veiksmīgi izveidota</v>
+        <v>Neizdevās augšupielādēt failu</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Failed to create issue</v>
+        <v>File size too large</v>
       </c>
       <c r="B594" t="str">
-        <v>فشل في إنشاء القضية</v>
+        <v>حجم الملف كبير جداً</v>
       </c>
       <c r="C594" t="str">
-        <v>Neizdevās izveidot problēmu</v>
+        <v>Faila izmērs ir pārāk liels</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Issue updated successfully</v>
+        <v>Invalid file type</v>
       </c>
       <c r="B595" t="str">
-        <v>تم تحديث القضية بنجاح</v>
+        <v>نوع الملف غير صالح</v>
       </c>
       <c r="C595" t="str">
-        <v>Problēma veiksmīgi atjaunināta</v>
+        <v>Nederīgs faila tips</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Failed to update issue</v>
+        <v>Edit Issue</v>
       </c>
       <c r="B596" t="str">
-        <v>فشل في تحديث القضية</v>
+        <v>تعديل القضية</v>
       </c>
       <c r="C596" t="str">
-        <v>Neizdevās atjaunināt problēmu</v>
+        <v>Rediģēt problēmu</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Stakeholder updated successfully</v>
+        <v>Enter issue title</v>
       </c>
       <c r="B597" t="str">
-        <v>تم تحديث صاحب المصلحة بنجاح</v>
+        <v>أدخل عنوان القضية</v>
       </c>
       <c r="C597" t="str">
-        <v>Ieinteresētā puse veiksmīgi atjaunināta</v>
+        <v>Ievadiet problēmas nosaukumu</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Failed to update stakeholder</v>
+        <v>Select domain</v>
       </c>
       <c r="B598" t="str">
-        <v>فشل في تحديث صاحب المصلحة</v>
+        <v>اختر المجال</v>
       </c>
       <c r="C598" t="str">
-        <v>Neizdevās atjaunināt ieinteresēto pusi</v>
+        <v>Izvēlieties domēnu</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Open</v>
+        <v>Issue Owner</v>
       </c>
       <c r="B599" t="str">
-        <v>مفتوح</v>
+        <v>مالك القضية</v>
       </c>
       <c r="C599" t="str">
-        <v>Atvērts</v>
+        <v>Problēmas īpašnieks</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>In Progress</v>
+        <v>Select owner</v>
       </c>
       <c r="B600" t="str">
-        <v>قيد التنفيذ</v>
+        <v>اختر المالك</v>
       </c>
       <c r="C600" t="str">
-        <v>Procesā</v>
+        <v>Izvēlieties īpašnieku</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Action type and description are required</v>
+        <v>Select department first</v>
       </c>
       <c r="B601" t="str">
-        <v>نوع الإجراء والوصف مطلوبان</v>
+        <v>اختر القسم أولاً</v>
       </c>
       <c r="C601" t="str">
-        <v>Darbības tips un apraksts ir obligāti</v>
+        <v>Vispirms izvēlieties nodaļu</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Action created successfully</v>
+        <v>Select type</v>
       </c>
       <c r="B602" t="str">
-        <v>تم إنشاء الإجراء بنجاح</v>
+        <v>اختر النوع</v>
       </c>
       <c r="C602" t="str">
-        <v>Darbība veiksmīgi izveidota</v>
+        <v>Izvēlieties tipu</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Failed to create action</v>
+        <v>Enter issue description</v>
       </c>
       <c r="B603" t="str">
-        <v>فشل في إنشاء الإجراء</v>
+        <v>أدخل وصف القضية</v>
       </c>
       <c r="C603" t="str">
-        <v>Neizdevās izveidot darbību</v>
+        <v>Ievadiet problēmas aprakstu</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Action is resolved</v>
+        <v>New Stakeholder</v>
       </c>
       <c r="B604" t="str">
-        <v>تم حل الإجراء</v>
+        <v>صاحب مصلحة جديد</v>
       </c>
       <c r="C604" t="str">
-        <v>Darbība ir atrisināta</v>
+        <v>Jauna ieinteresētā puse</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Failed to resolve action</v>
+        <v>Edit Stakeholder</v>
       </c>
       <c r="B605" t="str">
-        <v>فشل في حل الإجراء</v>
+        <v>تعديل صاحب المصلحة</v>
       </c>
       <c r="C605" t="str">
-        <v>Neizdevās atrisināt darbību</v>
+        <v>Rediģēt ieinteresēto pusi</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Comment is required</v>
+        <v>Search stakeholders...</v>
       </c>
       <c r="B606" t="str">
-        <v>التعليق مطلوب</v>
+        <v>البحث في أصحاب المصلحة...</v>
       </c>
       <c r="C606" t="str">
-        <v>Komentārs ir obligāts</v>
+        <v>Meklēt ieinteresētās puses...</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Action is sent back</v>
+        <v>Search issues...</v>
       </c>
       <c r="B607" t="str">
-        <v>تم إرجاع الإجراء</v>
+        <v>البحث في القضايا...</v>
       </c>
       <c r="C607" t="str">
-        <v>Darbība ir nosūtīta atpakaļ</v>
+        <v>Meklēt problēmas...</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Failed to send back action</v>
+        <v>All Types</v>
       </c>
       <c r="B608" t="str">
-        <v>فشل في إرجاع الإجراء</v>
+        <v>جميع الأنواع</v>
       </c>
       <c r="C608" t="str">
-        <v>Neizdevās nosūtīt atpakaļ darbību</v>
+        <v>Visi tipi</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Action updated and resubmitted</v>
+        <v>All Status</v>
       </c>
       <c r="B609" t="str">
-        <v>تم تحديث الإجراء وإعادة إرساله</v>
+        <v>جميع الحالات</v>
       </c>
       <c r="C609" t="str">
-        <v>Darbība atjaunināta un atkārtoti iesniegta</v>
+        <v>Visi statusi</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Failed to update action</v>
+        <v>All Categories</v>
       </c>
       <c r="B610" t="str">
-        <v>فشل في تحديث الإجراء</v>
+        <v>جميع الفئات</v>
       </c>
       <c r="C610" t="str">
-        <v>Neizdevās atjaunināt darbību</v>
+        <v>Visas kategorijas</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Saving...</v>
+        <v>All Domains</v>
       </c>
       <c r="B611" t="str">
-        <v>جاري الحفظ...</v>
+        <v>جميع المجالات</v>
       </c>
       <c r="C611" t="str">
-        <v>Saglabā...</v>
+        <v>Visi domēni</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Save &amp; Resubmit</v>
+        <v>No Issues Found</v>
       </c>
       <c r="B612" t="str">
-        <v>حفظ وإعادة الإرسال</v>
+        <v>لم يتم العثور على قضايا</v>
       </c>
       <c r="C612" t="str">
-        <v>Saglabāt un iesniegt atkārtoti</v>
+        <v>Problēmas nav atrastas</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Import Issues</v>
+        <v>Try adjusting your filters to find issues.</v>
       </c>
       <c r="B613" t="str">
-        <v>استيراد القضايا</v>
+        <v>حاول تعديل الفلاتر للعثور على القضايا.</v>
       </c>
       <c r="C613" t="str">
-        <v>Importēt problēmas</v>
+        <v>Mēģiniet pielāgot filtrus, lai atrastu problēmas.</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>CSV file must have a header row and at least one data row</v>
+        <v>Create your first issue to get started.</v>
       </c>
       <c r="B614" t="str">
-        <v>يجب أن يحتوي ملف CSV على صف رأس وصف بيانات واحد على الأقل</v>
+        <v>أنشئ أول قضية للبدء.</v>
       </c>
       <c r="C614" t="str">
-        <v>CSV failam jābūt galvenes rindai un vismaz vienai datu rindai</v>
+        <v>Izveidojiet savu pirmo problēmu, lai sāktu.</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>CSV must have a "title" column</v>
+        <v>Create Action</v>
       </c>
       <c r="B615" t="str">
-        <v>يجب أن يحتوي ملف CSV على عمود "title"</v>
+        <v>إنشاء إجراء</v>
       </c>
       <c r="C615" t="str">
-        <v>CSV ir jābūt kolonnai "title"</v>
+        <v>Izveidot darbību</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Successfully imported</v>
+        <v>View Actions</v>
       </c>
       <c r="B616" t="str">
-        <v>تم الاستيراد بنجاح</v>
+        <v>عرض الإجراءات</v>
       </c>
       <c r="C616" t="str">
-        <v>Veiksmīgi importēts</v>
+        <v>Skatīt darbības</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>issues</v>
+        <v>Review Actions</v>
       </c>
       <c r="B617" t="str">
-        <v>قضايا</v>
+        <v>مراجعة الإجراءات</v>
       </c>
       <c r="C617" t="str">
-        <v>problēmas</v>
+        <v>Pārskatīt darbības</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Error importing issues. Please check the file format.</v>
+        <v>Select stakeholder</v>
       </c>
       <c r="B618" t="str">
-        <v>خطأ في استيراد القضايا. يرجى التحقق من تنسيق الملف.</v>
+        <v>اختر صاحب المصلحة</v>
       </c>
       <c r="C618" t="str">
-        <v>Kļūda importējot problēmas. Lūdzu, pārbaudiet faila formātu.</v>
+        <v>Izvēlieties ieinteresēto pusi</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>File attached to action</v>
+        <v>Need and Expectation</v>
       </c>
       <c r="B619" t="str">
-        <v>تم إرفاق الملف بالإجراء</v>
+        <v>الاحتياجات والتوقعات</v>
       </c>
       <c r="C619" t="str">
-        <v>Fails pievienots darbībai</v>
+        <v>Vajadzība un gaidījums</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Failed to attach file to action</v>
+        <v>Select need/expectation</v>
       </c>
       <c r="B620" t="str">
-        <v>فشل في إرفاق الملف بالإجراء</v>
+        <v>اختر الاحتياج/التوقع</v>
       </c>
       <c r="C620" t="str">
-        <v>Neizdevās pievienot failu darbībai</v>
+        <v>Izvēlieties vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>File deleted successfully</v>
+        <v>Stakeholder Needs and Expectations</v>
       </c>
       <c r="B621" t="str">
-        <v>تم حذف الملف بنجاح</v>
+        <v>احتياجات وتوقعات أصحاب المصلحة</v>
       </c>
       <c r="C621" t="str">
-        <v>Fails veiksmīgi dzēsts</v>
+        <v>Ieinteresēto pušu vajadzības un gaidījumi</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Failed to delete file</v>
+        <v>Add New Domain</v>
       </c>
       <c r="B622" t="str">
-        <v>فشل في حذف الملف</v>
+        <v>إضافة مجال جديد</v>
       </c>
       <c r="C622" t="str">
-        <v>Neizdevās dzēst failu</v>
+        <v>Pievienot jaunu domēnu</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Repository</v>
+        <v>Enter domain name</v>
       </c>
       <c r="B623" t="str">
-        <v>المستودع</v>
+        <v>أدخل اسم المجال</v>
       </c>
       <c r="C623" t="str">
-        <v>Repozitorijs</v>
+        <v>Ievadiet domēna nosaukumu</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Performance Dashboard</v>
+        <v>Add New Category</v>
       </c>
       <c r="B624" t="str">
-        <v>لوحة الأداء</v>
+        <v>إضافة فئة جديدة</v>
       </c>
       <c r="C624" t="str">
-        <v>Veiktspējas panelis</v>
+        <v>Pievienot jaunu kategoriju</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Search By Process ID, Name</v>
+        <v>Add New Issue Type</v>
       </c>
       <c r="B625" t="str">
-        <v>البحث بمعرف العملية أو الاسم</v>
+        <v>إضافة نوع قضية جديد</v>
       </c>
       <c r="C625" t="str">
-        <v>Meklēt pēc procesa ID, nosaukuma</v>
+        <v>Pievienot jaunu problēmas tipu</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>All Owners</v>
+        <v>Issue Type Name</v>
       </c>
       <c r="B626" t="str">
-        <v>جميع المالكين</v>
+        <v>اسم نوع القضية</v>
       </c>
       <c r="C626" t="str">
-        <v>Visi īpašnieki</v>
+        <v>Problēmas tipa nosaukums</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>All Frequencies</v>
+        <v>Enter issue type name</v>
       </c>
       <c r="B627" t="str">
-        <v>جميع الترددات</v>
+        <v>أدخل اسم نوع القضية</v>
       </c>
       <c r="C627" t="str">
-        <v>Visi biežumi</v>
+        <v>Ievadiet problēmas tipa nosaukumu</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Edit Process</v>
+        <v>Link Process</v>
       </c>
       <c r="B628" t="str">
-        <v>تعديل العملية</v>
+        <v>ربط العملية</v>
       </c>
       <c r="C628" t="str">
-        <v>Rediģēt procesu</v>
+        <v>Saistīt procesu</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Confirm Delete</v>
+        <v>No processes found</v>
       </c>
       <c r="B629" t="str">
-        <v>تأكيد الحذف</v>
+        <v>لم يتم العثور على عمليات</v>
       </c>
       <c r="C629" t="str">
-        <v>Apstiprināt dzēšanu</v>
+        <v>Procesi nav atrasti</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Are you sure you want to delete this process? This action cannot be undone.</v>
+        <v>Add New Need/Expectation</v>
       </c>
       <c r="B630" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه العملية؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>إضافة احتياج/توقع جديد</v>
       </c>
       <c r="C630" t="str">
-        <v>Vai tiešām vēlaties dzēst šo procesu? Šo darbību nevar atsaukt.</v>
+        <v>Pievienot jaunu vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Add New Process</v>
+        <v>Need/Expectation</v>
       </c>
       <c r="B631" t="str">
-        <v>إضافة عملية جديدة</v>
+        <v>الاحتياج/التوقع</v>
       </c>
       <c r="C631" t="str">
-        <v>Pievienot jaunu procesu</v>
+        <v>Vajadzība/Gaidījums</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Basic Information</v>
+        <v>Enter need/expectation</v>
       </c>
       <c r="B632" t="str">
-        <v>المعلومات الأساسية</v>
+        <v>أدخل الاحتياج/التوقع</v>
       </c>
       <c r="C632" t="str">
-        <v>Pamatinformācija</v>
+        <v>Ievadiet vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Process Details</v>
+        <v>Enter a new need or expectation type.</v>
       </c>
       <c r="B633" t="str">
-        <v>تفاصيل العملية</v>
+        <v>أدخل نوع احتياج أو توقع جديد.</v>
       </c>
       <c r="C633" t="str">
-        <v>Procesa detaļas</v>
+        <v>Ievadiet jaunu vajadzības vai gaidījumu tipu.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Dependencies &amp; Options</v>
+        <v>Title is required</v>
       </c>
       <c r="B634" t="str">
-        <v>التبعيات والخيارات</v>
+        <v>العنوان مطلوب</v>
       </c>
       <c r="C634" t="str">
-        <v>Atkarības un opcijas</v>
+        <v>Nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>RACI Matrix</v>
+        <v>Issue created successfully</v>
       </c>
       <c r="B635" t="str">
-        <v>مصفوفة RACI</v>
+        <v>تم إنشاء القضية بنجاح</v>
       </c>
       <c r="C635" t="str">
-        <v>RACI matrica</v>
+        <v>Problēma veiksmīgi izveidota</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Enter process name</v>
+        <v>Failed to create issue</v>
       </c>
       <c r="B636" t="str">
-        <v>أدخل اسم العملية</v>
+        <v>فشل في إنشاء القضية</v>
       </c>
       <c r="C636" t="str">
-        <v>Ievadiet procesa nosaukumu</v>
+        <v>Neizdevās izveidot problēmu</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Enter process description</v>
+        <v>Issue updated successfully</v>
       </c>
       <c r="B637" t="str">
-        <v>أدخل وصف العملية</v>
+        <v>تم تحديث القضية بنجاح</v>
       </c>
       <c r="C637" t="str">
-        <v>Ievadiet procesa aprakstu</v>
+        <v>Problēma veiksmīgi atjaunināta</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Nature of Implementation</v>
+        <v>Failed to update issue</v>
       </c>
       <c r="B638" t="str">
-        <v>طبيعة التنفيذ</v>
+        <v>فشل في تحديث القضية</v>
       </c>
       <c r="C638" t="str">
-        <v>Ieviešanas veids</v>
+        <v>Neizdevās atjaunināt problēmu</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Select implementation type</v>
+        <v>Stakeholder updated successfully</v>
       </c>
       <c r="B639" t="str">
-        <v>اختر نوع التنفيذ</v>
+        <v>تم تحديث صاحب المصلحة بنجاح</v>
       </c>
       <c r="C639" t="str">
-        <v>Izvēlieties ieviešanas tipu</v>
+        <v>Ieinteresētā puse veiksmīgi atjaunināta</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Select location</v>
+        <v>Failed to update stakeholder</v>
       </c>
       <c r="B640" t="str">
-        <v>اختر الموقع</v>
+        <v>فشل في تحديث صاحب المصلحة</v>
       </c>
       <c r="C640" t="str">
-        <v>Izvēlieties atrašanās vietu</v>
+        <v>Neizdevās atjaunināt ieinteresēto pusi</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Operational Complexity</v>
+        <v>Open</v>
       </c>
       <c r="B641" t="str">
-        <v>التعقيد التشغيلي</v>
+        <v>مفتوح</v>
       </c>
       <c r="C641" t="str">
-        <v>Operacionālā sarežģītība</v>
+        <v>Atvērts</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Select complexity</v>
+        <v>In Progress</v>
       </c>
       <c r="B642" t="str">
-        <v>اختر التعقيد</v>
+        <v>قيد التنفيذ</v>
       </c>
       <c r="C642" t="str">
-        <v>Izvēlieties sarežģītību</v>
+        <v>Procesā</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Asset Dependency</v>
+        <v>Action type and description are required</v>
       </c>
       <c r="B643" t="str">
-        <v>تبعية الأصول</v>
+        <v>نوع الإجراء والوصف مطلوبان</v>
       </c>
       <c r="C643" t="str">
-        <v>Aktīvu atkarība</v>
+        <v>Darbības tips un apraksts ir obligāti</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>External Dependency</v>
+        <v>Action created successfully</v>
       </c>
       <c r="B644" t="str">
-        <v>تبعية خارجية</v>
+        <v>تم إنشاء الإجراء بنجاح</v>
       </c>
       <c r="C644" t="str">
-        <v>Ārējā atkarība</v>
+        <v>Darbība veiksmīgi izveidota</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>KPI Measurement Required</v>
+        <v>Failed to create action</v>
       </c>
       <c r="B645" t="str">
-        <v>قياس مؤشرات الأداء مطلوب</v>
+        <v>فشل في إنشاء الإجراء</v>
       </c>
       <c r="C645" t="str">
-        <v>Nepieciešams KPI mērījums</v>
+        <v>Neizdevās izveidot darbību</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>PII Capture</v>
+        <v>Action is resolved</v>
       </c>
       <c r="B646" t="str">
-        <v>التقاط البيانات الشخصية</v>
+        <v>تم حل الإجراء</v>
       </c>
       <c r="C646" t="str">
-        <v>PII uztveršana</v>
+        <v>Darbība ir atrisināta</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Auto-generated</v>
+        <v>Failed to resolve action</v>
       </c>
       <c r="B647" t="str">
-        <v>يتم إنشاؤه تلقائياً</v>
+        <v>فشل في حل الإجراء</v>
       </c>
       <c r="C647" t="str">
-        <v>Automātiski ģenerēts</v>
+        <v>Neizdevās atrisināt darbību</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Process created successfully</v>
+        <v>Comment is required</v>
       </c>
       <c r="B648" t="str">
-        <v>تم إنشاء العملية بنجاح</v>
+        <v>التعليق مطلوب</v>
       </c>
       <c r="C648" t="str">
-        <v>Process veiksmīgi izveidots</v>
+        <v>Komentārs ir obligāts</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Failed to create process</v>
+        <v>Action is sent back</v>
       </c>
       <c r="B649" t="str">
-        <v>فشل في إنشاء العملية</v>
+        <v>تم إرجاع الإجراء</v>
       </c>
       <c r="C649" t="str">
-        <v>Neizdevās izveidot procesu</v>
+        <v>Darbība ir nosūtīta atpakaļ</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Process updated successfully</v>
+        <v>Failed to send back action</v>
       </c>
       <c r="B650" t="str">
-        <v>تم تحديث العملية بنجاح</v>
+        <v>فشل في إرجاع الإجراء</v>
       </c>
       <c r="C650" t="str">
-        <v>Process veiksmīgi atjaunināts</v>
+        <v>Neizdevās nosūtīt atpakaļ darbību</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Failed to update process</v>
+        <v>Action updated and resubmitted</v>
       </c>
       <c r="B651" t="str">
-        <v>فشل في تحديث العملية</v>
+        <v>تم تحديث الإجراء وإعادة إرساله</v>
       </c>
       <c r="C651" t="str">
-        <v>Neizdevās atjaunināt procesu</v>
+        <v>Darbība atjaunināta un atkārtoti iesniegta</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Please fill in required fields (Name and Process Type)</v>
+        <v>Failed to update action</v>
       </c>
       <c r="B652" t="str">
-        <v>يرجى ملء الحقول المطلوبة (الاسم ونوع العملية)</v>
+        <v>فشل في تحديث الإجراء</v>
       </c>
       <c r="C652" t="str">
-        <v>Lūdzu, aizpildiet obligātos laukus (Nosaukums un procesa tips)</v>
+        <v>Neizdevās atjaunināt darbību</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Save Changes</v>
+        <v>Saving...</v>
       </c>
       <c r="B653" t="str">
-        <v>حفظ التغييرات</v>
+        <v>جاري الحفظ...</v>
       </c>
       <c r="C653" t="str">
-        <v>Saglabāt izmaiņas</v>
+        <v>Saglabā...</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Reference ID</v>
+        <v>Save &amp; Resubmit</v>
       </c>
       <c r="B654" t="str">
-        <v>المعرف المرجعي</v>
+        <v>حفظ وإعادة الإرسال</v>
       </c>
       <c r="C654" t="str">
-        <v>Atsauces ID</v>
+        <v>Saglabāt un iesniegt atkārtoti</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Process Criticality</v>
+        <v>Import Issues</v>
       </c>
       <c r="B655" t="str">
-        <v>أهمية العملية</v>
+        <v>استيراد القضايا</v>
       </c>
       <c r="C655" t="str">
-        <v>Procesa kritiskums</v>
+        <v>Importēt problēmas</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Process Frequency</v>
+        <v>CSV file must have a header row and at least one data row</v>
       </c>
       <c r="B656" t="str">
-        <v>تكرار العملية</v>
+        <v>يجب أن يحتوي ملف CSV على صف رأس وصف بيانات واحد على الأقل</v>
       </c>
       <c r="C656" t="str">
-        <v>Procesa biežums</v>
+        <v>CSV failam jābūt galvenes rindai un vismaz vienai datu rindai</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Nature Of Implementation</v>
+        <v>CSV must have a "title" column</v>
       </c>
       <c r="B657" t="str">
-        <v>طبيعة التنفيذ</v>
+        <v>يجب أن يحتوي ملف CSV على عمود "title"</v>
       </c>
       <c r="C657" t="str">
-        <v>Ieviešanas veids</v>
+        <v>CSV ir jābūt kolonnai "title"</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>AI Risk</v>
+        <v>Successfully imported</v>
       </c>
       <c r="B658" t="str">
-        <v>مخاطر الذكاء الاصطناعي</v>
+        <v>تم الاستيراد بنجاح</v>
       </c>
       <c r="C658" t="str">
-        <v>AI risks</v>
+        <v>Veiksmīgi importēts</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>AI Risk Evaluation</v>
+        <v>issues</v>
       </c>
       <c r="B659" t="str">
-        <v>تقييم مخاطر الذكاء الاصطناعي</v>
+        <v>قضايا</v>
       </c>
       <c r="C659" t="str">
-        <v>AI risku novērtējums</v>
+        <v>problēmas</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>AI is identifying potential risks...</v>
+        <v>Error importing issues. Please check the file format.</v>
       </c>
       <c r="B660" t="str">
-        <v>الذكاء الاصطناعي يحدد المخاطر المحتملة...</v>
+        <v>خطأ في استيراد القضايا. يرجى التحقق من تنسيق الملف.</v>
       </c>
       <c r="C660" t="str">
-        <v>AI identificē potenciālos riskus...</v>
+        <v>Kļūda importējot problēmas. Lūdzu, pārbaudiet faila formātu.</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>This may take up to 30 seconds</v>
+        <v>File attached to action</v>
       </c>
       <c r="B661" t="str">
-        <v>قد يستغرق هذا ما يصل إلى 30 ثانية</v>
+        <v>تم إرفاق الملف بالإجراء</v>
       </c>
       <c r="C661" t="str">
-        <v>Tas var aizņemt līdz 30 sekundēm</v>
+        <v>Fails pievienots darbībai</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Detected Risks</v>
+        <v>Failed to attach file to action</v>
       </c>
       <c r="B662" t="str">
-        <v>المخاطر المكتشفة</v>
+        <v>فشل في إرفاق الملف بالإجراء</v>
       </c>
       <c r="C662" t="str">
-        <v>Atklātie riski</v>
+        <v>Neizdevās pievienot failu darbībai</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>The AI has identified the following risks, threats, and suggested controls...</v>
+        <v>File deleted successfully</v>
       </c>
       <c r="B663" t="str">
-        <v>حدد الذكاء الاصطناعي المخاطر والتهديدات والضوابط المقترحة التالية...</v>
+        <v>تم حذف الملف بنجاح</v>
       </c>
       <c r="C663" t="str">
-        <v>AI ir identificējis šādus riskus, draudus un ieteiktos kontroles...</v>
+        <v>Fails veiksmīgi dzēsts</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Threats</v>
+        <v>Failed to delete file</v>
       </c>
       <c r="B664" t="str">
-        <v>التهديدات</v>
+        <v>فشل في حذف الملف</v>
       </c>
       <c r="C664" t="str">
-        <v>Draudi</v>
+        <v>Neizdevās dzēst failu</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Suggested Controls</v>
+        <v>Repository</v>
       </c>
       <c r="B665" t="str">
-        <v>الضوابط المقترحة</v>
+        <v>المستودع</v>
       </c>
       <c r="C665" t="str">
-        <v>Ieteiktās kontroles</v>
+        <v>Repozitorijs</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No risks generated yet.</v>
+        <v>Performance Dashboard</v>
       </c>
       <c r="B666" t="str">
-        <v>لم يتم إنشاء مخاطر بعد.</v>
+        <v>لوحة الأداء</v>
       </c>
       <c r="C666" t="str">
-        <v>Vēl nav ģenerēti riski.</v>
+        <v>Veiktspējas panelis</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>AI Risks Generated</v>
+        <v>Search By Process ID, Name</v>
       </c>
       <c r="B667" t="str">
-        <v>تم إنشاء مخاطر الذكاء الاصطناعي</v>
+        <v>البحث بمعرف العملية أو الاسم</v>
       </c>
       <c r="C667" t="str">
-        <v>AI riski ģenerēti</v>
+        <v>Meklēt pēc procesa ID, nosaukuma</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>AI Generation Failed</v>
+        <v>All Owners</v>
       </c>
       <c r="B668" t="str">
-        <v>فشل إنشاء الذكاء الاصطناعي</v>
+        <v>جميع المالكين</v>
       </c>
       <c r="C668" t="str">
-        <v>AI ģenerēšana neizdevās</v>
+        <v>Visi īpašnieki</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Communication with AI service failed.</v>
+        <v>All Frequencies</v>
       </c>
       <c r="B669" t="str">
-        <v>فشل الاتصال بخدمة الذكاء الاصطناعي.</v>
+        <v>جميع الترددات</v>
       </c>
       <c r="C669" t="str">
-        <v>Saziņa ar AI servisu neizdevās.</v>
+        <v>Visi biežumi</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Please try again later.</v>
+        <v>Edit Process</v>
       </c>
       <c r="B670" t="str">
-        <v>يرجى المحاولة مرة أخرى لاحقاً.</v>
+        <v>تعديل العملية</v>
       </c>
       <c r="C670" t="str">
-        <v>Lūdzu, mēģiniet vēlreiz vēlāk.</v>
+        <v>Rediģēt procesu</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Go to Risk Register</v>
+        <v>Confirm Delete</v>
       </c>
       <c r="B671" t="str">
-        <v>الذهاب إلى سجل المخاطر</v>
+        <v>تأكيد الحذف</v>
       </c>
       <c r="C671" t="str">
-        <v>Doties uz risku reģistru</v>
+        <v>Apstiprināt dzēšanu</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Perform BIA</v>
+        <v>Are you sure you want to delete this process? This action cannot be undone.</v>
       </c>
       <c r="B672" t="str">
-        <v>إجراء تحليل تأثير الأعمال</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه العملية؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C672" t="str">
-        <v>Veikt BIA</v>
+        <v>Vai tiešām vēlaties dzēst šo procesu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Submit For Approval</v>
+        <v>Add New Process</v>
       </c>
       <c r="B673" t="str">
-        <v>إرسال للموافقة</v>
+        <v>إضافة عملية جديدة</v>
       </c>
       <c r="C673" t="str">
-        <v>Iesniegt apstiprināšanai</v>
+        <v>Pievienot jaunu procesu</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Status &amp; Approval</v>
+        <v>Basic Information</v>
       </c>
       <c r="B674" t="str">
-        <v>الحالة والموافقة</v>
+        <v>المعلومات الأساسية</v>
       </c>
       <c r="C674" t="str">
-        <v>Statuss un apstiprinājums</v>
+        <v>Pamatinformācija</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Impact Assessment</v>
+        <v>Process Details</v>
       </c>
       <c r="B675" t="str">
-        <v>تقييم التأثير</v>
+        <v>تفاصيل العملية</v>
       </c>
       <c r="C675" t="str">
-        <v>Ietekmes novērtējums</v>
+        <v>Procesa detaļas</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Recovery Metrics</v>
+        <v>Dependencies &amp; Options</v>
       </c>
       <c r="B676" t="str">
-        <v>مقاييس الاستعادة</v>
+        <v>التبعيات والخيارات</v>
       </c>
       <c r="C676" t="str">
-        <v>Atjaunošanas metrikas</v>
+        <v>Atkarības un opcijas</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>BIA Rating</v>
+        <v>RACI Matrix</v>
       </c>
       <c r="B677" t="str">
-        <v>تصنيف تحليل تأثير الأعمال</v>
+        <v>مصفوفة RACI</v>
       </c>
       <c r="C677" t="str">
-        <v>BIA vērtējums</v>
+        <v>RACI matrica</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Impact Rating</v>
+        <v>Enter process name</v>
       </c>
       <c r="B678" t="str">
-        <v>تصنيف التأثير</v>
+        <v>أدخل اسم العملية</v>
       </c>
       <c r="C678" t="str">
-        <v>Ietekmes vērtējums</v>
+        <v>Ievadiet procesa nosaukumu</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Note: The highest rating will be taken</v>
+        <v>Enter process description</v>
       </c>
       <c r="B679" t="str">
-        <v>ملاحظة: سيتم أخذ أعلى تصنيف</v>
+        <v>أدخل وصف العملية</v>
       </c>
       <c r="C679" t="str">
-        <v>Piezīme: Tiks ņemts augstākais vērtējums</v>
+        <v>Ievadiet procesa aprakstu</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>RTO (Recovery Time Objective) - Hours</v>
+        <v>Nature of Implementation</v>
       </c>
       <c r="B680" t="str">
-        <v>هدف وقت الاستعادة - ساعات</v>
+        <v>طبيعة التنفيذ</v>
       </c>
       <c r="C680" t="str">
-        <v>RTO (Atjaunošanas laika mērķis) - Stundas</v>
+        <v>Ieviešanas veids</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>RPO (Recovery Point Objective) - Hours</v>
+        <v>Select implementation type</v>
       </c>
       <c r="B681" t="str">
-        <v>هدف نقطة الاستعادة - ساعات</v>
+        <v>اختر نوع التنفيذ</v>
       </c>
       <c r="C681" t="str">
-        <v>RPO (Atjaunošanas punkta mērķis) - Stundas</v>
+        <v>Izvēlieties ieviešanas tipu</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>N/A</v>
+        <v>Select location</v>
       </c>
       <c r="B682" t="str">
-        <v>غير متاح</v>
+        <v>اختر الموقع</v>
       </c>
       <c r="C682" t="str">
-        <v>Nav piemērojams</v>
+        <v>Izvēlieties atrašanās vietu</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>KPI Details</v>
+        <v>Operational Complexity</v>
       </c>
       <c r="B683" t="str">
-        <v>تفاصيل مؤشرات الأداء</v>
+        <v>التعقيد التشغيلي</v>
       </c>
       <c r="C683" t="str">
-        <v>KPI detaļas</v>
+        <v>Operacionālā sarežģītība</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Performance Chart</v>
+        <v>Select complexity</v>
       </c>
       <c r="B684" t="str">
-        <v>مخطط الأداء</v>
+        <v>اختر التعقيد</v>
       </c>
       <c r="C684" t="str">
-        <v>Veiktspējas diagramma</v>
+        <v>Izvēlieties sarežģītību</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>KPI Configuration</v>
+        <v>Asset Dependency</v>
       </c>
       <c r="B685" t="str">
-        <v>إعدادات مؤشرات الأداء</v>
+        <v>تبعية الأصول</v>
       </c>
       <c r="C685" t="str">
-        <v>KPI konfigurācija</v>
+        <v>Aktīvu atkarība</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>KPI Records</v>
+        <v>External Dependency</v>
       </c>
       <c r="B686" t="str">
-        <v>سجلات مؤشرات الأداء</v>
+        <v>تبعية خارجية</v>
       </c>
       <c r="C686" t="str">
-        <v>KPI ieraksti</v>
+        <v>Ārējā atkarība</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Year</v>
+        <v>KPI Measurement Required</v>
       </c>
       <c r="B687" t="str">
-        <v>السنة</v>
+        <v>قياس مؤشرات الأداء مطلوب</v>
       </c>
       <c r="C687" t="str">
-        <v>Gads</v>
+        <v>Nepieciešams KPI mērījums</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Achieved Value</v>
+        <v>PII Capture</v>
       </c>
       <c r="B688" t="str">
-        <v>القيمة المحققة</v>
+        <v>التقاط البيانات الشخصية</v>
       </c>
       <c r="C688" t="str">
-        <v>Sasniegtā vērtība</v>
+        <v>PII uztveršana</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Expected Value</v>
+        <v>Auto-generated</v>
       </c>
       <c r="B689" t="str">
-        <v>القيمة المتوقعة</v>
+        <v>يتم إنشاؤه تلقائياً</v>
       </c>
       <c r="C689" t="str">
-        <v>Gaidāmā vērtība</v>
+        <v>Automātiski ģenerēts</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>KPI Objective</v>
+        <v>Process created successfully</v>
       </c>
       <c r="B690" t="str">
-        <v>هدف مؤشر الأداء</v>
+        <v>تم إنشاء العملية بنجاح</v>
       </c>
       <c r="C690" t="str">
-        <v>KPI mērķis</v>
+        <v>Process veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Enter Objective</v>
+        <v>Failed to create process</v>
       </c>
       <c r="B691" t="str">
-        <v>أدخل الهدف</v>
+        <v>فشل في إنشاء العملية</v>
       </c>
       <c r="C691" t="str">
-        <v>Ievadiet mērķi</v>
+        <v>Neizdevās izveidot procesu</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>KPI Description</v>
+        <v>Process updated successfully</v>
       </c>
       <c r="B692" t="str">
-        <v>وصف مؤشر الأداء</v>
+        <v>تم تحديث العملية بنجاح</v>
       </c>
       <c r="C692" t="str">
-        <v>KPI apraksts</v>
+        <v>Process veiksmīgi atjaunināts</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Enter Description</v>
+        <v>Failed to update process</v>
       </c>
       <c r="B693" t="str">
-        <v>أدخل الوصف</v>
+        <v>فشل في تحديث العملية</v>
       </c>
       <c r="C693" t="str">
-        <v>Ievadiet aprakstu</v>
+        <v>Neizdevās atjaunināt procesu</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>KPI Data Source</v>
+        <v>Please fill in required fields (Name and Process Type)</v>
       </c>
       <c r="B694" t="str">
-        <v>مصدر بيانات مؤشر الأداء</v>
+        <v>يرجى ملء الحقول المطلوبة (الاسم ونوع العملية)</v>
       </c>
       <c r="C694" t="str">
-        <v>KPI datu avots</v>
+        <v>Lūdzu, aizpildiet obligātos laukus (Nosaukums un procesa tips)</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Enter Data Source</v>
+        <v>Save Changes</v>
       </c>
       <c r="B695" t="str">
-        <v>أدخل مصدر البيانات</v>
+        <v>حفظ التغييرات</v>
       </c>
       <c r="C695" t="str">
-        <v>Ievadiet datu avotu</v>
+        <v>Saglabāt izmaiņas</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>KPI Measurement Formula</v>
+        <v>Reference ID</v>
       </c>
       <c r="B696" t="str">
-        <v>صيغة قياس مؤشر الأداء</v>
+        <v>المعرف المرجعي</v>
       </c>
       <c r="C696" t="str">
-        <v>KPI mērīšanas formula</v>
+        <v>Atsauces ID</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Enter the KPI Calculation Formula</v>
+        <v>Process Criticality</v>
       </c>
       <c r="B697" t="str">
-        <v>أدخل صيغة حساب مؤشر الأداء</v>
+        <v>أهمية العملية</v>
       </c>
       <c r="C697" t="str">
-        <v>Ievadiet KPI aprēķina formulu</v>
+        <v>Procesa kritiskums</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>Targeted Achieved Value</v>
+        <v>Process Frequency</v>
       </c>
       <c r="B698" t="str">
-        <v>القيمة المستهدفة المحققة</v>
+        <v>تكرار العملية</v>
       </c>
       <c r="C698" t="str">
-        <v>Mērķa sasniegtā vērtība</v>
+        <v>Procesa biežums</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>No KPI records yet</v>
+        <v>Nature Of Implementation</v>
       </c>
       <c r="B699" t="str">
-        <v>لا توجد سجلات مؤشرات أداء بعد</v>
+        <v>طبيعة التنفيذ</v>
       </c>
       <c r="C699" t="str">
-        <v>Vēl nav KPI ierakstu</v>
+        <v>Ieviešanas veids</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>No KPI Data</v>
+        <v>AI Risk</v>
       </c>
       <c r="B700" t="str">
-        <v>لا توجد بيانات مؤشرات أداء</v>
+        <v>مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C700" t="str">
-        <v>Nav KPI datu</v>
+        <v>AI risks</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>No processes have KPI measurement enabled...</v>
+        <v>AI Risk Evaluation</v>
       </c>
       <c r="B701" t="str">
-        <v>لم يتم تمكين قياس مؤشرات الأداء لأي عملية...</v>
+        <v>تقييم مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C701" t="str">
-        <v>Nevienam procesam nav iespējots KPI mērījums...</v>
+        <v>AI risku novērtējums</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Unassigned</v>
+        <v>AI is identifying potential risks...</v>
       </c>
       <c r="B702" t="str">
-        <v>غير معين</v>
+        <v>الذكاء الاصطناعي يحدد المخاطر المحتملة...</v>
       </c>
       <c r="C702" t="str">
-        <v>Nepiešķirts</v>
+        <v>AI identificē potenciālos riskus...</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Primary</v>
+        <v>This may take up to 30 seconds</v>
       </c>
       <c r="B703" t="str">
-        <v>أساسي</v>
+        <v>قد يستغرق هذا ما يصل إلى 30 ثانية</v>
       </c>
       <c r="C703" t="str">
-        <v>Primārais</v>
+        <v>Tas var aizņemt līdz 30 sekundēm</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>Supporting</v>
+        <v>Detected Risks</v>
       </c>
       <c r="B704" t="str">
-        <v>داعم</v>
+        <v>المخاطر المكتشفة</v>
       </c>
       <c r="C704" t="str">
-        <v>Atbalsta</v>
+        <v>Atklātie riski</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>Manual</v>
+        <v>The AI has identified the following risks, threats, and suggested controls...</v>
       </c>
       <c r="B705" t="str">
-        <v>يدوي</v>
+        <v>حدد الذكاء الاصطناعي المخاطر والتهديدات والضوابط المقترحة التالية...</v>
       </c>
       <c r="C705" t="str">
-        <v>Manuāls</v>
+        <v>AI ir identificējis šādus riskus, draudus un ieteiktos kontroles...</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>Automated</v>
+        <v>Threats</v>
       </c>
       <c r="B706" t="str">
-        <v>آلي</v>
+        <v>التهديدات</v>
       </c>
       <c r="C706" t="str">
-        <v>Automatizēts</v>
+        <v>Draudi</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>Manual + Automated</v>
+        <v>Suggested Controls</v>
       </c>
       <c r="B707" t="str">
-        <v>يدوي + آلي</v>
+        <v>الضوابط المقترحة</v>
       </c>
       <c r="C707" t="str">
-        <v>Manuāls + Automatizēts</v>
+        <v>Ieteiktās kontroles</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>Branch Office</v>
+        <v>No risks generated yet.</v>
       </c>
       <c r="B708" t="str">
-        <v>فرع المكتب</v>
+        <v>لم يتم إنشاء مخاطر بعد.</v>
       </c>
       <c r="C708" t="str">
-        <v>Filiāles birojs</v>
+        <v>Vēl nav ģenerēti riski.</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>Remote</v>
+        <v>AI Risks Generated</v>
       </c>
       <c r="B709" t="str">
-        <v>عن بعد</v>
+        <v>تم إنشاء مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C709" t="str">
-        <v>Attālināti</v>
+        <v>AI riski ģenerēti</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>Select frequency</v>
+        <v>AI Generation Failed</v>
       </c>
       <c r="B710" t="str">
-        <v>اختر التكرار</v>
+        <v>فشل إنشاء الذكاء الاصطناعي</v>
       </c>
       <c r="C710" t="str">
-        <v>Izvēlieties biežumu</v>
+        <v>AI ģenerēšana neizdevās</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>Bi-annually</v>
+        <v>Communication with AI service failed.</v>
       </c>
       <c r="B711" t="str">
-        <v>نصف سنوي</v>
+        <v>فشل الاتصال بخدمة الذكاء الاصطناعي.</v>
       </c>
       <c r="C711" t="str">
-        <v>Divreiz gadā</v>
+        <v>Saziņa ar AI servisu neizdevās.</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
+        <v>Please try again later.</v>
+      </c>
+      <c r="B712" t="str">
+        <v>يرجى المحاولة مرة أخرى لاحقاً.</v>
+      </c>
+      <c r="C712" t="str">
+        <v>Lūdzu, mēģiniet vēlreiz vēlāk.</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="str">
+        <v>Go to Risk Register</v>
+      </c>
+      <c r="B713" t="str">
+        <v>الذهاب إلى سجل المخاطر</v>
+      </c>
+      <c r="C713" t="str">
+        <v>Doties uz risku reģistru</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v>Perform BIA</v>
+      </c>
+      <c r="B714" t="str">
+        <v>إجراء تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C714" t="str">
+        <v>Veikt BIA</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v>Submit For Approval</v>
+      </c>
+      <c r="B715" t="str">
+        <v>إرسال للموافقة</v>
+      </c>
+      <c r="C715" t="str">
+        <v>Iesniegt apstiprināšanai</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="str">
+        <v>Status &amp; Approval</v>
+      </c>
+      <c r="B716" t="str">
+        <v>الحالة والموافقة</v>
+      </c>
+      <c r="C716" t="str">
+        <v>Statuss un apstiprinājums</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="str">
+        <v>Impact Assessment</v>
+      </c>
+      <c r="B717" t="str">
+        <v>تقييم التأثير</v>
+      </c>
+      <c r="C717" t="str">
+        <v>Ietekmes novērtējums</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="str">
+        <v>Recovery Metrics</v>
+      </c>
+      <c r="B718" t="str">
+        <v>مقاييس الاستعادة</v>
+      </c>
+      <c r="C718" t="str">
+        <v>Atjaunošanas metrikas</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="str">
+        <v>BIA Rating</v>
+      </c>
+      <c r="B719" t="str">
+        <v>تصنيف تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C719" t="str">
+        <v>BIA vērtējums</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="str">
+        <v>Impact Rating</v>
+      </c>
+      <c r="B720" t="str">
+        <v>تصنيف التأثير</v>
+      </c>
+      <c r="C720" t="str">
+        <v>Ietekmes vērtējums</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="str">
+        <v>Note: The highest rating will be taken</v>
+      </c>
+      <c r="B721" t="str">
+        <v>ملاحظة: سيتم أخذ أعلى تصنيف</v>
+      </c>
+      <c r="C721" t="str">
+        <v>Piezīme: Tiks ņemts augstākais vērtējums</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="str">
+        <v>RTO (Recovery Time Objective) - Hours</v>
+      </c>
+      <c r="B722" t="str">
+        <v>هدف وقت الاستعادة - ساعات</v>
+      </c>
+      <c r="C722" t="str">
+        <v>RTO (Atjaunošanas laika mērķis) - Stundas</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="str">
+        <v>RPO (Recovery Point Objective) - Hours</v>
+      </c>
+      <c r="B723" t="str">
+        <v>هدف نقطة الاستعادة - ساعات</v>
+      </c>
+      <c r="C723" t="str">
+        <v>RPO (Atjaunošanas punkta mērķis) - Stundas</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="B724" t="str">
+        <v>غير متاح</v>
+      </c>
+      <c r="C724" t="str">
+        <v>Nav piemērojams</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="str">
+        <v>KPI Details</v>
+      </c>
+      <c r="B725" t="str">
+        <v>تفاصيل مؤشرات الأداء</v>
+      </c>
+      <c r="C725" t="str">
+        <v>KPI detaļas</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="str">
+        <v>Performance Chart</v>
+      </c>
+      <c r="B726" t="str">
+        <v>مخطط الأداء</v>
+      </c>
+      <c r="C726" t="str">
+        <v>Veiktspējas diagramma</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v>KPI Configuration</v>
+      </c>
+      <c r="B727" t="str">
+        <v>إعدادات مؤشرات الأداء</v>
+      </c>
+      <c r="C727" t="str">
+        <v>KPI konfigurācija</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v>KPI Records</v>
+      </c>
+      <c r="B728" t="str">
+        <v>سجلات مؤشرات الأداء</v>
+      </c>
+      <c r="C728" t="str">
+        <v>KPI ieraksti</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v>Year</v>
+      </c>
+      <c r="B729" t="str">
+        <v>السنة</v>
+      </c>
+      <c r="C729" t="str">
+        <v>Gads</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v>Achieved Value</v>
+      </c>
+      <c r="B730" t="str">
+        <v>القيمة المحققة</v>
+      </c>
+      <c r="C730" t="str">
+        <v>Sasniegtā vērtība</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v>Expected Value</v>
+      </c>
+      <c r="B731" t="str">
+        <v>القيمة المتوقعة</v>
+      </c>
+      <c r="C731" t="str">
+        <v>Gaidāmā vērtība</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v>KPI Objective</v>
+      </c>
+      <c r="B732" t="str">
+        <v>هدف مؤشر الأداء</v>
+      </c>
+      <c r="C732" t="str">
+        <v>KPI mērķis</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v>Enter Objective</v>
+      </c>
+      <c r="B733" t="str">
+        <v>أدخل الهدف</v>
+      </c>
+      <c r="C733" t="str">
+        <v>Ievadiet mērķi</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>KPI Description</v>
+      </c>
+      <c r="B734" t="str">
+        <v>وصف مؤشر الأداء</v>
+      </c>
+      <c r="C734" t="str">
+        <v>KPI apraksts</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="str">
+        <v>Enter Description</v>
+      </c>
+      <c r="B735" t="str">
+        <v>أدخل الوصف</v>
+      </c>
+      <c r="C735" t="str">
+        <v>Ievadiet aprakstu</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="str">
+        <v>KPI Data Source</v>
+      </c>
+      <c r="B736" t="str">
+        <v>مصدر بيانات مؤشر الأداء</v>
+      </c>
+      <c r="C736" t="str">
+        <v>KPI datu avots</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="str">
+        <v>Enter Data Source</v>
+      </c>
+      <c r="B737" t="str">
+        <v>أدخل مصدر البيانات</v>
+      </c>
+      <c r="C737" t="str">
+        <v>Ievadiet datu avotu</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="str">
+        <v>KPI Measurement Formula</v>
+      </c>
+      <c r="B738" t="str">
+        <v>صيغة قياس مؤشر الأداء</v>
+      </c>
+      <c r="C738" t="str">
+        <v>KPI mērīšanas formula</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="str">
+        <v>Enter the KPI Calculation Formula</v>
+      </c>
+      <c r="B739" t="str">
+        <v>أدخل صيغة حساب مؤشر الأداء</v>
+      </c>
+      <c r="C739" t="str">
+        <v>Ievadiet KPI aprēķina formulu</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="str">
+        <v>Targeted Achieved Value</v>
+      </c>
+      <c r="B740" t="str">
+        <v>القيمة المستهدفة المحققة</v>
+      </c>
+      <c r="C740" t="str">
+        <v>Mērķa sasniegtā vērtība</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="str">
+        <v>No KPI records yet</v>
+      </c>
+      <c r="B741" t="str">
+        <v>لا توجد سجلات مؤشرات أداء بعد</v>
+      </c>
+      <c r="C741" t="str">
+        <v>Vēl nav KPI ierakstu</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="str">
+        <v>No KPI Data</v>
+      </c>
+      <c r="B742" t="str">
+        <v>لا توجد بيانات مؤشرات أداء</v>
+      </c>
+      <c r="C742" t="str">
+        <v>Nav KPI datu</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="str">
+        <v>No processes have KPI measurement enabled...</v>
+      </c>
+      <c r="B743" t="str">
+        <v>لم يتم تمكين قياس مؤشرات الأداء لأي عملية...</v>
+      </c>
+      <c r="C743" t="str">
+        <v>Nevienam procesam nav iespējots KPI mērījums...</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="B744" t="str">
+        <v>غير معين</v>
+      </c>
+      <c r="C744" t="str">
+        <v>Nepiešķirts</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B745" t="str">
+        <v>أساسي</v>
+      </c>
+      <c r="C745" t="str">
+        <v>Primārais</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="str">
+        <v>Supporting</v>
+      </c>
+      <c r="B746" t="str">
+        <v>داعم</v>
+      </c>
+      <c r="C746" t="str">
+        <v>Atbalsta</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="B747" t="str">
+        <v>يدوي</v>
+      </c>
+      <c r="C747" t="str">
+        <v>Manuāls</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="B748" t="str">
+        <v>آلي</v>
+      </c>
+      <c r="C748" t="str">
+        <v>Automatizēts</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="str">
+        <v>Manual + Automated</v>
+      </c>
+      <c r="B749" t="str">
+        <v>يدوي + آلي</v>
+      </c>
+      <c r="C749" t="str">
+        <v>Manuāls + Automatizēts</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="str">
+        <v>Branch Office</v>
+      </c>
+      <c r="B750" t="str">
+        <v>فرع المكتب</v>
+      </c>
+      <c r="C750" t="str">
+        <v>Filiāles birojs</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="B751" t="str">
+        <v>عن بعد</v>
+      </c>
+      <c r="C751" t="str">
+        <v>Attālināti</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="str">
+        <v>Select frequency</v>
+      </c>
+      <c r="B752" t="str">
+        <v>اختر التكرار</v>
+      </c>
+      <c r="C752" t="str">
+        <v>Izvēlieties biežumu</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="str">
+        <v>Bi-annually</v>
+      </c>
+      <c r="B753" t="str">
+        <v>نصف سنوي</v>
+      </c>
+      <c r="C753" t="str">
+        <v>Divreiz gadā</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="str">
         <v>As needed</v>
       </c>
-      <c r="B712" t="str">
+      <c r="B754" t="str">
         <v>حسب الحاجة</v>
       </c>
-      <c r="C712" t="str">
+      <c r="C754" t="str">
         <v>Pēc vajadzības</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C712"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C754"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C754"/>
+  <dimension ref="A1:C775"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -4817,3890 +4817,4121 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Business Impact Analysis</v>
+        <v>Select Process</v>
       </c>
       <c r="B402" t="str">
-        <v>تحليل تأثير الأعمال</v>
+        <v>اختر العملية</v>
       </c>
       <c r="C402" t="str">
-        <v>Biznesa ietekmes analīze</v>
+        <v>Izvēlēties procesu</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Add BIA</v>
+        <v>No processes available</v>
       </c>
       <c r="B403" t="str">
-        <v>إضافة تحليل تأثير</v>
+        <v>لا توجد عمليات متاحة</v>
       </c>
       <c r="C403" t="str">
-        <v>Pievienot BIA</v>
+        <v>Nav pieejamu procesu</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Criticality</v>
+        <v>Business Impact Analysis</v>
       </c>
       <c r="B404" t="str">
-        <v>الأهمية</v>
+        <v>تحليل تأثير الأعمال</v>
       </c>
       <c r="C404" t="str">
-        <v>Kritiskums</v>
+        <v>Biznesa ietekmes analīze</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Critical</v>
+        <v>Add BIA</v>
       </c>
       <c r="B405" t="str">
-        <v>حرج</v>
+        <v>إضافة تحليل تأثير</v>
       </c>
       <c r="C405" t="str">
-        <v>Kritisks</v>
+        <v>Pievienot BIA</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>High</v>
+        <v>Criticality</v>
       </c>
       <c r="B406" t="str">
-        <v>عالي</v>
+        <v>الأهمية</v>
       </c>
       <c r="C406" t="str">
-        <v>Augsts</v>
+        <v>Kritiskums</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Medium</v>
+        <v>Critical</v>
       </c>
       <c r="B407" t="str">
-        <v>متوسط</v>
+        <v>حرج</v>
       </c>
       <c r="C407" t="str">
-        <v>Vidējs</v>
+        <v>Kritisks</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="B408" t="str">
-        <v>منخفض</v>
+        <v>عالي</v>
       </c>
       <c r="C408" t="str">
-        <v>Zems</v>
+        <v>Augsts</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>RTO (Recovery Time Objective)</v>
+        <v>Medium</v>
       </c>
       <c r="B409" t="str">
-        <v>هدف وقت الاستعادة</v>
+        <v>متوسط</v>
       </c>
       <c r="C409" t="str">
-        <v>RTO (Atjaunošanas laika mērķis)</v>
+        <v>Vidējs</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>RPO (Recovery Point Objective)</v>
+        <v>Low</v>
       </c>
       <c r="B410" t="str">
-        <v>هدف نقطة الاستعادة</v>
+        <v>منخفض</v>
       </c>
       <c r="C410" t="str">
-        <v>RPO (Atjaunošanas punkta mērķis)</v>
+        <v>Zems</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>MTPD (Maximum Tolerable Period of Disruption)</v>
+        <v>RTO (Recovery Time Objective)</v>
       </c>
       <c r="B411" t="str">
-        <v>أقصى فترة تعطل مقبولة</v>
+        <v>هدف وقت الاستعادة</v>
       </c>
       <c r="C411" t="str">
-        <v>MTPD (Maksimālais pieļaujamais pārtraukuma periods)</v>
+        <v>RTO (Atjaunošanas laika mērķis)</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Dependencies</v>
+        <v>RPO (Recovery Point Objective)</v>
       </c>
       <c r="B412" t="str">
-        <v>التبعيات</v>
+        <v>هدف نقطة الاستعادة</v>
       </c>
       <c r="C412" t="str">
-        <v>Atkarības</v>
+        <v>RPO (Atjaunošanas punkta mērķis)</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Resources</v>
+        <v>MTPD (Maximum Tolerable Period of Disruption)</v>
       </c>
       <c r="B413" t="str">
-        <v>الموارد</v>
+        <v>أقصى فترة تعطل مقبولة</v>
       </c>
       <c r="C413" t="str">
-        <v>Resursi</v>
+        <v>MTPD (Maksimālais pieļaujamais pārtraukuma periods)</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Impact Analysis</v>
+        <v>Dependencies</v>
       </c>
       <c r="B414" t="str">
-        <v>تحليل التأثير</v>
+        <v>التبعيات</v>
       </c>
       <c r="C414" t="str">
-        <v>Ietekmes analīze</v>
+        <v>Atkarības</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Search by control code or name...</v>
+        <v>Resources</v>
       </c>
       <c r="B415" t="str">
-        <v>البحث برمز الضابطة أو الاسم...</v>
+        <v>الموارد</v>
       </c>
       <c r="C415" t="str">
-        <v>Meklēt pēc kontroles koda vai nosaukuma...</v>
+        <v>Resursi</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Integrated Framework</v>
+        <v>Impact Analysis</v>
       </c>
       <c r="B416" t="str">
-        <v>الإطار المتكامل</v>
+        <v>تحليل التأثير</v>
       </c>
       <c r="C416" t="str">
-        <v>Integrētais ietvars</v>
+        <v>Ietekmes analīze</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>All Frameworks</v>
+        <v>Search by control code or name...</v>
       </c>
       <c r="B417" t="str">
-        <v>جميع الأطر</v>
+        <v>البحث برمز الضابطة أو الاسم...</v>
       </c>
       <c r="C417" t="str">
-        <v>Visi ietvari</v>
+        <v>Meklēt pēc kontroles koda vai nosaukuma...</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Delete All</v>
+        <v>Integrated Framework</v>
       </c>
       <c r="B418" t="str">
-        <v>حذف الكل</v>
+        <v>الإطار المتكامل</v>
       </c>
       <c r="C418" t="str">
-        <v>Dzēst visu</v>
+        <v>Integrētais ietvars</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>New Control</v>
+        <v>All Frameworks</v>
       </c>
       <c r="B419" t="str">
-        <v>ضابطة جديدة</v>
+        <v>جميع الأطر</v>
       </c>
       <c r="C419" t="str">
-        <v>Jauna kontrole</v>
+        <v>Visi ietvari</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Control Name</v>
+        <v>Delete All</v>
       </c>
       <c r="B420" t="str">
-        <v>اسم الضابطة</v>
+        <v>حذف الكل</v>
       </c>
       <c r="C420" t="str">
-        <v>Kontroles nosaukums</v>
+        <v>Dzēst visu</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Control Code</v>
+        <v>New Control</v>
       </c>
       <c r="B421" t="str">
-        <v>رمز الضابطة</v>
+        <v>ضابطة جديدة</v>
       </c>
       <c r="C421" t="str">
-        <v>Kontroles kods</v>
+        <v>Jauna kontrole</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Functional Grouping</v>
+        <v>Control Name</v>
       </c>
       <c r="B422" t="str">
-        <v>التجميع الوظيفي</v>
+        <v>اسم الضابطة</v>
       </c>
       <c r="C422" t="str">
-        <v>Funkcionālā grupēšana</v>
+        <v>Kontroles nosaukums</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Assignee</v>
+        <v>Control Code</v>
       </c>
       <c r="B423" t="str">
-        <v>المسؤول</v>
+        <v>رمز الضابطة</v>
       </c>
       <c r="C423" t="str">
-        <v>Piešķirtais</v>
+        <v>Kontroles kods</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Domain Name</v>
+        <v>Functional Grouping</v>
       </c>
       <c r="B424" t="str">
-        <v>اسم المجال</v>
+        <v>التجميع الوظيفي</v>
       </c>
       <c r="C424" t="str">
-        <v>Domēna nosaukums</v>
+        <v>Funkcionālā grupēšana</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>No controls found.</v>
+        <v>Assignee</v>
       </c>
       <c r="B425" t="str">
-        <v>لم يتم العثور على ضوابط.</v>
+        <v>المسؤول</v>
       </c>
       <c r="C425" t="str">
-        <v>Kontroles nav atrastas.</v>
+        <v>Piešķirtais</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>No controls</v>
+        <v>Domain Name</v>
       </c>
       <c r="B426" t="str">
-        <v>لا توجد ضوابط</v>
+        <v>اسم المجال</v>
       </c>
       <c r="C426" t="str">
-        <v>Nav kontroles</v>
+        <v>Domēna nosaukums</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Govern</v>
+        <v>No controls found.</v>
       </c>
       <c r="B427" t="str">
-        <v>الحوكمة</v>
+        <v>لم يتم العثور على ضوابط.</v>
       </c>
       <c r="C427" t="str">
-        <v>Pārvaldīt</v>
+        <v>Kontroles nav atrastas.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Identify</v>
+        <v>No controls</v>
       </c>
       <c r="B428" t="str">
-        <v>تحديد</v>
+        <v>لا توجد ضوابط</v>
       </c>
       <c r="C428" t="str">
-        <v>Identificēt</v>
+        <v>Nav kontroles</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Protect</v>
+        <v>Govern</v>
       </c>
       <c r="B429" t="str">
-        <v>حماية</v>
+        <v>الحوكمة</v>
       </c>
       <c r="C429" t="str">
-        <v>Aizsargāt</v>
+        <v>Pārvaldīt</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Detect</v>
+        <v>Identify</v>
       </c>
       <c r="B430" t="str">
-        <v>اكتشاف</v>
+        <v>تحديد</v>
       </c>
       <c r="C430" t="str">
-        <v>Atklāt</v>
+        <v>Identificēt</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Respond</v>
+        <v>Protect</v>
       </c>
       <c r="B431" t="str">
-        <v>استجابة</v>
+        <v>حماية</v>
       </c>
       <c r="C431" t="str">
-        <v>Reaģēt</v>
+        <v>Aizsargāt</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Recover</v>
+        <v>Detect</v>
       </c>
       <c r="B432" t="str">
-        <v>استعادة</v>
+        <v>اكتشاف</v>
       </c>
       <c r="C432" t="str">
-        <v>Atjaunot</v>
+        <v>Atklāt</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>You don't have permission to access Controls.</v>
+        <v>Respond</v>
       </c>
       <c r="B433" t="str">
-        <v>ليس لديك صلاحية للوصول إلى الضوابط.</v>
+        <v>استجابة</v>
       </c>
       <c r="C433" t="str">
-        <v>Jums nav atļaujas piekļūt kontrolēm.</v>
+        <v>Reaģēt</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Policy</v>
+        <v>Recover</v>
       </c>
       <c r="B434" t="str">
-        <v>السياسة</v>
+        <v>استعادة</v>
       </c>
       <c r="C434" t="str">
-        <v>Politika</v>
+        <v>Atjaunot</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Standards</v>
+        <v>You don't have permission to access Controls.</v>
       </c>
       <c r="B435" t="str">
-        <v>المعايير</v>
+        <v>ليس لديك صلاحية للوصول إلى الضوابط.</v>
       </c>
       <c r="C435" t="str">
-        <v>Standarti</v>
+        <v>Jums nav atļaujas piekļūt kontrolēm.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Procedures</v>
+        <v>Policy</v>
       </c>
       <c r="B436" t="str">
-        <v>الإجراءات</v>
+        <v>السياسة</v>
       </c>
       <c r="C436" t="str">
-        <v>Procedūras</v>
+        <v>Politika</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Search by policy name or code...</v>
+        <v>Standards</v>
       </c>
       <c r="B437" t="str">
-        <v>البحث باسم السياسة أو الرمز...</v>
+        <v>المعايير</v>
       </c>
       <c r="C437" t="str">
-        <v>Meklēt pēc politikas nosaukuma vai koda...</v>
+        <v>Standarti</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Search by standard name or code...</v>
+        <v>Procedures</v>
       </c>
       <c r="B438" t="str">
-        <v>البحث باسم المعيار أو الرمز...</v>
+        <v>الإجراءات</v>
       </c>
       <c r="C438" t="str">
-        <v>Meklēt pēc standarta nosaukuma vai koda...</v>
+        <v>Procedūras</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Search by procedure name or code...</v>
+        <v>Search by policy name or code...</v>
       </c>
       <c r="B439" t="str">
-        <v>البحث باسم الإجراء أو الرمز...</v>
+        <v>البحث باسم السياسة أو الرمز...</v>
       </c>
       <c r="C439" t="str">
-        <v>Meklēt pēc procedūras nosaukuma vai koda...</v>
+        <v>Meklēt pēc politikas nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>New Governance</v>
+        <v>Search by standard name or code...</v>
       </c>
       <c r="B440" t="str">
-        <v>حوكمة جديدة</v>
+        <v>البحث باسم المعيار أو الرمز...</v>
       </c>
       <c r="C440" t="str">
-        <v>Jauna pārvaldība</v>
+        <v>Meklēt pēc standarta nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Code</v>
+        <v>Search by procedure name or code...</v>
       </c>
       <c r="B441" t="str">
-        <v>الرمز</v>
+        <v>البحث باسم الإجراء أو الرمز...</v>
       </c>
       <c r="C441" t="str">
-        <v>Kods</v>
+        <v>Meklēt pēc procedūras nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Approver</v>
+        <v>New Governance</v>
       </c>
       <c r="B442" t="str">
-        <v>المعتمد</v>
+        <v>حوكمة جديدة</v>
       </c>
       <c r="C442" t="str">
-        <v>Apstiprinātājs</v>
+        <v>Jauna pārvaldība</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Action</v>
+        <v>Code</v>
       </c>
       <c r="B443" t="str">
-        <v>الإجراء</v>
+        <v>الرمز</v>
       </c>
       <c r="C443" t="str">
-        <v>Darbība</v>
+        <v>Kods</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No policys found</v>
+        <v>Approver</v>
       </c>
       <c r="B444" t="str">
-        <v>لم يتم العثور على سياسات</v>
+        <v>المعتمد</v>
       </c>
       <c r="C444" t="str">
-        <v>Politikas nav atrastas</v>
+        <v>Apstiprinātājs</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>No standards found</v>
+        <v>Action</v>
       </c>
       <c r="B445" t="str">
-        <v>لم يتم العثور على معايير</v>
+        <v>الإجراء</v>
       </c>
       <c r="C445" t="str">
-        <v>Standarti nav atrasti</v>
+        <v>Darbība</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>No procedures found</v>
+        <v>No policys found</v>
       </c>
       <c r="B446" t="str">
-        <v>لم يتم العثور على إجراءات</v>
+        <v>لم يتم العثور على سياسات</v>
       </c>
       <c r="C446" t="str">
-        <v>Procedūras nav atrastas</v>
+        <v>Politikas nav atrastas</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Compliant</v>
+        <v>No standards found</v>
       </c>
       <c r="B447" t="str">
-        <v>متوافق</v>
+        <v>لم يتم العثور على معايير</v>
       </c>
       <c r="C447" t="str">
-        <v>Atbilstošs</v>
+        <v>Standarti nav atrasti</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Non Compliant</v>
+        <v>No procedures found</v>
       </c>
       <c r="B448" t="str">
-        <v>غير متوافق</v>
+        <v>لم يتم العثور على إجراءات</v>
       </c>
       <c r="C448" t="str">
-        <v>Neatbilstošs</v>
+        <v>Procedūras nav atrastas</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Not Applicable</v>
+        <v>Compliant</v>
       </c>
       <c r="B449" t="str">
-        <v>غير قابل للتطبيق</v>
+        <v>متوافق</v>
       </c>
       <c r="C449" t="str">
-        <v>Nav piemērojams</v>
+        <v>Atbilstošs</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Needs Review</v>
+        <v>Non Compliant</v>
       </c>
       <c r="B450" t="str">
-        <v>يحتاج مراجعة</v>
+        <v>غير متوافق</v>
       </c>
       <c r="C450" t="str">
-        <v>Nepieciešama pārskatīšana</v>
+        <v>Neatbilstošs</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Not Uploaded</v>
+        <v>Not Applicable</v>
       </c>
       <c r="B451" t="str">
-        <v>لم يتم الرفع</v>
+        <v>غير قابل للتطبيق</v>
       </c>
       <c r="C451" t="str">
-        <v>Nav augšupielādēts</v>
+        <v>Nav piemērojams</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Pending Approval</v>
+        <v>Needs Review</v>
       </c>
       <c r="B452" t="str">
-        <v>في انتظار الموافقة</v>
+        <v>يحتاج مراجعة</v>
       </c>
       <c r="C452" t="str">
-        <v>Gaida apstiprinājumu</v>
+        <v>Nepieciešama pārskatīšana</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Yearly</v>
+        <v>Not Uploaded</v>
       </c>
       <c r="B453" t="str">
-        <v>سنوي</v>
+        <v>لم يتم الرفع</v>
       </c>
       <c r="C453" t="str">
-        <v>Ikgadējs</v>
+        <v>Nav augšupielādēts</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Half-yearly</v>
+        <v>Pending Approval</v>
       </c>
       <c r="B454" t="str">
-        <v>نصف سنوي</v>
+        <v>في انتظار الموافقة</v>
       </c>
       <c r="C454" t="str">
-        <v>Pusgada</v>
+        <v>Gaida apstiprinājumu</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>New Governance - Step 1 of 3</v>
+        <v>Yearly</v>
       </c>
       <c r="B455" t="str">
-        <v>حوكمة جديدة - الخطوة 1 من 3</v>
+        <v>سنوي</v>
       </c>
       <c r="C455" t="str">
-        <v>Jauna pārvaldība - 1. solis no 3</v>
+        <v>Ikgadējs</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>New Governance - Step 2 of 3</v>
+        <v>Half-yearly</v>
       </c>
       <c r="B456" t="str">
-        <v>حوكمة جديدة - الخطوة 2 من 3</v>
+        <v>نصف سنوي</v>
       </c>
       <c r="C456" t="str">
-        <v>Jauna pārvaldība - 2. solis no 3</v>
+        <v>Pusgada</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>New Governance - Step 3 of 3</v>
+        <v>New Governance - Step 1 of 3</v>
       </c>
       <c r="B457" t="str">
-        <v>حوكمة جديدة - الخطوة 3 من 3</v>
+        <v>حوكمة جديدة - الخطوة 1 من 3</v>
       </c>
       <c r="C457" t="str">
-        <v>Jauna pārvaldība - 3. solis no 3</v>
+        <v>Jauna pārvaldība - 1. solis no 3</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Governance Name</v>
+        <v>New Governance - Step 2 of 3</v>
       </c>
       <c r="B458" t="str">
-        <v>اسم الحوكمة</v>
+        <v>حوكمة جديدة - الخطوة 2 من 3</v>
       </c>
       <c r="C458" t="str">
-        <v>Pārvaldības nosaukums</v>
+        <v>Jauna pārvaldība - 2. solis no 3</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Enter governance name</v>
+        <v>New Governance - Step 3 of 3</v>
       </c>
       <c r="B459" t="str">
-        <v>أدخل اسم الحوكمة</v>
+        <v>حوكمة جديدة - الخطوة 3 من 3</v>
       </c>
       <c r="C459" t="str">
-        <v>Ievadiet pārvaldības nosaukumu</v>
+        <v>Jauna pārvaldība - 3. solis no 3</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>You don't have permission to access Governance.</v>
+        <v>Governance Name</v>
       </c>
       <c r="B460" t="str">
-        <v>ليس لديك صلاحية للوصول إلى الحوكمة.</v>
+        <v>اسم الحوكمة</v>
       </c>
       <c r="C460" t="str">
-        <v>Jums nav atļaujas piekļūt pārvaldībai.</v>
+        <v>Pārvaldības nosaukums</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Standard</v>
+        <v>Enter governance name</v>
       </c>
       <c r="B461" t="str">
-        <v>المعيار</v>
+        <v>أدخل اسم الحوكمة</v>
       </c>
       <c r="C461" t="str">
-        <v>Standarts</v>
+        <v>Ievadiet pārvaldības nosaukumu</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Procedure</v>
+        <v>You don't have permission to access Governance.</v>
       </c>
       <c r="B462" t="str">
-        <v>الإجراء</v>
+        <v>ليس لديك صلاحية للوصول إلى الحوكمة.</v>
       </c>
       <c r="C462" t="str">
-        <v>Procedūra</v>
+        <v>Jums nav atļaujas piekļūt pārvaldībai.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Validated</v>
+        <v>Standard</v>
       </c>
       <c r="B463" t="str">
-        <v>تم التحقق</v>
+        <v>المعيار</v>
       </c>
       <c r="C463" t="str">
-        <v>Validēts</v>
+        <v>Standarts</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Need Attention</v>
+        <v>Procedure</v>
       </c>
       <c r="B464" t="str">
-        <v>يحتاج انتباه</v>
+        <v>الإجراء</v>
       </c>
       <c r="C464" t="str">
-        <v>Nepieciešama uzmanība</v>
+        <v>Procedūra</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Risk ID</v>
+        <v>Validated</v>
       </c>
       <c r="B465" t="str">
-        <v>معرف المخاطر</v>
+        <v>تم التحقق</v>
       </c>
       <c r="C465" t="str">
-        <v>Riska ID</v>
+        <v>Validēts</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Risk Name</v>
+        <v>Need Attention</v>
       </c>
       <c r="B466" t="str">
-        <v>اسم المخاطر</v>
+        <v>يحتاج انتباه</v>
       </c>
       <c r="C466" t="str">
-        <v>Riska nosaukums</v>
+        <v>Nepieciešama uzmanība</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Risk Description</v>
+        <v>Risk ID</v>
       </c>
       <c r="B467" t="str">
-        <v>وصف المخاطر</v>
+        <v>معرف المخاطر</v>
       </c>
       <c r="C467" t="str">
-        <v>Riska apraksts</v>
+        <v>Riska ID</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Risk Category</v>
+        <v>Risk Name</v>
       </c>
       <c r="B468" t="str">
-        <v>فئة المخاطر</v>
+        <v>اسم المخاطر</v>
       </c>
       <c r="C468" t="str">
-        <v>Riska kategorija</v>
+        <v>Riska nosaukums</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Risk Owner</v>
+        <v>Risk Description</v>
       </c>
       <c r="B469" t="str">
-        <v>مالك المخاطر</v>
+        <v>وصف المخاطر</v>
       </c>
       <c r="C469" t="str">
-        <v>Riska īpašnieks</v>
+        <v>Riska apraksts</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Risk Rating</v>
+        <v>Risk Category</v>
       </c>
       <c r="B470" t="str">
-        <v>تصنيف المخاطر</v>
+        <v>فئة المخاطر</v>
       </c>
       <c r="C470" t="str">
-        <v>Riska novērtējums</v>
+        <v>Riska kategorija</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Risk Type</v>
+        <v>Risk Owner</v>
       </c>
       <c r="B471" t="str">
-        <v>نوع المخاطر</v>
+        <v>مالك المخاطر</v>
       </c>
       <c r="C471" t="str">
-        <v>Riska tips</v>
+        <v>Riska īpašnieks</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>You don't have permission to access Risk Register.</v>
+        <v>Risk Rating</v>
       </c>
       <c r="B472" t="str">
-        <v>ليس لديك صلاحية للوصول إلى سجل المخاطر.</v>
+        <v>تصنيف المخاطر</v>
       </c>
       <c r="C472" t="str">
-        <v>Jums nav atļaujas piekļūt risku reģistram.</v>
+        <v>Riska novērtējums</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>RiskRegister</v>
+        <v>Risk Type</v>
       </c>
       <c r="B473" t="str">
-        <v>سجل المخاطر</v>
+        <v>نوع المخاطر</v>
       </c>
       <c r="C473" t="str">
-        <v>Risku reģistrs</v>
+        <v>Riska tips</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Register</v>
+        <v>You don't have permission to access Risk Register.</v>
       </c>
       <c r="B474" t="str">
-        <v>السجل</v>
+        <v>ليس لديك صلاحية للوصول إلى سجل المخاطر.</v>
       </c>
       <c r="C474" t="str">
-        <v>Reģistrs</v>
+        <v>Jums nav atļaujas piekļūt risku reģistram.</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Total Risks</v>
+        <v>RiskRegister</v>
       </c>
       <c r="B475" t="str">
-        <v>إجمالي المخاطر</v>
+        <v>سجل المخاطر</v>
       </c>
       <c r="C475" t="str">
-        <v>Kopējie riski</v>
+        <v>Risku reģistrs</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Open Risks</v>
+        <v>Register</v>
       </c>
       <c r="B476" t="str">
-        <v>المخاطر المفتوحة</v>
+        <v>السجل</v>
       </c>
       <c r="C476" t="str">
-        <v>Atvērtie riski</v>
+        <v>Reģistrs</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Closed Risks</v>
+        <v>Total Risks</v>
       </c>
       <c r="B477" t="str">
-        <v>المخاطر المغلقة</v>
+        <v>إجمالي المخاطر</v>
       </c>
       <c r="C477" t="str">
-        <v>Slēgtie riski</v>
+        <v>Kopējie riski</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Search risks...</v>
+        <v>Open Risks</v>
       </c>
       <c r="B478" t="str">
-        <v>البحث في المخاطر...</v>
+        <v>المخاطر المفتوحة</v>
       </c>
       <c r="C478" t="str">
-        <v>Meklēt riskus...</v>
+        <v>Atvērtie riski</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>All Ratings</v>
+        <v>Closed Risks</v>
       </c>
       <c r="B479" t="str">
-        <v>جميع التصنيفات</v>
+        <v>المخاطر المغلقة</v>
       </c>
       <c r="C479" t="str">
-        <v>Visi vērtējumi</v>
+        <v>Slēgtie riski</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Activity Log</v>
+        <v>Search risks...</v>
       </c>
       <c r="B480" t="str">
-        <v>سجل النشاط</v>
+        <v>البحث في المخاطر...</v>
       </c>
       <c r="C480" t="str">
-        <v>Aktivitāšu žurnāls</v>
+        <v>Meklēt riskus...</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>New Risk</v>
+        <v>All Ratings</v>
       </c>
       <c r="B481" t="str">
-        <v>مخاطر جديدة</v>
+        <v>جميع التصنيفات</v>
       </c>
       <c r="C481" t="str">
-        <v>Jauns risks</v>
+        <v>Visi vērtējumi</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Risk</v>
+        <v>Activity Log</v>
       </c>
       <c r="B482" t="str">
-        <v>المخاطر</v>
+        <v>سجل النشاط</v>
       </c>
       <c r="C482" t="str">
-        <v>Risks</v>
+        <v>Aktivitāšu žurnāls</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Activity</v>
+        <v>New Risk</v>
       </c>
       <c r="B483" t="str">
-        <v>النشاط</v>
+        <v>مخاطر جديدة</v>
       </c>
       <c r="C483" t="str">
-        <v>Aktivitāte</v>
+        <v>Jauns risks</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Actor</v>
+        <v>Risk</v>
       </c>
       <c r="B484" t="str">
-        <v>الفاعل</v>
+        <v>المخاطر</v>
       </c>
       <c r="C484" t="str">
-        <v>Dalībnieks</v>
+        <v>Risks</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>activities</v>
+        <v>Activity</v>
       </c>
       <c r="B485" t="str">
-        <v>الأنشطة</v>
+        <v>النشاط</v>
       </c>
       <c r="C485" t="str">
-        <v>aktivitātes</v>
+        <v>Aktivitāte</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No activity log entries found</v>
+        <v>Actor</v>
       </c>
       <c r="B486" t="str">
-        <v>لم يتم العثور على إدخالات في سجل النشاط</v>
+        <v>الفاعل</v>
       </c>
       <c r="C486" t="str">
-        <v>Nav atrasti aktivitāšu žurnāla ieraksti</v>
+        <v>Dalībnieks</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Import Risks</v>
+        <v>activities</v>
       </c>
       <c r="B487" t="str">
-        <v>استيراد المخاطر</v>
+        <v>الأنشطة</v>
       </c>
       <c r="C487" t="str">
-        <v>Importēt riskus</v>
+        <v>aktivitātes</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Upload a CSV file to import risks</v>
+        <v>No activity log entries found</v>
       </c>
       <c r="B488" t="str">
-        <v>ارفع ملف CSV لاستيراد المخاطر</v>
+        <v>لم يتم العثور على إدخالات في سجل النشاط</v>
       </c>
       <c r="C488" t="str">
-        <v>Augšupielādējiet CSV failu, lai importētu riskus</v>
+        <v>Nav atrasti aktivitāšu žurnāla ieraksti</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Required columns:</v>
+        <v>Import Risks</v>
       </c>
       <c r="B489" t="str">
-        <v>الأعمدة المطلوبة:</v>
+        <v>استيراد المخاطر</v>
       </c>
       <c r="C489" t="str">
-        <v>Obligātās kolonnas:</v>
+        <v>Importēt riskus</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Risk name, Risk description, Risk category, Risk type</v>
+        <v>Upload a CSV file to import risks</v>
       </c>
       <c r="B490" t="str">
-        <v>اسم المخاطر، وصف المخاطر، فئة المخاطر، نوع المخاطر</v>
+        <v>ارفع ملف CSV لاستيراد المخاطر</v>
       </c>
       <c r="C490" t="str">
-        <v>Riska nosaukums, Riska apraksts, Riska kategorija, Riska tips</v>
+        <v>Augšupielādējiet CSV failu, lai importētu riskus</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Click to select a file or drag and drop</v>
+        <v>Required columns:</v>
       </c>
       <c r="B491" t="str">
-        <v>انقر لاختيار ملف أو اسحب وأفلت</v>
+        <v>الأعمدة المطلوبة:</v>
       </c>
       <c r="C491" t="str">
-        <v>Noklikšķiniet, lai izvēlētos failu, vai velciet un nometiet</v>
+        <v>Obligātās kolonnas:</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Select File</v>
+        <v>Risk name, Risk description, Risk category, Risk type</v>
       </c>
       <c r="B492" t="str">
-        <v>اختيار ملف</v>
+        <v>اسم المخاطر، وصف المخاطر، فئة المخاطر، نوع المخاطر</v>
       </c>
       <c r="C492" t="str">
-        <v>Izvēlēties failu</v>
+        <v>Riska nosaukums, Riska apraksts, Riska kategorija, Riska tips</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Confirmation</v>
+        <v>Click to select a file or drag and drop</v>
       </c>
       <c r="B493" t="str">
-        <v>تأكيد</v>
+        <v>انقر لاختيار ملف أو اسحب وأفلت</v>
       </c>
       <c r="C493" t="str">
-        <v>Apstiprinājums</v>
+        <v>Noklikšķiniet, lai izvēlētos failu, vai velciet un nometiet</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Are you sure you want to delete this risk?</v>
+        <v>Select File</v>
       </c>
       <c r="B494" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه المخاطر؟</v>
+        <v>اختيار ملف</v>
       </c>
       <c r="C494" t="str">
-        <v>Vai tiešām vēlaties dzēst šo risku?</v>
+        <v>Izvēlēties failu</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Catastrophic</v>
+        <v>Confirmation</v>
       </c>
       <c r="B495" t="str">
-        <v>كارثي</v>
+        <v>تأكيد</v>
       </c>
       <c r="C495" t="str">
-        <v>Katastrofāls</v>
+        <v>Apstiprinājums</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Very high</v>
+        <v>Are you sure you want to delete this risk?</v>
       </c>
       <c r="B496" t="str">
-        <v>عالي جداً</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه المخاطر؟</v>
       </c>
       <c r="C496" t="str">
-        <v>Ļoti augsts</v>
+        <v>Vai tiešām vēlaties dzēst šo risku?</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Very Low</v>
+        <v>Catastrophic</v>
       </c>
       <c r="B497" t="str">
-        <v>منخفض جداً</v>
+        <v>كارثي</v>
       </c>
       <c r="C497" t="str">
-        <v>Ļoti zems</v>
+        <v>Katastrofāls</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Low Risk</v>
+        <v>Very high</v>
       </c>
       <c r="B498" t="str">
-        <v>مخاطر منخفضة</v>
+        <v>عالي جداً</v>
       </c>
       <c r="C498" t="str">
-        <v>Zems risks</v>
+        <v>Ļoti augsts</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Medium Risk</v>
+        <v>Very Low</v>
       </c>
       <c r="B499" t="str">
-        <v>مخاطر متوسطة</v>
+        <v>منخفض جداً</v>
       </c>
       <c r="C499" t="str">
-        <v>Vidējs risks</v>
+        <v>Ļoti zems</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>High Risk</v>
+        <v>Low Risk</v>
       </c>
       <c r="B500" t="str">
-        <v>مخاطر عالية</v>
+        <v>مخاطر منخفضة</v>
       </c>
       <c r="C500" t="str">
-        <v>Augsts risks</v>
+        <v>Zems risks</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical Risk</v>
+        <v>Medium Risk</v>
       </c>
       <c r="B501" t="str">
-        <v>مخاطر حرجة</v>
+        <v>مخاطر متوسطة</v>
       </c>
       <c r="C501" t="str">
-        <v>Kritisks risks</v>
+        <v>Vidējs risks</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Failed to fetch fieldwork data</v>
+        <v>High Risk</v>
       </c>
       <c r="B502" t="str">
-        <v>فشل في جلب بيانات العمل الميداني</v>
+        <v>مخاطر عالية</v>
       </c>
       <c r="C502" t="str">
-        <v>Neizdevās ielādēt lauka darba datus</v>
+        <v>Augsts risks</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Framework Created Successfully</v>
+        <v>Critical Risk</v>
       </c>
       <c r="B503" t="str">
-        <v>تم إنشاء الإطار بنجاح</v>
+        <v>مخاطر حرجة</v>
       </c>
       <c r="C503" t="str">
-        <v>Ietvars veiksmīgi izveidots</v>
+        <v>Kritisks risks</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Framework</v>
+        <v>Failed to fetch fieldwork data</v>
       </c>
       <c r="B504" t="str">
-        <v>الإطار</v>
+        <v>فشل في جلب بيانات العمل الميداني</v>
       </c>
       <c r="C504" t="str">
-        <v>Ietvars</v>
+        <v>Neizdevās ielādēt lauka darba datus</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Unknown</v>
+        <v>Framework Created Successfully</v>
       </c>
       <c r="B505" t="str">
-        <v>غير معروف</v>
+        <v>تم إنشاء الإطار بنجاح</v>
       </c>
       <c r="C505" t="str">
-        <v>Nezināms</v>
+        <v>Ietvars veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>is ready to use!</v>
+        <v>Framework</v>
       </c>
       <c r="B506" t="str">
-        <v>جاهز للاستخدام!</v>
+        <v>الإطار</v>
       </c>
       <c r="C506" t="str">
-        <v>ir gatavs lietošanai!</v>
+        <v>Ietvars</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Framework was created but couldn't retrieve result. Check dashboard.</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>تم إنشاء الإطار ولكن لم يتم استرجاع النتيجة. تحقق من لوحة التحكم.</v>
+        <v>غير معروف</v>
       </c>
       <c r="C507" t="str">
-        <v>Ietvars izveidots, bet neizdevās iegūt rezultātu. Pārbaudiet vadības paneli.</v>
+        <v>Nezināms</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Framework Generation Failed</v>
+        <v>is ready to use!</v>
       </c>
       <c r="B508" t="str">
-        <v>فشل في إنشاء الإطار</v>
+        <v>جاهز للاستخدام!</v>
       </c>
       <c r="C508" t="str">
-        <v>Ietvara izveide neizdevās</v>
+        <v>ir gatavs lietošanai!</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Validation Error</v>
+        <v>Framework was created but couldn't retrieve result. Check dashboard.</v>
       </c>
       <c r="B509" t="str">
-        <v>خطأ في التحقق</v>
+        <v>تم إنشاء الإطار ولكن لم يتم استرجاع النتيجة. تحقق من لوحة التحكم.</v>
       </c>
       <c r="C509" t="str">
-        <v>Validācijas kļūda</v>
+        <v>Ietvars izveidots, bet neizdevās iegūt rezultātu. Pārbaudiet vadības paneli.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Framework name is required</v>
+        <v>Framework Generation Failed</v>
       </c>
       <c r="B510" t="str">
-        <v>اسم الإطار مطلوب</v>
+        <v>فشل في إنشاء الإطار</v>
       </c>
       <c r="C510" t="str">
-        <v>Ietvara nosaukums ir obligāts</v>
+        <v>Ietvara izveide neizdevās</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Framework Already Exists</v>
+        <v>Validation Error</v>
       </c>
       <c r="B511" t="str">
-        <v>الإطار موجود بالفعل</v>
+        <v>خطأ في التحقق</v>
       </c>
       <c r="C511" t="str">
-        <v>Ietvars jau pastāv</v>
+        <v>Validācijas kļūda</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>A framework named</v>
+        <v>Framework name is required</v>
       </c>
       <c r="B512" t="str">
-        <v>إطار باسم</v>
+        <v>اسم الإطار مطلوب</v>
       </c>
       <c r="C512" t="str">
-        <v>Ietvars ar nosaukumu</v>
+        <v>Ietvara nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>already exists.</v>
+        <v>Framework Already Exists</v>
       </c>
       <c r="B513" t="str">
-        <v>موجود بالفعل.</v>
+        <v>الإطار موجود بالفعل</v>
       </c>
       <c r="C513" t="str">
-        <v>jau pastāv.</v>
+        <v>Ietvars jau pastāv</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Failed to create framework</v>
+        <v>A framework named</v>
       </c>
       <c r="B514" t="str">
-        <v>فشل في إنشاء الإطار</v>
+        <v>إطار باسم</v>
       </c>
       <c r="C514" t="str">
-        <v>Neizdevās izveidot ietvaru</v>
+        <v>Ietvars ar nosaukumu</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Framework Generation Started</v>
+        <v>already exists.</v>
       </c>
       <c r="B515" t="str">
-        <v>بدأ إنشاء الإطار</v>
+        <v>موجود بالفعل.</v>
       </c>
       <c r="C515" t="str">
-        <v>Ietvara izveide sākta</v>
+        <v>jau pastāv.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Polling Stopped</v>
+        <v>Failed to create framework</v>
       </c>
       <c r="B516" t="str">
-        <v>توقف الاستطلاع</v>
+        <v>فشل في إنشاء الإطار</v>
       </c>
       <c r="C516" t="str">
-        <v>Aptauja apturēta</v>
+        <v>Neizdevās izveidot ietvaru</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>You can check the status manually from the dashboard.</v>
+        <v>Framework Generation Started</v>
       </c>
       <c r="B517" t="str">
-        <v>يمكنك التحقق من الحالة يدوياً من لوحة التحكم.</v>
+        <v>بدأ إنشاء الإطار</v>
       </c>
       <c r="C517" t="str">
-        <v>Jūs varat manuāli pārbaudīt statusu vadības panelī.</v>
+        <v>Ietvara izveide sākta</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Regulation</v>
+        <v>Polling Stopped</v>
       </c>
       <c r="B518" t="str">
-        <v>اللائحة</v>
+        <v>توقف الاستطلاع</v>
       </c>
       <c r="C518" t="str">
-        <v>Regula</v>
+        <v>Aptauja apturēta</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Additional details about the framework...</v>
+        <v>You can check the status manually from the dashboard.</v>
       </c>
       <c r="B519" t="str">
-        <v>تفاصيل إضافية حول الإطار...</v>
+        <v>يمكنك التحقق من الحالة يدوياً من لوحة التحكم.</v>
       </c>
       <c r="C519" t="str">
-        <v>Papildu informācija par ietvaru...</v>
+        <v>Jūs varat manuāli pārbaudīt statusu vadības panelī.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Generate Framework</v>
+        <v>Regulation</v>
       </c>
       <c r="B520" t="str">
-        <v>إنشاء الإطار</v>
+        <v>اللائحة</v>
       </c>
       <c r="C520" t="str">
-        <v>Ģenerēt ietvaru</v>
+        <v>Regula</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>QUEUED</v>
+        <v>Additional details about the framework...</v>
       </c>
       <c r="B521" t="str">
-        <v>في قائمة الانتظار</v>
+        <v>تفاصيل إضافية حول الإطار...</v>
       </c>
       <c r="C521" t="str">
-        <v>RINDĀ</v>
+        <v>Papildu informācija par ietvaru...</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>PROCESSING</v>
+        <v>Generate Framework</v>
       </c>
       <c r="B522" t="str">
-        <v>قيد المعالجة</v>
+        <v>إنشاء الإطار</v>
       </c>
       <c r="C522" t="str">
-        <v>APSTRĀDĀ</v>
+        <v>Ģenerēt ietvaru</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>COMPLETED</v>
+        <v>QUEUED</v>
       </c>
       <c r="B523" t="str">
-        <v>مكتمل</v>
+        <v>في قائمة الانتظار</v>
       </c>
       <c r="C523" t="str">
-        <v>PABEIGTS</v>
+        <v>RINDĀ</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>FAILED</v>
+        <v>PROCESSING</v>
       </c>
       <c r="B524" t="str">
-        <v>فشل</v>
+        <v>قيد المعالجة</v>
       </c>
       <c r="C524" t="str">
-        <v>NEIZDEVĀS</v>
+        <v>APSTRĀDĀ</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>PENDING_RESULT</v>
+        <v>COMPLETED</v>
       </c>
       <c r="B525" t="str">
-        <v>في انتظار النتيجة</v>
+        <v>مكتمل</v>
       </c>
       <c r="C525" t="str">
-        <v>GAIDA_REZULTĀTU</v>
+        <v>PABEIGTS</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Overall Compliance Status</v>
+        <v>FAILED</v>
       </c>
       <c r="B526" t="str">
-        <v>حالة الامتثال الشاملة</v>
+        <v>فشل</v>
       </c>
       <c r="C526" t="str">
-        <v>Kopējais atbilstības statuss</v>
+        <v>NEIZDEVĀS</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Overall:</v>
+        <v>PENDING_RESULT</v>
       </c>
       <c r="B527" t="str">
-        <v>الإجمالي:</v>
+        <v>في انتظار النتيجة</v>
       </c>
       <c r="C527" t="str">
-        <v>Kopā:</v>
+        <v>GAIDA_REZULTĀTU</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Loading dashboard...</v>
+        <v>Overall Compliance Status</v>
       </c>
       <c r="B528" t="str">
-        <v>جاري تحميل لوحة التحكم...</v>
+        <v>حالة الامتثال الشاملة</v>
       </c>
       <c r="C528" t="str">
-        <v>Ielādē vadības paneli...</v>
+        <v>Kopējais atbilstības statuss</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Risks</v>
+        <v>Overall:</v>
       </c>
       <c r="B529" t="str">
-        <v>المخاطر</v>
+        <v>الإجمالي:</v>
       </c>
       <c r="C529" t="str">
-        <v>Riski</v>
+        <v>Kopā:</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Exceptions</v>
+        <v>Loading dashboard...</v>
       </c>
       <c r="B530" t="str">
-        <v>الاستثناءات</v>
+        <v>جاري تحميل لوحة التحكم...</v>
       </c>
       <c r="C530" t="str">
-        <v>Izņēmumi</v>
+        <v>Ielādē vadības paneli...</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Risk Assessment Overview</v>
+        <v>Risks</v>
       </c>
       <c r="B531" t="str">
-        <v>نظرة عامة على تقييم المخاطر</v>
+        <v>المخاطر</v>
       </c>
       <c r="C531" t="str">
-        <v>Risku novērtējuma pārskats</v>
+        <v>Riski</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Closed</v>
+        <v>Exceptions</v>
       </c>
       <c r="B532" t="str">
-        <v>مغلق</v>
+        <v>الاستثناءات</v>
       </c>
       <c r="C532" t="str">
-        <v>Slēgts</v>
+        <v>Izņēmumi</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Total</v>
+        <v>Risk Assessment Overview</v>
       </c>
       <c r="B533" t="str">
-        <v>الإجمالي</v>
+        <v>نظرة عامة على تقييم المخاطر</v>
       </c>
       <c r="C533" t="str">
-        <v>Kopā</v>
+        <v>Risku novērtējuma pārskats</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Issue By Category</v>
+        <v>Closed</v>
       </c>
       <c r="B534" t="str">
-        <v>القضايا حسب الفئة</v>
+        <v>مغلق</v>
       </c>
       <c r="C534" t="str">
-        <v>Problēmas pēc kategorijas</v>
+        <v>Slēgts</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Issue By Department</v>
+        <v>Total</v>
       </c>
       <c r="B535" t="str">
-        <v>القضايا حسب القسم</v>
+        <v>الإجمالي</v>
       </c>
       <c r="C535" t="str">
-        <v>Problēmas pēc nodaļas</v>
+        <v>Kopā</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Issue By Domain</v>
+        <v>Issue By Category</v>
       </c>
       <c r="B536" t="str">
-        <v>القضايا حسب المجال</v>
+        <v>القضايا حسب الفئة</v>
       </c>
       <c r="C536" t="str">
-        <v>Problēmas pēc domēna</v>
+        <v>Problēmas pēc kategorijas</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>items</v>
+        <v>Issue By Department</v>
       </c>
       <c r="B537" t="str">
-        <v>عناصر</v>
+        <v>القضايا حسب القسم</v>
       </c>
       <c r="C537" t="str">
-        <v>vienumi</v>
+        <v>Problēmas pēc nodaļas</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Evidence KPI</v>
+        <v>Issue By Domain</v>
       </c>
       <c r="B538" t="str">
-        <v>مؤشرات أداء الأدلة</v>
+        <v>القضايا حسب المجال</v>
       </c>
       <c r="C538" t="str">
-        <v>Pierādījumu KPI</v>
+        <v>Problēmas pēc domēna</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Process KPI</v>
+        <v>items</v>
       </c>
       <c r="B539" t="str">
-        <v>مؤشرات أداء العمليات</v>
+        <v>عناصر</v>
       </c>
       <c r="C539" t="str">
-        <v>Procesu KPI</v>
+        <v>vienumi</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Achieved</v>
+        <v>Evidence KPI</v>
       </c>
       <c r="B540" t="str">
-        <v>محقق</v>
+        <v>مؤشرات أداء الأدلة</v>
       </c>
       <c r="C540" t="str">
-        <v>Sasniegts</v>
+        <v>Pierādījumu KPI</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Scheduled</v>
+        <v>Process KPI</v>
       </c>
       <c r="B541" t="str">
-        <v>مجدول</v>
+        <v>مؤشرات أداء العمليات</v>
       </c>
       <c r="C541" t="str">
-        <v>Ieplānots</v>
+        <v>Procesu KPI</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Missed</v>
+        <v>Achieved</v>
       </c>
       <c r="B542" t="str">
-        <v>فائت</v>
+        <v>محقق</v>
       </c>
       <c r="C542" t="str">
-        <v>Nokavēts</v>
+        <v>Sasniegts</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Overdue</v>
+        <v>Scheduled</v>
       </c>
       <c r="B543" t="str">
-        <v>متأخر</v>
+        <v>مجدول</v>
       </c>
       <c r="C543" t="str">
-        <v>Nokavēts</v>
+        <v>Ieplānots</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Governance Status</v>
+        <v>Missed</v>
       </c>
       <c r="B544" t="str">
-        <v>حالة الحوكمة</v>
+        <v>فائت</v>
       </c>
       <c r="C544" t="str">
-        <v>Pārvaldības statuss</v>
+        <v>Nokavēts</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Exception Status</v>
+        <v>Overdue</v>
       </c>
       <c r="B545" t="str">
-        <v>حالة الاستثناءات</v>
+        <v>متأخر</v>
       </c>
       <c r="C545" t="str">
-        <v>Izņēmumu statuss</v>
+        <v>Nokavēts</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Authorized</v>
+        <v>Governance Status</v>
       </c>
       <c r="B546" t="str">
-        <v>مصرح</v>
+        <v>حالة الحوكمة</v>
       </c>
       <c r="C546" t="str">
-        <v>Autorizēts</v>
+        <v>Pārvaldības statuss</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Showing</v>
+        <v>Exception Status</v>
       </c>
       <c r="B547" t="str">
-        <v>عرض</v>
+        <v>حالة الاستثناءات</v>
       </c>
       <c r="C547" t="str">
-        <v>Rāda</v>
+        <v>Izņēmumu statuss</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>to</v>
+        <v>Authorized</v>
       </c>
       <c r="B548" t="str">
-        <v>إلى</v>
+        <v>مصرح</v>
       </c>
       <c r="C548" t="str">
-        <v>līdz</v>
+        <v>Autorizēts</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>of</v>
+        <v>Showing</v>
       </c>
       <c r="B549" t="str">
-        <v>من</v>
+        <v>عرض</v>
       </c>
       <c r="C549" t="str">
-        <v>no</v>
+        <v>Rāda</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>entries</v>
+        <v>to</v>
       </c>
       <c r="B550" t="str">
-        <v>إدخالات</v>
+        <v>إلى</v>
       </c>
       <c r="C550" t="str">
-        <v>ierakstiem</v>
+        <v>līdz</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>rows per page</v>
+        <v>of</v>
       </c>
       <c r="B551" t="str">
-        <v>صفوف في الصفحة</v>
+        <v>من</v>
       </c>
       <c r="C551" t="str">
-        <v>rindas lapā</v>
+        <v>no</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Page</v>
+        <v>entries</v>
       </c>
       <c r="B552" t="str">
-        <v>صفحة</v>
+        <v>إدخالات</v>
       </c>
       <c r="C552" t="str">
-        <v>Lapa</v>
+        <v>ierakstiem</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>First</v>
+        <v>rows per page</v>
       </c>
       <c r="B553" t="str">
-        <v>الأول</v>
+        <v>صفوف في الصفحة</v>
       </c>
       <c r="C553" t="str">
-        <v>Pirmā</v>
+        <v>rindas lapā</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Last</v>
+        <v>Page</v>
       </c>
       <c r="B554" t="str">
-        <v>الأخير</v>
+        <v>صفحة</v>
       </c>
       <c r="C554" t="str">
-        <v>Pēdējā</v>
+        <v>Lapa</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Go to page</v>
+        <v>First</v>
       </c>
       <c r="B555" t="str">
-        <v>انتقل إلى الصفحة</v>
+        <v>الأول</v>
       </c>
       <c r="C555" t="str">
-        <v>Doties uz lapu</v>
+        <v>Pirmā</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Search...</v>
+        <v>Last</v>
       </c>
       <c r="B556" t="str">
-        <v>بحث...</v>
+        <v>الأخير</v>
       </c>
       <c r="C556" t="str">
-        <v>Meklēt...</v>
+        <v>Pēdējā</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>No data</v>
+        <v>Go to page</v>
       </c>
       <c r="B557" t="str">
-        <v>لا توجد بيانات</v>
+        <v>انتقل إلى الصفحة</v>
       </c>
       <c r="C557" t="str">
-        <v>Nav datu</v>
+        <v>Doties uz lapu</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Search By Name</v>
+        <v>Search...</v>
       </c>
       <c r="B558" t="str">
-        <v>البحث بالاسم</v>
+        <v>بحث...</v>
       </c>
       <c r="C558" t="str">
-        <v>Meklēt pēc nosaukuma</v>
+        <v>Meklēt...</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Search By Control Code , Name</v>
+        <v>No data</v>
       </c>
       <c r="B559" t="str">
-        <v>البحث برمز الضابطة أو الاسم</v>
+        <v>لا توجد بيانات</v>
       </c>
       <c r="C559" t="str">
-        <v>Meklēt pēc kontroles koda, nosaukuma</v>
+        <v>Nav datu</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>This field is required</v>
+        <v>Search By Name</v>
       </c>
       <c r="B560" t="str">
-        <v>هذا الحقل مطلوب</v>
+        <v>البحث بالاسم</v>
       </c>
       <c r="C560" t="str">
-        <v>Šis lauks ir obligāts</v>
+        <v>Meklēt pēc nosaukuma</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Invalid email format</v>
+        <v>Search By Control Code , Name</v>
       </c>
       <c r="B561" t="str">
-        <v>تنسيق البريد الإلكتروني غير صالح</v>
+        <v>البحث برمز الضابطة أو الاسم</v>
       </c>
       <c r="C561" t="str">
-        <v>Nederīgs e-pasta formāts</v>
+        <v>Meklēt pēc kontroles koda, nosaukuma</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Password must be at least 8 characters</v>
+        <v>This field is required</v>
       </c>
       <c r="B562" t="str">
-        <v>يجب أن تكون كلمة المرور 8 أحرف على الأقل</v>
+        <v>هذا الحقل مطلوب</v>
       </c>
       <c r="C562" t="str">
-        <v>Parolei jābūt vismaz 8 rakstzīmēm</v>
+        <v>Šis lauks ir obligāts</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Passwords do not match</v>
+        <v>Invalid email format</v>
       </c>
       <c r="B563" t="str">
-        <v>كلمات المرور غير متطابقة</v>
+        <v>تنسيق البريد الإلكتروني غير صالح</v>
       </c>
       <c r="C563" t="str">
-        <v>Paroles nesakrīt</v>
+        <v>Nederīgs e-pasta formāts</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Please enter a valid value</v>
+        <v>Password must be at least 8 characters</v>
       </c>
       <c r="B564" t="str">
-        <v>يرجى إدخال قيمة صالحة</v>
+        <v>يجب أن تكون كلمة المرور 8 أحرف على الأقل</v>
       </c>
       <c r="C564" t="str">
-        <v>Lūdzu, ievadiet derīgu vērtību</v>
+        <v>Parolei jābūt vismaz 8 rakstzīmēm</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Maximum length exceeded</v>
+        <v>Passwords do not match</v>
       </c>
       <c r="B565" t="str">
-        <v>تم تجاوز الحد الأقصى للطول</v>
+        <v>كلمات المرور غير متطابقة</v>
       </c>
       <c r="C565" t="str">
-        <v>Pārsniegts maksimālais garums</v>
+        <v>Paroles nesakrīt</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Minimum length not met</v>
+        <v>Please enter a valid value</v>
       </c>
       <c r="B566" t="str">
-        <v>لم يتم تحقيق الحد الأدنى للطول</v>
+        <v>يرجى إدخال قيمة صالحة</v>
       </c>
       <c r="C566" t="str">
-        <v>Nav sasniegts minimālais garums</v>
+        <v>Lūdzu, ievadiet derīgu vērtību</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>An error occurred</v>
+        <v>Maximum length exceeded</v>
       </c>
       <c r="B567" t="str">
-        <v>حدث خطأ</v>
+        <v>تم تجاوز الحد الأقصى للطول</v>
       </c>
       <c r="C567" t="str">
-        <v>Radās kļūda</v>
+        <v>Pārsniegts maksimālais garums</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Not found</v>
+        <v>Minimum length not met</v>
       </c>
       <c r="B568" t="str">
-        <v>غير موجود</v>
+        <v>لم يتم تحقيق الحد الأدنى للطول</v>
       </c>
       <c r="C568" t="str">
-        <v>Nav atrasts</v>
+        <v>Nav sasniegts minimālais garums</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Unauthorized</v>
+        <v>An error occurred</v>
       </c>
       <c r="B569" t="str">
-        <v>غير مصرح</v>
+        <v>حدث خطأ</v>
       </c>
       <c r="C569" t="str">
-        <v>Nav autorizēts</v>
+        <v>Radās kļūda</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Forbidden</v>
+        <v>Not found</v>
       </c>
       <c r="B570" t="str">
-        <v>محظور</v>
+        <v>غير موجود</v>
       </c>
       <c r="C570" t="str">
-        <v>Aizliegts</v>
+        <v>Nav atrasts</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Network error</v>
+        <v>Unauthorized</v>
       </c>
       <c r="B571" t="str">
-        <v>خطأ في الشبكة</v>
+        <v>غير مصرح</v>
       </c>
       <c r="C571" t="str">
-        <v>Tīkla kļūda</v>
+        <v>Nav autorizēts</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Server error</v>
+        <v>Forbidden</v>
       </c>
       <c r="B572" t="str">
-        <v>خطأ في الخادم</v>
+        <v>محظور</v>
       </c>
       <c r="C572" t="str">
-        <v>Servera kļūda</v>
+        <v>Aizliegts</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Session expired</v>
+        <v>Network error</v>
       </c>
       <c r="B573" t="str">
-        <v>انتهت صلاحية الجلسة</v>
+        <v>خطأ في الشبكة</v>
       </c>
       <c r="C573" t="str">
-        <v>Sesija ir beigusies</v>
+        <v>Tīkla kļūda</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Please login again</v>
+        <v>Server error</v>
       </c>
       <c r="B574" t="str">
-        <v>يرجى تسجيل الدخول مرة أخرى</v>
+        <v>خطأ في الخادم</v>
       </c>
       <c r="C574" t="str">
-        <v>Lūdzu, piesakieties vēlreiz</v>
+        <v>Servera kļūda</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Saved successfully</v>
+        <v>Session expired</v>
       </c>
       <c r="B575" t="str">
-        <v>تم الحفظ بنجاح</v>
+        <v>انتهت صلاحية الجلسة</v>
       </c>
       <c r="C575" t="str">
-        <v>Veiksmīgi saglabāts</v>
+        <v>Sesija ir beigusies</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Deleted successfully</v>
+        <v>Please login again</v>
       </c>
       <c r="B576" t="str">
-        <v>تم الحذف بنجاح</v>
+        <v>يرجى تسجيل الدخول مرة أخرى</v>
       </c>
       <c r="C576" t="str">
-        <v>Veiksmīgi dzēsts</v>
+        <v>Lūdzu, piesakieties vēlreiz</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Updated successfully</v>
+        <v>Saved successfully</v>
       </c>
       <c r="B577" t="str">
-        <v>تم التحديث بنجاح</v>
+        <v>تم الحفظ بنجاح</v>
       </c>
       <c r="C577" t="str">
-        <v>Veiksmīgi atjaunināts</v>
+        <v>Veiksmīgi saglabāts</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Created successfully</v>
+        <v>Deleted successfully</v>
       </c>
       <c r="B578" t="str">
-        <v>تم الإنشاء بنجاح</v>
+        <v>تم الحذف بنجاح</v>
       </c>
       <c r="C578" t="str">
-        <v>Veiksmīgi izveidots</v>
+        <v>Veiksmīgi dzēsts</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Operation completed</v>
+        <v>Updated successfully</v>
       </c>
       <c r="B579" t="str">
-        <v>تمت العملية</v>
+        <v>تم التحديث بنجاح</v>
       </c>
       <c r="C579" t="str">
-        <v>Darbība pabeigta</v>
+        <v>Veiksmīgi atjaunināts</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Today</v>
+        <v>Created successfully</v>
       </c>
       <c r="B580" t="str">
-        <v>اليوم</v>
+        <v>تم الإنشاء بنجاح</v>
       </c>
       <c r="C580" t="str">
-        <v>Šodien</v>
+        <v>Veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Tomorrow</v>
+        <v>Operation completed</v>
       </c>
       <c r="B581" t="str">
-        <v>غداً</v>
+        <v>تمت العملية</v>
       </c>
       <c r="C581" t="str">
-        <v>Rīt</v>
+        <v>Darbība pabeigta</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Select date</v>
+        <v>Today</v>
       </c>
       <c r="B582" t="str">
-        <v>اختر التاريخ</v>
+        <v>اليوم</v>
       </c>
       <c r="C582" t="str">
-        <v>Izvēlieties datumu</v>
+        <v>Šodien</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Select time</v>
+        <v>Tomorrow</v>
       </c>
       <c r="B583" t="str">
-        <v>اختر الوقت</v>
+        <v>غداً</v>
       </c>
       <c r="C583" t="str">
-        <v>Izvēlieties laiku</v>
+        <v>Rīt</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>From</v>
+        <v>Select date</v>
       </c>
       <c r="B584" t="str">
-        <v>من</v>
+        <v>اختر التاريخ</v>
       </c>
       <c r="C584" t="str">
-        <v>No</v>
+        <v>Izvēlieties datumu</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>To</v>
+        <v>Select time</v>
       </c>
       <c r="B585" t="str">
-        <v>إلى</v>
+        <v>اختر الوقت</v>
       </c>
       <c r="C585" t="str">
-        <v>Līdz</v>
+        <v>Izvēlieties laiku</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Start Date</v>
+        <v>From</v>
       </c>
       <c r="B586" t="str">
-        <v>تاريخ البداية</v>
+        <v>من</v>
       </c>
       <c r="C586" t="str">
-        <v>Sākuma datums</v>
+        <v>No</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>End Date</v>
+        <v>To</v>
       </c>
       <c r="B587" t="str">
-        <v>تاريخ النهاية</v>
+        <v>إلى</v>
       </c>
       <c r="C587" t="str">
-        <v>Beigu datums</v>
+        <v>Līdz</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Select file</v>
+        <v>Start Date</v>
       </c>
       <c r="B588" t="str">
-        <v>اختر ملف</v>
+        <v>تاريخ البداية</v>
       </c>
       <c r="C588" t="str">
-        <v>Izvēlieties failu</v>
+        <v>Sākuma datums</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Select files</v>
+        <v>End Date</v>
       </c>
       <c r="B589" t="str">
-        <v>اختر ملفات</v>
+        <v>تاريخ النهاية</v>
       </c>
       <c r="C589" t="str">
-        <v>Izvēlieties failus</v>
+        <v>Beigu datums</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Drop files here</v>
+        <v>Select file</v>
       </c>
       <c r="B590" t="str">
-        <v>أسقط الملفات هنا</v>
+        <v>اختر ملف</v>
       </c>
       <c r="C590" t="str">
-        <v>Nometiet failus šeit</v>
+        <v>Izvēlieties failu</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>or click to select</v>
+        <v>Select files</v>
       </c>
       <c r="B591" t="str">
-        <v>أو انقر للاختيار</v>
+        <v>اختر ملفات</v>
       </c>
       <c r="C591" t="str">
-        <v>vai noklikšķiniet, lai izvēlētos</v>
+        <v>Izvēlieties failus</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>File uploaded successfully</v>
+        <v>Drop files here</v>
       </c>
       <c r="B592" t="str">
-        <v>تم رفع الملف بنجاح</v>
+        <v>أسقط الملفات هنا</v>
       </c>
       <c r="C592" t="str">
-        <v>Fails veiksmīgi augšupielādēts</v>
+        <v>Nometiet failus šeit</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Failed to upload file</v>
+        <v>or click to select</v>
       </c>
       <c r="B593" t="str">
-        <v>فشل في رفع الملف</v>
+        <v>أو انقر للاختيار</v>
       </c>
       <c r="C593" t="str">
-        <v>Neizdevās augšupielādēt failu</v>
+        <v>vai noklikšķiniet, lai izvēlētos</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>File size too large</v>
+        <v>File uploaded successfully</v>
       </c>
       <c r="B594" t="str">
-        <v>حجم الملف كبير جداً</v>
+        <v>تم رفع الملف بنجاح</v>
       </c>
       <c r="C594" t="str">
-        <v>Faila izmērs ir pārāk liels</v>
+        <v>Fails veiksmīgi augšupielādēts</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Invalid file type</v>
+        <v>Failed to upload file</v>
       </c>
       <c r="B595" t="str">
-        <v>نوع الملف غير صالح</v>
+        <v>فشل في رفع الملف</v>
       </c>
       <c r="C595" t="str">
-        <v>Nederīgs faila tips</v>
+        <v>Neizdevās augšupielādēt failu</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Edit Issue</v>
+        <v>File size too large</v>
       </c>
       <c r="B596" t="str">
-        <v>تعديل القضية</v>
+        <v>حجم الملف كبير جداً</v>
       </c>
       <c r="C596" t="str">
-        <v>Rediģēt problēmu</v>
+        <v>Faila izmērs ir pārāk liels</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Enter issue title</v>
+        <v>Invalid file type</v>
       </c>
       <c r="B597" t="str">
-        <v>أدخل عنوان القضية</v>
+        <v>نوع الملف غير صالح</v>
       </c>
       <c r="C597" t="str">
-        <v>Ievadiet problēmas nosaukumu</v>
+        <v>Nederīgs faila tips</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Select domain</v>
+        <v>Edit Issue</v>
       </c>
       <c r="B598" t="str">
-        <v>اختر المجال</v>
+        <v>تعديل القضية</v>
       </c>
       <c r="C598" t="str">
-        <v>Izvēlieties domēnu</v>
+        <v>Rediģēt problēmu</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Issue Owner</v>
+        <v>Enter issue title</v>
       </c>
       <c r="B599" t="str">
-        <v>مالك القضية</v>
+        <v>أدخل عنوان القضية</v>
       </c>
       <c r="C599" t="str">
-        <v>Problēmas īpašnieks</v>
+        <v>Ievadiet problēmas nosaukumu</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Select owner</v>
+        <v>Select domain</v>
       </c>
       <c r="B600" t="str">
-        <v>اختر المالك</v>
+        <v>اختر المجال</v>
       </c>
       <c r="C600" t="str">
-        <v>Izvēlieties īpašnieku</v>
+        <v>Izvēlieties domēnu</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Select department first</v>
+        <v>Issue Owner</v>
       </c>
       <c r="B601" t="str">
-        <v>اختر القسم أولاً</v>
+        <v>مالك القضية</v>
       </c>
       <c r="C601" t="str">
-        <v>Vispirms izvēlieties nodaļu</v>
+        <v>Problēmas īpašnieks</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Select type</v>
+        <v>Select owner</v>
       </c>
       <c r="B602" t="str">
-        <v>اختر النوع</v>
+        <v>اختر المالك</v>
       </c>
       <c r="C602" t="str">
-        <v>Izvēlieties tipu</v>
+        <v>Izvēlieties īpašnieku</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Enter issue description</v>
+        <v>Select department first</v>
       </c>
       <c r="B603" t="str">
-        <v>أدخل وصف القضية</v>
+        <v>اختر القسم أولاً</v>
       </c>
       <c r="C603" t="str">
-        <v>Ievadiet problēmas aprakstu</v>
+        <v>Vispirms izvēlieties nodaļu</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>New Stakeholder</v>
+        <v>Select type</v>
       </c>
       <c r="B604" t="str">
-        <v>صاحب مصلحة جديد</v>
+        <v>اختر النوع</v>
       </c>
       <c r="C604" t="str">
-        <v>Jauna ieinteresētā puse</v>
+        <v>Izvēlieties tipu</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Edit Stakeholder</v>
+        <v>Enter issue description</v>
       </c>
       <c r="B605" t="str">
-        <v>تعديل صاحب المصلحة</v>
+        <v>أدخل وصف القضية</v>
       </c>
       <c r="C605" t="str">
-        <v>Rediģēt ieinteresēto pusi</v>
+        <v>Ievadiet problēmas aprakstu</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Search stakeholders...</v>
+        <v>New Stakeholder</v>
       </c>
       <c r="B606" t="str">
-        <v>البحث في أصحاب المصلحة...</v>
+        <v>صاحب مصلحة جديد</v>
       </c>
       <c r="C606" t="str">
-        <v>Meklēt ieinteresētās puses...</v>
+        <v>Jauna ieinteresētā puse</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Search issues...</v>
+        <v>Edit Stakeholder</v>
       </c>
       <c r="B607" t="str">
-        <v>البحث في القضايا...</v>
+        <v>تعديل صاحب المصلحة</v>
       </c>
       <c r="C607" t="str">
-        <v>Meklēt problēmas...</v>
+        <v>Rediģēt ieinteresēto pusi</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>All Types</v>
+        <v>Search stakeholders...</v>
       </c>
       <c r="B608" t="str">
-        <v>جميع الأنواع</v>
+        <v>البحث في أصحاب المصلحة...</v>
       </c>
       <c r="C608" t="str">
-        <v>Visi tipi</v>
+        <v>Meklēt ieinteresētās puses...</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>All Status</v>
+        <v>Search issues...</v>
       </c>
       <c r="B609" t="str">
-        <v>جميع الحالات</v>
+        <v>البحث في القضايا...</v>
       </c>
       <c r="C609" t="str">
-        <v>Visi statusi</v>
+        <v>Meklēt problēmas...</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>All Categories</v>
+        <v>All Types</v>
       </c>
       <c r="B610" t="str">
-        <v>جميع الفئات</v>
+        <v>جميع الأنواع</v>
       </c>
       <c r="C610" t="str">
-        <v>Visas kategorijas</v>
+        <v>Visi tipi</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>All Domains</v>
+        <v>All Status</v>
       </c>
       <c r="B611" t="str">
-        <v>جميع المجالات</v>
+        <v>جميع الحالات</v>
       </c>
       <c r="C611" t="str">
-        <v>Visi domēni</v>
+        <v>Visi statusi</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>No Issues Found</v>
+        <v>All Categories</v>
       </c>
       <c r="B612" t="str">
-        <v>لم يتم العثور على قضايا</v>
+        <v>جميع الفئات</v>
       </c>
       <c r="C612" t="str">
-        <v>Problēmas nav atrastas</v>
+        <v>Visas kategorijas</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Try adjusting your filters to find issues.</v>
+        <v>All Domains</v>
       </c>
       <c r="B613" t="str">
-        <v>حاول تعديل الفلاتر للعثور على القضايا.</v>
+        <v>جميع المجالات</v>
       </c>
       <c r="C613" t="str">
-        <v>Mēģiniet pielāgot filtrus, lai atrastu problēmas.</v>
+        <v>Visi domēni</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Create your first issue to get started.</v>
+        <v>No Issues Found</v>
       </c>
       <c r="B614" t="str">
-        <v>أنشئ أول قضية للبدء.</v>
+        <v>لم يتم العثور على قضايا</v>
       </c>
       <c r="C614" t="str">
-        <v>Izveidojiet savu pirmo problēmu, lai sāktu.</v>
+        <v>Problēmas nav atrastas</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Create Action</v>
+        <v>Try adjusting your filters to find issues.</v>
       </c>
       <c r="B615" t="str">
-        <v>إنشاء إجراء</v>
+        <v>حاول تعديل الفلاتر للعثور على القضايا.</v>
       </c>
       <c r="C615" t="str">
-        <v>Izveidot darbību</v>
+        <v>Mēģiniet pielāgot filtrus, lai atrastu problēmas.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>View Actions</v>
+        <v>Create your first issue to get started.</v>
       </c>
       <c r="B616" t="str">
-        <v>عرض الإجراءات</v>
+        <v>أنشئ أول قضية للبدء.</v>
       </c>
       <c r="C616" t="str">
-        <v>Skatīt darbības</v>
+        <v>Izveidojiet savu pirmo problēmu, lai sāktu.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Review Actions</v>
+        <v>Create Action</v>
       </c>
       <c r="B617" t="str">
-        <v>مراجعة الإجراءات</v>
+        <v>إنشاء إجراء</v>
       </c>
       <c r="C617" t="str">
-        <v>Pārskatīt darbības</v>
+        <v>Izveidot darbību</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Select stakeholder</v>
+        <v>View Actions</v>
       </c>
       <c r="B618" t="str">
-        <v>اختر صاحب المصلحة</v>
+        <v>عرض الإجراءات</v>
       </c>
       <c r="C618" t="str">
-        <v>Izvēlieties ieinteresēto pusi</v>
+        <v>Skatīt darbības</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Need and Expectation</v>
+        <v>Review Actions</v>
       </c>
       <c r="B619" t="str">
-        <v>الاحتياجات والتوقعات</v>
+        <v>مراجعة الإجراءات</v>
       </c>
       <c r="C619" t="str">
-        <v>Vajadzība un gaidījums</v>
+        <v>Pārskatīt darbības</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Select need/expectation</v>
+        <v>Select stakeholder</v>
       </c>
       <c r="B620" t="str">
-        <v>اختر الاحتياج/التوقع</v>
+        <v>اختر صاحب المصلحة</v>
       </c>
       <c r="C620" t="str">
-        <v>Izvēlieties vajadzību/gaidījumu</v>
+        <v>Izvēlieties ieinteresēto pusi</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Stakeholder Needs and Expectations</v>
+        <v>Need and Expectation</v>
       </c>
       <c r="B621" t="str">
-        <v>احتياجات وتوقعات أصحاب المصلحة</v>
+        <v>الاحتياجات والتوقعات</v>
       </c>
       <c r="C621" t="str">
-        <v>Ieinteresēto pušu vajadzības un gaidījumi</v>
+        <v>Vajadzība un gaidījums</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Add New Domain</v>
+        <v>Select need/expectation</v>
       </c>
       <c r="B622" t="str">
-        <v>إضافة مجال جديد</v>
+        <v>اختر الاحتياج/التوقع</v>
       </c>
       <c r="C622" t="str">
-        <v>Pievienot jaunu domēnu</v>
+        <v>Izvēlieties vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Enter domain name</v>
+        <v>Stakeholder Needs and Expectations</v>
       </c>
       <c r="B623" t="str">
-        <v>أدخل اسم المجال</v>
+        <v>احتياجات وتوقعات أصحاب المصلحة</v>
       </c>
       <c r="C623" t="str">
-        <v>Ievadiet domēna nosaukumu</v>
+        <v>Ieinteresēto pušu vajadzības un gaidījumi</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Add New Category</v>
+        <v>Add New Domain</v>
       </c>
       <c r="B624" t="str">
-        <v>إضافة فئة جديدة</v>
+        <v>إضافة مجال جديد</v>
       </c>
       <c r="C624" t="str">
-        <v>Pievienot jaunu kategoriju</v>
+        <v>Pievienot jaunu domēnu</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Add New Issue Type</v>
+        <v>Enter domain name</v>
       </c>
       <c r="B625" t="str">
-        <v>إضافة نوع قضية جديد</v>
+        <v>أدخل اسم المجال</v>
       </c>
       <c r="C625" t="str">
-        <v>Pievienot jaunu problēmas tipu</v>
+        <v>Ievadiet domēna nosaukumu</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Issue Type Name</v>
+        <v>Add New Category</v>
       </c>
       <c r="B626" t="str">
-        <v>اسم نوع القضية</v>
+        <v>إضافة فئة جديدة</v>
       </c>
       <c r="C626" t="str">
-        <v>Problēmas tipa nosaukums</v>
+        <v>Pievienot jaunu kategoriju</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Enter issue type name</v>
+        <v>Add New Issue Type</v>
       </c>
       <c r="B627" t="str">
-        <v>أدخل اسم نوع القضية</v>
+        <v>إضافة نوع قضية جديد</v>
       </c>
       <c r="C627" t="str">
-        <v>Ievadiet problēmas tipa nosaukumu</v>
+        <v>Pievienot jaunu problēmas tipu</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Link Process</v>
+        <v>Issue Type Name</v>
       </c>
       <c r="B628" t="str">
-        <v>ربط العملية</v>
+        <v>اسم نوع القضية</v>
       </c>
       <c r="C628" t="str">
-        <v>Saistīt procesu</v>
+        <v>Problēmas tipa nosaukums</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>No processes found</v>
+        <v>Enter issue type name</v>
       </c>
       <c r="B629" t="str">
-        <v>لم يتم العثور على عمليات</v>
+        <v>أدخل اسم نوع القضية</v>
       </c>
       <c r="C629" t="str">
-        <v>Procesi nav atrasti</v>
+        <v>Ievadiet problēmas tipa nosaukumu</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Add New Need/Expectation</v>
+        <v>Link Process</v>
       </c>
       <c r="B630" t="str">
-        <v>إضافة احتياج/توقع جديد</v>
+        <v>ربط العملية</v>
       </c>
       <c r="C630" t="str">
-        <v>Pievienot jaunu vajadzību/gaidījumu</v>
+        <v>Saistīt procesu</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Need/Expectation</v>
+        <v>No processes found</v>
       </c>
       <c r="B631" t="str">
-        <v>الاحتياج/التوقع</v>
+        <v>لم يتم العثور على عمليات</v>
       </c>
       <c r="C631" t="str">
-        <v>Vajadzība/Gaidījums</v>
+        <v>Procesi nav atrasti</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Enter need/expectation</v>
+        <v>Add New Need/Expectation</v>
       </c>
       <c r="B632" t="str">
-        <v>أدخل الاحتياج/التوقع</v>
+        <v>إضافة احتياج/توقع جديد</v>
       </c>
       <c r="C632" t="str">
-        <v>Ievadiet vajadzību/gaidījumu</v>
+        <v>Pievienot jaunu vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Enter a new need or expectation type.</v>
+        <v>Need/Expectation</v>
       </c>
       <c r="B633" t="str">
-        <v>أدخل نوع احتياج أو توقع جديد.</v>
+        <v>الاحتياج/التوقع</v>
       </c>
       <c r="C633" t="str">
-        <v>Ievadiet jaunu vajadzības vai gaidījumu tipu.</v>
+        <v>Vajadzība/Gaidījums</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Title is required</v>
+        <v>Enter need/expectation</v>
       </c>
       <c r="B634" t="str">
-        <v>العنوان مطلوب</v>
+        <v>أدخل الاحتياج/التوقع</v>
       </c>
       <c r="C634" t="str">
-        <v>Nosaukums ir obligāts</v>
+        <v>Ievadiet vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Issue created successfully</v>
+        <v>Enter a new need or expectation type.</v>
       </c>
       <c r="B635" t="str">
-        <v>تم إنشاء القضية بنجاح</v>
+        <v>أدخل نوع احتياج أو توقع جديد.</v>
       </c>
       <c r="C635" t="str">
-        <v>Problēma veiksmīgi izveidota</v>
+        <v>Ievadiet jaunu vajadzības vai gaidījumu tipu.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Failed to create issue</v>
+        <v>Title is required</v>
       </c>
       <c r="B636" t="str">
-        <v>فشل في إنشاء القضية</v>
+        <v>العنوان مطلوب</v>
       </c>
       <c r="C636" t="str">
-        <v>Neizdevās izveidot problēmu</v>
+        <v>Nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Issue updated successfully</v>
+        <v>Issue created successfully</v>
       </c>
       <c r="B637" t="str">
-        <v>تم تحديث القضية بنجاح</v>
+        <v>تم إنشاء القضية بنجاح</v>
       </c>
       <c r="C637" t="str">
-        <v>Problēma veiksmīgi atjaunināta</v>
+        <v>Problēma veiksmīgi izveidota</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Failed to update issue</v>
+        <v>Failed to create issue</v>
       </c>
       <c r="B638" t="str">
-        <v>فشل في تحديث القضية</v>
+        <v>فشل في إنشاء القضية</v>
       </c>
       <c r="C638" t="str">
-        <v>Neizdevās atjaunināt problēmu</v>
+        <v>Neizdevās izveidot problēmu</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Stakeholder updated successfully</v>
+        <v>Issue updated successfully</v>
       </c>
       <c r="B639" t="str">
-        <v>تم تحديث صاحب المصلحة بنجاح</v>
+        <v>تم تحديث القضية بنجاح</v>
       </c>
       <c r="C639" t="str">
-        <v>Ieinteresētā puse veiksmīgi atjaunināta</v>
+        <v>Problēma veiksmīgi atjaunināta</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Failed to update stakeholder</v>
+        <v>Failed to update issue</v>
       </c>
       <c r="B640" t="str">
-        <v>فشل في تحديث صاحب المصلحة</v>
+        <v>فشل في تحديث القضية</v>
       </c>
       <c r="C640" t="str">
-        <v>Neizdevās atjaunināt ieinteresēto pusi</v>
+        <v>Neizdevās atjaunināt problēmu</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Open</v>
+        <v>Stakeholder updated successfully</v>
       </c>
       <c r="B641" t="str">
-        <v>مفتوح</v>
+        <v>تم تحديث صاحب المصلحة بنجاح</v>
       </c>
       <c r="C641" t="str">
-        <v>Atvērts</v>
+        <v>Ieinteresētā puse veiksmīgi atjaunināta</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>In Progress</v>
+        <v>Failed to update stakeholder</v>
       </c>
       <c r="B642" t="str">
-        <v>قيد التنفيذ</v>
+        <v>فشل في تحديث صاحب المصلحة</v>
       </c>
       <c r="C642" t="str">
-        <v>Procesā</v>
+        <v>Neizdevās atjaunināt ieinteresēto pusi</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Action type and description are required</v>
+        <v>Open</v>
       </c>
       <c r="B643" t="str">
-        <v>نوع الإجراء والوصف مطلوبان</v>
+        <v>مفتوح</v>
       </c>
       <c r="C643" t="str">
-        <v>Darbības tips un apraksts ir obligāti</v>
+        <v>Atvērts</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Action created successfully</v>
+        <v>In Progress</v>
       </c>
       <c r="B644" t="str">
-        <v>تم إنشاء الإجراء بنجاح</v>
+        <v>قيد التنفيذ</v>
       </c>
       <c r="C644" t="str">
-        <v>Darbība veiksmīgi izveidota</v>
+        <v>Procesā</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Failed to create action</v>
+        <v>Action type and description are required</v>
       </c>
       <c r="B645" t="str">
-        <v>فشل في إنشاء الإجراء</v>
+        <v>نوع الإجراء والوصف مطلوبان</v>
       </c>
       <c r="C645" t="str">
-        <v>Neizdevās izveidot darbību</v>
+        <v>Darbības tips un apraksts ir obligāti</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Action is resolved</v>
+        <v>Action created successfully</v>
       </c>
       <c r="B646" t="str">
-        <v>تم حل الإجراء</v>
+        <v>تم إنشاء الإجراء بنجاح</v>
       </c>
       <c r="C646" t="str">
-        <v>Darbība ir atrisināta</v>
+        <v>Darbība veiksmīgi izveidota</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Failed to resolve action</v>
+        <v>Failed to create action</v>
       </c>
       <c r="B647" t="str">
-        <v>فشل في حل الإجراء</v>
+        <v>فشل في إنشاء الإجراء</v>
       </c>
       <c r="C647" t="str">
-        <v>Neizdevās atrisināt darbību</v>
+        <v>Neizdevās izveidot darbību</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Comment is required</v>
+        <v>Action is resolved</v>
       </c>
       <c r="B648" t="str">
-        <v>التعليق مطلوب</v>
+        <v>تم حل الإجراء</v>
       </c>
       <c r="C648" t="str">
-        <v>Komentārs ir obligāts</v>
+        <v>Darbība ir atrisināta</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Action is sent back</v>
+        <v>Failed to resolve action</v>
       </c>
       <c r="B649" t="str">
-        <v>تم إرجاع الإجراء</v>
+        <v>فشل في حل الإجراء</v>
       </c>
       <c r="C649" t="str">
-        <v>Darbība ir nosūtīta atpakaļ</v>
+        <v>Neizdevās atrisināt darbību</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Failed to send back action</v>
+        <v>Comment is required</v>
       </c>
       <c r="B650" t="str">
-        <v>فشل في إرجاع الإجراء</v>
+        <v>التعليق مطلوب</v>
       </c>
       <c r="C650" t="str">
-        <v>Neizdevās nosūtīt atpakaļ darbību</v>
+        <v>Komentārs ir obligāts</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Action updated and resubmitted</v>
+        <v>Action is sent back</v>
       </c>
       <c r="B651" t="str">
-        <v>تم تحديث الإجراء وإعادة إرساله</v>
+        <v>تم إرجاع الإجراء</v>
       </c>
       <c r="C651" t="str">
-        <v>Darbība atjaunināta un atkārtoti iesniegta</v>
+        <v>Darbība ir nosūtīta atpakaļ</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Failed to update action</v>
+        <v>Failed to send back action</v>
       </c>
       <c r="B652" t="str">
-        <v>فشل في تحديث الإجراء</v>
+        <v>فشل في إرجاع الإجراء</v>
       </c>
       <c r="C652" t="str">
-        <v>Neizdevās atjaunināt darbību</v>
+        <v>Neizdevās nosūtīt atpakaļ darbību</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Saving...</v>
+        <v>Action updated and resubmitted</v>
       </c>
       <c r="B653" t="str">
-        <v>جاري الحفظ...</v>
+        <v>تم تحديث الإجراء وإعادة إرساله</v>
       </c>
       <c r="C653" t="str">
-        <v>Saglabā...</v>
+        <v>Darbība atjaunināta un atkārtoti iesniegta</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Save &amp; Resubmit</v>
+        <v>Failed to update action</v>
       </c>
       <c r="B654" t="str">
-        <v>حفظ وإعادة الإرسال</v>
+        <v>فشل في تحديث الإجراء</v>
       </c>
       <c r="C654" t="str">
-        <v>Saglabāt un iesniegt atkārtoti</v>
+        <v>Neizdevās atjaunināt darbību</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Import Issues</v>
+        <v>Saving...</v>
       </c>
       <c r="B655" t="str">
-        <v>استيراد القضايا</v>
+        <v>جاري الحفظ...</v>
       </c>
       <c r="C655" t="str">
-        <v>Importēt problēmas</v>
+        <v>Saglabā...</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>CSV file must have a header row and at least one data row</v>
+        <v>Save &amp; Resubmit</v>
       </c>
       <c r="B656" t="str">
-        <v>يجب أن يحتوي ملف CSV على صف رأس وصف بيانات واحد على الأقل</v>
+        <v>حفظ وإعادة الإرسال</v>
       </c>
       <c r="C656" t="str">
-        <v>CSV failam jābūt galvenes rindai un vismaz vienai datu rindai</v>
+        <v>Saglabāt un iesniegt atkārtoti</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>CSV must have a "title" column</v>
+        <v>Import Issues</v>
       </c>
       <c r="B657" t="str">
-        <v>يجب أن يحتوي ملف CSV على عمود "title"</v>
+        <v>استيراد القضايا</v>
       </c>
       <c r="C657" t="str">
-        <v>CSV ir jābūt kolonnai "title"</v>
+        <v>Importēt problēmas</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Successfully imported</v>
+        <v>CSV file must have a header row and at least one data row</v>
       </c>
       <c r="B658" t="str">
-        <v>تم الاستيراد بنجاح</v>
+        <v>يجب أن يحتوي ملف CSV على صف رأس وصف بيانات واحد على الأقل</v>
       </c>
       <c r="C658" t="str">
-        <v>Veiksmīgi importēts</v>
+        <v>CSV failam jābūt galvenes rindai un vismaz vienai datu rindai</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>issues</v>
+        <v>CSV must have a "title" column</v>
       </c>
       <c r="B659" t="str">
-        <v>قضايا</v>
+        <v>يجب أن يحتوي ملف CSV على عمود "title"</v>
       </c>
       <c r="C659" t="str">
-        <v>problēmas</v>
+        <v>CSV ir jābūt kolonnai "title"</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Error importing issues. Please check the file format.</v>
+        <v>Successfully imported</v>
       </c>
       <c r="B660" t="str">
-        <v>خطأ في استيراد القضايا. يرجى التحقق من تنسيق الملف.</v>
+        <v>تم الاستيراد بنجاح</v>
       </c>
       <c r="C660" t="str">
-        <v>Kļūda importējot problēmas. Lūdzu, pārbaudiet faila formātu.</v>
+        <v>Veiksmīgi importēts</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>File attached to action</v>
+        <v>issues</v>
       </c>
       <c r="B661" t="str">
-        <v>تم إرفاق الملف بالإجراء</v>
+        <v>قضايا</v>
       </c>
       <c r="C661" t="str">
-        <v>Fails pievienots darbībai</v>
+        <v>problēmas</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Failed to attach file to action</v>
+        <v>Error importing issues. Please check the file format.</v>
       </c>
       <c r="B662" t="str">
-        <v>فشل في إرفاق الملف بالإجراء</v>
+        <v>خطأ في استيراد القضايا. يرجى التحقق من تنسيق الملف.</v>
       </c>
       <c r="C662" t="str">
-        <v>Neizdevās pievienot failu darbībai</v>
+        <v>Kļūda importējot problēmas. Lūdzu, pārbaudiet faila formātu.</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>File deleted successfully</v>
+        <v>File attached to action</v>
       </c>
       <c r="B663" t="str">
-        <v>تم حذف الملف بنجاح</v>
+        <v>تم إرفاق الملف بالإجراء</v>
       </c>
       <c r="C663" t="str">
-        <v>Fails veiksmīgi dzēsts</v>
+        <v>Fails pievienots darbībai</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Failed to delete file</v>
+        <v>Failed to attach file to action</v>
       </c>
       <c r="B664" t="str">
-        <v>فشل في حذف الملف</v>
+        <v>فشل في إرفاق الملف بالإجراء</v>
       </c>
       <c r="C664" t="str">
-        <v>Neizdevās dzēst failu</v>
+        <v>Neizdevās pievienot failu darbībai</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Repository</v>
+        <v>File deleted successfully</v>
       </c>
       <c r="B665" t="str">
-        <v>المستودع</v>
+        <v>تم حذف الملف بنجاح</v>
       </c>
       <c r="C665" t="str">
-        <v>Repozitorijs</v>
+        <v>Fails veiksmīgi dzēsts</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Performance Dashboard</v>
+        <v>Failed to delete file</v>
       </c>
       <c r="B666" t="str">
-        <v>لوحة الأداء</v>
+        <v>فشل في حذف الملف</v>
       </c>
       <c r="C666" t="str">
-        <v>Veiktspējas panelis</v>
+        <v>Neizdevās dzēst failu</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Search By Process ID, Name</v>
+        <v>Repository</v>
       </c>
       <c r="B667" t="str">
-        <v>البحث بمعرف العملية أو الاسم</v>
+        <v>المستودع</v>
       </c>
       <c r="C667" t="str">
-        <v>Meklēt pēc procesa ID, nosaukuma</v>
+        <v>Repozitorijs</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>All Owners</v>
+        <v>Performance Dashboard</v>
       </c>
       <c r="B668" t="str">
-        <v>جميع المالكين</v>
+        <v>لوحة الأداء</v>
       </c>
       <c r="C668" t="str">
-        <v>Visi īpašnieki</v>
+        <v>Veiktspējas panelis</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>All Frequencies</v>
+        <v>Search By Process ID, Name</v>
       </c>
       <c r="B669" t="str">
-        <v>جميع الترددات</v>
+        <v>البحث بمعرف العملية أو الاسم</v>
       </c>
       <c r="C669" t="str">
-        <v>Visi biežumi</v>
+        <v>Meklēt pēc procesa ID, nosaukuma</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Edit Process</v>
+        <v>All Owners</v>
       </c>
       <c r="B670" t="str">
-        <v>تعديل العملية</v>
+        <v>جميع المالكين</v>
       </c>
       <c r="C670" t="str">
-        <v>Rediģēt procesu</v>
+        <v>Visi īpašnieki</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Confirm Delete</v>
+        <v>All Frequencies</v>
       </c>
       <c r="B671" t="str">
-        <v>تأكيد الحذف</v>
+        <v>جميع الترددات</v>
       </c>
       <c r="C671" t="str">
-        <v>Apstiprināt dzēšanu</v>
+        <v>Visi biežumi</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Are you sure you want to delete this process? This action cannot be undone.</v>
+        <v>Edit Process</v>
       </c>
       <c r="B672" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه العملية؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>تعديل العملية</v>
       </c>
       <c r="C672" t="str">
-        <v>Vai tiešām vēlaties dzēst šo procesu? Šo darbību nevar atsaukt.</v>
+        <v>Rediģēt procesu</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Add New Process</v>
+        <v>Confirm Delete</v>
       </c>
       <c r="B673" t="str">
-        <v>إضافة عملية جديدة</v>
+        <v>تأكيد الحذف</v>
       </c>
       <c r="C673" t="str">
-        <v>Pievienot jaunu procesu</v>
+        <v>Apstiprināt dzēšanu</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Basic Information</v>
+        <v>Are you sure you want to delete this process? This action cannot be undone.</v>
       </c>
       <c r="B674" t="str">
-        <v>المعلومات الأساسية</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه العملية؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C674" t="str">
-        <v>Pamatinformācija</v>
+        <v>Vai tiešām vēlaties dzēst šo procesu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Process Details</v>
+        <v>Add New Process</v>
       </c>
       <c r="B675" t="str">
-        <v>تفاصيل العملية</v>
+        <v>إضافة عملية جديدة</v>
       </c>
       <c r="C675" t="str">
-        <v>Procesa detaļas</v>
+        <v>Pievienot jaunu procesu</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Dependencies &amp; Options</v>
+        <v>Basic Information</v>
       </c>
       <c r="B676" t="str">
-        <v>التبعيات والخيارات</v>
+        <v>المعلومات الأساسية</v>
       </c>
       <c r="C676" t="str">
-        <v>Atkarības un opcijas</v>
+        <v>Pamatinformācija</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>RACI Matrix</v>
+        <v>Process Details</v>
       </c>
       <c r="B677" t="str">
-        <v>مصفوفة RACI</v>
+        <v>تفاصيل العملية</v>
       </c>
       <c r="C677" t="str">
-        <v>RACI matrica</v>
+        <v>Procesa detaļas</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Enter process name</v>
+        <v>Dependencies &amp; Options</v>
       </c>
       <c r="B678" t="str">
-        <v>أدخل اسم العملية</v>
+        <v>التبعيات والخيارات</v>
       </c>
       <c r="C678" t="str">
-        <v>Ievadiet procesa nosaukumu</v>
+        <v>Atkarības un opcijas</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Enter process description</v>
+        <v>RACI Matrix</v>
       </c>
       <c r="B679" t="str">
-        <v>أدخل وصف العملية</v>
+        <v>مصفوفة RACI</v>
       </c>
       <c r="C679" t="str">
-        <v>Ievadiet procesa aprakstu</v>
+        <v>RACI matrica</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Nature of Implementation</v>
+        <v>Enter process name</v>
       </c>
       <c r="B680" t="str">
-        <v>طبيعة التنفيذ</v>
+        <v>أدخل اسم العملية</v>
       </c>
       <c r="C680" t="str">
-        <v>Ieviešanas veids</v>
+        <v>Ievadiet procesa nosaukumu</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Select implementation type</v>
+        <v>Enter process description</v>
       </c>
       <c r="B681" t="str">
-        <v>اختر نوع التنفيذ</v>
+        <v>أدخل وصف العملية</v>
       </c>
       <c r="C681" t="str">
-        <v>Izvēlieties ieviešanas tipu</v>
+        <v>Ievadiet procesa aprakstu</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Select location</v>
+        <v>Nature of Implementation</v>
       </c>
       <c r="B682" t="str">
-        <v>اختر الموقع</v>
+        <v>طبيعة التنفيذ</v>
       </c>
       <c r="C682" t="str">
-        <v>Izvēlieties atrašanās vietu</v>
+        <v>Ieviešanas veids</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Operational Complexity</v>
+        <v>Select implementation type</v>
       </c>
       <c r="B683" t="str">
-        <v>التعقيد التشغيلي</v>
+        <v>اختر نوع التنفيذ</v>
       </c>
       <c r="C683" t="str">
-        <v>Operacionālā sarežģītība</v>
+        <v>Izvēlieties ieviešanas tipu</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Select complexity</v>
+        <v>Select location</v>
       </c>
       <c r="B684" t="str">
-        <v>اختر التعقيد</v>
+        <v>اختر الموقع</v>
       </c>
       <c r="C684" t="str">
-        <v>Izvēlieties sarežģītību</v>
+        <v>Izvēlieties atrašanās vietu</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Asset Dependency</v>
+        <v>Operational Complexity</v>
       </c>
       <c r="B685" t="str">
-        <v>تبعية الأصول</v>
+        <v>التعقيد التشغيلي</v>
       </c>
       <c r="C685" t="str">
-        <v>Aktīvu atkarība</v>
+        <v>Operacionālā sarežģītība</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>External Dependency</v>
+        <v>Select complexity</v>
       </c>
       <c r="B686" t="str">
-        <v>تبعية خارجية</v>
+        <v>اختر التعقيد</v>
       </c>
       <c r="C686" t="str">
-        <v>Ārējā atkarība</v>
+        <v>Izvēlieties sarežģītību</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>KPI Measurement Required</v>
+        <v>Asset Dependency</v>
       </c>
       <c r="B687" t="str">
-        <v>قياس مؤشرات الأداء مطلوب</v>
+        <v>تبعية الأصول</v>
       </c>
       <c r="C687" t="str">
-        <v>Nepieciešams KPI mērījums</v>
+        <v>Aktīvu atkarība</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>PII Capture</v>
+        <v>External Dependency</v>
       </c>
       <c r="B688" t="str">
-        <v>التقاط البيانات الشخصية</v>
+        <v>تبعية خارجية</v>
       </c>
       <c r="C688" t="str">
-        <v>PII uztveršana</v>
+        <v>Ārējā atkarība</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Auto-generated</v>
+        <v>KPI Measurement Required</v>
       </c>
       <c r="B689" t="str">
-        <v>يتم إنشاؤه تلقائياً</v>
+        <v>قياس مؤشرات الأداء مطلوب</v>
       </c>
       <c r="C689" t="str">
-        <v>Automātiski ģenerēts</v>
+        <v>Nepieciešams KPI mērījums</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Process created successfully</v>
+        <v>PII Capture</v>
       </c>
       <c r="B690" t="str">
-        <v>تم إنشاء العملية بنجاح</v>
+        <v>التقاط البيانات الشخصية</v>
       </c>
       <c r="C690" t="str">
-        <v>Process veiksmīgi izveidots</v>
+        <v>PII uztveršana</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Failed to create process</v>
+        <v>Auto-generated</v>
       </c>
       <c r="B691" t="str">
-        <v>فشل في إنشاء العملية</v>
+        <v>يتم إنشاؤه تلقائياً</v>
       </c>
       <c r="C691" t="str">
-        <v>Neizdevās izveidot procesu</v>
+        <v>Automātiski ģenerēts</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Process updated successfully</v>
+        <v>Process created successfully</v>
       </c>
       <c r="B692" t="str">
-        <v>تم تحديث العملية بنجاح</v>
+        <v>تم إنشاء العملية بنجاح</v>
       </c>
       <c r="C692" t="str">
-        <v>Process veiksmīgi atjaunināts</v>
+        <v>Process veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Failed to update process</v>
+        <v>Failed to create process</v>
       </c>
       <c r="B693" t="str">
-        <v>فشل في تحديث العملية</v>
+        <v>فشل في إنشاء العملية</v>
       </c>
       <c r="C693" t="str">
-        <v>Neizdevās atjaunināt procesu</v>
+        <v>Neizdevās izveidot procesu</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Please fill in required fields (Name and Process Type)</v>
+        <v>Process updated successfully</v>
       </c>
       <c r="B694" t="str">
-        <v>يرجى ملء الحقول المطلوبة (الاسم ونوع العملية)</v>
+        <v>تم تحديث العملية بنجاح</v>
       </c>
       <c r="C694" t="str">
-        <v>Lūdzu, aizpildiet obligātos laukus (Nosaukums un procesa tips)</v>
+        <v>Process veiksmīgi atjaunināts</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Save Changes</v>
+        <v>Failed to update process</v>
       </c>
       <c r="B695" t="str">
-        <v>حفظ التغييرات</v>
+        <v>فشل في تحديث العملية</v>
       </c>
       <c r="C695" t="str">
-        <v>Saglabāt izmaiņas</v>
+        <v>Neizdevās atjaunināt procesu</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Reference ID</v>
+        <v>Please fill in required fields (Name and Process Type)</v>
       </c>
       <c r="B696" t="str">
-        <v>المعرف المرجعي</v>
+        <v>يرجى ملء الحقول المطلوبة (الاسم ونوع العملية)</v>
       </c>
       <c r="C696" t="str">
-        <v>Atsauces ID</v>
+        <v>Lūdzu, aizpildiet obligātos laukus (Nosaukums un procesa tips)</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Process Criticality</v>
+        <v>Save Changes</v>
       </c>
       <c r="B697" t="str">
-        <v>أهمية العملية</v>
+        <v>حفظ التغييرات</v>
       </c>
       <c r="C697" t="str">
-        <v>Procesa kritiskums</v>
+        <v>Saglabāt izmaiņas</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>Process Frequency</v>
+        <v>Reference ID</v>
       </c>
       <c r="B698" t="str">
-        <v>تكرار العملية</v>
+        <v>المعرف المرجعي</v>
       </c>
       <c r="C698" t="str">
-        <v>Procesa biežums</v>
+        <v>Atsauces ID</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>Nature Of Implementation</v>
+        <v>Process Criticality</v>
       </c>
       <c r="B699" t="str">
-        <v>طبيعة التنفيذ</v>
+        <v>أهمية العملية</v>
       </c>
       <c r="C699" t="str">
-        <v>Ieviešanas veids</v>
+        <v>Procesa kritiskums</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>AI Risk</v>
+        <v>Process Frequency</v>
       </c>
       <c r="B700" t="str">
-        <v>مخاطر الذكاء الاصطناعي</v>
+        <v>تكرار العملية</v>
       </c>
       <c r="C700" t="str">
-        <v>AI risks</v>
+        <v>Procesa biežums</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>AI Risk Evaluation</v>
+        <v>Nature Of Implementation</v>
       </c>
       <c r="B701" t="str">
-        <v>تقييم مخاطر الذكاء الاصطناعي</v>
+        <v>طبيعة التنفيذ</v>
       </c>
       <c r="C701" t="str">
-        <v>AI risku novērtējums</v>
+        <v>Ieviešanas veids</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>AI is identifying potential risks...</v>
+        <v>AI Risk</v>
       </c>
       <c r="B702" t="str">
-        <v>الذكاء الاصطناعي يحدد المخاطر المحتملة...</v>
+        <v>مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C702" t="str">
-        <v>AI identificē potenciālos riskus...</v>
+        <v>AI risks</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>This may take up to 30 seconds</v>
+        <v>AI Risk Evaluation</v>
       </c>
       <c r="B703" t="str">
-        <v>قد يستغرق هذا ما يصل إلى 30 ثانية</v>
+        <v>تقييم مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C703" t="str">
-        <v>Tas var aizņemt līdz 30 sekundēm</v>
+        <v>AI risku novērtējums</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>Detected Risks</v>
+        <v>AI is identifying potential risks...</v>
       </c>
       <c r="B704" t="str">
-        <v>المخاطر المكتشفة</v>
+        <v>الذكاء الاصطناعي يحدد المخاطر المحتملة...</v>
       </c>
       <c r="C704" t="str">
-        <v>Atklātie riski</v>
+        <v>AI identificē potenciālos riskus...</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>The AI has identified the following risks, threats, and suggested controls...</v>
+        <v>This may take up to 30 seconds</v>
       </c>
       <c r="B705" t="str">
-        <v>حدد الذكاء الاصطناعي المخاطر والتهديدات والضوابط المقترحة التالية...</v>
+        <v>قد يستغرق هذا ما يصل إلى 30 ثانية</v>
       </c>
       <c r="C705" t="str">
-        <v>AI ir identificējis šādus riskus, draudus un ieteiktos kontroles...</v>
+        <v>Tas var aizņemt līdz 30 sekundēm</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>Threats</v>
+        <v>Detected Risks</v>
       </c>
       <c r="B706" t="str">
-        <v>التهديدات</v>
+        <v>المخاطر المكتشفة</v>
       </c>
       <c r="C706" t="str">
-        <v>Draudi</v>
+        <v>Atklātie riski</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>Suggested Controls</v>
+        <v>The AI has identified the following risks, threats, and suggested controls...</v>
       </c>
       <c r="B707" t="str">
-        <v>الضوابط المقترحة</v>
+        <v>حدد الذكاء الاصطناعي المخاطر والتهديدات والضوابط المقترحة التالية...</v>
       </c>
       <c r="C707" t="str">
-        <v>Ieteiktās kontroles</v>
+        <v>AI ir identificējis šādus riskus, draudus un ieteiktos kontroles...</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>No risks generated yet.</v>
+        <v>Threats</v>
       </c>
       <c r="B708" t="str">
-        <v>لم يتم إنشاء مخاطر بعد.</v>
+        <v>التهديدات</v>
       </c>
       <c r="C708" t="str">
-        <v>Vēl nav ģenerēti riski.</v>
+        <v>Draudi</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>AI Risks Generated</v>
+        <v>Suggested Controls</v>
       </c>
       <c r="B709" t="str">
-        <v>تم إنشاء مخاطر الذكاء الاصطناعي</v>
+        <v>الضوابط المقترحة</v>
       </c>
       <c r="C709" t="str">
-        <v>AI riski ģenerēti</v>
+        <v>Ieteiktās kontroles</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>AI Generation Failed</v>
+        <v>No risks generated yet.</v>
       </c>
       <c r="B710" t="str">
-        <v>فشل إنشاء الذكاء الاصطناعي</v>
+        <v>لم يتم إنشاء مخاطر بعد.</v>
       </c>
       <c r="C710" t="str">
-        <v>AI ģenerēšana neizdevās</v>
+        <v>Vēl nav ģenerēti riski.</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>Communication with AI service failed.</v>
+        <v>AI Risks Generated</v>
       </c>
       <c r="B711" t="str">
-        <v>فشل الاتصال بخدمة الذكاء الاصطناعي.</v>
+        <v>تم إنشاء مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C711" t="str">
-        <v>Saziņa ar AI servisu neizdevās.</v>
+        <v>AI riski ģenerēti</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>Please try again later.</v>
+        <v>AI Generation Failed</v>
       </c>
       <c r="B712" t="str">
-        <v>يرجى المحاولة مرة أخرى لاحقاً.</v>
+        <v>فشل إنشاء الذكاء الاصطناعي</v>
       </c>
       <c r="C712" t="str">
-        <v>Lūdzu, mēģiniet vēlreiz vēlāk.</v>
+        <v>AI ģenerēšana neizdevās</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>Go to Risk Register</v>
+        <v>Communication with AI service failed.</v>
       </c>
       <c r="B713" t="str">
-        <v>الذهاب إلى سجل المخاطر</v>
+        <v>فشل الاتصال بخدمة الذكاء الاصطناعي.</v>
       </c>
       <c r="C713" t="str">
-        <v>Doties uz risku reģistru</v>
+        <v>Saziņa ar AI servisu neizdevās.</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>Perform BIA</v>
+        <v>Please try again later.</v>
       </c>
       <c r="B714" t="str">
-        <v>إجراء تحليل تأثير الأعمال</v>
+        <v>يرجى المحاولة مرة أخرى لاحقاً.</v>
       </c>
       <c r="C714" t="str">
-        <v>Veikt BIA</v>
+        <v>Lūdzu, mēģiniet vēlreiz vēlāk.</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>Submit For Approval</v>
+        <v>Go to Risk Register</v>
       </c>
       <c r="B715" t="str">
-        <v>إرسال للموافقة</v>
+        <v>الذهاب إلى سجل المخاطر</v>
       </c>
       <c r="C715" t="str">
-        <v>Iesniegt apstiprināšanai</v>
+        <v>Doties uz risku reģistru</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>Status &amp; Approval</v>
+        <v>Add to Risk Register</v>
       </c>
       <c r="B716" t="str">
-        <v>الحالة والموافقة</v>
+        <v>إضافة إلى سجل المخاطر</v>
       </c>
       <c r="C716" t="str">
-        <v>Statuss un apstiprinājums</v>
+        <v>Pievienot risku reģistram</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>Impact Assessment</v>
+        <v>Adding...</v>
       </c>
       <c r="B717" t="str">
-        <v>تقييم التأثير</v>
+        <v>جاري الإضافة...</v>
       </c>
       <c r="C717" t="str">
-        <v>Ietekmes novērtējums</v>
+        <v>Pievieno...</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>Recovery Metrics</v>
+        <v>No risks to add</v>
       </c>
       <c r="B718" t="str">
-        <v>مقاييس الاستعادة</v>
+        <v>لا توجد مخاطر للإضافة</v>
       </c>
       <c r="C718" t="str">
-        <v>Atjaunošanas metrikas</v>
+        <v>Nav risku, ko pievienot</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>BIA Rating</v>
+        <v>Keep at least one risk before adding to the register.</v>
       </c>
       <c r="B719" t="str">
-        <v>تصنيف تحليل تأثير الأعمال</v>
+        <v>احتفظ بخطر واحد على الأقل قبل الإضافة إلى السجل.</v>
       </c>
       <c r="C719" t="str">
-        <v>BIA vērtējums</v>
+        <v>Paturiet vismaz vienu risku pirms pievienošanas reģistram.</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>Impact Rating</v>
+        <v>Risks have been added to the Risk Register.</v>
       </c>
       <c r="B720" t="str">
-        <v>تصنيف التأثير</v>
+        <v>تمت إضافة المخاطر إلى سجل المخاطر.</v>
       </c>
       <c r="C720" t="str">
-        <v>Ietekmes vērtējums</v>
+        <v>Riski ir pievienoti risku reģistram.</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>Note: The highest rating will be taken</v>
+        <v>Adding to risk register timed out. Please try again.</v>
       </c>
       <c r="B721" t="str">
-        <v>ملاحظة: سيتم أخذ أعلى تصنيف</v>
+        <v>انتهت مهلة الإضافة إلى سجل المخاطر. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C721" t="str">
-        <v>Piezīme: Tiks ņemts augstākais vērtējums</v>
+        <v>Pievienošanas reģistram laiks beidzās. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>RTO (Recovery Time Objective) - Hours</v>
+        <v>Failed to add risks to register</v>
       </c>
       <c r="B722" t="str">
-        <v>هدف وقت الاستعادة - ساعات</v>
+        <v>فشل في إضافة المخاطر إلى السجل</v>
       </c>
       <c r="C722" t="str">
-        <v>RTO (Atjaunošanas laika mērķis) - Stundas</v>
+        <v>Neizdevās pievienot riskus reģistram</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>RPO (Recovery Point Objective) - Hours</v>
+        <v>Failed to register risks</v>
       </c>
       <c r="B723" t="str">
-        <v>هدف نقطة الاستعادة - ساعات</v>
+        <v>فشل في تسجيل المخاطر</v>
       </c>
       <c r="C723" t="str">
-        <v>RPO (Atjaunošanas punkta mērķis) - Stundas</v>
+        <v>Neizdevās reģistrēt riskus</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>N/A</v>
+        <v>No risks in semantic result to register</v>
       </c>
       <c r="B724" t="str">
-        <v>غير متاح</v>
+        <v>لا توجد مخاطر في نتيجة البحث الدلالي للتسجيل</v>
       </c>
       <c r="C724" t="str">
-        <v>Nav piemērojams</v>
+        <v>Nav risku semantiskajā rezultātā reģistrēšanai</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>KPI Details</v>
+        <v>Failed to add to risk register</v>
       </c>
       <c r="B725" t="str">
-        <v>تفاصيل مؤشرات الأداء</v>
+        <v>فشل في الإضافة إلى سجل المخاطر</v>
       </c>
       <c r="C725" t="str">
-        <v>KPI detaļas</v>
+        <v>Neizdevās pievienot risku reģistram</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>Performance Chart</v>
+        <v>Add to Audit Plan</v>
       </c>
       <c r="B726" t="str">
-        <v>مخطط الأداء</v>
+        <v>إضافة إلى خطة التدقيق</v>
       </c>
       <c r="C726" t="str">
-        <v>Veiktspējas diagramma</v>
+        <v>Pievienot audita plānam</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>KPI Configuration</v>
+        <v>Department information missing</v>
       </c>
       <c r="B727" t="str">
-        <v>إعدادات مؤشرات الأداء</v>
+        <v>معلومات القسم مفقودة</v>
       </c>
       <c r="C727" t="str">
-        <v>KPI konfigurācija</v>
+        <v>Trūkst nodaļas informācijas</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>KPI Records</v>
+        <v>Failed to add to audit plan</v>
       </c>
       <c r="B728" t="str">
-        <v>سجلات مؤشرات الأداء</v>
+        <v>فشل في الإضافة إلى خطة التدقيق</v>
       </c>
       <c r="C728" t="str">
-        <v>KPI ieraksti</v>
+        <v>Neizdevās pievienot audita plānam</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>Year</v>
+        <v>Successfully added to Audit Planning!</v>
       </c>
       <c r="B729" t="str">
-        <v>السنة</v>
+        <v>تمت الإضافة بنجاح إلى تخطيط التدقيق!</v>
       </c>
       <c r="C729" t="str">
-        <v>Gads</v>
+        <v>Veiksmīgi pievienots audita plānošanai!</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>Achieved Value</v>
+        <v>Already Added</v>
       </c>
       <c r="B730" t="str">
-        <v>القيمة المحققة</v>
+        <v>تمت الإضافة بالفعل</v>
       </c>
       <c r="C730" t="str">
-        <v>Sasniegtā vērtība</v>
+        <v>Jau pievienots</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>Expected Value</v>
+        <v>This audit plan has already been added to Audit Planning.</v>
       </c>
       <c r="B731" t="str">
-        <v>القيمة المتوقعة</v>
+        <v>تمت إضافة خطة التدقيق هذه بالفعل إلى تخطيط التدقيق.</v>
       </c>
       <c r="C731" t="str">
-        <v>Gaidāmā vērtība</v>
+        <v>Šis audita plāns jau ir pievienots audita plānošanai.</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>KPI Objective</v>
+        <v>Failed to check status</v>
       </c>
       <c r="B732" t="str">
-        <v>هدف مؤشر الأداء</v>
+        <v>فشل في التحقق من الحالة</v>
       </c>
       <c r="C732" t="str">
-        <v>KPI mērķis</v>
+        <v>Neizdevās pārbaudīt statusu</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>Enter Objective</v>
+        <v>Remove risk</v>
       </c>
       <c r="B733" t="str">
-        <v>أدخل الهدف</v>
+        <v>إزالة الخطر</v>
       </c>
       <c r="C733" t="str">
-        <v>Ievadiet mērķi</v>
+        <v>Noņemt risku</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>KPI Description</v>
+        <v>Remove risks you do not need; only the remaining risks will be sent to the next step.</v>
       </c>
       <c r="B734" t="str">
-        <v>وصف مؤشر الأداء</v>
+        <v>أزل المخاطر التي لا تحتاجها؛ فقط المخاطر المتبقية سيتم إرسالها إلى الخطوة التالية.</v>
       </c>
       <c r="C734" t="str">
-        <v>KPI apraksts</v>
+        <v>Noņemiet riskus, kas nav nepieciešami; tikai atlikušie riski tiks nosūtīti nākamajā solī.</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>Enter Description</v>
+        <v>Perform BIA</v>
       </c>
       <c r="B735" t="str">
-        <v>أدخل الوصف</v>
+        <v>إجراء تحليل تأثير الأعمال</v>
       </c>
       <c r="C735" t="str">
-        <v>Ievadiet aprakstu</v>
+        <v>Veikt BIA</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>KPI Data Source</v>
+        <v>Submit For Approval</v>
       </c>
       <c r="B736" t="str">
-        <v>مصدر بيانات مؤشر الأداء</v>
+        <v>إرسال للموافقة</v>
       </c>
       <c r="C736" t="str">
-        <v>KPI datu avots</v>
+        <v>Iesniegt apstiprināšanai</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>Enter Data Source</v>
+        <v>Status &amp; Approval</v>
       </c>
       <c r="B737" t="str">
-        <v>أدخل مصدر البيانات</v>
+        <v>الحالة والموافقة</v>
       </c>
       <c r="C737" t="str">
-        <v>Ievadiet datu avotu</v>
+        <v>Statuss un apstiprinājums</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>KPI Measurement Formula</v>
+        <v>Impact Assessment</v>
       </c>
       <c r="B738" t="str">
-        <v>صيغة قياس مؤشر الأداء</v>
+        <v>تقييم التأثير</v>
       </c>
       <c r="C738" t="str">
-        <v>KPI mērīšanas formula</v>
+        <v>Ietekmes novērtējums</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>Enter the KPI Calculation Formula</v>
+        <v>Recovery Metrics</v>
       </c>
       <c r="B739" t="str">
-        <v>أدخل صيغة حساب مؤشر الأداء</v>
+        <v>مقاييس الاستعادة</v>
       </c>
       <c r="C739" t="str">
-        <v>Ievadiet KPI aprēķina formulu</v>
+        <v>Atjaunošanas metrikas</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>Targeted Achieved Value</v>
+        <v>BIA Rating</v>
       </c>
       <c r="B740" t="str">
-        <v>القيمة المستهدفة المحققة</v>
+        <v>تصنيف تحليل تأثير الأعمال</v>
       </c>
       <c r="C740" t="str">
-        <v>Mērķa sasniegtā vērtība</v>
+        <v>BIA vērtējums</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>No KPI records yet</v>
+        <v>Impact Rating</v>
       </c>
       <c r="B741" t="str">
-        <v>لا توجد سجلات مؤشرات أداء بعد</v>
+        <v>تصنيف التأثير</v>
       </c>
       <c r="C741" t="str">
-        <v>Vēl nav KPI ierakstu</v>
+        <v>Ietekmes vērtējums</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>No KPI Data</v>
+        <v>Note: The highest rating will be taken</v>
       </c>
       <c r="B742" t="str">
-        <v>لا توجد بيانات مؤشرات أداء</v>
+        <v>ملاحظة: سيتم أخذ أعلى تصنيف</v>
       </c>
       <c r="C742" t="str">
-        <v>Nav KPI datu</v>
+        <v>Piezīme: Tiks ņemts augstākais vērtējums</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>No processes have KPI measurement enabled...</v>
+        <v>RTO (Recovery Time Objective) - Hours</v>
       </c>
       <c r="B743" t="str">
-        <v>لم يتم تمكين قياس مؤشرات الأداء لأي عملية...</v>
+        <v>هدف وقت الاستعادة - ساعات</v>
       </c>
       <c r="C743" t="str">
-        <v>Nevienam procesam nav iespējots KPI mērījums...</v>
+        <v>RTO (Atjaunošanas laika mērķis) - Stundas</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>Unassigned</v>
+        <v>RPO (Recovery Point Objective) - Hours</v>
       </c>
       <c r="B744" t="str">
-        <v>غير معين</v>
+        <v>هدف نقطة الاستعادة - ساعات</v>
       </c>
       <c r="C744" t="str">
-        <v>Nepiešķirts</v>
+        <v>RPO (Atjaunošanas punkta mērķis) - Stundas</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>Primary</v>
+        <v>N/A</v>
       </c>
       <c r="B745" t="str">
-        <v>أساسي</v>
+        <v>غير متاح</v>
       </c>
       <c r="C745" t="str">
-        <v>Primārais</v>
+        <v>Nav piemērojams</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>Supporting</v>
+        <v>KPI Details</v>
       </c>
       <c r="B746" t="str">
-        <v>داعم</v>
+        <v>تفاصيل مؤشرات الأداء</v>
       </c>
       <c r="C746" t="str">
-        <v>Atbalsta</v>
+        <v>KPI detaļas</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>Manual</v>
+        <v>Performance Chart</v>
       </c>
       <c r="B747" t="str">
-        <v>يدوي</v>
+        <v>مخطط الأداء</v>
       </c>
       <c r="C747" t="str">
-        <v>Manuāls</v>
+        <v>Veiktspējas diagramma</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>Automated</v>
+        <v>KPI Configuration</v>
       </c>
       <c r="B748" t="str">
-        <v>آلي</v>
+        <v>إعدادات مؤشرات الأداء</v>
       </c>
       <c r="C748" t="str">
-        <v>Automatizēts</v>
+        <v>KPI konfigurācija</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>Manual + Automated</v>
+        <v>KPI Records</v>
       </c>
       <c r="B749" t="str">
-        <v>يدوي + آلي</v>
+        <v>سجلات مؤشرات الأداء</v>
       </c>
       <c r="C749" t="str">
-        <v>Manuāls + Automatizēts</v>
+        <v>KPI ieraksti</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>Branch Office</v>
+        <v>Year</v>
       </c>
       <c r="B750" t="str">
-        <v>فرع المكتب</v>
+        <v>السنة</v>
       </c>
       <c r="C750" t="str">
-        <v>Filiāles birojs</v>
+        <v>Gads</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>Remote</v>
+        <v>Achieved Value</v>
       </c>
       <c r="B751" t="str">
-        <v>عن بعد</v>
+        <v>القيمة المحققة</v>
       </c>
       <c r="C751" t="str">
-        <v>Attālināti</v>
+        <v>Sasniegtā vērtība</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>Select frequency</v>
+        <v>Expected Value</v>
       </c>
       <c r="B752" t="str">
-        <v>اختر التكرار</v>
+        <v>القيمة المتوقعة</v>
       </c>
       <c r="C752" t="str">
-        <v>Izvēlieties biežumu</v>
+        <v>Gaidāmā vērtība</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>Bi-annually</v>
+        <v>KPI Objective</v>
       </c>
       <c r="B753" t="str">
-        <v>نصف سنوي</v>
+        <v>هدف مؤشر الأداء</v>
       </c>
       <c r="C753" t="str">
-        <v>Divreiz gadā</v>
+        <v>KPI mērķis</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
+        <v>Enter Objective</v>
+      </c>
+      <c r="B754" t="str">
+        <v>أدخل الهدف</v>
+      </c>
+      <c r="C754" t="str">
+        <v>Ievadiet mērķi</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="str">
+        <v>KPI Description</v>
+      </c>
+      <c r="B755" t="str">
+        <v>وصف مؤشر الأداء</v>
+      </c>
+      <c r="C755" t="str">
+        <v>KPI apraksts</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="str">
+        <v>Enter Description</v>
+      </c>
+      <c r="B756" t="str">
+        <v>أدخل الوصف</v>
+      </c>
+      <c r="C756" t="str">
+        <v>Ievadiet aprakstu</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="str">
+        <v>KPI Data Source</v>
+      </c>
+      <c r="B757" t="str">
+        <v>مصدر بيانات مؤشر الأداء</v>
+      </c>
+      <c r="C757" t="str">
+        <v>KPI datu avots</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="str">
+        <v>Enter Data Source</v>
+      </c>
+      <c r="B758" t="str">
+        <v>أدخل مصدر البيانات</v>
+      </c>
+      <c r="C758" t="str">
+        <v>Ievadiet datu avotu</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="str">
+        <v>KPI Measurement Formula</v>
+      </c>
+      <c r="B759" t="str">
+        <v>صيغة قياس مؤشر الأداء</v>
+      </c>
+      <c r="C759" t="str">
+        <v>KPI mērīšanas formula</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="str">
+        <v>Enter the KPI Calculation Formula</v>
+      </c>
+      <c r="B760" t="str">
+        <v>أدخل صيغة حساب مؤشر الأداء</v>
+      </c>
+      <c r="C760" t="str">
+        <v>Ievadiet KPI aprēķina formulu</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="str">
+        <v>Targeted Achieved Value</v>
+      </c>
+      <c r="B761" t="str">
+        <v>القيمة المستهدفة المحققة</v>
+      </c>
+      <c r="C761" t="str">
+        <v>Mērķa sasniegtā vērtība</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="str">
+        <v>No KPI records yet</v>
+      </c>
+      <c r="B762" t="str">
+        <v>لا توجد سجلات مؤشرات أداء بعد</v>
+      </c>
+      <c r="C762" t="str">
+        <v>Vēl nav KPI ierakstu</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="str">
+        <v>No KPI Data</v>
+      </c>
+      <c r="B763" t="str">
+        <v>لا توجد بيانات مؤشرات أداء</v>
+      </c>
+      <c r="C763" t="str">
+        <v>Nav KPI datu</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="str">
+        <v>No processes have KPI measurement enabled...</v>
+      </c>
+      <c r="B764" t="str">
+        <v>لم يتم تمكين قياس مؤشرات الأداء لأي عملية...</v>
+      </c>
+      <c r="C764" t="str">
+        <v>Nevienam procesam nav iespējots KPI mērījums...</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="B765" t="str">
+        <v>غير معين</v>
+      </c>
+      <c r="C765" t="str">
+        <v>Nepiešķirts</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B766" t="str">
+        <v>أساسي</v>
+      </c>
+      <c r="C766" t="str">
+        <v>Primārais</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="str">
+        <v>Supporting</v>
+      </c>
+      <c r="B767" t="str">
+        <v>داعم</v>
+      </c>
+      <c r="C767" t="str">
+        <v>Atbalsta</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="B768" t="str">
+        <v>يدوي</v>
+      </c>
+      <c r="C768" t="str">
+        <v>Manuāls</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="B769" t="str">
+        <v>آلي</v>
+      </c>
+      <c r="C769" t="str">
+        <v>Automatizēts</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="str">
+        <v>Manual + Automated</v>
+      </c>
+      <c r="B770" t="str">
+        <v>يدوي + آلي</v>
+      </c>
+      <c r="C770" t="str">
+        <v>Manuāls + Automatizēts</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="str">
+        <v>Branch Office</v>
+      </c>
+      <c r="B771" t="str">
+        <v>فرع المكتب</v>
+      </c>
+      <c r="C771" t="str">
+        <v>Filiāles birojs</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="B772" t="str">
+        <v>عن بعد</v>
+      </c>
+      <c r="C772" t="str">
+        <v>Attālināti</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="str">
+        <v>Select frequency</v>
+      </c>
+      <c r="B773" t="str">
+        <v>اختر التكرار</v>
+      </c>
+      <c r="C773" t="str">
+        <v>Izvēlieties biežumu</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="str">
+        <v>Bi-annually</v>
+      </c>
+      <c r="B774" t="str">
+        <v>نصف سنوي</v>
+      </c>
+      <c r="C774" t="str">
+        <v>Divreiz gadā</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="str">
         <v>As needed</v>
       </c>
-      <c r="B754" t="str">
+      <c r="B775" t="str">
         <v>حسب الحاجة</v>
       </c>
-      <c r="C754" t="str">
+      <c r="C775" t="str">
         <v>Pēc vajadzības</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C754"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C775"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C775"/>
+  <dimension ref="A1:C797"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -7039,1899 +7039,2141 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Select type</v>
+        <v>Select Sub Category first</v>
       </c>
       <c r="B604" t="str">
-        <v>اختر النوع</v>
+        <v>اختر الفئة الفرعية أولاً</v>
       </c>
       <c r="C604" t="str">
-        <v>Izvēlieties tipu</v>
+        <v>Vispirms izvēlieties apakškategoriju</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Enter issue description</v>
+        <v>Select type</v>
       </c>
       <c r="B605" t="str">
-        <v>أدخل وصف القضية</v>
+        <v>اختر النوع</v>
       </c>
       <c r="C605" t="str">
-        <v>Ievadiet problēmas aprakstu</v>
+        <v>Izvēlieties tipu</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>New Stakeholder</v>
+        <v>Enter issue description</v>
       </c>
       <c r="B606" t="str">
-        <v>صاحب مصلحة جديد</v>
+        <v>أدخل وصف القضية</v>
       </c>
       <c r="C606" t="str">
-        <v>Jauna ieinteresētā puse</v>
+        <v>Ievadiet problēmas aprakstu</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Edit Stakeholder</v>
+        <v>New Stakeholder</v>
       </c>
       <c r="B607" t="str">
-        <v>تعديل صاحب المصلحة</v>
+        <v>صاحب مصلحة جديد</v>
       </c>
       <c r="C607" t="str">
-        <v>Rediģēt ieinteresēto pusi</v>
+        <v>Jauna ieinteresētā puse</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Search stakeholders...</v>
+        <v>Edit Stakeholder</v>
       </c>
       <c r="B608" t="str">
-        <v>البحث في أصحاب المصلحة...</v>
+        <v>تعديل صاحب المصلحة</v>
       </c>
       <c r="C608" t="str">
-        <v>Meklēt ieinteresētās puses...</v>
+        <v>Rediģēt ieinteresēto pusi</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Search issues...</v>
+        <v>Search stakeholders...</v>
       </c>
       <c r="B609" t="str">
-        <v>البحث في القضايا...</v>
+        <v>البحث في أصحاب المصلحة...</v>
       </c>
       <c r="C609" t="str">
-        <v>Meklēt problēmas...</v>
+        <v>Meklēt ieinteresētās puses...</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>All Types</v>
+        <v>Search issues...</v>
       </c>
       <c r="B610" t="str">
-        <v>جميع الأنواع</v>
+        <v>البحث في القضايا...</v>
       </c>
       <c r="C610" t="str">
-        <v>Visi tipi</v>
+        <v>Meklēt problēmas...</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>All Status</v>
+        <v>All Types</v>
       </c>
       <c r="B611" t="str">
-        <v>جميع الحالات</v>
+        <v>جميع الأنواع</v>
       </c>
       <c r="C611" t="str">
-        <v>Visi statusi</v>
+        <v>Visi tipi</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>All Categories</v>
+        <v>All Status</v>
       </c>
       <c r="B612" t="str">
-        <v>جميع الفئات</v>
+        <v>جميع الحالات</v>
       </c>
       <c r="C612" t="str">
-        <v>Visas kategorijas</v>
+        <v>Visi statusi</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>All Domains</v>
+        <v>All Categories</v>
       </c>
       <c r="B613" t="str">
-        <v>جميع المجالات</v>
+        <v>جميع الفئات</v>
       </c>
       <c r="C613" t="str">
-        <v>Visi domēni</v>
+        <v>Visas kategorijas</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>No Issues Found</v>
+        <v>All Domains</v>
       </c>
       <c r="B614" t="str">
-        <v>لم يتم العثور على قضايا</v>
+        <v>جميع المجالات</v>
       </c>
       <c r="C614" t="str">
-        <v>Problēmas nav atrastas</v>
+        <v>Visi domēni</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Try adjusting your filters to find issues.</v>
+        <v>No Issues Found</v>
       </c>
       <c r="B615" t="str">
-        <v>حاول تعديل الفلاتر للعثور على القضايا.</v>
+        <v>لم يتم العثور على قضايا</v>
       </c>
       <c r="C615" t="str">
-        <v>Mēģiniet pielāgot filtrus, lai atrastu problēmas.</v>
+        <v>Problēmas nav atrastas</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Create your first issue to get started.</v>
+        <v>Try adjusting your filters to find issues.</v>
       </c>
       <c r="B616" t="str">
-        <v>أنشئ أول قضية للبدء.</v>
+        <v>حاول تعديل الفلاتر للعثور على القضايا.</v>
       </c>
       <c r="C616" t="str">
-        <v>Izveidojiet savu pirmo problēmu, lai sāktu.</v>
+        <v>Mēģiniet pielāgot filtrus, lai atrastu problēmas.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Create Action</v>
+        <v>Create your first issue to get started.</v>
       </c>
       <c r="B617" t="str">
-        <v>إنشاء إجراء</v>
+        <v>أنشئ أول قضية للبدء.</v>
       </c>
       <c r="C617" t="str">
-        <v>Izveidot darbību</v>
+        <v>Izveidojiet savu pirmo problēmu, lai sāktu.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>View Actions</v>
+        <v>Create Action</v>
       </c>
       <c r="B618" t="str">
-        <v>عرض الإجراءات</v>
+        <v>إنشاء إجراء</v>
       </c>
       <c r="C618" t="str">
-        <v>Skatīt darbības</v>
+        <v>Izveidot darbību</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Review Actions</v>
+        <v>View Actions</v>
       </c>
       <c r="B619" t="str">
-        <v>مراجعة الإجراءات</v>
+        <v>عرض الإجراءات</v>
       </c>
       <c r="C619" t="str">
-        <v>Pārskatīt darbības</v>
+        <v>Skatīt darbības</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Select stakeholder</v>
+        <v>Review Actions</v>
       </c>
       <c r="B620" t="str">
-        <v>اختر صاحب المصلحة</v>
+        <v>مراجعة الإجراءات</v>
       </c>
       <c r="C620" t="str">
-        <v>Izvēlieties ieinteresēto pusi</v>
+        <v>Pārskatīt darbības</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Need and Expectation</v>
+        <v>Select stakeholder</v>
       </c>
       <c r="B621" t="str">
-        <v>الاحتياجات والتوقعات</v>
+        <v>اختر صاحب المصلحة</v>
       </c>
       <c r="C621" t="str">
-        <v>Vajadzība un gaidījums</v>
+        <v>Izvēlieties ieinteresēto pusi</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Select need/expectation</v>
+        <v>Need and Expectation</v>
       </c>
       <c r="B622" t="str">
-        <v>اختر الاحتياج/التوقع</v>
+        <v>الاحتياجات والتوقعات</v>
       </c>
       <c r="C622" t="str">
-        <v>Izvēlieties vajadzību/gaidījumu</v>
+        <v>Vajadzība un gaidījums</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Stakeholder Needs and Expectations</v>
+        <v>Select need/expectation</v>
       </c>
       <c r="B623" t="str">
-        <v>احتياجات وتوقعات أصحاب المصلحة</v>
+        <v>اختر الاحتياج/التوقع</v>
       </c>
       <c r="C623" t="str">
-        <v>Ieinteresēto pušu vajadzības un gaidījumi</v>
+        <v>Izvēlieties vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Add New Domain</v>
+        <v>Stakeholder Needs and Expectations</v>
       </c>
       <c r="B624" t="str">
-        <v>إضافة مجال جديد</v>
+        <v>احتياجات وتوقعات أصحاب المصلحة</v>
       </c>
       <c r="C624" t="str">
-        <v>Pievienot jaunu domēnu</v>
+        <v>Ieinteresēto pušu vajadzības un gaidījumi</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Enter domain name</v>
+        <v>Add New Domain</v>
       </c>
       <c r="B625" t="str">
-        <v>أدخل اسم المجال</v>
+        <v>إضافة مجال جديد</v>
       </c>
       <c r="C625" t="str">
-        <v>Ievadiet domēna nosaukumu</v>
+        <v>Pievienot jaunu domēnu</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Add New Category</v>
+        <v>Enter domain name</v>
       </c>
       <c r="B626" t="str">
-        <v>إضافة فئة جديدة</v>
+        <v>أدخل اسم المجال</v>
       </c>
       <c r="C626" t="str">
-        <v>Pievienot jaunu kategoriju</v>
+        <v>Ievadiet domēna nosaukumu</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Add New Issue Type</v>
+        <v>Add New Category</v>
       </c>
       <c r="B627" t="str">
-        <v>إضافة نوع قضية جديد</v>
+        <v>إضافة فئة جديدة</v>
       </c>
       <c r="C627" t="str">
-        <v>Pievienot jaunu problēmas tipu</v>
+        <v>Pievienot jaunu kategoriju</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Issue Type Name</v>
+        <v>Add New Issue Type</v>
       </c>
       <c r="B628" t="str">
-        <v>اسم نوع القضية</v>
+        <v>إضافة نوع قضية جديد</v>
       </c>
       <c r="C628" t="str">
-        <v>Problēmas tipa nosaukums</v>
+        <v>Pievienot jaunu problēmas tipu</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Enter issue type name</v>
+        <v>Issue Type Name</v>
       </c>
       <c r="B629" t="str">
-        <v>أدخل اسم نوع القضية</v>
+        <v>اسم نوع القضية</v>
       </c>
       <c r="C629" t="str">
-        <v>Ievadiet problēmas tipa nosaukumu</v>
+        <v>Problēmas tipa nosaukums</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Link Process</v>
+        <v>Enter issue type name</v>
       </c>
       <c r="B630" t="str">
-        <v>ربط العملية</v>
+        <v>أدخل اسم نوع القضية</v>
       </c>
       <c r="C630" t="str">
-        <v>Saistīt procesu</v>
+        <v>Ievadiet problēmas tipa nosaukumu</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No processes found</v>
+        <v>Link Process</v>
       </c>
       <c r="B631" t="str">
-        <v>لم يتم العثور على عمليات</v>
+        <v>ربط العملية</v>
       </c>
       <c r="C631" t="str">
-        <v>Procesi nav atrasti</v>
+        <v>Saistīt procesu</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Add New Need/Expectation</v>
+        <v>No processes found</v>
       </c>
       <c r="B632" t="str">
-        <v>إضافة احتياج/توقع جديد</v>
+        <v>لم يتم العثور على عمليات</v>
       </c>
       <c r="C632" t="str">
-        <v>Pievienot jaunu vajadzību/gaidījumu</v>
+        <v>Procesi nav atrasti</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Need/Expectation</v>
+        <v>Add New Need/Expectation</v>
       </c>
       <c r="B633" t="str">
-        <v>الاحتياج/التوقع</v>
+        <v>إضافة احتياج/توقع جديد</v>
       </c>
       <c r="C633" t="str">
-        <v>Vajadzība/Gaidījums</v>
+        <v>Pievienot jaunu vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Enter need/expectation</v>
+        <v>Need/Expectation</v>
       </c>
       <c r="B634" t="str">
-        <v>أدخل الاحتياج/التوقع</v>
+        <v>الاحتياج/التوقع</v>
       </c>
       <c r="C634" t="str">
-        <v>Ievadiet vajadzību/gaidījumu</v>
+        <v>Vajadzība/Gaidījums</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Enter a new need or expectation type.</v>
+        <v>Enter need/expectation</v>
       </c>
       <c r="B635" t="str">
-        <v>أدخل نوع احتياج أو توقع جديد.</v>
+        <v>أدخل الاحتياج/التوقع</v>
       </c>
       <c r="C635" t="str">
-        <v>Ievadiet jaunu vajadzības vai gaidījumu tipu.</v>
+        <v>Ievadiet vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Title is required</v>
+        <v>Enter a new need or expectation type.</v>
       </c>
       <c r="B636" t="str">
-        <v>العنوان مطلوب</v>
+        <v>أدخل نوع احتياج أو توقع جديد.</v>
       </c>
       <c r="C636" t="str">
-        <v>Nosaukums ir obligāts</v>
+        <v>Ievadiet jaunu vajadzības vai gaidījumu tipu.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Issue created successfully</v>
+        <v>Title is required</v>
       </c>
       <c r="B637" t="str">
-        <v>تم إنشاء القضية بنجاح</v>
+        <v>العنوان مطلوب</v>
       </c>
       <c r="C637" t="str">
-        <v>Problēma veiksmīgi izveidota</v>
+        <v>Nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Failed to create issue</v>
+        <v>Issue created successfully</v>
       </c>
       <c r="B638" t="str">
-        <v>فشل في إنشاء القضية</v>
+        <v>تم إنشاء القضية بنجاح</v>
       </c>
       <c r="C638" t="str">
-        <v>Neizdevās izveidot problēmu</v>
+        <v>Problēma veiksmīgi izveidota</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Issue updated successfully</v>
+        <v>Failed to create issue</v>
       </c>
       <c r="B639" t="str">
-        <v>تم تحديث القضية بنجاح</v>
+        <v>فشل في إنشاء القضية</v>
       </c>
       <c r="C639" t="str">
-        <v>Problēma veiksmīgi atjaunināta</v>
+        <v>Neizdevās izveidot problēmu</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Failed to update issue</v>
+        <v>Issue updated successfully</v>
       </c>
       <c r="B640" t="str">
-        <v>فشل في تحديث القضية</v>
+        <v>تم تحديث القضية بنجاح</v>
       </c>
       <c r="C640" t="str">
-        <v>Neizdevās atjaunināt problēmu</v>
+        <v>Problēma veiksmīgi atjaunināta</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Stakeholder updated successfully</v>
+        <v>Failed to update issue</v>
       </c>
       <c r="B641" t="str">
-        <v>تم تحديث صاحب المصلحة بنجاح</v>
+        <v>فشل في تحديث القضية</v>
       </c>
       <c r="C641" t="str">
-        <v>Ieinteresētā puse veiksmīgi atjaunināta</v>
+        <v>Neizdevās atjaunināt problēmu</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Failed to update stakeholder</v>
+        <v>Stakeholder updated successfully</v>
       </c>
       <c r="B642" t="str">
-        <v>فشل في تحديث صاحب المصلحة</v>
+        <v>تم تحديث صاحب المصلحة بنجاح</v>
       </c>
       <c r="C642" t="str">
-        <v>Neizdevās atjaunināt ieinteresēto pusi</v>
+        <v>Ieinteresētā puse veiksmīgi atjaunināta</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Open</v>
+        <v>Failed to update stakeholder</v>
       </c>
       <c r="B643" t="str">
-        <v>مفتوح</v>
+        <v>فشل في تحديث صاحب المصلحة</v>
       </c>
       <c r="C643" t="str">
-        <v>Atvērts</v>
+        <v>Neizdevās atjaunināt ieinteresēto pusi</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>In Progress</v>
+        <v>Open</v>
       </c>
       <c r="B644" t="str">
-        <v>قيد التنفيذ</v>
+        <v>مفتوح</v>
       </c>
       <c r="C644" t="str">
-        <v>Procesā</v>
+        <v>Atvērts</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Action type and description are required</v>
+        <v>In Progress</v>
       </c>
       <c r="B645" t="str">
-        <v>نوع الإجراء والوصف مطلوبان</v>
+        <v>قيد التنفيذ</v>
       </c>
       <c r="C645" t="str">
-        <v>Darbības tips un apraksts ir obligāti</v>
+        <v>Procesā</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Action created successfully</v>
+        <v>Action type and description are required</v>
       </c>
       <c r="B646" t="str">
-        <v>تم إنشاء الإجراء بنجاح</v>
+        <v>نوع الإجراء والوصف مطلوبان</v>
       </c>
       <c r="C646" t="str">
-        <v>Darbība veiksmīgi izveidota</v>
+        <v>Darbības tips un apraksts ir obligāti</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Failed to create action</v>
+        <v>Action created successfully</v>
       </c>
       <c r="B647" t="str">
-        <v>فشل في إنشاء الإجراء</v>
+        <v>تم إنشاء الإجراء بنجاح</v>
       </c>
       <c r="C647" t="str">
-        <v>Neizdevās izveidot darbību</v>
+        <v>Darbība veiksmīgi izveidota</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Action is resolved</v>
+        <v>Failed to create action</v>
       </c>
       <c r="B648" t="str">
-        <v>تم حل الإجراء</v>
+        <v>فشل في إنشاء الإجراء</v>
       </c>
       <c r="C648" t="str">
-        <v>Darbība ir atrisināta</v>
+        <v>Neizdevās izveidot darbību</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Failed to resolve action</v>
+        <v>Action is resolved</v>
       </c>
       <c r="B649" t="str">
-        <v>فشل في حل الإجراء</v>
+        <v>تم حل الإجراء</v>
       </c>
       <c r="C649" t="str">
-        <v>Neizdevās atrisināt darbību</v>
+        <v>Darbība ir atrisināta</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Comment is required</v>
+        <v>Failed to resolve action</v>
       </c>
       <c r="B650" t="str">
-        <v>التعليق مطلوب</v>
+        <v>فشل في حل الإجراء</v>
       </c>
       <c r="C650" t="str">
-        <v>Komentārs ir obligāts</v>
+        <v>Neizdevās atrisināt darbību</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Action is sent back</v>
+        <v>Comment is required</v>
       </c>
       <c r="B651" t="str">
-        <v>تم إرجاع الإجراء</v>
+        <v>التعليق مطلوب</v>
       </c>
       <c r="C651" t="str">
-        <v>Darbība ir nosūtīta atpakaļ</v>
+        <v>Komentārs ir obligāts</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Failed to send back action</v>
+        <v>Action is sent back</v>
       </c>
       <c r="B652" t="str">
-        <v>فشل في إرجاع الإجراء</v>
+        <v>تم إرجاع الإجراء</v>
       </c>
       <c r="C652" t="str">
-        <v>Neizdevās nosūtīt atpakaļ darbību</v>
+        <v>Darbība ir nosūtīta atpakaļ</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Action updated and resubmitted</v>
+        <v>Failed to send back action</v>
       </c>
       <c r="B653" t="str">
-        <v>تم تحديث الإجراء وإعادة إرساله</v>
+        <v>فشل في إرجاع الإجراء</v>
       </c>
       <c r="C653" t="str">
-        <v>Darbība atjaunināta un atkārtoti iesniegta</v>
+        <v>Neizdevās nosūtīt atpakaļ darbību</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Failed to update action</v>
+        <v>Action updated and resubmitted</v>
       </c>
       <c r="B654" t="str">
-        <v>فشل في تحديث الإجراء</v>
+        <v>تم تحديث الإجراء وإعادة إرساله</v>
       </c>
       <c r="C654" t="str">
-        <v>Neizdevās atjaunināt darbību</v>
+        <v>Darbība atjaunināta un atkārtoti iesniegta</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Saving...</v>
+        <v>Failed to update action</v>
       </c>
       <c r="B655" t="str">
-        <v>جاري الحفظ...</v>
+        <v>فشل في تحديث الإجراء</v>
       </c>
       <c r="C655" t="str">
-        <v>Saglabā...</v>
+        <v>Neizdevās atjaunināt darbību</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Save &amp; Resubmit</v>
+        <v>Saving...</v>
       </c>
       <c r="B656" t="str">
-        <v>حفظ وإعادة الإرسال</v>
+        <v>جاري الحفظ...</v>
       </c>
       <c r="C656" t="str">
-        <v>Saglabāt un iesniegt atkārtoti</v>
+        <v>Saglabā...</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Import Issues</v>
+        <v>Save &amp; Resubmit</v>
       </c>
       <c r="B657" t="str">
-        <v>استيراد القضايا</v>
+        <v>حفظ وإعادة الإرسال</v>
       </c>
       <c r="C657" t="str">
-        <v>Importēt problēmas</v>
+        <v>Saglabāt un iesniegt atkārtoti</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>CSV file must have a header row and at least one data row</v>
+        <v>Import Issues</v>
       </c>
       <c r="B658" t="str">
-        <v>يجب أن يحتوي ملف CSV على صف رأس وصف بيانات واحد على الأقل</v>
+        <v>استيراد القضايا</v>
       </c>
       <c r="C658" t="str">
-        <v>CSV failam jābūt galvenes rindai un vismaz vienai datu rindai</v>
+        <v>Importēt problēmas</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>CSV must have a "title" column</v>
+        <v>CSV file must have a header row and at least one data row</v>
       </c>
       <c r="B659" t="str">
-        <v>يجب أن يحتوي ملف CSV على عمود "title"</v>
+        <v>يجب أن يحتوي ملف CSV على صف رأس وصف بيانات واحد على الأقل</v>
       </c>
       <c r="C659" t="str">
-        <v>CSV ir jābūt kolonnai "title"</v>
+        <v>CSV failam jābūt galvenes rindai un vismaz vienai datu rindai</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Successfully imported</v>
+        <v>CSV must have a "title" column</v>
       </c>
       <c r="B660" t="str">
-        <v>تم الاستيراد بنجاح</v>
+        <v>يجب أن يحتوي ملف CSV على عمود "title"</v>
       </c>
       <c r="C660" t="str">
-        <v>Veiksmīgi importēts</v>
+        <v>CSV ir jābūt kolonnai "title"</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>issues</v>
+        <v>Successfully imported</v>
       </c>
       <c r="B661" t="str">
-        <v>قضايا</v>
+        <v>تم الاستيراد بنجاح</v>
       </c>
       <c r="C661" t="str">
-        <v>problēmas</v>
+        <v>Veiksmīgi importēts</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Error importing issues. Please check the file format.</v>
+        <v>issues</v>
       </c>
       <c r="B662" t="str">
-        <v>خطأ في استيراد القضايا. يرجى التحقق من تنسيق الملف.</v>
+        <v>قضايا</v>
       </c>
       <c r="C662" t="str">
-        <v>Kļūda importējot problēmas. Lūdzu, pārbaudiet faila formātu.</v>
+        <v>problēmas</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>File attached to action</v>
+        <v>Error importing issues. Please check the file format.</v>
       </c>
       <c r="B663" t="str">
-        <v>تم إرفاق الملف بالإجراء</v>
+        <v>خطأ في استيراد القضايا. يرجى التحقق من تنسيق الملف.</v>
       </c>
       <c r="C663" t="str">
-        <v>Fails pievienots darbībai</v>
+        <v>Kļūda importējot problēmas. Lūdzu, pārbaudiet faila formātu.</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Failed to attach file to action</v>
+        <v>File attached to action</v>
       </c>
       <c r="B664" t="str">
-        <v>فشل في إرفاق الملف بالإجراء</v>
+        <v>تم إرفاق الملف بالإجراء</v>
       </c>
       <c r="C664" t="str">
-        <v>Neizdevās pievienot failu darbībai</v>
+        <v>Fails pievienots darbībai</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>File deleted successfully</v>
+        <v>Failed to attach file to action</v>
       </c>
       <c r="B665" t="str">
-        <v>تم حذف الملف بنجاح</v>
+        <v>فشل في إرفاق الملف بالإجراء</v>
       </c>
       <c r="C665" t="str">
-        <v>Fails veiksmīgi dzēsts</v>
+        <v>Neizdevās pievienot failu darbībai</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Failed to delete file</v>
+        <v>File deleted successfully</v>
       </c>
       <c r="B666" t="str">
-        <v>فشل في حذف الملف</v>
+        <v>تم حذف الملف بنجاح</v>
       </c>
       <c r="C666" t="str">
-        <v>Neizdevās dzēst failu</v>
+        <v>Fails veiksmīgi dzēsts</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Repository</v>
+        <v>Failed to delete file</v>
       </c>
       <c r="B667" t="str">
-        <v>المستودع</v>
+        <v>فشل في حذف الملف</v>
       </c>
       <c r="C667" t="str">
-        <v>Repozitorijs</v>
+        <v>Neizdevās dzēst failu</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Performance Dashboard</v>
+        <v>Repository</v>
       </c>
       <c r="B668" t="str">
-        <v>لوحة الأداء</v>
+        <v>المستودع</v>
       </c>
       <c r="C668" t="str">
-        <v>Veiktspējas panelis</v>
+        <v>Repozitorijs</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Search By Process ID, Name</v>
+        <v>Performance Dashboard</v>
       </c>
       <c r="B669" t="str">
-        <v>البحث بمعرف العملية أو الاسم</v>
+        <v>لوحة الأداء</v>
       </c>
       <c r="C669" t="str">
-        <v>Meklēt pēc procesa ID, nosaukuma</v>
+        <v>Veiktspējas panelis</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>All Owners</v>
+        <v>Search By Process ID, Name</v>
       </c>
       <c r="B670" t="str">
-        <v>جميع المالكين</v>
+        <v>البحث بمعرف العملية أو الاسم</v>
       </c>
       <c r="C670" t="str">
-        <v>Visi īpašnieki</v>
+        <v>Meklēt pēc procesa ID, nosaukuma</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>All Frequencies</v>
+        <v>All Owners</v>
       </c>
       <c r="B671" t="str">
-        <v>جميع الترددات</v>
+        <v>جميع المالكين</v>
       </c>
       <c r="C671" t="str">
-        <v>Visi biežumi</v>
+        <v>Visi īpašnieki</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Edit Process</v>
+        <v>All Frequencies</v>
       </c>
       <c r="B672" t="str">
-        <v>تعديل العملية</v>
+        <v>جميع الترددات</v>
       </c>
       <c r="C672" t="str">
-        <v>Rediģēt procesu</v>
+        <v>Visi biežumi</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Confirm Delete</v>
+        <v>Edit Process</v>
       </c>
       <c r="B673" t="str">
-        <v>تأكيد الحذف</v>
+        <v>تعديل العملية</v>
       </c>
       <c r="C673" t="str">
-        <v>Apstiprināt dzēšanu</v>
+        <v>Rediģēt procesu</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Are you sure you want to delete this process? This action cannot be undone.</v>
+        <v>Confirm Delete</v>
       </c>
       <c r="B674" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه العملية؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>تأكيد الحذف</v>
       </c>
       <c r="C674" t="str">
-        <v>Vai tiešām vēlaties dzēst šo procesu? Šo darbību nevar atsaukt.</v>
+        <v>Apstiprināt dzēšanu</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Add New Process</v>
+        <v>Are you sure you want to delete this process? This action cannot be undone.</v>
       </c>
       <c r="B675" t="str">
-        <v>إضافة عملية جديدة</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه العملية؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C675" t="str">
-        <v>Pievienot jaunu procesu</v>
+        <v>Vai tiešām vēlaties dzēst šo procesu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Basic Information</v>
+        <v>Add New Process</v>
       </c>
       <c r="B676" t="str">
-        <v>المعلومات الأساسية</v>
+        <v>إضافة عملية جديدة</v>
       </c>
       <c r="C676" t="str">
-        <v>Pamatinformācija</v>
+        <v>Pievienot jaunu procesu</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Process Details</v>
+        <v>Basic Information</v>
       </c>
       <c r="B677" t="str">
-        <v>تفاصيل العملية</v>
+        <v>المعلومات الأساسية</v>
       </c>
       <c r="C677" t="str">
-        <v>Procesa detaļas</v>
+        <v>Pamatinformācija</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Dependencies &amp; Options</v>
+        <v>Process Details</v>
       </c>
       <c r="B678" t="str">
-        <v>التبعيات والخيارات</v>
+        <v>تفاصيل العملية</v>
       </c>
       <c r="C678" t="str">
-        <v>Atkarības un opcijas</v>
+        <v>Procesa detaļas</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>RACI Matrix</v>
+        <v>Dependencies &amp; Options</v>
       </c>
       <c r="B679" t="str">
-        <v>مصفوفة RACI</v>
+        <v>التبعيات والخيارات</v>
       </c>
       <c r="C679" t="str">
-        <v>RACI matrica</v>
+        <v>Atkarības un opcijas</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Enter process name</v>
+        <v>RACI Matrix</v>
       </c>
       <c r="B680" t="str">
-        <v>أدخل اسم العملية</v>
+        <v>مصفوفة RACI</v>
       </c>
       <c r="C680" t="str">
-        <v>Ievadiet procesa nosaukumu</v>
+        <v>RACI matrica</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Enter process description</v>
+        <v>Enter process name</v>
       </c>
       <c r="B681" t="str">
-        <v>أدخل وصف العملية</v>
+        <v>أدخل اسم العملية</v>
       </c>
       <c r="C681" t="str">
-        <v>Ievadiet procesa aprakstu</v>
+        <v>Ievadiet procesa nosaukumu</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Nature of Implementation</v>
+        <v>Enter process description</v>
       </c>
       <c r="B682" t="str">
-        <v>طبيعة التنفيذ</v>
+        <v>أدخل وصف العملية</v>
       </c>
       <c r="C682" t="str">
-        <v>Ieviešanas veids</v>
+        <v>Ievadiet procesa aprakstu</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Select implementation type</v>
+        <v>Nature of Implementation</v>
       </c>
       <c r="B683" t="str">
-        <v>اختر نوع التنفيذ</v>
+        <v>طبيعة التنفيذ</v>
       </c>
       <c r="C683" t="str">
-        <v>Izvēlieties ieviešanas tipu</v>
+        <v>Ieviešanas veids</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Select location</v>
+        <v>Select implementation type</v>
       </c>
       <c r="B684" t="str">
-        <v>اختر الموقع</v>
+        <v>اختر نوع التنفيذ</v>
       </c>
       <c r="C684" t="str">
-        <v>Izvēlieties atrašanās vietu</v>
+        <v>Izvēlieties ieviešanas tipu</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Operational Complexity</v>
+        <v>Select location</v>
       </c>
       <c r="B685" t="str">
-        <v>التعقيد التشغيلي</v>
+        <v>اختر الموقع</v>
       </c>
       <c r="C685" t="str">
-        <v>Operacionālā sarežģītība</v>
+        <v>Izvēlieties atrašanās vietu</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Select complexity</v>
+        <v>Operational Complexity</v>
       </c>
       <c r="B686" t="str">
-        <v>اختر التعقيد</v>
+        <v>التعقيد التشغيلي</v>
       </c>
       <c r="C686" t="str">
-        <v>Izvēlieties sarežģītību</v>
+        <v>Operacionālā sarežģītība</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Asset Dependency</v>
+        <v>Select complexity</v>
       </c>
       <c r="B687" t="str">
-        <v>تبعية الأصول</v>
+        <v>اختر التعقيد</v>
       </c>
       <c r="C687" t="str">
-        <v>Aktīvu atkarība</v>
+        <v>Izvēlieties sarežģītību</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>External Dependency</v>
+        <v>Asset Dependency</v>
       </c>
       <c r="B688" t="str">
-        <v>تبعية خارجية</v>
+        <v>تبعية الأصول</v>
       </c>
       <c r="C688" t="str">
-        <v>Ārējā atkarība</v>
+        <v>Aktīvu atkarība</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>KPI Measurement Required</v>
+        <v>External Dependency</v>
       </c>
       <c r="B689" t="str">
-        <v>قياس مؤشرات الأداء مطلوب</v>
+        <v>تبعية خارجية</v>
       </c>
       <c r="C689" t="str">
-        <v>Nepieciešams KPI mērījums</v>
+        <v>Ārējā atkarība</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>PII Capture</v>
+        <v>KPI Measurement Required</v>
       </c>
       <c r="B690" t="str">
-        <v>التقاط البيانات الشخصية</v>
+        <v>قياس مؤشرات الأداء مطلوب</v>
       </c>
       <c r="C690" t="str">
-        <v>PII uztveršana</v>
+        <v>Nepieciešams KPI mērījums</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Auto-generated</v>
+        <v>PII Capture</v>
       </c>
       <c r="B691" t="str">
-        <v>يتم إنشاؤه تلقائياً</v>
+        <v>التقاط البيانات الشخصية</v>
       </c>
       <c r="C691" t="str">
-        <v>Automātiski ģenerēts</v>
+        <v>PII uztveršana</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Process created successfully</v>
+        <v>Auto-generated</v>
       </c>
       <c r="B692" t="str">
-        <v>تم إنشاء العملية بنجاح</v>
+        <v>يتم إنشاؤه تلقائياً</v>
       </c>
       <c r="C692" t="str">
-        <v>Process veiksmīgi izveidots</v>
+        <v>Automātiski ģenerēts</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Failed to create process</v>
+        <v>Auto-generated if left empty</v>
       </c>
       <c r="B693" t="str">
-        <v>فشل في إنشاء العملية</v>
+        <v>يتم إنشاؤه تلقائياً إذا تُرك فارغاً</v>
       </c>
       <c r="C693" t="str">
-        <v>Neizdevās izveidot procesu</v>
+        <v>Automātiski ģenerēts, ja atstāts tukšs</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Process updated successfully</v>
+        <v>Risk name is required</v>
       </c>
       <c r="B694" t="str">
-        <v>تم تحديث العملية بنجاح</v>
+        <v>اسم المخاطرة مطلوب</v>
       </c>
       <c r="C694" t="str">
-        <v>Process veiksmīgi atjaunināts</v>
+        <v>Riska nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Failed to update process</v>
+        <v>Risk description is required</v>
       </c>
       <c r="B695" t="str">
-        <v>فشل في تحديث العملية</v>
+        <v>وصف المخاطرة مطلوب</v>
       </c>
       <c r="C695" t="str">
-        <v>Neizdevās atjaunināt procesu</v>
+        <v>Riska apraksts ir obligāts</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Please fill in required fields (Name and Process Type)</v>
+        <v>Inherent likelihood is required</v>
       </c>
       <c r="B696" t="str">
-        <v>يرجى ملء الحقول المطلوبة (الاسم ونوع العملية)</v>
+        <v>احتمالية المخاطر الكامنة مطلوبة</v>
       </c>
       <c r="C696" t="str">
-        <v>Lūdzu, aizpildiet obligātos laukus (Nosaukums un procesa tips)</v>
+        <v>Iedzimtā varbūtība ir obligāta</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Save Changes</v>
+        <v>Inherent impact is required</v>
       </c>
       <c r="B697" t="str">
-        <v>حفظ التغييرات</v>
+        <v>تأثير المخاطر الكامنة مطلوب</v>
       </c>
       <c r="C697" t="str">
-        <v>Saglabāt izmaiņas</v>
+        <v>Iedzimtā ietekme ir obligāta</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>Reference ID</v>
+        <v>Residual likelihood is required</v>
       </c>
       <c r="B698" t="str">
-        <v>المعرف المرجعي</v>
+        <v>احتمالية المخاطر المتبقية مطلوبة</v>
       </c>
       <c r="C698" t="str">
-        <v>Atsauces ID</v>
+        <v>Atlikušā varbūtība ir obligāta</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>Process Criticality</v>
+        <v>Residual impact is required</v>
       </c>
       <c r="B699" t="str">
-        <v>أهمية العملية</v>
+        <v>تأثير المخاطر المتبقية مطلوب</v>
       </c>
       <c r="C699" t="str">
-        <v>Procesa kritiskums</v>
+        <v>Atlikušā ietekme ir obligāta</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>Process Frequency</v>
+        <v>Process created successfully</v>
       </c>
       <c r="B700" t="str">
-        <v>تكرار العملية</v>
+        <v>تم إنشاء العملية بنجاح</v>
       </c>
       <c r="C700" t="str">
-        <v>Procesa biežums</v>
+        <v>Process veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Nature Of Implementation</v>
+        <v>Failed to create process</v>
       </c>
       <c r="B701" t="str">
-        <v>طبيعة التنفيذ</v>
+        <v>فشل في إنشاء العملية</v>
       </c>
       <c r="C701" t="str">
-        <v>Ieviešanas veids</v>
+        <v>Neizdevās izveidot procesu</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>AI Risk</v>
+        <v>Process updated successfully</v>
       </c>
       <c r="B702" t="str">
-        <v>مخاطر الذكاء الاصطناعي</v>
+        <v>تم تحديث العملية بنجاح</v>
       </c>
       <c r="C702" t="str">
-        <v>AI risks</v>
+        <v>Process veiksmīgi atjaunināts</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>AI Risk Evaluation</v>
+        <v>Failed to update process</v>
       </c>
       <c r="B703" t="str">
-        <v>تقييم مخاطر الذكاء الاصطناعي</v>
+        <v>فشل في تحديث العملية</v>
       </c>
       <c r="C703" t="str">
-        <v>AI risku novērtējums</v>
+        <v>Neizdevās atjaunināt procesu</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>AI is identifying potential risks...</v>
+        <v>Please fill in required fields (Name and Process Type)</v>
       </c>
       <c r="B704" t="str">
-        <v>الذكاء الاصطناعي يحدد المخاطر المحتملة...</v>
+        <v>يرجى ملء الحقول المطلوبة (الاسم ونوع العملية)</v>
       </c>
       <c r="C704" t="str">
-        <v>AI identificē potenciālos riskus...</v>
+        <v>Lūdzu, aizpildiet obligātos laukus (Nosaukums un procesa tips)</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>This may take up to 30 seconds</v>
+        <v>Save Changes</v>
       </c>
       <c r="B705" t="str">
-        <v>قد يستغرق هذا ما يصل إلى 30 ثانية</v>
+        <v>حفظ التغييرات</v>
       </c>
       <c r="C705" t="str">
-        <v>Tas var aizņemt līdz 30 sekundēm</v>
+        <v>Saglabāt izmaiņas</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>Detected Risks</v>
+        <v>Reference ID</v>
       </c>
       <c r="B706" t="str">
-        <v>المخاطر المكتشفة</v>
+        <v>المعرف المرجعي</v>
       </c>
       <c r="C706" t="str">
-        <v>Atklātie riski</v>
+        <v>Atsauces ID</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>The AI has identified the following risks, threats, and suggested controls...</v>
+        <v>Process Criticality</v>
       </c>
       <c r="B707" t="str">
-        <v>حدد الذكاء الاصطناعي المخاطر والتهديدات والضوابط المقترحة التالية...</v>
+        <v>أهمية العملية</v>
       </c>
       <c r="C707" t="str">
-        <v>AI ir identificējis šādus riskus, draudus un ieteiktos kontroles...</v>
+        <v>Procesa kritiskums</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>Threats</v>
+        <v>Process Frequency</v>
       </c>
       <c r="B708" t="str">
-        <v>التهديدات</v>
+        <v>تكرار العملية</v>
       </c>
       <c r="C708" t="str">
-        <v>Draudi</v>
+        <v>Procesa biežums</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>Suggested Controls</v>
+        <v>Nature Of Implementation</v>
       </c>
       <c r="B709" t="str">
-        <v>الضوابط المقترحة</v>
+        <v>طبيعة التنفيذ</v>
       </c>
       <c r="C709" t="str">
-        <v>Ieteiktās kontroles</v>
+        <v>Ieviešanas veids</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>No risks generated yet.</v>
+        <v>AI Risk</v>
       </c>
       <c r="B710" t="str">
-        <v>لم يتم إنشاء مخاطر بعد.</v>
+        <v>مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C710" t="str">
-        <v>Vēl nav ģenerēti riski.</v>
+        <v>AI risks</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>AI Risks Generated</v>
+        <v>AI Risk Evaluation</v>
       </c>
       <c r="B711" t="str">
-        <v>تم إنشاء مخاطر الذكاء الاصطناعي</v>
+        <v>تقييم مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C711" t="str">
-        <v>AI riski ģenerēti</v>
+        <v>AI risku novērtējums</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>AI Generation Failed</v>
+        <v>AI is identifying potential risks...</v>
       </c>
       <c r="B712" t="str">
-        <v>فشل إنشاء الذكاء الاصطناعي</v>
+        <v>الذكاء الاصطناعي يحدد المخاطر المحتملة...</v>
       </c>
       <c r="C712" t="str">
-        <v>AI ģenerēšana neizdevās</v>
+        <v>AI identificē potenciālos riskus...</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>Communication with AI service failed.</v>
+        <v>This may take up to 30 seconds</v>
       </c>
       <c r="B713" t="str">
-        <v>فشل الاتصال بخدمة الذكاء الاصطناعي.</v>
+        <v>قد يستغرق هذا ما يصل إلى 30 ثانية</v>
       </c>
       <c r="C713" t="str">
-        <v>Saziņa ar AI servisu neizdevās.</v>
+        <v>Tas var aizņemt līdz 30 sekundēm</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>Please try again later.</v>
+        <v>Detected Risks</v>
       </c>
       <c r="B714" t="str">
-        <v>يرجى المحاولة مرة أخرى لاحقاً.</v>
+        <v>المخاطر المكتشفة</v>
       </c>
       <c r="C714" t="str">
-        <v>Lūdzu, mēģiniet vēlreiz vēlāk.</v>
+        <v>Atklātie riski</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>Go to Risk Register</v>
+        <v>The AI has identified the following risks, threats, and suggested controls...</v>
       </c>
       <c r="B715" t="str">
-        <v>الذهاب إلى سجل المخاطر</v>
+        <v>حدد الذكاء الاصطناعي المخاطر والتهديدات والضوابط المقترحة التالية...</v>
       </c>
       <c r="C715" t="str">
-        <v>Doties uz risku reģistru</v>
+        <v>AI ir identificējis šādus riskus, draudus un ieteiktos kontroles...</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>Add to Risk Register</v>
+        <v>Threats</v>
       </c>
       <c r="B716" t="str">
-        <v>إضافة إلى سجل المخاطر</v>
+        <v>التهديدات</v>
       </c>
       <c r="C716" t="str">
-        <v>Pievienot risku reģistram</v>
+        <v>Draudi</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>Adding...</v>
+        <v>Suggested Controls</v>
       </c>
       <c r="B717" t="str">
-        <v>جاري الإضافة...</v>
+        <v>الضوابط المقترحة</v>
       </c>
       <c r="C717" t="str">
-        <v>Pievieno...</v>
+        <v>Ieteiktās kontroles</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>No risks to add</v>
+        <v>No risks generated yet.</v>
       </c>
       <c r="B718" t="str">
-        <v>لا توجد مخاطر للإضافة</v>
+        <v>لم يتم إنشاء مخاطر بعد.</v>
       </c>
       <c r="C718" t="str">
-        <v>Nav risku, ko pievienot</v>
+        <v>Vēl nav ģenerēti riski.</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>Keep at least one risk before adding to the register.</v>
+        <v>AI Risks Generated</v>
       </c>
       <c r="B719" t="str">
-        <v>احتفظ بخطر واحد على الأقل قبل الإضافة إلى السجل.</v>
+        <v>تم إنشاء مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C719" t="str">
-        <v>Paturiet vismaz vienu risku pirms pievienošanas reģistram.</v>
+        <v>AI riski ģenerēti</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>Risks have been added to the Risk Register.</v>
+        <v>AI Generation Failed</v>
       </c>
       <c r="B720" t="str">
-        <v>تمت إضافة المخاطر إلى سجل المخاطر.</v>
+        <v>فشل إنشاء الذكاء الاصطناعي</v>
       </c>
       <c r="C720" t="str">
-        <v>Riski ir pievienoti risku reģistram.</v>
+        <v>AI ģenerēšana neizdevās</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>Adding to risk register timed out. Please try again.</v>
+        <v>Communication with AI service failed.</v>
       </c>
       <c r="B721" t="str">
-        <v>انتهت مهلة الإضافة إلى سجل المخاطر. يرجى المحاولة مرة أخرى.</v>
+        <v>فشل الاتصال بخدمة الذكاء الاصطناعي.</v>
       </c>
       <c r="C721" t="str">
-        <v>Pievienošanas reģistram laiks beidzās. Lūdzu, mēģiniet vēlreiz.</v>
+        <v>Saziņa ar AI servisu neizdevās.</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>Failed to add risks to register</v>
+        <v>Please try again later.</v>
       </c>
       <c r="B722" t="str">
-        <v>فشل في إضافة المخاطر إلى السجل</v>
+        <v>يرجى المحاولة مرة أخرى لاحقاً.</v>
       </c>
       <c r="C722" t="str">
-        <v>Neizdevās pievienot riskus reģistram</v>
+        <v>Lūdzu, mēģiniet vēlreiz vēlāk.</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>Failed to register risks</v>
+        <v>Go to Risk Register</v>
       </c>
       <c r="B723" t="str">
-        <v>فشل في تسجيل المخاطر</v>
+        <v>الذهاب إلى سجل المخاطر</v>
       </c>
       <c r="C723" t="str">
-        <v>Neizdevās reģistrēt riskus</v>
+        <v>Doties uz risku reģistru</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>No risks in semantic result to register</v>
+        <v>Add to Risk Register</v>
       </c>
       <c r="B724" t="str">
-        <v>لا توجد مخاطر في نتيجة البحث الدلالي للتسجيل</v>
+        <v>إضافة إلى سجل المخاطر</v>
       </c>
       <c r="C724" t="str">
-        <v>Nav risku semantiskajā rezultātā reģistrēšanai</v>
+        <v>Pievienot risku reģistram</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>Failed to add to risk register</v>
+        <v>Adding...</v>
       </c>
       <c r="B725" t="str">
-        <v>فشل في الإضافة إلى سجل المخاطر</v>
+        <v>جاري الإضافة...</v>
       </c>
       <c r="C725" t="str">
-        <v>Neizdevās pievienot risku reģistram</v>
+        <v>Pievieno...</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>Add to Audit Plan</v>
+        <v>No risks to add</v>
       </c>
       <c r="B726" t="str">
-        <v>إضافة إلى خطة التدقيق</v>
+        <v>لا توجد مخاطر للإضافة</v>
       </c>
       <c r="C726" t="str">
-        <v>Pievienot audita plānam</v>
+        <v>Nav risku, ko pievienot</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>Department information missing</v>
+        <v>Keep at least one risk before adding to the register.</v>
       </c>
       <c r="B727" t="str">
-        <v>معلومات القسم مفقودة</v>
+        <v>احتفظ بخطر واحد على الأقل قبل الإضافة إلى السجل.</v>
       </c>
       <c r="C727" t="str">
-        <v>Trūkst nodaļas informācijas</v>
+        <v>Paturiet vismaz vienu risku pirms pievienošanas reģistram.</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>Failed to add to audit plan</v>
+        <v>Risks have been added to the Risk Register.</v>
       </c>
       <c r="B728" t="str">
-        <v>فشل في الإضافة إلى خطة التدقيق</v>
+        <v>تمت إضافة المخاطر إلى سجل المخاطر.</v>
       </c>
       <c r="C728" t="str">
-        <v>Neizdevās pievienot audita plānam</v>
+        <v>Riski ir pievienoti risku reģistram.</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>Successfully added to Audit Planning!</v>
+        <v>Adding to risk register timed out. Please try again.</v>
       </c>
       <c r="B729" t="str">
-        <v>تمت الإضافة بنجاح إلى تخطيط التدقيق!</v>
+        <v>انتهت مهلة الإضافة إلى سجل المخاطر. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C729" t="str">
-        <v>Veiksmīgi pievienots audita plānošanai!</v>
+        <v>Pievienošanas reģistram laiks beidzās. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>Already Added</v>
+        <v>Failed to add risks to register</v>
       </c>
       <c r="B730" t="str">
-        <v>تمت الإضافة بالفعل</v>
+        <v>فشل في إضافة المخاطر إلى السجل</v>
       </c>
       <c r="C730" t="str">
-        <v>Jau pievienots</v>
+        <v>Neizdevās pievienot riskus reģistram</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>This audit plan has already been added to Audit Planning.</v>
+        <v>Failed to register risks</v>
       </c>
       <c r="B731" t="str">
-        <v>تمت إضافة خطة التدقيق هذه بالفعل إلى تخطيط التدقيق.</v>
+        <v>فشل في تسجيل المخاطر</v>
       </c>
       <c r="C731" t="str">
-        <v>Šis audita plāns jau ir pievienots audita plānošanai.</v>
+        <v>Neizdevās reģistrēt riskus</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>Failed to check status</v>
+        <v>No risks in semantic result to register</v>
       </c>
       <c r="B732" t="str">
-        <v>فشل في التحقق من الحالة</v>
+        <v>لا توجد مخاطر في نتيجة البحث الدلالي للتسجيل</v>
       </c>
       <c r="C732" t="str">
-        <v>Neizdevās pārbaudīt statusu</v>
+        <v>Nav risku semantiskajā rezultātā reģistrēšanai</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>Remove risk</v>
+        <v>Failed to add to risk register</v>
       </c>
       <c r="B733" t="str">
-        <v>إزالة الخطر</v>
+        <v>فشل في الإضافة إلى سجل المخاطر</v>
       </c>
       <c r="C733" t="str">
-        <v>Noņemt risku</v>
+        <v>Neizdevās pievienot risku reģistram</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>Remove risks you do not need; only the remaining risks will be sent to the next step.</v>
+        <v>Add to Audit Plan</v>
       </c>
       <c r="B734" t="str">
-        <v>أزل المخاطر التي لا تحتاجها؛ فقط المخاطر المتبقية سيتم إرسالها إلى الخطوة التالية.</v>
+        <v>إضافة إلى خطة التدقيق</v>
       </c>
       <c r="C734" t="str">
-        <v>Noņemiet riskus, kas nav nepieciešami; tikai atlikušie riski tiks nosūtīti nākamajā solī.</v>
+        <v>Pievienot audita plānam</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>Perform BIA</v>
+        <v>Department information missing</v>
       </c>
       <c r="B735" t="str">
-        <v>إجراء تحليل تأثير الأعمال</v>
+        <v>معلومات القسم مفقودة</v>
       </c>
       <c r="C735" t="str">
-        <v>Veikt BIA</v>
+        <v>Trūkst nodaļas informācijas</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>Submit For Approval</v>
+        <v>Failed to add to audit plan</v>
       </c>
       <c r="B736" t="str">
-        <v>إرسال للموافقة</v>
+        <v>فشل في الإضافة إلى خطة التدقيق</v>
       </c>
       <c r="C736" t="str">
-        <v>Iesniegt apstiprināšanai</v>
+        <v>Neizdevās pievienot audita plānam</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>Status &amp; Approval</v>
+        <v>Successfully added to Audit Planning!</v>
       </c>
       <c r="B737" t="str">
-        <v>الحالة والموافقة</v>
+        <v>تمت الإضافة بنجاح إلى تخطيط التدقيق!</v>
       </c>
       <c r="C737" t="str">
-        <v>Statuss un apstiprinājums</v>
+        <v>Veiksmīgi pievienots audita plānošanai!</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>Impact Assessment</v>
+        <v>Already Added</v>
       </c>
       <c r="B738" t="str">
-        <v>تقييم التأثير</v>
+        <v>تمت الإضافة بالفعل</v>
       </c>
       <c r="C738" t="str">
-        <v>Ietekmes novērtējums</v>
+        <v>Jau pievienots</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>Recovery Metrics</v>
+        <v>This audit plan has already been added to Audit Planning.</v>
       </c>
       <c r="B739" t="str">
-        <v>مقاييس الاستعادة</v>
+        <v>تمت إضافة خطة التدقيق هذه بالفعل إلى تخطيط التدقيق.</v>
       </c>
       <c r="C739" t="str">
-        <v>Atjaunošanas metrikas</v>
+        <v>Šis audita plāns jau ir pievienots audita plānošanai.</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>BIA Rating</v>
+        <v>Suggest Risks with AI</v>
       </c>
       <c r="B740" t="str">
-        <v>تصنيف تحليل تأثير الأعمال</v>
+        <v>اقتراح المخاطر بالذكاء الاصطناعي</v>
       </c>
       <c r="C740" t="str">
-        <v>BIA vērtējums</v>
+        <v>Ieteikt riskus ar AI</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>Impact Rating</v>
+        <v>Add to Register</v>
       </c>
       <c r="B741" t="str">
-        <v>تصنيف التأثير</v>
+        <v>إضافة إلى السجل</v>
       </c>
       <c r="C741" t="str">
-        <v>Ietekmes vērtējums</v>
+        <v>Pievienot reģistram</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>Note: The highest rating will be taken</v>
+        <v>Please select a department first</v>
       </c>
       <c r="B742" t="str">
-        <v>ملاحظة: سيتم أخذ أعلى تصنيف</v>
+        <v>يرجى تحديد قسم أولاً</v>
       </c>
       <c r="C742" t="str">
-        <v>Piezīme: Tiks ņemts augstākais vērtējums</v>
+        <v>Lūdzu, vispirms izvēlieties nodaļu</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>RTO (Recovery Time Objective) - Hours</v>
+        <v>Only Audit Head can suggest risks with AI</v>
       </c>
       <c r="B743" t="str">
-        <v>هدف وقت الاستعادة - ساعات</v>
+        <v>فقط رئيس التدقيق يمكنه اقتراح المخاطر بالذكاء الاصطناعي</v>
       </c>
       <c r="C743" t="str">
-        <v>RTO (Atjaunošanas laika mērķis) - Stundas</v>
+        <v>Tikai audita vadītājs var ieteikt riskus ar AI</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>RPO (Recovery Point Objective) - Hours</v>
+        <v>Only Audit Head can add risks to register</v>
       </c>
       <c r="B744" t="str">
-        <v>هدف نقطة الاستعادة - ساعات</v>
+        <v>فقط رئيس التدقيق يمكنه إضافة المخاطر إلى السجل</v>
       </c>
       <c r="C744" t="str">
-        <v>RPO (Atjaunošanas punkta mērķis) - Stundas</v>
+        <v>Tikai audita vadītājs var pievienot riskus reģistram</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>N/A</v>
+        <v>Failed to check status</v>
       </c>
       <c r="B745" t="str">
-        <v>غير متاح</v>
+        <v>فشل في التحقق من الحالة</v>
       </c>
       <c r="C745" t="str">
-        <v>Nav piemērojams</v>
+        <v>Neizdevās pārbaudīt statusu</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>KPI Details</v>
+        <v>Remove risk</v>
       </c>
       <c r="B746" t="str">
-        <v>تفاصيل مؤشرات الأداء</v>
+        <v>إزالة الخطر</v>
       </c>
       <c r="C746" t="str">
-        <v>KPI detaļas</v>
+        <v>Noņemt risku</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>Performance Chart</v>
+        <v>Remove risks you do not need; only the remaining risks will be sent to the next step.</v>
       </c>
       <c r="B747" t="str">
-        <v>مخطط الأداء</v>
+        <v>أزل المخاطر التي لا تحتاجها؛ فقط المخاطر المتبقية سيتم إرسالها إلى الخطوة التالية.</v>
       </c>
       <c r="C747" t="str">
-        <v>Veiktspējas diagramma</v>
+        <v>Noņemiet riskus, kas nav nepieciešami; tikai atlikušie riski tiks nosūtīti nākamajā solī.</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>KPI Configuration</v>
+        <v>Perform BIA</v>
       </c>
       <c r="B748" t="str">
-        <v>إعدادات مؤشرات الأداء</v>
+        <v>إجراء تحليل تأثير الأعمال</v>
       </c>
       <c r="C748" t="str">
-        <v>KPI konfigurācija</v>
+        <v>Veikt BIA</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>KPI Records</v>
+        <v>Submit For Approval</v>
       </c>
       <c r="B749" t="str">
-        <v>سجلات مؤشرات الأداء</v>
+        <v>إرسال للموافقة</v>
       </c>
       <c r="C749" t="str">
-        <v>KPI ieraksti</v>
+        <v>Iesniegt apstiprināšanai</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>Year</v>
+        <v>Status &amp; Approval</v>
       </c>
       <c r="B750" t="str">
-        <v>السنة</v>
+        <v>الحالة والموافقة</v>
       </c>
       <c r="C750" t="str">
-        <v>Gads</v>
+        <v>Statuss un apstiprinājums</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>Achieved Value</v>
+        <v>Impact Assessment</v>
       </c>
       <c r="B751" t="str">
-        <v>القيمة المحققة</v>
+        <v>تقييم التأثير</v>
       </c>
       <c r="C751" t="str">
-        <v>Sasniegtā vērtība</v>
+        <v>Ietekmes novērtējums</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>Expected Value</v>
+        <v>Recovery Metrics</v>
       </c>
       <c r="B752" t="str">
-        <v>القيمة المتوقعة</v>
+        <v>مقاييس الاستعادة</v>
       </c>
       <c r="C752" t="str">
-        <v>Gaidāmā vērtība</v>
+        <v>Atjaunošanas metrikas</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>KPI Objective</v>
+        <v>BIA Rating</v>
       </c>
       <c r="B753" t="str">
-        <v>هدف مؤشر الأداء</v>
+        <v>تصنيف تحليل تأثير الأعمال</v>
       </c>
       <c r="C753" t="str">
-        <v>KPI mērķis</v>
+        <v>BIA vērtējums</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>Enter Objective</v>
+        <v>Impact Rating</v>
       </c>
       <c r="B754" t="str">
-        <v>أدخل الهدف</v>
+        <v>تصنيف التأثير</v>
       </c>
       <c r="C754" t="str">
-        <v>Ievadiet mērķi</v>
+        <v>Ietekmes vērtējums</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>KPI Description</v>
+        <v>Note: The highest rating will be taken</v>
       </c>
       <c r="B755" t="str">
-        <v>وصف مؤشر الأداء</v>
+        <v>ملاحظة: سيتم أخذ أعلى تصنيف</v>
       </c>
       <c r="C755" t="str">
-        <v>KPI apraksts</v>
+        <v>Piezīme: Tiks ņemts augstākais vērtējums</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>Enter Description</v>
+        <v>RTO (Recovery Time Objective) - Hours</v>
       </c>
       <c r="B756" t="str">
-        <v>أدخل الوصف</v>
+        <v>هدف وقت الاستعادة - ساعات</v>
       </c>
       <c r="C756" t="str">
-        <v>Ievadiet aprakstu</v>
+        <v>RTO (Atjaunošanas laika mērķis) - Stundas</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>KPI Data Source</v>
+        <v>RPO (Recovery Point Objective) - Hours</v>
       </c>
       <c r="B757" t="str">
-        <v>مصدر بيانات مؤشر الأداء</v>
+        <v>هدف نقطة الاستعادة - ساعات</v>
       </c>
       <c r="C757" t="str">
-        <v>KPI datu avots</v>
+        <v>RPO (Atjaunošanas punkta mērķis) - Stundas</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>Enter Data Source</v>
+        <v>N/A</v>
       </c>
       <c r="B758" t="str">
-        <v>أدخل مصدر البيانات</v>
+        <v>غير متاح</v>
       </c>
       <c r="C758" t="str">
-        <v>Ievadiet datu avotu</v>
+        <v>Nav piemērojams</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>KPI Measurement Formula</v>
+        <v>KPI Details</v>
       </c>
       <c r="B759" t="str">
-        <v>صيغة قياس مؤشر الأداء</v>
+        <v>تفاصيل مؤشرات الأداء</v>
       </c>
       <c r="C759" t="str">
-        <v>KPI mērīšanas formula</v>
+        <v>KPI detaļas</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>Enter the KPI Calculation Formula</v>
+        <v>Performance Chart</v>
       </c>
       <c r="B760" t="str">
-        <v>أدخل صيغة حساب مؤشر الأداء</v>
+        <v>مخطط الأداء</v>
       </c>
       <c r="C760" t="str">
-        <v>Ievadiet KPI aprēķina formulu</v>
+        <v>Veiktspējas diagramma</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>Targeted Achieved Value</v>
+        <v>KPI Configuration</v>
       </c>
       <c r="B761" t="str">
-        <v>القيمة المستهدفة المحققة</v>
+        <v>إعدادات مؤشرات الأداء</v>
       </c>
       <c r="C761" t="str">
-        <v>Mērķa sasniegtā vērtība</v>
+        <v>KPI konfigurācija</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>No KPI records yet</v>
+        <v>KPI Records</v>
       </c>
       <c r="B762" t="str">
-        <v>لا توجد سجلات مؤشرات أداء بعد</v>
+        <v>سجلات مؤشرات الأداء</v>
       </c>
       <c r="C762" t="str">
-        <v>Vēl nav KPI ierakstu</v>
+        <v>KPI ieraksti</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>No KPI Data</v>
+        <v>Year</v>
       </c>
       <c r="B763" t="str">
-        <v>لا توجد بيانات مؤشرات أداء</v>
+        <v>السنة</v>
       </c>
       <c r="C763" t="str">
-        <v>Nav KPI datu</v>
+        <v>Gads</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>No processes have KPI measurement enabled...</v>
+        <v>Achieved Value</v>
       </c>
       <c r="B764" t="str">
-        <v>لم يتم تمكين قياس مؤشرات الأداء لأي عملية...</v>
+        <v>القيمة المحققة</v>
       </c>
       <c r="C764" t="str">
-        <v>Nevienam procesam nav iespējots KPI mērījums...</v>
+        <v>Sasniegtā vērtība</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>Unassigned</v>
+        <v>Expected Value</v>
       </c>
       <c r="B765" t="str">
-        <v>غير معين</v>
+        <v>القيمة المتوقعة</v>
       </c>
       <c r="C765" t="str">
-        <v>Nepiešķirts</v>
+        <v>Gaidāmā vērtība</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>Primary</v>
+        <v>KPI Objective</v>
       </c>
       <c r="B766" t="str">
-        <v>أساسي</v>
+        <v>هدف مؤشر الأداء</v>
       </c>
       <c r="C766" t="str">
-        <v>Primārais</v>
+        <v>KPI mērķis</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>Supporting</v>
+        <v>Enter Objective</v>
       </c>
       <c r="B767" t="str">
-        <v>داعم</v>
+        <v>أدخل الهدف</v>
       </c>
       <c r="C767" t="str">
-        <v>Atbalsta</v>
+        <v>Ievadiet mērķi</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>Manual</v>
+        <v>KPI Description</v>
       </c>
       <c r="B768" t="str">
-        <v>يدوي</v>
+        <v>وصف مؤشر الأداء</v>
       </c>
       <c r="C768" t="str">
-        <v>Manuāls</v>
+        <v>KPI apraksts</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>Automated</v>
+        <v>Enter Description</v>
       </c>
       <c r="B769" t="str">
-        <v>آلي</v>
+        <v>أدخل الوصف</v>
       </c>
       <c r="C769" t="str">
-        <v>Automatizēts</v>
+        <v>Ievadiet aprakstu</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>Manual + Automated</v>
+        <v>KPI Data Source</v>
       </c>
       <c r="B770" t="str">
-        <v>يدوي + آلي</v>
+        <v>مصدر بيانات مؤشر الأداء</v>
       </c>
       <c r="C770" t="str">
-        <v>Manuāls + Automatizēts</v>
+        <v>KPI datu avots</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>Branch Office</v>
+        <v>Enter Data Source</v>
       </c>
       <c r="B771" t="str">
-        <v>فرع المكتب</v>
+        <v>أدخل مصدر البيانات</v>
       </c>
       <c r="C771" t="str">
-        <v>Filiāles birojs</v>
+        <v>Ievadiet datu avotu</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>Remote</v>
+        <v>KPI Measurement Formula</v>
       </c>
       <c r="B772" t="str">
-        <v>عن بعد</v>
+        <v>صيغة قياس مؤشر الأداء</v>
       </c>
       <c r="C772" t="str">
-        <v>Attālināti</v>
+        <v>KPI mērīšanas formula</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>Select frequency</v>
+        <v>Enter the KPI Calculation Formula</v>
       </c>
       <c r="B773" t="str">
-        <v>اختر التكرار</v>
+        <v>أدخل صيغة حساب مؤشر الأداء</v>
       </c>
       <c r="C773" t="str">
-        <v>Izvēlieties biežumu</v>
+        <v>Ievadiet KPI aprēķina formulu</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>Bi-annually</v>
+        <v>Targeted Achieved Value</v>
       </c>
       <c r="B774" t="str">
-        <v>نصف سنوي</v>
+        <v>القيمة المستهدفة المحققة</v>
       </c>
       <c r="C774" t="str">
-        <v>Divreiz gadā</v>
+        <v>Mērķa sasniegtā vērtība</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
+        <v>No KPI records yet</v>
+      </c>
+      <c r="B775" t="str">
+        <v>لا توجد سجلات مؤشرات أداء بعد</v>
+      </c>
+      <c r="C775" t="str">
+        <v>Vēl nav KPI ierakstu</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="str">
+        <v>No KPI Data</v>
+      </c>
+      <c r="B776" t="str">
+        <v>لا توجد بيانات مؤشرات أداء</v>
+      </c>
+      <c r="C776" t="str">
+        <v>Nav KPI datu</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="str">
+        <v>No processes have KPI measurement enabled...</v>
+      </c>
+      <c r="B777" t="str">
+        <v>لم يتم تمكين قياس مؤشرات الأداء لأي عملية...</v>
+      </c>
+      <c r="C777" t="str">
+        <v>Nevienam procesam nav iespējots KPI mērījums...</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="B778" t="str">
+        <v>غير معين</v>
+      </c>
+      <c r="C778" t="str">
+        <v>Nepiešķirts</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B779" t="str">
+        <v>أساسي</v>
+      </c>
+      <c r="C779" t="str">
+        <v>Primārais</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="str">
+        <v>Supporting</v>
+      </c>
+      <c r="B780" t="str">
+        <v>داعم</v>
+      </c>
+      <c r="C780" t="str">
+        <v>Atbalsta</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="B781" t="str">
+        <v>يدوي</v>
+      </c>
+      <c r="C781" t="str">
+        <v>Manuāls</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="B782" t="str">
+        <v>آلي</v>
+      </c>
+      <c r="C782" t="str">
+        <v>Automatizēts</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="str">
+        <v>Manual + Automated</v>
+      </c>
+      <c r="B783" t="str">
+        <v>يدوي + آلي</v>
+      </c>
+      <c r="C783" t="str">
+        <v>Manuāls + Automatizēts</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="str">
+        <v>Branch Office</v>
+      </c>
+      <c r="B784" t="str">
+        <v>فرع المكتب</v>
+      </c>
+      <c r="C784" t="str">
+        <v>Filiāles birojs</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="B785" t="str">
+        <v>عن بعد</v>
+      </c>
+      <c r="C785" t="str">
+        <v>Attālināti</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="str">
+        <v>Select frequency</v>
+      </c>
+      <c r="B786" t="str">
+        <v>اختر التكرار</v>
+      </c>
+      <c r="C786" t="str">
+        <v>Izvēlieties biežumu</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="str">
+        <v>Bi-annually</v>
+      </c>
+      <c r="B787" t="str">
+        <v>نصف سنوي</v>
+      </c>
+      <c r="C787" t="str">
+        <v>Divreiz gadā</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="str">
         <v>As needed</v>
       </c>
-      <c r="B775" t="str">
+      <c r="B788" t="str">
         <v>حسب الحاجة</v>
       </c>
-      <c r="C775" t="str">
+      <c r="C788" t="str">
         <v>Pēc vajadzības</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="str">
+        <v>Imported</v>
+      </c>
+      <c r="B789" t="str">
+        <v>تم استيراد</v>
+      </c>
+      <c r="C789" t="str">
+        <v>Importēts</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="str">
+        <v>categories</v>
+      </c>
+      <c r="B790" t="str">
+        <v>فئات</v>
+      </c>
+      <c r="C790" t="str">
+        <v>kategorijas</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="str">
+        <v>sub-categories</v>
+      </c>
+      <c r="B791" t="str">
+        <v>فئات فرعية</v>
+      </c>
+      <c r="C791" t="str">
+        <v>apakškategorijas</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="str">
+        <v>groups</v>
+      </c>
+      <c r="B792" t="str">
+        <v>مجموعات</v>
+      </c>
+      <c r="C792" t="str">
+        <v>grupas</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="str">
+        <v>sensitivities</v>
+      </c>
+      <c r="B793" t="str">
+        <v>حساسيات</v>
+      </c>
+      <c r="C793" t="str">
+        <v>jutīgumi</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="str">
+        <v>assets</v>
+      </c>
+      <c r="B794" t="str">
+        <v>أصول</v>
+      </c>
+      <c r="C794" t="str">
+        <v>aktīvi</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="str">
+        <v>lifecycle statuses</v>
+      </c>
+      <c r="B795" t="str">
+        <v>حالات دورة الحياة</v>
+      </c>
+      <c r="C795" t="str">
+        <v>dzīves cikla statusi</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="str">
+        <v>failed</v>
+      </c>
+      <c r="B796" t="str">
+        <v>فشل</v>
+      </c>
+      <c r="C796" t="str">
+        <v>neizdevās</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="str">
+        <v>category not found</v>
+      </c>
+      <c r="B797" t="str">
+        <v>الفئة غير موجودة</v>
+      </c>
+      <c r="C797" t="str">
+        <v>kategorija nav atrasta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C775"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C797"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C799"/>
+  <dimension ref="A1:C849"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -2595,6607 +2595,7157 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Delete Department</v>
+        <v>Delete User</v>
       </c>
       <c r="B200" t="str">
-        <v>حذف القسم</v>
+        <v>حذف المستخدم</v>
       </c>
       <c r="C200" t="str">
-        <v>Dzēst nodaļu</v>
+        <v>Dzēst lietotāju</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Are you sure you want to delete this department?</v>
+        <v>Are you sure you want to delete</v>
       </c>
       <c r="B201" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذا القسم؟</v>
+        <v>هل أنت متأكد أنك تريد حذف</v>
       </c>
       <c r="C201" t="str">
-        <v>Vai tiešām vēlaties dzēst šo nodaļu?</v>
+        <v>Vai tiešām vēlaties dzēst</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Edit Service</v>
+        <v>Delete Department</v>
       </c>
       <c r="B202" t="str">
-        <v>تعديل الخدمة</v>
+        <v>حذف القسم</v>
       </c>
       <c r="C202" t="str">
-        <v>Rediģēt pakalpojumu</v>
+        <v>Dzēst nodaļu</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Delete Service</v>
+        <v>Are you sure you want to delete this department?</v>
       </c>
       <c r="B203" t="str">
-        <v>حذف الخدمة</v>
+        <v>هل أنت متأكد أنك تريد حذف هذا القسم؟</v>
       </c>
       <c r="C203" t="str">
-        <v>Dzēst pakalpojumu</v>
+        <v>Vai tiešām vēlaties dzēst šo nodaļu?</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Are you sure you want to delete this service?</v>
+        <v>Edit Service</v>
       </c>
       <c r="B204" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه الخدمة؟</v>
+        <v>تعديل الخدمة</v>
       </c>
       <c r="C204" t="str">
-        <v>Vai tiešām vēlaties dzēst šo pakalpojumu?</v>
+        <v>Rediģēt pakalpojumu</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Edit Regulation</v>
+        <v>Delete Service</v>
       </c>
       <c r="B205" t="str">
-        <v>تعديل اللائحة</v>
+        <v>حذف الخدمة</v>
       </c>
       <c r="C205" t="str">
-        <v>Rediģēt noteikumus</v>
+        <v>Dzēst pakalpojumu</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Unsubscribe from Regulation</v>
+        <v>Are you sure you want to delete this service?</v>
       </c>
       <c r="B206" t="str">
-        <v>إلغاء الاشتراك من اللائحة</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه الخدمة؟</v>
       </c>
       <c r="C206" t="str">
-        <v>Atteikties no noteikumiem</v>
+        <v>Vai tiešām vēlaties dzēst šo pakalpojumu?</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Are you sure you want to unsubscribe from this regulation?</v>
+        <v>Edit Regulation</v>
       </c>
       <c r="B207" t="str">
-        <v>هل أنت متأكد أنك تريد إلغاء الاشتراك من هذه اللائحة؟</v>
+        <v>تعديل اللائحة</v>
       </c>
       <c r="C207" t="str">
-        <v>Vai tiešām vēlaties atteikties no šiem noteikumiem?</v>
+        <v>Rediģēt noteikumus</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Unsubscribe</v>
+        <v>Unsubscribe from Regulation</v>
       </c>
       <c r="B208" t="str">
-        <v>إلغاء الاشتراك</v>
+        <v>إلغاء الاشتراك من اللائحة</v>
       </c>
       <c r="C208" t="str">
-        <v>Atteikties</v>
+        <v>Atteikties no noteikumiem</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Add Service Category</v>
+        <v>Are you sure you want to unsubscribe from this regulation?</v>
       </c>
       <c r="B209" t="str">
-        <v>إضافة فئة خدمة</v>
+        <v>هل أنت متأكد أنك تريد إلغاء الاشتراك من هذه اللائحة؟</v>
       </c>
       <c r="C209" t="str">
-        <v>Pievienot pakalpojuma kategoriju</v>
+        <v>Vai tiešām vēlaties atteikties no šiem noteikumiem?</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Category Name</v>
+        <v>Unsubscribe</v>
       </c>
       <c r="B210" t="str">
-        <v>اسم الفئة</v>
+        <v>إلغاء الاشتراك</v>
       </c>
       <c r="C210" t="str">
-        <v>Kategorijas nosaukums</v>
+        <v>Atteikties</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Add Service Item</v>
+        <v>Add Service Category</v>
       </c>
       <c r="B211" t="str">
-        <v>إضافة عنصر خدمة</v>
+        <v>إضافة فئة خدمة</v>
       </c>
       <c r="C211" t="str">
-        <v>Pievienot pakalpojuma vienumu</v>
+        <v>Pievienot pakalpojuma kategoriju</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Item Name</v>
+        <v>Category Name</v>
       </c>
       <c r="B212" t="str">
-        <v>اسم العنصر</v>
+        <v>اسم الفئة</v>
       </c>
       <c r="C212" t="str">
-        <v>Vienuma nosaukums</v>
+        <v>Kategorijas nosaukums</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>User Type</v>
+        <v>Add Service Item</v>
       </c>
       <c r="B213" t="str">
-        <v>نوع المستخدم</v>
+        <v>إضافة عنصر خدمة</v>
       </c>
       <c r="C213" t="str">
-        <v>Lietotāja tips</v>
+        <v>Pievienot pakalpojuma vienumu</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Category</v>
+        <v>Item Name</v>
       </c>
       <c r="B214" t="str">
-        <v>الفئة</v>
+        <v>اسم العنصر</v>
       </c>
       <c r="C214" t="str">
-        <v>Kategorija</v>
+        <v>Vienuma nosaukums</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Item</v>
+        <v>User Type</v>
       </c>
       <c r="B215" t="str">
-        <v>العنصر</v>
+        <v>نوع المستخدم</v>
       </c>
       <c r="C215" t="str">
-        <v>Vienums</v>
+        <v>Lietotāja tips</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Internal</v>
+        <v>Category</v>
       </c>
       <c r="B216" t="str">
-        <v>داخلي</v>
+        <v>الفئة</v>
       </c>
       <c r="C216" t="str">
-        <v>Iekšējs</v>
+        <v>Kategorija</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>External</v>
+        <v>Item</v>
       </c>
       <c r="B217" t="str">
-        <v>خارجي</v>
+        <v>العنصر</v>
       </c>
       <c r="C217" t="str">
-        <v>Ārējs</v>
+        <v>Vienums</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Public</v>
+        <v>Internal</v>
       </c>
       <c r="B218" t="str">
-        <v>عام</v>
+        <v>داخلي</v>
       </c>
       <c r="C218" t="str">
-        <v>Publisks</v>
+        <v>Iekšējs</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>SA1 Date</v>
+        <v>External</v>
       </c>
       <c r="B219" t="str">
-        <v>تاريخ SA1</v>
+        <v>خارجي</v>
       </c>
       <c r="C219" t="str">
-        <v>SA1 datums</v>
+        <v>Ārējs</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>SA2 Date</v>
+        <v>Public</v>
       </c>
       <c r="B220" t="str">
-        <v>تاريخ SA2</v>
+        <v>عام</v>
       </c>
       <c r="C220" t="str">
-        <v>SA2 datums</v>
+        <v>Publisks</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Exclusion and Justification</v>
+        <v>SA1 Date</v>
       </c>
       <c r="B221" t="str">
-        <v>الاستثناء والتبرير</v>
+        <v>تاريخ SA1</v>
       </c>
       <c r="C221" t="str">
-        <v>Izslēgšana un pamatojums</v>
+        <v>SA1 datums</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Document</v>
+        <v>SA2 Date</v>
       </c>
       <c r="B222" t="str">
-        <v>المستند</v>
+        <v>تاريخ SA2</v>
       </c>
       <c r="C222" t="str">
-        <v>Dokuments</v>
+        <v>SA2 datums</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Certificate</v>
+        <v>Exclusion and Justification</v>
       </c>
       <c r="B223" t="str">
-        <v>الشهادة</v>
+        <v>الاستثناء والتبرير</v>
       </c>
       <c r="C223" t="str">
-        <v>Sertifikāts</v>
+        <v>Izslēgšana un pamatojums</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Click to upload document</v>
+        <v>Document</v>
       </c>
       <c r="B224" t="str">
-        <v>انقر لتحميل المستند</v>
+        <v>المستند</v>
       </c>
       <c r="C224" t="str">
-        <v>Noklikšķiniet, lai augšupielādētu dokumentu</v>
+        <v>Dokuments</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Click to upload certificate</v>
+        <v>Certificate</v>
       </c>
       <c r="B225" t="str">
-        <v>انقر لتحميل الشهادة</v>
+        <v>الشهادة</v>
       </c>
       <c r="C225" t="str">
-        <v>Noklikšķiniet, lai augšupielādētu sertifikātu</v>
+        <v>Sertifikāts</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Replace</v>
+        <v>Click to upload document</v>
       </c>
       <c r="B226" t="str">
-        <v>استبدال</v>
+        <v>انقر لتحميل المستند</v>
       </c>
       <c r="C226" t="str">
-        <v>Aizstāt</v>
+        <v>Noklikšķiniet, lai augšupielādētu dokumentu</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Compliance Status</v>
+        <v>Click to upload certificate</v>
       </c>
       <c r="B227" t="str">
-        <v>حالة الامتثال</v>
+        <v>انقر لتحميل الشهادة</v>
       </c>
       <c r="C227" t="str">
-        <v>Atbilstības statuss</v>
+        <v>Noklikšķiniet, lai augšupielādētu sertifikātu</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Subscribed</v>
+        <v>Replace</v>
       </c>
       <c r="B228" t="str">
-        <v>مشترك</v>
+        <v>استبدال</v>
       </c>
       <c r="C228" t="str">
-        <v>Abonēts</v>
+        <v>Aizstāt</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Loading profile...</v>
+        <v>Compliance Status</v>
       </c>
       <c r="B229" t="str">
-        <v>جاري تحميل الملف...</v>
+        <v>حالة الامتثال</v>
       </c>
       <c r="C229" t="str">
-        <v>Ielādē profilu...</v>
+        <v>Atbilstības statuss</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Company Info</v>
+        <v>Subscribed</v>
       </c>
       <c r="B230" t="str">
-        <v>معلومات الشركة</v>
+        <v>مشترك</v>
       </c>
       <c r="C230" t="str">
-        <v>Uzņēmuma info</v>
+        <v>Abonēts</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Organization Chart</v>
+        <v>Loading profile...</v>
       </c>
       <c r="B231" t="str">
-        <v>الهيكل التنظيمي</v>
+        <v>جاري تحميل الملف...</v>
       </c>
       <c r="C231" t="str">
-        <v>Organizācijas shēma</v>
+        <v>Ielādē profilu...</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>No Profile</v>
+        <v>Company Info</v>
       </c>
       <c r="B232" t="str">
-        <v>لا يوجد ملف تعريفي</v>
+        <v>معلومات الشركة</v>
       </c>
       <c r="C232" t="str">
-        <v>Nav profila</v>
+        <v>Uzņēmuma info</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Enter department name</v>
+        <v>Organization Chart</v>
       </c>
       <c r="B233" t="str">
-        <v>أدخل اسم القسم</v>
+        <v>الهيكل التنظيمي</v>
       </c>
       <c r="C233" t="str">
-        <v>Ievadiet nodaļas nosaukumu</v>
+        <v>Organizācijas shēma</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Enter service title</v>
+        <v>No Profile</v>
       </c>
       <c r="B234" t="str">
-        <v>أدخل عنوان الخدمة</v>
+        <v>لا يوجد ملف تعريفي</v>
       </c>
       <c r="C234" t="str">
-        <v>Ievadiet pakalpojuma nosaukumu</v>
+        <v>Nav profila</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Enter service description</v>
+        <v>Enter department name</v>
       </c>
       <c r="B235" t="str">
-        <v>أدخل وصف الخدمة</v>
+        <v>أدخل اسم القسم</v>
       </c>
       <c r="C235" t="str">
-        <v>Ievadiet pakalpojuma aprakstu</v>
+        <v>Ievadiet nodaļas nosaukumu</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Select category</v>
+        <v>Enter service title</v>
       </c>
       <c r="B236" t="str">
-        <v>اختر الفئة</v>
+        <v>أدخل عنوان الخدمة</v>
       </c>
       <c r="C236" t="str">
-        <v>Izvēlieties kategoriju</v>
+        <v>Ievadiet pakalpojuma nosaukumu</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Select item</v>
+        <v>Enter service description</v>
       </c>
       <c r="B237" t="str">
-        <v>اختر العنصر</v>
+        <v>أدخل وصف الخدمة</v>
       </c>
       <c r="C237" t="str">
-        <v>Izvēlieties vienumu</v>
+        <v>Ievadiet pakalpojuma aprakstu</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Enter category name</v>
+        <v>Select category</v>
       </c>
       <c r="B238" t="str">
-        <v>أدخل اسم الفئة</v>
+        <v>اختر الفئة</v>
       </c>
       <c r="C238" t="str">
-        <v>Ievadiet kategorijas nosaukumu</v>
+        <v>Izvēlieties kategoriju</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Enter item name</v>
+        <v>Select item</v>
       </c>
       <c r="B239" t="str">
-        <v>أدخل اسم العنصر</v>
+        <v>اختر العنصر</v>
       </c>
       <c r="C239" t="str">
-        <v>Ievadiet vienuma nosaukumu</v>
+        <v>Izvēlieties vienumu</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Enter regulation name</v>
+        <v>Enter category name</v>
       </c>
       <c r="B240" t="str">
-        <v>أدخل اسم اللائحة</v>
+        <v>أدخل اسم الفئة</v>
       </c>
       <c r="C240" t="str">
-        <v>Ievadiet noteikumu nosaukumu</v>
+        <v>Ievadiet kategorijas nosaukumu</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Enter version</v>
+        <v>Enter item name</v>
       </c>
       <c r="B241" t="str">
-        <v>أدخل الإصدار</v>
+        <v>أدخل اسم العنصر</v>
       </c>
       <c r="C241" t="str">
-        <v>Ievadiet versiju</v>
+        <v>Ievadiet vienuma nosaukumu</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Select SA1 date</v>
+        <v>Enter regulation name</v>
       </c>
       <c r="B242" t="str">
-        <v>اختر تاريخ SA1</v>
+        <v>أدخل اسم اللائحة</v>
       </c>
       <c r="C242" t="str">
-        <v>Izvēlieties SA1 datumu</v>
+        <v>Ievadiet noteikumu nosaukumu</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Select SA2 date</v>
+        <v>Enter version</v>
       </c>
       <c r="B243" t="str">
-        <v>اختر تاريخ SA2</v>
+        <v>أدخل الإصدار</v>
       </c>
       <c r="C243" t="str">
-        <v>Izvēlieties SA2 datumu</v>
+        <v>Ievadiet versiju</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Enter scope</v>
+        <v>Select SA1 date</v>
       </c>
       <c r="B244" t="str">
-        <v>أدخل النطاق</v>
+        <v>اختر تاريخ SA1</v>
       </c>
       <c r="C244" t="str">
-        <v>Ievadiet tvērumu</v>
+        <v>Izvēlieties SA1 datumu</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Enter exclusion and justification</v>
+        <v>Select SA2 date</v>
       </c>
       <c r="B245" t="str">
-        <v>أدخل الاستثناء والتبرير</v>
+        <v>اختر تاريخ SA2</v>
       </c>
       <c r="C245" t="str">
-        <v>Ievadiet izslēgšanu un pamatojumu</v>
+        <v>Izvēlieties SA2 datumu</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Search departments...</v>
+        <v>Enter scope</v>
       </c>
       <c r="B246" t="str">
-        <v>البحث في الأقسام...</v>
+        <v>أدخل النطاق</v>
       </c>
       <c r="C246" t="str">
-        <v>Meklēt nodaļas...</v>
+        <v>Ievadiet tvērumu</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Search regulations...</v>
+        <v>Enter exclusion and justification</v>
       </c>
       <c r="B247" t="str">
-        <v>البحث في اللوائح...</v>
+        <v>أدخل الاستثناء والتبرير</v>
       </c>
       <c r="C247" t="str">
-        <v>Meklēt noteikumus...</v>
+        <v>Ievadiet izslēgšanu un pamatojumu</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Are you sure you want to delete this department? This action cannot be undone.</v>
+        <v>Search departments...</v>
       </c>
       <c r="B248" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذا القسم؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>البحث في الأقسام...</v>
       </c>
       <c r="C248" t="str">
-        <v>Vai tiešām vēlaties dzēst šo nodaļu? Šo darbību nevar atsaukt.</v>
+        <v>Meklēt nodaļas...</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Are you sure you want to delete this service? This action cannot be undone.</v>
+        <v>Search regulations...</v>
       </c>
       <c r="B249" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه الخدمة؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>البحث في اللوائح...</v>
       </c>
       <c r="C249" t="str">
-        <v>Vai tiešām vēlaties dzēst šo pakalpojumu? Šo darbību nevar atsaukt.</v>
+        <v>Meklēt noteikumus...</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Are you sure you want to unsubscribe from this regulation? This action cannot be undone.</v>
+        <v>Are you sure you want to delete this department? This action cannot be undone.</v>
       </c>
       <c r="B250" t="str">
-        <v>هل أنت متأكد أنك تريد إلغاء الاشتراك من هذه اللائحة؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>هل أنت متأكد أنك تريد حذف هذا القسم؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C250" t="str">
-        <v>Vai tiešām vēlaties atteikties no šiem noteikumiem? Šo darbību nevar atsaukt.</v>
+        <v>Vai tiešām vēlaties dzēst šo nodaļu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Stakeholder</v>
+        <v>Are you sure you want to delete this service? This action cannot be undone.</v>
       </c>
       <c r="B251" t="str">
-        <v>صاحب المصلحة</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه الخدمة؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C251" t="str">
-        <v>Ieinteresētā puse</v>
+        <v>Vai tiešām vēlaties dzēst šo pakalpojumu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Stakeholders</v>
+        <v>Are you sure you want to unsubscribe from this regulation? This action cannot be undone.</v>
       </c>
       <c r="B252" t="str">
-        <v>أصحاب المصلحة</v>
+        <v>هل أنت متأكد أنك تريد إلغاء الاشتراك من هذه اللائحة؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C252" t="str">
-        <v>Ieinteresētās puses</v>
+        <v>Vai tiešām vēlaties atteikties no šiem noteikumiem? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Add Stakeholder</v>
+        <v>Stakeholder</v>
       </c>
       <c r="B253" t="str">
-        <v>إضافة صاحب مصلحة</v>
+        <v>صاحب المصلحة</v>
       </c>
       <c r="C253" t="str">
-        <v>Pievienot ieinteresēto pusi</v>
+        <v>Ieinteresētā puse</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Stakeholder Name</v>
+        <v>Stakeholders</v>
       </c>
       <c r="B254" t="str">
-        <v>اسم صاحب المصلحة</v>
+        <v>أصحاب المصلحة</v>
       </c>
       <c r="C254" t="str">
-        <v>Ieinteresētās puses nosaukums</v>
+        <v>Ieinteresētās puses</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Stakeholder Type</v>
+        <v>Add Stakeholder</v>
       </c>
       <c r="B255" t="str">
-        <v>نوع صاحب المصلحة</v>
+        <v>إضافة صاحب مصلحة</v>
       </c>
       <c r="C255" t="str">
-        <v>Ieinteresētās puses tips</v>
+        <v>Pievienot ieinteresēto pusi</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Third Party</v>
+        <v>Stakeholder Name</v>
       </c>
       <c r="B256" t="str">
-        <v>طرف ثالث</v>
+        <v>اسم صاحب المصلحة</v>
       </c>
       <c r="C256" t="str">
-        <v>Trešā puse</v>
+        <v>Ieinteresētās puses nosaukums</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Department</v>
+        <v>Stakeholder Type</v>
       </c>
       <c r="B257" t="str">
-        <v>القسم</v>
+        <v>نوع صاحب المصلحة</v>
       </c>
       <c r="C257" t="str">
-        <v>Nodaļa</v>
+        <v>Ieinteresētās puses tips</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Issues</v>
+        <v>Third Party</v>
       </c>
       <c r="B258" t="str">
-        <v>القضايا</v>
+        <v>طرف ثالث</v>
       </c>
       <c r="C258" t="str">
-        <v>Problēmas</v>
+        <v>Trešā puse</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Issue List</v>
+        <v>Department</v>
       </c>
       <c r="B259" t="str">
-        <v>قائمة القضايا</v>
+        <v>القسم</v>
       </c>
       <c r="C259" t="str">
-        <v>Problēmu saraksts</v>
+        <v>Nodaļa</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Add Issue</v>
+        <v>Issues</v>
       </c>
       <c r="B260" t="str">
-        <v>إضافة قضية</v>
+        <v>القضايا</v>
       </c>
       <c r="C260" t="str">
-        <v>Pievienot problēmu</v>
+        <v>Problēmas</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Issue Title</v>
+        <v>Issue List</v>
       </c>
       <c r="B261" t="str">
-        <v>عنوان القضية</v>
+        <v>قائمة القضايا</v>
       </c>
       <c r="C261" t="str">
-        <v>Problēmas nosaukums</v>
+        <v>Problēmu saraksts</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Domain</v>
+        <v>Add Issue</v>
       </c>
       <c r="B262" t="str">
-        <v>المجال</v>
+        <v>إضافة قضية</v>
       </c>
       <c r="C262" t="str">
-        <v>Domēns</v>
+        <v>Pievienot problēmu</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Issue Type</v>
+        <v>Issue Title</v>
       </c>
       <c r="B263" t="str">
-        <v>نوع القضية</v>
+        <v>عنوان القضية</v>
       </c>
       <c r="C263" t="str">
-        <v>Problēmas tips</v>
+        <v>Problēmas nosaukums</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Owner</v>
+        <v>Domain</v>
       </c>
       <c r="B264" t="str">
-        <v>المالك</v>
+        <v>المجال</v>
       </c>
       <c r="C264" t="str">
-        <v>Īpašnieks</v>
+        <v>Domēns</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Due Date</v>
+        <v>Issue Type</v>
       </c>
       <c r="B265" t="str">
-        <v>تاريخ الاستحقاق</v>
+        <v>نوع القضية</v>
       </c>
       <c r="C265" t="str">
-        <v>Izpildes termiņš</v>
+        <v>Problēmas tips</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Related Regulations</v>
+        <v>Owner</v>
       </c>
       <c r="B266" t="str">
-        <v>اللوائح ذات الصلة</v>
+        <v>المالك</v>
       </c>
       <c r="C266" t="str">
-        <v>Saistītie noteikumi</v>
+        <v>Īpašnieks</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Related Processes</v>
+        <v>Due Date</v>
       </c>
       <c r="B267" t="str">
-        <v>العمليات ذات الصلة</v>
+        <v>تاريخ الاستحقاق</v>
       </c>
       <c r="C267" t="str">
-        <v>Saistītie procesi</v>
+        <v>Izpildes termiņš</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Related Stakeholders</v>
+        <v>Related Regulations</v>
       </c>
       <c r="B268" t="str">
-        <v>أصحاب المصلحة ذوي الصلة</v>
+        <v>اللوائح ذات الصلة</v>
       </c>
       <c r="C268" t="str">
-        <v>Saistītās ieinteresētās puses</v>
+        <v>Saistītie noteikumi</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Needs &amp; Expectations</v>
+        <v>Related Processes</v>
       </c>
       <c r="B269" t="str">
-        <v>الاحتياجات والتوقعات</v>
+        <v>العمليات ذات الصلة</v>
       </c>
       <c r="C269" t="str">
-        <v>Vajadzības un gaidas</v>
+        <v>Saistītie procesi</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Preventive</v>
+        <v>Related Stakeholders</v>
       </c>
       <c r="B270" t="str">
-        <v>وقائي</v>
+        <v>أصحاب المصلحة ذوي الصلة</v>
       </c>
       <c r="C270" t="str">
-        <v>Preventīvs</v>
+        <v>Saistītās ieinteresētās puses</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Corrective</v>
+        <v>Needs &amp; Expectations</v>
       </c>
       <c r="B271" t="str">
-        <v>تصحيحي</v>
+        <v>الاحتياجات والتوقعات</v>
       </c>
       <c r="C271" t="str">
-        <v>Korektīvs</v>
+        <v>Vajadzības un gaidas</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Resolved</v>
+        <v>Preventive</v>
       </c>
       <c r="B272" t="str">
-        <v>تم الحل</v>
+        <v>وقائي</v>
       </c>
       <c r="C272" t="str">
-        <v>Atrisināts</v>
+        <v>Preventīvs</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Sent Back</v>
+        <v>Corrective</v>
       </c>
       <c r="B273" t="str">
-        <v>تم الإرجاع</v>
+        <v>تصحيحي</v>
       </c>
       <c r="C273" t="str">
-        <v>Nosūtīts atpakaļ</v>
+        <v>Korektīvs</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Add User</v>
+        <v>Resolved</v>
       </c>
       <c r="B274" t="str">
-        <v>إضافة مستخدم</v>
+        <v>تم الحل</v>
       </c>
       <c r="C274" t="str">
-        <v>Pievienot lietotāju</v>
+        <v>Atrisināts</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Full Name</v>
+        <v>Sent Back</v>
       </c>
       <c r="B275" t="str">
-        <v>الاسم الكامل</v>
+        <v>تم الإرجاع</v>
       </c>
       <c r="C275" t="str">
-        <v>Pilns vārds</v>
+        <v>Nosūtīts atpakaļ</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>First Name</v>
+        <v>Add User</v>
       </c>
       <c r="B276" t="str">
-        <v>الاسم الأول</v>
+        <v>إضافة مستخدم</v>
       </c>
       <c r="C276" t="str">
-        <v>Vārds</v>
+        <v>Pievienot lietotāju</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Last Name</v>
+        <v>Full Name</v>
       </c>
       <c r="B277" t="str">
-        <v>اسم العائلة</v>
+        <v>الاسم الكامل</v>
       </c>
       <c r="C277" t="str">
-        <v>Uzvārds</v>
+        <v>Pilns vārds</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Designation</v>
+        <v>First Name</v>
       </c>
       <c r="B278" t="str">
-        <v>المسمى الوظيفي</v>
+        <v>الاسم الأول</v>
       </c>
       <c r="C278" t="str">
-        <v>Amats</v>
+        <v>Vārds</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Function</v>
+        <v>Last Name</v>
       </c>
       <c r="B279" t="str">
-        <v>الوظيفة</v>
+        <v>اسم العائلة</v>
       </c>
       <c r="C279" t="str">
-        <v>Funkcija</v>
+        <v>Uzvārds</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Role</v>
+        <v>Designation</v>
       </c>
       <c r="B280" t="str">
-        <v>الدور</v>
+        <v>المسمى الوظيفي</v>
       </c>
       <c r="C280" t="str">
-        <v>Loma</v>
+        <v>Amats</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Roles</v>
+        <v>Function</v>
       </c>
       <c r="B281" t="str">
-        <v>الأدوار</v>
+        <v>الوظيفة</v>
       </c>
       <c r="C281" t="str">
-        <v>Lomas</v>
+        <v>Funkcija</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Is Active</v>
+        <v>Role</v>
       </c>
       <c r="B282" t="str">
-        <v>نشط</v>
+        <v>الدور</v>
       </c>
       <c r="C282" t="str">
-        <v>Ir aktīvs</v>
+        <v>Loma</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Is Blocked</v>
+        <v>Roles</v>
       </c>
       <c r="B283" t="str">
-        <v>محظور</v>
+        <v>الأدوار</v>
       </c>
       <c r="C283" t="str">
-        <v>Ir bloķēts</v>
+        <v>Lomas</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Last Login</v>
+        <v>Is Active</v>
       </c>
       <c r="B284" t="str">
-        <v>آخر تسجيل دخول</v>
+        <v>نشط</v>
       </c>
       <c r="C284" t="str">
-        <v>Pēdējā pieteikšanās</v>
+        <v>Ir aktīvs</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Created At</v>
+        <v>Is Blocked</v>
       </c>
       <c r="B285" t="str">
-        <v>تاريخ الإنشاء</v>
+        <v>محظور</v>
       </c>
       <c r="C285" t="str">
-        <v>Izveidots</v>
+        <v>Ir bloķēts</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Confirm Password</v>
+        <v>Last Login</v>
       </c>
       <c r="B286" t="str">
-        <v>تأكيد كلمة المرور</v>
+        <v>آخر تسجيل دخول</v>
       </c>
       <c r="C286" t="str">
-        <v>Apstiprināt paroli</v>
+        <v>Pēdējā pieteikšanās</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Change Password</v>
+        <v>Created At</v>
       </c>
       <c r="B287" t="str">
-        <v>تغيير كلمة المرور</v>
+        <v>تاريخ الإنشاء</v>
       </c>
       <c r="C287" t="str">
-        <v>Mainīt paroli</v>
+        <v>Izveidots</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Business</v>
+        <v>Confirm Password</v>
       </c>
       <c r="B288" t="str">
-        <v>الأعمال</v>
+        <v>تأكيد كلمة المرور</v>
       </c>
       <c r="C288" t="str">
-        <v>Bizness</v>
+        <v>Apstiprināt paroli</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Security</v>
+        <v>Change Password</v>
       </c>
       <c r="B289" t="str">
-        <v>الأمان</v>
+        <v>تغيير كلمة المرور</v>
       </c>
       <c r="C289" t="str">
-        <v>Drošība</v>
+        <v>Mainīt paroli</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Audit</v>
+        <v>Business</v>
       </c>
       <c r="B290" t="str">
-        <v>التدقيق</v>
+        <v>الأعمال</v>
       </c>
       <c r="C290" t="str">
-        <v>Audits</v>
+        <v>Bizness</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Account Overview</v>
+        <v>Security</v>
       </c>
       <c r="B291" t="str">
-        <v>نظرة عامة على الحساب</v>
+        <v>الأمان</v>
       </c>
       <c r="C291" t="str">
-        <v>Konta pārskats</v>
+        <v>Drošība</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>User Management</v>
+        <v>Audit</v>
       </c>
       <c r="B292" t="str">
-        <v>إدارة المستخدمين</v>
+        <v>التدقيق</v>
       </c>
       <c r="C292" t="str">
-        <v>Lietotāju pārvaldība</v>
+        <v>Audits</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>New Account</v>
+        <v>Account Overview</v>
       </c>
       <c r="B293" t="str">
-        <v>حساب جديد</v>
+        <v>نظرة عامة على الحساب</v>
       </c>
       <c r="C293" t="str">
-        <v>Jauns konts</v>
+        <v>Konta pārskats</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Edit Account</v>
+        <v>User Management</v>
       </c>
       <c r="B294" t="str">
-        <v>تعديل الحساب</v>
+        <v>إدارة المستخدمين</v>
       </c>
       <c r="C294" t="str">
-        <v>Rediģēt kontu</v>
+        <v>Lietotāju pārvaldība</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Import Users</v>
+        <v>New Account</v>
       </c>
       <c r="B295" t="str">
-        <v>استيراد المستخدمين</v>
+        <v>حساب جديد</v>
       </c>
       <c r="C295" t="str">
-        <v>Importēt lietotājus</v>
+        <v>Jauns konts</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Search by Department Name</v>
+        <v>Edit Account</v>
       </c>
       <c r="B296" t="str">
-        <v>البحث باسم القسم</v>
+        <v>تعديل الحساب</v>
       </c>
       <c r="C296" t="str">
-        <v>Meklēt pēc nodaļas nosaukuma</v>
+        <v>Rediģēt kontu</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Search user...</v>
+        <v>Import Users</v>
       </c>
       <c r="B297" t="str">
-        <v>البحث عن مستخدم...</v>
+        <v>استيراد المستخدمين</v>
       </c>
       <c r="C297" t="str">
-        <v>Meklēt lietotāju...</v>
+        <v>Importēt lietotājus</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>All Roles</v>
+        <v>Search by Department Name</v>
       </c>
       <c r="B298" t="str">
-        <v>جميع الأدوار</v>
+        <v>البحث باسم القسم</v>
       </c>
       <c r="C298" t="str">
-        <v>Visas lomas</v>
+        <v>Meklēt pēc nodaļas nosaukuma</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>All Departments</v>
+        <v>Search user...</v>
       </c>
       <c r="B299" t="str">
-        <v>جميع الأقسام</v>
+        <v>البحث عن مستخدم...</v>
       </c>
       <c r="C299" t="str">
-        <v>Visas nodaļas</v>
+        <v>Meklēt lietotāju...</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Account Credentials</v>
+        <v>All Roles</v>
       </c>
       <c r="B300" t="str">
-        <v>بيانات اعتماد الحساب</v>
+        <v>جميع الأدوار</v>
       </c>
       <c r="C300" t="str">
-        <v>Konta akreditācijas dati</v>
+        <v>Visas lomas</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Personal Information</v>
+        <v>All Departments</v>
       </c>
       <c r="B301" t="str">
-        <v>المعلومات الشخصية</v>
+        <v>جميع الأقسام</v>
       </c>
       <c r="C301" t="str">
-        <v>Personīgā informācija</v>
+        <v>Visas nodaļas</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Organization &amp; Role</v>
+        <v>Account Credentials</v>
       </c>
       <c r="B302" t="str">
-        <v>المنظمة والدور</v>
+        <v>بيانات اعتماد الحساب</v>
       </c>
       <c r="C302" t="str">
-        <v>Organizācija un loma</v>
+        <v>Konta akreditācijas dati</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Preferences</v>
+        <v>Personal Information</v>
       </c>
       <c r="B303" t="str">
-        <v>التفضيلات</v>
+        <v>المعلومات الشخصية</v>
       </c>
       <c r="C303" t="str">
-        <v>Preferences</v>
+        <v>Personīgā informācija</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Account Status</v>
+        <v>Organization &amp; Role</v>
       </c>
       <c r="B304" t="str">
-        <v>حالة الحساب</v>
+        <v>المنظمة والدور</v>
       </c>
       <c r="C304" t="str">
-        <v>Konta statuss</v>
+        <v>Organizācija un loma</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>User ID</v>
+        <v>Preferences</v>
       </c>
       <c r="B305" t="str">
-        <v>معرف المستخدم</v>
+        <v>التفضيلات</v>
       </c>
       <c r="C305" t="str">
-        <v>Lietotāja ID</v>
+        <v>Preferences</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>User Name</v>
+        <v>Account Status</v>
       </c>
       <c r="B306" t="str">
-        <v>اسم المستخدم</v>
+        <v>حالة الحساب</v>
       </c>
       <c r="C306" t="str">
-        <v>Lietotājvārds</v>
+        <v>Konta statuss</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Enter username</v>
+        <v>User ID</v>
       </c>
       <c r="B307" t="str">
-        <v>أدخل اسم المستخدم</v>
+        <v>معرف المستخدم</v>
       </c>
       <c r="C307" t="str">
-        <v>Ievadiet lietotājvārdu</v>
+        <v>Lietotāja ID</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Enter email</v>
+        <v>User Name</v>
       </c>
       <c r="B308" t="str">
-        <v>أدخل البريد الإلكتروني</v>
+        <v>اسم المستخدم</v>
       </c>
       <c r="C308" t="str">
-        <v>Ievadiet e-pastu</v>
+        <v>Lietotājvārds</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Enter password</v>
+        <v>Enter username</v>
       </c>
       <c r="B309" t="str">
-        <v>أدخل كلمة المرور</v>
+        <v>أدخل اسم المستخدم</v>
       </c>
       <c r="C309" t="str">
-        <v>Ievadiet paroli</v>
+        <v>Ievadiet lietotājvārdu</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Confirm password</v>
+        <v>Enter email</v>
       </c>
       <c r="B310" t="str">
-        <v>تأكيد كلمة المرور</v>
+        <v>أدخل البريد الإلكتروني</v>
       </c>
       <c r="C310" t="str">
-        <v>Apstipriniet paroli</v>
+        <v>Ievadiet e-pastu</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Enter first name</v>
+        <v>Enter password</v>
       </c>
       <c r="B311" t="str">
-        <v>أدخل الاسم الأول</v>
+        <v>أدخل كلمة المرور</v>
       </c>
       <c r="C311" t="str">
-        <v>Ievadiet vārdu</v>
+        <v>Ievadiet paroli</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Enter last name</v>
+        <v>Confirm password</v>
       </c>
       <c r="B312" t="str">
-        <v>أدخل اسم العائلة</v>
+        <v>تأكيد كلمة المرور</v>
       </c>
       <c r="C312" t="str">
-        <v>Ievadiet uzvārdu</v>
+        <v>Apstipriniet paroli</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Enter full name</v>
+        <v>Enter first name</v>
       </c>
       <c r="B313" t="str">
-        <v>أدخل الاسم الكامل</v>
+        <v>أدخل الاسم الأول</v>
       </c>
       <c r="C313" t="str">
-        <v>Ievadiet pilnu vārdu</v>
+        <v>Ievadiet vārdu</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Enter designation</v>
+        <v>Enter last name</v>
       </c>
       <c r="B314" t="str">
-        <v>أدخل المسمى الوظيفي</v>
+        <v>أدخل اسم العائلة</v>
       </c>
       <c r="C314" t="str">
-        <v>Ievadiet amatu</v>
+        <v>Ievadiet uzvārdu</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select function</v>
+        <v>Enter full name</v>
       </c>
       <c r="B315" t="str">
-        <v>اختر الوظيفة</v>
+        <v>أدخل الاسم الكامل</v>
       </c>
       <c r="C315" t="str">
-        <v>Izvēlieties funkciju</v>
+        <v>Ievadiet pilnu vārdu</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Select function first</v>
+        <v>Enter designation</v>
       </c>
       <c r="B316" t="str">
-        <v>اختر الوظيفة أولاً</v>
+        <v>أدخل المسمى الوظيفي</v>
       </c>
       <c r="C316" t="str">
-        <v>Vispirms izvēlieties funkciju</v>
+        <v>Ievadiet amatu</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Please select a function first</v>
+        <v>Select function</v>
       </c>
       <c r="B317" t="str">
-        <v>يرجى اختيار الوظيفة أولاً</v>
+        <v>اختر الوظيفة</v>
       </c>
       <c r="C317" t="str">
-        <v>Lūdzu, vispirms izvēlieties funkciju</v>
+        <v>Izvēlieties funkciju</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Select role</v>
+        <v>Select function first</v>
       </c>
       <c r="B318" t="str">
-        <v>اختر الدور</v>
+        <v>اختر الوظيفة أولاً</v>
       </c>
       <c r="C318" t="str">
-        <v>Izvēlieties lomu</v>
+        <v>Vispirms izvēlieties funkciju</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Select department</v>
+        <v>Please select a function first</v>
       </c>
       <c r="B319" t="str">
-        <v>اختر القسم</v>
+        <v>يرجى اختيار الوظيفة أولاً</v>
       </c>
       <c r="C319" t="str">
-        <v>Izvēlieties nodaļu</v>
+        <v>Lūdzu, vispirms izvēlieties funkciju</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Reporting Manager</v>
+        <v>Select role</v>
       </c>
       <c r="B320" t="str">
-        <v>المدير المباشر</v>
+        <v>اختر الدور</v>
       </c>
       <c r="C320" t="str">
-        <v>Ziņojošais vadītājs</v>
+        <v>Izvēlieties lomu</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Select reporting manager</v>
+        <v>Select department</v>
       </c>
       <c r="B321" t="str">
-        <v>اختر المدير المباشر</v>
+        <v>اختر القسم</v>
       </c>
       <c r="C321" t="str">
-        <v>Izvēlieties ziņojošo vadītāju</v>
+        <v>Izvēlieties nodaļu</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Language</v>
+        <v>Reporting Manager</v>
       </c>
       <c r="B322" t="str">
-        <v>اللغة</v>
+        <v>المدير المباشر</v>
       </c>
       <c r="C322" t="str">
-        <v>Valoda</v>
+        <v>Ziņojošais vadītājs</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Select language</v>
+        <v>Select reporting manager</v>
       </c>
       <c r="B323" t="str">
-        <v>اختر اللغة</v>
+        <v>اختر المدير المباشر</v>
       </c>
       <c r="C323" t="str">
-        <v>Izvēlieties valodu</v>
+        <v>Izvēlieties ziņojošo vadītāju</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Time Zone</v>
+        <v>Language</v>
       </c>
       <c r="B324" t="str">
-        <v>المنطقة الزمنية</v>
+        <v>اللغة</v>
       </c>
       <c r="C324" t="str">
-        <v>Laika zona</v>
+        <v>Valoda</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Select timezone</v>
+        <v>Select language</v>
       </c>
       <c r="B325" t="str">
-        <v>اختر المنطقة الزمنية</v>
+        <v>اختر اللغة</v>
       </c>
       <c r="C325" t="str">
-        <v>Izvēlieties laika zonu</v>
+        <v>Izvēlieties valodu</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Blocked</v>
+        <v>Time Zone</v>
       </c>
       <c r="B326" t="str">
-        <v>محظور</v>
+        <v>المنطقة الزمنية</v>
       </c>
       <c r="C326" t="str">
-        <v>Bloķēts</v>
+        <v>Laika zona</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Is local user</v>
+        <v>Select timezone</v>
       </c>
       <c r="B327" t="str">
-        <v>مستخدم محلي</v>
+        <v>اختر المنطقة الزمنية</v>
       </c>
       <c r="C327" t="str">
-        <v>Ir vietējais lietotājs</v>
+        <v>Izvēlieties laika zonu</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>User Role</v>
+        <v>Blocked</v>
       </c>
       <c r="B328" t="str">
-        <v>دور المستخدم</v>
+        <v>محظور</v>
       </c>
       <c r="C328" t="str">
-        <v>Lietotāja loma</v>
+        <v>Bloķēts</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Select Designation</v>
+        <v>Is local user</v>
       </c>
       <c r="B329" t="str">
-        <v>اختر المسمى الوظيفي</v>
+        <v>مستخدم محلي</v>
       </c>
       <c r="C329" t="str">
-        <v>Izvēlieties amatu</v>
+        <v>Ir vietējais lietotājs</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Analyst</v>
+        <v>User Role</v>
       </c>
       <c r="B330" t="str">
-        <v>محلل</v>
+        <v>دور المستخدم</v>
       </c>
       <c r="C330" t="str">
-        <v>Analītiķis</v>
+        <v>Lietotāja loma</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Developer</v>
+        <v>Select Designation</v>
       </c>
       <c r="B331" t="str">
-        <v>مطور</v>
+        <v>اختر المسمى الوظيفي</v>
       </c>
       <c r="C331" t="str">
-        <v>Izstrādātājs</v>
+        <v>Izvēlieties amatu</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Financial Analyst</v>
+        <v>Analyst</v>
       </c>
       <c r="B332" t="str">
-        <v>محلل مالي</v>
+        <v>محلل</v>
       </c>
       <c r="C332" t="str">
-        <v>Finanšu analītiķis</v>
+        <v>Analītiķis</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>HR Manager</v>
+        <v>Developer</v>
       </c>
       <c r="B333" t="str">
-        <v>مدير الموارد البشرية</v>
+        <v>مطور</v>
       </c>
       <c r="C333" t="str">
-        <v>Personāla vadītājs</v>
+        <v>Izstrādātājs</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Manager</v>
+        <v>Financial Analyst</v>
       </c>
       <c r="B334" t="str">
-        <v>مدير</v>
+        <v>محلل مالي</v>
       </c>
       <c r="C334" t="str">
-        <v>Vadītājs</v>
+        <v>Finanšu analītiķis</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Marketing Specialist</v>
+        <v>HR Manager</v>
       </c>
       <c r="B335" t="str">
-        <v>أخصائي تسويق</v>
+        <v>مدير الموارد البشرية</v>
       </c>
       <c r="C335" t="str">
-        <v>Mārketinga speciālists</v>
+        <v>Personāla vadītājs</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Operations Executive</v>
+        <v>Manager</v>
       </c>
       <c r="B336" t="str">
-        <v>تنفيذي العمليات</v>
+        <v>مدير</v>
       </c>
       <c r="C336" t="str">
-        <v>Operāciju vadītājs</v>
+        <v>Vadītājs</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Senior Manager</v>
+        <v>Marketing Specialist</v>
       </c>
       <c r="B337" t="str">
-        <v>مدير أول</v>
+        <v>أخصائي تسويق</v>
       </c>
       <c r="C337" t="str">
-        <v>Vecākais vadītājs</v>
+        <v>Mārketinga speciālists</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Software Engineer</v>
+        <v>Operations Executive</v>
       </c>
       <c r="B338" t="str">
-        <v>مهندس برمجيات</v>
+        <v>تنفيذي العمليات</v>
       </c>
       <c r="C338" t="str">
-        <v>Programmatūras inženieris</v>
+        <v>Operāciju vadītājs</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Team Lead</v>
+        <v>Senior Manager</v>
       </c>
       <c r="B339" t="str">
-        <v>قائد الفريق</v>
+        <v>مدير أول</v>
       </c>
       <c r="C339" t="str">
-        <v>Komandas vadītājs</v>
+        <v>Vecākais vadītājs</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>View Details</v>
+        <v>Software Engineer</v>
       </c>
       <c r="B340" t="str">
-        <v>عرض التفاصيل</v>
+        <v>مهندس برمجيات</v>
       </c>
       <c r="C340" t="str">
-        <v>Skatīt detaļas</v>
+        <v>Programmatūras inženieris</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Reset Password</v>
+        <v>Team Lead</v>
       </c>
       <c r="B341" t="str">
-        <v>إعادة تعيين كلمة المرور</v>
+        <v>قائد الفريق</v>
       </c>
       <c r="C341" t="str">
-        <v>Atiestatīt paroli</v>
+        <v>Komandas vadītājs</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Deactivate</v>
+        <v>View Details</v>
       </c>
       <c r="B342" t="str">
-        <v>إلغاء التفعيل</v>
+        <v>عرض التفاصيل</v>
       </c>
       <c r="C342" t="str">
-        <v>Deaktivizēt</v>
+        <v>Skatīt detaļas</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Download Template</v>
+        <v>Reset Password</v>
       </c>
       <c r="B343" t="str">
-        <v>تحميل القالب</v>
+        <v>إعادة تعيين كلمة المرور</v>
       </c>
       <c r="C343" t="str">
-        <v>Lejupielādēt veidni</v>
+        <v>Atiestatīt paroli</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Importing...</v>
+        <v>Deactivate</v>
       </c>
       <c r="B344" t="str">
-        <v>جاري الاستيراد...</v>
+        <v>إلغاء التفعيل</v>
       </c>
       <c r="C344" t="str">
-        <v>Importē...</v>
+        <v>Deaktivizēt</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Changing...</v>
+        <v>Download Template</v>
       </c>
       <c r="B345" t="str">
-        <v>جاري التغيير...</v>
+        <v>تحميل القالب</v>
       </c>
       <c r="C345" t="str">
-        <v>Maina...</v>
+        <v>Lejupielādēt veidni</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>New Password</v>
+        <v>Importing...</v>
       </c>
       <c r="B346" t="str">
-        <v>كلمة المرور الجديدة</v>
+        <v>جاري الاستيراد...</v>
       </c>
       <c r="C346" t="str">
-        <v>Jaunā parole</v>
+        <v>Importē...</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Enter new password</v>
+        <v>Import Assets</v>
       </c>
       <c r="B347" t="str">
-        <v>أدخل كلمة المرور الجديدة</v>
+        <v>استيراد الأصول</v>
       </c>
       <c r="C347" t="str">
-        <v>Ievadiet jauno paroli</v>
+        <v>Importēt aktīvus</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Confirm new password</v>
+        <v>Upload a CSV file to import assets. You can download a template to see the required format.</v>
       </c>
       <c r="B348" t="str">
-        <v>تأكيد كلمة المرور الجديدة</v>
+        <v>قم بتحميل ملف CSV لاستيراد الأصول. يمكنك تنزيل قالب لرؤية التنسيق المطلوب.</v>
       </c>
       <c r="C348" t="str">
-        <v>Apstipriniet jauno paroli</v>
+        <v>Augšupielādējiet CSV failu, lai importētu aktīvus. Varat lejupielādēt veidni, lai redzētu nepieciešamo formātu.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Enter a new password for</v>
+        <v>Choose a file...</v>
       </c>
       <c r="B349" t="str">
-        <v>أدخل كلمة مرور جديدة لـ</v>
+        <v>اختر ملفاً...</v>
       </c>
       <c r="C349" t="str">
-        <v>Ievadiet jaunu paroli lietotājam</v>
+        <v>Izvēlieties failu...</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>No users in this department</v>
+        <v>Browse...</v>
       </c>
       <c r="B350" t="str">
-        <v>لا يوجد مستخدمون في هذا القسم</v>
+        <v>تصفح...</v>
       </c>
       <c r="C350" t="str">
-        <v>Šajā nodaļā nav lietotāju</v>
+        <v>Pārlūkot...</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>users</v>
+        <v>Supported formats: CSV, XLSX, XLS</v>
       </c>
       <c r="B351" t="str">
-        <v>مستخدمون</v>
+        <v>التنسيقات المدعومة: CSV، XLSX، XLS</v>
       </c>
       <c r="C351" t="str">
-        <v>lietotāji</v>
+        <v>Atbalstītie formāti: CSV, XLSX, XLS</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Please fill in all required fields</v>
+        <v>Changing...</v>
       </c>
       <c r="B352" t="str">
-        <v>يرجى ملء جميع الحقول المطلوبة</v>
+        <v>جاري التغيير...</v>
       </c>
       <c r="C352" t="str">
-        <v>Lūdzu, aizpildiet visus obligātos laukus</v>
+        <v>Maina...</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Failed to create user</v>
+        <v>New Password</v>
       </c>
       <c r="B353" t="str">
-        <v>فشل في إنشاء المستخدم</v>
+        <v>كلمة المرور الجديدة</v>
       </c>
       <c r="C353" t="str">
-        <v>Neizdevās izveidot lietotāju</v>
+        <v>Jaunā parole</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Please enter a new password</v>
+        <v>Enter new password</v>
       </c>
       <c r="B354" t="str">
-        <v>يرجى إدخال كلمة مرور جديدة</v>
+        <v>أدخل كلمة المرور الجديدة</v>
       </c>
       <c r="C354" t="str">
-        <v>Lūdzu, ievadiet jaunu paroli</v>
+        <v>Ievadiet jauno paroli</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Password changed successfully</v>
+        <v>Confirm new password</v>
       </c>
       <c r="B355" t="str">
-        <v>تم تغيير كلمة المرور بنجاح</v>
+        <v>تأكيد كلمة المرور الجديدة</v>
       </c>
       <c r="C355" t="str">
-        <v>Parole veiksmīgi nomainīta</v>
+        <v>Apstipriniet jauno paroli</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Failed to change password</v>
+        <v>Enter a new password for</v>
       </c>
       <c r="B356" t="str">
-        <v>فشل في تغيير كلمة المرور</v>
+        <v>أدخل كلمة مرور جديدة لـ</v>
       </c>
       <c r="C356" t="str">
-        <v>Neizdevās nomainīt paroli</v>
+        <v>Ievadiet jaunu paroli lietotājam</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Import completed:</v>
+        <v>No users in this department</v>
       </c>
       <c r="B357" t="str">
-        <v>اكتمل الاستيراد:</v>
+        <v>لا يوجد مستخدمون في هذا القسم</v>
       </c>
       <c r="C357" t="str">
-        <v>Imports pabeigts:</v>
+        <v>Šajā nodaļā nav lietotāju</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>users imported,</v>
+        <v>users</v>
       </c>
       <c r="B358" t="str">
-        <v>مستخدم تم استيرادهم،</v>
+        <v>مستخدمون</v>
       </c>
       <c r="C358" t="str">
-        <v>lietotāji importēti,</v>
+        <v>lietotāji</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>errors</v>
+        <v>Please fill in all required fields</v>
       </c>
       <c r="B359" t="str">
-        <v>أخطاء</v>
+        <v>يرجى ملء جميع الحقول المطلوبة</v>
       </c>
       <c r="C359" t="str">
-        <v>kļūdas</v>
+        <v>Lūdzu, aizpildiet visus obligātos laukus</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Failed to import users. Please check the file format.</v>
+        <v>Failed to create user</v>
       </c>
       <c r="B360" t="str">
-        <v>فشل في استيراد المستخدمين. يرجى التحقق من تنسيق الملف.</v>
+        <v>فشل في إنشاء المستخدم</v>
       </c>
       <c r="C360" t="str">
-        <v>Neizdevās importēt lietotājus. Lūdzu, pārbaudiet faila formātu.</v>
+        <v>Neizdevās izveidot lietotāju</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Designation Name</v>
+        <v>Please enter a new password</v>
       </c>
       <c r="B361" t="str">
-        <v>اسم المسمى الوظيفي</v>
+        <v>يرجى إدخال كلمة مرور جديدة</v>
       </c>
       <c r="C361" t="str">
-        <v>Amata nosaukums</v>
+        <v>Lūdzu, ievadiet jaunu paroli</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Email ID</v>
+        <v>Password changed successfully</v>
       </c>
       <c r="B362" t="str">
-        <v>معرف البريد الإلكتروني</v>
+        <v>تم تغيير كلمة المرور بنجاح</v>
       </c>
       <c r="C362" t="str">
-        <v>E-pasta ID</v>
+        <v>Parole veiksmīgi nomainīta</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Add New</v>
+        <v>Failed to change password</v>
       </c>
       <c r="B363" t="str">
-        <v>إضافة جديد</v>
+        <v>فشل في تغيير كلمة المرور</v>
       </c>
       <c r="C363" t="str">
-        <v>Pievienot jaunu</v>
+        <v>Neizdevās nomainīt paroli</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>File</v>
+        <v>Import completed:</v>
       </c>
       <c r="B364" t="str">
-        <v>ملف</v>
+        <v>اكتمل الاستيراد:</v>
       </c>
       <c r="C364" t="str">
-        <v>Fails</v>
+        <v>Imports pabeigts:</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Selected:</v>
+        <v>users imported,</v>
       </c>
       <c r="B365" t="str">
-        <v>المحدد:</v>
+        <v>مستخدم تم استيرادهم،</v>
       </c>
       <c r="C365" t="str">
-        <v>Izvēlēts:</v>
+        <v>lietotāji importēti,</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Search users...</v>
+        <v>errors</v>
       </c>
       <c r="B366" t="str">
-        <v>البحث في المستخدمين...</v>
+        <v>أخطاء</v>
       </c>
       <c r="C366" t="str">
-        <v>Meklēt lietotājus...</v>
+        <v>kļūdas</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>English</v>
+        <v>Failed to import users. Please check the file format.</v>
       </c>
       <c r="B367" t="str">
-        <v>الإنجليزية</v>
+        <v>فشل في استيراد المستخدمين. يرجى التحقق من تنسيق الملف.</v>
       </c>
       <c r="C367" t="str">
-        <v>Angļu</v>
+        <v>Neizdevās importēt lietotājus. Lūdzu, pārbaudiet faila formātu.</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Arabic</v>
+        <v>Designation Name</v>
       </c>
       <c r="B368" t="str">
-        <v>العربية</v>
+        <v>اسم المسمى الوظيفي</v>
       </c>
       <c r="C368" t="str">
-        <v>Arābu</v>
+        <v>Amata nosaukums</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Hindi</v>
+        <v>Email ID</v>
       </c>
       <c r="B369" t="str">
-        <v>الهندية</v>
+        <v>معرف البريد الإلكتروني</v>
       </c>
       <c r="C369" t="str">
-        <v>Hindi</v>
+        <v>E-pasta ID</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Latvian</v>
+        <v>Add New</v>
       </c>
       <c r="B370" t="str">
-        <v>اللاتفية</v>
+        <v>إضافة جديد</v>
       </c>
       <c r="C370" t="str">
-        <v>Latviešu</v>
+        <v>Pievienot jaunu</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Select...</v>
+        <v>File</v>
       </c>
       <c r="B371" t="str">
-        <v>اختر...</v>
+        <v>ملف</v>
       </c>
       <c r="C371" t="str">
-        <v>Izvēlieties...</v>
+        <v>Fails</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Download the template file and fill in your data</v>
+        <v>Selected:</v>
       </c>
       <c r="B372" t="str">
-        <v>قم بتحميل ملف القالب وملء بياناتك</v>
+        <v>المحدد:</v>
       </c>
       <c r="C372" t="str">
-        <v>Lejupielādējiet veidnes failu un aizpildiet savus datus</v>
+        <v>Izvēlēts:</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Import users from a CSV file. The file should have columns: Username, Email, Password, First Name, Last Name, Full Name, Designation, Function, Role, Department, Language, Timezone.</v>
+        <v>Search users...</v>
       </c>
       <c r="B373" t="str">
-        <v>استيراد المستخدمين من ملف CSV. يجب أن يحتوي الملف على أعمدة: اسم المستخدم، البريد الإلكتروني، كلمة المرور، الاسم الأول، اسم العائلة، الاسم الكامل، المسمى الوظيفي، الوظيفة، الدور، القسم، اللغة، المنطقة الزمنية.</v>
+        <v>البحث في المستخدمين...</v>
       </c>
       <c r="C373" t="str">
-        <v>Importējiet lietotājus no CSV faila. Failam jābūt ar kolonnām: Lietotājvārds, E-pasts, Parole, Vārds, Uzvārds, Pilns vārds, Amats, Funkcija, Loma, Nodaļa, Valoda, Laika zona.</v>
+        <v>Meklēt lietotājus...</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>View Mode</v>
+        <v>English</v>
       </c>
       <c r="B374" t="str">
-        <v>وضع العرض</v>
+        <v>الإنجليزية</v>
       </c>
       <c r="C374" t="str">
-        <v>Skata režīms</v>
+        <v>Angļu</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Role-wise Chart</v>
+        <v>Arabic</v>
       </c>
       <c r="B375" t="str">
-        <v>مخطط حسب الدور</v>
+        <v>العربية</v>
       </c>
       <c r="C375" t="str">
-        <v>Lomu diagramma</v>
+        <v>Arābu</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Department-wise Chart</v>
+        <v>Hindi</v>
       </c>
       <c r="B376" t="str">
-        <v>مخطط حسب القسم</v>
+        <v>الهندية</v>
       </c>
       <c r="C376" t="str">
-        <v>Nodaļu diagramma</v>
+        <v>Hindi</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Loading organization chart...</v>
+        <v>Latvian</v>
       </c>
       <c r="B377" t="str">
-        <v>جاري تحميل الهيكل التنظيمي...</v>
+        <v>اللاتفية</v>
       </c>
       <c r="C377" t="str">
-        <v>Ielādē organizācijas shēmu...</v>
+        <v>Latviešu</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>No users found. Add users and assign reporting managers to build the organization chart.</v>
+        <v>Select...</v>
       </c>
       <c r="B378" t="str">
-        <v>لم يتم العثور على مستخدمين. أضف مستخدمين وعيّن مدراء للتقارير لبناء الهيكل التنظيمي.</v>
+        <v>اختر...</v>
       </c>
       <c r="C378" t="str">
-        <v>Nav atrasts neviens lietotājs. Pievienojiet lietotājus un piešķiriet vadītājus, lai izveidotu organizācijas shēmu.</v>
+        <v>Izvēlieties...</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No users found in</v>
+        <v>Download the template file and fill in your data</v>
       </c>
       <c r="B379" t="str">
-        <v>لم يتم العثور على مستخدمين في</v>
+        <v>قم بتحميل ملف القالب وملء بياناتك</v>
       </c>
       <c r="C379" t="str">
-        <v>Nav atrasts neviens lietotājs</v>
+        <v>Lejupielādējiet veidnes failu un aizpildiet savus datus</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>selected department</v>
+        <v>Import users from a CSV file. The file should have columns: Username, Email, Password, First Name, Last Name, Full Name, Designation, Function, Role, Department, Language, Timezone.</v>
       </c>
       <c r="B380" t="str">
-        <v>القسم المحدد</v>
+        <v>استيراد المستخدمين من ملف CSV. يجب أن يحتوي الملف على أعمدة: اسم المستخدم، البريد الإلكتروني، كلمة المرور، الاسم الأول، اسم العائلة، الاسم الكامل، المسمى الوظيفي، الوظيفة، الدور، القسم، اللغة، المنطقة الزمنية.</v>
       </c>
       <c r="C380" t="str">
-        <v>izvēlētajā nodaļā</v>
+        <v>Importējiet lietotājus no CSV faila. Failam jābūt ar kolonnām: Lietotājvārds, E-pasts, Parole, Vārds, Uzvārds, Pilns vārds, Amats, Funkcija, Loma, Nodaļa, Valoda, Laika zona.</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Assign users to this department to see the hierarchy.</v>
+        <v>View Mode</v>
       </c>
       <c r="B381" t="str">
-        <v>عيّن مستخدمين لهذا القسم لرؤية التسلسل الهرمي.</v>
+        <v>وضع العرض</v>
       </c>
       <c r="C381" t="str">
-        <v>Piešķiriet lietotājus šai nodaļai, lai redzētu hierarhiju.</v>
+        <v>Skata režīms</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Select a department to view its hierarchy.</v>
+        <v>Role-wise Chart</v>
       </c>
       <c r="B382" t="str">
-        <v>حدد قسماً لعرض تسلسله الهرمي.</v>
+        <v>مخطط حسب الدور</v>
       </c>
       <c r="C382" t="str">
-        <v>Izvēlieties nodaļu, lai skatītu tās hierarhiju.</v>
+        <v>Lomu diagramma</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No organization hierarchy defined. Assign reporting managers to users to build the chart.</v>
+        <v>Department-wise Chart</v>
       </c>
       <c r="B383" t="str">
-        <v>لم يتم تحديد تسلسل هرمي للمنظمة. عيّن مدراء للتقارير للمستخدمين لبناء المخطط.</v>
+        <v>مخطط حسب القسم</v>
       </c>
       <c r="C383" t="str">
-        <v>Nav definēta organizācijas hierarhija. Piešķiriet vadītājus lietotājiem, lai izveidotu shēmu.</v>
+        <v>Nodaļu diagramma</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Processes</v>
+        <v>Loading organization chart...</v>
       </c>
       <c r="B384" t="str">
-        <v>العمليات</v>
+        <v>جاري تحميل الهيكل التنظيمي...</v>
       </c>
       <c r="C384" t="str">
-        <v>Procesi</v>
+        <v>Ielādē organizācijas shēmu...</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Add Process</v>
+        <v>No users found. Add users and assign reporting managers to build the organization chart.</v>
       </c>
       <c r="B385" t="str">
-        <v>إضافة عملية</v>
+        <v>لم يتم العثور على مستخدمين. أضف مستخدمين وعيّن مدراء للتقارير لبناء الهيكل التنظيمي.</v>
       </c>
       <c r="C385" t="str">
-        <v>Pievienot procesu</v>
+        <v>Nav atrasts neviens lietotājs. Pievienojiet lietotājus un piešķiriet vadītājus, lai izveidotu organizācijas shēmu.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Process Code</v>
+        <v>No users found in</v>
       </c>
       <c r="B386" t="str">
-        <v>رمز العملية</v>
+        <v>لم يتم العثور على مستخدمين في</v>
       </c>
       <c r="C386" t="str">
-        <v>Procesa kods</v>
+        <v>Nav atrasts neviens lietotājs</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Process Name</v>
+        <v>selected department</v>
       </c>
       <c r="B387" t="str">
-        <v>اسم العملية</v>
+        <v>القسم المحدد</v>
       </c>
       <c r="C387" t="str">
-        <v>Procesa nosaukums</v>
+        <v>izvēlētajā nodaļā</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Process Owner</v>
+        <v>Assign users to this department to see the hierarchy.</v>
       </c>
       <c r="B388" t="str">
-        <v>مالك العملية</v>
+        <v>عيّن مستخدمين لهذا القسم لرؤية التسلسل الهرمي.</v>
       </c>
       <c r="C388" t="str">
-        <v>Procesa īpašnieks</v>
+        <v>Piešķiriet lietotājus šai nodaļai, lai redzētu hierarhiju.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Process Type</v>
+        <v>Select a department to view its hierarchy.</v>
       </c>
       <c r="B389" t="str">
-        <v>نوع العملية</v>
+        <v>حدد قسماً لعرض تسلسله الهرمي.</v>
       </c>
       <c r="C389" t="str">
-        <v>Procesa tips</v>
+        <v>Izvēlieties nodaļu, lai skatītu tās hierarhiju.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Core</v>
+        <v>No organization hierarchy defined. Assign reporting managers to users to build the chart.</v>
       </c>
       <c r="B390" t="str">
-        <v>أساسي</v>
+        <v>لم يتم تحديد تسلسل هرمي للمنظمة. عيّن مدراء للتقارير للمستخدمين لبناء المخطط.</v>
       </c>
       <c r="C390" t="str">
-        <v>Pamata</v>
+        <v>Nav definēta organizācijas hierarhija. Piešķiriet vadītājus lietotājiem, lai izveidotu shēmu.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Support</v>
+        <v>Processes</v>
       </c>
       <c r="B391" t="str">
-        <v>دعم</v>
+        <v>العمليات</v>
       </c>
       <c r="C391" t="str">
-        <v>Atbalsta</v>
+        <v>Procesi</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Management</v>
+        <v>Add Process</v>
       </c>
       <c r="B392" t="str">
-        <v>إدارة</v>
+        <v>إضافة عملية</v>
       </c>
       <c r="C392" t="str">
-        <v>Vadības</v>
+        <v>Pievienot procesu</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Frequency</v>
+        <v>Process Code</v>
       </c>
       <c r="B393" t="str">
-        <v>التكرار</v>
+        <v>رمز العملية</v>
       </c>
       <c r="C393" t="str">
-        <v>Biežums</v>
+        <v>Procesa kods</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Daily</v>
+        <v>Process Name</v>
       </c>
       <c r="B394" t="str">
-        <v>يومي</v>
+        <v>اسم العملية</v>
       </c>
       <c r="C394" t="str">
-        <v>Ikdienas</v>
+        <v>Procesa nosaukums</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Weekly</v>
+        <v>Process Owner</v>
       </c>
       <c r="B395" t="str">
-        <v>أسبوعي</v>
+        <v>مالك العملية</v>
       </c>
       <c r="C395" t="str">
-        <v>Iknedēļas</v>
+        <v>Procesa īpašnieks</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Monthly</v>
+        <v>Process Type</v>
       </c>
       <c r="B396" t="str">
-        <v>شهري</v>
+        <v>نوع العملية</v>
       </c>
       <c r="C396" t="str">
-        <v>Ikmēneša</v>
+        <v>Procesa tips</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Quarterly</v>
+        <v>Core</v>
       </c>
       <c r="B397" t="str">
-        <v>ربع سنوي</v>
+        <v>أساسي</v>
       </c>
       <c r="C397" t="str">
-        <v>Ceturkšņa</v>
+        <v>Pamata</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Annually</v>
+        <v>Support</v>
       </c>
       <c r="B398" t="str">
-        <v>سنوي</v>
+        <v>دعم</v>
       </c>
       <c r="C398" t="str">
-        <v>Ikgadējs</v>
+        <v>Atbalsta</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>As Needed</v>
+        <v>Management</v>
       </c>
       <c r="B399" t="str">
-        <v>حسب الحاجة</v>
+        <v>إدارة</v>
       </c>
       <c r="C399" t="str">
-        <v>Pēc vajadzības</v>
+        <v>Vadības</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Responsible</v>
+        <v>Frequency</v>
       </c>
       <c r="B400" t="str">
-        <v>المسؤول</v>
+        <v>التكرار</v>
       </c>
       <c r="C400" t="str">
-        <v>Atbildīgais</v>
+        <v>Biežums</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Accountable</v>
+        <v>Daily</v>
       </c>
       <c r="B401" t="str">
-        <v>المحاسب</v>
+        <v>يومي</v>
       </c>
       <c r="C401" t="str">
-        <v>Uzraugošais</v>
+        <v>Ikdienas</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Consulted</v>
+        <v>Weekly</v>
       </c>
       <c r="B402" t="str">
-        <v>المستشار</v>
+        <v>أسبوعي</v>
       </c>
       <c r="C402" t="str">
-        <v>Konsultējamais</v>
+        <v>Iknedēļas</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Informed</v>
+        <v>Monthly</v>
       </c>
       <c r="B403" t="str">
-        <v>المُبلَّغ</v>
+        <v>شهري</v>
       </c>
       <c r="C403" t="str">
-        <v>Informējamais</v>
+        <v>Ikmēneša</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Select Process</v>
+        <v>Quarterly</v>
       </c>
       <c r="B404" t="str">
-        <v>اختر العملية</v>
+        <v>ربع سنوي</v>
       </c>
       <c r="C404" t="str">
-        <v>Izvēlēties procesu</v>
+        <v>Ceturkšņa</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>No processes available</v>
+        <v>Annually</v>
       </c>
       <c r="B405" t="str">
-        <v>لا توجد عمليات متاحة</v>
+        <v>سنوي</v>
       </c>
       <c r="C405" t="str">
-        <v>Nav pieejamu procesu</v>
+        <v>Ikgadējs</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Business Impact Analysis</v>
+        <v>As Needed</v>
       </c>
       <c r="B406" t="str">
-        <v>تحليل تأثير الأعمال</v>
+        <v>حسب الحاجة</v>
       </c>
       <c r="C406" t="str">
-        <v>Biznesa ietekmes analīze</v>
+        <v>Pēc vajadzības</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Add BIA</v>
+        <v>Responsible</v>
       </c>
       <c r="B407" t="str">
-        <v>إضافة تحليل تأثير</v>
+        <v>المسؤول</v>
       </c>
       <c r="C407" t="str">
-        <v>Pievienot BIA</v>
+        <v>Atbildīgais</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Criticality</v>
+        <v>Accountable</v>
       </c>
       <c r="B408" t="str">
-        <v>الأهمية</v>
+        <v>المحاسب</v>
       </c>
       <c r="C408" t="str">
-        <v>Kritiskums</v>
+        <v>Uzraugošais</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Critical</v>
+        <v>Consulted</v>
       </c>
       <c r="B409" t="str">
-        <v>حرج</v>
+        <v>المستشار</v>
       </c>
       <c r="C409" t="str">
-        <v>Kritisks</v>
+        <v>Konsultējamais</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>High</v>
+        <v>Informed</v>
       </c>
       <c r="B410" t="str">
-        <v>عالي</v>
+        <v>المُبلَّغ</v>
       </c>
       <c r="C410" t="str">
-        <v>Augsts</v>
+        <v>Informējamais</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Medium</v>
+        <v>Select Process</v>
       </c>
       <c r="B411" t="str">
-        <v>متوسط</v>
+        <v>اختر العملية</v>
       </c>
       <c r="C411" t="str">
-        <v>Vidējs</v>
+        <v>Izvēlēties procesu</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Low</v>
+        <v>No processes available</v>
       </c>
       <c r="B412" t="str">
-        <v>منخفض</v>
+        <v>لا توجد عمليات متاحة</v>
       </c>
       <c r="C412" t="str">
-        <v>Zems</v>
+        <v>Nav pieejamu procesu</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>RTO (Recovery Time Objective)</v>
+        <v>Business Impact Analysis</v>
       </c>
       <c r="B413" t="str">
-        <v>هدف وقت الاستعادة</v>
+        <v>تحليل تأثير الأعمال</v>
       </c>
       <c r="C413" t="str">
-        <v>RTO (Atjaunošanas laika mērķis)</v>
+        <v>Biznesa ietekmes analīze</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>RPO (Recovery Point Objective)</v>
+        <v>Add BIA</v>
       </c>
       <c r="B414" t="str">
-        <v>هدف نقطة الاستعادة</v>
+        <v>إضافة تحليل تأثير</v>
       </c>
       <c r="C414" t="str">
-        <v>RPO (Atjaunošanas punkta mērķis)</v>
+        <v>Pievienot BIA</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>MTPD (Maximum Tolerable Period of Disruption)</v>
+        <v>Criticality</v>
       </c>
       <c r="B415" t="str">
-        <v>أقصى فترة تعطل مقبولة</v>
+        <v>الأهمية</v>
       </c>
       <c r="C415" t="str">
-        <v>MTPD (Maksimālais pieļaujamais pārtraukuma periods)</v>
+        <v>Kritiskums</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Dependencies</v>
+        <v>Critical</v>
       </c>
       <c r="B416" t="str">
-        <v>التبعيات</v>
+        <v>حرج</v>
       </c>
       <c r="C416" t="str">
-        <v>Atkarības</v>
+        <v>Kritisks</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Resources</v>
+        <v>High</v>
       </c>
       <c r="B417" t="str">
-        <v>الموارد</v>
+        <v>عالي</v>
       </c>
       <c r="C417" t="str">
-        <v>Resursi</v>
+        <v>Augsts</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Impact Analysis</v>
+        <v>Medium</v>
       </c>
       <c r="B418" t="str">
-        <v>تحليل التأثير</v>
+        <v>متوسط</v>
       </c>
       <c r="C418" t="str">
-        <v>Ietekmes analīze</v>
+        <v>Vidējs</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Search by control code or name...</v>
+        <v>Low</v>
       </c>
       <c r="B419" t="str">
-        <v>البحث برمز الضابطة أو الاسم...</v>
+        <v>منخفض</v>
       </c>
       <c r="C419" t="str">
-        <v>Meklēt pēc kontroles koda vai nosaukuma...</v>
+        <v>Zems</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Integrated Framework</v>
+        <v>RTO (Recovery Time Objective)</v>
       </c>
       <c r="B420" t="str">
-        <v>الإطار المتكامل</v>
+        <v>هدف وقت الاستعادة</v>
       </c>
       <c r="C420" t="str">
-        <v>Integrētais ietvars</v>
+        <v>RTO (Atjaunošanas laika mērķis)</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>All Frameworks</v>
+        <v>RPO (Recovery Point Objective)</v>
       </c>
       <c r="B421" t="str">
-        <v>جميع الأطر</v>
+        <v>هدف نقطة الاستعادة</v>
       </c>
       <c r="C421" t="str">
-        <v>Visi ietvari</v>
+        <v>RPO (Atjaunošanas punkta mērķis)</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Delete All</v>
+        <v>MTPD (Maximum Tolerable Period of Disruption)</v>
       </c>
       <c r="B422" t="str">
-        <v>حذف الكل</v>
+        <v>أقصى فترة تعطل مقبولة</v>
       </c>
       <c r="C422" t="str">
-        <v>Dzēst visu</v>
+        <v>MTPD (Maksimālais pieļaujamais pārtraukuma periods)</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>New Control</v>
+        <v>Dependencies</v>
       </c>
       <c r="B423" t="str">
-        <v>ضابطة جديدة</v>
+        <v>التبعيات</v>
       </c>
       <c r="C423" t="str">
-        <v>Jauna kontrole</v>
+        <v>Atkarības</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Control Name</v>
+        <v>Resources</v>
       </c>
       <c r="B424" t="str">
-        <v>اسم الضابطة</v>
+        <v>الموارد</v>
       </c>
       <c r="C424" t="str">
-        <v>Kontroles nosaukums</v>
+        <v>Resursi</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Control Code</v>
+        <v>Impact Analysis</v>
       </c>
       <c r="B425" t="str">
-        <v>رمز الضابطة</v>
+        <v>تحليل التأثير</v>
       </c>
       <c r="C425" t="str">
-        <v>Kontroles kods</v>
+        <v>Ietekmes analīze</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Functional Grouping</v>
+        <v>Search by control code or name...</v>
       </c>
       <c r="B426" t="str">
-        <v>التجميع الوظيفي</v>
+        <v>البحث برمز الضابطة أو الاسم...</v>
       </c>
       <c r="C426" t="str">
-        <v>Funkcionālā grupēšana</v>
+        <v>Meklēt pēc kontroles koda vai nosaukuma...</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Assignee</v>
+        <v>Integrated Framework</v>
       </c>
       <c r="B427" t="str">
-        <v>المسؤول</v>
+        <v>الإطار المتكامل</v>
       </c>
       <c r="C427" t="str">
-        <v>Piešķirtais</v>
+        <v>Integrētais ietvars</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Domain Name</v>
+        <v>All Frameworks</v>
       </c>
       <c r="B428" t="str">
-        <v>اسم المجال</v>
+        <v>جميع الأطر</v>
       </c>
       <c r="C428" t="str">
-        <v>Domēna nosaukums</v>
+        <v>Visi ietvari</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No controls found.</v>
+        <v>Delete All</v>
       </c>
       <c r="B429" t="str">
-        <v>لم يتم العثور على ضوابط.</v>
+        <v>حذف الكل</v>
       </c>
       <c r="C429" t="str">
-        <v>Kontroles nav atrastas.</v>
+        <v>Dzēst visu</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>No controls</v>
+        <v>New Control</v>
       </c>
       <c r="B430" t="str">
-        <v>لا توجد ضوابط</v>
+        <v>ضابطة جديدة</v>
       </c>
       <c r="C430" t="str">
-        <v>Nav kontroles</v>
+        <v>Jauna kontrole</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Govern</v>
+        <v>Control Name</v>
       </c>
       <c r="B431" t="str">
-        <v>الحوكمة</v>
+        <v>اسم الضابطة</v>
       </c>
       <c r="C431" t="str">
-        <v>Pārvaldīt</v>
+        <v>Kontroles nosaukums</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Identify</v>
+        <v>Control Code</v>
       </c>
       <c r="B432" t="str">
-        <v>تحديد</v>
+        <v>رمز الضابطة</v>
       </c>
       <c r="C432" t="str">
-        <v>Identificēt</v>
+        <v>Kontroles kods</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Protect</v>
+        <v>Functional Grouping</v>
       </c>
       <c r="B433" t="str">
-        <v>حماية</v>
+        <v>التجميع الوظيفي</v>
       </c>
       <c r="C433" t="str">
-        <v>Aizsargāt</v>
+        <v>Funkcionālā grupēšana</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Detect</v>
+        <v>Assignee</v>
       </c>
       <c r="B434" t="str">
-        <v>اكتشاف</v>
+        <v>المسؤول</v>
       </c>
       <c r="C434" t="str">
-        <v>Atklāt</v>
+        <v>Piešķirtais</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Respond</v>
+        <v>Domain Name</v>
       </c>
       <c r="B435" t="str">
-        <v>استجابة</v>
+        <v>اسم المجال</v>
       </c>
       <c r="C435" t="str">
-        <v>Reaģēt</v>
+        <v>Domēna nosaukums</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Recover</v>
+        <v>No controls found.</v>
       </c>
       <c r="B436" t="str">
-        <v>استعادة</v>
+        <v>لم يتم العثور على ضوابط.</v>
       </c>
       <c r="C436" t="str">
-        <v>Atjaunot</v>
+        <v>Kontroles nav atrastas.</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You don't have permission to access Controls.</v>
+        <v>No controls</v>
       </c>
       <c r="B437" t="str">
-        <v>ليس لديك صلاحية للوصول إلى الضوابط.</v>
+        <v>لا توجد ضوابط</v>
       </c>
       <c r="C437" t="str">
-        <v>Jums nav atļaujas piekļūt kontrolēm.</v>
+        <v>Nav kontroles</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Policy</v>
+        <v>Govern</v>
       </c>
       <c r="B438" t="str">
-        <v>السياسة</v>
+        <v>الحوكمة</v>
       </c>
       <c r="C438" t="str">
-        <v>Politika</v>
+        <v>Pārvaldīt</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Standards</v>
+        <v>Identify</v>
       </c>
       <c r="B439" t="str">
-        <v>المعايير</v>
+        <v>تحديد</v>
       </c>
       <c r="C439" t="str">
-        <v>Standarti</v>
+        <v>Identificēt</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Procedures</v>
+        <v>Protect</v>
       </c>
       <c r="B440" t="str">
-        <v>الإجراءات</v>
+        <v>حماية</v>
       </c>
       <c r="C440" t="str">
-        <v>Procedūras</v>
+        <v>Aizsargāt</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Search by policy name or code...</v>
+        <v>Detect</v>
       </c>
       <c r="B441" t="str">
-        <v>البحث باسم السياسة أو الرمز...</v>
+        <v>اكتشاف</v>
       </c>
       <c r="C441" t="str">
-        <v>Meklēt pēc politikas nosaukuma vai koda...</v>
+        <v>Atklāt</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Search by standard name or code...</v>
+        <v>Respond</v>
       </c>
       <c r="B442" t="str">
-        <v>البحث باسم المعيار أو الرمز...</v>
+        <v>استجابة</v>
       </c>
       <c r="C442" t="str">
-        <v>Meklēt pēc standarta nosaukuma vai koda...</v>
+        <v>Reaģēt</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Search by procedure name or code...</v>
+        <v>Recover</v>
       </c>
       <c r="B443" t="str">
-        <v>البحث باسم الإجراء أو الرمز...</v>
+        <v>استعادة</v>
       </c>
       <c r="C443" t="str">
-        <v>Meklēt pēc procedūras nosaukuma vai koda...</v>
+        <v>Atjaunot</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>New Governance</v>
+        <v>You don't have permission to access Controls.</v>
       </c>
       <c r="B444" t="str">
-        <v>حوكمة جديدة</v>
+        <v>ليس لديك صلاحية للوصول إلى الضوابط.</v>
       </c>
       <c r="C444" t="str">
-        <v>Jauna pārvaldība</v>
+        <v>Jums nav atļaujas piekļūt kontrolēm.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Code</v>
+        <v>Policy</v>
       </c>
       <c r="B445" t="str">
-        <v>الرمز</v>
+        <v>السياسة</v>
       </c>
       <c r="C445" t="str">
-        <v>Kods</v>
+        <v>Politika</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Approver</v>
+        <v>Standards</v>
       </c>
       <c r="B446" t="str">
-        <v>المعتمد</v>
+        <v>المعايير</v>
       </c>
       <c r="C446" t="str">
-        <v>Apstiprinātājs</v>
+        <v>Standarti</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Action</v>
+        <v>Procedures</v>
       </c>
       <c r="B447" t="str">
-        <v>الإجراء</v>
+        <v>الإجراءات</v>
       </c>
       <c r="C447" t="str">
-        <v>Darbība</v>
+        <v>Procedūras</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>No policys found</v>
+        <v>Search by policy name or code...</v>
       </c>
       <c r="B448" t="str">
-        <v>لم يتم العثور على سياسات</v>
+        <v>البحث باسم السياسة أو الرمز...</v>
       </c>
       <c r="C448" t="str">
-        <v>Politikas nav atrastas</v>
+        <v>Meklēt pēc politikas nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No standards found</v>
+        <v>Search by standard name or code...</v>
       </c>
       <c r="B449" t="str">
-        <v>لم يتم العثور على معايير</v>
+        <v>البحث باسم المعيار أو الرمز...</v>
       </c>
       <c r="C449" t="str">
-        <v>Standarti nav atrasti</v>
+        <v>Meklēt pēc standarta nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>No procedures found</v>
+        <v>Search by procedure name or code...</v>
       </c>
       <c r="B450" t="str">
-        <v>لم يتم العثور على إجراءات</v>
+        <v>البحث باسم الإجراء أو الرمز...</v>
       </c>
       <c r="C450" t="str">
-        <v>Procedūras nav atrastas</v>
+        <v>Meklēt pēc procedūras nosaukuma vai koda...</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Compliant</v>
+        <v>New Governance</v>
       </c>
       <c r="B451" t="str">
-        <v>متوافق</v>
+        <v>حوكمة جديدة</v>
       </c>
       <c r="C451" t="str">
-        <v>Atbilstošs</v>
+        <v>Jauna pārvaldība</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Non Compliant</v>
+        <v>Code</v>
       </c>
       <c r="B452" t="str">
-        <v>غير متوافق</v>
+        <v>الرمز</v>
       </c>
       <c r="C452" t="str">
-        <v>Neatbilstošs</v>
+        <v>Kods</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Not Applicable</v>
+        <v>Approver</v>
       </c>
       <c r="B453" t="str">
-        <v>غير قابل للتطبيق</v>
+        <v>المعتمد</v>
       </c>
       <c r="C453" t="str">
-        <v>Nav piemērojams</v>
+        <v>Apstiprinātājs</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Needs Review</v>
+        <v>Action</v>
       </c>
       <c r="B454" t="str">
-        <v>يحتاج مراجعة</v>
+        <v>الإجراء</v>
       </c>
       <c r="C454" t="str">
-        <v>Nepieciešama pārskatīšana</v>
+        <v>Darbība</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Not Uploaded</v>
+        <v>No policys found</v>
       </c>
       <c r="B455" t="str">
-        <v>لم يتم الرفع</v>
+        <v>لم يتم العثور على سياسات</v>
       </c>
       <c r="C455" t="str">
-        <v>Nav augšupielādēts</v>
+        <v>Politikas nav atrastas</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pending Approval</v>
+        <v>No standards found</v>
       </c>
       <c r="B456" t="str">
-        <v>في انتظار الموافقة</v>
+        <v>لم يتم العثور على معايير</v>
       </c>
       <c r="C456" t="str">
-        <v>Gaida apstiprinājumu</v>
+        <v>Standarti nav atrasti</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Yearly</v>
+        <v>No procedures found</v>
       </c>
       <c r="B457" t="str">
-        <v>سنوي</v>
+        <v>لم يتم العثور على إجراءات</v>
       </c>
       <c r="C457" t="str">
-        <v>Ikgadējs</v>
+        <v>Procedūras nav atrastas</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Half-yearly</v>
+        <v>Compliant</v>
       </c>
       <c r="B458" t="str">
-        <v>نصف سنوي</v>
+        <v>متوافق</v>
       </c>
       <c r="C458" t="str">
-        <v>Pusgada</v>
+        <v>Atbilstošs</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>New Governance - Step 1 of 3</v>
+        <v>Non Compliant</v>
       </c>
       <c r="B459" t="str">
-        <v>حوكمة جديدة - الخطوة 1 من 3</v>
+        <v>غير متوافق</v>
       </c>
       <c r="C459" t="str">
-        <v>Jauna pārvaldība - 1. solis no 3</v>
+        <v>Neatbilstošs</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>New Governance - Step 2 of 3</v>
+        <v>Not Applicable</v>
       </c>
       <c r="B460" t="str">
-        <v>حوكمة جديدة - الخطوة 2 من 3</v>
+        <v>غير قابل للتطبيق</v>
       </c>
       <c r="C460" t="str">
-        <v>Jauna pārvaldība - 2. solis no 3</v>
+        <v>Nav piemērojams</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>New Governance - Step 3 of 3</v>
+        <v>Needs Review</v>
       </c>
       <c r="B461" t="str">
-        <v>حوكمة جديدة - الخطوة 3 من 3</v>
+        <v>يحتاج مراجعة</v>
       </c>
       <c r="C461" t="str">
-        <v>Jauna pārvaldība - 3. solis no 3</v>
+        <v>Nepieciešama pārskatīšana</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Governance Name</v>
+        <v>Not Uploaded</v>
       </c>
       <c r="B462" t="str">
-        <v>اسم الحوكمة</v>
+        <v>لم يتم الرفع</v>
       </c>
       <c r="C462" t="str">
-        <v>Pārvaldības nosaukums</v>
+        <v>Nav augšupielādēts</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Enter governance name</v>
+        <v>Pending Approval</v>
       </c>
       <c r="B463" t="str">
-        <v>أدخل اسم الحوكمة</v>
+        <v>في انتظار الموافقة</v>
       </c>
       <c r="C463" t="str">
-        <v>Ievadiet pārvaldības nosaukumu</v>
+        <v>Gaida apstiprinājumu</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>You don't have permission to access Governance.</v>
+        <v>Yearly</v>
       </c>
       <c r="B464" t="str">
-        <v>ليس لديك صلاحية للوصول إلى الحوكمة.</v>
+        <v>سنوي</v>
       </c>
       <c r="C464" t="str">
-        <v>Jums nav atļaujas piekļūt pārvaldībai.</v>
+        <v>Ikgadējs</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Standard</v>
+        <v>Half-yearly</v>
       </c>
       <c r="B465" t="str">
-        <v>المعيار</v>
+        <v>نصف سنوي</v>
       </c>
       <c r="C465" t="str">
-        <v>Standarts</v>
+        <v>Pusgada</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Procedure</v>
+        <v>New Governance - Step 1 of 3</v>
       </c>
       <c r="B466" t="str">
-        <v>الإجراء</v>
+        <v>حوكمة جديدة - الخطوة 1 من 3</v>
       </c>
       <c r="C466" t="str">
-        <v>Procedūra</v>
+        <v>Jauna pārvaldība - 1. solis no 3</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Validated</v>
+        <v>New Governance - Step 2 of 3</v>
       </c>
       <c r="B467" t="str">
-        <v>تم التحقق</v>
+        <v>حوكمة جديدة - الخطوة 2 من 3</v>
       </c>
       <c r="C467" t="str">
-        <v>Validēts</v>
+        <v>Jauna pārvaldība - 2. solis no 3</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Need Attention</v>
+        <v>New Governance - Step 3 of 3</v>
       </c>
       <c r="B468" t="str">
-        <v>يحتاج انتباه</v>
+        <v>حوكمة جديدة - الخطوة 3 من 3</v>
       </c>
       <c r="C468" t="str">
-        <v>Nepieciešama uzmanība</v>
+        <v>Jauna pārvaldība - 3. solis no 3</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Risk ID</v>
+        <v>Governance Name</v>
       </c>
       <c r="B469" t="str">
-        <v>معرف المخاطر</v>
+        <v>اسم الحوكمة</v>
       </c>
       <c r="C469" t="str">
-        <v>Riska ID</v>
+        <v>Pārvaldības nosaukums</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Risk Name</v>
+        <v>Enter governance name</v>
       </c>
       <c r="B470" t="str">
-        <v>اسم المخاطر</v>
+        <v>أدخل اسم الحوكمة</v>
       </c>
       <c r="C470" t="str">
-        <v>Riska nosaukums</v>
+        <v>Ievadiet pārvaldības nosaukumu</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Risk Description</v>
+        <v>You don't have permission to access Governance.</v>
       </c>
       <c r="B471" t="str">
-        <v>وصف المخاطر</v>
+        <v>ليس لديك صلاحية للوصول إلى الحوكمة.</v>
       </c>
       <c r="C471" t="str">
-        <v>Riska apraksts</v>
+        <v>Jums nav atļaujas piekļūt pārvaldībai.</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Risk Category</v>
+        <v>Standard</v>
       </c>
       <c r="B472" t="str">
-        <v>فئة المخاطر</v>
+        <v>المعيار</v>
       </c>
       <c r="C472" t="str">
-        <v>Riska kategorija</v>
+        <v>Standarts</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Risk Owner</v>
+        <v>Procedure</v>
       </c>
       <c r="B473" t="str">
-        <v>مالك المخاطر</v>
+        <v>الإجراء</v>
       </c>
       <c r="C473" t="str">
-        <v>Riska īpašnieks</v>
+        <v>Procedūra</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Risk Rating</v>
+        <v>Validated</v>
       </c>
       <c r="B474" t="str">
-        <v>تصنيف المخاطر</v>
+        <v>تم التحقق</v>
       </c>
       <c r="C474" t="str">
-        <v>Riska novērtējums</v>
+        <v>Validēts</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Risk Type</v>
+        <v>Need Attention</v>
       </c>
       <c r="B475" t="str">
-        <v>نوع المخاطر</v>
+        <v>يحتاج انتباه</v>
       </c>
       <c r="C475" t="str">
-        <v>Riska tips</v>
+        <v>Nepieciešama uzmanība</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>You don't have permission to access Risk Register.</v>
+        <v>Risk ID</v>
       </c>
       <c r="B476" t="str">
-        <v>ليس لديك صلاحية للوصول إلى سجل المخاطر.</v>
+        <v>معرف المخاطر</v>
       </c>
       <c r="C476" t="str">
-        <v>Jums nav atļaujas piekļūt risku reģistram.</v>
+        <v>Riska ID</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>RiskRegister</v>
+        <v>Risk Name</v>
       </c>
       <c r="B477" t="str">
-        <v>سجل المخاطر</v>
+        <v>اسم المخاطر</v>
       </c>
       <c r="C477" t="str">
-        <v>Risku reģistrs</v>
+        <v>Riska nosaukums</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Register</v>
+        <v>Risk Description</v>
       </c>
       <c r="B478" t="str">
-        <v>السجل</v>
+        <v>وصف المخاطر</v>
       </c>
       <c r="C478" t="str">
-        <v>Reģistrs</v>
+        <v>Riska apraksts</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Total Risks</v>
+        <v>Risk Category</v>
       </c>
       <c r="B479" t="str">
-        <v>إجمالي المخاطر</v>
+        <v>فئة المخاطر</v>
       </c>
       <c r="C479" t="str">
-        <v>Kopējie riski</v>
+        <v>Riska kategorija</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Open Risks</v>
+        <v>Risk Owner</v>
       </c>
       <c r="B480" t="str">
-        <v>المخاطر المفتوحة</v>
+        <v>مالك المخاطر</v>
       </c>
       <c r="C480" t="str">
-        <v>Atvērtie riski</v>
+        <v>Riska īpašnieks</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Closed Risks</v>
+        <v>Risk Rating</v>
       </c>
       <c r="B481" t="str">
-        <v>المخاطر المغلقة</v>
+        <v>تصنيف المخاطر</v>
       </c>
       <c r="C481" t="str">
-        <v>Slēgtie riski</v>
+        <v>Riska novērtējums</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Search risks...</v>
+        <v>Risk Type</v>
       </c>
       <c r="B482" t="str">
-        <v>البحث في المخاطر...</v>
+        <v>نوع المخاطر</v>
       </c>
       <c r="C482" t="str">
-        <v>Meklēt riskus...</v>
+        <v>Riska tips</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>All Ratings</v>
+        <v>You don't have permission to access Risk Register.</v>
       </c>
       <c r="B483" t="str">
-        <v>جميع التصنيفات</v>
+        <v>ليس لديك صلاحية للوصول إلى سجل المخاطر.</v>
       </c>
       <c r="C483" t="str">
-        <v>Visi vērtējumi</v>
+        <v>Jums nav atļaujas piekļūt risku reģistram.</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Activity Log</v>
+        <v>RiskRegister</v>
       </c>
       <c r="B484" t="str">
-        <v>سجل النشاط</v>
+        <v>سجل المخاطر</v>
       </c>
       <c r="C484" t="str">
-        <v>Aktivitāšu žurnāls</v>
+        <v>Risku reģistrs</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>New Risk</v>
+        <v>Register</v>
       </c>
       <c r="B485" t="str">
-        <v>مخاطر جديدة</v>
+        <v>السجل</v>
       </c>
       <c r="C485" t="str">
-        <v>Jauns risks</v>
+        <v>Reģistrs</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Risk</v>
+        <v>Total Risks</v>
       </c>
       <c r="B486" t="str">
-        <v>المخاطر</v>
+        <v>إجمالي المخاطر</v>
       </c>
       <c r="C486" t="str">
-        <v>Risks</v>
+        <v>Kopējie riski</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Activity</v>
+        <v>Open Risks</v>
       </c>
       <c r="B487" t="str">
-        <v>النشاط</v>
+        <v>المخاطر المفتوحة</v>
       </c>
       <c r="C487" t="str">
-        <v>Aktivitāte</v>
+        <v>Atvērtie riski</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Actor</v>
+        <v>Closed Risks</v>
       </c>
       <c r="B488" t="str">
-        <v>الفاعل</v>
+        <v>المخاطر المغلقة</v>
       </c>
       <c r="C488" t="str">
-        <v>Dalībnieks</v>
+        <v>Slēgtie riski</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>activities</v>
+        <v>Search risks...</v>
       </c>
       <c r="B489" t="str">
-        <v>الأنشطة</v>
+        <v>البحث في المخاطر...</v>
       </c>
       <c r="C489" t="str">
-        <v>aktivitātes</v>
+        <v>Meklēt riskus...</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>No activity log entries found</v>
+        <v>All Ratings</v>
       </c>
       <c r="B490" t="str">
-        <v>لم يتم العثور على إدخالات في سجل النشاط</v>
+        <v>جميع التصنيفات</v>
       </c>
       <c r="C490" t="str">
-        <v>Nav atrasti aktivitāšu žurnāla ieraksti</v>
+        <v>Visi vērtējumi</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Import Risks</v>
+        <v>Activity Log</v>
       </c>
       <c r="B491" t="str">
-        <v>استيراد المخاطر</v>
+        <v>سجل النشاط</v>
       </c>
       <c r="C491" t="str">
-        <v>Importēt riskus</v>
+        <v>Aktivitāšu žurnāls</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Upload a CSV file to import risks</v>
+        <v>New Risk</v>
       </c>
       <c r="B492" t="str">
-        <v>ارفع ملف CSV لاستيراد المخاطر</v>
+        <v>مخاطر جديدة</v>
       </c>
       <c r="C492" t="str">
-        <v>Augšupielādējiet CSV failu, lai importētu riskus</v>
+        <v>Jauns risks</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Required columns:</v>
+        <v>Risk</v>
       </c>
       <c r="B493" t="str">
-        <v>الأعمدة المطلوبة:</v>
+        <v>المخاطر</v>
       </c>
       <c r="C493" t="str">
-        <v>Obligātās kolonnas:</v>
+        <v>Risks</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Risk name, Risk description, Risk category, Risk type</v>
+        <v>Activity</v>
       </c>
       <c r="B494" t="str">
-        <v>اسم المخاطر، وصف المخاطر، فئة المخاطر، نوع المخاطر</v>
+        <v>النشاط</v>
       </c>
       <c r="C494" t="str">
-        <v>Riska nosaukums, Riska apraksts, Riska kategorija, Riska tips</v>
+        <v>Aktivitāte</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click to select a file or drag and drop</v>
+        <v>Actor</v>
       </c>
       <c r="B495" t="str">
-        <v>انقر لاختيار ملف أو اسحب وأفلت</v>
+        <v>الفاعل</v>
       </c>
       <c r="C495" t="str">
-        <v>Noklikšķiniet, lai izvēlētos failu, vai velciet un nometiet</v>
+        <v>Dalībnieks</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Select File</v>
+        <v>activities</v>
       </c>
       <c r="B496" t="str">
-        <v>اختيار ملف</v>
+        <v>الأنشطة</v>
       </c>
       <c r="C496" t="str">
-        <v>Izvēlēties failu</v>
+        <v>aktivitātes</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Confirmation</v>
+        <v>No activity log entries found</v>
       </c>
       <c r="B497" t="str">
-        <v>تأكيد</v>
+        <v>لم يتم العثور على إدخالات في سجل النشاط</v>
       </c>
       <c r="C497" t="str">
-        <v>Apstiprinājums</v>
+        <v>Nav atrasti aktivitāšu žurnāla ieraksti</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Are you sure you want to delete this risk?</v>
+        <v>Import Risks</v>
       </c>
       <c r="B498" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه المخاطر؟</v>
+        <v>استيراد المخاطر</v>
       </c>
       <c r="C498" t="str">
-        <v>Vai tiešām vēlaties dzēst šo risku?</v>
+        <v>Importēt riskus</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Catastrophic</v>
+        <v>Upload a CSV file to import risks</v>
       </c>
       <c r="B499" t="str">
-        <v>كارثي</v>
+        <v>ارفع ملف CSV لاستيراد المخاطر</v>
       </c>
       <c r="C499" t="str">
-        <v>Katastrofāls</v>
+        <v>Augšupielādējiet CSV failu, lai importētu riskus</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Very high</v>
+        <v>Required columns:</v>
       </c>
       <c r="B500" t="str">
-        <v>عالي جداً</v>
+        <v>الأعمدة المطلوبة:</v>
       </c>
       <c r="C500" t="str">
-        <v>Ļoti augsts</v>
+        <v>Obligātās kolonnas:</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Very Low</v>
+        <v>Risk name, Risk description, Risk category, Risk type</v>
       </c>
       <c r="B501" t="str">
-        <v>منخفض جداً</v>
+        <v>اسم المخاطر، وصف المخاطر، فئة المخاطر، نوع المخاطر</v>
       </c>
       <c r="C501" t="str">
-        <v>Ļoti zems</v>
+        <v>Riska nosaukums, Riska apraksts, Riska kategorija, Riska tips</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Low Risk</v>
+        <v>Click to select a file or drag and drop</v>
       </c>
       <c r="B502" t="str">
-        <v>مخاطر منخفضة</v>
+        <v>انقر لاختيار ملف أو اسحب وأفلت</v>
       </c>
       <c r="C502" t="str">
-        <v>Zems risks</v>
+        <v>Noklikšķiniet, lai izvēlētos failu, vai velciet un nometiet</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Medium Risk</v>
+        <v>Select File</v>
       </c>
       <c r="B503" t="str">
-        <v>مخاطر متوسطة</v>
+        <v>اختيار ملف</v>
       </c>
       <c r="C503" t="str">
-        <v>Vidējs risks</v>
+        <v>Izvēlēties failu</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>High Risk</v>
+        <v>Confirmation</v>
       </c>
       <c r="B504" t="str">
-        <v>مخاطر عالية</v>
+        <v>تأكيد</v>
       </c>
       <c r="C504" t="str">
-        <v>Augsts risks</v>
+        <v>Apstiprinājums</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Critical Risk</v>
+        <v>Are you sure you want to delete this risk?</v>
       </c>
       <c r="B505" t="str">
-        <v>مخاطر حرجة</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه المخاطر؟</v>
       </c>
       <c r="C505" t="str">
-        <v>Kritisks risks</v>
+        <v>Vai tiešām vēlaties dzēst šo risku?</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Failed to fetch fieldwork data</v>
+        <v>Catastrophic</v>
       </c>
       <c r="B506" t="str">
-        <v>فشل في جلب بيانات العمل الميداني</v>
+        <v>كارثي</v>
       </c>
       <c r="C506" t="str">
-        <v>Neizdevās ielādēt lauka darba datus</v>
+        <v>Katastrofāls</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Framework Created Successfully</v>
+        <v>Very high</v>
       </c>
       <c r="B507" t="str">
-        <v>تم إنشاء الإطار بنجاح</v>
+        <v>عالي جداً</v>
       </c>
       <c r="C507" t="str">
-        <v>Ietvars veiksmīgi izveidots</v>
+        <v>Ļoti augsts</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Framework</v>
+        <v>Very Low</v>
       </c>
       <c r="B508" t="str">
-        <v>الإطار</v>
+        <v>منخفض جداً</v>
       </c>
       <c r="C508" t="str">
-        <v>Ietvars</v>
+        <v>Ļoti zems</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Unknown</v>
+        <v>Low Risk</v>
       </c>
       <c r="B509" t="str">
-        <v>غير معروف</v>
+        <v>مخاطر منخفضة</v>
       </c>
       <c r="C509" t="str">
-        <v>Nezināms</v>
+        <v>Zems risks</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>is ready to use!</v>
+        <v>Medium Risk</v>
       </c>
       <c r="B510" t="str">
-        <v>جاهز للاستخدام!</v>
+        <v>مخاطر متوسطة</v>
       </c>
       <c r="C510" t="str">
-        <v>ir gatavs lietošanai!</v>
+        <v>Vidējs risks</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Framework was created but couldn't retrieve result. Check dashboard.</v>
+        <v>High Risk</v>
       </c>
       <c r="B511" t="str">
-        <v>تم إنشاء الإطار ولكن لم يتم استرجاع النتيجة. تحقق من لوحة التحكم.</v>
+        <v>مخاطر عالية</v>
       </c>
       <c r="C511" t="str">
-        <v>Ietvars izveidots, bet neizdevās iegūt rezultātu. Pārbaudiet vadības paneli.</v>
+        <v>Augsts risks</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Framework Generation Failed</v>
+        <v>Critical Risk</v>
       </c>
       <c r="B512" t="str">
-        <v>فشل في إنشاء الإطار</v>
+        <v>مخاطر حرجة</v>
       </c>
       <c r="C512" t="str">
-        <v>Ietvara izveide neizdevās</v>
+        <v>Kritisks risks</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Validation Error</v>
+        <v>Failed to fetch fieldwork data</v>
       </c>
       <c r="B513" t="str">
-        <v>خطأ في التحقق</v>
+        <v>فشل في جلب بيانات العمل الميداني</v>
       </c>
       <c r="C513" t="str">
-        <v>Validācijas kļūda</v>
+        <v>Neizdevās ielādēt lauka darba datus</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Framework name is required</v>
+        <v>Framework Created Successfully</v>
       </c>
       <c r="B514" t="str">
-        <v>اسم الإطار مطلوب</v>
+        <v>تم إنشاء الإطار بنجاح</v>
       </c>
       <c r="C514" t="str">
-        <v>Ietvara nosaukums ir obligāts</v>
+        <v>Ietvars veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Framework Already Exists</v>
+        <v>Framework</v>
       </c>
       <c r="B515" t="str">
-        <v>الإطار موجود بالفعل</v>
+        <v>الإطار</v>
       </c>
       <c r="C515" t="str">
-        <v>Ietvars jau pastāv</v>
+        <v>Ietvars</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>A framework named</v>
+        <v>Unknown</v>
       </c>
       <c r="B516" t="str">
-        <v>إطار باسم</v>
+        <v>غير معروف</v>
       </c>
       <c r="C516" t="str">
-        <v>Ietvars ar nosaukumu</v>
+        <v>Nezināms</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>already exists.</v>
+        <v>is ready to use!</v>
       </c>
       <c r="B517" t="str">
-        <v>موجود بالفعل.</v>
+        <v>جاهز للاستخدام!</v>
       </c>
       <c r="C517" t="str">
-        <v>jau pastāv.</v>
+        <v>ir gatavs lietošanai!</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Failed to create framework</v>
+        <v>Framework was created but couldn't retrieve result. Check dashboard.</v>
       </c>
       <c r="B518" t="str">
-        <v>فشل في إنشاء الإطار</v>
+        <v>تم إنشاء الإطار ولكن لم يتم استرجاع النتيجة. تحقق من لوحة التحكم.</v>
       </c>
       <c r="C518" t="str">
-        <v>Neizdevās izveidot ietvaru</v>
+        <v>Ietvars izveidots, bet neizdevās iegūt rezultātu. Pārbaudiet vadības paneli.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Framework Generation Started</v>
+        <v>Framework Generation Failed</v>
       </c>
       <c r="B519" t="str">
-        <v>بدأ إنشاء الإطار</v>
+        <v>فشل في إنشاء الإطار</v>
       </c>
       <c r="C519" t="str">
-        <v>Ietvara izveide sākta</v>
+        <v>Ietvara izveide neizdevās</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Polling Stopped</v>
+        <v>Validation Error</v>
       </c>
       <c r="B520" t="str">
-        <v>توقف الاستطلاع</v>
+        <v>خطأ في التحقق</v>
       </c>
       <c r="C520" t="str">
-        <v>Aptauja apturēta</v>
+        <v>Validācijas kļūda</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You can check the status manually from the dashboard.</v>
+        <v>Framework name is required</v>
       </c>
       <c r="B521" t="str">
-        <v>يمكنك التحقق من الحالة يدوياً من لوحة التحكم.</v>
+        <v>اسم الإطار مطلوب</v>
       </c>
       <c r="C521" t="str">
-        <v>Jūs varat manuāli pārbaudīt statusu vadības panelī.</v>
+        <v>Ietvara nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Regulation</v>
+        <v>Framework Already Exists</v>
       </c>
       <c r="B522" t="str">
-        <v>اللائحة</v>
+        <v>الإطار موجود بالفعل</v>
       </c>
       <c r="C522" t="str">
-        <v>Regula</v>
+        <v>Ietvars jau pastāv</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Additional details about the framework...</v>
+        <v>A framework named</v>
       </c>
       <c r="B523" t="str">
-        <v>تفاصيل إضافية حول الإطار...</v>
+        <v>إطار باسم</v>
       </c>
       <c r="C523" t="str">
-        <v>Papildu informācija par ietvaru...</v>
+        <v>Ietvars ar nosaukumu</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Generate Framework</v>
+        <v>already exists.</v>
       </c>
       <c r="B524" t="str">
-        <v>إنشاء الإطار</v>
+        <v>موجود بالفعل.</v>
       </c>
       <c r="C524" t="str">
-        <v>Ģenerēt ietvaru</v>
+        <v>jau pastāv.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>QUEUED</v>
+        <v>Failed to create framework</v>
       </c>
       <c r="B525" t="str">
-        <v>في قائمة الانتظار</v>
+        <v>فشل في إنشاء الإطار</v>
       </c>
       <c r="C525" t="str">
-        <v>RINDĀ</v>
+        <v>Neizdevās izveidot ietvaru</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>PROCESSING</v>
+        <v>Framework Generation Started</v>
       </c>
       <c r="B526" t="str">
-        <v>قيد المعالجة</v>
+        <v>بدأ إنشاء الإطار</v>
       </c>
       <c r="C526" t="str">
-        <v>APSTRĀDĀ</v>
+        <v>Ietvara izveide sākta</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>COMPLETED</v>
+        <v>Polling Stopped</v>
       </c>
       <c r="B527" t="str">
-        <v>مكتمل</v>
+        <v>توقف الاستطلاع</v>
       </c>
       <c r="C527" t="str">
-        <v>PABEIGTS</v>
+        <v>Aptauja apturēta</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>FAILED</v>
+        <v>You can check the status manually from the dashboard.</v>
       </c>
       <c r="B528" t="str">
-        <v>فشل</v>
+        <v>يمكنك التحقق من الحالة يدوياً من لوحة التحكم.</v>
       </c>
       <c r="C528" t="str">
-        <v>NEIZDEVĀS</v>
+        <v>Jūs varat manuāli pārbaudīt statusu vadības panelī.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>PENDING_RESULT</v>
+        <v>Regulation</v>
       </c>
       <c r="B529" t="str">
-        <v>في انتظار النتيجة</v>
+        <v>اللائحة</v>
       </c>
       <c r="C529" t="str">
-        <v>GAIDA_REZULTĀTU</v>
+        <v>Regula</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Overall Compliance Status</v>
+        <v>Additional details about the framework...</v>
       </c>
       <c r="B530" t="str">
-        <v>حالة الامتثال الشاملة</v>
+        <v>تفاصيل إضافية حول الإطار...</v>
       </c>
       <c r="C530" t="str">
-        <v>Kopējais atbilstības statuss</v>
+        <v>Papildu informācija par ietvaru...</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Overall:</v>
+        <v>Generate Framework</v>
       </c>
       <c r="B531" t="str">
-        <v>الإجمالي:</v>
+        <v>إنشاء الإطار</v>
       </c>
       <c r="C531" t="str">
-        <v>Kopā:</v>
+        <v>Ģenerēt ietvaru</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Loading dashboard...</v>
+        <v>QUEUED</v>
       </c>
       <c r="B532" t="str">
-        <v>جاري تحميل لوحة التحكم...</v>
+        <v>في قائمة الانتظار</v>
       </c>
       <c r="C532" t="str">
-        <v>Ielādē vadības paneli...</v>
+        <v>RINDĀ</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Risks</v>
+        <v>PROCESSING</v>
       </c>
       <c r="B533" t="str">
-        <v>المخاطر</v>
+        <v>قيد المعالجة</v>
       </c>
       <c r="C533" t="str">
-        <v>Riski</v>
+        <v>APSTRĀDĀ</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Exceptions</v>
+        <v>COMPLETED</v>
       </c>
       <c r="B534" t="str">
-        <v>الاستثناءات</v>
+        <v>مكتمل</v>
       </c>
       <c r="C534" t="str">
-        <v>Izņēmumi</v>
+        <v>PABEIGTS</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Risk Assessment Overview</v>
+        <v>FAILED</v>
       </c>
       <c r="B535" t="str">
-        <v>نظرة عامة على تقييم المخاطر</v>
+        <v>فشل</v>
       </c>
       <c r="C535" t="str">
-        <v>Risku novērtējuma pārskats</v>
+        <v>NEIZDEVĀS</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Closed</v>
+        <v>PENDING_RESULT</v>
       </c>
       <c r="B536" t="str">
-        <v>مغلق</v>
+        <v>في انتظار النتيجة</v>
       </c>
       <c r="C536" t="str">
-        <v>Slēgts</v>
+        <v>GAIDA_REZULTĀTU</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Total</v>
+        <v>Overall Compliance Status</v>
       </c>
       <c r="B537" t="str">
-        <v>الإجمالي</v>
+        <v>حالة الامتثال الشاملة</v>
       </c>
       <c r="C537" t="str">
-        <v>Kopā</v>
+        <v>Kopējais atbilstības statuss</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Issue By Category</v>
+        <v>Overall:</v>
       </c>
       <c r="B538" t="str">
-        <v>القضايا حسب الفئة</v>
+        <v>الإجمالي:</v>
       </c>
       <c r="C538" t="str">
-        <v>Problēmas pēc kategorijas</v>
+        <v>Kopā:</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Issue By Department</v>
+        <v>Loading dashboard...</v>
       </c>
       <c r="B539" t="str">
-        <v>القضايا حسب القسم</v>
+        <v>جاري تحميل لوحة التحكم...</v>
       </c>
       <c r="C539" t="str">
-        <v>Problēmas pēc nodaļas</v>
+        <v>Ielādē vadības paneli...</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Issue By Domain</v>
+        <v>Risks</v>
       </c>
       <c r="B540" t="str">
-        <v>القضايا حسب المجال</v>
+        <v>المخاطر</v>
       </c>
       <c r="C540" t="str">
-        <v>Problēmas pēc domēna</v>
+        <v>Riski</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>items</v>
+        <v>Exceptions</v>
       </c>
       <c r="B541" t="str">
-        <v>عناصر</v>
+        <v>الاستثناءات</v>
       </c>
       <c r="C541" t="str">
-        <v>vienumi</v>
+        <v>Izņēmumi</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Evidence KPI</v>
+        <v>Risk Assessment Overview</v>
       </c>
       <c r="B542" t="str">
-        <v>مؤشرات أداء الأدلة</v>
+        <v>نظرة عامة على تقييم المخاطر</v>
       </c>
       <c r="C542" t="str">
-        <v>Pierādījumu KPI</v>
+        <v>Risku novērtējuma pārskats</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Process KPI</v>
+        <v>Closed</v>
       </c>
       <c r="B543" t="str">
-        <v>مؤشرات أداء العمليات</v>
+        <v>مغلق</v>
       </c>
       <c r="C543" t="str">
-        <v>Procesu KPI</v>
+        <v>Slēgts</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Achieved</v>
+        <v>Total</v>
       </c>
       <c r="B544" t="str">
-        <v>محقق</v>
+        <v>الإجمالي</v>
       </c>
       <c r="C544" t="str">
-        <v>Sasniegts</v>
+        <v>Kopā</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Scheduled</v>
+        <v>Issue By Category</v>
       </c>
       <c r="B545" t="str">
-        <v>مجدول</v>
+        <v>القضايا حسب الفئة</v>
       </c>
       <c r="C545" t="str">
-        <v>Ieplānots</v>
+        <v>Problēmas pēc kategorijas</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Missed</v>
+        <v>Issue By Department</v>
       </c>
       <c r="B546" t="str">
-        <v>فائت</v>
+        <v>القضايا حسب القسم</v>
       </c>
       <c r="C546" t="str">
-        <v>Nokavēts</v>
+        <v>Problēmas pēc nodaļas</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Overdue</v>
+        <v>Issue By Domain</v>
       </c>
       <c r="B547" t="str">
-        <v>متأخر</v>
+        <v>القضايا حسب المجال</v>
       </c>
       <c r="C547" t="str">
-        <v>Nokavēts</v>
+        <v>Problēmas pēc domēna</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Governance Status</v>
+        <v>items</v>
       </c>
       <c r="B548" t="str">
-        <v>حالة الحوكمة</v>
+        <v>عناصر</v>
       </c>
       <c r="C548" t="str">
-        <v>Pārvaldības statuss</v>
+        <v>vienumi</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Exception Status</v>
+        <v>Evidence KPI</v>
       </c>
       <c r="B549" t="str">
-        <v>حالة الاستثناءات</v>
+        <v>مؤشرات أداء الأدلة</v>
       </c>
       <c r="C549" t="str">
-        <v>Izņēmumu statuss</v>
+        <v>Pierādījumu KPI</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Authorized</v>
+        <v>Process KPI</v>
       </c>
       <c r="B550" t="str">
-        <v>مصرح</v>
+        <v>مؤشرات أداء العمليات</v>
       </c>
       <c r="C550" t="str">
-        <v>Autorizēts</v>
+        <v>Procesu KPI</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Showing</v>
+        <v>Achieved</v>
       </c>
       <c r="B551" t="str">
-        <v>عرض</v>
+        <v>محقق</v>
       </c>
       <c r="C551" t="str">
-        <v>Rāda</v>
+        <v>Sasniegts</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>to</v>
+        <v>Scheduled</v>
       </c>
       <c r="B552" t="str">
-        <v>إلى</v>
+        <v>مجدول</v>
       </c>
       <c r="C552" t="str">
-        <v>līdz</v>
+        <v>Ieplānots</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>of</v>
+        <v>Missed</v>
       </c>
       <c r="B553" t="str">
-        <v>من</v>
+        <v>فائت</v>
       </c>
       <c r="C553" t="str">
-        <v>no</v>
+        <v>Nokavēts</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>entries</v>
+        <v>Overdue</v>
       </c>
       <c r="B554" t="str">
-        <v>إدخالات</v>
+        <v>متأخر</v>
       </c>
       <c r="C554" t="str">
-        <v>ierakstiem</v>
+        <v>Nokavēts</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>rows per page</v>
+        <v>Governance Status</v>
       </c>
       <c r="B555" t="str">
-        <v>صفوف في الصفحة</v>
+        <v>حالة الحوكمة</v>
       </c>
       <c r="C555" t="str">
-        <v>rindas lapā</v>
+        <v>Pārvaldības statuss</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Page</v>
+        <v>Exception Status</v>
       </c>
       <c r="B556" t="str">
-        <v>صفحة</v>
+        <v>حالة الاستثناءات</v>
       </c>
       <c r="C556" t="str">
-        <v>Lapa</v>
+        <v>Izņēmumu statuss</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>First</v>
+        <v>Authorized</v>
       </c>
       <c r="B557" t="str">
-        <v>الأول</v>
+        <v>مصرح</v>
       </c>
       <c r="C557" t="str">
-        <v>Pirmā</v>
+        <v>Autorizēts</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Last</v>
+        <v>Showing</v>
       </c>
       <c r="B558" t="str">
-        <v>الأخير</v>
+        <v>عرض</v>
       </c>
       <c r="C558" t="str">
-        <v>Pēdējā</v>
+        <v>Rāda</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Go to page</v>
+        <v>to</v>
       </c>
       <c r="B559" t="str">
-        <v>انتقل إلى الصفحة</v>
+        <v>إلى</v>
       </c>
       <c r="C559" t="str">
-        <v>Doties uz lapu</v>
+        <v>līdz</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Search...</v>
+        <v>of</v>
       </c>
       <c r="B560" t="str">
-        <v>بحث...</v>
+        <v>من</v>
       </c>
       <c r="C560" t="str">
-        <v>Meklēt...</v>
+        <v>no</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No data</v>
+        <v>entries</v>
       </c>
       <c r="B561" t="str">
-        <v>لا توجد بيانات</v>
+        <v>إدخالات</v>
       </c>
       <c r="C561" t="str">
-        <v>Nav datu</v>
+        <v>ierakstiem</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Search By Name</v>
+        <v>rows per page</v>
       </c>
       <c r="B562" t="str">
-        <v>البحث بالاسم</v>
+        <v>صفوف في الصفحة</v>
       </c>
       <c r="C562" t="str">
-        <v>Meklēt pēc nosaukuma</v>
+        <v>rindas lapā</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Search By Control Code , Name</v>
+        <v>Page</v>
       </c>
       <c r="B563" t="str">
-        <v>البحث برمز الضابطة أو الاسم</v>
+        <v>صفحة</v>
       </c>
       <c r="C563" t="str">
-        <v>Meklēt pēc kontroles koda, nosaukuma</v>
+        <v>Lapa</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>This field is required</v>
+        <v>First</v>
       </c>
       <c r="B564" t="str">
-        <v>هذا الحقل مطلوب</v>
+        <v>الأول</v>
       </c>
       <c r="C564" t="str">
-        <v>Šis lauks ir obligāts</v>
+        <v>Pirmā</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Invalid email format</v>
+        <v>Last</v>
       </c>
       <c r="B565" t="str">
-        <v>تنسيق البريد الإلكتروني غير صالح</v>
+        <v>الأخير</v>
       </c>
       <c r="C565" t="str">
-        <v>Nederīgs e-pasta formāts</v>
+        <v>Pēdējā</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Password must be at least 8 characters</v>
+        <v>Go to page</v>
       </c>
       <c r="B566" t="str">
-        <v>يجب أن تكون كلمة المرور 8 أحرف على الأقل</v>
+        <v>انتقل إلى الصفحة</v>
       </c>
       <c r="C566" t="str">
-        <v>Parolei jābūt vismaz 8 rakstzīmēm</v>
+        <v>Doties uz lapu</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Passwords do not match</v>
+        <v>Search...</v>
       </c>
       <c r="B567" t="str">
-        <v>كلمات المرور غير متطابقة</v>
+        <v>بحث...</v>
       </c>
       <c r="C567" t="str">
-        <v>Paroles nesakrīt</v>
+        <v>Meklēt...</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Please enter a valid value</v>
+        <v>No data</v>
       </c>
       <c r="B568" t="str">
-        <v>يرجى إدخال قيمة صالحة</v>
+        <v>لا توجد بيانات</v>
       </c>
       <c r="C568" t="str">
-        <v>Lūdzu, ievadiet derīgu vērtību</v>
+        <v>Nav datu</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Maximum length exceeded</v>
+        <v>Search By Name</v>
       </c>
       <c r="B569" t="str">
-        <v>تم تجاوز الحد الأقصى للطول</v>
+        <v>البحث بالاسم</v>
       </c>
       <c r="C569" t="str">
-        <v>Pārsniegts maksimālais garums</v>
+        <v>Meklēt pēc nosaukuma</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Minimum length not met</v>
+        <v>Search By Control Code , Name</v>
       </c>
       <c r="B570" t="str">
-        <v>لم يتم تحقيق الحد الأدنى للطول</v>
+        <v>البحث برمز الضابطة أو الاسم</v>
       </c>
       <c r="C570" t="str">
-        <v>Nav sasniegts minimālais garums</v>
+        <v>Meklēt pēc kontroles koda, nosaukuma</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>An error occurred</v>
+        <v>This field is required</v>
       </c>
       <c r="B571" t="str">
-        <v>حدث خطأ</v>
+        <v>هذا الحقل مطلوب</v>
       </c>
       <c r="C571" t="str">
-        <v>Radās kļūda</v>
+        <v>Šis lauks ir obligāts</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Not found</v>
+        <v>Invalid email format</v>
       </c>
       <c r="B572" t="str">
-        <v>غير موجود</v>
+        <v>تنسيق البريد الإلكتروني غير صالح</v>
       </c>
       <c r="C572" t="str">
-        <v>Nav atrasts</v>
+        <v>Nederīgs e-pasta formāts</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Unauthorized</v>
+        <v>Password must be at least 8 characters</v>
       </c>
       <c r="B573" t="str">
-        <v>غير مصرح</v>
+        <v>يجب أن تكون كلمة المرور 8 أحرف على الأقل</v>
       </c>
       <c r="C573" t="str">
-        <v>Nav autorizēts</v>
+        <v>Parolei jābūt vismaz 8 rakstzīmēm</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Forbidden</v>
+        <v>Passwords do not match</v>
       </c>
       <c r="B574" t="str">
-        <v>محظور</v>
+        <v>كلمات المرور غير متطابقة</v>
       </c>
       <c r="C574" t="str">
-        <v>Aizliegts</v>
+        <v>Paroles nesakrīt</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Network error</v>
+        <v>Please enter a valid value</v>
       </c>
       <c r="B575" t="str">
-        <v>خطأ في الشبكة</v>
+        <v>يرجى إدخال قيمة صالحة</v>
       </c>
       <c r="C575" t="str">
-        <v>Tīkla kļūda</v>
+        <v>Lūdzu, ievadiet derīgu vērtību</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Server error</v>
+        <v>Maximum length exceeded</v>
       </c>
       <c r="B576" t="str">
-        <v>خطأ في الخادم</v>
+        <v>تم تجاوز الحد الأقصى للطول</v>
       </c>
       <c r="C576" t="str">
-        <v>Servera kļūda</v>
+        <v>Pārsniegts maksimālais garums</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Session expired</v>
+        <v>Minimum length not met</v>
       </c>
       <c r="B577" t="str">
-        <v>انتهت صلاحية الجلسة</v>
+        <v>لم يتم تحقيق الحد الأدنى للطول</v>
       </c>
       <c r="C577" t="str">
-        <v>Sesija ir beigusies</v>
+        <v>Nav sasniegts minimālais garums</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Please login again</v>
+        <v>An error occurred</v>
       </c>
       <c r="B578" t="str">
-        <v>يرجى تسجيل الدخول مرة أخرى</v>
+        <v>حدث خطأ</v>
       </c>
       <c r="C578" t="str">
-        <v>Lūdzu, piesakieties vēlreiz</v>
+        <v>Radās kļūda</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Saved successfully</v>
+        <v>Not found</v>
       </c>
       <c r="B579" t="str">
-        <v>تم الحفظ بنجاح</v>
+        <v>غير موجود</v>
       </c>
       <c r="C579" t="str">
-        <v>Veiksmīgi saglabāts</v>
+        <v>Nav atrasts</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Deleted successfully</v>
+        <v>Unauthorized</v>
       </c>
       <c r="B580" t="str">
-        <v>تم الحذف بنجاح</v>
+        <v>غير مصرح</v>
       </c>
       <c r="C580" t="str">
-        <v>Veiksmīgi dzēsts</v>
+        <v>Nav autorizēts</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Updated successfully</v>
+        <v>Forbidden</v>
       </c>
       <c r="B581" t="str">
-        <v>تم التحديث بنجاح</v>
+        <v>محظور</v>
       </c>
       <c r="C581" t="str">
-        <v>Veiksmīgi atjaunināts</v>
+        <v>Aizliegts</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Created successfully</v>
+        <v>Network error</v>
       </c>
       <c r="B582" t="str">
-        <v>تم الإنشاء بنجاح</v>
+        <v>خطأ في الشبكة</v>
       </c>
       <c r="C582" t="str">
-        <v>Veiksmīgi izveidots</v>
+        <v>Tīkla kļūda</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Operation completed</v>
+        <v>Server error</v>
       </c>
       <c r="B583" t="str">
-        <v>تمت العملية</v>
+        <v>خطأ في الخادم</v>
       </c>
       <c r="C583" t="str">
-        <v>Darbība pabeigta</v>
+        <v>Servera kļūda</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Today</v>
+        <v>Session expired</v>
       </c>
       <c r="B584" t="str">
-        <v>اليوم</v>
+        <v>انتهت صلاحية الجلسة</v>
       </c>
       <c r="C584" t="str">
-        <v>Šodien</v>
+        <v>Sesija ir beigusies</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Tomorrow</v>
+        <v>Please login again</v>
       </c>
       <c r="B585" t="str">
-        <v>غداً</v>
+        <v>يرجى تسجيل الدخول مرة أخرى</v>
       </c>
       <c r="C585" t="str">
-        <v>Rīt</v>
+        <v>Lūdzu, piesakieties vēlreiz</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Select date</v>
+        <v>Saved successfully</v>
       </c>
       <c r="B586" t="str">
-        <v>اختر التاريخ</v>
+        <v>تم الحفظ بنجاح</v>
       </c>
       <c r="C586" t="str">
-        <v>Izvēlieties datumu</v>
+        <v>Veiksmīgi saglabāts</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Select time</v>
+        <v>Deleted successfully</v>
       </c>
       <c r="B587" t="str">
-        <v>اختر الوقت</v>
+        <v>تم الحذف بنجاح</v>
       </c>
       <c r="C587" t="str">
-        <v>Izvēlieties laiku</v>
+        <v>Veiksmīgi dzēsts</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>From</v>
+        <v>Updated successfully</v>
       </c>
       <c r="B588" t="str">
-        <v>من</v>
+        <v>تم التحديث بنجاح</v>
       </c>
       <c r="C588" t="str">
-        <v>No</v>
+        <v>Veiksmīgi atjaunināts</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>To</v>
+        <v>Created successfully</v>
       </c>
       <c r="B589" t="str">
-        <v>إلى</v>
+        <v>تم الإنشاء بنجاح</v>
       </c>
       <c r="C589" t="str">
-        <v>Līdz</v>
+        <v>Veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Start Date</v>
+        <v>Operation completed</v>
       </c>
       <c r="B590" t="str">
-        <v>تاريخ البداية</v>
+        <v>تمت العملية</v>
       </c>
       <c r="C590" t="str">
-        <v>Sākuma datums</v>
+        <v>Darbība pabeigta</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>End Date</v>
+        <v>Today</v>
       </c>
       <c r="B591" t="str">
-        <v>تاريخ النهاية</v>
+        <v>اليوم</v>
       </c>
       <c r="C591" t="str">
-        <v>Beigu datums</v>
+        <v>Šodien</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Select file</v>
+        <v>Tomorrow</v>
       </c>
       <c r="B592" t="str">
-        <v>اختر ملف</v>
+        <v>غداً</v>
       </c>
       <c r="C592" t="str">
-        <v>Izvēlieties failu</v>
+        <v>Rīt</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Select files</v>
+        <v>Select date</v>
       </c>
       <c r="B593" t="str">
-        <v>اختر ملفات</v>
+        <v>اختر التاريخ</v>
       </c>
       <c r="C593" t="str">
-        <v>Izvēlieties failus</v>
+        <v>Izvēlieties datumu</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Drop files here</v>
+        <v>Select time</v>
       </c>
       <c r="B594" t="str">
-        <v>أسقط الملفات هنا</v>
+        <v>اختر الوقت</v>
       </c>
       <c r="C594" t="str">
-        <v>Nometiet failus šeit</v>
+        <v>Izvēlieties laiku</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>or click to select</v>
+        <v>From</v>
       </c>
       <c r="B595" t="str">
-        <v>أو انقر للاختيار</v>
+        <v>من</v>
       </c>
       <c r="C595" t="str">
-        <v>vai noklikšķiniet, lai izvēlētos</v>
+        <v>No</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>File uploaded successfully</v>
+        <v>To</v>
       </c>
       <c r="B596" t="str">
-        <v>تم رفع الملف بنجاح</v>
+        <v>إلى</v>
       </c>
       <c r="C596" t="str">
-        <v>Fails veiksmīgi augšupielādēts</v>
+        <v>Līdz</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Failed to upload file</v>
+        <v>Start Date</v>
       </c>
       <c r="B597" t="str">
-        <v>فشل في رفع الملف</v>
+        <v>تاريخ البداية</v>
       </c>
       <c r="C597" t="str">
-        <v>Neizdevās augšupielādēt failu</v>
+        <v>Sākuma datums</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>File size too large</v>
+        <v>End Date</v>
       </c>
       <c r="B598" t="str">
-        <v>حجم الملف كبير جداً</v>
+        <v>تاريخ النهاية</v>
       </c>
       <c r="C598" t="str">
-        <v>Faila izmērs ir pārāk liels</v>
+        <v>Beigu datums</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid file type</v>
+        <v>Select file</v>
       </c>
       <c r="B599" t="str">
-        <v>نوع الملف غير صالح</v>
+        <v>اختر ملف</v>
       </c>
       <c r="C599" t="str">
-        <v>Nederīgs faila tips</v>
+        <v>Izvēlieties failu</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Edit Issue</v>
+        <v>Select files</v>
       </c>
       <c r="B600" t="str">
-        <v>تعديل القضية</v>
+        <v>اختر ملفات</v>
       </c>
       <c r="C600" t="str">
-        <v>Rediģēt problēmu</v>
+        <v>Izvēlieties failus</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Enter issue title</v>
+        <v>Drop files here</v>
       </c>
       <c r="B601" t="str">
-        <v>أدخل عنوان القضية</v>
+        <v>أسقط الملفات هنا</v>
       </c>
       <c r="C601" t="str">
-        <v>Ievadiet problēmas nosaukumu</v>
+        <v>Nometiet failus šeit</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Select domain</v>
+        <v>or click to select</v>
       </c>
       <c r="B602" t="str">
-        <v>اختر المجال</v>
+        <v>أو انقر للاختيار</v>
       </c>
       <c r="C602" t="str">
-        <v>Izvēlieties domēnu</v>
+        <v>vai noklikšķiniet, lai izvēlētos</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Issue Owner</v>
+        <v>File uploaded successfully</v>
       </c>
       <c r="B603" t="str">
-        <v>مالك القضية</v>
+        <v>تم رفع الملف بنجاح</v>
       </c>
       <c r="C603" t="str">
-        <v>Problēmas īpašnieks</v>
+        <v>Fails veiksmīgi augšupielādēts</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Select owner</v>
+        <v>Failed to upload file</v>
       </c>
       <c r="B604" t="str">
-        <v>اختر المالك</v>
+        <v>فشل في رفع الملف</v>
       </c>
       <c r="C604" t="str">
-        <v>Izvēlieties īpašnieku</v>
+        <v>Neizdevās augšupielādēt failu</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Select department first</v>
+        <v>File size too large</v>
       </c>
       <c r="B605" t="str">
-        <v>اختر القسم أولاً</v>
+        <v>حجم الملف كبير جداً</v>
       </c>
       <c r="C605" t="str">
-        <v>Vispirms izvēlieties nodaļu</v>
+        <v>Faila izmērs ir pārāk liels</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Select Sub Category first</v>
+        <v>Invalid file type</v>
       </c>
       <c r="B606" t="str">
-        <v>اختر الفئة الفرعية أولاً</v>
+        <v>نوع الملف غير صالح</v>
       </c>
       <c r="C606" t="str">
-        <v>Vispirms izvēlieties apakškategoriju</v>
+        <v>Nederīgs faila tips</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Select type</v>
+        <v>Edit Issue</v>
       </c>
       <c r="B607" t="str">
-        <v>اختر النوع</v>
+        <v>تعديل القضية</v>
       </c>
       <c r="C607" t="str">
-        <v>Izvēlieties tipu</v>
+        <v>Rediģēt problēmu</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Enter issue description</v>
+        <v>Enter issue title</v>
       </c>
       <c r="B608" t="str">
-        <v>أدخل وصف القضية</v>
+        <v>أدخل عنوان القضية</v>
       </c>
       <c r="C608" t="str">
-        <v>Ievadiet problēmas aprakstu</v>
+        <v>Ievadiet problēmas nosaukumu</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>New Stakeholder</v>
+        <v>Select domain</v>
       </c>
       <c r="B609" t="str">
-        <v>صاحب مصلحة جديد</v>
+        <v>اختر المجال</v>
       </c>
       <c r="C609" t="str">
-        <v>Jauna ieinteresētā puse</v>
+        <v>Izvēlieties domēnu</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Edit Stakeholder</v>
+        <v>Issue Owner</v>
       </c>
       <c r="B610" t="str">
-        <v>تعديل صاحب المصلحة</v>
+        <v>مالك القضية</v>
       </c>
       <c r="C610" t="str">
-        <v>Rediģēt ieinteresēto pusi</v>
+        <v>Problēmas īpašnieks</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Search stakeholders...</v>
+        <v>Select owner</v>
       </c>
       <c r="B611" t="str">
-        <v>البحث في أصحاب المصلحة...</v>
+        <v>اختر المالك</v>
       </c>
       <c r="C611" t="str">
-        <v>Meklēt ieinteresētās puses...</v>
+        <v>Izvēlieties īpašnieku</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Search issues...</v>
+        <v>Select department first</v>
       </c>
       <c r="B612" t="str">
-        <v>البحث في القضايا...</v>
+        <v>اختر القسم أولاً</v>
       </c>
       <c r="C612" t="str">
-        <v>Meklēt problēmas...</v>
+        <v>Vispirms izvēlieties nodaļu</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>All Types</v>
+        <v>Select Sub Category first</v>
       </c>
       <c r="B613" t="str">
-        <v>جميع الأنواع</v>
+        <v>اختر الفئة الفرعية أولاً</v>
       </c>
       <c r="C613" t="str">
-        <v>Visi tipi</v>
+        <v>Vispirms izvēlieties apakškategoriju</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>All Status</v>
+        <v>Select type</v>
       </c>
       <c r="B614" t="str">
-        <v>جميع الحالات</v>
+        <v>اختر النوع</v>
       </c>
       <c r="C614" t="str">
-        <v>Visi statusi</v>
+        <v>Izvēlieties tipu</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>All Categories</v>
+        <v>Enter issue description</v>
       </c>
       <c r="B615" t="str">
-        <v>جميع الفئات</v>
+        <v>أدخل وصف القضية</v>
       </c>
       <c r="C615" t="str">
-        <v>Visas kategorijas</v>
+        <v>Ievadiet problēmas aprakstu</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>All Domains</v>
+        <v>New Stakeholder</v>
       </c>
       <c r="B616" t="str">
-        <v>جميع المجالات</v>
+        <v>صاحب مصلحة جديد</v>
       </c>
       <c r="C616" t="str">
-        <v>Visi domēni</v>
+        <v>Jauna ieinteresētā puse</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>No Issues Found</v>
+        <v>Edit Stakeholder</v>
       </c>
       <c r="B617" t="str">
-        <v>لم يتم العثور على قضايا</v>
+        <v>تعديل صاحب المصلحة</v>
       </c>
       <c r="C617" t="str">
-        <v>Problēmas nav atrastas</v>
+        <v>Rediģēt ieinteresēto pusi</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Try adjusting your filters to find issues.</v>
+        <v>Search stakeholders...</v>
       </c>
       <c r="B618" t="str">
-        <v>حاول تعديل الفلاتر للعثور على القضايا.</v>
+        <v>البحث في أصحاب المصلحة...</v>
       </c>
       <c r="C618" t="str">
-        <v>Mēģiniet pielāgot filtrus, lai atrastu problēmas.</v>
+        <v>Meklēt ieinteresētās puses...</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Create your first issue to get started.</v>
+        <v>Search issues...</v>
       </c>
       <c r="B619" t="str">
-        <v>أنشئ أول قضية للبدء.</v>
+        <v>البحث في القضايا...</v>
       </c>
       <c r="C619" t="str">
-        <v>Izveidojiet savu pirmo problēmu, lai sāktu.</v>
+        <v>Meklēt problēmas...</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Create Action</v>
+        <v>All Types</v>
       </c>
       <c r="B620" t="str">
-        <v>إنشاء إجراء</v>
+        <v>جميع الأنواع</v>
       </c>
       <c r="C620" t="str">
-        <v>Izveidot darbību</v>
+        <v>Visi tipi</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>View Actions</v>
+        <v>All Status</v>
       </c>
       <c r="B621" t="str">
-        <v>عرض الإجراءات</v>
+        <v>جميع الحالات</v>
       </c>
       <c r="C621" t="str">
-        <v>Skatīt darbības</v>
+        <v>Visi statusi</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Review Actions</v>
+        <v>All Categories</v>
       </c>
       <c r="B622" t="str">
-        <v>مراجعة الإجراءات</v>
+        <v>جميع الفئات</v>
       </c>
       <c r="C622" t="str">
-        <v>Pārskatīt darbības</v>
+        <v>Visas kategorijas</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Select stakeholder</v>
+        <v>All Domains</v>
       </c>
       <c r="B623" t="str">
-        <v>اختر صاحب المصلحة</v>
+        <v>جميع المجالات</v>
       </c>
       <c r="C623" t="str">
-        <v>Izvēlieties ieinteresēto pusi</v>
+        <v>Visi domēni</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Need and Expectation</v>
+        <v>No Issues Found</v>
       </c>
       <c r="B624" t="str">
-        <v>الاحتياجات والتوقعات</v>
+        <v>لم يتم العثور على قضايا</v>
       </c>
       <c r="C624" t="str">
-        <v>Vajadzība un gaidījums</v>
+        <v>Problēmas nav atrastas</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Select need/expectation</v>
+        <v>Try adjusting your filters to find issues.</v>
       </c>
       <c r="B625" t="str">
-        <v>اختر الاحتياج/التوقع</v>
+        <v>حاول تعديل الفلاتر للعثور على القضايا.</v>
       </c>
       <c r="C625" t="str">
-        <v>Izvēlieties vajadzību/gaidījumu</v>
+        <v>Mēģiniet pielāgot filtrus, lai atrastu problēmas.</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Stakeholder Needs and Expectations</v>
+        <v>Create your first issue to get started.</v>
       </c>
       <c r="B626" t="str">
-        <v>احتياجات وتوقعات أصحاب المصلحة</v>
+        <v>أنشئ أول قضية للبدء.</v>
       </c>
       <c r="C626" t="str">
-        <v>Ieinteresēto pušu vajadzības un gaidījumi</v>
+        <v>Izveidojiet savu pirmo problēmu, lai sāktu.</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Add New Domain</v>
+        <v>Create Action</v>
       </c>
       <c r="B627" t="str">
-        <v>إضافة مجال جديد</v>
+        <v>إنشاء إجراء</v>
       </c>
       <c r="C627" t="str">
-        <v>Pievienot jaunu domēnu</v>
+        <v>Izveidot darbību</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Enter domain name</v>
+        <v>View Actions</v>
       </c>
       <c r="B628" t="str">
-        <v>أدخل اسم المجال</v>
+        <v>عرض الإجراءات</v>
       </c>
       <c r="C628" t="str">
-        <v>Ievadiet domēna nosaukumu</v>
+        <v>Skatīt darbības</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Add New Category</v>
+        <v>Review Actions</v>
       </c>
       <c r="B629" t="str">
-        <v>إضافة فئة جديدة</v>
+        <v>مراجعة الإجراءات</v>
       </c>
       <c r="C629" t="str">
-        <v>Pievienot jaunu kategoriju</v>
+        <v>Pārskatīt darbības</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Add New Issue Type</v>
+        <v>Select stakeholder</v>
       </c>
       <c r="B630" t="str">
-        <v>إضافة نوع قضية جديد</v>
+        <v>اختر صاحب المصلحة</v>
       </c>
       <c r="C630" t="str">
-        <v>Pievienot jaunu problēmas tipu</v>
+        <v>Izvēlieties ieinteresēto pusi</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Issue Type Name</v>
+        <v>Need and Expectation</v>
       </c>
       <c r="B631" t="str">
-        <v>اسم نوع القضية</v>
+        <v>الاحتياجات والتوقعات</v>
       </c>
       <c r="C631" t="str">
-        <v>Problēmas tipa nosaukums</v>
+        <v>Vajadzība un gaidījums</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Enter issue type name</v>
+        <v>Select need/expectation</v>
       </c>
       <c r="B632" t="str">
-        <v>أدخل اسم نوع القضية</v>
+        <v>اختر الاحتياج/التوقع</v>
       </c>
       <c r="C632" t="str">
-        <v>Ievadiet problēmas tipa nosaukumu</v>
+        <v>Izvēlieties vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Link Process</v>
+        <v>Stakeholder Needs and Expectations</v>
       </c>
       <c r="B633" t="str">
-        <v>ربط العملية</v>
+        <v>احتياجات وتوقعات أصحاب المصلحة</v>
       </c>
       <c r="C633" t="str">
-        <v>Saistīt procesu</v>
+        <v>Ieinteresēto pušu vajadzības un gaidījumi</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>No processes found</v>
+        <v>Add New Domain</v>
       </c>
       <c r="B634" t="str">
-        <v>لم يتم العثور على عمليات</v>
+        <v>إضافة مجال جديد</v>
       </c>
       <c r="C634" t="str">
-        <v>Procesi nav atrasti</v>
+        <v>Pievienot jaunu domēnu</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Add New Need/Expectation</v>
+        <v>Enter domain name</v>
       </c>
       <c r="B635" t="str">
-        <v>إضافة احتياج/توقع جديد</v>
+        <v>أدخل اسم المجال</v>
       </c>
       <c r="C635" t="str">
-        <v>Pievienot jaunu vajadzību/gaidījumu</v>
+        <v>Ievadiet domēna nosaukumu</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Need/Expectation</v>
+        <v>Add New Category</v>
       </c>
       <c r="B636" t="str">
-        <v>الاحتياج/التوقع</v>
+        <v>إضافة فئة جديدة</v>
       </c>
       <c r="C636" t="str">
-        <v>Vajadzība/Gaidījums</v>
+        <v>Pievienot jaunu kategoriju</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Enter need/expectation</v>
+        <v>Add New Issue Type</v>
       </c>
       <c r="B637" t="str">
-        <v>أدخل الاحتياج/التوقع</v>
+        <v>إضافة نوع قضية جديد</v>
       </c>
       <c r="C637" t="str">
-        <v>Ievadiet vajadzību/gaidījumu</v>
+        <v>Pievienot jaunu problēmas tipu</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Enter a new need or expectation type.</v>
+        <v>Issue Type Name</v>
       </c>
       <c r="B638" t="str">
-        <v>أدخل نوع احتياج أو توقع جديد.</v>
+        <v>اسم نوع القضية</v>
       </c>
       <c r="C638" t="str">
-        <v>Ievadiet jaunu vajadzības vai gaidījumu tipu.</v>
+        <v>Problēmas tipa nosaukums</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Title is required</v>
+        <v>Enter issue type name</v>
       </c>
       <c r="B639" t="str">
-        <v>العنوان مطلوب</v>
+        <v>أدخل اسم نوع القضية</v>
       </c>
       <c r="C639" t="str">
-        <v>Nosaukums ir obligāts</v>
+        <v>Ievadiet problēmas tipa nosaukumu</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Issue created successfully</v>
+        <v>Link Process</v>
       </c>
       <c r="B640" t="str">
-        <v>تم إنشاء القضية بنجاح</v>
+        <v>ربط العملية</v>
       </c>
       <c r="C640" t="str">
-        <v>Problēma veiksmīgi izveidota</v>
+        <v>Saistīt procesu</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Failed to create issue</v>
+        <v>No processes found</v>
       </c>
       <c r="B641" t="str">
-        <v>فشل في إنشاء القضية</v>
+        <v>لم يتم العثور على عمليات</v>
       </c>
       <c r="C641" t="str">
-        <v>Neizdevās izveidot problēmu</v>
+        <v>Procesi nav atrasti</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Issue updated successfully</v>
+        <v>Add New Need/Expectation</v>
       </c>
       <c r="B642" t="str">
-        <v>تم تحديث القضية بنجاح</v>
+        <v>إضافة احتياج/توقع جديد</v>
       </c>
       <c r="C642" t="str">
-        <v>Problēma veiksmīgi atjaunināta</v>
+        <v>Pievienot jaunu vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Failed to update issue</v>
+        <v>Need/Expectation</v>
       </c>
       <c r="B643" t="str">
-        <v>فشل في تحديث القضية</v>
+        <v>الاحتياج/التوقع</v>
       </c>
       <c r="C643" t="str">
-        <v>Neizdevās atjaunināt problēmu</v>
+        <v>Vajadzība/Gaidījums</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Stakeholder updated successfully</v>
+        <v>Enter need/expectation</v>
       </c>
       <c r="B644" t="str">
-        <v>تم تحديث صاحب المصلحة بنجاح</v>
+        <v>أدخل الاحتياج/التوقع</v>
       </c>
       <c r="C644" t="str">
-        <v>Ieinteresētā puse veiksmīgi atjaunināta</v>
+        <v>Ievadiet vajadzību/gaidījumu</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Failed to update stakeholder</v>
+        <v>Enter a new need or expectation type.</v>
       </c>
       <c r="B645" t="str">
-        <v>فشل في تحديث صاحب المصلحة</v>
+        <v>أدخل نوع احتياج أو توقع جديد.</v>
       </c>
       <c r="C645" t="str">
-        <v>Neizdevās atjaunināt ieinteresēto pusi</v>
+        <v>Ievadiet jaunu vajadzības vai gaidījumu tipu.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Open</v>
+        <v>Title is required</v>
       </c>
       <c r="B646" t="str">
-        <v>مفتوح</v>
+        <v>العنوان مطلوب</v>
       </c>
       <c r="C646" t="str">
-        <v>Atvērts</v>
+        <v>Nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>In Progress</v>
+        <v>Issue created successfully</v>
       </c>
       <c r="B647" t="str">
-        <v>قيد التنفيذ</v>
+        <v>تم إنشاء القضية بنجاح</v>
       </c>
       <c r="C647" t="str">
-        <v>Procesā</v>
+        <v>Problēma veiksmīgi izveidota</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Action type and description are required</v>
+        <v>Failed to create issue</v>
       </c>
       <c r="B648" t="str">
-        <v>نوع الإجراء والوصف مطلوبان</v>
+        <v>فشل في إنشاء القضية</v>
       </c>
       <c r="C648" t="str">
-        <v>Darbības tips un apraksts ir obligāti</v>
+        <v>Neizdevās izveidot problēmu</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Action created successfully</v>
+        <v>Issue updated successfully</v>
       </c>
       <c r="B649" t="str">
-        <v>تم إنشاء الإجراء بنجاح</v>
+        <v>تم تحديث القضية بنجاح</v>
       </c>
       <c r="C649" t="str">
-        <v>Darbība veiksmīgi izveidota</v>
+        <v>Problēma veiksmīgi atjaunināta</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Failed to create action</v>
+        <v>Failed to update issue</v>
       </c>
       <c r="B650" t="str">
-        <v>فشل في إنشاء الإجراء</v>
+        <v>فشل في تحديث القضية</v>
       </c>
       <c r="C650" t="str">
-        <v>Neizdevās izveidot darbību</v>
+        <v>Neizdevās atjaunināt problēmu</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Action is resolved</v>
+        <v>Stakeholder updated successfully</v>
       </c>
       <c r="B651" t="str">
-        <v>تم حل الإجراء</v>
+        <v>تم تحديث صاحب المصلحة بنجاح</v>
       </c>
       <c r="C651" t="str">
-        <v>Darbība ir atrisināta</v>
+        <v>Ieinteresētā puse veiksmīgi atjaunināta</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Failed to resolve action</v>
+        <v>Failed to update stakeholder</v>
       </c>
       <c r="B652" t="str">
-        <v>فشل في حل الإجراء</v>
+        <v>فشل في تحديث صاحب المصلحة</v>
       </c>
       <c r="C652" t="str">
-        <v>Neizdevās atrisināt darbību</v>
+        <v>Neizdevās atjaunināt ieinteresēto pusi</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Comment is required</v>
+        <v>Open</v>
       </c>
       <c r="B653" t="str">
-        <v>التعليق مطلوب</v>
+        <v>مفتوح</v>
       </c>
       <c r="C653" t="str">
-        <v>Komentārs ir obligāts</v>
+        <v>Atvērts</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Action is sent back</v>
+        <v>In Progress</v>
       </c>
       <c r="B654" t="str">
-        <v>تم إرجاع الإجراء</v>
+        <v>قيد التنفيذ</v>
       </c>
       <c r="C654" t="str">
-        <v>Darbība ir nosūtīta atpakaļ</v>
+        <v>Procesā</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Failed to send back action</v>
+        <v>Action type and description are required</v>
       </c>
       <c r="B655" t="str">
-        <v>فشل في إرجاع الإجراء</v>
+        <v>نوع الإجراء والوصف مطلوبان</v>
       </c>
       <c r="C655" t="str">
-        <v>Neizdevās nosūtīt atpakaļ darbību</v>
+        <v>Darbības tips un apraksts ir obligāti</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Action updated and resubmitted</v>
+        <v>Action created successfully</v>
       </c>
       <c r="B656" t="str">
-        <v>تم تحديث الإجراء وإعادة إرساله</v>
+        <v>تم إنشاء الإجراء بنجاح</v>
       </c>
       <c r="C656" t="str">
-        <v>Darbība atjaunināta un atkārtoti iesniegta</v>
+        <v>Darbība veiksmīgi izveidota</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Failed to update action</v>
+        <v>Failed to create action</v>
       </c>
       <c r="B657" t="str">
-        <v>فشل في تحديث الإجراء</v>
+        <v>فشل في إنشاء الإجراء</v>
       </c>
       <c r="C657" t="str">
-        <v>Neizdevās atjaunināt darbību</v>
+        <v>Neizdevās izveidot darbību</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Saving...</v>
+        <v>Action is resolved</v>
       </c>
       <c r="B658" t="str">
-        <v>جاري الحفظ...</v>
+        <v>تم حل الإجراء</v>
       </c>
       <c r="C658" t="str">
-        <v>Saglabā...</v>
+        <v>Darbība ir atrisināta</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Save &amp; Resubmit</v>
+        <v>Failed to resolve action</v>
       </c>
       <c r="B659" t="str">
-        <v>حفظ وإعادة الإرسال</v>
+        <v>فشل في حل الإجراء</v>
       </c>
       <c r="C659" t="str">
-        <v>Saglabāt un iesniegt atkārtoti</v>
+        <v>Neizdevās atrisināt darbību</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Import Issues</v>
+        <v>Comment is required</v>
       </c>
       <c r="B660" t="str">
-        <v>استيراد القضايا</v>
+        <v>التعليق مطلوب</v>
       </c>
       <c r="C660" t="str">
-        <v>Importēt problēmas</v>
+        <v>Komentārs ir obligāts</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>CSV file must have a header row and at least one data row</v>
+        <v>Action is sent back</v>
       </c>
       <c r="B661" t="str">
-        <v>يجب أن يحتوي ملف CSV على صف رأس وصف بيانات واحد على الأقل</v>
+        <v>تم إرجاع الإجراء</v>
       </c>
       <c r="C661" t="str">
-        <v>CSV failam jābūt galvenes rindai un vismaz vienai datu rindai</v>
+        <v>Darbība ir nosūtīta atpakaļ</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>CSV must have a "title" column</v>
+        <v>Failed to send back action</v>
       </c>
       <c r="B662" t="str">
-        <v>يجب أن يحتوي ملف CSV على عمود "title"</v>
+        <v>فشل في إرجاع الإجراء</v>
       </c>
       <c r="C662" t="str">
-        <v>CSV ir jābūt kolonnai "title"</v>
+        <v>Neizdevās nosūtīt atpakaļ darbību</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Successfully imported</v>
+        <v>Action updated and resubmitted</v>
       </c>
       <c r="B663" t="str">
-        <v>تم الاستيراد بنجاح</v>
+        <v>تم تحديث الإجراء وإعادة إرساله</v>
       </c>
       <c r="C663" t="str">
-        <v>Veiksmīgi importēts</v>
+        <v>Darbība atjaunināta un atkārtoti iesniegta</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>issues</v>
+        <v>Failed to update action</v>
       </c>
       <c r="B664" t="str">
-        <v>قضايا</v>
+        <v>فشل في تحديث الإجراء</v>
       </c>
       <c r="C664" t="str">
-        <v>problēmas</v>
+        <v>Neizdevās atjaunināt darbību</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Error importing issues. Please check the file format.</v>
+        <v>Saving...</v>
       </c>
       <c r="B665" t="str">
-        <v>خطأ في استيراد القضايا. يرجى التحقق من تنسيق الملف.</v>
+        <v>جاري الحفظ...</v>
       </c>
       <c r="C665" t="str">
-        <v>Kļūda importējot problēmas. Lūdzu, pārbaudiet faila formātu.</v>
+        <v>Saglabā...</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>File attached to action</v>
+        <v>Save &amp; Resubmit</v>
       </c>
       <c r="B666" t="str">
-        <v>تم إرفاق الملف بالإجراء</v>
+        <v>حفظ وإعادة الإرسال</v>
       </c>
       <c r="C666" t="str">
-        <v>Fails pievienots darbībai</v>
+        <v>Saglabāt un iesniegt atkārtoti</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Failed to attach file to action</v>
+        <v>Import Issues</v>
       </c>
       <c r="B667" t="str">
-        <v>فشل في إرفاق الملف بالإجراء</v>
+        <v>استيراد القضايا</v>
       </c>
       <c r="C667" t="str">
-        <v>Neizdevās pievienot failu darbībai</v>
+        <v>Importēt problēmas</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>File deleted successfully</v>
+        <v>CSV file must have a header row and at least one data row</v>
       </c>
       <c r="B668" t="str">
-        <v>تم حذف الملف بنجاح</v>
+        <v>يجب أن يحتوي ملف CSV على صف رأس وصف بيانات واحد على الأقل</v>
       </c>
       <c r="C668" t="str">
-        <v>Fails veiksmīgi dzēsts</v>
+        <v>CSV failam jābūt galvenes rindai un vismaz vienai datu rindai</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Failed to delete file</v>
+        <v>CSV must have a "title" column</v>
       </c>
       <c r="B669" t="str">
-        <v>فشل في حذف الملف</v>
+        <v>يجب أن يحتوي ملف CSV على عمود "title"</v>
       </c>
       <c r="C669" t="str">
-        <v>Neizdevās dzēst failu</v>
+        <v>CSV ir jābūt kolonnai "title"</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Repository</v>
+        <v>Successfully imported</v>
       </c>
       <c r="B670" t="str">
-        <v>المستودع</v>
+        <v>تم الاستيراد بنجاح</v>
       </c>
       <c r="C670" t="str">
-        <v>Repozitorijs</v>
+        <v>Veiksmīgi importēts</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Performance Dashboard</v>
+        <v>issues</v>
       </c>
       <c r="B671" t="str">
-        <v>لوحة الأداء</v>
+        <v>قضايا</v>
       </c>
       <c r="C671" t="str">
-        <v>Veiktspējas panelis</v>
+        <v>problēmas</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Search By Process ID, Name</v>
+        <v>Error importing issues. Please check the file format.</v>
       </c>
       <c r="B672" t="str">
-        <v>البحث بمعرف العملية أو الاسم</v>
+        <v>خطأ في استيراد القضايا. يرجى التحقق من تنسيق الملف.</v>
       </c>
       <c r="C672" t="str">
-        <v>Meklēt pēc procesa ID, nosaukuma</v>
+        <v>Kļūda importējot problēmas. Lūdzu, pārbaudiet faila formātu.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>All Owners</v>
+        <v>File attached to action</v>
       </c>
       <c r="B673" t="str">
-        <v>جميع المالكين</v>
+        <v>تم إرفاق الملف بالإجراء</v>
       </c>
       <c r="C673" t="str">
-        <v>Visi īpašnieki</v>
+        <v>Fails pievienots darbībai</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>All Frequencies</v>
+        <v>Failed to attach file to action</v>
       </c>
       <c r="B674" t="str">
-        <v>جميع الترددات</v>
+        <v>فشل في إرفاق الملف بالإجراء</v>
       </c>
       <c r="C674" t="str">
-        <v>Visi biežumi</v>
+        <v>Neizdevās pievienot failu darbībai</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Edit Process</v>
+        <v>File deleted successfully</v>
       </c>
       <c r="B675" t="str">
-        <v>تعديل العملية</v>
+        <v>تم حذف الملف بنجاح</v>
       </c>
       <c r="C675" t="str">
-        <v>Rediģēt procesu</v>
+        <v>Fails veiksmīgi dzēsts</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Confirm Delete</v>
+        <v>Failed to delete file</v>
       </c>
       <c r="B676" t="str">
-        <v>تأكيد الحذف</v>
+        <v>فشل في حذف الملف</v>
       </c>
       <c r="C676" t="str">
-        <v>Apstiprināt dzēšanu</v>
+        <v>Neizdevās dzēst failu</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Are you sure you want to delete this process? This action cannot be undone.</v>
+        <v>Repository</v>
       </c>
       <c r="B677" t="str">
-        <v>هل أنت متأكد أنك تريد حذف هذه العملية؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>المستودع</v>
       </c>
       <c r="C677" t="str">
-        <v>Vai tiešām vēlaties dzēst šo procesu? Šo darbību nevar atsaukt.</v>
+        <v>Repozitorijs</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Add New Process</v>
+        <v>Performance Dashboard</v>
       </c>
       <c r="B678" t="str">
-        <v>إضافة عملية جديدة</v>
+        <v>لوحة الأداء</v>
       </c>
       <c r="C678" t="str">
-        <v>Pievienot jaunu procesu</v>
+        <v>Veiktspējas panelis</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Basic Information</v>
+        <v>Search By Process ID, Name</v>
       </c>
       <c r="B679" t="str">
-        <v>المعلومات الأساسية</v>
+        <v>البحث بمعرف العملية أو الاسم</v>
       </c>
       <c r="C679" t="str">
-        <v>Pamatinformācija</v>
+        <v>Meklēt pēc procesa ID, nosaukuma</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Process Details</v>
+        <v>All Owners</v>
       </c>
       <c r="B680" t="str">
-        <v>تفاصيل العملية</v>
+        <v>جميع المالكين</v>
       </c>
       <c r="C680" t="str">
-        <v>Procesa detaļas</v>
+        <v>Visi īpašnieki</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Dependencies &amp; Options</v>
+        <v>All Frequencies</v>
       </c>
       <c r="B681" t="str">
-        <v>التبعيات والخيارات</v>
+        <v>جميع الترددات</v>
       </c>
       <c r="C681" t="str">
-        <v>Atkarības un opcijas</v>
+        <v>Visi biežumi</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>RACI Matrix</v>
+        <v>Edit Process</v>
       </c>
       <c r="B682" t="str">
-        <v>مصفوفة RACI</v>
+        <v>تعديل العملية</v>
       </c>
       <c r="C682" t="str">
-        <v>RACI matrica</v>
+        <v>Rediģēt procesu</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Enter process name</v>
+        <v>Confirm Delete</v>
       </c>
       <c r="B683" t="str">
-        <v>أدخل اسم العملية</v>
+        <v>تأكيد الحذف</v>
       </c>
       <c r="C683" t="str">
-        <v>Ievadiet procesa nosaukumu</v>
+        <v>Apstiprināt dzēšanu</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Enter process description</v>
+        <v>Are you sure you want to delete this process? This action cannot be undone.</v>
       </c>
       <c r="B684" t="str">
-        <v>أدخل وصف العملية</v>
+        <v>هل أنت متأكد أنك تريد حذف هذه العملية؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C684" t="str">
-        <v>Ievadiet procesa aprakstu</v>
+        <v>Vai tiešām vēlaties dzēst šo procesu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Nature of Implementation</v>
+        <v>Add New Process</v>
       </c>
       <c r="B685" t="str">
-        <v>طبيعة التنفيذ</v>
+        <v>إضافة عملية جديدة</v>
       </c>
       <c r="C685" t="str">
-        <v>Ieviešanas veids</v>
+        <v>Pievienot jaunu procesu</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Select implementation type</v>
+        <v>Basic Information</v>
       </c>
       <c r="B686" t="str">
-        <v>اختر نوع التنفيذ</v>
+        <v>المعلومات الأساسية</v>
       </c>
       <c r="C686" t="str">
-        <v>Izvēlieties ieviešanas tipu</v>
+        <v>Pamatinformācija</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Select location</v>
+        <v>Process Details</v>
       </c>
       <c r="B687" t="str">
-        <v>اختر الموقع</v>
+        <v>تفاصيل العملية</v>
       </c>
       <c r="C687" t="str">
-        <v>Izvēlieties atrašanās vietu</v>
+        <v>Procesa detaļas</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Operational Complexity</v>
+        <v>Dependencies &amp; Options</v>
       </c>
       <c r="B688" t="str">
-        <v>التعقيد التشغيلي</v>
+        <v>التبعيات والخيارات</v>
       </c>
       <c r="C688" t="str">
-        <v>Operacionālā sarežģītība</v>
+        <v>Atkarības un opcijas</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Select complexity</v>
+        <v>RACI Matrix</v>
       </c>
       <c r="B689" t="str">
-        <v>اختر التعقيد</v>
+        <v>مصفوفة RACI</v>
       </c>
       <c r="C689" t="str">
-        <v>Izvēlieties sarežģītību</v>
+        <v>RACI matrica</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Asset Dependency</v>
+        <v>Enter process name</v>
       </c>
       <c r="B690" t="str">
-        <v>تبعية الأصول</v>
+        <v>أدخل اسم العملية</v>
       </c>
       <c r="C690" t="str">
-        <v>Aktīvu atkarība</v>
+        <v>Ievadiet procesa nosaukumu</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>External Dependency</v>
+        <v>Enter process description</v>
       </c>
       <c r="B691" t="str">
-        <v>تبعية خارجية</v>
+        <v>أدخل وصف العملية</v>
       </c>
       <c r="C691" t="str">
-        <v>Ārējā atkarība</v>
+        <v>Ievadiet procesa aprakstu</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>KPI Measurement Required</v>
+        <v>Nature of Implementation</v>
       </c>
       <c r="B692" t="str">
-        <v>قياس مؤشرات الأداء مطلوب</v>
+        <v>طبيعة التنفيذ</v>
       </c>
       <c r="C692" t="str">
-        <v>Nepieciešams KPI mērījums</v>
+        <v>Ieviešanas veids</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>PII Capture</v>
+        <v>Select implementation type</v>
       </c>
       <c r="B693" t="str">
-        <v>التقاط البيانات الشخصية</v>
+        <v>اختر نوع التنفيذ</v>
       </c>
       <c r="C693" t="str">
-        <v>PII uztveršana</v>
+        <v>Izvēlieties ieviešanas tipu</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Auto-generated</v>
+        <v>Select location</v>
       </c>
       <c r="B694" t="str">
-        <v>يتم إنشاؤه تلقائياً</v>
+        <v>اختر الموقع</v>
       </c>
       <c r="C694" t="str">
-        <v>Automātiski ģenerēts</v>
+        <v>Izvēlieties atrašanās vietu</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Auto-generated if left empty</v>
+        <v>Operational Complexity</v>
       </c>
       <c r="B695" t="str">
-        <v>يتم إنشاؤه تلقائياً إذا تُرك فارغاً</v>
+        <v>التعقيد التشغيلي</v>
       </c>
       <c r="C695" t="str">
-        <v>Automātiski ģenerēts, ja atstāts tukšs</v>
+        <v>Operacionālā sarežģītība</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Risk name is required</v>
+        <v>Select complexity</v>
       </c>
       <c r="B696" t="str">
-        <v>اسم المخاطرة مطلوب</v>
+        <v>اختر التعقيد</v>
       </c>
       <c r="C696" t="str">
-        <v>Riska nosaukums ir obligāts</v>
+        <v>Izvēlieties sarežģītību</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Risk description is required</v>
+        <v>Asset Dependency</v>
       </c>
       <c r="B697" t="str">
-        <v>وصف المخاطرة مطلوب</v>
+        <v>تبعية الأصول</v>
       </c>
       <c r="C697" t="str">
-        <v>Riska apraksts ir obligāts</v>
+        <v>Aktīvu atkarība</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>Inherent likelihood is required</v>
+        <v>External Dependency</v>
       </c>
       <c r="B698" t="str">
-        <v>احتمالية المخاطر الكامنة مطلوبة</v>
+        <v>تبعية خارجية</v>
       </c>
       <c r="C698" t="str">
-        <v>Iedzimtā varbūtība ir obligāta</v>
+        <v>Ārējā atkarība</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>Inherent impact is required</v>
+        <v>KPI Measurement Required</v>
       </c>
       <c r="B699" t="str">
-        <v>تأثير المخاطر الكامنة مطلوب</v>
+        <v>قياس مؤشرات الأداء مطلوب</v>
       </c>
       <c r="C699" t="str">
-        <v>Iedzimtā ietekme ir obligāta</v>
+        <v>Nepieciešams KPI mērījums</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>Residual likelihood is required</v>
+        <v>PII Capture</v>
       </c>
       <c r="B700" t="str">
-        <v>احتمالية المخاطر المتبقية مطلوبة</v>
+        <v>التقاط البيانات الشخصية</v>
       </c>
       <c r="C700" t="str">
-        <v>Atlikušā varbūtība ir obligāta</v>
+        <v>PII uztveršana</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Residual impact is required</v>
+        <v>Auto-generated</v>
       </c>
       <c r="B701" t="str">
-        <v>تأثير المخاطر المتبقية مطلوب</v>
+        <v>يتم إنشاؤه تلقائياً</v>
       </c>
       <c r="C701" t="str">
-        <v>Atlikušā ietekme ir obligāta</v>
+        <v>Automātiski ģenerēts</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Process created successfully</v>
+        <v>Auto-generated if left empty</v>
       </c>
       <c r="B702" t="str">
-        <v>تم إنشاء العملية بنجاح</v>
+        <v>يتم إنشاؤه تلقائياً إذا تُرك فارغاً</v>
       </c>
       <c r="C702" t="str">
-        <v>Process veiksmīgi izveidots</v>
+        <v>Automātiski ģenerēts, ja atstāts tukšs</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Failed to create process</v>
+        <v>Risk name is required</v>
       </c>
       <c r="B703" t="str">
-        <v>فشل في إنشاء العملية</v>
+        <v>اسم المخاطرة مطلوب</v>
       </c>
       <c r="C703" t="str">
-        <v>Neizdevās izveidot procesu</v>
+        <v>Riska nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>Process updated successfully</v>
+        <v>Risk description is required</v>
       </c>
       <c r="B704" t="str">
-        <v>تم تحديث العملية بنجاح</v>
+        <v>وصف المخاطرة مطلوب</v>
       </c>
       <c r="C704" t="str">
-        <v>Process veiksmīgi atjaunināts</v>
+        <v>Riska apraksts ir obligāts</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>Failed to update process</v>
+        <v>Inherent likelihood is required</v>
       </c>
       <c r="B705" t="str">
-        <v>فشل في تحديث العملية</v>
+        <v>احتمالية المخاطر الكامنة مطلوبة</v>
       </c>
       <c r="C705" t="str">
-        <v>Neizdevās atjaunināt procesu</v>
+        <v>Iedzimtā varbūtība ir obligāta</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>Please fill in required fields (Name and Process Type)</v>
+        <v>Inherent impact is required</v>
       </c>
       <c r="B706" t="str">
-        <v>يرجى ملء الحقول المطلوبة (الاسم ونوع العملية)</v>
+        <v>تأثير المخاطر الكامنة مطلوب</v>
       </c>
       <c r="C706" t="str">
-        <v>Lūdzu, aizpildiet obligātos laukus (Nosaukums un procesa tips)</v>
+        <v>Iedzimtā ietekme ir obligāta</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>Save Changes</v>
+        <v>Residual likelihood is required</v>
       </c>
       <c r="B707" t="str">
-        <v>حفظ التغييرات</v>
+        <v>احتمالية المخاطر المتبقية مطلوبة</v>
       </c>
       <c r="C707" t="str">
-        <v>Saglabāt izmaiņas</v>
+        <v>Atlikušā varbūtība ir obligāta</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>Reference ID</v>
+        <v>Residual impact is required</v>
       </c>
       <c r="B708" t="str">
-        <v>المعرف المرجعي</v>
+        <v>تأثير المخاطر المتبقية مطلوب</v>
       </c>
       <c r="C708" t="str">
-        <v>Atsauces ID</v>
+        <v>Atlikušā ietekme ir obligāta</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>Process Criticality</v>
+        <v>Asset ID is required</v>
       </c>
       <c r="B709" t="str">
-        <v>أهمية العملية</v>
+        <v>معرف الأصل مطلوب</v>
       </c>
       <c r="C709" t="str">
-        <v>Procesa kritiskums</v>
+        <v>Aktīva ID ir obligāts</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>Process Frequency</v>
+        <v>Asset name is required</v>
       </c>
       <c r="B710" t="str">
-        <v>تكرار العملية</v>
+        <v>اسم الأصل مطلوب</v>
       </c>
       <c r="C710" t="str">
-        <v>Procesa biežums</v>
+        <v>Aktīva nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>Nature Of Implementation</v>
+        <v>Please select the department</v>
       </c>
       <c r="B711" t="str">
-        <v>طبيعة التنفيذ</v>
+        <v>يرجى تحديد القسم</v>
       </c>
       <c r="C711" t="str">
-        <v>Ieviešanas veids</v>
+        <v>Lūdzu, izvēlieties nodaļu</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>AI Risk</v>
+        <v>Please select the asset owner</v>
       </c>
       <c r="B712" t="str">
-        <v>مخاطر الذكاء الاصطناعي</v>
+        <v>يرجى تحديد مالك الأصل</v>
       </c>
       <c r="C712" t="str">
-        <v>AI risks</v>
+        <v>Lūdzu, izvēlieties aktīva īpašnieku</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>AI Risk Evaluation</v>
+        <v>Please select the asset category</v>
       </c>
       <c r="B713" t="str">
-        <v>تقييم مخاطر الذكاء الاصطناعي</v>
+        <v>يرجى تحديد فئة الأصل</v>
       </c>
       <c r="C713" t="str">
-        <v>AI risku novērtējums</v>
+        <v>Lūdzu, izvēlieties aktīva kategoriju</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>AI is identifying potential risks...</v>
+        <v>Please select the asset sub category</v>
       </c>
       <c r="B714" t="str">
-        <v>الذكاء الاصطناعي يحدد المخاطر المحتملة...</v>
+        <v>يرجى تحديد الفئة الفرعية للأصل</v>
       </c>
       <c r="C714" t="str">
-        <v>AI identificē potenciālos riskus...</v>
+        <v>Lūdzu, izvēlieties aktīva apakškategoriju</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>This may take up to 30 seconds</v>
+        <v>Please select the asset group</v>
       </c>
       <c r="B715" t="str">
-        <v>قد يستغرق هذا ما يصل إلى 30 ثانية</v>
+        <v>يرجى تحديد مجموعة الأصول</v>
       </c>
       <c r="C715" t="str">
-        <v>Tas var aizņemt līdz 30 sekundēm</v>
+        <v>Lūdzu, izvēlieties aktīvu grupu</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>Detected Risks</v>
+        <v>Please select the asset custodian</v>
       </c>
       <c r="B716" t="str">
-        <v>المخاطر المكتشفة</v>
+        <v>يرجى تحديد حارس الأصل</v>
       </c>
       <c r="C716" t="str">
-        <v>Atklātie riski</v>
+        <v>Lūdzu, izvēlieties aktīva glabātāju</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>The AI has identified the following risks, threats, and suggested controls...</v>
+        <v>Please enter the asset location</v>
       </c>
       <c r="B717" t="str">
-        <v>حدد الذكاء الاصطناعي المخاطر والتهديدات والضوابط المقترحة التالية...</v>
+        <v>يرجى إدخال موقع الأصل</v>
       </c>
       <c r="C717" t="str">
-        <v>AI ir identificējis šādus riskus, draudus un ieteiktos kontroles...</v>
+        <v>Lūdzu, ievadiet aktīva atrašanās vietu</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>Threats</v>
+        <v>Please select asset sub category</v>
       </c>
       <c r="B718" t="str">
-        <v>التهديدات</v>
+        <v>يرجى تحديد الفئة الفرعية للأصل</v>
       </c>
       <c r="C718" t="str">
-        <v>Draudi</v>
+        <v>Lūdzu, izvēlieties aktīva apakškategoriju</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>Suggested Controls</v>
+        <v>Please select asset group</v>
       </c>
       <c r="B719" t="str">
-        <v>الضوابط المقترحة</v>
+        <v>يرجى تحديد مجموعة الأصول</v>
       </c>
       <c r="C719" t="str">
-        <v>Ieteiktās kontroles</v>
+        <v>Lūdzu, izvēlieties aktīvu grupu</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>No risks generated yet.</v>
+        <v>Please select sensitivity rating</v>
       </c>
       <c r="B720" t="str">
-        <v>لم يتم إنشاء مخاطر بعد.</v>
+        <v>يرجى تحديد تصنيف الحساسية</v>
       </c>
       <c r="C720" t="str">
-        <v>Vēl nav ģenerēti riski.</v>
+        <v>Lūdzu, izvēlieties jutīguma novērtējumu</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>AI Risks Generated</v>
+        <v>Please select confidentiality rating</v>
       </c>
       <c r="B721" t="str">
-        <v>تم إنشاء مخاطر الذكاء الاصطناعي</v>
+        <v>يرجى تحديد تصنيف السرية</v>
       </c>
       <c r="C721" t="str">
-        <v>AI riski ģenerēti</v>
+        <v>Lūdzu, izvēlieties konfidencialitātes novērtējumu</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>AI Generation Failed</v>
+        <v>Please select integrity rating</v>
       </c>
       <c r="B722" t="str">
-        <v>فشل إنشاء الذكاء الاصطناعي</v>
+        <v>يرجى تحديد تصنيف النزاهة</v>
       </c>
       <c r="C722" t="str">
-        <v>AI ģenerēšana neizdevās</v>
+        <v>Lūdzu, izvēlieties integritātes novērtējumu</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>Communication with AI service failed.</v>
+        <v>Please select availability rating</v>
       </c>
       <c r="B723" t="str">
-        <v>فشل الاتصال بخدمة الذكاء الاصطناعي.</v>
+        <v>يرجى تحديد تصنيف التوافر</v>
       </c>
       <c r="C723" t="str">
-        <v>Saziņa ar AI servisu neizdevās.</v>
+        <v>Lūdzu, izvēlieties pieejamības novērtējumu</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>Please try again later.</v>
+        <v>Process created successfully</v>
       </c>
       <c r="B724" t="str">
-        <v>يرجى المحاولة مرة أخرى لاحقاً.</v>
+        <v>تم إنشاء العملية بنجاح</v>
       </c>
       <c r="C724" t="str">
-        <v>Lūdzu, mēģiniet vēlreiz vēlāk.</v>
+        <v>Process veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>Go to Risk Register</v>
+        <v>Failed to create process</v>
       </c>
       <c r="B725" t="str">
-        <v>الذهاب إلى سجل المخاطر</v>
+        <v>فشل في إنشاء العملية</v>
       </c>
       <c r="C725" t="str">
-        <v>Doties uz risku reģistru</v>
+        <v>Neizdevās izveidot procesu</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>Add to Risk Register</v>
+        <v>Process updated successfully</v>
       </c>
       <c r="B726" t="str">
-        <v>إضافة إلى سجل المخاطر</v>
+        <v>تم تحديث العملية بنجاح</v>
       </c>
       <c r="C726" t="str">
-        <v>Pievienot risku reģistram</v>
+        <v>Process veiksmīgi atjaunināts</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>Adding...</v>
+        <v>Failed to update process</v>
       </c>
       <c r="B727" t="str">
-        <v>جاري الإضافة...</v>
+        <v>فشل في تحديث العملية</v>
       </c>
       <c r="C727" t="str">
-        <v>Pievieno...</v>
+        <v>Neizdevās atjaunināt procesu</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>No risks to add</v>
+        <v>Please fill in required fields (Name and Process Type)</v>
       </c>
       <c r="B728" t="str">
-        <v>لا توجد مخاطر للإضافة</v>
+        <v>يرجى ملء الحقول المطلوبة (الاسم ونوع العملية)</v>
       </c>
       <c r="C728" t="str">
-        <v>Nav risku, ko pievienot</v>
+        <v>Lūdzu, aizpildiet obligātos laukus (Nosaukums un procesa tips)</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>Keep at least one risk before adding to the register.</v>
+        <v>Save Changes</v>
       </c>
       <c r="B729" t="str">
-        <v>احتفظ بخطر واحد على الأقل قبل الإضافة إلى السجل.</v>
+        <v>حفظ التغييرات</v>
       </c>
       <c r="C729" t="str">
-        <v>Paturiet vismaz vienu risku pirms pievienošanas reģistram.</v>
+        <v>Saglabāt izmaiņas</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>Risks have been added to the Risk Register.</v>
+        <v>Reference ID</v>
       </c>
       <c r="B730" t="str">
-        <v>تمت إضافة المخاطر إلى سجل المخاطر.</v>
+        <v>المعرف المرجعي</v>
       </c>
       <c r="C730" t="str">
-        <v>Riski ir pievienoti risku reģistram.</v>
+        <v>Atsauces ID</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>Adding to risk register timed out. Please try again.</v>
+        <v>Process Criticality</v>
       </c>
       <c r="B731" t="str">
-        <v>انتهت مهلة الإضافة إلى سجل المخاطر. يرجى المحاولة مرة أخرى.</v>
+        <v>أهمية العملية</v>
       </c>
       <c r="C731" t="str">
-        <v>Pievienošanas reģistram laiks beidzās. Lūdzu, mēģiniet vēlreiz.</v>
+        <v>Procesa kritiskums</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>Failed to add risks to register</v>
+        <v>Process Frequency</v>
       </c>
       <c r="B732" t="str">
-        <v>فشل في إضافة المخاطر إلى السجل</v>
+        <v>تكرار العملية</v>
       </c>
       <c r="C732" t="str">
-        <v>Neizdevās pievienot riskus reģistram</v>
+        <v>Procesa biežums</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>Failed to register risks</v>
+        <v>Nature Of Implementation</v>
       </c>
       <c r="B733" t="str">
-        <v>فشل في تسجيل المخاطر</v>
+        <v>طبيعة التنفيذ</v>
       </c>
       <c r="C733" t="str">
-        <v>Neizdevās reģistrēt riskus</v>
+        <v>Ieviešanas veids</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>No risks in semantic result to register</v>
+        <v>AI Risk</v>
       </c>
       <c r="B734" t="str">
-        <v>لا توجد مخاطر في نتيجة البحث الدلالي للتسجيل</v>
+        <v>مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C734" t="str">
-        <v>Nav risku semantiskajā rezultātā reģistrēšanai</v>
+        <v>AI risks</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>Failed to add to risk register</v>
+        <v>AI Risk Evaluation</v>
       </c>
       <c r="B735" t="str">
-        <v>فشل في الإضافة إلى سجل المخاطر</v>
+        <v>تقييم مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C735" t="str">
-        <v>Neizdevās pievienot risku reģistram</v>
+        <v>AI risku novērtējums</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>Add to Audit Plan</v>
+        <v>AI is identifying potential risks...</v>
       </c>
       <c r="B736" t="str">
-        <v>إضافة إلى خطة التدقيق</v>
+        <v>الذكاء الاصطناعي يحدد المخاطر المحتملة...</v>
       </c>
       <c r="C736" t="str">
-        <v>Pievienot audita plānam</v>
+        <v>AI identificē potenciālos riskus...</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>Department information missing</v>
+        <v>This may take up to 30 seconds</v>
       </c>
       <c r="B737" t="str">
-        <v>معلومات القسم مفقودة</v>
+        <v>قد يستغرق هذا ما يصل إلى 30 ثانية</v>
       </c>
       <c r="C737" t="str">
-        <v>Trūkst nodaļas informācijas</v>
+        <v>Tas var aizņemt līdz 30 sekundēm</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>Failed to add to audit plan</v>
+        <v>Detected Risks</v>
       </c>
       <c r="B738" t="str">
-        <v>فشل في الإضافة إلى خطة التدقيق</v>
+        <v>المخاطر المكتشفة</v>
       </c>
       <c r="C738" t="str">
-        <v>Neizdevās pievienot audita plānam</v>
+        <v>Atklātie riski</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>Successfully added to Audit Planning!</v>
+        <v>The AI has identified the following risks, threats, and suggested controls...</v>
       </c>
       <c r="B739" t="str">
-        <v>تمت الإضافة بنجاح إلى تخطيط التدقيق!</v>
+        <v>حدد الذكاء الاصطناعي المخاطر والتهديدات والضوابط المقترحة التالية...</v>
       </c>
       <c r="C739" t="str">
-        <v>Veiksmīgi pievienots audita plānošanai!</v>
+        <v>AI ir identificējis šādus riskus, draudus un ieteiktos kontroles...</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>Already Added</v>
+        <v>Threats</v>
       </c>
       <c r="B740" t="str">
-        <v>تمت الإضافة بالفعل</v>
+        <v>التهديدات</v>
       </c>
       <c r="C740" t="str">
-        <v>Jau pievienots</v>
+        <v>Draudi</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>This audit plan has already been added to Audit Planning.</v>
+        <v>Suggested Controls</v>
       </c>
       <c r="B741" t="str">
-        <v>تمت إضافة خطة التدقيق هذه بالفعل إلى تخطيط التدقيق.</v>
+        <v>الضوابط المقترحة</v>
       </c>
       <c r="C741" t="str">
-        <v>Šis audita plāns jau ir pievienots audita plānošanai.</v>
+        <v>Ieteiktās kontroles</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>Suggest Risks with AI</v>
+        <v>No risks generated yet.</v>
       </c>
       <c r="B742" t="str">
-        <v>اقتراح المخاطر بالذكاء الاصطناعي</v>
+        <v>لم يتم إنشاء مخاطر بعد.</v>
       </c>
       <c r="C742" t="str">
-        <v>Ieteikt riskus ar AI</v>
+        <v>Vēl nav ģenerēti riski.</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>Add to Register</v>
+        <v>AI Risks Generated</v>
       </c>
       <c r="B743" t="str">
-        <v>إضافة إلى السجل</v>
+        <v>تم إنشاء مخاطر الذكاء الاصطناعي</v>
       </c>
       <c r="C743" t="str">
-        <v>Pievienot reģistram</v>
+        <v>AI riski ģenerēti</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>Please select a department first</v>
+        <v>AI Generation Failed</v>
       </c>
       <c r="B744" t="str">
-        <v>يرجى تحديد قسم أولاً</v>
+        <v>فشل إنشاء الذكاء الاصطناعي</v>
       </c>
       <c r="C744" t="str">
-        <v>Lūdzu, vispirms izvēlieties nodaļu</v>
+        <v>AI ģenerēšana neizdevās</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>Only Audit Head can suggest risks with AI</v>
+        <v>Communication with AI service failed.</v>
       </c>
       <c r="B745" t="str">
-        <v>فقط رئيس التدقيق يمكنه اقتراح المخاطر بالذكاء الاصطناعي</v>
+        <v>فشل الاتصال بخدمة الذكاء الاصطناعي.</v>
       </c>
       <c r="C745" t="str">
-        <v>Tikai audita vadītājs var ieteikt riskus ar AI</v>
+        <v>Saziņa ar AI servisu neizdevās.</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>Only Audit Head can add risks to register</v>
+        <v>Please try again later.</v>
       </c>
       <c r="B746" t="str">
-        <v>فقط رئيس التدقيق يمكنه إضافة المخاطر إلى السجل</v>
+        <v>يرجى المحاولة مرة أخرى لاحقاً.</v>
       </c>
       <c r="C746" t="str">
-        <v>Tikai audita vadītājs var pievienot riskus reģistram</v>
+        <v>Lūdzu, mēģiniet vēlreiz vēlāk.</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>Failed to check status</v>
+        <v>Go to Risk Register</v>
       </c>
       <c r="B747" t="str">
-        <v>فشل في التحقق من الحالة</v>
+        <v>الذهاب إلى سجل المخاطر</v>
       </c>
       <c r="C747" t="str">
-        <v>Neizdevās pārbaudīt statusu</v>
+        <v>Doties uz risku reģistru</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>Remove risk</v>
+        <v>Add to Risk Register</v>
       </c>
       <c r="B748" t="str">
-        <v>إزالة الخطر</v>
+        <v>إضافة إلى سجل المخاطر</v>
       </c>
       <c r="C748" t="str">
-        <v>Noņemt risku</v>
+        <v>Pievienot risku reģistram</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>Remove risks you do not need; only the remaining risks will be sent to the next step.</v>
+        <v>Adding...</v>
       </c>
       <c r="B749" t="str">
-        <v>أزل المخاطر التي لا تحتاجها؛ فقط المخاطر المتبقية سيتم إرسالها إلى الخطوة التالية.</v>
+        <v>جاري الإضافة...</v>
       </c>
       <c r="C749" t="str">
-        <v>Noņemiet riskus, kas nav nepieciešami; tikai atlikušie riski tiks nosūtīti nākamajā solī.</v>
+        <v>Pievieno...</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>Perform BIA</v>
+        <v>No risks to add</v>
       </c>
       <c r="B750" t="str">
-        <v>إجراء تحليل تأثير الأعمال</v>
+        <v>لا توجد مخاطر للإضافة</v>
       </c>
       <c r="C750" t="str">
-        <v>Veikt BIA</v>
+        <v>Nav risku, ko pievienot</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>Submit For Approval</v>
+        <v>Keep at least one risk before adding to the register.</v>
       </c>
       <c r="B751" t="str">
-        <v>إرسال للموافقة</v>
+        <v>احتفظ بخطر واحد على الأقل قبل الإضافة إلى السجل.</v>
       </c>
       <c r="C751" t="str">
-        <v>Iesniegt apstiprināšanai</v>
+        <v>Paturiet vismaz vienu risku pirms pievienošanas reģistram.</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>Status &amp; Approval</v>
+        <v>Risks have been added to the Risk Register.</v>
       </c>
       <c r="B752" t="str">
-        <v>الحالة والموافقة</v>
+        <v>تمت إضافة المخاطر إلى سجل المخاطر.</v>
       </c>
       <c r="C752" t="str">
-        <v>Statuss un apstiprinājums</v>
+        <v>Riski ir pievienoti risku reģistram.</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>Impact Assessment</v>
+        <v>Adding to risk register timed out. Please try again.</v>
       </c>
       <c r="B753" t="str">
-        <v>تقييم التأثير</v>
+        <v>انتهت مهلة الإضافة إلى سجل المخاطر. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C753" t="str">
-        <v>Ietekmes novērtējums</v>
+        <v>Pievienošanas reģistram laiks beidzās. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>Recovery Metrics</v>
+        <v>Failed to add risks to register</v>
       </c>
       <c r="B754" t="str">
-        <v>مقاييس الاستعادة</v>
+        <v>فشل في إضافة المخاطر إلى السجل</v>
       </c>
       <c r="C754" t="str">
-        <v>Atjaunošanas metrikas</v>
+        <v>Neizdevās pievienot riskus reģistram</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>BIA Rating</v>
+        <v>Failed to register risks</v>
       </c>
       <c r="B755" t="str">
-        <v>تصنيف تحليل تأثير الأعمال</v>
+        <v>فشل في تسجيل المخاطر</v>
       </c>
       <c r="C755" t="str">
-        <v>BIA vērtējums</v>
+        <v>Neizdevās reģistrēt riskus</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>Impact Rating</v>
+        <v>No risks in semantic result to register</v>
       </c>
       <c r="B756" t="str">
-        <v>تصنيف التأثير</v>
+        <v>لا توجد مخاطر في نتيجة البحث الدلالي للتسجيل</v>
       </c>
       <c r="C756" t="str">
-        <v>Ietekmes vērtējums</v>
+        <v>Nav risku semantiskajā rezultātā reģistrēšanai</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>Note: The highest rating will be taken</v>
+        <v>Failed to add to risk register</v>
       </c>
       <c r="B757" t="str">
-        <v>ملاحظة: سيتم أخذ أعلى تصنيف</v>
+        <v>فشل في الإضافة إلى سجل المخاطر</v>
       </c>
       <c r="C757" t="str">
-        <v>Piezīme: Tiks ņemts augstākais vērtējums</v>
+        <v>Neizdevās pievienot risku reģistram</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>RTO (Recovery Time Objective) - Hours</v>
+        <v>Add to Audit Plan</v>
       </c>
       <c r="B758" t="str">
-        <v>هدف وقت الاستعادة - ساعات</v>
+        <v>إضافة إلى خطة التدقيق</v>
       </c>
       <c r="C758" t="str">
-        <v>RTO (Atjaunošanas laika mērķis) - Stundas</v>
+        <v>Pievienot audita plānam</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>RPO (Recovery Point Objective) - Hours</v>
+        <v>Department information missing</v>
       </c>
       <c r="B759" t="str">
-        <v>هدف نقطة الاستعادة - ساعات</v>
+        <v>معلومات القسم مفقودة</v>
       </c>
       <c r="C759" t="str">
-        <v>RPO (Atjaunošanas punkta mērķis) - Stundas</v>
+        <v>Trūkst nodaļas informācijas</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>N/A</v>
+        <v>Failed to add to audit plan</v>
       </c>
       <c r="B760" t="str">
-        <v>غير متاح</v>
+        <v>فشل في الإضافة إلى خطة التدقيق</v>
       </c>
       <c r="C760" t="str">
-        <v>Nav piemērojams</v>
+        <v>Neizdevās pievienot audita plānam</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>KPI Details</v>
+        <v>Successfully added to Audit Planning!</v>
       </c>
       <c r="B761" t="str">
-        <v>تفاصيل مؤشرات الأداء</v>
+        <v>تمت الإضافة بنجاح إلى تخطيط التدقيق!</v>
       </c>
       <c r="C761" t="str">
-        <v>KPI detaļas</v>
+        <v>Veiksmīgi pievienots audita plānošanai!</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>Performance Chart</v>
+        <v>Already Added</v>
       </c>
       <c r="B762" t="str">
-        <v>مخطط الأداء</v>
+        <v>تمت الإضافة بالفعل</v>
       </c>
       <c r="C762" t="str">
-        <v>Veiktspējas diagramma</v>
+        <v>Jau pievienots</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>KPI Configuration</v>
+        <v>This audit plan has already been added to Audit Planning.</v>
       </c>
       <c r="B763" t="str">
-        <v>إعدادات مؤشرات الأداء</v>
+        <v>تمت إضافة خطة التدقيق هذه بالفعل إلى تخطيط التدقيق.</v>
       </c>
       <c r="C763" t="str">
-        <v>KPI konfigurācija</v>
+        <v>Šis audita plāns jau ir pievienots audita plānošanai.</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>KPI Records</v>
+        <v>Suggest Risks with AI</v>
       </c>
       <c r="B764" t="str">
-        <v>سجلات مؤشرات الأداء</v>
+        <v>اقتراح المخاطر بالذكاء الاصطناعي</v>
       </c>
       <c r="C764" t="str">
-        <v>KPI ieraksti</v>
+        <v>Ieteikt riskus ar AI</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>Year</v>
+        <v>Add to Register</v>
       </c>
       <c r="B765" t="str">
-        <v>السنة</v>
+        <v>إضافة إلى السجل</v>
       </c>
       <c r="C765" t="str">
-        <v>Gads</v>
+        <v>Pievienot reģistram</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>Achieved Value</v>
+        <v>Please select a department first</v>
       </c>
       <c r="B766" t="str">
-        <v>القيمة المحققة</v>
+        <v>يرجى تحديد قسم أولاً</v>
       </c>
       <c r="C766" t="str">
-        <v>Sasniegtā vērtība</v>
+        <v>Lūdzu, vispirms izvēlieties nodaļu</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>Expected Value</v>
+        <v>Only Audit Head can suggest risks with AI</v>
       </c>
       <c r="B767" t="str">
-        <v>القيمة المتوقعة</v>
+        <v>فقط رئيس التدقيق يمكنه اقتراح المخاطر بالذكاء الاصطناعي</v>
       </c>
       <c r="C767" t="str">
-        <v>Gaidāmā vērtība</v>
+        <v>Tikai audita vadītājs var ieteikt riskus ar AI</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>KPI Objective</v>
+        <v>Only Audit Head can add risks to register</v>
       </c>
       <c r="B768" t="str">
-        <v>هدف مؤشر الأداء</v>
+        <v>فقط رئيس التدقيق يمكنه إضافة المخاطر إلى السجل</v>
       </c>
       <c r="C768" t="str">
-        <v>KPI mērķis</v>
+        <v>Tikai audita vadītājs var pievienot riskus reģistram</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>Enter Objective</v>
+        <v>Failed to check status</v>
       </c>
       <c r="B769" t="str">
-        <v>أدخل الهدف</v>
+        <v>فشل في التحقق من الحالة</v>
       </c>
       <c r="C769" t="str">
-        <v>Ievadiet mērķi</v>
+        <v>Neizdevās pārbaudīt statusu</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>KPI Description</v>
+        <v>Remove risk</v>
       </c>
       <c r="B770" t="str">
-        <v>وصف مؤشر الأداء</v>
+        <v>إزالة الخطر</v>
       </c>
       <c r="C770" t="str">
-        <v>KPI apraksts</v>
+        <v>Noņemt risku</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>Enter Description</v>
+        <v>Remove risks you do not need; only the remaining risks will be sent to the next step.</v>
       </c>
       <c r="B771" t="str">
-        <v>أدخل الوصف</v>
+        <v>أزل المخاطر التي لا تحتاجها؛ فقط المخاطر المتبقية سيتم إرسالها إلى الخطوة التالية.</v>
       </c>
       <c r="C771" t="str">
-        <v>Ievadiet aprakstu</v>
+        <v>Noņemiet riskus, kas nav nepieciešami; tikai atlikušie riski tiks nosūtīti nākamajā solī.</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>KPI Data Source</v>
+        <v>Perform BIA</v>
       </c>
       <c r="B772" t="str">
-        <v>مصدر بيانات مؤشر الأداء</v>
+        <v>إجراء تحليل تأثير الأعمال</v>
       </c>
       <c r="C772" t="str">
-        <v>KPI datu avots</v>
+        <v>Veikt BIA</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>Enter Data Source</v>
+        <v>Submit For Approval</v>
       </c>
       <c r="B773" t="str">
-        <v>أدخل مصدر البيانات</v>
+        <v>إرسال للموافقة</v>
       </c>
       <c r="C773" t="str">
-        <v>Ievadiet datu avotu</v>
+        <v>Iesniegt apstiprināšanai</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>KPI Measurement Formula</v>
+        <v>Status &amp; Approval</v>
       </c>
       <c r="B774" t="str">
-        <v>صيغة قياس مؤشر الأداء</v>
+        <v>الحالة والموافقة</v>
       </c>
       <c r="C774" t="str">
-        <v>KPI mērīšanas formula</v>
+        <v>Statuss un apstiprinājums</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>Enter the KPI Calculation Formula</v>
+        <v>Impact Assessment</v>
       </c>
       <c r="B775" t="str">
-        <v>أدخل صيغة حساب مؤشر الأداء</v>
+        <v>تقييم التأثير</v>
       </c>
       <c r="C775" t="str">
-        <v>Ievadiet KPI aprēķina formulu</v>
+        <v>Ietekmes novērtējums</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>Targeted Achieved Value</v>
+        <v>Recovery Metrics</v>
       </c>
       <c r="B776" t="str">
-        <v>القيمة المستهدفة المحققة</v>
+        <v>مقاييس الاستعادة</v>
       </c>
       <c r="C776" t="str">
-        <v>Mērķa sasniegtā vērtība</v>
+        <v>Atjaunošanas metrikas</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>No KPI records yet</v>
+        <v>BIA Rating</v>
       </c>
       <c r="B777" t="str">
-        <v>لا توجد سجلات مؤشرات أداء بعد</v>
+        <v>تصنيف تحليل تأثير الأعمال</v>
       </c>
       <c r="C777" t="str">
-        <v>Vēl nav KPI ierakstu</v>
+        <v>BIA vērtējums</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>No KPI Data</v>
+        <v>Impact Rating</v>
       </c>
       <c r="B778" t="str">
-        <v>لا توجد بيانات مؤشرات أداء</v>
+        <v>تصنيف التأثير</v>
       </c>
       <c r="C778" t="str">
-        <v>Nav KPI datu</v>
+        <v>Ietekmes vērtējums</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>No processes have KPI measurement enabled...</v>
+        <v>Note: The highest rating will be taken</v>
       </c>
       <c r="B779" t="str">
-        <v>لم يتم تمكين قياس مؤشرات الأداء لأي عملية...</v>
+        <v>ملاحظة: سيتم أخذ أعلى تصنيف</v>
       </c>
       <c r="C779" t="str">
-        <v>Nevienam procesam nav iespējots KPI mērījums...</v>
+        <v>Piezīme: Tiks ņemts augstākais vērtējums</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>Unassigned</v>
+        <v>RTO (Recovery Time Objective) - Hours</v>
       </c>
       <c r="B780" t="str">
-        <v>غير معين</v>
+        <v>هدف وقت الاستعادة - ساعات</v>
       </c>
       <c r="C780" t="str">
-        <v>Nepiešķirts</v>
+        <v>RTO (Atjaunošanas laika mērķis) - Stundas</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>Primary</v>
+        <v>RPO (Recovery Point Objective) - Hours</v>
       </c>
       <c r="B781" t="str">
-        <v>أساسي</v>
+        <v>هدف نقطة الاستعادة - ساعات</v>
       </c>
       <c r="C781" t="str">
-        <v>Primārais</v>
+        <v>RPO (Atjaunošanas punkta mērķis) - Stundas</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>Supporting</v>
+        <v>N/A</v>
       </c>
       <c r="B782" t="str">
-        <v>داعم</v>
+        <v>غير متاح</v>
       </c>
       <c r="C782" t="str">
-        <v>Atbalsta</v>
+        <v>Nav piemērojams</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>Manual</v>
+        <v>KPI Details</v>
       </c>
       <c r="B783" t="str">
-        <v>يدوي</v>
+        <v>تفاصيل مؤشرات الأداء</v>
       </c>
       <c r="C783" t="str">
-        <v>Manuāls</v>
+        <v>KPI detaļas</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>Automated</v>
+        <v>Performance Chart</v>
       </c>
       <c r="B784" t="str">
-        <v>آلي</v>
+        <v>مخطط الأداء</v>
       </c>
       <c r="C784" t="str">
-        <v>Automatizēts</v>
+        <v>Veiktspējas diagramma</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>Manual + Automated</v>
+        <v>KPI Configuration</v>
       </c>
       <c r="B785" t="str">
-        <v>يدوي + آلي</v>
+        <v>إعدادات مؤشرات الأداء</v>
       </c>
       <c r="C785" t="str">
-        <v>Manuāls + Automatizēts</v>
+        <v>KPI konfigurācija</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>Branch Office</v>
+        <v>KPI Records</v>
       </c>
       <c r="B786" t="str">
-        <v>فرع المكتب</v>
+        <v>سجلات مؤشرات الأداء</v>
       </c>
       <c r="C786" t="str">
-        <v>Filiāles birojs</v>
+        <v>KPI ieraksti</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>Remote</v>
+        <v>Year</v>
       </c>
       <c r="B787" t="str">
-        <v>عن بعد</v>
+        <v>السنة</v>
       </c>
       <c r="C787" t="str">
-        <v>Attālināti</v>
+        <v>Gads</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>Select frequency</v>
+        <v>Achieved Value</v>
       </c>
       <c r="B788" t="str">
-        <v>اختر التكرار</v>
+        <v>القيمة المحققة</v>
       </c>
       <c r="C788" t="str">
-        <v>Izvēlieties biežumu</v>
+        <v>Sasniegtā vērtība</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>Bi-annually</v>
+        <v>Expected Value</v>
       </c>
       <c r="B789" t="str">
-        <v>نصف سنوي</v>
+        <v>القيمة المتوقعة</v>
       </c>
       <c r="C789" t="str">
-        <v>Divreiz gadā</v>
+        <v>Gaidāmā vērtība</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>As needed</v>
+        <v>KPI Objective</v>
       </c>
       <c r="B790" t="str">
-        <v>حسب الحاجة</v>
+        <v>هدف مؤشر الأداء</v>
       </c>
       <c r="C790" t="str">
-        <v>Pēc vajadzības</v>
+        <v>KPI mērķis</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>Imported</v>
+        <v>Enter Objective</v>
       </c>
       <c r="B791" t="str">
-        <v>تم استيراد</v>
+        <v>أدخل الهدف</v>
       </c>
       <c r="C791" t="str">
-        <v>Importēts</v>
+        <v>Ievadiet mērķi</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>categories</v>
+        <v>KPI Description</v>
       </c>
       <c r="B792" t="str">
-        <v>فئات</v>
+        <v>وصف مؤشر الأداء</v>
       </c>
       <c r="C792" t="str">
-        <v>kategorijas</v>
+        <v>KPI apraksts</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>sub-categories</v>
+        <v>Enter Description</v>
       </c>
       <c r="B793" t="str">
-        <v>فئات فرعية</v>
+        <v>أدخل الوصف</v>
       </c>
       <c r="C793" t="str">
-        <v>apakškategorijas</v>
+        <v>Ievadiet aprakstu</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>groups</v>
+        <v>KPI Data Source</v>
       </c>
       <c r="B794" t="str">
-        <v>مجموعات</v>
+        <v>مصدر بيانات مؤشر الأداء</v>
       </c>
       <c r="C794" t="str">
-        <v>grupas</v>
+        <v>KPI datu avots</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>sensitivities</v>
+        <v>Enter Data Source</v>
       </c>
       <c r="B795" t="str">
-        <v>حساسيات</v>
+        <v>أدخل مصدر البيانات</v>
       </c>
       <c r="C795" t="str">
-        <v>jutīgumi</v>
+        <v>Ievadiet datu avotu</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>assets</v>
+        <v>KPI Measurement Formula</v>
       </c>
       <c r="B796" t="str">
-        <v>أصول</v>
+        <v>صيغة قياس مؤشر الأداء</v>
       </c>
       <c r="C796" t="str">
-        <v>aktīvi</v>
+        <v>KPI mērīšanas formula</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>lifecycle statuses</v>
+        <v>Enter the KPI Calculation Formula</v>
       </c>
       <c r="B797" t="str">
-        <v>حالات دورة الحياة</v>
+        <v>أدخل صيغة حساب مؤشر الأداء</v>
       </c>
       <c r="C797" t="str">
-        <v>dzīves cikla statusi</v>
+        <v>Ievadiet KPI aprēķina formulu</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>failed</v>
+        <v>Targeted Achieved Value</v>
       </c>
       <c r="B798" t="str">
-        <v>فشل</v>
+        <v>القيمة المستهدفة المحققة</v>
       </c>
       <c r="C798" t="str">
-        <v>neizdevās</v>
+        <v>Mērķa sasniegtā vērtība</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
+        <v>No KPI records yet</v>
+      </c>
+      <c r="B799" t="str">
+        <v>لا توجد سجلات مؤشرات أداء بعد</v>
+      </c>
+      <c r="C799" t="str">
+        <v>Vēl nav KPI ierakstu</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="str">
+        <v>No KPI Data</v>
+      </c>
+      <c r="B800" t="str">
+        <v>لا توجد بيانات مؤشرات أداء</v>
+      </c>
+      <c r="C800" t="str">
+        <v>Nav KPI datu</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="str">
+        <v>No processes have KPI measurement enabled...</v>
+      </c>
+      <c r="B801" t="str">
+        <v>لم يتم تمكين قياس مؤشرات الأداء لأي عملية...</v>
+      </c>
+      <c r="C801" t="str">
+        <v>Nevienam procesam nav iespējots KPI mērījums...</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="B802" t="str">
+        <v>غير معين</v>
+      </c>
+      <c r="C802" t="str">
+        <v>Nepiešķirts</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B803" t="str">
+        <v>أساسي</v>
+      </c>
+      <c r="C803" t="str">
+        <v>Primārais</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="str">
+        <v>Supporting</v>
+      </c>
+      <c r="B804" t="str">
+        <v>داعم</v>
+      </c>
+      <c r="C804" t="str">
+        <v>Atbalsta</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="B805" t="str">
+        <v>يدوي</v>
+      </c>
+      <c r="C805" t="str">
+        <v>Manuāls</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="str">
+        <v>Automated</v>
+      </c>
+      <c r="B806" t="str">
+        <v>آلي</v>
+      </c>
+      <c r="C806" t="str">
+        <v>Automatizēts</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="str">
+        <v>Manual + Automated</v>
+      </c>
+      <c r="B807" t="str">
+        <v>يدوي + آلي</v>
+      </c>
+      <c r="C807" t="str">
+        <v>Manuāls + Automatizēts</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="str">
+        <v>Branch Office</v>
+      </c>
+      <c r="B808" t="str">
+        <v>فرع المكتب</v>
+      </c>
+      <c r="C808" t="str">
+        <v>Filiāles birojs</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="B809" t="str">
+        <v>عن بعد</v>
+      </c>
+      <c r="C809" t="str">
+        <v>Attālināti</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="str">
+        <v>Select frequency</v>
+      </c>
+      <c r="B810" t="str">
+        <v>اختر التكرار</v>
+      </c>
+      <c r="C810" t="str">
+        <v>Izvēlieties biežumu</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="str">
+        <v>Bi-annually</v>
+      </c>
+      <c r="B811" t="str">
+        <v>نصف سنوي</v>
+      </c>
+      <c r="C811" t="str">
+        <v>Divreiz gadā</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="str">
+        <v>As needed</v>
+      </c>
+      <c r="B812" t="str">
+        <v>حسب الحاجة</v>
+      </c>
+      <c r="C812" t="str">
+        <v>Pēc vajadzības</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="str">
+        <v>Imported</v>
+      </c>
+      <c r="B813" t="str">
+        <v>تم استيراد</v>
+      </c>
+      <c r="C813" t="str">
+        <v>Importēts</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="str">
+        <v>categories</v>
+      </c>
+      <c r="B814" t="str">
+        <v>فئات</v>
+      </c>
+      <c r="C814" t="str">
+        <v>kategorijas</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="str">
+        <v>sub-categories</v>
+      </c>
+      <c r="B815" t="str">
+        <v>فئات فرعية</v>
+      </c>
+      <c r="C815" t="str">
+        <v>apakškategorijas</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="str">
+        <v>groups</v>
+      </c>
+      <c r="B816" t="str">
+        <v>مجموعات</v>
+      </c>
+      <c r="C816" t="str">
+        <v>grupas</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="str">
+        <v>sensitivities</v>
+      </c>
+      <c r="B817" t="str">
+        <v>حساسيات</v>
+      </c>
+      <c r="C817" t="str">
+        <v>jutīgumi</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="str">
+        <v>assets</v>
+      </c>
+      <c r="B818" t="str">
+        <v>أصول</v>
+      </c>
+      <c r="C818" t="str">
+        <v>aktīvi</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="str">
+        <v>lifecycle statuses</v>
+      </c>
+      <c r="B819" t="str">
+        <v>حالات دورة الحياة</v>
+      </c>
+      <c r="C819" t="str">
+        <v>dzīves cikla statusi</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="str">
+        <v>failed</v>
+      </c>
+      <c r="B820" t="str">
+        <v>فشل</v>
+      </c>
+      <c r="C820" t="str">
+        <v>neizdevās</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="str">
         <v>category not found</v>
       </c>
-      <c r="B799" t="str">
+      <c r="B821" t="str">
         <v>الفئة غير موجودة</v>
       </c>
-      <c r="C799" t="str">
+      <c r="C821" t="str">
         <v>kategorija nav atrasta</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="str">
+        <v>Please add a subscription plan to continue!</v>
+      </c>
+      <c r="B822" t="str">
+        <v>يرجى إضافة خطة اشتراك للمتابعة!</v>
+      </c>
+      <c r="C822" t="str">
+        <v>Lūdzu, pievienojiet abonēšanas plānu, lai turpinātu!</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="str">
+        <v>OK</v>
+      </c>
+      <c r="B823" t="str">
+        <v>حسناً</v>
+      </c>
+      <c r="C823" t="str">
+        <v>Labi</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="str">
+        <v>Please Enter the Customer Name</v>
+      </c>
+      <c r="B824" t="str">
+        <v>يرجى إدخال اسم العميل</v>
+      </c>
+      <c r="C824" t="str">
+        <v>Lūdzu, ievadiet klienta nosaukumu</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="str">
+        <v>Please Enter the Username</v>
+      </c>
+      <c r="B825" t="str">
+        <v>يرجى إدخال اسم المستخدم</v>
+      </c>
+      <c r="C825" t="str">
+        <v>Lūdzu, ievadiet lietotājvārdu</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="str">
+        <v>Please Enter the Email</v>
+      </c>
+      <c r="B826" t="str">
+        <v>يرجى إدخال البريد الإلكتروني</v>
+      </c>
+      <c r="C826" t="str">
+        <v>Lūdzu, ievadiet e-pastu</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="str">
+        <v>Password can not be empty</v>
+      </c>
+      <c r="B827" t="str">
+        <v>لا يمكن أن تكون كلمة المرور فارغة</v>
+      </c>
+      <c r="C827" t="str">
+        <v>Parole nedrīkst būt tukša</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="str">
+        <v>Please enter the subscription start date.</v>
+      </c>
+      <c r="B828" t="str">
+        <v>يرجى إدخال تاريخ بدء الاشتراك.</v>
+      </c>
+      <c r="C828" t="str">
+        <v>Lūdzu, ievadiet abonēšanas sākuma datumu.</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="str">
+        <v>Expiry date is required and should be greater than the start date!</v>
+      </c>
+      <c r="B829" t="str">
+        <v>تاريخ الانتهاء مطلوب ويجب أن يكون أكبر من تاريخ البدء!</v>
+      </c>
+      <c r="C829" t="str">
+        <v>Derīguma termiņš ir obligāts un tam jābūt lielākam par sākuma datumu!</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="str">
+        <v>Please enter the maximum allowed frameworks.</v>
+      </c>
+      <c r="B830" t="str">
+        <v>يرجى إدخال الحد الأقصى للأطر المسموح بها.</v>
+      </c>
+      <c r="C830" t="str">
+        <v>Lūdzu, ievadiet maksimāli atļauto ietvaru skaitu.</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="str">
+        <v>Please enter the maximum allowed accounts.</v>
+      </c>
+      <c r="B831" t="str">
+        <v>يرجى إدخال الحد الأقصى للحسابات المسموح بها.</v>
+      </c>
+      <c r="C831" t="str">
+        <v>Lūdzu, ievadiet maksimāli atļauto kontu skaitu.</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="str">
+        <v>Status is required!</v>
+      </c>
+      <c r="B832" t="str">
+        <v>الحالة مطلوبة!</v>
+      </c>
+      <c r="C832" t="str">
+        <v>Statuss ir obligāts!</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="str">
+        <v>Subscription plan has expired, kindly contact VerifAI support</v>
+      </c>
+      <c r="B833" t="str">
+        <v>انتهت صلاحية خطة الاشتراك، يرجى التواصل مع دعم VerifAI</v>
+      </c>
+      <c r="C833" t="str">
+        <v>Abonēšanas plāns ir beidzies, lūdzu, sazinieties ar VerifAI atbalstu</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="str">
+        <v>You don't have an active Subscription plan, kindly contact VerifAI support</v>
+      </c>
+      <c r="B834" t="str">
+        <v>ليس لديك خطة اشتراك نشطة، يرجى التواصل مع دعم VerifAI</v>
+      </c>
+      <c r="C834" t="str">
+        <v>Jums nav aktīva abonēšanas plāna, lūdzu, sazinieties ar VerifAI atbalstu</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="str">
+        <v>Maximum accounts limit reached. Your plan allows</v>
+      </c>
+      <c r="B835" t="str">
+        <v>تم الوصول إلى الحد الأقصى للحسابات. خطتك تسمح بـ</v>
+      </c>
+      <c r="C835" t="str">
+        <v>Sasniegts maksimālais kontu limits. Jūsu plāns atļauj</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="str">
+        <v>accounts</v>
+      </c>
+      <c r="B836" t="str">
+        <v>حسابات</v>
+      </c>
+      <c r="C836" t="str">
+        <v>kontus</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="str">
+        <v>Kindly contact VerifAI support to upgrade your plan.</v>
+      </c>
+      <c r="B837" t="str">
+        <v>يرجى التواصل مع دعم VerifAI لترقية خطتك.</v>
+      </c>
+      <c r="C837" t="str">
+        <v>Lūdzu, sazinieties ar VerifAI atbalstu, lai uzlabotu savu plānu.</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="str">
+        <v>Maximum frameworks limit reached. Your plan allows</v>
+      </c>
+      <c r="B838" t="str">
+        <v>تم الوصول إلى الحد الأقصى للأطر. خطتك تسمح بـ</v>
+      </c>
+      <c r="C838" t="str">
+        <v>Sasniegts maksimālais ietvaru limits. Jūsu plāns atļauj</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="str">
+        <v>frameworks</v>
+      </c>
+      <c r="B839" t="str">
+        <v>أطر</v>
+      </c>
+      <c r="C839" t="str">
+        <v>ietvarus</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="str">
+        <v>Sign in with Google</v>
+      </c>
+      <c r="B840" t="str">
+        <v>تسجيل الدخول عبر Google</v>
+      </c>
+      <c r="C840" t="str">
+        <v>Pierakstīties ar Google</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="str">
+        <v>Sign in with Microsoft</v>
+      </c>
+      <c r="B841" t="str">
+        <v>تسجيل الدخول عبر Microsoft</v>
+      </c>
+      <c r="C841" t="str">
+        <v>Pierakstīties ar Microsoft</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="str">
+        <v>Or continue with</v>
+      </c>
+      <c r="B842" t="str">
+        <v>أو تابع باستخدام</v>
+      </c>
+      <c r="C842" t="str">
+        <v>Vai turpiniet ar</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="str">
+        <v>Redirecting...</v>
+      </c>
+      <c r="B843" t="str">
+        <v>جاري التحويل...</v>
+      </c>
+      <c r="C843" t="str">
+        <v>Pāradresē...</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="str">
+        <v>Your account is not registered. Please contact your administrator.</v>
+      </c>
+      <c r="B844" t="str">
+        <v>حسابك غير مسجل. يرجى الاتصال بالمسؤول.</v>
+      </c>
+      <c r="C844" t="str">
+        <v>Jūsu konts nav reģistrēts. Lūdzu, sazinieties ar administratoru.</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="str">
+        <v>Your email address is not verified with the provider.</v>
+      </c>
+      <c r="B845" t="str">
+        <v>لم يتم التحقق من عنوان بريدك الإلكتروني لدى المزود.</v>
+      </c>
+      <c r="C845" t="str">
+        <v>Jūsu e-pasta adrese nav verificēta pie pakalpojuma sniedzēja.</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="str">
+        <v>No email address was provided by the sign-in provider.</v>
+      </c>
+      <c r="B846" t="str">
+        <v>لم يتم توفير عنوان بريد إلكتروني من قبل مزود تسجيل الدخول.</v>
+      </c>
+      <c r="C846" t="str">
+        <v>Pierakstīšanās pakalpojuma sniedzējs nesniedza e-pasta adresi.</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="str">
+        <v>An error occurred during sign-in. Please try again.</v>
+      </c>
+      <c r="B847" t="str">
+        <v>حدث خطأ أثناء تسجيل الدخول. يرجى المحاولة مرة أخرى.</v>
+      </c>
+      <c r="C847" t="str">
+        <v>Pierakstīšanās laikā radās kļūda. Lūdzu, mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="str">
+        <v>This email is already associated with another sign-in method.</v>
+      </c>
+      <c r="B848" t="str">
+        <v>هذا البريد الإلكتروني مرتبط بالفعل بطريقة تسجيل دخول أخرى.</v>
+      </c>
+      <c r="C848" t="str">
+        <v>Šis e-pasts jau ir saistīts ar citu pierakstīšanās metodi.</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="str">
+        <v>SSO provider is not configured. Please contact your administrator.</v>
+      </c>
+      <c r="B849" t="str">
+        <v>مزود SSO غير مُهيأ. يرجى الاتصال بالمسؤول.</v>
+      </c>
+      <c r="C849" t="str">
+        <v>SSO pakalpojuma sniedzējs nav konfigurēts. Lūdzu, sazinieties ar administratoru.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C799"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C849"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1137"/>
+  <dimension ref="A1:C1403"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -12911,9 +12911,2935 @@
         <v>Nodaļas nosaukums</v>
       </c>
     </row>
+    <row r="1138">
+      <c r="A1138" t="str">
+        <v>Integrated Frameworks</v>
+      </c>
+      <c r="B1138" t="str">
+        <v>الأطر المتكاملة</v>
+      </c>
+      <c r="C1138" t="str">
+        <v>Integrētie ietvari</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="str">
+        <v>New Framework</v>
+      </c>
+      <c r="B1139" t="str">
+        <v>إطار جديد</v>
+      </c>
+      <c r="C1139" t="str">
+        <v>Jauns ietvars</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="str">
+        <v>New Framework (AI)</v>
+      </c>
+      <c r="B1140" t="str">
+        <v>إطار جديد (ذكاء اصطناعي)</v>
+      </c>
+      <c r="C1140" t="str">
+        <v>Jauns ietvars (MI)</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="str">
+        <v>Search frameworks...</v>
+      </c>
+      <c r="B1141" t="str">
+        <v>البحث في الأطر...</v>
+      </c>
+      <c r="C1141" t="str">
+        <v>Meklēt ietvarus...</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="str">
+        <v>All Statuses</v>
+      </c>
+      <c r="B1142" t="str">
+        <v>جميع الحالات</v>
+      </c>
+      <c r="C1142" t="str">
+        <v>Visi statusi</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="str">
+        <v>Grouping</v>
+      </c>
+      <c r="B1143" t="str">
+        <v>التصنيف</v>
+      </c>
+      <c r="C1143" t="str">
+        <v>Grupēšana</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="str">
+        <v>Function Grouping</v>
+      </c>
+      <c r="B1144" t="str">
+        <v>تصنيف الوظائف</v>
+      </c>
+      <c r="C1144" t="str">
+        <v>Funkciju grupēšana</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="str">
+        <v>No controls linked yet</v>
+      </c>
+      <c r="B1145" t="str">
+        <v>لا توجد ضوابط مرتبطة بعد</v>
+      </c>
+      <c r="C1145" t="str">
+        <v>Vēl nav saistītu kontroles pasākumu</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="str">
+        <v>Link controls to requirements in the framework to see them here</v>
+      </c>
+      <c r="B1146" t="str">
+        <v>اربط الضوابط بالمتطلبات في الإطار لرؤيتها هنا</v>
+      </c>
+      <c r="C1146" t="str">
+        <v>Saistiet kontroles pasākumus ar prasībām ietvarā, lai tos redzētu šeit</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="str">
+        <v>Policies</v>
+      </c>
+      <c r="B1147" t="str">
+        <v>السياسات</v>
+      </c>
+      <c r="C1147" t="str">
+        <v>Politikas</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="str">
+        <v>All Requirements</v>
+      </c>
+      <c r="B1148" t="str">
+        <v>جميع المتطلبات</v>
+      </c>
+      <c r="C1148" t="str">
+        <v>Visas prasības</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="str">
+        <v>SOA</v>
+      </c>
+      <c r="B1149" t="str">
+        <v>بيان التطبيق</v>
+      </c>
+      <c r="C1149" t="str">
+        <v>SOA</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="str">
+        <v>Audit Logs</v>
+      </c>
+      <c r="B1150" t="str">
+        <v>سجلات التدقيق</v>
+      </c>
+      <c r="C1150" t="str">
+        <v>Audita žurnāli</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="str">
+        <v>Search requirements...</v>
+      </c>
+      <c r="B1151" t="str">
+        <v>البحث في المتطلبات...</v>
+      </c>
+      <c r="C1151" t="str">
+        <v>Meklēt prasības...</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="str">
+        <v>New Requirement</v>
+      </c>
+      <c r="B1152" t="str">
+        <v>متطلب جديد</v>
+      </c>
+      <c r="C1152" t="str">
+        <v>Jauna prasība</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="B1153" t="str">
+        <v>جزئي</v>
+      </c>
+      <c r="C1153" t="str">
+        <v>Daļējs</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="str">
+        <v>requirements</v>
+      </c>
+      <c r="B1154" t="str">
+        <v>متطلبات</v>
+      </c>
+      <c r="C1154" t="str">
+        <v>prasības</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="str">
+        <v>Requirement</v>
+      </c>
+      <c r="B1155" t="str">
+        <v>المتطلب</v>
+      </c>
+      <c r="C1155" t="str">
+        <v>Prasība</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="str">
+        <v>Requirement Name</v>
+      </c>
+      <c r="B1156" t="str">
+        <v>اسم المتطلب</v>
+      </c>
+      <c r="C1156" t="str">
+        <v>Prasības nosaukums</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="str">
+        <v>Requirement Category</v>
+      </c>
+      <c r="B1157" t="str">
+        <v>فئة المتطلب</v>
+      </c>
+      <c r="C1157" t="str">
+        <v>Prasības kategorija</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="str">
+        <v>Requirement Code</v>
+      </c>
+      <c r="B1158" t="str">
+        <v>رمز المتطلب</v>
+      </c>
+      <c r="C1158" t="str">
+        <v>Prasības kods</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="str">
+        <v>Requirement Description</v>
+      </c>
+      <c r="B1159" t="str">
+        <v>وصف المتطلب</v>
+      </c>
+      <c r="C1159" t="str">
+        <v>Prasības apraksts</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="str">
+        <v>Requirement Type</v>
+      </c>
+      <c r="B1160" t="str">
+        <v>نوع المتطلب</v>
+      </c>
+      <c r="C1160" t="str">
+        <v>Prasības veids</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="str">
+        <v>Chapter Type</v>
+      </c>
+      <c r="B1161" t="str">
+        <v>نوع الفصل</v>
+      </c>
+      <c r="C1161" t="str">
+        <v>Nodaļas veids</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="str">
+        <v>Add Requirement</v>
+      </c>
+      <c r="B1162" t="str">
+        <v>إضافة متطلب</v>
+      </c>
+      <c r="C1162" t="str">
+        <v>Pievienot prasību</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="str">
+        <v>Update Requirement</v>
+      </c>
+      <c r="B1163" t="str">
+        <v>تحديث المتطلب</v>
+      </c>
+      <c r="C1163" t="str">
+        <v>Atjaunināt prasību</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="str">
+        <v>Mandatory</v>
+      </c>
+      <c r="B1164" t="str">
+        <v>إلزامي</v>
+      </c>
+      <c r="C1164" t="str">
+        <v>Obligāts</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="str">
+        <v>Additional</v>
+      </c>
+      <c r="B1165" t="str">
+        <v>إضافي</v>
+      </c>
+      <c r="C1165" t="str">
+        <v>Papildu</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="str">
+        <v>Process Domain</v>
+      </c>
+      <c r="B1166" t="str">
+        <v>مجال العمليات</v>
+      </c>
+      <c r="C1166" t="str">
+        <v>Procesu domēns</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="str">
+        <v>Technical Domain</v>
+      </c>
+      <c r="B1167" t="str">
+        <v>المجال التقني</v>
+      </c>
+      <c r="C1167" t="str">
+        <v>Tehniskais domēns</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="str">
+        <v>Applicability</v>
+      </c>
+      <c r="B1168" t="str">
+        <v>قابلية التطبيق</v>
+      </c>
+      <c r="C1168" t="str">
+        <v>Piemērojamība</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="str">
+        <v>Implementation</v>
+      </c>
+      <c r="B1169" t="str">
+        <v>التنفيذ</v>
+      </c>
+      <c r="C1169" t="str">
+        <v>Ieviešana</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="str">
+        <v>Linked Controls</v>
+      </c>
+      <c r="B1170" t="str">
+        <v>الضوابط المرتبطة</v>
+      </c>
+      <c r="C1170" t="str">
+        <v>Saistītās kontroles</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="str">
+        <v>Link</v>
+      </c>
+      <c r="B1171" t="str">
+        <v>ربط</v>
+      </c>
+      <c r="C1171" t="str">
+        <v>Saistīt</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="str">
+        <v>No controls found</v>
+      </c>
+      <c r="B1172" t="str">
+        <v>لم يتم العثور على ضوابط</v>
+      </c>
+      <c r="C1172" t="str">
+        <v>Kontroles nav atrastas</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="str">
+        <v>Control Select</v>
+      </c>
+      <c r="B1173" t="str">
+        <v>اختيار الضوابط</v>
+      </c>
+      <c r="C1173" t="str">
+        <v>Kontroles izvēle</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="str">
+        <v>All Functions</v>
+      </c>
+      <c r="B1174" t="str">
+        <v>جميع الوظائف</v>
+      </c>
+      <c r="C1174" t="str">
+        <v>Visas funkcijas</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="str">
+        <v>Search by code, name</v>
+      </c>
+      <c r="B1175" t="str">
+        <v>البحث بالرمز أو الاسم</v>
+      </c>
+      <c r="C1175" t="str">
+        <v>Meklēt pēc koda, nosaukuma</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="str">
+        <v>Exception Code</v>
+      </c>
+      <c r="B1176" t="str">
+        <v>رمز الاستثناء</v>
+      </c>
+      <c r="C1176" t="str">
+        <v>Izņēmuma kods</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="str">
+        <v>Exception Name</v>
+      </c>
+      <c r="B1177" t="str">
+        <v>اسم الاستثناء</v>
+      </c>
+      <c r="C1177" t="str">
+        <v>Izņēmuma nosaukums</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="str">
+        <v>Description/Justification</v>
+      </c>
+      <c r="B1178" t="str">
+        <v>الوصف/المبرر</v>
+      </c>
+      <c r="C1178" t="str">
+        <v>Apraksts/Pamatojums</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="str">
+        <v>Provide justification for this exception</v>
+      </c>
+      <c r="B1179" t="str">
+        <v>قدم مبرراً لهذا الاستثناء</v>
+      </c>
+      <c r="C1179" t="str">
+        <v>Sniedziet pamatojumu šim izņēmumam</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="str">
+        <v>Authorised</v>
+      </c>
+      <c r="B1180" t="str">
+        <v>مصرح به</v>
+      </c>
+      <c r="C1180" t="str">
+        <v>Autorizēts</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="str">
+        <v>Submitted for Closure</v>
+      </c>
+      <c r="B1181" t="str">
+        <v>مقدم للإغلاق</v>
+      </c>
+      <c r="C1181" t="str">
+        <v>Iesniegts slēgšanai</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="str">
+        <v>Risk Accepted</v>
+      </c>
+      <c r="B1182" t="str">
+        <v>المخاطر مقبولة</v>
+      </c>
+      <c r="C1182" t="str">
+        <v>Risks pieņemts</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="str">
+        <v>Enter exception name</v>
+      </c>
+      <c r="B1183" t="str">
+        <v>أدخل اسم الاستثناء</v>
+      </c>
+      <c r="C1183" t="str">
+        <v>Ievadiet izņēmuma nosaukumu</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="str">
+        <v>Partial Compliant</v>
+      </c>
+      <c r="B1184" t="str">
+        <v>متوافق جزئياً</v>
+      </c>
+      <c r="C1184" t="str">
+        <v>Daļēji atbilstošs</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="str">
+        <v>No Requirements</v>
+      </c>
+      <c r="B1185" t="str">
+        <v>لا توجد متطلبات</v>
+      </c>
+      <c r="C1185" t="str">
+        <v>Nav prasību</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="str">
+        <v>Add your first requirement to get started.</v>
+      </c>
+      <c r="B1186" t="str">
+        <v>أضف أول متطلب للبدء.</v>
+      </c>
+      <c r="C1186" t="str">
+        <v>Pievienojiet savu pirmo prasību, lai sāktu.</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="str">
+        <v>Search logs...</v>
+      </c>
+      <c r="B1187" t="str">
+        <v>البحث في السجلات...</v>
+      </c>
+      <c r="C1187" t="str">
+        <v>Meklēt žurnālos...</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="str">
+        <v>All Actions</v>
+      </c>
+      <c r="B1188" t="str">
+        <v>جميع الإجراءات</v>
+      </c>
+      <c r="C1188" t="str">
+        <v>Visas darbības</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="str">
+        <v>Linked</v>
+      </c>
+      <c r="B1189" t="str">
+        <v>مرتبط</v>
+      </c>
+      <c r="C1189" t="str">
+        <v>Saistīts</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="str">
+        <v>Unlinked</v>
+      </c>
+      <c r="B1190" t="str">
+        <v>غير مرتبط</v>
+      </c>
+      <c r="C1190" t="str">
+        <v>Atsaistīts</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="str">
+        <v>Created</v>
+      </c>
+      <c r="B1191" t="str">
+        <v>تم الإنشاء</v>
+      </c>
+      <c r="C1191" t="str">
+        <v>Izveidots</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="str">
+        <v>Updated</v>
+      </c>
+      <c r="B1192" t="str">
+        <v>تم التحديث</v>
+      </c>
+      <c r="C1192" t="str">
+        <v>Atjaunināts</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="str">
+        <v>Deleted</v>
+      </c>
+      <c r="B1193" t="str">
+        <v>تم الحذف</v>
+      </c>
+      <c r="C1193" t="str">
+        <v>Dzēsts</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="str">
+        <v>Exported</v>
+      </c>
+      <c r="B1194" t="str">
+        <v>تم التصدير</v>
+      </c>
+      <c r="C1194" t="str">
+        <v>Eksportēts</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="str">
+        <v>SOA report exported successfully</v>
+      </c>
+      <c r="B1195" t="str">
+        <v>تم تصدير تقرير بيان التطبيق بنجاح</v>
+      </c>
+      <c r="C1195" t="str">
+        <v>SOA atskaite veiksmīgi eksportēta</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="str">
+        <v>Audit logs exported successfully</v>
+      </c>
+      <c r="B1196" t="str">
+        <v>تم تصدير سجلات التدقيق بنجاح</v>
+      </c>
+      <c r="C1196" t="str">
+        <v>Audita žurnāli veiksmīgi eksportēti</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="str">
+        <v>No audit logs match your search.</v>
+      </c>
+      <c r="B1197" t="str">
+        <v>لا توجد سجلات تدقيق تطابق بحثك.</v>
+      </c>
+      <c r="C1197" t="str">
+        <v>Neviens audita ieraksts neatbilst jūsu meklējumam.</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="str">
+        <v>No requirements match your search.</v>
+      </c>
+      <c r="B1198" t="str">
+        <v>لا توجد متطلبات تطابق بحثك.</v>
+      </c>
+      <c r="C1198" t="str">
+        <v>Neviena prasība neatbilst jūsu meklējumam.</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="str">
+        <v>No requirements match your filters.</v>
+      </c>
+      <c r="B1199" t="str">
+        <v>لا توجد متطلبات تطابق عوامل التصفية.</v>
+      </c>
+      <c r="C1199" t="str">
+        <v>Neviena prasība neatbilst jūsu filtriem.</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="str">
+        <v>Requirement name should not be empty.</v>
+      </c>
+      <c r="B1200" t="str">
+        <v>يجب ألا يكون اسم المتطلب فارغاً.</v>
+      </c>
+      <c r="C1200" t="str">
+        <v>Prasības nosaukums nedrīkst būt tukšs.</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="str">
+        <v>Requirement category should not be empty.</v>
+      </c>
+      <c r="B1201" t="str">
+        <v>يجب ألا تكون فئة المتطلب فارغة.</v>
+      </c>
+      <c r="C1201" t="str">
+        <v>Prasības kategorija nedrīkst būt tukša.</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="str">
+        <v>Requirement code should not be empty.</v>
+      </c>
+      <c r="B1202" t="str">
+        <v>يجب ألا يكون رمز المتطلب فارغاً.</v>
+      </c>
+      <c r="C1202" t="str">
+        <v>Prasības kods nedrīkst būt tukšs.</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="str">
+        <v>Enter Name</v>
+      </c>
+      <c r="B1203" t="str">
+        <v>أدخل الاسم</v>
+      </c>
+      <c r="C1203" t="str">
+        <v>Ievadiet nosaukumu</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="str">
+        <v>Enter Category</v>
+      </c>
+      <c r="B1204" t="str">
+        <v>أدخل الفئة</v>
+      </c>
+      <c r="C1204" t="str">
+        <v>Ievadiet kategoriju</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="str">
+        <v>Enter Code</v>
+      </c>
+      <c r="B1205" t="str">
+        <v>أدخل الرمز</v>
+      </c>
+      <c r="C1205" t="str">
+        <v>Ievadiet kodu</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="str">
+        <v>Type here</v>
+      </c>
+      <c r="B1206" t="str">
+        <v>اكتب هنا</v>
+      </c>
+      <c r="C1206" t="str">
+        <v>Rakstiet šeit</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="str">
+        <v>To add a requirement to this framework, please accurately fill in the fields below.</v>
+      </c>
+      <c r="B1207" t="str">
+        <v>لإضافة متطلب إلى هذا الإطار، يرجى ملء الحقول أدناه بدقة.</v>
+      </c>
+      <c r="C1207" t="str">
+        <v>Lai pievienotu prasību šim ietvaram, lūdzu, precīzi aizpildiet zemāk esošos laukus.</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="str">
+        <v>Applicable</v>
+      </c>
+      <c r="B1208" t="str">
+        <v>قابل للتطبيق</v>
+      </c>
+      <c r="C1208" t="str">
+        <v>Piemērojams</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="str">
+        <v>Justification</v>
+      </c>
+      <c r="B1209" t="str">
+        <v>المبرر</v>
+      </c>
+      <c r="C1209" t="str">
+        <v>Pamatojums</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="str">
+        <v>Enter justification...</v>
+      </c>
+      <c r="B1210" t="str">
+        <v>أدخل المبرر...</v>
+      </c>
+      <c r="C1210" t="str">
+        <v>Ievadiet pamatojumu...</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="str">
+        <v>Impl. Status</v>
+      </c>
+      <c r="B1211" t="str">
+        <v>حالة التنفيذ</v>
+      </c>
+      <c r="C1211" t="str">
+        <v>Ievieš. statuss</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="str">
+        <v>No SOA data available to export</v>
+      </c>
+      <c r="B1212" t="str">
+        <v>لا توجد بيانات بيان التطبيق للتصدير</v>
+      </c>
+      <c r="C1212" t="str">
+        <v>Nav SOA datu eksportēšanai</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="str">
+        <v>No audit logs available to export</v>
+      </c>
+      <c r="B1213" t="str">
+        <v>لا توجد سجلات تدقيق للتصدير</v>
+      </c>
+      <c r="C1213" t="str">
+        <v>Nav audita žurnālu eksportēšanai</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="str">
+        <v>Framework Not Subscribed</v>
+      </c>
+      <c r="B1214" t="str">
+        <v>الإطار غير مشترك</v>
+      </c>
+      <c r="C1214" t="str">
+        <v>Ietvars nav abonēts</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="str">
+        <v>You do not have access to this framework. Please subscribe to view its contents.</v>
+      </c>
+      <c r="B1215" t="str">
+        <v>ليس لديك صلاحية الوصول إلى هذا الإطار. يرجى الاشتراك لعرض محتوياته.</v>
+      </c>
+      <c r="C1215" t="str">
+        <v>Jums nav piekļuves šim ietvaram. Lūdzu, abonējiet, lai skatītu tā saturu.</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="str">
+        <v>Loading framework...</v>
+      </c>
+      <c r="B1216" t="str">
+        <v>جاري تحميل الإطار...</v>
+      </c>
+      <c r="C1216" t="str">
+        <v>Ielādē ietvaru...</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="str">
+        <v>Framework not found</v>
+      </c>
+      <c r="B1217" t="str">
+        <v>لم يتم العثور على الإطار</v>
+      </c>
+      <c r="C1217" t="str">
+        <v>Ietvars nav atrasts</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="str">
+        <v>The requested framework could not be loaded.</v>
+      </c>
+      <c r="B1218" t="str">
+        <v>تعذر تحميل الإطار المطلوب.</v>
+      </c>
+      <c r="C1218" t="str">
+        <v>Pieprasīto ietvaru nevarēja ielādēt.</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="str">
+        <v>Framework Details</v>
+      </c>
+      <c r="B1219" t="str">
+        <v>تفاصيل الإطار</v>
+      </c>
+      <c r="C1219" t="str">
+        <v>Ietvara detaļas</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="str">
+        <v>Date &amp; Time</v>
+      </c>
+      <c r="B1220" t="str">
+        <v>التاريخ والوقت</v>
+      </c>
+      <c r="C1220" t="str">
+        <v>Datums un laiks</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="str">
+        <v>Target</v>
+      </c>
+      <c r="B1221" t="str">
+        <v>الهدف</v>
+      </c>
+      <c r="C1221" t="str">
+        <v>Mērķis</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="str">
+        <v>Details</v>
+      </c>
+      <c r="B1222" t="str">
+        <v>التفاصيل</v>
+      </c>
+      <c r="C1222" t="str">
+        <v>Detaļas</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="str">
+        <v>Unlink control</v>
+      </c>
+      <c r="B1223" t="str">
+        <v>إلغاء ربط الضابط</v>
+      </c>
+      <c r="C1223" t="str">
+        <v>Atsaistīt kontroli</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="str">
+        <v>Add Exception</v>
+      </c>
+      <c r="B1224" t="str">
+        <v>إضافة استثناء</v>
+      </c>
+      <c r="C1224" t="str">
+        <v>Pievienot izņēmumu</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="str">
+        <v>Please enter the reason for exception</v>
+      </c>
+      <c r="B1225" t="str">
+        <v>يرجى إدخال سبب الاستثناء</v>
+      </c>
+      <c r="C1225" t="str">
+        <v>Lūdzu, ievadiet izņēmuma iemeslu</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="str">
+        <v>Please select the enddate</v>
+      </c>
+      <c r="B1226" t="str">
+        <v>يرجى اختيار تاريخ النهاية</v>
+      </c>
+      <c r="C1226" t="str">
+        <v>Lūdzu, izvēlieties beigu datumu</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="str">
+        <v>Search by name or code...</v>
+      </c>
+      <c r="B1227" t="str">
+        <v>البحث بالاسم أو الرمز...</v>
+      </c>
+      <c r="C1227" t="str">
+        <v>Meklēt pēc nosaukuma vai koda...</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="str">
+        <v>No items match your search</v>
+      </c>
+      <c r="B1228" t="str">
+        <v>لا توجد عناصر تطابق بحثك</v>
+      </c>
+      <c r="C1228" t="str">
+        <v>Neviens elements neatbilst jūsu meklējumam</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="str">
+        <v>No items found for this framework</v>
+      </c>
+      <c r="B1229" t="str">
+        <v>لم يتم العثور على عناصر لهذا الإطار</v>
+      </c>
+      <c r="C1229" t="str">
+        <v>Šim ietvaram nav atrasts neviens elements</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="str">
+        <v>Try adjusting your search term</v>
+      </c>
+      <c r="B1230" t="str">
+        <v>حاول تعديل مصطلح البحث</v>
+      </c>
+      <c r="C1230" t="str">
+        <v>Mēģiniet mainīt meklēšanas terminu</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="str">
+        <v>Items will appear here once linked to this framework</v>
+      </c>
+      <c r="B1231" t="str">
+        <v>ستظهر العناصر هنا بمجرد ربطها بهذا الإطار</v>
+      </c>
+      <c r="C1231" t="str">
+        <v>Elementi parādīsies šeit, kad tie tiks saistīti ar šo ietvaru</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="str">
+        <v>No items</v>
+      </c>
+      <c r="B1232" t="str">
+        <v>لا توجد عناصر</v>
+      </c>
+      <c r="C1232" t="str">
+        <v>Nav elementu</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="str">
+        <v>Search by name, domain or assignee...</v>
+      </c>
+      <c r="B1233" t="str">
+        <v>البحث بالاسم أو المجال أو المسؤول...</v>
+      </c>
+      <c r="C1233" t="str">
+        <v>Meklēt pēc nosaukuma, domēna vai atbildīgā...</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="str">
+        <v>Evidence Code</v>
+      </c>
+      <c r="B1234" t="str">
+        <v>رمز الدليل</v>
+      </c>
+      <c r="C1234" t="str">
+        <v>Pierādījuma kods</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="str">
+        <v>No evidence matches your search</v>
+      </c>
+      <c r="B1235" t="str">
+        <v>لا توجد أدلة تطابق بحثك</v>
+      </c>
+      <c r="C1235" t="str">
+        <v>Neviens pierādījums neatbilst jūsu meklējumam</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="str">
+        <v>No evidence records found for this framework</v>
+      </c>
+      <c r="B1236" t="str">
+        <v>لم يتم العثور على سجلات أدلة لهذا الإطار</v>
+      </c>
+      <c r="C1236" t="str">
+        <v>Šim ietvaram nav atrasti pierādījumu ieraksti</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="str">
+        <v>Try adjusting your search</v>
+      </c>
+      <c r="B1237" t="str">
+        <v>حاول تعديل البحث</v>
+      </c>
+      <c r="C1237" t="str">
+        <v>Mēģiniet mainīt meklējumu</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="str">
+        <v>Link evidence to controls in the framework to see them here</v>
+      </c>
+      <c r="B1238" t="str">
+        <v>اربط الأدلة بالضوابط في الإطار لرؤيتها هنا</v>
+      </c>
+      <c r="C1238" t="str">
+        <v>Saistiet pierādījumus ar kontrolēm ietvaram, lai tos redzētu šeit</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="str">
+        <v>No evidence</v>
+      </c>
+      <c r="B1239" t="str">
+        <v>لا توجد أدلة</v>
+      </c>
+      <c r="C1239" t="str">
+        <v>Nav pierādījumu</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="str">
+        <v>Showing {start} to {end} of {total}</v>
+      </c>
+      <c r="B1240" t="str">
+        <v>عرض {start} إلى {end} من {total}</v>
+      </c>
+      <c r="C1240" t="str">
+        <v>Rāda {start} līdz {end} no {total}</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="str">
+        <v>Create Integrated Framework</v>
+      </c>
+      <c r="B1241" t="str">
+        <v>إنشاء إطار متكامل</v>
+      </c>
+      <c r="C1241" t="str">
+        <v>Izveidot integrētu ietvaru</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="str">
+        <v>Create Integrated Framework (AI)</v>
+      </c>
+      <c r="B1242" t="str">
+        <v>إنشاء إطار متكامل (ذكاء اصطناعي)</v>
+      </c>
+      <c r="C1242" t="str">
+        <v>Izveidot integrētu ietvaru (AI)</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="str">
+        <v>Custom framework will be automatically added in grey color to differentiate between Subscribed Frameworks.</v>
+      </c>
+      <c r="B1243" t="str">
+        <v>سيتم إضافة الإطار المخصص تلقائياً باللون الرمادي للتمييز بين الأطر المشترك بها.</v>
+      </c>
+      <c r="C1243" t="str">
+        <v>Pielāgotais ietvars tiks automātiski pievienots pelēkā krāsā, lai atšķirtu no abonētajiem ietvariem.</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="str">
+        <v>Integrated Framework Name</v>
+      </c>
+      <c r="B1244" t="str">
+        <v>اسم الإطار المتكامل</v>
+      </c>
+      <c r="C1244" t="str">
+        <v>Integrētā ietvara nosaukums</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="str">
+        <v>Framework Type</v>
+      </c>
+      <c r="B1245" t="str">
+        <v>نوع الإطار</v>
+      </c>
+      <c r="C1245" t="str">
+        <v>Ietvara veids</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="str">
+        <v>Enter framework name</v>
+      </c>
+      <c r="B1246" t="str">
+        <v>أدخل اسم الإطار</v>
+      </c>
+      <c r="C1246" t="str">
+        <v>Ievadiet ietvara nosaukumu</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="str">
+        <v>Enter code</v>
+      </c>
+      <c r="B1247" t="str">
+        <v>أدخل الرمز</v>
+      </c>
+      <c r="C1247" t="str">
+        <v>Ievadiet kodu</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="str">
+        <v>Enter country</v>
+      </c>
+      <c r="B1248" t="str">
+        <v>أدخل الدولة</v>
+      </c>
+      <c r="C1248" t="str">
+        <v>Ievadiet valsti</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="str">
+        <v>Enter industry</v>
+      </c>
+      <c r="B1249" t="str">
+        <v>أدخل الصناعة</v>
+      </c>
+      <c r="C1249" t="str">
+        <v>Ievadiet nozari</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="str">
+        <v>Create &amp; Import</v>
+      </c>
+      <c r="B1250" t="str">
+        <v>إنشاء واستيراد</v>
+      </c>
+      <c r="C1250" t="str">
+        <v>Izveidot un importēt</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="str">
+        <v>Upload Support Document</v>
+      </c>
+      <c r="B1251" t="str">
+        <v>رفع مستند داعم</v>
+      </c>
+      <c r="C1251" t="str">
+        <v>Augšupielādēt atbalsta dokumentu</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="str">
+        <v>Click here, or drop files here to upload.</v>
+      </c>
+      <c r="B1252" t="str">
+        <v>انقر هنا، أو اسحب الملفات هنا للرفع.</v>
+      </c>
+      <c r="C1252" t="str">
+        <v>Noklikšķiniet šeit vai velciet failus šeit, lai augšupielādētu.</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="str">
+        <v>Import Framework Requirements</v>
+      </c>
+      <c r="B1253" t="str">
+        <v>استيراد متطلبات الإطار</v>
+      </c>
+      <c r="C1253" t="str">
+        <v>Importēt ietvara prasības</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="str">
+        <v>Upload an Excel file (.xlsx) containing your framework requirements.</v>
+      </c>
+      <c r="B1254" t="str">
+        <v>ارفع ملف إكسل (.xlsx) يحتوي على متطلبات الإطار.</v>
+      </c>
+      <c r="C1254" t="str">
+        <v>Augšupielādējiet Excel failu (.xlsx) ar ietvara prasībām.</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="str">
+        <v>You can download the sample template to see the required format.</v>
+      </c>
+      <c r="B1255" t="str">
+        <v>يمكنك تحميل القالب النموذجي لمعرفة التنسيق المطلوب.</v>
+      </c>
+      <c r="C1255" t="str">
+        <v>Varat lejupielādēt parauga veidni, lai redzētu nepieciešamo formātu.</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="str">
+        <v>Download Sample Template</v>
+      </c>
+      <c r="B1256" t="str">
+        <v>تحميل القالب النموذجي</v>
+      </c>
+      <c r="C1256" t="str">
+        <v>Lejupielādēt parauga veidni</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="str">
+        <v>Use this template to ensure correct column headers</v>
+      </c>
+      <c r="B1257" t="str">
+        <v>استخدم هذا القالب لضمان عناوين الأعمدة الصحيحة</v>
+      </c>
+      <c r="C1257" t="str">
+        <v>Izmantojiet šo veidni, lai nodrošinātu pareizus kolonnu virsrakstus</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="str">
+        <v>Upload Document</v>
+      </c>
+      <c r="B1258" t="str">
+        <v>رفع مستند</v>
+      </c>
+      <c r="C1258" t="str">
+        <v>Augšupielādēt dokumentu</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="str">
+        <v>Click to upload or drag and drop</v>
+      </c>
+      <c r="B1259" t="str">
+        <v>انقر للرفع أو اسحب وأفلت</v>
+      </c>
+      <c r="C1259" t="str">
+        <v>Noklikšķiniet, lai augšupielādētu, vai velciet un nometiet</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="str">
+        <v>Excel files only (.xlsx)</v>
+      </c>
+      <c r="B1260" t="str">
+        <v>ملفات إكسل فقط (.xlsx)</v>
+      </c>
+      <c r="C1260" t="str">
+        <v>Tikai Excel faili (.xlsx)</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="str">
+        <v>Required Column Headers:</v>
+      </c>
+      <c r="B1261" t="str">
+        <v>عناوين الأعمدة المطلوبة:</v>
+      </c>
+      <c r="C1261" t="str">
+        <v>Nepieciešamie kolonnu virsraksti:</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="str">
+        <v>Control Mapping</v>
+      </c>
+      <c r="B1262" t="str">
+        <v>ربط الضوابط</v>
+      </c>
+      <c r="C1262" t="str">
+        <v>Kontroles kartēšana</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="str">
+        <v>Skip</v>
+      </c>
+      <c r="B1263" t="str">
+        <v>تخطي</v>
+      </c>
+      <c r="C1263" t="str">
+        <v>Izlaist</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="str">
+        <v>Import Successful</v>
+      </c>
+      <c r="B1264" t="str">
+        <v>تم الاستيراد بنجاح</v>
+      </c>
+      <c r="C1264" t="str">
+        <v>Imports veiksmīgs</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="str">
+        <v>Import Failed</v>
+      </c>
+      <c r="B1265" t="str">
+        <v>فشل الاستيراد</v>
+      </c>
+      <c r="C1265" t="str">
+        <v>Imports neizdevās</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="str">
+        <v>Failed to import requirements</v>
+      </c>
+      <c r="B1266" t="str">
+        <v>فشل استيراد المتطلبات</v>
+      </c>
+      <c r="C1266" t="str">
+        <v>Neizdevās importēt prasības</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="str">
+        <v>Template Downloaded</v>
+      </c>
+      <c r="B1267" t="str">
+        <v>تم تحميل القالب</v>
+      </c>
+      <c r="C1267" t="str">
+        <v>Veidne lejupielādēta</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="str">
+        <v>Sample template has been downloaded successfully</v>
+      </c>
+      <c r="B1268" t="str">
+        <v>تم تحميل القالب النموذجي بنجاح</v>
+      </c>
+      <c r="C1268" t="str">
+        <v>Parauga veidne veiksmīgi lejupielādēta</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="str">
+        <v>Failed to download template</v>
+      </c>
+      <c r="B1269" t="str">
+        <v>فشل تحميل القالب</v>
+      </c>
+      <c r="C1269" t="str">
+        <v>Neizdevās lejupielādēt veidni</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="str">
+        <v>Invalid File</v>
+      </c>
+      <c r="B1270" t="str">
+        <v>ملف غير صالح</v>
+      </c>
+      <c r="C1270" t="str">
+        <v>Nederīgs fails</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="str">
+        <v>Please upload an Excel file (.xlsx)</v>
+      </c>
+      <c r="B1271" t="str">
+        <v>يرجى رفع ملف إكسل (.xlsx)</v>
+      </c>
+      <c r="C1271" t="str">
+        <v>Lūdzu, augšupielādējiet Excel failu (.xlsx)</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="str">
+        <v>Please enter Country</v>
+      </c>
+      <c r="B1272" t="str">
+        <v>يرجى إدخال الدولة</v>
+      </c>
+      <c r="C1272" t="str">
+        <v>Lūdzu, ievadiet valsti</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="str">
+        <v>Please enter Industry</v>
+      </c>
+      <c r="B1273" t="str">
+        <v>يرجى إدخال الصناعة</v>
+      </c>
+      <c r="C1273" t="str">
+        <v>Lūdzu, ievadiet nozari</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="str">
+        <v>Generating... (AI)</v>
+      </c>
+      <c r="B1274" t="str">
+        <v>جاري الإنشاء... (ذكاء اصطناعي)</v>
+      </c>
+      <c r="C1274" t="str">
+        <v>Ģenerē... (AI)</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="str">
+        <v>AI framework generation failed</v>
+      </c>
+      <c r="B1275" t="str">
+        <v>فشل إنشاء الإطار بالذكاء الاصطناعي</v>
+      </c>
+      <c r="C1275" t="str">
+        <v>AI ietvara ģenerēšana neizdevās</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="str">
+        <v>Polling failed</v>
+      </c>
+      <c r="B1276" t="str">
+        <v>فشل الاستعلام</v>
+      </c>
+      <c r="C1276" t="str">
+        <v>Aptauja neizdevās</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="str">
+        <v>Framework created successfully</v>
+      </c>
+      <c r="B1277" t="str">
+        <v>تم إنشاء الإطار بنجاح</v>
+      </c>
+      <c r="C1277" t="str">
+        <v>Ietvars veiksmīgi izveidots</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="str">
+        <v>Some warnings occurred during import. See details below.</v>
+      </c>
+      <c r="B1278" t="str">
+        <v>حدثت بعض التحذيرات أثناء الاستيراد. انظر التفاصيل أدناه.</v>
+      </c>
+      <c r="C1278" t="str">
+        <v>Importēšanas laikā radās daži brīdinājumi. Skatiet detaļas zemāk.</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="str">
+        <v>Warnings</v>
+      </c>
+      <c r="B1279" t="str">
+        <v>تحذيرات</v>
+      </c>
+      <c r="C1279" t="str">
+        <v>Brīdinājumi</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="str">
+        <v>Validation Errors</v>
+      </c>
+      <c r="B1280" t="str">
+        <v>أخطاء التحقق</v>
+      </c>
+      <c r="C1280" t="str">
+        <v>Validācijas kļūdas</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="str">
+        <v>Row</v>
+      </c>
+      <c r="B1281" t="str">
+        <v>صف</v>
+      </c>
+      <c r="C1281" t="str">
+        <v>Rinda</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="str">
+        <v>Country</v>
+      </c>
+      <c r="B1282" t="str">
+        <v>الدولة</v>
+      </c>
+      <c r="C1282" t="str">
+        <v>Valsts</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="str">
+        <v>Industry</v>
+      </c>
+      <c r="B1283" t="str">
+        <v>الصناعة</v>
+      </c>
+      <c r="C1283" t="str">
+        <v>Nozare</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="str">
+        <v>Total Controls</v>
+      </c>
+      <c r="B1284" t="str">
+        <v>إجمالي الضوابط</v>
+      </c>
+      <c r="C1284" t="str">
+        <v>Kopējās kontroles</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="str">
+        <v>Controls by Framework</v>
+      </c>
+      <c r="B1285" t="str">
+        <v>الضوابط حسب الإطار</v>
+      </c>
+      <c r="C1285" t="str">
+        <v>Kontroles pēc ietvara</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="str">
+        <v>Control Question</v>
+      </c>
+      <c r="B1286" t="str">
+        <v>سؤال الضابطة</v>
+      </c>
+      <c r="C1286" t="str">
+        <v>Kontroles jautājums</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="str">
+        <v>Control Information</v>
+      </c>
+      <c r="B1287" t="str">
+        <v>معلومات الضابطة</v>
+      </c>
+      <c r="C1287" t="str">
+        <v>Kontroles informācija</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="str">
+        <v>Domain Code</v>
+      </c>
+      <c r="B1288" t="str">
+        <v>رمز المجال</v>
+      </c>
+      <c r="C1288" t="str">
+        <v>Domēna kods</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="str">
+        <v>Create New Domain</v>
+      </c>
+      <c r="B1289" t="str">
+        <v>إنشاء مجال جديد</v>
+      </c>
+      <c r="C1289" t="str">
+        <v>Izveidot jaunu domēnu</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="str">
+        <v>Enter control name</v>
+      </c>
+      <c r="B1290" t="str">
+        <v>أدخل اسم الضابطة</v>
+      </c>
+      <c r="C1290" t="str">
+        <v>Ievadiet kontroles nosaukumu</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="str">
+        <v>Enter control question</v>
+      </c>
+      <c r="B1291" t="str">
+        <v>أدخل سؤال الضابطة</v>
+      </c>
+      <c r="C1291" t="str">
+        <v>Ievadiet kontroles jautājumu</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="str">
+        <v>Select grouping</v>
+      </c>
+      <c r="B1292" t="str">
+        <v>اختر التجميع</v>
+      </c>
+      <c r="C1292" t="str">
+        <v>Izvēlieties grupēšanu</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="str">
+        <v>Select assignee</v>
+      </c>
+      <c r="B1293" t="str">
+        <v>اختر المسؤول</v>
+      </c>
+      <c r="C1293" t="str">
+        <v>Izvēlieties atbildīgo</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="str">
+        <v>Assignment</v>
+      </c>
+      <c r="B1294" t="str">
+        <v>التعيين</v>
+      </c>
+      <c r="C1294" t="str">
+        <v>Piešķiršana</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="str">
+        <v>Review</v>
+      </c>
+      <c r="B1295" t="str">
+        <v>المراجعة</v>
+      </c>
+      <c r="C1295" t="str">
+        <v>Pārskatīšana</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="str">
+        <v>Assignment Details</v>
+      </c>
+      <c r="B1296" t="str">
+        <v>تفاصيل التعيين</v>
+      </c>
+      <c r="C1296" t="str">
+        <v>Piešķiršanas detaļas</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="str">
+        <v>Review Information</v>
+      </c>
+      <c r="B1297" t="str">
+        <v>مراجعة المعلومات</v>
+      </c>
+      <c r="C1297" t="str">
+        <v>Pārskatīt informāciju</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="str">
+        <v>e.g., GOV</v>
+      </c>
+      <c r="B1298" t="str">
+        <v>مثال: GOV</v>
+      </c>
+      <c r="C1298" t="str">
+        <v>piem., GOV</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="str">
+        <v>e.g., Governance</v>
+      </c>
+      <c r="B1299" t="str">
+        <v>مثال: الحوكمة</v>
+      </c>
+      <c r="C1299" t="str">
+        <v>piem., Pārvaldība</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="str">
+        <v>Please enter the question</v>
+      </c>
+      <c r="B1300" t="str">
+        <v>يرجى إدخال السؤال</v>
+      </c>
+      <c r="C1300" t="str">
+        <v>Lūdzu, ievadiet jautājumu</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="str">
+        <v>Please select the Functional Grouping</v>
+      </c>
+      <c r="B1301" t="str">
+        <v>يرجى اختيار التجميع الوظيفي</v>
+      </c>
+      <c r="C1301" t="str">
+        <v>Lūdzu, izvēlieties funkcionālo grupēšanu</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="str">
+        <v>No department reviewers found</v>
+      </c>
+      <c r="B1302" t="str">
+        <v>لم يتم العثور على مراجعين للقسم</v>
+      </c>
+      <c r="C1302" t="str">
+        <v>Nav atrasti nodaļas pārskatītāji</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="str">
+        <v>Information Security Vault</v>
+      </c>
+      <c r="B1303" t="str">
+        <v>خزنة أمن المعلومات</v>
+      </c>
+      <c r="C1303" t="str">
+        <v>Informācijas drošības glabātuve</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="str">
+        <v>Import Controls</v>
+      </c>
+      <c r="B1304" t="str">
+        <v>استيراد الضوابط</v>
+      </c>
+      <c r="C1304" t="str">
+        <v>Importēt kontroles</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="str">
+        <v>Upload a CSV file to import controls. You can download a template to see the required format.</v>
+      </c>
+      <c r="B1305" t="str">
+        <v>ارفع ملف CSV لاستيراد الضوابط. يمكنك تنزيل قالب لمعرفة التنسيق المطلوب.</v>
+      </c>
+      <c r="C1305" t="str">
+        <v>Augšupielādējiet CSV failu, lai importētu kontroles. Varat lejupielādēt veidni, lai redzētu nepieciešamo formātu.</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="str">
+        <v>Search by code, name, department...</v>
+      </c>
+      <c r="B1306" t="str">
+        <v>البحث بالرمز، الاسم، القسم...</v>
+      </c>
+      <c r="C1306" t="str">
+        <v>Meklēt pēc koda, nosaukuma, nodaļas...</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="str">
+        <v>Link Governance Documents</v>
+      </c>
+      <c r="B1307" t="str">
+        <v>ربط مستندات الحوكمة</v>
+      </c>
+      <c r="C1307" t="str">
+        <v>Saistīt pārvaldības dokumentus</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="str">
+        <v>Link Governance</v>
+      </c>
+      <c r="B1308" t="str">
+        <v>ربط الحوكمة</v>
+      </c>
+      <c r="C1308" t="str">
+        <v>Saistīt pārvaldību</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="str">
+        <v>Link Selected</v>
+      </c>
+      <c r="B1309" t="str">
+        <v>ربط المحدد</v>
+      </c>
+      <c r="C1309" t="str">
+        <v>Saistīt izvēlētos</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="str">
+        <v>Search by code or name...</v>
+      </c>
+      <c r="B1310" t="str">
+        <v>البحث بالرمز أو الاسم...</v>
+      </c>
+      <c r="C1310" t="str">
+        <v>Meklēt pēc koda vai nosaukuma...</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="str">
+        <v>selected</v>
+      </c>
+      <c r="B1311" t="str">
+        <v>محدد</v>
+      </c>
+      <c r="C1311" t="str">
+        <v>izvēlēts</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="str">
+        <v>No Documents</v>
+      </c>
+      <c r="B1312" t="str">
+        <v>لا توجد مستندات</v>
+      </c>
+      <c r="C1312" t="str">
+        <v>Nav dokumentu</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="str">
+        <v>Upload your first document to get started.</v>
+      </c>
+      <c r="B1313" t="str">
+        <v>ارفع أول مستند للبدء.</v>
+      </c>
+      <c r="C1313" t="str">
+        <v>Augšupielādējiet pirmo dokumentu, lai sāktu.</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="str">
+        <v>Drag and drop files here</v>
+      </c>
+      <c r="B1314" t="str">
+        <v>اسحب وأفلت الملفات هنا</v>
+      </c>
+      <c r="C1314" t="str">
+        <v>Velciet un nometiet failus šeit</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="str">
+        <v>or click to browse from your computer</v>
+      </c>
+      <c r="B1315" t="str">
+        <v>أو انقر للتصفح من جهازك</v>
+      </c>
+      <c r="C1315" t="str">
+        <v>vai noklikšķiniet, lai pārlūkotu no datora</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="str">
+        <v>Document ID</v>
+      </c>
+      <c r="B1316" t="str">
+        <v>معرّف المستند</v>
+      </c>
+      <c r="C1316" t="str">
+        <v>Dokumenta ID</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="str">
+        <v>Document Name</v>
+      </c>
+      <c r="B1317" t="str">
+        <v>اسم المستند</v>
+      </c>
+      <c r="C1317" t="str">
+        <v>Dokumenta nosaukums</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="str">
+        <v>Uploaded</v>
+      </c>
+      <c r="B1318" t="str">
+        <v>تاريخ الرفع</v>
+      </c>
+      <c r="C1318" t="str">
+        <v>Augšupielādēts</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="str">
+        <v>Edit Control</v>
+      </c>
+      <c r="B1319" t="str">
+        <v>تعديل الضابطة</v>
+      </c>
+      <c r="C1319" t="str">
+        <v>Rediģēt kontroli</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="str">
+        <v>Assigned To</v>
+      </c>
+      <c r="B1320" t="str">
+        <v>مُسند إلى</v>
+      </c>
+      <c r="C1320" t="str">
+        <v>Piešķirts</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="str">
+        <v>No risks linked</v>
+      </c>
+      <c r="B1321" t="str">
+        <v>لا توجد مخاطر مرتبطة</v>
+      </c>
+      <c r="C1321" t="str">
+        <v>Nav saistītu risku</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="str">
+        <v>No linked risks</v>
+      </c>
+      <c r="B1322" t="str">
+        <v>لا توجد مخاطر مرتبطة</v>
+      </c>
+      <c r="C1322" t="str">
+        <v>Nav saistītu risku</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="str">
+        <v>No linked exceptions</v>
+      </c>
+      <c r="B1323" t="str">
+        <v>لا توجد استثناءات مرتبطة</v>
+      </c>
+      <c r="C1323" t="str">
+        <v>Nav saistītu izņēmumu</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="str">
+        <v>No linked evidences</v>
+      </c>
+      <c r="B1324" t="str">
+        <v>لا توجد أدلة مرتبطة</v>
+      </c>
+      <c r="C1324" t="str">
+        <v>Nav saistītu pierādījumu</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="str">
+        <v>No linked requirements</v>
+      </c>
+      <c r="B1325" t="str">
+        <v>لا توجد متطلبات مرتبطة</v>
+      </c>
+      <c r="C1325" t="str">
+        <v>Nav saistītu prasību</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="str">
+        <v>No linked policies</v>
+      </c>
+      <c r="B1326" t="str">
+        <v>لا توجد سياسات مرتبطة</v>
+      </c>
+      <c r="C1326" t="str">
+        <v>Nav saistītu politiku</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="str">
+        <v>Select Risks</v>
+      </c>
+      <c r="B1327" t="str">
+        <v>اختر المخاطر</v>
+      </c>
+      <c r="C1327" t="str">
+        <v>Izvēlieties riskus</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="str">
+        <v>Select Requirements</v>
+      </c>
+      <c r="B1328" t="str">
+        <v>اختر المتطلبات</v>
+      </c>
+      <c r="C1328" t="str">
+        <v>Izvēlieties prasības</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="str">
+        <v>Select Policies</v>
+      </c>
+      <c r="B1329" t="str">
+        <v>اختر السياسات</v>
+      </c>
+      <c r="C1329" t="str">
+        <v>Izvēlieties politikas</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="str">
+        <v>Select Evidence</v>
+      </c>
+      <c r="B1330" t="str">
+        <v>اختر الأدلة</v>
+      </c>
+      <c r="C1330" t="str">
+        <v>Izvēlieties pierādījumus</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="str">
+        <v>Select Exceptions</v>
+      </c>
+      <c r="B1331" t="str">
+        <v>اختر الاستثناءات</v>
+      </c>
+      <c r="C1331" t="str">
+        <v>Izvēlieties izņēmumus</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="str">
+        <v>Linked Requirement</v>
+      </c>
+      <c r="B1332" t="str">
+        <v>المتطلبات المرتبطة</v>
+      </c>
+      <c r="C1332" t="str">
+        <v>Saistītā prasība</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="str">
+        <v>Linked Requirements</v>
+      </c>
+      <c r="B1333" t="str">
+        <v>المتطلبات المرتبطة</v>
+      </c>
+      <c r="C1333" t="str">
+        <v>Saistītās prasības</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="str">
+        <v>Add Selected</v>
+      </c>
+      <c r="B1334" t="str">
+        <v>إضافة المحدد</v>
+      </c>
+      <c r="C1334" t="str">
+        <v>Pievienot izvēlētos</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="str">
+        <v>Add Approver</v>
+      </c>
+      <c r="B1335" t="str">
+        <v>إضافة معتمد</v>
+      </c>
+      <c r="C1335" t="str">
+        <v>Pievienot apstiprinātāju</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="str">
+        <v>Select Approver</v>
+      </c>
+      <c r="B1336" t="str">
+        <v>اختر المعتمد</v>
+      </c>
+      <c r="C1336" t="str">
+        <v>Izvēlieties apstiprinātāju</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="str">
+        <v>Only Department Reviewers from the assigned department are shown.</v>
+      </c>
+      <c r="B1337" t="str">
+        <v>يتم عرض مراجعي القسم من القسم المعيّن فقط.</v>
+      </c>
+      <c r="C1337" t="str">
+        <v>Tiek rādīti tikai nodaļas pārskatītāji no piešķirtās nodaļas.</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="str">
+        <v>Select approver</v>
+      </c>
+      <c r="B1338" t="str">
+        <v>اختر المعتمد</v>
+      </c>
+      <c r="C1338" t="str">
+        <v>Izvēlieties apstiprinātāju</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="str">
+        <v>Linked Frameworks</v>
+      </c>
+      <c r="B1339" t="str">
+        <v>الأطر المرتبطة</v>
+      </c>
+      <c r="C1339" t="str">
+        <v>Saistītie ietvari</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="str">
+        <v>Policy Details</v>
+      </c>
+      <c r="B1340" t="str">
+        <v>تفاصيل السياسة</v>
+      </c>
+      <c r="C1340" t="str">
+        <v>Politikas detaļas</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="str">
+        <v>AI Review</v>
+      </c>
+      <c r="B1341" t="str">
+        <v>مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1341" t="str">
+        <v>AI pārskatīšana</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="str">
+        <v>AI Review has not been performed yet</v>
+      </c>
+      <c r="B1342" t="str">
+        <v>لم تتم مراجعة الذكاء الاصطناعي بعد</v>
+      </c>
+      <c r="C1342" t="str">
+        <v>AI pārskatīšana vēl nav veikta</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="str">
+        <v>Start an AI review to analyze this document</v>
+      </c>
+      <c r="B1343" t="str">
+        <v>ابدأ مراجعة بالذكاء الاصطناعي لتحليل هذا المستند</v>
+      </c>
+      <c r="C1343" t="str">
+        <v>Sāciet AI pārskatīšanu, lai analizētu šo dokumentu</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="str">
+        <v>Attachments</v>
+      </c>
+      <c r="B1344" t="str">
+        <v>المرفقات</v>
+      </c>
+      <c r="C1344" t="str">
+        <v>Pielikumi</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="str">
+        <v>Link from Vault</v>
+      </c>
+      <c r="B1345" t="str">
+        <v>ربط من الخزنة</v>
+      </c>
+      <c r="C1345" t="str">
+        <v>Saistīt no glabātuves</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="str">
+        <v>Link existing vault documents</v>
+      </c>
+      <c r="B1346" t="str">
+        <v>ربط مستندات الخزنة الحالية</v>
+      </c>
+      <c r="C1346" t="str">
+        <v>Saistīt esošos glabātuves dokumentus</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="str">
+        <v>Generate Policy Using AI</v>
+      </c>
+      <c r="B1347" t="str">
+        <v>إنشاء سياسة باستخدام الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1347" t="str">
+        <v>Ģenerēt politiku ar AI</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="str">
+        <v>Create document with AI assistance</v>
+      </c>
+      <c r="B1348" t="str">
+        <v>إنشاء مستند بمساعدة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1348" t="str">
+        <v>Izveidot dokumentu ar AI palīdzību</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="str">
+        <v>Upload Existing File</v>
+      </c>
+      <c r="B1349" t="str">
+        <v>رفع ملف موجود</v>
+      </c>
+      <c r="C1349" t="str">
+        <v>Augšupielādēt esošu failu</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="str">
+        <v>Upload document from your device</v>
+      </c>
+      <c r="B1350" t="str">
+        <v>رفع مستند من جهازك</v>
+      </c>
+      <c r="C1350" t="str">
+        <v>Augšupielādēt dokumentu no ierīces</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="str">
+        <v>Linked Documents</v>
+      </c>
+      <c r="B1351" t="str">
+        <v>المستندات المرتبطة</v>
+      </c>
+      <c r="C1351" t="str">
+        <v>Saistītie dokumenti</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="str">
+        <v>Linked Exception</v>
+      </c>
+      <c r="B1352" t="str">
+        <v>الاستثناء المرتبط</v>
+      </c>
+      <c r="C1352" t="str">
+        <v>Saistītais izņēmums</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="str">
+        <v>Linked Control</v>
+      </c>
+      <c r="B1353" t="str">
+        <v>الضابطة المرتبطة</v>
+      </c>
+      <c r="C1353" t="str">
+        <v>Saistītā kontrole</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="str">
+        <v>Link Control</v>
+      </c>
+      <c r="B1354" t="str">
+        <v>ربط ضابطة</v>
+      </c>
+      <c r="C1354" t="str">
+        <v>Saistīt kontroli</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="str">
+        <v>Control ID</v>
+      </c>
+      <c r="B1355" t="str">
+        <v>معرّف الضابطة</v>
+      </c>
+      <c r="C1355" t="str">
+        <v>Kontroles ID</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="str">
+        <v>No exceptions linked to this</v>
+      </c>
+      <c r="B1356" t="str">
+        <v>لا توجد استثناءات مرتبطة بهذا</v>
+      </c>
+      <c r="C1356" t="str">
+        <v>Nav izņēmumu saistītu ar šo</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="str">
+        <v>Link exceptions to track deviations</v>
+      </c>
+      <c r="B1357" t="str">
+        <v>ربط الاستثناءات لتتبع الانحرافات</v>
+      </c>
+      <c r="C1357" t="str">
+        <v>Saistīt izņēmumus, lai izsekotu novirzes</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="str">
+        <v>Link Exception</v>
+      </c>
+      <c r="B1358" t="str">
+        <v>ربط استثناء</v>
+      </c>
+      <c r="C1358" t="str">
+        <v>Saistīt izņēmumu</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="str">
+        <v>No documents linked to this</v>
+      </c>
+      <c r="B1359" t="str">
+        <v>لا توجد مستندات مرتبطة بهذا</v>
+      </c>
+      <c r="C1359" t="str">
+        <v>Nav dokumentu saistītu ar šo</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="str">
+        <v>Documents linked to this policy will appear here</v>
+      </c>
+      <c r="B1360" t="str">
+        <v>ستظهر المستندات المرتبطة بهذه السياسة هنا</v>
+      </c>
+      <c r="C1360" t="str">
+        <v>Ar šo politiku saistītie dokumenti parādīsies šeit</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="str">
+        <v>Start AI Review</v>
+      </c>
+      <c r="B1361" t="str">
+        <v>بدء مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1361" t="str">
+        <v>Sākt AI pārskatīšanu</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="str">
+        <v>Publish</v>
+      </c>
+      <c r="B1362" t="str">
+        <v>نشر</v>
+      </c>
+      <c r="C1362" t="str">
+        <v>Publicēt</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="str">
+        <v>Select recurrence</v>
+      </c>
+      <c r="B1363" t="str">
+        <v>اختر التكرار</v>
+      </c>
+      <c r="C1363" t="str">
+        <v>Izvēlieties atkārtošanos</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="str">
+        <v>Review Date</v>
+      </c>
+      <c r="B1364" t="str">
+        <v>تاريخ المراجعة</v>
+      </c>
+      <c r="C1364" t="str">
+        <v>Pārskatīšanas datums</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="str">
+        <v>Recurrence</v>
+      </c>
+      <c r="B1365" t="str">
+        <v>التكرار</v>
+      </c>
+      <c r="C1365" t="str">
+        <v>Atkārtošanās</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="str">
+        <v>Edit Assignee</v>
+      </c>
+      <c r="B1366" t="str">
+        <v>تعديل المكلّف</v>
+      </c>
+      <c r="C1366" t="str">
+        <v>Rediģēt pilnvaroto</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="str">
+        <v>Select Assignee</v>
+      </c>
+      <c r="B1367" t="str">
+        <v>اختر المكلّف</v>
+      </c>
+      <c r="C1367" t="str">
+        <v>Izvēlieties pilnvaroto</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="str">
+        <v>Only Department Contributors and Department Reviewers from the assigned department are shown.</v>
+      </c>
+      <c r="B1368" t="str">
+        <v>يتم عرض مساهمي ومراجعي القسم من القسم المعيّن فقط.</v>
+      </c>
+      <c r="C1368" t="str">
+        <v>Tiek rādīti tikai nodaļas līdzstrādnieki un pārskatītāji no piešķirtās nodaļas.</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="str">
+        <v>Approvers</v>
+      </c>
+      <c r="B1369" t="str">
+        <v>المعتمدون</v>
+      </c>
+      <c r="C1369" t="str">
+        <v>Apstiprinātāji</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="str">
+        <v>Evidence Request List</v>
+      </c>
+      <c r="B1370" t="str">
+        <v>قائمة طلبات الأدلة</v>
+      </c>
+      <c r="C1370" t="str">
+        <v>Pierādījumu pieprasījumu saraksts</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="str">
+        <v>Artifacts</v>
+      </c>
+      <c r="B1371" t="str">
+        <v>المستندات المرفقة</v>
+      </c>
+      <c r="C1371" t="str">
+        <v>Artefakti</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="str">
+        <v>New Evidence</v>
+      </c>
+      <c r="B1372" t="str">
+        <v>دليل جديد</v>
+      </c>
+      <c r="C1372" t="str">
+        <v>Jauns pierādījums</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="str">
+        <v>Evidence Name</v>
+      </c>
+      <c r="B1373" t="str">
+        <v>اسم الدليل</v>
+      </c>
+      <c r="C1373" t="str">
+        <v>Pierādījuma nosaukums</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="str">
+        <v>Issue Identified By</v>
+      </c>
+      <c r="B1374" t="str">
+        <v>تم تحديد المشكلة بواسطة</v>
+      </c>
+      <c r="C1374" t="str">
+        <v>Problēmu identificēja</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="str">
+        <v>Submitted</v>
+      </c>
+      <c r="B1375" t="str">
+        <v>تم التقديم</v>
+      </c>
+      <c r="C1375" t="str">
+        <v>Iesniegts</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="str">
+        <v>Evidence Requirement</v>
+      </c>
+      <c r="B1376" t="str">
+        <v>متطلبات الدليل</v>
+      </c>
+      <c r="C1376" t="str">
+        <v>Pierādījuma prasība</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="str">
+        <v>Enter evidence requirement</v>
+      </c>
+      <c r="B1377" t="str">
+        <v>أدخل متطلبات الدليل</v>
+      </c>
+      <c r="C1377" t="str">
+        <v>Ievadiet pierādījuma prasību</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="str">
+        <v>Select Controls to Link</v>
+      </c>
+      <c r="B1378" t="str">
+        <v>اختر الضوابط للربط</v>
+      </c>
+      <c r="C1378" t="str">
+        <v>Izvēlieties kontroles saistīšanai</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="str">
+        <v>Search controls...</v>
+      </c>
+      <c r="B1379" t="str">
+        <v>البحث في الضوابط...</v>
+      </c>
+      <c r="C1379" t="str">
+        <v>Meklēt kontroles...</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="str">
+        <v>All Groupings</v>
+      </c>
+      <c r="B1380" t="str">
+        <v>جميع التصنيفات</v>
+      </c>
+      <c r="C1380" t="str">
+        <v>Visas grupas</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="str">
+        <v>controls</v>
+      </c>
+      <c r="B1381" t="str">
+        <v>ضوابط</v>
+      </c>
+      <c r="C1381" t="str">
+        <v>kontroles</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="str">
+        <v>Selected Controls</v>
+      </c>
+      <c r="B1382" t="str">
+        <v>الضوابط المحددة</v>
+      </c>
+      <c r="C1382" t="str">
+        <v>Izvēlētās kontroles</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="str">
+        <v>Create Evidence</v>
+      </c>
+      <c r="B1383" t="str">
+        <v>إنشاء دليل</v>
+      </c>
+      <c r="C1383" t="str">
+        <v>Izveidot pierādījumu</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="str">
+        <v>Delete All Evidence</v>
+      </c>
+      <c r="B1384" t="str">
+        <v>حذف جميع الأدلة</v>
+      </c>
+      <c r="C1384" t="str">
+        <v>Dzēst visus pierādījumus</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="str">
+        <v>Are you sure you want to delete all evidence records? This action cannot be undone.</v>
+      </c>
+      <c r="B1385" t="str">
+        <v>هل أنت متأكد أنك تريد حذف جميع سجلات الأدلة؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C1385" t="str">
+        <v>Vai tiešām vēlaties dzēst visus pierādījumu ierakstus? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="str">
+        <v>Import Evidence</v>
+      </c>
+      <c r="B1386" t="str">
+        <v>استيراد الأدلة</v>
+      </c>
+      <c r="C1386" t="str">
+        <v>Importēt pierādījumus</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="str">
+        <v>Upload a CSV or Excel file to import evidence records.</v>
+      </c>
+      <c r="B1387" t="str">
+        <v>ارفع ملف CSV أو Excel لاستيراد سجلات الأدلة.</v>
+      </c>
+      <c r="C1387" t="str">
+        <v>Augšupielādējiet CSV vai Excel failu, lai importētu pierādījumu ierakstus.</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="str">
+        <v>Drag and drop a file here, or click to browse</v>
+      </c>
+      <c r="B1388" t="str">
+        <v>اسحب وأفلت ملفاً هنا، أو انقر للتصفح</v>
+      </c>
+      <c r="C1388" t="str">
+        <v>Velciet un nometiet failu šeit vai noklikšķiniet, lai pārlūkotu</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="str">
+        <v>Search by Evidence Code, Name</v>
+      </c>
+      <c r="B1389" t="str">
+        <v>البحث برمز الدليل أو الاسم</v>
+      </c>
+      <c r="C1389" t="str">
+        <v>Meklēt pēc pierādījuma koda, nosaukuma</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="str">
+        <v>No evidences found</v>
+      </c>
+      <c r="B1390" t="str">
+        <v>لم يتم العثور على أدلة</v>
+      </c>
+      <c r="C1390" t="str">
+        <v>Nav atrasti pierādījumi</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="str">
+        <v>Link Evidences</v>
+      </c>
+      <c r="B1391" t="str">
+        <v>ربط الأدلة</v>
+      </c>
+      <c r="C1391" t="str">
+        <v>Saistīt pierādījumus</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="str">
+        <v>No evidence records found</v>
+      </c>
+      <c r="B1392" t="str">
+        <v>لم يتم العثور على سجلات أدلة</v>
+      </c>
+      <c r="C1392" t="str">
+        <v>Nav atrasti pierādījumu ieraksti</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="str">
+        <v>Create a new evidence record to get started</v>
+      </c>
+      <c r="B1393" t="str">
+        <v>أنشئ سجل دليل جديد للبدء</v>
+      </c>
+      <c r="C1393" t="str">
+        <v>Izveidojiet jaunu pierādījuma ierakstu, lai sāktu</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="str">
+        <v>Add Artifact</v>
+      </c>
+      <c r="B1394" t="str">
+        <v>إضافة مستند مرفق</v>
+      </c>
+      <c r="C1394" t="str">
+        <v>Pievienot artefaktu</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="str">
+        <v>AI Review Artifacts</v>
+      </c>
+      <c r="B1395" t="str">
+        <v>مراجعة المستندات بالذكاء الاصطناعي</v>
+      </c>
+      <c r="C1395" t="str">
+        <v>AI pārskatīt artefaktus</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="str">
+        <v>click to upload</v>
+      </c>
+      <c r="B1396" t="str">
+        <v>انقر للرفع</v>
+      </c>
+      <c r="C1396" t="str">
+        <v>noklikšķiniet, lai augšupielādētu</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="str">
+        <v>Supported formats: PDF, PNG, JPG, XLSX, DOC, DOCX</v>
+      </c>
+      <c r="B1397" t="str">
+        <v>الصيغ المدعومة: PDF، PNG، JPG، XLSX، DOC، DOCX</v>
+      </c>
+      <c r="C1397" t="str">
+        <v>Atbalstītie formāti: PDF, PNG, JPG, XLSX, DOC, DOCX</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="str">
+        <v>Uploaded Artifacts</v>
+      </c>
+      <c r="B1398" t="str">
+        <v>المستندات المرفقة المرفوعة</v>
+      </c>
+      <c r="C1398" t="str">
+        <v>Augšupielādētie artefakti</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="str">
+        <v>No artifacts uploaded yet</v>
+      </c>
+      <c r="B1399" t="str">
+        <v>لم يتم رفع مستندات مرفقة بعد</v>
+      </c>
+      <c r="C1399" t="str">
+        <v>Vēl nav augšupielādēti artefakti</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="str">
+        <v>Upload files above to get started</v>
+      </c>
+      <c r="B1400" t="str">
+        <v>ارفع الملفات أعلاه للبدء</v>
+      </c>
+      <c r="C1400" t="str">
+        <v>Augšupielādējiet failus iepriekš, lai sāktu</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="str">
+        <v>Link to Evidence</v>
+      </c>
+      <c r="B1401" t="str">
+        <v>ربط بالدليل</v>
+      </c>
+      <c r="C1401" t="str">
+        <v>Saistīt ar pierādījumu</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="str">
+        <v>Enter description</v>
+      </c>
+      <c r="B1402" t="str">
+        <v>أدخل الوصف</v>
+      </c>
+      <c r="C1402" t="str">
+        <v>Ievadiet aprakstu</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="str">
+        <v>Please select the recurrence</v>
+      </c>
+      <c r="B1403" t="str">
+        <v>يرجى اختيار التكرار</v>
+      </c>
+      <c r="C1403" t="str">
+        <v>Lūdzu izvēlieties atkārtošanos</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1403"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1403"/>
+  <dimension ref="A1:C1536"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -15837,9 +15837,1472 @@
         <v>Lūdzu izvēlieties atkārtošanos</v>
       </c>
     </row>
+    <row r="1404">
+      <c r="A1404" t="str">
+        <v>Jan</v>
+      </c>
+      <c r="B1404" t="str">
+        <v>يناير</v>
+      </c>
+      <c r="C1404" t="str">
+        <v>Jan</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="str">
+        <v>Feb</v>
+      </c>
+      <c r="B1405" t="str">
+        <v>فبراير</v>
+      </c>
+      <c r="C1405" t="str">
+        <v>Feb</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="str">
+        <v>Mar</v>
+      </c>
+      <c r="B1406" t="str">
+        <v>مارس</v>
+      </c>
+      <c r="C1406" t="str">
+        <v>Mar</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="str">
+        <v>Apr</v>
+      </c>
+      <c r="B1407" t="str">
+        <v>أبريل</v>
+      </c>
+      <c r="C1407" t="str">
+        <v>Apr</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="str">
+        <v>May</v>
+      </c>
+      <c r="B1408" t="str">
+        <v>مايو</v>
+      </c>
+      <c r="C1408" t="str">
+        <v>Mai</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="str">
+        <v>Jun</v>
+      </c>
+      <c r="B1409" t="str">
+        <v>يونيو</v>
+      </c>
+      <c r="C1409" t="str">
+        <v>Jūn</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="str">
+        <v>Jul</v>
+      </c>
+      <c r="B1410" t="str">
+        <v>يوليو</v>
+      </c>
+      <c r="C1410" t="str">
+        <v>Jūl</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="str">
+        <v>Aug</v>
+      </c>
+      <c r="B1411" t="str">
+        <v>أغسطس</v>
+      </c>
+      <c r="C1411" t="str">
+        <v>Aug</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="str">
+        <v>Sep</v>
+      </c>
+      <c r="B1412" t="str">
+        <v>سبتمبر</v>
+      </c>
+      <c r="C1412" t="str">
+        <v>Sep</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="B1413" t="str">
+        <v>أكتوبر</v>
+      </c>
+      <c r="C1413" t="str">
+        <v>Okt</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="str">
+        <v>Nov</v>
+      </c>
+      <c r="B1414" t="str">
+        <v>نوفمبر</v>
+      </c>
+      <c r="C1414" t="str">
+        <v>Nov</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="B1415" t="str">
+        <v>ديسمبر</v>
+      </c>
+      <c r="C1415" t="str">
+        <v>Dec</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="str">
+        <v>Jan–Mar</v>
+      </c>
+      <c r="B1416" t="str">
+        <v>يناير–مارس</v>
+      </c>
+      <c r="C1416" t="str">
+        <v>Jan–Mar</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="str">
+        <v>Apr–Jun</v>
+      </c>
+      <c r="B1417" t="str">
+        <v>أبريل–يونيو</v>
+      </c>
+      <c r="C1417" t="str">
+        <v>Apr–Jūn</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="str">
+        <v>Jul–Sep</v>
+      </c>
+      <c r="B1418" t="str">
+        <v>يوليو–سبتمبر</v>
+      </c>
+      <c r="C1418" t="str">
+        <v>Jūl–Sep</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="str">
+        <v>Oct–Dec</v>
+      </c>
+      <c r="B1419" t="str">
+        <v>أكتوبر–ديسمبر</v>
+      </c>
+      <c r="C1419" t="str">
+        <v>Okt–Dec</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="str">
+        <v>Jan–Jun</v>
+      </c>
+      <c r="B1420" t="str">
+        <v>يناير–يونيو</v>
+      </c>
+      <c r="C1420" t="str">
+        <v>Jan–Jūn</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="str">
+        <v>Jul–Dec</v>
+      </c>
+      <c r="B1421" t="str">
+        <v>يوليو–ديسمبر</v>
+      </c>
+      <c r="C1421" t="str">
+        <v>Jūl–Dec</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="str">
+        <v>Jan–Dec</v>
+      </c>
+      <c r="B1422" t="str">
+        <v>يناير–ديسمبر</v>
+      </c>
+      <c r="C1422" t="str">
+        <v>Jan–Dec</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="str">
+        <v>Organization Wide</v>
+      </c>
+      <c r="B1423" t="str">
+        <v>على مستوى المنظمة</v>
+      </c>
+      <c r="C1423" t="str">
+        <v>Organizācijas mērogā</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="str">
+        <v>No attachments for</v>
+      </c>
+      <c r="B1424" t="str">
+        <v>لا توجد مرفقات لـ</v>
+      </c>
+      <c r="C1424" t="str">
+        <v>Nav pielikumu par</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="str">
+        <v>No attachments</v>
+      </c>
+      <c r="B1425" t="str">
+        <v>لا توجد مرفقات</v>
+      </c>
+      <c r="C1425" t="str">
+        <v>Nav pielikumu</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="str">
+        <v>Evidence Details</v>
+      </c>
+      <c r="B1426" t="str">
+        <v>تفاصيل الدليل</v>
+      </c>
+      <c r="C1426" t="str">
+        <v>Pierādījuma detaļas</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="str">
+        <v>Evidence not found</v>
+      </c>
+      <c r="B1427" t="str">
+        <v>لم يتم العثور على الدليل</v>
+      </c>
+      <c r="C1427" t="str">
+        <v>Pierādījums nav atrasts</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="str">
+        <v>Artifact</v>
+      </c>
+      <c r="B1428" t="str">
+        <v>المستند المرفق</v>
+      </c>
+      <c r="C1428" t="str">
+        <v>Artefakts</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="str">
+        <v>Review date</v>
+      </c>
+      <c r="B1429" t="str">
+        <v>تاريخ المراجعة</v>
+      </c>
+      <c r="C1429" t="str">
+        <v>Pārskatīšanas datums</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="str">
+        <v>Select review date</v>
+      </c>
+      <c r="B1430" t="str">
+        <v>اختر تاريخ المراجعة</v>
+      </c>
+      <c r="C1430" t="str">
+        <v>Izvēlieties pārskatīšanas datumu</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="str">
+        <v>Linked Artifact</v>
+      </c>
+      <c r="B1431" t="str">
+        <v>المستند المرتبط</v>
+      </c>
+      <c r="C1431" t="str">
+        <v>Saistītais artefakts</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="str">
+        <v>Linked Artifacts</v>
+      </c>
+      <c r="B1432" t="str">
+        <v>المستندات المرتبطة</v>
+      </c>
+      <c r="C1432" t="str">
+        <v>Saistītie artefakti</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="str">
+        <v>KPI Calculation Formula</v>
+      </c>
+      <c r="B1433" t="str">
+        <v>صيغة حساب مؤشر الأداء</v>
+      </c>
+      <c r="C1433" t="str">
+        <v>KPI aprēķina formula</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="str">
+        <v>Linked Frameworks:</v>
+      </c>
+      <c r="B1434" t="str">
+        <v>الأطر المرتبطة:</v>
+      </c>
+      <c r="C1434" t="str">
+        <v>Saistītie ietvari:</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="str">
+        <v>No controls linked to this evidence</v>
+      </c>
+      <c r="B1435" t="str">
+        <v>لا توجد ضوابط مرتبطة بهذا الدليل</v>
+      </c>
+      <c r="C1435" t="str">
+        <v>Nav kontroles saistītas ar šo pierādījumu</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="str">
+        <v>No artifacts linked to this evidence</v>
+      </c>
+      <c r="B1436" t="str">
+        <v>لا توجد مستندات مرتبطة بهذا الدليل</v>
+      </c>
+      <c r="C1436" t="str">
+        <v>Nav artefaktu saistītu ar šo pierādījumu</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="str">
+        <v>Assigned to</v>
+      </c>
+      <c r="B1437" t="str">
+        <v>مكلّف إلى</v>
+      </c>
+      <c r="C1437" t="str">
+        <v>Piešķirts</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="str">
+        <v>KPI Required</v>
+      </c>
+      <c r="B1438" t="str">
+        <v>مؤشر الأداء مطلوب</v>
+      </c>
+      <c r="C1438" t="str">
+        <v>KPI nepieciešams</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="str">
+        <v>KPI Expected Score (%)</v>
+      </c>
+      <c r="B1439" t="str">
+        <v>الدرجة المتوقعة لمؤشر الأداء (%)</v>
+      </c>
+      <c r="C1439" t="str">
+        <v>KPI sagaidāmais rezultāts (%)</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="str">
+        <v>KPI Actual Score</v>
+      </c>
+      <c r="B1440" t="str">
+        <v>الدرجة الفعلية لمؤشر الأداء</v>
+      </c>
+      <c r="C1440" t="str">
+        <v>KPI faktiskais rezultāts</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="str">
+        <v>Enter expected score</v>
+      </c>
+      <c r="B1441" t="str">
+        <v>أدخل الدرجة المتوقعة</v>
+      </c>
+      <c r="C1441" t="str">
+        <v>Ievadiet sagaidāmo rezultātu</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="str">
+        <v>Enter KPI Description</v>
+      </c>
+      <c r="B1442" t="str">
+        <v>أدخل وصف مؤشر الأداء</v>
+      </c>
+      <c r="C1442" t="str">
+        <v>Ievadiet KPI aprakstu</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="str">
+        <v>Enter actual score</v>
+      </c>
+      <c r="B1443" t="str">
+        <v>أدخل الدرجة الفعلية</v>
+      </c>
+      <c r="C1443" t="str">
+        <v>Ievadiet faktisko rezultātu</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="str">
+        <v>Save KPI details first</v>
+      </c>
+      <c r="B1444" t="str">
+        <v>احفظ تفاصيل مؤشر الأداء أولاً</v>
+      </c>
+      <c r="C1444" t="str">
+        <v>Vispirms saglabājiet KPI detaļas</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="str">
+        <v>Save actual score</v>
+      </c>
+      <c r="B1445" t="str">
+        <v>حفظ الدرجة الفعلية</v>
+      </c>
+      <c r="C1445" t="str">
+        <v>Saglabāt faktisko rezultātu</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="str">
+        <v>Edit actual score</v>
+      </c>
+      <c r="B1446" t="str">
+        <v>تعديل الدرجة الفعلية</v>
+      </c>
+      <c r="C1446" t="str">
+        <v>Rediģēt faktisko rezultātu</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="str">
+        <v>Save KPI details first to enable saving actual score</v>
+      </c>
+      <c r="B1447" t="str">
+        <v>احفظ تفاصيل مؤشر الأداء أولاً لتتمكن من حفظ الدرجة الفعلية</v>
+      </c>
+      <c r="C1447" t="str">
+        <v>Vispirms saglabājiet KPI detaļas, lai varētu saglabāt faktisko rezultātu</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="str">
+        <v>Unpublish</v>
+      </c>
+      <c r="B1448" t="str">
+        <v>إلغاء النشر</v>
+      </c>
+      <c r="C1448" t="str">
+        <v>Atcelt publicēšanu</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="str">
+        <v>Published On:</v>
+      </c>
+      <c r="B1449" t="str">
+        <v>تاريخ النشر:</v>
+      </c>
+      <c r="C1449" t="str">
+        <v>Publicēts:</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="str">
+        <v>No published files</v>
+      </c>
+      <c r="B1450" t="str">
+        <v>لا توجد ملفات منشورة</v>
+      </c>
+      <c r="C1450" t="str">
+        <v>Nav publicētu failu</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="str">
+        <v>Add Attachment</v>
+      </c>
+      <c r="B1451" t="str">
+        <v>إضافة مرفق</v>
+      </c>
+      <c r="C1451" t="str">
+        <v>Pievienot pielikumu</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="str">
+        <v>Add Evidence Attachment</v>
+      </c>
+      <c r="B1452" t="str">
+        <v>إضافة مرفق الدليل</v>
+      </c>
+      <c r="C1452" t="str">
+        <v>Pievienot pierādījuma pielikumu</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="str">
+        <v>Drag and drop or select file.</v>
+      </c>
+      <c r="B1453" t="str">
+        <v>اسحب وأفلت أو اختر ملفاً.</v>
+      </c>
+      <c r="C1453" t="str">
+        <v>Velciet un nometiet vai izvēlieties failu.</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="str">
+        <v>Submitting...</v>
+      </c>
+      <c r="B1454" t="str">
+        <v>جارٍ الإرسال...</v>
+      </c>
+      <c r="C1454" t="str">
+        <v>Iesniedz...</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="str">
+        <v>Link Artifacts</v>
+      </c>
+      <c r="B1455" t="str">
+        <v>ربط المستندات المرفقة</v>
+      </c>
+      <c r="C1455" t="str">
+        <v>Saistīt artefaktus</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="str">
+        <v>Search by Artifact Code or Name...</v>
+      </c>
+      <c r="B1456" t="str">
+        <v>البحث برمز المستند أو الاسم...</v>
+      </c>
+      <c r="C1456" t="str">
+        <v>Meklēt pēc artefakta koda vai nosaukuma...</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="str">
+        <v>No artifacts found matching your search</v>
+      </c>
+      <c r="B1457" t="str">
+        <v>لم يتم العثور على مستندات تطابق بحثك</v>
+      </c>
+      <c r="C1457" t="str">
+        <v>Nav atrasti artefakti, kas atbilst jūsu meklējumam</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="str">
+        <v>No available artifacts to link</v>
+      </c>
+      <c r="B1458" t="str">
+        <v>لا توجد مستندات متاحة للربط</v>
+      </c>
+      <c r="C1458" t="str">
+        <v>Nav pieejamu artefaktu saistīšanai</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="str">
+        <v>artifact(s) selected</v>
+      </c>
+      <c r="B1459" t="str">
+        <v>مستند(ات) محددة</v>
+      </c>
+      <c r="C1459" t="str">
+        <v>artefakts(-i) izvēlēti</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="str">
+        <v>Linking...</v>
+      </c>
+      <c r="B1460" t="str">
+        <v>جارٍ الربط...</v>
+      </c>
+      <c r="C1460" t="str">
+        <v>Saista...</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="str">
+        <v>Link Controls</v>
+      </c>
+      <c r="B1461" t="str">
+        <v>ربط الضوابط</v>
+      </c>
+      <c r="C1461" t="str">
+        <v>Saistīt kontroles</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="str">
+        <v>No controls found matching your filters</v>
+      </c>
+      <c r="B1462" t="str">
+        <v>لم يتم العثور على ضوابط تطابق عوامل التصفية</v>
+      </c>
+      <c r="C1462" t="str">
+        <v>Nav atrasti kontroli, kas atbilst jūsu filtriem</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="str">
+        <v>No available controls to link</v>
+      </c>
+      <c r="B1463" t="str">
+        <v>لا توجد ضوابط متاحة للربط</v>
+      </c>
+      <c r="C1463" t="str">
+        <v>Nav pieejamu kontrolu saistīšanai</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="str">
+        <v>Unlink</v>
+      </c>
+      <c r="B1464" t="str">
+        <v>إلغاء الربط</v>
+      </c>
+      <c r="C1464" t="str">
+        <v>Atsaistīt</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="str">
+        <v>Recent Comments</v>
+      </c>
+      <c r="B1465" t="str">
+        <v>التعليقات الأخيرة</v>
+      </c>
+      <c r="C1465" t="str">
+        <v>Jaunākie komentāri</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="str">
+        <v>Add Comment</v>
+      </c>
+      <c r="B1466" t="str">
+        <v>إضافة تعليق</v>
+      </c>
+      <c r="C1466" t="str">
+        <v>Pievienot komentāru</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="str">
+        <v>Add a comment</v>
+      </c>
+      <c r="B1467" t="str">
+        <v>أضف تعليقاً</v>
+      </c>
+      <c r="C1467" t="str">
+        <v>Pievienojiet komentāru</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="str">
+        <v>Type your comment...</v>
+      </c>
+      <c r="B1468" t="str">
+        <v>اكتب تعليقك...</v>
+      </c>
+      <c r="C1468" t="str">
+        <v>Rakstiet komentāru...</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="str">
+        <v>No comments yet</v>
+      </c>
+      <c r="B1469" t="str">
+        <v>لا توجد تعليقات بعد</v>
+      </c>
+      <c r="C1469" t="str">
+        <v>Vēl nav komentāru</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="str">
+        <v>Unknown User</v>
+      </c>
+      <c r="B1470" t="str">
+        <v>مستخدم غير معروف</v>
+      </c>
+      <c r="C1470" t="str">
+        <v>Nezināms lietotājs</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="str">
+        <v>View all</v>
+      </c>
+      <c r="B1471" t="str">
+        <v>عرض الكل</v>
+      </c>
+      <c r="C1471" t="str">
+        <v>Skatīt visus</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="str">
+        <v>comments</v>
+      </c>
+      <c r="B1472" t="str">
+        <v>تعليقات</v>
+      </c>
+      <c r="C1472" t="str">
+        <v>komentāri</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="str">
+        <v>View Comments</v>
+      </c>
+      <c r="B1473" t="str">
+        <v>عرض التعليقات</v>
+      </c>
+      <c r="C1473" t="str">
+        <v>Skatīt komentārus</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="str">
+        <v>Comment</v>
+      </c>
+      <c r="B1474" t="str">
+        <v>تعليق</v>
+      </c>
+      <c r="C1474" t="str">
+        <v>Komentārs</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="str">
+        <v>Enter your comment...</v>
+      </c>
+      <c r="B1475" t="str">
+        <v>أدخل تعليقك...</v>
+      </c>
+      <c r="C1475" t="str">
+        <v>Ievadiet komentāru...</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="str">
+        <v>Previous Comments</v>
+      </c>
+      <c r="B1476" t="str">
+        <v>التعليقات السابقة</v>
+      </c>
+      <c r="C1476" t="str">
+        <v>Iepriekšējie komentāri</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="str">
+        <v>Submit for Approval</v>
+      </c>
+      <c r="B1477" t="str">
+        <v>إرسال للموافقة</v>
+      </c>
+      <c r="C1477" t="str">
+        <v>Iesniegt apstiprināšanai</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="str">
+        <v>Validate</v>
+      </c>
+      <c r="B1478" t="str">
+        <v>تحقق</v>
+      </c>
+      <c r="C1478" t="str">
+        <v>Validēt</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="str">
+        <v>Send Back</v>
+      </c>
+      <c r="B1479" t="str">
+        <v>إرجاع</v>
+      </c>
+      <c r="C1479" t="str">
+        <v>Nosūtīt atpakaļ</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="str">
+        <v>Resubmit</v>
+      </c>
+      <c r="B1480" t="str">
+        <v>إعادة الإرسال</v>
+      </c>
+      <c r="C1480" t="str">
+        <v>Iesniegt atkārtoti</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="str">
+        <v>Resend</v>
+      </c>
+      <c r="B1481" t="str">
+        <v>إعادة الإرسال</v>
+      </c>
+      <c r="C1481" t="str">
+        <v>Nosūtīt atkārtoti</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="str">
+        <v>This cycle has been validated</v>
+      </c>
+      <c r="B1482" t="str">
+        <v>تم التحقق من هذه الدورة</v>
+      </c>
+      <c r="C1482" t="str">
+        <v>Šis cikls ir validēts</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="str">
+        <v>This cycle has been sent back</v>
+      </c>
+      <c r="B1483" t="str">
+        <v>تم إرجاع هذه الدورة</v>
+      </c>
+      <c r="C1483" t="str">
+        <v>Šis cikls ir nosūtīts atpakaļ</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="str">
+        <v>Awaiting submission from Department Contributor</v>
+      </c>
+      <c r="B1484" t="str">
+        <v>في انتظار الإرسال من مساهم القسم</v>
+      </c>
+      <c r="C1484" t="str">
+        <v>Gaida iesniegumu no nodaļas līdzstrādnieka</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="str">
+        <v>Evidence Send Back</v>
+      </c>
+      <c r="B1485" t="str">
+        <v>إرجاع الدليل</v>
+      </c>
+      <c r="C1485" t="str">
+        <v>Pierādījuma nosūtīšana atpakaļ</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="str">
+        <v>Cannot Publish</v>
+      </c>
+      <c r="B1486" t="str">
+        <v>لا يمكن النشر</v>
+      </c>
+      <c r="C1486" t="str">
+        <v>Nevar publicēt</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="str">
+        <v>Current cycle:</v>
+      </c>
+      <c r="B1487" t="str">
+        <v>الدورة الحالية:</v>
+      </c>
+      <c r="C1487" t="str">
+        <v>Pašreizējais cikls:</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="str">
+        <v>Are you sure you want to delete this evidence? This action cannot be undone.</v>
+      </c>
+      <c r="B1488" t="str">
+        <v>هل أنت متأكد أنك تريد حذف هذا الدليل؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C1488" t="str">
+        <v>Vai tiešām vēlaties dzēst šo pierādījumu? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="str">
+        <v>Status reverted to Draft: Current cycle is not validated.</v>
+      </c>
+      <c r="B1489" t="str">
+        <v>تم إرجاع الحالة إلى مسودة: الدورة الحالية غير مُتحقق منها.</v>
+      </c>
+      <c r="C1489" t="str">
+        <v>Statuss atgriezts uz Melnrakstu: Pašreizējais cikls nav validēts.</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="str">
+        <v>Please upload an attachment for this cycle first.</v>
+      </c>
+      <c r="B1490" t="str">
+        <v>يرجى رفع مرفق لهذه الدورة أولاً.</v>
+      </c>
+      <c r="C1490" t="str">
+        <v>Lūdzu vispirms augšupielādējiet pielikumu šim ciklam.</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="str">
+        <v>Submitted for approval successfully.</v>
+      </c>
+      <c r="B1491" t="str">
+        <v>تم الإرسال للموافقة بنجاح.</v>
+      </c>
+      <c r="C1491" t="str">
+        <v>Veiksmīgi iesniegts apstiprināšanai.</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="str">
+        <v>cycle validated. Evidence status updated to Validated.</v>
+      </c>
+      <c r="B1492" t="str">
+        <v>تم التحقق من الدورة. تم تحديث حالة الدليل إلى مُتحقق.</v>
+      </c>
+      <c r="C1492" t="str">
+        <v>Cikls validēts. Pierādījuma statuss atjaunināts uz Validēts.</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="str">
+        <v>cycle validated successfully.</v>
+      </c>
+      <c r="B1493" t="str">
+        <v>تم التحقق من الدورة بنجاح.</v>
+      </c>
+      <c r="C1493" t="str">
+        <v>Cikls veiksmīgi validēts.</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="str">
+        <v>cycle sent back.</v>
+      </c>
+      <c r="B1494" t="str">
+        <v>تم إرجاع الدورة.</v>
+      </c>
+      <c r="C1494" t="str">
+        <v>Cikls nosūtīts atpakaļ.</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="str">
+        <v>Failed to send back.</v>
+      </c>
+      <c r="B1495" t="str">
+        <v>فشل الإرجاع.</v>
+      </c>
+      <c r="C1495" t="str">
+        <v>Neizdevās nosūtīt atpakaļ.</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="str">
+        <v>cycle resubmitted.</v>
+      </c>
+      <c r="B1496" t="str">
+        <v>تم إعادة إرسال الدورة.</v>
+      </c>
+      <c r="C1496" t="str">
+        <v>Cikls atkārtoti iesniegts.</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="str">
+        <v>Failed to resubmit.</v>
+      </c>
+      <c r="B1497" t="str">
+        <v>فشلت إعادة الإرسال.</v>
+      </c>
+      <c r="C1497" t="str">
+        <v>Neizdevās iesniegt atkārtoti.</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="str">
+        <v>Current cycle document is not validated.</v>
+      </c>
+      <c r="B1498" t="str">
+        <v>مستند الدورة الحالية غير مُتحقق منه.</v>
+      </c>
+      <c r="C1498" t="str">
+        <v>Pašreizējā cikla dokuments nav validēts.</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="str">
+        <v>Failed to save KPI details to evidence</v>
+      </c>
+      <c r="B1499" t="str">
+        <v>فشل حفظ تفاصيل مؤشر الأداء في الدليل</v>
+      </c>
+      <c r="C1499" t="str">
+        <v>Neizdevās saglabāt KPI detaļas pierādījumam</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="str">
+        <v>KPI updated successfully!</v>
+      </c>
+      <c r="B1500" t="str">
+        <v>تم تحديث مؤشر الأداء بنجاح!</v>
+      </c>
+      <c r="C1500" t="str">
+        <v>KPI veiksmīgi atjaunināts!</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="str">
+        <v>KPI created successfully!</v>
+      </c>
+      <c r="B1501" t="str">
+        <v>تم إنشاء مؤشر الأداء بنجاح!</v>
+      </c>
+      <c r="C1501" t="str">
+        <v>KPI veiksmīgi izveidots!</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="str">
+        <v>Failed to save KPI</v>
+      </c>
+      <c r="B1502" t="str">
+        <v>فشل حفظ مؤشر الأداء</v>
+      </c>
+      <c r="C1502" t="str">
+        <v>Neizdevās saglabāt KPI</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="str">
+        <v>Please save KPI details first before saving actual score</v>
+      </c>
+      <c r="B1503" t="str">
+        <v>يرجى حفظ تفاصيل مؤشر الأداء أولاً قبل حفظ الدرجة الفعلية</v>
+      </c>
+      <c r="C1503" t="str">
+        <v>Lūdzu vispirms saglabājiet KPI detaļas pirms faktiskā rezultāta saglabāšanas</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="str">
+        <v>KPI Actual Score saved successfully!</v>
+      </c>
+      <c r="B1504" t="str">
+        <v>تم حفظ الدرجة الفعلية لمؤشر الأداء بنجاح!</v>
+      </c>
+      <c r="C1504" t="str">
+        <v>KPI faktiskais rezultāts veiksmīgi saglabāts!</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="str">
+        <v>Failed to save KPI Actual Score</v>
+      </c>
+      <c r="B1505" t="str">
+        <v>فشل حفظ الدرجة الفعلية لمؤشر الأداء</v>
+      </c>
+      <c r="C1505" t="str">
+        <v>Neizdevās saglabāt KPI faktisko rezultātu</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="str">
+        <v>Attachment uploaded successfully!</v>
+      </c>
+      <c r="B1506" t="str">
+        <v>تم رفع المرفق بنجاح!</v>
+      </c>
+      <c r="C1506" t="str">
+        <v>Pielikums veiksmīgi augšupielādēts!</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="str">
+        <v>Failed to upload attachment</v>
+      </c>
+      <c r="B1507" t="str">
+        <v>فشل رفع المرفق</v>
+      </c>
+      <c r="C1507" t="str">
+        <v>Neizdevās augšupielādēt pielikumu</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="str">
+        <v>Attachment deleted successfully!</v>
+      </c>
+      <c r="B1508" t="str">
+        <v>تم حذف المرفق بنجاح!</v>
+      </c>
+      <c r="C1508" t="str">
+        <v>Pielikums veiksmīgi dzēsts!</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="str">
+        <v>Artifacts linked successfully!</v>
+      </c>
+      <c r="B1509" t="str">
+        <v>تم ربط المستندات بنجاح!</v>
+      </c>
+      <c r="C1509" t="str">
+        <v>Artefakti veiksmīgi saistīti!</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="str">
+        <v>Failed to link artifacts</v>
+      </c>
+      <c r="B1510" t="str">
+        <v>فشل ربط المستندات</v>
+      </c>
+      <c r="C1510" t="str">
+        <v>Neizdevās saistīt artefaktus</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="str">
+        <v>Artifact unlinked successfully!</v>
+      </c>
+      <c r="B1511" t="str">
+        <v>تم إلغاء ربط المستند بنجاح!</v>
+      </c>
+      <c r="C1511" t="str">
+        <v>Artefakts veiksmīgi atsaistīts!</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="str">
+        <v>Please upload evidence files first</v>
+      </c>
+      <c r="B1512" t="str">
+        <v>يرجى رفع ملفات الأدلة أولاً</v>
+      </c>
+      <c r="C1512" t="str">
+        <v>Lūdzu vispirms augšupielādējiet pierādījumu failus</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="str">
+        <v>Failed to trigger AI ingest</v>
+      </c>
+      <c r="B1513" t="str">
+        <v>فشل بدء معالجة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1513" t="str">
+        <v>Neizdevās aktivizēt AI apstrādi</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="str">
+        <v>AI ingest started successfully</v>
+      </c>
+      <c r="B1514" t="str">
+        <v>بدأت معالجة الذكاء الاصطناعي بنجاح</v>
+      </c>
+      <c r="C1514" t="str">
+        <v>AI apstrāde veiksmīgi sākta</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="str">
+        <v>Failed to trigger AI review</v>
+      </c>
+      <c r="B1515" t="str">
+        <v>فشل بدء مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1515" t="str">
+        <v>Neizdevās aktivizēt AI pārskatīšanu</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="str">
+        <v>AI review completed successfully</v>
+      </c>
+      <c r="B1516" t="str">
+        <v>اكتملت مراجعة الذكاء الاصطناعي بنجاح</v>
+      </c>
+      <c r="C1516" t="str">
+        <v>AI pārskatīšana veiksmīgi pabeigta</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="str">
+        <v>Failed to clear AI review</v>
+      </c>
+      <c r="B1517" t="str">
+        <v>فشل مسح مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1517" t="str">
+        <v>Neizdevās notīrīt AI pārskatīšanu</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="str">
+        <v>AI review cleared successfully</v>
+      </c>
+      <c r="B1518" t="str">
+        <v>تم مسح مراجعة الذكاء الاصطناعي بنجاح</v>
+      </c>
+      <c r="C1518" t="str">
+        <v>AI pārskatīšana veiksmīgi notīrīta</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="str">
+        <v>Clear AI Review</v>
+      </c>
+      <c r="B1519" t="str">
+        <v>مسح مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1519" t="str">
+        <v>Notīrīt AI pārskatīšanu</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="str">
+        <v>Upload evidence files and trigger AI processing to extract and analyze content.</v>
+      </c>
+      <c r="B1520" t="str">
+        <v>ارفع ملفات الأدلة وابدأ معالجة الذكاء الاصطناعي لاستخراج المحتوى وتحليله.</v>
+      </c>
+      <c r="C1520" t="str">
+        <v>Augšupielādējiet pierādījumu failus un aktivizējiet AI apstrādi, lai izvilktu un analizētu saturu.</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="str">
+        <v>Starting AI Processing...</v>
+      </c>
+      <c r="B1521" t="str">
+        <v>جارٍ بدء معالجة الذكاء الاصطناعي...</v>
+      </c>
+      <c r="C1521" t="str">
+        <v>Sāk AI apstrādi...</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="str">
+        <v>Start AI Processing</v>
+      </c>
+      <c r="B1522" t="str">
+        <v>بدء معالجة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1522" t="str">
+        <v>Sākt AI apstrādi</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="str">
+        <v>Upload evidence files first</v>
+      </c>
+      <c r="B1523" t="str">
+        <v>ارفع ملفات الأدلة أولاً</v>
+      </c>
+      <c r="C1523" t="str">
+        <v>Vispirms augšupielādējiet pierādījumu failus</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="str">
+        <v>AI is processing your evidence files. This may take a few minutes...</v>
+      </c>
+      <c r="B1524" t="str">
+        <v>يقوم الذكاء الاصطناعي بمعالجة ملفات الأدلة الخاصة بك. قد يستغرق هذا بضع دقائق...</v>
+      </c>
+      <c r="C1524" t="str">
+        <v>AI apstrādā jūsu pierādījumu failus. Tas var aizņemt dažas minūtes...</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="str">
+        <v>AI processing failed:</v>
+      </c>
+      <c r="B1525" t="str">
+        <v>فشلت معالجة الذكاء الاصطناعي:</v>
+      </c>
+      <c r="C1525" t="str">
+        <v>AI apstrāde neizdevās:</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="str">
+        <v>AI review completed</v>
+      </c>
+      <c r="B1526" t="str">
+        <v>اكتملت مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1526" t="str">
+        <v>AI pārskatīšana pabeigta</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="str">
+        <v>AI review in progress...</v>
+      </c>
+      <c r="B1527" t="str">
+        <v>مراجعة الذكاء الاصطناعي جارية...</v>
+      </c>
+      <c r="C1527" t="str">
+        <v>AI pārskatīšana norit...</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="str">
+        <v>Evidence processed and ready for AI review</v>
+      </c>
+      <c r="B1528" t="str">
+        <v>تمت معالجة الأدلة وهي جاهزة لمراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1528" t="str">
+        <v>Pierādījumi apstrādāti un gatavi AI pārskatīšanai</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="str">
+        <v>AI Review Results</v>
+      </c>
+      <c r="B1529" t="str">
+        <v>نتائج مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1529" t="str">
+        <v>AI pārskatīšanas rezultāti</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="str">
+        <v>Compliance Score</v>
+      </c>
+      <c r="B1530" t="str">
+        <v>درجة الامتثال</v>
+      </c>
+      <c r="C1530" t="str">
+        <v>Atbilstības vērtējums</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="str">
+        <v>AI Analysis</v>
+      </c>
+      <c r="B1531" t="str">
+        <v>تحليل الذكاء الاصطناعي</v>
+      </c>
+      <c r="C1531" t="str">
+        <v>AI analīze</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="str">
+        <v>Identified Issues</v>
+      </c>
+      <c r="B1532" t="str">
+        <v>المشكلات المحددة</v>
+      </c>
+      <c r="C1532" t="str">
+        <v>Identificētās problēmas</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="str">
+        <v>Severity</v>
+      </c>
+      <c r="B1533" t="str">
+        <v>الخطورة</v>
+      </c>
+      <c r="C1533" t="str">
+        <v>Smagums</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="str">
+        <v>Control Assessment Details</v>
+      </c>
+      <c r="B1534" t="str">
+        <v>تفاصيل تقييم الضوابط</v>
+      </c>
+      <c r="C1534" t="str">
+        <v>Kontroles novērtējuma detaļas</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="str">
+        <v>Control</v>
+      </c>
+      <c r="B1535" t="str">
+        <v>الضابطة</v>
+      </c>
+      <c r="C1535" t="str">
+        <v>Kontrole</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="str">
+        <v>Reviewed</v>
+      </c>
+      <c r="B1536" t="str">
+        <v>تمت المراجعة</v>
+      </c>
+      <c r="C1536" t="str">
+        <v>Pārskatīts</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1403"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1536"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2533"/>
+  <dimension ref="A1:C2580"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -28267,9 +28267,526 @@
         <v>Neizdevās izveidot</v>
       </c>
     </row>
+    <row r="2534">
+      <c r="A2534" t="str">
+        <v>Risk Code</v>
+      </c>
+      <c r="B2534" t="str">
+        <v>رمز المخاطر</v>
+      </c>
+      <c r="C2534" t="str">
+        <v>Riska kods</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="str">
+        <v>Inherent</v>
+      </c>
+      <c r="B2535" t="str">
+        <v>الأصيل</v>
+      </c>
+      <c r="C2535" t="str">
+        <v>Sākotnējais</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="str">
+        <v>Sync from Risks</v>
+      </c>
+      <c r="B2536" t="str">
+        <v>مزامنة من المخاطر</v>
+      </c>
+      <c r="C2536" t="str">
+        <v>Sinhronizēt no riskiem</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="str">
+        <v>Search by risk code, name, or owner...</v>
+      </c>
+      <c r="B2537" t="str">
+        <v>البحث برمز المخاطر أو الاسم أو المالك...</v>
+      </c>
+      <c r="C2537" t="str">
+        <v>Meklēt pēc riska koda, nosaukuma vai īpašnieka...</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="str">
+        <v>Delete All Matrix Entries?</v>
+      </c>
+      <c r="B2538" t="str">
+        <v>حذف جميع إدخالات المصفوفة؟</v>
+      </c>
+      <c r="C2538" t="str">
+        <v>Dzēst visus matricas ierakstus?</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="str">
+        <v>entry(ies) from the Risk Control Matrix.</v>
+      </c>
+      <c r="B2539" t="str">
+        <v>إدخال(ات) من مصفوفة التحكم في المخاطر.</v>
+      </c>
+      <c r="C2539" t="str">
+        <v>ierakstu(-s) no Risku kontroles matricas.</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="str">
+        <v>The underlying Risk records will NOT be deleted.</v>
+      </c>
+      <c r="B2540" t="str">
+        <v>لن يتم حذف سجلات المخاطر الأساسية.</v>
+      </c>
+      <c r="C2540" t="str">
+        <v>Pamata risku ieraksti NETIKS dzēsti.</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="str">
+        <v>Delete Matrix Entry?</v>
+      </c>
+      <c r="B2541" t="str">
+        <v>حذف إدخال المصفوفة؟</v>
+      </c>
+      <c r="C2541" t="str">
+        <v>Dzēst matricas ierakstu?</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="str">
+        <v>This will remove entry</v>
+      </c>
+      <c r="B2542" t="str">
+        <v>سيؤدي هذا إلى إزالة الإدخال</v>
+      </c>
+      <c r="C2542" t="str">
+        <v>Tas noņems ierakstu</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="str">
+        <v>from the Risk Control Matrix.</v>
+      </c>
+      <c r="B2543" t="str">
+        <v>من مصفوفة التحكم في المخاطر.</v>
+      </c>
+      <c r="C2543" t="str">
+        <v>no Risku kontroles matricas.</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="str">
+        <v>The underlying Risk record will NOT be deleted.</v>
+      </c>
+      <c r="B2544" t="str">
+        <v>لن يتم حذف سجل المخاطر الأساسي.</v>
+      </c>
+      <c r="C2544" t="str">
+        <v>Pamata riska ieraksts NETIKS dzēsts.</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="str">
+        <v>This will remove all</v>
+      </c>
+      <c r="B2545" t="str">
+        <v>سيؤدي هذا إلى إزالة جميع</v>
+      </c>
+      <c r="C2545" t="str">
+        <v>Tas noņems visus</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="str">
+        <v>Deleting...</v>
+      </c>
+      <c r="B2546" t="str">
+        <v>جاري الحذف...</v>
+      </c>
+      <c r="C2546" t="str">
+        <v>Dzēš...</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="str">
+        <v>risks to the matrix.</v>
+      </c>
+      <c r="B2547" t="str">
+        <v>المخاطر إلى المصفوفة.</v>
+      </c>
+      <c r="C2547" t="str">
+        <v>riski matricā.</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="str">
+        <v>already existed.</v>
+      </c>
+      <c r="B2548" t="str">
+        <v>موجودة بالفعل.</v>
+      </c>
+      <c r="C2548" t="str">
+        <v>jau pastāvēja.</v>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="str">
+        <v>Import failed</v>
+      </c>
+      <c r="B2549" t="str">
+        <v>فشل الاستيراد</v>
+      </c>
+      <c r="C2549" t="str">
+        <v>Imports neizdevās</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="str">
+        <v>Failed to import risks.</v>
+      </c>
+      <c r="B2550" t="str">
+        <v>فشل في استيراد المخاطر.</v>
+      </c>
+      <c r="C2550" t="str">
+        <v>Neizdevās importēt riskus.</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="str">
+        <v>Failed to import risks to matrix.</v>
+      </c>
+      <c r="B2551" t="str">
+        <v>فشل في استيراد المخاطر إلى المصفوفة.</v>
+      </c>
+      <c r="C2551" t="str">
+        <v>Neizdevās importēt riskus matricā.</v>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" t="str">
+        <v>Entry deleted</v>
+      </c>
+      <c r="B2552" t="str">
+        <v>تم حذف الإدخال</v>
+      </c>
+      <c r="C2552" t="str">
+        <v>Ieraksts dzēsts</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="str">
+        <v>The matrix entry has been removed. The underlying risk is NOT affected.</v>
+      </c>
+      <c r="B2553" t="str">
+        <v>تمت إزالة إدخال المصفوفة. لن يتأثر سجل المخاطر الأساسي.</v>
+      </c>
+      <c r="C2553" t="str">
+        <v>Matricas ieraksts ir noņemts. Pamata risks NAV ietekmēts.</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" t="str">
+        <v>Failed to delete matrix entry.</v>
+      </c>
+      <c r="B2554" t="str">
+        <v>فشل في حذف إدخال المصفوفة.</v>
+      </c>
+      <c r="C2554" t="str">
+        <v>Neizdevās dzēst matricas ierakstu.</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="str">
+        <v>All entries deleted</v>
+      </c>
+      <c r="B2555" t="str">
+        <v>تم حذف جميع الإدخالات</v>
+      </c>
+      <c r="C2555" t="str">
+        <v>Visi ieraksti dzēsti</v>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" t="str">
+        <v>All matrix entries have been removed. The underlying risks are NOT affected.</v>
+      </c>
+      <c r="B2556" t="str">
+        <v>تمت إزالة جميع إدخالات المصفوفة. لن تتأثر سجلات المخاطر الأساسية.</v>
+      </c>
+      <c r="C2556" t="str">
+        <v>Visi matricas ieraksti ir noņemti. Pamata riski NAV ietekmēti.</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="str">
+        <v>Failed to delete matrix entries.</v>
+      </c>
+      <c r="B2557" t="str">
+        <v>فشل في حذف إدخالات المصفوفة.</v>
+      </c>
+      <c r="C2557" t="str">
+        <v>Neizdevās dzēst matricas ierakstus.</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" t="str">
+        <v>No entries in the Risk Control Matrix</v>
+      </c>
+      <c r="B2558" t="str">
+        <v>لا توجد إدخالات في مصفوفة التحكم في المخاطر</v>
+      </c>
+      <c r="C2558" t="str">
+        <v>Nav ierakstu Risku kontroles matricā</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="str">
+        <v>Import risks from the risk register to get started</v>
+      </c>
+      <c r="B2559" t="str">
+        <v>استيراد المخاطر من سجل المخاطر للبدء</v>
+      </c>
+      <c r="C2559" t="str">
+        <v>Importējiet riskus no risku reģistra, lai sāktu</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="str">
+        <v>Link Control to Risk</v>
+      </c>
+      <c r="B2560" t="str">
+        <v>ربط الضابط بالمخاطر</v>
+      </c>
+      <c r="C2560" t="str">
+        <v>Saistīt kontroli ar risku</v>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="str">
+        <v>Select a control</v>
+      </c>
+      <c r="B2561" t="str">
+        <v>اختر ضابطاً</v>
+      </c>
+      <c r="C2561" t="str">
+        <v>Izvēlieties kontroli</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" t="str">
+        <v>No controls linked to this risk</v>
+      </c>
+      <c r="B2562" t="str">
+        <v>لا توجد ضوابط مرتبطة بهذا الخطر</v>
+      </c>
+      <c r="C2562" t="str">
+        <v>Ar šo risku nav saistītas kontroles</v>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="str">
+        <v>Link controls to show how this risk is being mitigated</v>
+      </c>
+      <c r="B2563" t="str">
+        <v>ربط الضوابط لإظهار كيفية تخفيف هذا الخطر</v>
+      </c>
+      <c r="C2563" t="str">
+        <v>Saistiet kontroles, lai parādītu, kā šis risks tiek mazināts</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" t="str">
+        <v>No residual risk assessment available</v>
+      </c>
+      <c r="B2564" t="str">
+        <v>لا يوجد تقييم للمخاطر المتبقية</v>
+      </c>
+      <c r="C2564" t="str">
+        <v>Nav pieejams atlikušā riska novērtējums</v>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="str">
+        <v>Edit the risk to add residual risk values</v>
+      </c>
+      <c r="B2565" t="str">
+        <v>حرر المخاطر لإضافة قيم المخاطر المتبقية</v>
+      </c>
+      <c r="C2565" t="str">
+        <v>Rediģējiet risku, lai pievienotu atlikušā riska vērtības</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" t="str">
+        <v>Matrix Position</v>
+      </c>
+      <c r="B2566" t="str">
+        <v>موقع المصفوفة</v>
+      </c>
+      <c r="C2566" t="str">
+        <v>Matricas pozīcija</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="str">
+        <v>Mitigating Controls</v>
+      </c>
+      <c r="B2567" t="str">
+        <v>ضوابط التخفيف</v>
+      </c>
+      <c r="C2567" t="str">
+        <v>Mazinošās kontroles</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" t="str">
+        <v>After applying controls/mitigations</v>
+      </c>
+      <c r="B2568" t="str">
+        <v>بعد تطبيق الضوابط/التخفيفات</v>
+      </c>
+      <c r="C2568" t="str">
+        <v>Pēc kontroļu/mazinājumu piemērošanas</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" t="str">
+        <v>L x I</v>
+      </c>
+      <c r="B2569" t="str">
+        <v>الاحتمالية × التأثير</v>
+      </c>
+      <c r="C2569" t="str">
+        <v>V x I</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="B2570" t="str">
+        <v>تم التحقق</v>
+      </c>
+      <c r="C2570" t="str">
+        <v>Verificēts</v>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="str">
+        <v>Inherent Risk Assessment</v>
+      </c>
+      <c r="B2571" t="str">
+        <v>تقييم المخاطر الأصيلة</v>
+      </c>
+      <c r="C2571" t="str">
+        <v>Sākotnējā riska novērtējums</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" t="str">
+        <v>Residual Risk Assessment</v>
+      </c>
+      <c r="B2572" t="str">
+        <v>تقييم المخاطر المتبقية</v>
+      </c>
+      <c r="C2572" t="str">
+        <v>Atlikušā riska novērtējums</v>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="str">
+        <v>Residual Likelihood</v>
+      </c>
+      <c r="B2573" t="str">
+        <v>الاحتمالية المتبقية</v>
+      </c>
+      <c r="C2573" t="str">
+        <v>Atlikušā iespējamība</v>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" t="str">
+        <v>Residual Impact</v>
+      </c>
+      <c r="B2574" t="str">
+        <v>التأثير المتبقي</v>
+      </c>
+      <c r="C2574" t="str">
+        <v>Atlikušā ietekme</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="str">
+        <v>Other Details</v>
+      </c>
+      <c r="B2575" t="str">
+        <v>تفاصيل أخرى</v>
+      </c>
+      <c r="C2575" t="str">
+        <v>Cita informācija</v>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="str">
+        <v>Mitigation Status</v>
+      </c>
+      <c r="B2576" t="str">
+        <v>حالة التخفيف</v>
+      </c>
+      <c r="C2576" t="str">
+        <v>Mazināšanas statuss</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="str">
+        <v>Select likelihood</v>
+      </c>
+      <c r="B2577" t="str">
+        <v>اختر الاحتمالية</v>
+      </c>
+      <c r="C2577" t="str">
+        <v>Izvēlieties iespējamību</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" t="str">
+        <v>Select impact</v>
+      </c>
+      <c r="B2578" t="str">
+        <v>اختر التأثير</v>
+      </c>
+      <c r="C2578" t="str">
+        <v>Izvēlieties ietekmi</v>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="str">
+        <v>Select due date</v>
+      </c>
+      <c r="B2579" t="str">
+        <v>اختر تاريخ الاستحقاق</v>
+      </c>
+      <c r="C2579" t="str">
+        <v>Izvēlieties izpildes datumu</v>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" t="str">
+        <v>Implemented</v>
+      </c>
+      <c r="B2580" t="str">
+        <v>مُنفَّذ</v>
+      </c>
+      <c r="C2580" t="str">
+        <v>Ieviests</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2533"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2580"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,12 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3136"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C3178"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -34900,9 +34895,471 @@
         <v>risks(-i)</v>
       </c>
     </row>
+    <row r="3137">
+      <c r="A3137" t="str">
+        <v>Toggle Columns</v>
+      </c>
+      <c r="B3137" t="str">
+        <v>تبديل الأعمدة</v>
+      </c>
+      <c r="C3137" t="str">
+        <v>Pārslēgt kolonnas</v>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" t="str">
+        <v>No Data</v>
+      </c>
+      <c r="B3138" t="str">
+        <v>لا توجد بيانات</v>
+      </c>
+      <c r="C3138" t="str">
+        <v>Nav datu</v>
+      </c>
+    </row>
+    <row r="3139">
+      <c r="A3139" t="str">
+        <v>RTO</v>
+      </c>
+      <c r="B3139" t="str">
+        <v>RTO</v>
+      </c>
+      <c r="C3139" t="str">
+        <v>RTO</v>
+      </c>
+    </row>
+    <row r="3140">
+      <c r="A3140" t="str">
+        <v>RPO</v>
+      </c>
+      <c r="B3140" t="str">
+        <v>RPO</v>
+      </c>
+      <c r="C3140" t="str">
+        <v>RPO</v>
+      </c>
+    </row>
+    <row r="3141">
+      <c r="A3141" t="str">
+        <v>Match with Library</v>
+      </c>
+      <c r="B3141" t="str">
+        <v>مطابقة مع المكتبة</v>
+      </c>
+      <c r="C3141" t="str">
+        <v>Saskaņot ar bibliotēku</v>
+      </c>
+    </row>
+    <row r="3142">
+      <c r="A3142" t="str">
+        <v>Choose File</v>
+      </c>
+      <c r="B3142" t="str">
+        <v>اختر ملف</v>
+      </c>
+      <c r="C3142" t="str">
+        <v>Izvēlēties failu</v>
+      </c>
+    </row>
+    <row r="3143">
+      <c r="A3143" t="str">
+        <v>No file chosen</v>
+      </c>
+      <c r="B3143" t="str">
+        <v>لم يتم اختيار ملف</v>
+      </c>
+      <c r="C3143" t="str">
+        <v>Nav izvēlēts fails</v>
+      </c>
+    </row>
+    <row r="3144">
+      <c r="A3144" t="str">
+        <v>Select Department First</v>
+      </c>
+      <c r="B3144" t="str">
+        <v>اختر القسم أولاً</v>
+      </c>
+      <c r="C3144" t="str">
+        <v>Vispirms atlasiet nodaļu</v>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" t="str">
+        <v>Enable KPI Measurement Required when adding a process to see it here</v>
+      </c>
+      <c r="B3145" t="str">
+        <v>قم بتمكين خيار قياس مؤشرات الأداء عند إضافة عملية لرؤيتها هنا</v>
+      </c>
+      <c r="C3145" t="str">
+        <v>Iespējojiet KPI mērīšanu, pievienojot procesu, lai to redzētu šeit</v>
+      </c>
+    </row>
+    <row r="3146">
+      <c r="A3146" t="str">
+        <v>BIA Categories</v>
+      </c>
+      <c r="B3146" t="str">
+        <v>فئات تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3146" t="str">
+        <v>BIA kategorijas</v>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" t="str">
+        <v>Add Category</v>
+      </c>
+      <c r="B3147" t="str">
+        <v>إضافة فئة</v>
+      </c>
+      <c r="C3147" t="str">
+        <v>Pievienot kategoriju</v>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" t="str">
+        <v>Add BIA Category</v>
+      </c>
+      <c r="B3148" t="str">
+        <v>إضافة فئة تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3148" t="str">
+        <v>Pievienot BIA kategoriju</v>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" t="str">
+        <v>Edit BIA Category</v>
+      </c>
+      <c r="B3149" t="str">
+        <v>تعديل فئة تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3149" t="str">
+        <v>Rediģēt BIA kategoriju</v>
+      </c>
+    </row>
+    <row r="3150">
+      <c r="A3150" t="str">
+        <v>Sort Order</v>
+      </c>
+      <c r="B3150" t="str">
+        <v>ترتيب الفرز</v>
+      </c>
+      <c r="C3150" t="str">
+        <v>Kārtošanas secība</v>
+      </c>
+    </row>
+    <row r="3151">
+      <c r="A3151" t="str">
+        <v>e.g., Financial, Reputational</v>
+      </c>
+      <c r="B3151" t="str">
+        <v>مثال: مالي، سمعة</v>
+      </c>
+      <c r="C3151" t="str">
+        <v>piem., Finanšu, Reputācijas</v>
+      </c>
+    </row>
+    <row r="3152">
+      <c r="A3152" t="str">
+        <v>Are you sure you want to delete this category? This action cannot be undone.</v>
+      </c>
+      <c r="B3152" t="str">
+        <v>هل أنت متأكد أنك تريد حذف هذه الفئة؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C3152" t="str">
+        <v>Vai tiešām vēlaties dzēst šo kategoriju? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="3153">
+      <c r="A3153" t="str">
+        <v>Add a new impact category for Business Impact Analysis</v>
+      </c>
+      <c r="B3153" t="str">
+        <v>إضافة فئة تأثير جديدة لتحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3153" t="str">
+        <v>Pievienojiet jaunu ietekmes kategoriju biznesa ietekmes analīzei</v>
+      </c>
+    </row>
+    <row r="3154">
+      <c r="A3154" t="str">
+        <v>Rating Label</v>
+      </c>
+      <c r="B3154" t="str">
+        <v>تسمية التقييم</v>
+      </c>
+      <c r="C3154" t="str">
+        <v>Novērtējuma etiķete</v>
+      </c>
+    </row>
+    <row r="3155">
+      <c r="A3155" t="str">
+        <v>Score Value</v>
+      </c>
+      <c r="B3155" t="str">
+        <v>قيمة النقاط</v>
+      </c>
+      <c r="C3155" t="str">
+        <v>Punktu vērtība</v>
+      </c>
+    </row>
+    <row r="3156">
+      <c r="A3156" t="str">
+        <v>Criticality Label</v>
+      </c>
+      <c r="B3156" t="str">
+        <v>تسمية الخطورة</v>
+      </c>
+      <c r="C3156" t="str">
+        <v>Kritiskuma etiķete</v>
+      </c>
+    </row>
+    <row r="3157">
+      <c r="A3157" t="str">
+        <v>Criticality Ranges</v>
+      </c>
+      <c r="B3157" t="str">
+        <v>نطاقات مستويات الخطورة</v>
+      </c>
+      <c r="C3157" t="str">
+        <v>Kritiskuma diapazoni</v>
+      </c>
+    </row>
+    <row r="3158">
+      <c r="A3158" t="str">
+        <v>Rating Methodology</v>
+      </c>
+      <c r="B3158" t="str">
+        <v>منهجية التقييم</v>
+      </c>
+      <c r="C3158" t="str">
+        <v>Novērtējuma metodika</v>
+      </c>
+    </row>
+    <row r="3159">
+      <c r="A3159" t="str">
+        <v>High of all (Maximum)</v>
+      </c>
+      <c r="B3159" t="str">
+        <v>الأعلى من الكل (الحد الأقصى)</v>
+      </c>
+      <c r="C3159" t="str">
+        <v>Augstākais no visiem (Maksimums)</v>
+      </c>
+    </row>
+    <row r="3160">
+      <c r="A3160" t="str">
+        <v>Addition of all (Sum)</v>
+      </c>
+      <c r="B3160" t="str">
+        <v>جمع الكل (المجموع)</v>
+      </c>
+      <c r="C3160" t="str">
+        <v>Visu pievienošana (Summa)</v>
+      </c>
+    </row>
+    <row r="3161">
+      <c r="A3161" t="str">
+        <v>Product of all (Multiply)</v>
+      </c>
+      <c r="B3161" t="str">
+        <v>حاصل ضرب الكل (الضرب)</v>
+      </c>
+      <c r="C3161" t="str">
+        <v>Visu reizinājums (Reizinājums)</v>
+      </c>
+    </row>
+    <row r="3162">
+      <c r="A3162" t="str">
+        <v>Add Rating</v>
+      </c>
+      <c r="B3162" t="str">
+        <v>إضافة تقييم</v>
+      </c>
+      <c r="C3162" t="str">
+        <v>Pievienot novērtējumu</v>
+      </c>
+    </row>
+    <row r="3163">
+      <c r="A3163" t="str">
+        <v>Add Range</v>
+      </c>
+      <c r="B3163" t="str">
+        <v>إضافة نطاق</v>
+      </c>
+      <c r="C3163" t="str">
+        <v>Pievienot diapazonu</v>
+      </c>
+    </row>
+    <row r="3164">
+      <c r="A3164" t="str">
+        <v>No limit</v>
+      </c>
+      <c r="B3164" t="str">
+        <v>بدون حد</v>
+      </c>
+      <c r="C3164" t="str">
+        <v>Bez ierobežojuma</v>
+      </c>
+    </row>
+    <row r="3165">
+      <c r="A3165" t="str">
+        <v>overlaps with</v>
+      </c>
+      <c r="B3165" t="str">
+        <v>يتداخل مع</v>
+      </c>
+      <c r="C3165" t="str">
+        <v>pārklājas ar</v>
+      </c>
+    </row>
+    <row r="3166">
+      <c r="A3166" t="str">
+        <v>Define a criticality level based on score range</v>
+      </c>
+      <c r="B3166" t="str">
+        <v>تحديد مستوى خطورة بناءً على نطاق النقاط</v>
+      </c>
+      <c r="C3166" t="str">
+        <v>Definējiet kritiskuma līmeni, pamatojoties uz punktu diapazonu</v>
+      </c>
+    </row>
+    <row r="3167">
+      <c r="A3167" t="str">
+        <v>Configure how the BIA impact rating is calculated from individual category scores</v>
+      </c>
+      <c r="B3167" t="str">
+        <v>تكوين كيفية حساب تقييم تأثير تحليل الأعمال من درجات الفئات الفردية</v>
+      </c>
+      <c r="C3167" t="str">
+        <v>Konfigurējiet, kā BIA ietekmes vērtējums tiek aprēķināts no atsevišķo kategoriju rādītājiem</v>
+      </c>
+    </row>
+    <row r="3168">
+      <c r="A3168" t="str">
+        <v>Define score ranges to determine process criticality levels</v>
+      </c>
+      <c r="B3168" t="str">
+        <v>تحديد نطاقات النقاط لتحديد مستويات خطورة العملية</v>
+      </c>
+      <c r="C3168" t="str">
+        <v>Definējiet punktu diapazonus, lai noteiktu procesa kritiskuma līmeņus</v>
+      </c>
+    </row>
+    <row r="3169">
+      <c r="A3169" t="str">
+        <v>Recovery Time Objective (RTO)</v>
+      </c>
+      <c r="B3169" t="str">
+        <v>الوقت المستهدف للاسترجاع (RTO)</v>
+      </c>
+      <c r="C3169" t="str">
+        <v>Atveseļošanas laika mērķis (RTO)</v>
+      </c>
+    </row>
+    <row r="3170">
+      <c r="A3170" t="str">
+        <v>Recovery Point Objective (RPO)</v>
+      </c>
+      <c r="B3170" t="str">
+        <v>نقطة استرجاع البيانات المستهدفة (RPO)</v>
+      </c>
+      <c r="C3170" t="str">
+        <v>Datu atveseļošanas punkta mērķis (RPO)</v>
+      </c>
+    </row>
+    <row r="3171">
+      <c r="A3171" t="str">
+        <v>RTO Labels</v>
+      </c>
+      <c r="B3171" t="str">
+        <v>تسميات الوقت المستهدف للاسترجاع</v>
+      </c>
+      <c r="C3171" t="str">
+        <v>RTO etiķetes</v>
+      </c>
+    </row>
+    <row r="3172">
+      <c r="A3172" t="str">
+        <v>RPO Labels</v>
+      </c>
+      <c r="B3172" t="str">
+        <v>تسميات نقطة استرجاع البيانات</v>
+      </c>
+      <c r="C3172" t="str">
+        <v>RPO etiķetes</v>
+      </c>
+    </row>
+    <row r="3173">
+      <c r="A3173" t="str">
+        <v>Add RTO Label</v>
+      </c>
+      <c r="B3173" t="str">
+        <v>إضافة تسمية الوقت المستهدف للاسترجاع</v>
+      </c>
+      <c r="C3173" t="str">
+        <v>Pievienot RTO etiķeti</v>
+      </c>
+    </row>
+    <row r="3174">
+      <c r="A3174" t="str">
+        <v>Add RPO Label</v>
+      </c>
+      <c r="B3174" t="str">
+        <v>إضافة تسمية نقطة استرجاع البيانات</v>
+      </c>
+      <c r="C3174" t="str">
+        <v>Pievienot RPO etiķeti</v>
+      </c>
+    </row>
+    <row r="3175">
+      <c r="A3175" t="str">
+        <v>RTO defines the maximum acceptable time to restore a process after a disruption. Configure labels to standardize RTO options across your organization.</v>
+      </c>
+      <c r="B3175" t="str">
+        <v>يحدد الوقت المستهدف للاسترجاع الحد الأقصى للوقت المقبول لاستعادة العملية بعد الانقطاع. قم بتكوين التسميات لتوحيد خيارات الوقت المستهدف للاسترجاع في جميع أنحاء مؤسستك.</v>
+      </c>
+      <c r="C3175" t="str">
+        <v>RTO definē maksimālo pieņemamo laiku procesa atjaunošanai pēc pārtraukuma. Konfigurējiet etiķetes, lai standartizētu RTO opcijas visā jūsu organizācijā.</v>
+      </c>
+    </row>
+    <row r="3176">
+      <c r="A3176" t="str">
+        <v>RPO defines the maximum acceptable data loss measured in time. Configure labels to standardize RPO options across your organization.</v>
+      </c>
+      <c r="B3176" t="str">
+        <v>تحدد نقطة استرجاع البيانات أقصى فقدان مقبول للبيانات يُقاس بالوقت. قم بتكوين التسميات لتوحيد خيارات نقطة استرجاع البيانات في جميع أنحاء مؤسستك.</v>
+      </c>
+      <c r="C3176" t="str">
+        <v>RPO definē maksimāli pieņemamo datu zudumu, ko mēra laikā. Konfigurējiet etiķetes, lai standartizētu RPO opcijas visā jūsu organizācijā.</v>
+      </c>
+    </row>
+    <row r="3177">
+      <c r="A3177" t="str">
+        <v>Email notifications enabled</v>
+      </c>
+      <c r="B3177" t="str">
+        <v>تم تفعيل إشعارات البريد الإلكتروني</v>
+      </c>
+      <c r="C3177" t="str">
+        <v>E-pasta paziņojumi iespējoti</v>
+      </c>
+    </row>
+    <row r="3178">
+      <c r="A3178" t="str">
+        <v>Email notifications disabled</v>
+      </c>
+      <c r="B3178" t="str">
+        <v>تم تعطيل إشعارات البريد الإلكتروني</v>
+      </c>
+      <c r="C3178" t="str">
+        <v>E-pasta paziņojumi atspējoti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3136"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3178"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3178"/>
+  <dimension ref="A1:C3189"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -35357,9 +35357,130 @@
         <v>E-pasta paziņojumi atspējoti</v>
       </c>
     </row>
+    <row r="3179">
+      <c r="A3179" t="str">
+        <v>BIA submitted for approval</v>
+      </c>
+      <c r="B3179" t="str">
+        <v>تم تقديم تحليل أثر الأعمال للموافقة</v>
+      </c>
+      <c r="C3179" t="str">
+        <v>BIA iesniegts apstiprināšanai</v>
+      </c>
+    </row>
+    <row r="3180">
+      <c r="A3180" t="str">
+        <v>BIA approved</v>
+      </c>
+      <c r="B3180" t="str">
+        <v>تمت الموافقة على تحليل أثر الأعمال</v>
+      </c>
+      <c r="C3180" t="str">
+        <v>BIA apstiprināts</v>
+      </c>
+    </row>
+    <row r="3181">
+      <c r="A3181" t="str">
+        <v>Failed to create rating</v>
+      </c>
+      <c r="B3181" t="str">
+        <v>فشل في إنشاء التصنيف</v>
+      </c>
+      <c r="C3181" t="str">
+        <v>Neizdevās izveidot vērtējumu</v>
+      </c>
+    </row>
+    <row r="3182">
+      <c r="A3182" t="str">
+        <v>Failed to update rating</v>
+      </c>
+      <c r="B3182" t="str">
+        <v>فشل في تحديث التصنيف</v>
+      </c>
+      <c r="C3182" t="str">
+        <v>Neizdevās atjaunināt vērtējumu</v>
+      </c>
+    </row>
+    <row r="3183">
+      <c r="A3183" t="str">
+        <v>Failed to create range</v>
+      </c>
+      <c r="B3183" t="str">
+        <v>فشل في إنشاء النطاق</v>
+      </c>
+      <c r="C3183" t="str">
+        <v>Neizdevās izveidot diapazonu</v>
+      </c>
+    </row>
+    <row r="3184">
+      <c r="A3184" t="str">
+        <v>Failed to create range. Please try again.</v>
+      </c>
+      <c r="B3184" t="str">
+        <v>فشل في إنشاء النطاق. يرجى المحاولة مرة أخرى.</v>
+      </c>
+      <c r="C3184" t="str">
+        <v>Neizdevās izveidot diapazonu. Lūdzu, mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="3185">
+      <c r="A3185" t="str">
+        <v>Failed to update range</v>
+      </c>
+      <c r="B3185" t="str">
+        <v>فشل في تحديث النطاق</v>
+      </c>
+      <c r="C3185" t="str">
+        <v>Neizdevās atjaunināt diapazonu</v>
+      </c>
+    </row>
+    <row r="3186">
+      <c r="A3186" t="str">
+        <v>Failed to update range. Please try again.</v>
+      </c>
+      <c r="B3186" t="str">
+        <v>فشل في تحديث النطاق. يرجى المحاولة مرة أخرى.</v>
+      </c>
+      <c r="C3186" t="str">
+        <v>Neizdevās atjaunināt diapazonu. Lūdzu, mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="3187">
+      <c r="A3187" t="str">
+        <v>Failed to create label</v>
+      </c>
+      <c r="B3187" t="str">
+        <v>فشل في إنشاء التسمية</v>
+      </c>
+      <c r="C3187" t="str">
+        <v>Neizdevās izveidot etiķeti</v>
+      </c>
+    </row>
+    <row r="3188">
+      <c r="A3188" t="str">
+        <v>Failed to update label</v>
+      </c>
+      <c r="B3188" t="str">
+        <v>فشل في تحديث التسمية</v>
+      </c>
+      <c r="C3188" t="str">
+        <v>Neizdevās atjaunināt etiķeti</v>
+      </c>
+    </row>
+    <row r="3189">
+      <c r="A3189" t="str">
+        <v>Select Process Type</v>
+      </c>
+      <c r="B3189" t="str">
+        <v>اختر نوع العملية</v>
+      </c>
+      <c r="C3189" t="str">
+        <v>Izvēlieties procesa veidu</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3178"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3189"/>
+  <dimension ref="A1:C3196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -35478,9 +35478,86 @@
         <v>Izvēlieties procesa veidu</v>
       </c>
     </row>
+    <row r="3190">
+      <c r="A3190" t="str">
+        <v>G R C Administrator</v>
+      </c>
+      <c r="B3190" t="str">
+        <v>مسؤول GRC</v>
+      </c>
+      <c r="C3190" t="str">
+        <v>GRC administrators</v>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" t="str">
+        <v>Customer Administrator</v>
+      </c>
+      <c r="B3191" t="str">
+        <v>مسؤول العميل</v>
+      </c>
+      <c r="C3191" t="str">
+        <v>Klienta administrators</v>
+      </c>
+    </row>
+    <row r="3192">
+      <c r="A3192" t="str">
+        <v>Audit Manager</v>
+      </c>
+      <c r="B3192" t="str">
+        <v>مدير التدقيق</v>
+      </c>
+      <c r="C3192" t="str">
+        <v>Audita menedžeris</v>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" t="str">
+        <v>Reviewer</v>
+      </c>
+      <c r="B3193" t="str">
+        <v>مراجع</v>
+      </c>
+      <c r="C3193" t="str">
+        <v>Pārskatītājs</v>
+      </c>
+    </row>
+    <row r="3194">
+      <c r="A3194" t="str">
+        <v>Contributor</v>
+      </c>
+      <c r="B3194" t="str">
+        <v>مساهم</v>
+      </c>
+      <c r="C3194" t="str">
+        <v>Līdzstrādnieks</v>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" t="str">
+        <v>Department Reviewer</v>
+      </c>
+      <c r="B3195" t="str">
+        <v>مراجع القسم</v>
+      </c>
+      <c r="C3195" t="str">
+        <v>Nodaļas pārskatītājs</v>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" t="str">
+        <v>Department Contributor</v>
+      </c>
+      <c r="B3196" t="str">
+        <v>مساهم القسم</v>
+      </c>
+      <c r="C3196" t="str">
+        <v>Nodaļas līdzstrādnieks</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3196"/>
+  <dimension ref="A1:C3198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -35555,9 +35555,31 @@
         <v>Nodaļas līdzstrādnieks</v>
       </c>
     </row>
+    <row r="3197">
+      <c r="A3197" t="str">
+        <v>Employee Size</v>
+      </c>
+      <c r="B3197" t="str">
+        <v>حجم الموظفين</v>
+      </c>
+      <c r="C3197" t="str">
+        <v>Darbinieku skaits</v>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" t="str">
+        <v>Branch Size</v>
+      </c>
+      <c r="B3198" t="str">
+        <v>حجم الفروع</v>
+      </c>
+      <c r="C3198" t="str">
+        <v>Filiāļu skaits</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,12 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3222"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C3422"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -35846,9 +35841,2209 @@
         <v>risks(-i)</v>
       </c>
     </row>
+    <row r="3223">
+      <c r="A3223" t="str">
+        <v>Program Monitor</v>
+      </c>
+      <c r="B3223" t="str">
+        <v>مراقب البرنامج</v>
+      </c>
+      <c r="C3223" t="str">
+        <v>Programmas monitors</v>
+      </c>
+    </row>
+    <row r="3224">
+      <c r="A3224" t="str">
+        <v>Control Center</v>
+      </c>
+      <c r="B3224" t="str">
+        <v>مركز التحكم</v>
+      </c>
+      <c r="C3224" t="str">
+        <v>Vadības centrs</v>
+      </c>
+    </row>
+    <row r="3225">
+      <c r="A3225" t="str">
+        <v>Vendor Management</v>
+      </c>
+      <c r="B3225" t="str">
+        <v>إدارة الموردين</v>
+      </c>
+      <c r="C3225" t="str">
+        <v>Piegādātāju pārvaldība</v>
+      </c>
+    </row>
+    <row r="3226">
+      <c r="A3226" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="B3226" t="str">
+        <v>المراقبة</v>
+      </c>
+      <c r="C3226" t="str">
+        <v>Uzraudzība</v>
+      </c>
+    </row>
+    <row r="3227">
+      <c r="A3227" t="str">
+        <v>Configurations</v>
+      </c>
+      <c r="B3227" t="str">
+        <v>التكوينات</v>
+      </c>
+      <c r="C3227" t="str">
+        <v>Konfigurācijas</v>
+      </c>
+    </row>
+    <row r="3228">
+      <c r="A3228" t="str">
+        <v>Assessment Workspace</v>
+      </c>
+      <c r="B3228" t="str">
+        <v>مساحة عمل التقييم</v>
+      </c>
+      <c r="C3228" t="str">
+        <v>Novērtējuma darbvieta</v>
+      </c>
+    </row>
+    <row r="3229">
+      <c r="A3229" t="str">
+        <v>Task Queue</v>
+      </c>
+      <c r="B3229" t="str">
+        <v>قائمة المهام</v>
+      </c>
+      <c r="C3229" t="str">
+        <v>Uzdevumu rinda</v>
+      </c>
+    </row>
+    <row r="3230">
+      <c r="A3230" t="str">
+        <v>Master Data Management</v>
+      </c>
+      <c r="B3230" t="str">
+        <v>إدارة البيانات الرئيسية</v>
+      </c>
+      <c r="C3230" t="str">
+        <v>Pamatdatu pārvaldība</v>
+      </c>
+    </row>
+    <row r="3231">
+      <c r="A3231" t="str">
+        <v>TPRM</v>
+      </c>
+      <c r="B3231" t="str">
+        <v>إدارة مخاطر الأطراف الثالثة</v>
+      </c>
+      <c r="C3231" t="str">
+        <v>TPRM</v>
+      </c>
+    </row>
+    <row r="3232">
+      <c r="A3232" t="str">
+        <v>TPRM Customer Admin</v>
+      </c>
+      <c r="B3232" t="str">
+        <v>مسؤول عملاء TPRM</v>
+      </c>
+      <c r="C3232" t="str">
+        <v>TPRM klientu administrators</v>
+      </c>
+    </row>
+    <row r="3233">
+      <c r="A3233" t="str">
+        <v>Total Assessment</v>
+      </c>
+      <c r="B3233" t="str">
+        <v>إجمالي التقييمات</v>
+      </c>
+      <c r="C3233" t="str">
+        <v>Kopējie novērtējumi</v>
+      </c>
+    </row>
+    <row r="3234">
+      <c r="A3234" t="str">
+        <v>Total Vendor</v>
+      </c>
+      <c r="B3234" t="str">
+        <v>إجمالي الموردين</v>
+      </c>
+      <c r="C3234" t="str">
+        <v>Kopējie piegādātāji</v>
+      </c>
+    </row>
+    <row r="3235">
+      <c r="A3235" t="str">
+        <v>Assessment Limit</v>
+      </c>
+      <c r="B3235" t="str">
+        <v>حد التقييمات</v>
+      </c>
+      <c r="C3235" t="str">
+        <v>Novērtējumu limits</v>
+      </c>
+    </row>
+    <row r="3236">
+      <c r="A3236" t="str">
+        <v>Vendor Limit</v>
+      </c>
+      <c r="B3236" t="str">
+        <v>حد الموردين</v>
+      </c>
+      <c r="C3236" t="str">
+        <v>Piegādātāju limits</v>
+      </c>
+    </row>
+    <row r="3237">
+      <c r="A3237" t="str">
+        <v>Assessment Factory</v>
+      </c>
+      <c r="B3237" t="str">
+        <v>مصنع التقييم</v>
+      </c>
+      <c r="C3237" t="str">
+        <v>Novērtējumu rūpnīca</v>
+      </c>
+    </row>
+    <row r="3238">
+      <c r="A3238" t="str">
+        <v>Onboarded Vendor</v>
+      </c>
+      <c r="B3238" t="str">
+        <v>مورد مسجل</v>
+      </c>
+      <c r="C3238" t="str">
+        <v>Reģistrēts piegādātājs</v>
+      </c>
+    </row>
+    <row r="3239">
+      <c r="A3239" t="str">
+        <v>Assessment limit</v>
+      </c>
+      <c r="B3239" t="str">
+        <v>حد التقييم</v>
+      </c>
+      <c r="C3239" t="str">
+        <v>Novērtējuma limits</v>
+      </c>
+    </row>
+    <row r="3240">
+      <c r="A3240" t="str">
+        <v>Vendor limit</v>
+      </c>
+      <c r="B3240" t="str">
+        <v>حد المورد</v>
+      </c>
+      <c r="C3240" t="str">
+        <v>Piegādātāja limits</v>
+      </c>
+    </row>
+    <row r="3241">
+      <c r="A3241" t="str">
+        <v>Overview of your TPRM program usage and limits</v>
+      </c>
+      <c r="B3241" t="str">
+        <v>نظرة عامة على استخدام برنامج TPRM وحدوده</v>
+      </c>
+      <c r="C3241" t="str">
+        <v>Jūsu TPRM programmas lietojuma un limitu pārskats</v>
+      </c>
+    </row>
+    <row r="3242">
+      <c r="A3242" t="str">
+        <v>Total Usage</v>
+      </c>
+      <c r="B3242" t="str">
+        <v>إجمالي الاستخدام</v>
+      </c>
+      <c r="C3242" t="str">
+        <v>Kopējais lietojums</v>
+      </c>
+    </row>
+    <row r="3243">
+      <c r="A3243" t="str">
+        <v>assessments</v>
+      </c>
+      <c r="B3243" t="str">
+        <v>التقييمات</v>
+      </c>
+      <c r="C3243" t="str">
+        <v>novērtējumi</v>
+      </c>
+    </row>
+    <row r="3244">
+      <c r="A3244" t="str">
+        <v>vendors</v>
+      </c>
+      <c r="B3244" t="str">
+        <v>الموردون</v>
+      </c>
+      <c r="C3244" t="str">
+        <v>piegādātāji</v>
+      </c>
+    </row>
+    <row r="3245">
+      <c r="A3245" t="str">
+        <v>DueDiligence Configuration</v>
+      </c>
+      <c r="B3245" t="str">
+        <v>تكوين العناية الواجبة</v>
+      </c>
+      <c r="C3245" t="str">
+        <v>Pienācīgas pārbaudes konfigurācija</v>
+      </c>
+    </row>
+    <row r="3246">
+      <c r="A3246" t="str">
+        <v>Scorecard Configuration</v>
+      </c>
+      <c r="B3246" t="str">
+        <v>تكوين بطاقة الأداء</v>
+      </c>
+      <c r="C3246" t="str">
+        <v>Rezultātu kartes konfigurācija</v>
+      </c>
+    </row>
+    <row r="3247">
+      <c r="A3247" t="str">
+        <v>Vendor Risk Rating Reference</v>
+      </c>
+      <c r="B3247" t="str">
+        <v>مرجع تصنيف مخاطر المورد</v>
+      </c>
+      <c r="C3247" t="str">
+        <v>Piegādātāja riska novērtējuma atsauce</v>
+      </c>
+    </row>
+    <row r="3248">
+      <c r="A3248" t="str">
+        <v>Configuration saved</v>
+      </c>
+      <c r="B3248" t="str">
+        <v>تم حفظ التكوين</v>
+      </c>
+      <c r="C3248" t="str">
+        <v>Konfigurācija saglabāta</v>
+      </c>
+    </row>
+    <row r="3249">
+      <c r="A3249" t="str">
+        <v>Control center settings have been updated successfully.</v>
+      </c>
+      <c r="B3249" t="str">
+        <v>تم تحديث إعدادات مركز التحكم بنجاح.</v>
+      </c>
+      <c r="C3249" t="str">
+        <v>Vadības centra iestatījumi ir veiksmīgi atjaunināti.</v>
+      </c>
+    </row>
+    <row r="3250">
+      <c r="A3250" t="str">
+        <v>Configure due diligence and scorecard thresholds</v>
+      </c>
+      <c r="B3250" t="str">
+        <v>تكوين عتبات العناية الواجبة وبطاقة الأداء</v>
+      </c>
+      <c r="C3250" t="str">
+        <v>Konfigurēt pienācīgas pārbaudes un rezultātu kartes sliekšņus</v>
+      </c>
+    </row>
+    <row r="3251">
+      <c r="A3251" t="str">
+        <v>Security Score</v>
+      </c>
+      <c r="B3251" t="str">
+        <v>درجة الأمان</v>
+      </c>
+      <c r="C3251" t="str">
+        <v>Drošības rādītājs</v>
+      </c>
+    </row>
+    <row r="3252">
+      <c r="A3252" t="str">
+        <v>Security Posture Score</v>
+      </c>
+      <c r="B3252" t="str">
+        <v>درجة الوضع الأمني</v>
+      </c>
+      <c r="C3252" t="str">
+        <v>Drošības stāvokļa rādītājs</v>
+      </c>
+    </row>
+    <row r="3253">
+      <c r="A3253" t="str">
+        <v>Security Posture Score Matrix</v>
+      </c>
+      <c r="B3253" t="str">
+        <v>مصفوفة درجة الوضع الأمني</v>
+      </c>
+      <c r="C3253" t="str">
+        <v>Drošības stāvokļa rādītāju matrica</v>
+      </c>
+    </row>
+    <row r="3254">
+      <c r="A3254" t="str">
+        <v>Threat Exposure Score</v>
+      </c>
+      <c r="B3254" t="str">
+        <v>درجة التعرض للتهديدات</v>
+      </c>
+      <c r="C3254" t="str">
+        <v>Draudu iedarbības rādītājs</v>
+      </c>
+    </row>
+    <row r="3255">
+      <c r="A3255" t="str">
+        <v>Threat Exposure Score Matrix</v>
+      </c>
+      <c r="B3255" t="str">
+        <v>مصفوفة درجة التعرض للتهديدات</v>
+      </c>
+      <c r="C3255" t="str">
+        <v>Draudu iedarbības rādītāju matrica</v>
+      </c>
+    </row>
+    <row r="3256">
+      <c r="A3256" t="str">
+        <v>Scoring Formula</v>
+      </c>
+      <c r="B3256" t="str">
+        <v>صيغة التسجيل</v>
+      </c>
+      <c r="C3256" t="str">
+        <v>Vērtēšanas formula</v>
+      </c>
+    </row>
+    <row r="3257">
+      <c r="A3257" t="str">
+        <v>AVG (Average)</v>
+      </c>
+      <c r="B3257" t="str">
+        <v>المتوسط</v>
+      </c>
+      <c r="C3257" t="str">
+        <v>Vidējais</v>
+      </c>
+    </row>
+    <row r="3258">
+      <c r="A3258" t="str">
+        <v>SUM (Summation)</v>
+      </c>
+      <c r="B3258" t="str">
+        <v>المجموع</v>
+      </c>
+      <c r="C3258" t="str">
+        <v>Summa</v>
+      </c>
+    </row>
+    <row r="3259">
+      <c r="A3259" t="str">
+        <v>Weightage</v>
+      </c>
+      <c r="B3259" t="str">
+        <v>الوزن</v>
+      </c>
+      <c r="C3259" t="str">
+        <v>Svērums</v>
+      </c>
+    </row>
+    <row r="3260">
+      <c r="A3260" t="str">
+        <v>Failed to save configuration</v>
+      </c>
+      <c r="B3260" t="str">
+        <v>فشل في حفظ التكوين</v>
+      </c>
+      <c r="C3260" t="str">
+        <v>Neizdevās saglabāt konfigurāciju</v>
+      </c>
+    </row>
+    <row r="3261">
+      <c r="A3261" t="str">
+        <v>Admin user full name</v>
+      </c>
+      <c r="B3261" t="str">
+        <v>الاسم الكامل للمسؤول</v>
+      </c>
+      <c r="C3261" t="str">
+        <v>Administratora pilns vārds</v>
+      </c>
+    </row>
+    <row r="3262">
+      <c r="A3262" t="str">
+        <v>Confirm password is required</v>
+      </c>
+      <c r="B3262" t="str">
+        <v>تأكيد كلمة المرور مطلوب</v>
+      </c>
+      <c r="C3262" t="str">
+        <v>Paroles apstiprināšana ir obligāta</v>
+      </c>
+    </row>
+    <row r="3263">
+      <c r="A3263" t="str">
+        <v>Email is required</v>
+      </c>
+      <c r="B3263" t="str">
+        <v>البريد الإلكتروني مطلوب</v>
+      </c>
+      <c r="C3263" t="str">
+        <v>E-pasts ir obligāts</v>
+      </c>
+    </row>
+    <row r="3264">
+      <c r="A3264" t="str">
+        <v>Full name is required</v>
+      </c>
+      <c r="B3264" t="str">
+        <v>الاسم الكامل مطلوب</v>
+      </c>
+      <c r="C3264" t="str">
+        <v>Pilns vārds ir obligāts</v>
+      </c>
+    </row>
+    <row r="3265">
+      <c r="A3265" t="str">
+        <v>Leave blank to keep current</v>
+      </c>
+      <c r="B3265" t="str">
+        <v>اترك فارغاً للإبقاء على الحالي</v>
+      </c>
+      <c r="C3265" t="str">
+        <v>Atstājiet tukšu, lai saglabātu pašreizējo</v>
+      </c>
+    </row>
+    <row r="3266">
+      <c r="A3266" t="str">
+        <v>Leave blank to keep current password</v>
+      </c>
+      <c r="B3266" t="str">
+        <v>اترك فارغاً للإبقاء على كلمة المرور الحالية</v>
+      </c>
+      <c r="C3266" t="str">
+        <v>Atstājiet tukšu, lai saglabātu pašreizējo paroli</v>
+      </c>
+    </row>
+    <row r="3267">
+      <c r="A3267" t="str">
+        <v>New password</v>
+      </c>
+      <c r="B3267" t="str">
+        <v>كلمة مرور جديدة</v>
+      </c>
+      <c r="C3267" t="str">
+        <v>Jauna parole</v>
+      </c>
+    </row>
+    <row r="3268">
+      <c r="A3268" t="str">
+        <v>Select Function</v>
+      </c>
+      <c r="B3268" t="str">
+        <v>اختر الوظيفة</v>
+      </c>
+      <c r="C3268" t="str">
+        <v>Izvēlēties funkciju</v>
+      </c>
+    </row>
+    <row r="3269">
+      <c r="A3269" t="str">
+        <v>Select Function first</v>
+      </c>
+      <c r="B3269" t="str">
+        <v>اختر الوظيفة أولاً</v>
+      </c>
+      <c r="C3269" t="str">
+        <v>Vispirms izvēlēties funkciju</v>
+      </c>
+    </row>
+    <row r="3270">
+      <c r="A3270" t="str">
+        <v>Select Role</v>
+      </c>
+      <c r="B3270" t="str">
+        <v>اختر الدور</v>
+      </c>
+      <c r="C3270" t="str">
+        <v>Izvēlēties lomu</v>
+      </c>
+    </row>
+    <row r="3271">
+      <c r="A3271" t="str">
+        <v>Please Select the Function</v>
+      </c>
+      <c r="B3271" t="str">
+        <v>يرجى اختيار الوظيفة</v>
+      </c>
+      <c r="C3271" t="str">
+        <v>Lūdzu izvēlieties funkciju</v>
+      </c>
+    </row>
+    <row r="3272">
+      <c r="A3272" t="str">
+        <v>Please enter the assessment limit.</v>
+      </c>
+      <c r="B3272" t="str">
+        <v>يرجى إدخال حد التقييم.</v>
+      </c>
+      <c r="C3272" t="str">
+        <v>Lūdzu ievadiet novērtējuma limitu.</v>
+      </c>
+    </row>
+    <row r="3273">
+      <c r="A3273" t="str">
+        <v>Please enter the vendor limit.</v>
+      </c>
+      <c r="B3273" t="str">
+        <v>يرجى إدخال حد المورد.</v>
+      </c>
+      <c r="C3273" t="str">
+        <v>Lūdzu ievadiet piegādātāja limitu.</v>
+      </c>
+    </row>
+    <row r="3274">
+      <c r="A3274" t="str">
+        <v>User created successfully</v>
+      </c>
+      <c r="B3274" t="str">
+        <v>تم إنشاء المستخدم بنجاح</v>
+      </c>
+      <c r="C3274" t="str">
+        <v>Lietotājs veiksmīgi izveidots</v>
+      </c>
+    </row>
+    <row r="3275">
+      <c r="A3275" t="str">
+        <v>User deleted successfully</v>
+      </c>
+      <c r="B3275" t="str">
+        <v>تم حذف المستخدم بنجاح</v>
+      </c>
+      <c r="C3275" t="str">
+        <v>Lietotājs veiksmīgi dzēsts</v>
+      </c>
+    </row>
+    <row r="3276">
+      <c r="A3276" t="str">
+        <v>User updated successfully</v>
+      </c>
+      <c r="B3276" t="str">
+        <v>تم تحديث المستخدم بنجاح</v>
+      </c>
+      <c r="C3276" t="str">
+        <v>Lietotājs veiksmīgi atjaunināts</v>
+      </c>
+    </row>
+    <row r="3277">
+      <c r="A3277" t="str">
+        <v>Failed to load user details</v>
+      </c>
+      <c r="B3277" t="str">
+        <v>فشل في تحميل تفاصيل المستخدم</v>
+      </c>
+      <c r="C3277" t="str">
+        <v>Neizdevās ielādēt lietotāja informāciju</v>
+      </c>
+    </row>
+    <row r="3278">
+      <c r="A3278" t="str">
+        <v>Failed to update user</v>
+      </c>
+      <c r="B3278" t="str">
+        <v>فشل في تحديث المستخدم</v>
+      </c>
+      <c r="C3278" t="str">
+        <v>Neizdevās atjaunināt lietotāju</v>
+      </c>
+    </row>
+    <row r="3279">
+      <c r="A3279" t="str">
+        <v>FullName</v>
+      </c>
+      <c r="B3279" t="str">
+        <v>الاسم الكامل</v>
+      </c>
+      <c r="C3279" t="str">
+        <v>Pilns vārds</v>
+      </c>
+    </row>
+    <row r="3280">
+      <c r="A3280" t="str">
+        <v>Configure TPRM module settings and parameters</v>
+      </c>
+      <c r="B3280" t="str">
+        <v>تكوين إعدادات ومعلمات وحدة TPRM</v>
+      </c>
+      <c r="C3280" t="str">
+        <v>Konfigurēt TPRM moduļa iestatījumus un parametrus</v>
+      </c>
+    </row>
+    <row r="3281">
+      <c r="A3281" t="str">
+        <v>Configure TPRM system settings and preferences</v>
+      </c>
+      <c r="B3281" t="str">
+        <v>تكوين إعدادات وتفضيلات نظام TPRM</v>
+      </c>
+      <c r="C3281" t="str">
+        <v>Konfigurēt TPRM sistēmas iestatījumus un preferences</v>
+      </c>
+    </row>
+    <row r="3282">
+      <c r="A3282" t="str">
+        <v>Get help and support for TPRM module</v>
+      </c>
+      <c r="B3282" t="str">
+        <v>الحصول على المساعدة والدعم لوحدة TPRM</v>
+      </c>
+      <c r="C3282" t="str">
+        <v>Saņemt palīdzību un atbalstu TPRM modulim</v>
+      </c>
+    </row>
+    <row r="3283">
+      <c r="A3283" t="str">
+        <v>Manage and monitor your third-party vendors</v>
+      </c>
+      <c r="B3283" t="str">
+        <v>إدارة ومراقبة موردي الطرف الثالث</v>
+      </c>
+      <c r="C3283" t="str">
+        <v>Pārvaldīt un uzraudzīt trešo pušu piegādātājus</v>
+      </c>
+    </row>
+    <row r="3284">
+      <c r="A3284" t="str">
+        <v>Manage master data for third-party risk management</v>
+      </c>
+      <c r="B3284" t="str">
+        <v>إدارة البيانات الرئيسية لإدارة مخاطر الأطراف الثالثة</v>
+      </c>
+      <c r="C3284" t="str">
+        <v>Pārvaldīt pamatdatus trešo pušu risku pārvaldībai</v>
+      </c>
+    </row>
+    <row r="3285">
+      <c r="A3285" t="str">
+        <v>Monitor third-party risk activities and alerts</v>
+      </c>
+      <c r="B3285" t="str">
+        <v>مراقبة أنشطة وتنبيهات مخاطر الطرف الثالث</v>
+      </c>
+      <c r="C3285" t="str">
+        <v>Uzraudzīt trešo pušu risku aktivitātes un brīdinājumus</v>
+      </c>
+    </row>
+    <row r="3286">
+      <c r="A3286" t="str">
+        <v>View and generate TPRM reports</v>
+      </c>
+      <c r="B3286" t="str">
+        <v>عرض وإنشاء تقارير TPRM</v>
+      </c>
+      <c r="C3286" t="str">
+        <v>Skatīt un ģenerēt TPRM pārskatus</v>
+      </c>
+    </row>
+    <row r="3287">
+      <c r="A3287" t="str">
+        <v>This feature is under development</v>
+      </c>
+      <c r="B3287" t="str">
+        <v>هذه الميزة قيد التطوير</v>
+      </c>
+      <c r="C3287" t="str">
+        <v>Šī funkcija tiek izstrādāta</v>
+      </c>
+    </row>
+    <row r="3288">
+      <c r="A3288" t="str">
+        <v>Coming Soon</v>
+      </c>
+      <c r="B3288" t="str">
+        <v>قريباً</v>
+      </c>
+      <c r="C3288" t="str">
+        <v>Drīzumā</v>
+      </c>
+    </row>
+    <row r="3289">
+      <c r="A3289" t="str">
+        <v>Vendor Profile Fields</v>
+      </c>
+      <c r="B3289" t="str">
+        <v>حقول ملف المورد</v>
+      </c>
+      <c r="C3289" t="str">
+        <v>Piegādātāja profila lauki</v>
+      </c>
+    </row>
+    <row r="3290">
+      <c r="A3290" t="str">
+        <v>Onboarding Questions</v>
+      </c>
+      <c r="B3290" t="str">
+        <v>أسئلة التسجيل</v>
+      </c>
+      <c r="C3290" t="str">
+        <v>Reģistrācijas jautājumi</v>
+      </c>
+    </row>
+    <row r="3291">
+      <c r="A3291" t="str">
+        <v>Add Field</v>
+      </c>
+      <c r="B3291" t="str">
+        <v>إضافة حقل</v>
+      </c>
+      <c r="C3291" t="str">
+        <v>Pievienot lauku</v>
+      </c>
+    </row>
+    <row r="3292">
+      <c r="A3292" t="str">
+        <v>Edit Field</v>
+      </c>
+      <c r="B3292" t="str">
+        <v>تعديل الحقل</v>
+      </c>
+      <c r="C3292" t="str">
+        <v>Rediģēt lauku</v>
+      </c>
+    </row>
+    <row r="3293">
+      <c r="A3293" t="str">
+        <v>Field Title</v>
+      </c>
+      <c r="B3293" t="str">
+        <v>عنوان الحقل</v>
+      </c>
+      <c r="C3293" t="str">
+        <v>Lauka nosaukums</v>
+      </c>
+    </row>
+    <row r="3294">
+      <c r="A3294" t="str">
+        <v>Enter field name</v>
+      </c>
+      <c r="B3294" t="str">
+        <v>أدخل اسم الحقل</v>
+      </c>
+      <c r="C3294" t="str">
+        <v>Ievadiet lauka nosaukumu</v>
+      </c>
+    </row>
+    <row r="3295">
+      <c r="A3295" t="str">
+        <v>Field created</v>
+      </c>
+      <c r="B3295" t="str">
+        <v>تم إنشاء الحقل</v>
+      </c>
+      <c r="C3295" t="str">
+        <v>Lauks izveidots</v>
+      </c>
+    </row>
+    <row r="3296">
+      <c r="A3296" t="str">
+        <v>Field updated</v>
+      </c>
+      <c r="B3296" t="str">
+        <v>تم تحديث الحقل</v>
+      </c>
+      <c r="C3296" t="str">
+        <v>Lauks atjaunināts</v>
+      </c>
+    </row>
+    <row r="3297">
+      <c r="A3297" t="str">
+        <v>Field deleted</v>
+      </c>
+      <c r="B3297" t="str">
+        <v>تم حذف الحقل</v>
+      </c>
+      <c r="C3297" t="str">
+        <v>Lauks dzēsts</v>
+      </c>
+    </row>
+    <row r="3298">
+      <c r="A3298" t="str">
+        <v>Failed to load profile fields</v>
+      </c>
+      <c r="B3298" t="str">
+        <v>فشل في تحميل حقول الملف الشخصي</v>
+      </c>
+      <c r="C3298" t="str">
+        <v>Neizdevās ielādēt profila laukus</v>
+      </c>
+    </row>
+    <row r="3299">
+      <c r="A3299" t="str">
+        <v>Add Question</v>
+      </c>
+      <c r="B3299" t="str">
+        <v>إضافة سؤال</v>
+      </c>
+      <c r="C3299" t="str">
+        <v>Pievienot jautājumu</v>
+      </c>
+    </row>
+    <row r="3300">
+      <c r="A3300" t="str">
+        <v>Edit Question</v>
+      </c>
+      <c r="B3300" t="str">
+        <v>تعديل السؤال</v>
+      </c>
+      <c r="C3300" t="str">
+        <v>Rediģēt jautājumu</v>
+      </c>
+    </row>
+    <row r="3301">
+      <c r="A3301" t="str">
+        <v>Question Title</v>
+      </c>
+      <c r="B3301" t="str">
+        <v>عنوان السؤال</v>
+      </c>
+      <c r="C3301" t="str">
+        <v>Jautājuma nosaukums</v>
+      </c>
+    </row>
+    <row r="3302">
+      <c r="A3302" t="str">
+        <v>Enter question title</v>
+      </c>
+      <c r="B3302" t="str">
+        <v>أدخل عنوان السؤال</v>
+      </c>
+      <c r="C3302" t="str">
+        <v>Ievadiet jautājuma nosaukumu</v>
+      </c>
+    </row>
+    <row r="3303">
+      <c r="A3303" t="str">
+        <v>Question</v>
+      </c>
+      <c r="B3303" t="str">
+        <v>السؤال</v>
+      </c>
+      <c r="C3303" t="str">
+        <v>Jautājums</v>
+      </c>
+    </row>
+    <row r="3304">
+      <c r="A3304" t="str">
+        <v>Enter question text</v>
+      </c>
+      <c r="B3304" t="str">
+        <v>أدخل نص السؤال</v>
+      </c>
+      <c r="C3304" t="str">
+        <v>Ievadiet jautājuma tekstu</v>
+      </c>
+    </row>
+    <row r="3305">
+      <c r="A3305" t="str">
+        <v>Enter question</v>
+      </c>
+      <c r="B3305" t="str">
+        <v>أدخل السؤال</v>
+      </c>
+      <c r="C3305" t="str">
+        <v>Ievadiet jautājumu</v>
+      </c>
+    </row>
+    <row r="3306">
+      <c r="A3306" t="str">
+        <v>Question Type</v>
+      </c>
+      <c r="B3306" t="str">
+        <v>نوع السؤال</v>
+      </c>
+      <c r="C3306" t="str">
+        <v>Jautājuma veids</v>
+      </c>
+    </row>
+    <row r="3307">
+      <c r="A3307" t="str">
+        <v>Response Type</v>
+      </c>
+      <c r="B3307" t="str">
+        <v>نوع الاستجابة</v>
+      </c>
+      <c r="C3307" t="str">
+        <v>Atbildes veids</v>
+      </c>
+    </row>
+    <row r="3308">
+      <c r="A3308" t="str">
+        <v>Yes/No</v>
+      </c>
+      <c r="B3308" t="str">
+        <v>نعم/لا</v>
+      </c>
+      <c r="C3308" t="str">
+        <v>Jā/Nē</v>
+      </c>
+    </row>
+    <row r="3309">
+      <c r="A3309" t="str">
+        <v>Free Text</v>
+      </c>
+      <c r="B3309" t="str">
+        <v>نص حر</v>
+      </c>
+      <c r="C3309" t="str">
+        <v>Brīvs teksts</v>
+      </c>
+    </row>
+    <row r="3310">
+      <c r="A3310" t="str">
+        <v>Parent</v>
+      </c>
+      <c r="B3310" t="str">
+        <v>الأصل</v>
+      </c>
+      <c r="C3310" t="str">
+        <v>Vecāks</v>
+      </c>
+    </row>
+    <row r="3311">
+      <c r="A3311" t="str">
+        <v>Child</v>
+      </c>
+      <c r="B3311" t="str">
+        <v>فرعي</v>
+      </c>
+      <c r="C3311" t="str">
+        <v>Bērns</v>
+      </c>
+    </row>
+    <row r="3312">
+      <c r="A3312" t="str">
+        <v>Question created</v>
+      </c>
+      <c r="B3312" t="str">
+        <v>تم إنشاء السؤال</v>
+      </c>
+      <c r="C3312" t="str">
+        <v>Jautājums izveidots</v>
+      </c>
+    </row>
+    <row r="3313">
+      <c r="A3313" t="str">
+        <v>Question updated</v>
+      </c>
+      <c r="B3313" t="str">
+        <v>تم تحديث السؤال</v>
+      </c>
+      <c r="C3313" t="str">
+        <v>Jautājums atjaunināts</v>
+      </c>
+    </row>
+    <row r="3314">
+      <c r="A3314" t="str">
+        <v>Question deleted</v>
+      </c>
+      <c r="B3314" t="str">
+        <v>تم حذف السؤال</v>
+      </c>
+      <c r="C3314" t="str">
+        <v>Jautājums dzēsts</v>
+      </c>
+    </row>
+    <row r="3315">
+      <c r="A3315" t="str">
+        <v>Failed to load questions</v>
+      </c>
+      <c r="B3315" t="str">
+        <v>فشل في تحميل الأسئلة</v>
+      </c>
+      <c r="C3315" t="str">
+        <v>Neizdevās ielādēt jautājumus</v>
+      </c>
+    </row>
+    <row r="3316">
+      <c r="A3316" t="str">
+        <v>Question Fields</v>
+      </c>
+      <c r="B3316" t="str">
+        <v>حقول السؤال</v>
+      </c>
+      <c r="C3316" t="str">
+        <v>Jautājuma lauki</v>
+      </c>
+    </row>
+    <row r="3317">
+      <c r="A3317" t="str">
+        <v>Question No</v>
+      </c>
+      <c r="B3317" t="str">
+        <v>رقم السؤال</v>
+      </c>
+      <c r="C3317" t="str">
+        <v>Jautājuma Nr.</v>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" t="str">
+        <v>Add Template</v>
+      </c>
+      <c r="B3318" t="str">
+        <v>إضافة قالب</v>
+      </c>
+      <c r="C3318" t="str">
+        <v>Pievienot veidni</v>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" t="str">
+        <v>Edit Template</v>
+      </c>
+      <c r="B3319" t="str">
+        <v>تعديل القالب</v>
+      </c>
+      <c r="C3319" t="str">
+        <v>Rediģēt veidni</v>
+      </c>
+    </row>
+    <row r="3320">
+      <c r="A3320" t="str">
+        <v>Template Category</v>
+      </c>
+      <c r="B3320" t="str">
+        <v>فئة القالب</v>
+      </c>
+      <c r="C3320" t="str">
+        <v>Veidnes kategorija</v>
+      </c>
+    </row>
+    <row r="3321">
+      <c r="A3321" t="str">
+        <v>Questionnaire Template</v>
+      </c>
+      <c r="B3321" t="str">
+        <v>قالب الاستبيان</v>
+      </c>
+      <c r="C3321" t="str">
+        <v>Anketas veidne</v>
+      </c>
+    </row>
+    <row r="3322">
+      <c r="A3322" t="str">
+        <v>Enter template name</v>
+      </c>
+      <c r="B3322" t="str">
+        <v>أدخل اسم القالب</v>
+      </c>
+      <c r="C3322" t="str">
+        <v>Ievadiet veidnes nosaukumu</v>
+      </c>
+    </row>
+    <row r="3323">
+      <c r="A3323" t="str">
+        <v>Template created</v>
+      </c>
+      <c r="B3323" t="str">
+        <v>تم إنشاء القالب</v>
+      </c>
+      <c r="C3323" t="str">
+        <v>Veidne izveidota</v>
+      </c>
+    </row>
+    <row r="3324">
+      <c r="A3324" t="str">
+        <v>Template updated</v>
+      </c>
+      <c r="B3324" t="str">
+        <v>تم تحديث القالب</v>
+      </c>
+      <c r="C3324" t="str">
+        <v>Veidne atjaunināta</v>
+      </c>
+    </row>
+    <row r="3325">
+      <c r="A3325" t="str">
+        <v>Template deleted</v>
+      </c>
+      <c r="B3325" t="str">
+        <v>تم حذف القالب</v>
+      </c>
+      <c r="C3325" t="str">
+        <v>Veidne dzēsta</v>
+      </c>
+    </row>
+    <row r="3326">
+      <c r="A3326" t="str">
+        <v>Failed to load templates</v>
+      </c>
+      <c r="B3326" t="str">
+        <v>فشل في تحميل القوالب</v>
+      </c>
+      <c r="C3326" t="str">
+        <v>Neizdevās ielādēt veidnes</v>
+      </c>
+    </row>
+    <row r="3327">
+      <c r="A3327" t="str">
+        <v>Formula</v>
+      </c>
+      <c r="B3327" t="str">
+        <v>الصيغة</v>
+      </c>
+      <c r="C3327" t="str">
+        <v>Formula</v>
+      </c>
+    </row>
+    <row r="3328">
+      <c r="A3328" t="str">
+        <v>Factor updated</v>
+      </c>
+      <c r="B3328" t="str">
+        <v>تم تحديث العامل</v>
+      </c>
+      <c r="C3328" t="str">
+        <v>Faktors atjaunināts</v>
+      </c>
+    </row>
+    <row r="3329">
+      <c r="A3329" t="str">
+        <v>Failed to load scorecard data</v>
+      </c>
+      <c r="B3329" t="str">
+        <v>فشل في تحميل بيانات بطاقة الأداء</v>
+      </c>
+      <c r="C3329" t="str">
+        <v>Neizdevās ielādēt rezultātu kartes datus</v>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" t="str">
+        <v>Failed to update factor</v>
+      </c>
+      <c r="B3330" t="str">
+        <v>فشل في تحديث العامل</v>
+      </c>
+      <c r="C3330" t="str">
+        <v>Neizdevās atjaunināt faktoru</v>
+      </c>
+    </row>
+    <row r="3331">
+      <c r="A3331" t="str">
+        <v>Failed to save</v>
+      </c>
+      <c r="B3331" t="str">
+        <v>فشل في الحفظ</v>
+      </c>
+      <c r="C3331" t="str">
+        <v>Neizdevās saglabāt</v>
+      </c>
+    </row>
+    <row r="3332">
+      <c r="A3332" t="str">
+        <v>Failed to delete</v>
+      </c>
+      <c r="B3332" t="str">
+        <v>فشل في الحذف</v>
+      </c>
+      <c r="C3332" t="str">
+        <v>Neizdevās dzēst</v>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" t="str">
+        <v>Failed to delete all</v>
+      </c>
+      <c r="B3333" t="str">
+        <v>فشل في حذف الكل</v>
+      </c>
+      <c r="C3333" t="str">
+        <v>Neizdevās dzēst visu</v>
+      </c>
+    </row>
+    <row r="3334">
+      <c r="A3334" t="str">
+        <v>Are you sure you want to delete all items?</v>
+      </c>
+      <c r="B3334" t="str">
+        <v>هل أنت متأكد من أنك تريد حذف جميع العناصر؟</v>
+      </c>
+      <c r="C3334" t="str">
+        <v>Vai tiešām vēlaties dzēst visus elementus?</v>
+      </c>
+    </row>
+    <row r="3335">
+      <c r="A3335" t="str">
+        <v>All items deleted</v>
+      </c>
+      <c r="B3335" t="str">
+        <v>تم حذف جميع العناصر</v>
+      </c>
+      <c r="C3335" t="str">
+        <v>Visi elementi dzēsti</v>
+      </c>
+    </row>
+    <row r="3336">
+      <c r="A3336" t="str">
+        <v>Account Information</v>
+      </c>
+      <c r="B3336" t="str">
+        <v>معلومات الحساب</v>
+      </c>
+      <c r="C3336" t="str">
+        <v>Konta informācija</v>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" t="str">
+        <v>Accounts Available</v>
+      </c>
+      <c r="B3337" t="str">
+        <v>الحسابات المتاحة</v>
+      </c>
+      <c r="C3337" t="str">
+        <v>Pieejamie konti</v>
+      </c>
+    </row>
+    <row r="3338">
+      <c r="A3338" t="str">
+        <v>Assessment Count</v>
+      </c>
+      <c r="B3338" t="str">
+        <v>عدد التقييمات</v>
+      </c>
+      <c r="C3338" t="str">
+        <v>Novērtējumu skaits</v>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" t="str">
+        <v>Create Factory Admin</v>
+      </c>
+      <c r="B3339" t="str">
+        <v>إنشاء مسؤول المصنع</v>
+      </c>
+      <c r="C3339" t="str">
+        <v>Izveidot rūpnīcas administratoru</v>
+      </c>
+    </row>
+    <row r="3340">
+      <c r="A3340" t="str">
+        <v>Create Factory Admin Account</v>
+      </c>
+      <c r="B3340" t="str">
+        <v>إنشاء حساب مسؤول المصنع</v>
+      </c>
+      <c r="C3340" t="str">
+        <v>Izveidot rūpnīcas administratora kontu</v>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" t="str">
+        <v>Create New Customer</v>
+      </c>
+      <c r="B3341" t="str">
+        <v>إنشاء عميل جديد</v>
+      </c>
+      <c r="C3341" t="str">
+        <v>Izveidot jaunu klientu</v>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" t="str">
+        <v>Create New SuperAdmin</v>
+      </c>
+      <c r="B3342" t="str">
+        <v>إنشاء مسؤول أعلى جديد</v>
+      </c>
+      <c r="C3342" t="str">
+        <v>Izveidot jaunu superadministratoru</v>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" t="str">
+        <v>Create New TPRM Admin Account</v>
+      </c>
+      <c r="B3343" t="str">
+        <v>إنشاء حساب مسؤول TPRM جديد</v>
+      </c>
+      <c r="C3343" t="str">
+        <v>Izveidot jaunu TPRM administratora kontu</v>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" t="str">
+        <v>Create New TPRM Customer Account</v>
+      </c>
+      <c r="B3344" t="str">
+        <v>إنشاء حساب عميل TPRM جديد</v>
+      </c>
+      <c r="C3344" t="str">
+        <v>Izveidot jaunu TPRM klienta kontu</v>
+      </c>
+    </row>
+    <row r="3345">
+      <c r="A3345" t="str">
+        <v>Created Date</v>
+      </c>
+      <c r="B3345" t="str">
+        <v>تاريخ الإنشاء</v>
+      </c>
+      <c r="C3345" t="str">
+        <v>Izveides datums</v>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" t="str">
+        <v>Customer Name</v>
+      </c>
+      <c r="B3346" t="str">
+        <v>اسم العميل</v>
+      </c>
+      <c r="C3346" t="str">
+        <v>Klienta nosaukums</v>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" t="str">
+        <v>Customer name is required</v>
+      </c>
+      <c r="B3347" t="str">
+        <v>اسم العميل مطلوب</v>
+      </c>
+      <c r="C3347" t="str">
+        <v>Klienta nosaukums ir obligāts</v>
+      </c>
+    </row>
+    <row r="3348">
+      <c r="A3348" t="str">
+        <v>Delete Account</v>
+      </c>
+      <c r="B3348" t="str">
+        <v>حذف الحساب</v>
+      </c>
+      <c r="C3348" t="str">
+        <v>Dzēst kontu</v>
+      </c>
+    </row>
+    <row r="3349">
+      <c r="A3349" t="str">
+        <v>Delete Super Admin</v>
+      </c>
+      <c r="B3349" t="str">
+        <v>حذف المسؤول الأعلى</v>
+      </c>
+      <c r="C3349" t="str">
+        <v>Dzēst superadministratoru</v>
+      </c>
+    </row>
+    <row r="3350">
+      <c r="A3350" t="str">
+        <v>Enter customer name</v>
+      </c>
+      <c r="B3350" t="str">
+        <v>أدخل اسم العميل</v>
+      </c>
+      <c r="C3350" t="str">
+        <v>Ievadiet klienta nosaukumu</v>
+      </c>
+    </row>
+    <row r="3351">
+      <c r="A3351" t="str">
+        <v>Enter email address</v>
+      </c>
+      <c r="B3351" t="str">
+        <v>أدخل عنوان البريد الإلكتروني</v>
+      </c>
+      <c r="C3351" t="str">
+        <v>Ievadiet e-pasta adresi</v>
+      </c>
+    </row>
+    <row r="3352">
+      <c r="A3352" t="str">
+        <v>Expiry date</v>
+      </c>
+      <c r="B3352" t="str">
+        <v>تاريخ الانتهاء</v>
+      </c>
+      <c r="C3352" t="str">
+        <v>Derīguma termiņš</v>
+      </c>
+    </row>
+    <row r="3353">
+      <c r="A3353" t="str">
+        <v>Failed to create account</v>
+      </c>
+      <c r="B3353" t="str">
+        <v>فشل في إنشاء الحساب</v>
+      </c>
+      <c r="C3353" t="str">
+        <v>Neizdevās izveidot kontu</v>
+      </c>
+    </row>
+    <row r="3354">
+      <c r="A3354" t="str">
+        <v>Failed to delete account</v>
+      </c>
+      <c r="B3354" t="str">
+        <v>فشل في حذف الحساب</v>
+      </c>
+      <c r="C3354" t="str">
+        <v>Neizdevās dzēst kontu</v>
+      </c>
+    </row>
+    <row r="3355">
+      <c r="A3355" t="str">
+        <v>Failed to update account</v>
+      </c>
+      <c r="B3355" t="str">
+        <v>فشل في تحديث الحساب</v>
+      </c>
+      <c r="C3355" t="str">
+        <v>Neizdevās atjaunināt kontu</v>
+      </c>
+    </row>
+    <row r="3356">
+      <c r="A3356" t="str">
+        <v>Frameworks Available</v>
+      </c>
+      <c r="B3356" t="str">
+        <v>الأطر المتاحة</v>
+      </c>
+      <c r="C3356" t="str">
+        <v>Pieejamie ietvari</v>
+      </c>
+    </row>
+    <row r="3357">
+      <c r="A3357" t="str">
+        <v>Is GRC Added</v>
+      </c>
+      <c r="B3357" t="str">
+        <v>هل تم إضافة GRC</v>
+      </c>
+      <c r="C3357" t="str">
+        <v>Vai GRC ir pievienots</v>
+      </c>
+    </row>
+    <row r="3358">
+      <c r="A3358" t="str">
+        <v>Is Local User</v>
+      </c>
+      <c r="B3358" t="str">
+        <v>هل هو مستخدم محلي</v>
+      </c>
+      <c r="C3358" t="str">
+        <v>Vai ir lokāls lietotājs</v>
+      </c>
+    </row>
+    <row r="3359">
+      <c r="A3359" t="str">
+        <v>Max accounts</v>
+      </c>
+      <c r="B3359" t="str">
+        <v>الحد الأقصى للحسابات</v>
+      </c>
+      <c r="C3359" t="str">
+        <v>Maksimālais kontu skaits</v>
+      </c>
+    </row>
+    <row r="3360">
+      <c r="A3360" t="str">
+        <v>Max frameworks</v>
+      </c>
+      <c r="B3360" t="str">
+        <v>الحد الأقصى للأطر</v>
+      </c>
+      <c r="C3360" t="str">
+        <v>Maksimālais ietvaru skaits</v>
+      </c>
+    </row>
+    <row r="3361">
+      <c r="A3361" t="str">
+        <v>New Subscription</v>
+      </c>
+      <c r="B3361" t="str">
+        <v>اشتراك جديد</v>
+      </c>
+      <c r="C3361" t="str">
+        <v>Jauns abonements</v>
+      </c>
+    </row>
+    <row r="3362">
+      <c r="A3362" t="str">
+        <v>Phone Number</v>
+      </c>
+      <c r="B3362" t="str">
+        <v>رقم الهاتف</v>
+      </c>
+      <c r="C3362" t="str">
+        <v>Tālruņa numurs</v>
+      </c>
+    </row>
+    <row r="3363">
+      <c r="A3363" t="str">
+        <v>Start date</v>
+      </c>
+      <c r="B3363" t="str">
+        <v>تاريخ البدء</v>
+      </c>
+      <c r="C3363" t="str">
+        <v>Sākuma datums</v>
+      </c>
+    </row>
+    <row r="3364">
+      <c r="A3364" t="str">
+        <v>Subscription Plan</v>
+      </c>
+      <c r="B3364" t="str">
+        <v>خطة الاشتراك</v>
+      </c>
+      <c r="C3364" t="str">
+        <v>Abonementa plāns</v>
+      </c>
+    </row>
+    <row r="3365">
+      <c r="A3365" t="str">
+        <v>Subscription Plans</v>
+      </c>
+      <c r="B3365" t="str">
+        <v>خطط الاشتراك</v>
+      </c>
+      <c r="C3365" t="str">
+        <v>Abonementa plāni</v>
+      </c>
+    </row>
+    <row r="3366">
+      <c r="A3366" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="B3366" t="str">
+        <v>المسؤول الأعلى</v>
+      </c>
+      <c r="C3366" t="str">
+        <v>Superadministrators</v>
+      </c>
+    </row>
+    <row r="3367">
+      <c r="A3367" t="str">
+        <v>Vendor Accounts</v>
+      </c>
+      <c r="B3367" t="str">
+        <v>حسابات الموردين</v>
+      </c>
+      <c r="C3367" t="str">
+        <v>Piegādātāju konti</v>
+      </c>
+    </row>
+    <row r="3368">
+      <c r="A3368" t="str">
+        <v>This will permanently delete the account, all associated users, vendors, assessments, and subscription plans. This action cannot be undone.</v>
+      </c>
+      <c r="B3368" t="str">
+        <v>سيؤدي هذا إلى حذف الحساب نهائياً وجميع المستخدمين والموردين والتقييمات وخطط الاشتراك المرتبطة. لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C3368" t="str">
+        <v>Tas neatgriezeniski dzēsīs kontu, visus saistītos lietotājus, piegādātājus, novērtējumus un abonementa plānus. Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="3369">
+      <c r="A3369" t="str">
+        <v>Are you sure you want to delete the account</v>
+      </c>
+      <c r="B3369" t="str">
+        <v>هل أنت متأكد من أنك تريد حذف الحساب</v>
+      </c>
+      <c r="C3369" t="str">
+        <v>Vai tiešām vēlaties dzēst kontu</v>
+      </c>
+    </row>
+    <row r="3370">
+      <c r="A3370" t="str">
+        <v>Assessment Detail</v>
+      </c>
+      <c r="B3370" t="str">
+        <v>تفاصيل التقييم</v>
+      </c>
+      <c r="C3370" t="str">
+        <v>Novērtējuma detaļas</v>
+      </c>
+    </row>
+    <row r="3371">
+      <c r="A3371" t="str">
+        <v>Assessment ID</v>
+      </c>
+      <c r="B3371" t="str">
+        <v>معرف التقييم</v>
+      </c>
+      <c r="C3371" t="str">
+        <v>Novērtējuma ID</v>
+      </c>
+    </row>
+    <row r="3372">
+      <c r="A3372" t="str">
+        <v>Assessment Logs</v>
+      </c>
+      <c r="B3372" t="str">
+        <v>سجلات التقييم</v>
+      </c>
+      <c r="C3372" t="str">
+        <v>Novērtējumu žurnāli</v>
+      </c>
+    </row>
+    <row r="3373">
+      <c r="A3373" t="str">
+        <v>Assessment Overview</v>
+      </c>
+      <c r="B3373" t="str">
+        <v>نظرة عامة على التقييم</v>
+      </c>
+      <c r="C3373" t="str">
+        <v>Novērtējumu pārskats</v>
+      </c>
+    </row>
+    <row r="3374">
+      <c r="A3374" t="str">
+        <v>Assessment Result</v>
+      </c>
+      <c r="B3374" t="str">
+        <v>نتيجة التقييم</v>
+      </c>
+      <c r="C3374" t="str">
+        <v>Novērtējuma rezultāts</v>
+      </c>
+    </row>
+    <row r="3375">
+      <c r="A3375" t="str">
+        <v>Assessment Template</v>
+      </c>
+      <c r="B3375" t="str">
+        <v>قالب التقييم</v>
+      </c>
+      <c r="C3375" t="str">
+        <v>Novērtējuma veidne</v>
+      </c>
+    </row>
+    <row r="3376">
+      <c r="A3376" t="str">
+        <v>Assessment Type</v>
+      </c>
+      <c r="B3376" t="str">
+        <v>نوع التقييم</v>
+      </c>
+      <c r="C3376" t="str">
+        <v>Novērtējuma veids</v>
+      </c>
+    </row>
+    <row r="3377">
+      <c r="A3377" t="str">
+        <v>Assessor</v>
+      </c>
+      <c r="B3377" t="str">
+        <v>المقيم</v>
+      </c>
+      <c r="C3377" t="str">
+        <v>Novērtētājs</v>
+      </c>
+    </row>
+    <row r="3378">
+      <c r="A3378" t="str">
+        <v>Assessor Completion Date</v>
+      </c>
+      <c r="B3378" t="str">
+        <v>تاريخ إتمام المقيم</v>
+      </c>
+      <c r="C3378" t="str">
+        <v>Novērtētāja pabeigšanas datums</v>
+      </c>
+    </row>
+    <row r="3379">
+      <c r="A3379" t="str">
+        <v>Approval Date</v>
+      </c>
+      <c r="B3379" t="str">
+        <v>تاريخ الموافقة</v>
+      </c>
+      <c r="C3379" t="str">
+        <v>Apstiprināšanas datums</v>
+      </c>
+    </row>
+    <row r="3380">
+      <c r="A3380" t="str">
+        <v>Approver Comment</v>
+      </c>
+      <c r="B3380" t="str">
+        <v>تعليق الموافق</v>
+      </c>
+      <c r="C3380" t="str">
+        <v>Apstiprinātāja komentārs</v>
+      </c>
+    </row>
+    <row r="3381">
+      <c r="A3381" t="str">
+        <v>Completion Date</v>
+      </c>
+      <c r="B3381" t="str">
+        <v>تاريخ الإتمام</v>
+      </c>
+      <c r="C3381" t="str">
+        <v>Pabeigšanas datums</v>
+      </c>
+    </row>
+    <row r="3382">
+      <c r="A3382" t="str">
+        <v>Date of Submission</v>
+      </c>
+      <c r="B3382" t="str">
+        <v>تاريخ التقديم</v>
+      </c>
+      <c r="C3382" t="str">
+        <v>Iesniegšanas datums</v>
+      </c>
+    </row>
+    <row r="3383">
+      <c r="A3383" t="str">
+        <v>Initiated By</v>
+      </c>
+      <c r="B3383" t="str">
+        <v>بدأه</v>
+      </c>
+      <c r="C3383" t="str">
+        <v>Iniciēja</v>
+      </c>
+    </row>
+    <row r="3384">
+      <c r="A3384" t="str">
+        <v>Log Date</v>
+      </c>
+      <c r="B3384" t="str">
+        <v>تاريخ السجل</v>
+      </c>
+      <c r="C3384" t="str">
+        <v>Žurnāla datums</v>
+      </c>
+    </row>
+    <row r="3385">
+      <c r="A3385" t="str">
+        <v>Log Message</v>
+      </c>
+      <c r="B3385" t="str">
+        <v>رسالة السجل</v>
+      </c>
+      <c r="C3385" t="str">
+        <v>Žurnāla ziņojums</v>
+      </c>
+    </row>
+    <row r="3386">
+      <c r="A3386" t="str">
+        <v>No logs found</v>
+      </c>
+      <c r="B3386" t="str">
+        <v>لم يتم العثور على سجلات</v>
+      </c>
+      <c r="C3386" t="str">
+        <v>Nav atrasti ieraksti</v>
+      </c>
+    </row>
+    <row r="3387">
+      <c r="A3387" t="str">
+        <v>Search assessments...</v>
+      </c>
+      <c r="B3387" t="str">
+        <v>البحث في التقييمات...</v>
+      </c>
+      <c r="C3387" t="str">
+        <v>Meklēt novērtējumus...</v>
+      </c>
+    </row>
+    <row r="3388">
+      <c r="A3388" t="str">
+        <v>Select an assessment</v>
+      </c>
+      <c r="B3388" t="str">
+        <v>اختر تقييماً</v>
+      </c>
+      <c r="C3388" t="str">
+        <v>Izvēlieties novērtējumu</v>
+      </c>
+    </row>
+    <row r="3389">
+      <c r="A3389" t="str">
+        <v>Select an assessment to view logs</v>
+      </c>
+      <c r="B3389" t="str">
+        <v>اختر تقييماً لعرض السجلات</v>
+      </c>
+      <c r="C3389" t="str">
+        <v>Izvēlieties novērtējumu, lai skatītu žurnālus</v>
+      </c>
+    </row>
+    <row r="3390">
+      <c r="A3390" t="str">
+        <v>Submission Date</v>
+      </c>
+      <c r="B3390" t="str">
+        <v>تاريخ التقديم</v>
+      </c>
+      <c r="C3390" t="str">
+        <v>Iesniegšanas datums</v>
+      </c>
+    </row>
+    <row r="3391">
+      <c r="A3391" t="str">
+        <v>Vendor Submission Date</v>
+      </c>
+      <c r="B3391" t="str">
+        <v>تاريخ تقديم المورد</v>
+      </c>
+      <c r="C3391" t="str">
+        <v>Piegādātāja iesniegšanas datums</v>
+      </c>
+    </row>
+    <row r="3392">
+      <c r="A3392" t="str">
+        <v>Initiate Reassessment</v>
+      </c>
+      <c r="B3392" t="str">
+        <v>بدء إعادة التقييم</v>
+      </c>
+      <c r="C3392" t="str">
+        <v>Uzsākt atkārtotu novērtēšanu</v>
+      </c>
+    </row>
+    <row r="3393">
+      <c r="A3393" t="str">
+        <v>My Queue</v>
+      </c>
+      <c r="B3393" t="str">
+        <v>قائمتي</v>
+      </c>
+      <c r="C3393" t="str">
+        <v>Mana rinda</v>
+      </c>
+    </row>
+    <row r="3394">
+      <c r="A3394" t="str">
+        <v>Returned</v>
+      </c>
+      <c r="B3394" t="str">
+        <v>مرتجع</v>
+      </c>
+      <c r="C3394" t="str">
+        <v>Atgriezts</v>
+      </c>
+    </row>
+    <row r="3395">
+      <c r="A3395" t="str">
+        <v>Export Excel</v>
+      </c>
+      <c r="B3395" t="str">
+        <v>تصدير إلى Excel</v>
+      </c>
+      <c r="C3395" t="str">
+        <v>Eksportēt uz Excel</v>
+      </c>
+    </row>
+    <row r="3396">
+      <c r="A3396" t="str">
+        <v>API URL</v>
+      </c>
+      <c r="B3396" t="str">
+        <v>عنوان API</v>
+      </c>
+      <c r="C3396" t="str">
+        <v>API URL</v>
+      </c>
+    </row>
+    <row r="3397">
+      <c r="A3397" t="str">
+        <v>Load more</v>
+      </c>
+      <c r="B3397" t="str">
+        <v>تحميل المزيد</v>
+      </c>
+      <c r="C3397" t="str">
+        <v>Ielādēt vairāk</v>
+      </c>
+    </row>
+    <row r="3398">
+      <c r="A3398" t="str">
+        <v>Refresh</v>
+      </c>
+      <c r="B3398" t="str">
+        <v>تحديث</v>
+      </c>
+      <c r="C3398" t="str">
+        <v>Atjaunināt</v>
+      </c>
+    </row>
+    <row r="3399">
+      <c r="A3399" t="str">
+        <v>Search by Name</v>
+      </c>
+      <c r="B3399" t="str">
+        <v>البحث بالاسم</v>
+      </c>
+      <c r="C3399" t="str">
+        <v>Meklēt pēc nosaukuma</v>
+      </c>
+    </row>
+    <row r="3400">
+      <c r="A3400" t="str">
+        <v>SQ.NO</v>
+      </c>
+      <c r="B3400" t="str">
+        <v>الرقم التسلسلي</v>
+      </c>
+      <c r="C3400" t="str">
+        <v>Nr.</v>
+      </c>
+    </row>
+    <row r="3401">
+      <c r="A3401" t="str">
+        <v>System</v>
+      </c>
+      <c r="B3401" t="str">
+        <v>النظام</v>
+      </c>
+      <c r="C3401" t="str">
+        <v>Sistēma</v>
+      </c>
+    </row>
+    <row r="3402">
+      <c r="A3402" t="str">
+        <v>Confirm Logout</v>
+      </c>
+      <c r="B3402" t="str">
+        <v>تأكيد تسجيل الخروج</v>
+      </c>
+      <c r="C3402" t="str">
+        <v>Apstiprināt izrakstīšanos</v>
+      </c>
+    </row>
+    <row r="3403">
+      <c r="A3403" t="str">
+        <v>Are you sure you want to log out?</v>
+      </c>
+      <c r="B3403" t="str">
+        <v>هل أنت متأكد من أنك تريد تسجيل الخروج؟</v>
+      </c>
+      <c r="C3403" t="str">
+        <v>Vai tiešām vēlaties izrakstīties?</v>
+      </c>
+    </row>
+    <row r="3404">
+      <c r="A3404" t="str">
+        <v>TPRM Platform</v>
+      </c>
+      <c r="B3404" t="str">
+        <v>منصة TPRM</v>
+      </c>
+      <c r="C3404" t="str">
+        <v>TPRM platforma</v>
+      </c>
+    </row>
+    <row r="3405">
+      <c r="A3405" t="str">
+        <v>Vendor Onboarding</v>
+      </c>
+      <c r="B3405" t="str">
+        <v>تسجيل المورد</v>
+      </c>
+      <c r="C3405" t="str">
+        <v>Piegādātāja reģistrācija</v>
+      </c>
+    </row>
+    <row r="3406">
+      <c r="A3406" t="str">
+        <v>Discipline</v>
+      </c>
+      <c r="B3406" t="str">
+        <v>التخصص</v>
+      </c>
+      <c r="C3406" t="str">
+        <v>Disciplīna</v>
+      </c>
+    </row>
+    <row r="3407">
+      <c r="A3407" t="str">
+        <v>Manage vendor profile fields and onboarding questions</v>
+      </c>
+      <c r="B3407" t="str">
+        <v>إدارة حقول ملف المورد وأسئلة التسجيل</v>
+      </c>
+      <c r="C3407" t="str">
+        <v>Pārvaldīt piegādātāja profila laukus un reģistrācijas jautājumus</v>
+      </c>
+    </row>
+    <row r="3408">
+      <c r="A3408" t="str">
+        <v>Manage service categories for vendor classification</v>
+      </c>
+      <c r="B3408" t="str">
+        <v>إدارة فئات الخدمة لتصنيف الموردين</v>
+      </c>
+      <c r="C3408" t="str">
+        <v>Pārvaldīt pakalpojumu kategorijas piegādātāju klasifikācijai</v>
+      </c>
+    </row>
+    <row r="3409">
+      <c r="A3409" t="str">
+        <v>Manage assessment disciplines</v>
+      </c>
+      <c r="B3409" t="str">
+        <v>إدارة تخصصات التقييم</v>
+      </c>
+      <c r="C3409" t="str">
+        <v>Pārvaldīt novērtējumu disciplīnas</v>
+      </c>
+    </row>
+    <row r="3410">
+      <c r="A3410" t="str">
+        <v>Manage TPRM departments</v>
+      </c>
+      <c r="B3410" t="str">
+        <v>إدارة أقسام TPRM</v>
+      </c>
+      <c r="C3410" t="str">
+        <v>Pārvaldīt TPRM departamentus</v>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" t="str">
+        <v>Questionnaire Management</v>
+      </c>
+      <c r="B3411" t="str">
+        <v>إدارة الاستبيانات</v>
+      </c>
+      <c r="C3411" t="str">
+        <v>Anketu pārvaldība</v>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" t="str">
+        <v>Manage assessment questionnaire templates</v>
+      </c>
+      <c r="B3412" t="str">
+        <v>إدارة قوالب استبيانات التقييم</v>
+      </c>
+      <c r="C3412" t="str">
+        <v>Pārvaldīt novērtējumu anketu veidnes</v>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" t="str">
+        <v>Vendor Offboarding</v>
+      </c>
+      <c r="B3413" t="str">
+        <v>إلغاء تسجيل المورد</v>
+      </c>
+      <c r="C3413" t="str">
+        <v>Piegādātāja izslēgšana</v>
+      </c>
+    </row>
+    <row r="3414">
+      <c r="A3414" t="str">
+        <v>Manage vendor offboarding questionnaire</v>
+      </c>
+      <c r="B3414" t="str">
+        <v>إدارة استبيان إلغاء تسجيل المورد</v>
+      </c>
+      <c r="C3414" t="str">
+        <v>Pārvaldīt piegādātāja izslēgšanas anketu</v>
+      </c>
+    </row>
+    <row r="3415">
+      <c r="A3415" t="str">
+        <v>Configure scoring formula and security factors</v>
+      </c>
+      <c r="B3415" t="str">
+        <v>تكوين صيغة التسجيل وعوامل الأمان</v>
+      </c>
+      <c r="C3415" t="str">
+        <v>Konfigurēt vērtēšanas formulu un drošības faktorus</v>
+      </c>
+    </row>
+    <row r="3416">
+      <c r="A3416" t="str">
+        <v>Are you sure you want to log out? You will need to sign in again to access the application.</v>
+      </c>
+      <c r="B3416" t="str">
+        <v>هل أنت متأكد من أنك تريد تسجيل الخروج؟ ستحتاج إلى تسجيل الدخول مرة أخرى للوصول إلى التطبيق.</v>
+      </c>
+      <c r="C3416" t="str">
+        <v>Vai tiešām vēlaties izrakstīties? Jums būs jāpiesakās vēlreiz, lai piekļūtu lietojumprogrammai.</v>
+      </c>
+    </row>
+    <row r="3417">
+      <c r="A3417" t="str">
+        <v>Total Score</v>
+      </c>
+      <c r="B3417" t="str">
+        <v>إجمالي الدرجات</v>
+      </c>
+      <c r="C3417" t="str">
+        <v>Kopējais rezultāts</v>
+      </c>
+    </row>
+    <row r="3418">
+      <c r="A3418" t="str">
+        <v>Total score</v>
+      </c>
+      <c r="B3418" t="str">
+        <v>إجمالي الدرجة</v>
+      </c>
+      <c r="C3418" t="str">
+        <v>Kopējais rezultāts</v>
+      </c>
+    </row>
+    <row r="3419">
+      <c r="A3419" t="str">
+        <v>exceeds max VRR</v>
+      </c>
+      <c r="B3419" t="str">
+        <v>يتجاوز الحد الأقصى لـ VRR</v>
+      </c>
+      <c r="C3419" t="str">
+        <v>pārsniedz maksimālo VRR</v>
+      </c>
+    </row>
+    <row r="3420">
+      <c r="A3420" t="str">
+        <v>Max</v>
+      </c>
+      <c r="B3420" t="str">
+        <v>الحد الأقصى</v>
+      </c>
+      <c r="C3420" t="str">
+        <v>Maks.</v>
+      </c>
+    </row>
+    <row r="3421">
+      <c r="A3421" t="str">
+        <v>Parent Question</v>
+      </c>
+      <c r="B3421" t="str">
+        <v>السؤال الرئيسي</v>
+      </c>
+      <c r="C3421" t="str">
+        <v>Vecāka jautājums</v>
+      </c>
+    </row>
+    <row r="3422">
+      <c r="A3422" t="str">
+        <v>Select parent question</v>
+      </c>
+      <c r="B3422" t="str">
+        <v>اختر السؤال الرئيسي</v>
+      </c>
+      <c r="C3422" t="str">
+        <v>Izvēlēties vecāka jautājumu</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3222"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3422"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3323"/>
+  <dimension ref="A1:C3888"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -36957,9 +36957,6224 @@
         <v>Nav nodaļas</v>
       </c>
     </row>
+    <row r="3324">
+      <c r="A3324" t="str">
+        <v>1 - Insignificant</v>
+      </c>
+      <c r="B3324" t="str">
+        <v>1 - غير مهم</v>
+      </c>
+      <c r="C3324" t="str">
+        <v>1 - Nenozīmīgs</v>
+      </c>
+    </row>
+    <row r="3325">
+      <c r="A3325" t="str">
+        <v>1 - Rare</v>
+      </c>
+      <c r="B3325" t="str">
+        <v>1 - نادر</v>
+      </c>
+      <c r="C3325" t="str">
+        <v>1 - Reti</v>
+      </c>
+    </row>
+    <row r="3326">
+      <c r="A3326" t="str">
+        <v>2 - Minor</v>
+      </c>
+      <c r="B3326" t="str">
+        <v>2 - طفيف</v>
+      </c>
+      <c r="C3326" t="str">
+        <v>2 - Neliels</v>
+      </c>
+    </row>
+    <row r="3327">
+      <c r="A3327" t="str">
+        <v>2 - Unlikely</v>
+      </c>
+      <c r="B3327" t="str">
+        <v>2 - غير محتمل</v>
+      </c>
+      <c r="C3327" t="str">
+        <v>2 - Maz ticams</v>
+      </c>
+    </row>
+    <row r="3328">
+      <c r="A3328" t="str">
+        <v>3 - Moderate</v>
+      </c>
+      <c r="B3328" t="str">
+        <v>3 - متوسط</v>
+      </c>
+      <c r="C3328" t="str">
+        <v>3 - Mērens</v>
+      </c>
+    </row>
+    <row r="3329">
+      <c r="A3329" t="str">
+        <v>3 - Possible</v>
+      </c>
+      <c r="B3329" t="str">
+        <v>3 - ممكن</v>
+      </c>
+      <c r="C3329" t="str">
+        <v>3 - Iespējams</v>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" t="str">
+        <v>4 - Likely</v>
+      </c>
+      <c r="B3330" t="str">
+        <v>4 - محتمل</v>
+      </c>
+      <c r="C3330" t="str">
+        <v>4 - Ticams</v>
+      </c>
+    </row>
+    <row r="3331">
+      <c r="A3331" t="str">
+        <v>4 - Major</v>
+      </c>
+      <c r="B3331" t="str">
+        <v>4 - كبير</v>
+      </c>
+      <c r="C3331" t="str">
+        <v>4 - Būtisks</v>
+      </c>
+    </row>
+    <row r="3332">
+      <c r="A3332" t="str">
+        <v>5 - Almost Certain</v>
+      </c>
+      <c r="B3332" t="str">
+        <v>5 - شبه مؤكد</v>
+      </c>
+      <c r="C3332" t="str">
+        <v>5 - Gandrīz noteikts</v>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" t="str">
+        <v>5 - Catastrophic</v>
+      </c>
+      <c r="B3333" t="str">
+        <v>5 - كارثي</v>
+      </c>
+      <c r="C3333" t="str">
+        <v>5 - Katastrofāls</v>
+      </c>
+    </row>
+    <row r="3334">
+      <c r="A3334" t="str">
+        <v>AI Evaluated Controls</v>
+      </c>
+      <c r="B3334" t="str">
+        <v>الضوابط المقيّمة بالذكاء الاصطناعي</v>
+      </c>
+      <c r="C3334" t="str">
+        <v>AI novērtētās kontroles</v>
+      </c>
+    </row>
+    <row r="3335">
+      <c r="A3335" t="str">
+        <v>AI Evaluated Threat</v>
+      </c>
+      <c r="B3335" t="str">
+        <v>التهديد المقيّم بالذكاء الاصطناعي</v>
+      </c>
+      <c r="C3335" t="str">
+        <v>AI novērtētais drauds</v>
+      </c>
+    </row>
+    <row r="3336">
+      <c r="A3336" t="str">
+        <v>AI Evaluated Vulnerabilities</v>
+      </c>
+      <c r="B3336" t="str">
+        <v>الثغرات المقيّمة بالذكاء الاصطناعي</v>
+      </c>
+      <c r="C3336" t="str">
+        <v>AI novērtētās ievainojamības</v>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" t="str">
+        <v>AI Review Details</v>
+      </c>
+      <c r="B3337" t="str">
+        <v>تفاصيل مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C3337" t="str">
+        <v>AI pārskata detaļas</v>
+      </c>
+    </row>
+    <row r="3338">
+      <c r="A3338" t="str">
+        <v>AI Review completed successfully</v>
+      </c>
+      <c r="B3338" t="str">
+        <v>تمت مراجعة الذكاء الاصطناعي بنجاح</v>
+      </c>
+      <c r="C3338" t="str">
+        <v>AI pārskats veiksmīgi pabeigts</v>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" t="str">
+        <v>AI Review in progress...</v>
+      </c>
+      <c r="B3339" t="str">
+        <v>مراجعة الذكاء الاصطناعي قيد التنفيذ...</v>
+      </c>
+      <c r="C3339" t="str">
+        <v>AI pārskats norit...</v>
+      </c>
+    </row>
+    <row r="3340">
+      <c r="A3340" t="str">
+        <v>AI did not identify any risks for this process.</v>
+      </c>
+      <c r="B3340" t="str">
+        <v>لم يحدد الذكاء الاصطناعي أي مخاطر لهذه العملية.</v>
+      </c>
+      <c r="C3340" t="str">
+        <v>AI neidentificēja riskus šim procesam.</v>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" t="str">
+        <v>Clear AI Results</v>
+      </c>
+      <c r="B3341" t="str">
+        <v>مسح نتائج الذكاء الاصطناعي</v>
+      </c>
+      <c r="C3341" t="str">
+        <v>Notīrīt AI rezultātus</v>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" t="str">
+        <v>Issue Identified by AI</v>
+      </c>
+      <c r="B3342" t="str">
+        <v>مشكلة حددها الذكاء الاصطناعي</v>
+      </c>
+      <c r="C3342" t="str">
+        <v>AI identificētā problēma</v>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" t="str">
+        <v>Retry AI Review</v>
+      </c>
+      <c r="B3343" t="str">
+        <v>إعادة مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C3343" t="str">
+        <v>Atkārtot AI pārskatu</v>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" t="str">
+        <v>Starting AI Review for</v>
+      </c>
+      <c r="B3344" t="str">
+        <v>بدء مراجعة الذكاء الاصطناعي لـ</v>
+      </c>
+      <c r="C3344" t="str">
+        <v>Sāk AI pārskatu priekš</v>
+      </c>
+    </row>
+    <row r="3345">
+      <c r="A3345" t="str">
+        <v>Semantic Matching in Progress</v>
+      </c>
+      <c r="B3345" t="str">
+        <v>المطابقة الدلالية قيد التنفيذ</v>
+      </c>
+      <c r="C3345" t="str">
+        <v>Semantiskā atbilstības noteikšana norit</v>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" t="str">
+        <v>Action completed successfully!</v>
+      </c>
+      <c r="B3346" t="str">
+        <v>تم إكمال الإجراء بنجاح!</v>
+      </c>
+      <c r="C3346" t="str">
+        <v>Darbība veiksmīgi pabeigta!</v>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" t="str">
+        <v>Control created successfully</v>
+      </c>
+      <c r="B3347" t="str">
+        <v>تم إنشاء الضابط بنجاح</v>
+      </c>
+      <c r="C3347" t="str">
+        <v>Kontrole veiksmīgi izveidota</v>
+      </c>
+    </row>
+    <row r="3348">
+      <c r="A3348" t="str">
+        <v>Framework deleted successfully</v>
+      </c>
+      <c r="B3348" t="str">
+        <v>تم حذف الإطار بنجاح</v>
+      </c>
+      <c r="C3348" t="str">
+        <v>Ietvars veiksmīgi dzēsts</v>
+      </c>
+    </row>
+    <row r="3349">
+      <c r="A3349" t="str">
+        <v>Framework updated successfully</v>
+      </c>
+      <c r="B3349" t="str">
+        <v>تم تحديث الإطار بنجاح</v>
+      </c>
+      <c r="C3349" t="str">
+        <v>Ietvars veiksmīgi atjaunināts</v>
+      </c>
+    </row>
+    <row r="3350">
+      <c r="A3350" t="str">
+        <v>Item added successfully</v>
+      </c>
+      <c r="B3350" t="str">
+        <v>تمت إضافة العنصر بنجاح</v>
+      </c>
+      <c r="C3350" t="str">
+        <v>Vienība veiksmīgi pievienota</v>
+      </c>
+    </row>
+    <row r="3351">
+      <c r="A3351" t="str">
+        <v>Item updated successfully</v>
+      </c>
+      <c r="B3351" t="str">
+        <v>تم تحديث العنصر بنجاح</v>
+      </c>
+      <c r="C3351" t="str">
+        <v>Vienība veiksmīgi atjaunināta</v>
+      </c>
+    </row>
+    <row r="3352">
+      <c r="A3352" t="str">
+        <v>KPI configuration has been saved</v>
+      </c>
+      <c r="B3352" t="str">
+        <v>تم حفظ إعدادات مؤشرات الأداء</v>
+      </c>
+      <c r="C3352" t="str">
+        <v>KPI konfigurācija ir saglabāta</v>
+      </c>
+    </row>
+    <row r="3353">
+      <c r="A3353" t="str">
+        <v>KPI configuration saved successfully</v>
+      </c>
+      <c r="B3353" t="str">
+        <v>تم حفظ إعدادات مؤشرات الأداء بنجاح</v>
+      </c>
+      <c r="C3353" t="str">
+        <v>KPI konfigurācija veiksmīgi saglabāta</v>
+      </c>
+    </row>
+    <row r="3354">
+      <c r="A3354" t="str">
+        <v>KPI record has been deleted</v>
+      </c>
+      <c r="B3354" t="str">
+        <v>تم حذف سجل مؤشر الأداء</v>
+      </c>
+      <c r="C3354" t="str">
+        <v>KPI ieraksts ir dzēsts</v>
+      </c>
+    </row>
+    <row r="3355">
+      <c r="A3355" t="str">
+        <v>Organisation profile created successfully</v>
+      </c>
+      <c r="B3355" t="str">
+        <v>تم إنشاء ملف المنظمة بنجاح</v>
+      </c>
+      <c r="C3355" t="str">
+        <v>Organizācijas profils veiksmīgi izveidots</v>
+      </c>
+    </row>
+    <row r="3356">
+      <c r="A3356" t="str">
+        <v>Organisation profile updated successfully</v>
+      </c>
+      <c r="B3356" t="str">
+        <v>تم تحديث ملف المنظمة بنجاح</v>
+      </c>
+      <c r="C3356" t="str">
+        <v>Organizācijas profils veiksmīgi atjaunināts</v>
+      </c>
+    </row>
+    <row r="3357">
+      <c r="A3357" t="str">
+        <v>Risk Approved Successfully !</v>
+      </c>
+      <c r="B3357" t="str">
+        <v>تمت الموافقة على المخاطرة بنجاح!</v>
+      </c>
+      <c r="C3357" t="str">
+        <v>Risks veiksmīgi apstiprināts!</v>
+      </c>
+    </row>
+    <row r="3358">
+      <c r="A3358" t="str">
+        <v>Risk Approved Successfully!</v>
+      </c>
+      <c r="B3358" t="str">
+        <v>تمت الموافقة على المخاطرة بنجاح!</v>
+      </c>
+      <c r="C3358" t="str">
+        <v>Risks veiksmīgi apstiprināts!</v>
+      </c>
+    </row>
+    <row r="3359">
+      <c r="A3359" t="str">
+        <v>Risk Library Updated</v>
+      </c>
+      <c r="B3359" t="str">
+        <v>تم تحديث مكتبة المخاطر</v>
+      </c>
+      <c r="C3359" t="str">
+        <v>Risku bibliotēka atjaunināta</v>
+      </c>
+    </row>
+    <row r="3360">
+      <c r="A3360" t="str">
+        <v>Risk Removed</v>
+      </c>
+      <c r="B3360" t="str">
+        <v>تمت إزالة المخاطرة</v>
+      </c>
+      <c r="C3360" t="str">
+        <v>Risks noņemts</v>
+      </c>
+    </row>
+    <row r="3361">
+      <c r="A3361" t="str">
+        <v>Risk Sent Back Successfully!</v>
+      </c>
+      <c r="B3361" t="str">
+        <v>تم إرجاع المخاطرة بنجاح!</v>
+      </c>
+      <c r="C3361" t="str">
+        <v>Risks veiksmīgi nosūtīts atpakaļ!</v>
+      </c>
+    </row>
+    <row r="3362">
+      <c r="A3362" t="str">
+        <v>Risk Submit for Approval Successfully !</v>
+      </c>
+      <c r="B3362" t="str">
+        <v>تم تقديم المخاطرة للموافقة بنجاح!</v>
+      </c>
+      <c r="C3362" t="str">
+        <v>Risks veiksmīgi iesniegts apstiprināšanai!</v>
+      </c>
+    </row>
+    <row r="3363">
+      <c r="A3363" t="str">
+        <v>Risk Submitted for Approval Successfully!</v>
+      </c>
+      <c r="B3363" t="str">
+        <v>تم تقديم المخاطرة للموافقة بنجاح!</v>
+      </c>
+      <c r="C3363" t="str">
+        <v>Risks veiksmīgi iesniegts apstiprināšanai!</v>
+      </c>
+    </row>
+    <row r="3364">
+      <c r="A3364" t="str">
+        <v>SOA changes saved successfully.</v>
+      </c>
+      <c r="B3364" t="str">
+        <v>تم حفظ تغييرات بيان التطبيق بنجاح.</v>
+      </c>
+      <c r="C3364" t="str">
+        <v>SOA izmaiņas veiksmīgi saglabātas.</v>
+      </c>
+    </row>
+    <row r="3365">
+      <c r="A3365" t="str">
+        <v>Exception approved successfully</v>
+      </c>
+      <c r="B3365" t="str">
+        <v>تمت الموافقة على الاستثناء بنجاح</v>
+      </c>
+      <c r="C3365" t="str">
+        <v>Izņēmums veiksmīgi apstiprināts</v>
+      </c>
+    </row>
+    <row r="3366">
+      <c r="A3366" t="str">
+        <v>Exception resubmitted for approval</v>
+      </c>
+      <c r="B3366" t="str">
+        <v>تمت إعادة تقديم الاستثناء للموافقة</v>
+      </c>
+      <c r="C3366" t="str">
+        <v>Izņēmums atkārtoti iesniegts apstiprināšanai</v>
+      </c>
+    </row>
+    <row r="3367">
+      <c r="A3367" t="str">
+        <v>Exception sent back successfully</v>
+      </c>
+      <c r="B3367" t="str">
+        <v>تم إرجاع الاستثناء بنجاح</v>
+      </c>
+      <c r="C3367" t="str">
+        <v>Izņēmums veiksmīgi nosūtīts atpakaļ</v>
+      </c>
+    </row>
+    <row r="3368">
+      <c r="A3368" t="str">
+        <v>User created successfully</v>
+      </c>
+      <c r="B3368" t="str">
+        <v>تم إنشاء المستخدم بنجاح</v>
+      </c>
+      <c r="C3368" t="str">
+        <v>Lietotājs veiksmīgi izveidots</v>
+      </c>
+    </row>
+    <row r="3369">
+      <c r="A3369" t="str">
+        <v>User deleted successfully</v>
+      </c>
+      <c r="B3369" t="str">
+        <v>تم حذف المستخدم بنجاح</v>
+      </c>
+      <c r="C3369" t="str">
+        <v>Lietotājs veiksmīgi dzēsts</v>
+      </c>
+    </row>
+    <row r="3370">
+      <c r="A3370" t="str">
+        <v>User updated successfully</v>
+      </c>
+      <c r="B3370" t="str">
+        <v>تم تحديث المستخدم بنجاح</v>
+      </c>
+      <c r="C3370" t="str">
+        <v>Lietotājs veiksmīgi atjaunināts</v>
+      </c>
+    </row>
+    <row r="3371">
+      <c r="A3371" t="str">
+        <v>Add BIA Category</v>
+      </c>
+      <c r="B3371" t="str">
+        <v>إضافة فئة تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3371" t="str">
+        <v>Pievienot BIA kategoriju</v>
+      </c>
+    </row>
+    <row r="3372">
+      <c r="A3372" t="str">
+        <v>Add BIA Rating</v>
+      </c>
+      <c r="B3372" t="str">
+        <v>إضافة تقييم تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3372" t="str">
+        <v>Pievienot BIA vērtējumu</v>
+      </c>
+    </row>
+    <row r="3373">
+      <c r="A3373" t="str">
+        <v>BIA Categories</v>
+      </c>
+      <c r="B3373" t="str">
+        <v>فئات تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3373" t="str">
+        <v>BIA kategorijas</v>
+      </c>
+    </row>
+    <row r="3374">
+      <c r="A3374" t="str">
+        <v>BIA Comments</v>
+      </c>
+      <c r="B3374" t="str">
+        <v>تعليقات تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3374" t="str">
+        <v>BIA komentāri</v>
+      </c>
+    </row>
+    <row r="3375">
+      <c r="A3375" t="str">
+        <v>BIA approved</v>
+      </c>
+      <c r="B3375" t="str">
+        <v>تمت الموافقة على تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3375" t="str">
+        <v>BIA apstiprināts</v>
+      </c>
+    </row>
+    <row r="3376">
+      <c r="A3376" t="str">
+        <v>BIA data has been saved</v>
+      </c>
+      <c r="B3376" t="str">
+        <v>تم حفظ بيانات تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3376" t="str">
+        <v>BIA dati ir saglabāti</v>
+      </c>
+    </row>
+    <row r="3377">
+      <c r="A3377" t="str">
+        <v>BIA data has been saved successfully</v>
+      </c>
+      <c r="B3377" t="str">
+        <v>تم حفظ بيانات تحليل تأثير الأعمال بنجاح</v>
+      </c>
+      <c r="C3377" t="str">
+        <v>BIA dati veiksmīgi saglabāti</v>
+      </c>
+    </row>
+    <row r="3378">
+      <c r="A3378" t="str">
+        <v>BIA has been approved</v>
+      </c>
+      <c r="B3378" t="str">
+        <v>تمت الموافقة على تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3378" t="str">
+        <v>BIA ir apstiprināts</v>
+      </c>
+    </row>
+    <row r="3379">
+      <c r="A3379" t="str">
+        <v>BIA has been sent back for revision</v>
+      </c>
+      <c r="B3379" t="str">
+        <v>تم إرجاع تحليل تأثير الأعمال للمراجعة</v>
+      </c>
+      <c r="C3379" t="str">
+        <v>BIA nosūtīts atpakaļ pārskatīšanai</v>
+      </c>
+    </row>
+    <row r="3380">
+      <c r="A3380" t="str">
+        <v>BIA has been submitted for approval</v>
+      </c>
+      <c r="B3380" t="str">
+        <v>تم تقديم تحليل تأثير الأعمال للموافقة</v>
+      </c>
+      <c r="C3380" t="str">
+        <v>BIA iesniegts apstiprināšanai</v>
+      </c>
+    </row>
+    <row r="3381">
+      <c r="A3381" t="str">
+        <v>BIA submitted for approval</v>
+      </c>
+      <c r="B3381" t="str">
+        <v>تم تقديم تحليل تأثير الأعمال للموافقة</v>
+      </c>
+      <c r="C3381" t="str">
+        <v>BIA iesniegts apstiprināšanai</v>
+      </c>
+    </row>
+    <row r="3382">
+      <c r="A3382" t="str">
+        <v>Edit BIA Category</v>
+      </c>
+      <c r="B3382" t="str">
+        <v>تعديل فئة تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3382" t="str">
+        <v>Rediģēt BIA kategoriju</v>
+      </c>
+    </row>
+    <row r="3383">
+      <c r="A3383" t="str">
+        <v>Edit BIA Rating</v>
+      </c>
+      <c r="B3383" t="str">
+        <v>تعديل تقييم تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3383" t="str">
+        <v>Rediģēt BIA vērtējumu</v>
+      </c>
+    </row>
+    <row r="3384">
+      <c r="A3384" t="str">
+        <v>Add a new impact category for Business Impact Analysis</v>
+      </c>
+      <c r="B3384" t="str">
+        <v>إضافة فئة تأثير جديدة لتحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3384" t="str">
+        <v>Pievienot jaunu ietekmes kategoriju biznesa ietekmes analīzei</v>
+      </c>
+    </row>
+    <row r="3385">
+      <c r="A3385" t="str">
+        <v>Configure how the BIA impact rating is calculated from individual category scores</v>
+      </c>
+      <c r="B3385" t="str">
+        <v>تكوين كيفية حساب تقييم تأثير تحليل الأعمال من درجات الفئات الفردية</v>
+      </c>
+      <c r="C3385" t="str">
+        <v>Konfigurēt, kā BIA ietekmes vērtējums tiek aprēķināts no kategoriju punktiem</v>
+      </c>
+    </row>
+    <row r="3386">
+      <c r="A3386" t="str">
+        <v>Define a new rating level for BIA assessments</v>
+      </c>
+      <c r="B3386" t="str">
+        <v>تحديد مستوى تقييم جديد لتقييمات تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3386" t="str">
+        <v>Definēt jaunu vērtējuma līmeni BIA novērtējumiem</v>
+      </c>
+    </row>
+    <row r="3387">
+      <c r="A3387" t="str">
+        <v>Enable KPI Measurement Required when adding a process to see it here</v>
+      </c>
+      <c r="B3387" t="str">
+        <v>فعّل قياس مؤشرات الأداء المطلوبة عند إضافة عملية لرؤيتها هنا</v>
+      </c>
+      <c r="C3387" t="str">
+        <v>Iespējojiet KPI mērījumu, pievienojot procesu, lai to redzētu šeit</v>
+      </c>
+    </row>
+    <row r="3388">
+      <c r="A3388" t="str">
+        <v>Add Organisation Profile</v>
+      </c>
+      <c r="B3388" t="str">
+        <v>إضافة ملف المنظمة</v>
+      </c>
+      <c r="C3388" t="str">
+        <v>Pievienot organizācijas profilu</v>
+      </c>
+    </row>
+    <row r="3389">
+      <c r="A3389" t="str">
+        <v>Edit Organisation Profile</v>
+      </c>
+      <c r="B3389" t="str">
+        <v>تعديل ملف المنظمة</v>
+      </c>
+      <c r="C3389" t="str">
+        <v>Rediģēt organizācijas profilu</v>
+      </c>
+    </row>
+    <row r="3390">
+      <c r="A3390" t="str">
+        <v>Branch Size</v>
+      </c>
+      <c r="B3390" t="str">
+        <v>حجم الفرع</v>
+      </c>
+      <c r="C3390" t="str">
+        <v>Filiāles lielums</v>
+      </c>
+    </row>
+    <row r="3391">
+      <c r="A3391" t="str">
+        <v>Budget Allocation Vs Used</v>
+      </c>
+      <c r="B3391" t="str">
+        <v>تخصيص الميزانية مقابل المستخدم</v>
+      </c>
+      <c r="C3391" t="str">
+        <v>Budžeta piešķīrums pret izlietoto</v>
+      </c>
+    </row>
+    <row r="3392">
+      <c r="A3392" t="str">
+        <v>Employee Size</v>
+      </c>
+      <c r="B3392" t="str">
+        <v>حجم الموظفين</v>
+      </c>
+      <c r="C3392" t="str">
+        <v>Darbinieku skaits</v>
+      </c>
+    </row>
+    <row r="3393">
+      <c r="A3393" t="str">
+        <v>Full Legal Entity Name</v>
+      </c>
+      <c r="B3393" t="str">
+        <v>الاسم القانوني الكامل للكيان</v>
+      </c>
+      <c r="C3393" t="str">
+        <v>Pilns juridiskās personas nosaukums</v>
+      </c>
+    </row>
+    <row r="3394">
+      <c r="A3394" t="str">
+        <v>Define your organisation's regulatory context and business details</v>
+      </c>
+      <c r="B3394" t="str">
+        <v>حدد السياق التنظيمي وتفاصيل الأعمال لمنظمتك</v>
+      </c>
+      <c r="C3394" t="str">
+        <v>Definējiet savas organizācijas regulatīvo kontekstu un biznesa detaļas</v>
+      </c>
+    </row>
+    <row r="3395">
+      <c r="A3395" t="str">
+        <v>Update your organisation's regulatory context and business details</v>
+      </c>
+      <c r="B3395" t="str">
+        <v>تحديث السياق التنظيمي وتفاصيل الأعمال لمنظمتك</v>
+      </c>
+      <c r="C3395" t="str">
+        <v>Atjauniniet savas organizācijas regulatīvo kontekstu un biznesa detaļas</v>
+      </c>
+    </row>
+    <row r="3396">
+      <c r="A3396" t="str">
+        <v>Enter admin contact email</v>
+      </c>
+      <c r="B3396" t="str">
+        <v>أدخل البريد الإلكتروني لجهة الاتصال الإدارية</v>
+      </c>
+      <c r="C3396" t="str">
+        <v>Ievadiet administratora kontakta e-pastu</v>
+      </c>
+    </row>
+    <row r="3397">
+      <c r="A3397" t="str">
+        <v>Enter full legal entity name</v>
+      </c>
+      <c r="B3397" t="str">
+        <v>أدخل الاسم القانوني الكامل للكيان</v>
+      </c>
+      <c r="C3397" t="str">
+        <v>Ievadiet pilnu juridiskās personas nosaukumu</v>
+      </c>
+    </row>
+    <row r="3398">
+      <c r="A3398" t="str">
+        <v>Enter headquarter address</v>
+      </c>
+      <c r="B3398" t="str">
+        <v>أدخل عنوان المقر الرئيسي</v>
+      </c>
+      <c r="C3398" t="str">
+        <v>Ievadiet galvenā biroja adresi</v>
+      </c>
+    </row>
+    <row r="3399">
+      <c r="A3399" t="str">
+        <v>Enter registration number</v>
+      </c>
+      <c r="B3399" t="str">
+        <v>أدخل رقم التسجيل</v>
+      </c>
+      <c r="C3399" t="str">
+        <v>Ievadiet reģistrācijas numuru</v>
+      </c>
+    </row>
+    <row r="3400">
+      <c r="A3400" t="str">
+        <v>Save Profile</v>
+      </c>
+      <c r="B3400" t="str">
+        <v>حفظ الملف الشخصي</v>
+      </c>
+      <c r="C3400" t="str">
+        <v>Saglabāt profilu</v>
+      </c>
+    </row>
+    <row r="3401">
+      <c r="A3401" t="str">
+        <v>Update Profile</v>
+      </c>
+      <c r="B3401" t="str">
+        <v>تحديث الملف الشخصي</v>
+      </c>
+      <c r="C3401" t="str">
+        <v>Atjaunināt profilu</v>
+      </c>
+    </row>
+    <row r="3402">
+      <c r="A3402" t="str">
+        <v>Select business model</v>
+      </c>
+      <c r="B3402" t="str">
+        <v>اختر نموذج الأعمال</v>
+      </c>
+      <c r="C3402" t="str">
+        <v>Atlasīt biznesa modeli</v>
+      </c>
+    </row>
+    <row r="3403">
+      <c r="A3403" t="str">
+        <v>Select countries</v>
+      </c>
+      <c r="B3403" t="str">
+        <v>اختر الدول</v>
+      </c>
+      <c r="C3403" t="str">
+        <v>Atlasīt valstis</v>
+      </c>
+    </row>
+    <row r="3404">
+      <c r="A3404" t="str">
+        <v>Select country</v>
+      </c>
+      <c r="B3404" t="str">
+        <v>اختر الدولة</v>
+      </c>
+      <c r="C3404" t="str">
+        <v>Atlasīt valsti</v>
+      </c>
+    </row>
+    <row r="3405">
+      <c r="A3405" t="str">
+        <v>Select entity</v>
+      </c>
+      <c r="B3405" t="str">
+        <v>اختر الكيان</v>
+      </c>
+      <c r="C3405" t="str">
+        <v>Atlasīt entītiju</v>
+      </c>
+    </row>
+    <row r="3406">
+      <c r="A3406" t="str">
+        <v>Select industries</v>
+      </c>
+      <c r="B3406" t="str">
+        <v>اختر الصناعات</v>
+      </c>
+      <c r="C3406" t="str">
+        <v>Atlasīt nozares</v>
+      </c>
+    </row>
+    <row r="3407">
+      <c r="A3407" t="str">
+        <v>Select organisation type</v>
+      </c>
+      <c r="B3407" t="str">
+        <v>اختر نوع المنظمة</v>
+      </c>
+      <c r="C3407" t="str">
+        <v>Atlasīt organizācijas tipu</v>
+      </c>
+    </row>
+    <row r="3408">
+      <c r="A3408" t="str">
+        <v>Select regulations related to this issue (optional)</v>
+      </c>
+      <c r="B3408" t="str">
+        <v>اختر اللوائح المتعلقة بهذه المشكلة (اختياري)</v>
+      </c>
+      <c r="C3408" t="str">
+        <v>Atlasīt ar šo problēmu saistītos noteikumus (neobligāti)</v>
+      </c>
+    </row>
+    <row r="3409">
+      <c r="A3409" t="str">
+        <v>Select scope</v>
+      </c>
+      <c r="B3409" t="str">
+        <v>اختر النطاق</v>
+      </c>
+      <c r="C3409" t="str">
+        <v>Atlasīt darbības jomu</v>
+      </c>
+    </row>
+    <row r="3410">
+      <c r="A3410" t="str">
+        <v>Select technologies</v>
+      </c>
+      <c r="B3410" t="str">
+        <v>اختر التقنيات</v>
+      </c>
+      <c r="C3410" t="str">
+        <v>Atlasīt tehnoloģijas</v>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" t="str">
+        <v>Select time zone</v>
+      </c>
+      <c r="B3411" t="str">
+        <v>اختر المنطقة الزمنية</v>
+      </c>
+      <c r="C3411" t="str">
+        <v>Atlasīt laika joslu</v>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" t="str">
+        <v>Specify other industry</v>
+      </c>
+      <c r="B3412" t="str">
+        <v>حدد صناعة أخرى</v>
+      </c>
+      <c r="C3412" t="str">
+        <v>Norādiet citu nozari</v>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" t="str">
+        <v>Timezone</v>
+      </c>
+      <c r="B3413" t="str">
+        <v>المنطقة الزمنية</v>
+      </c>
+      <c r="C3413" t="str">
+        <v>Laika josla</v>
+      </c>
+    </row>
+    <row r="3414">
+      <c r="A3414" t="str">
+        <v>Basic process information</v>
+      </c>
+      <c r="B3414" t="str">
+        <v>معلومات العملية الأساسية</v>
+      </c>
+      <c r="C3414" t="str">
+        <v>Pamatinformācija par procesu</v>
+      </c>
+    </row>
+    <row r="3415">
+      <c r="A3415" t="str">
+        <v>Complete the form to create a new process</v>
+      </c>
+      <c r="B3415" t="str">
+        <v>أكمل النموذج لإنشاء عملية جديدة</v>
+      </c>
+      <c r="C3415" t="str">
+        <v>Aizpildiet formu, lai izveidotu jaunu procesu</v>
+      </c>
+    </row>
+    <row r="3416">
+      <c r="A3416" t="str">
+        <v>Process Documents</v>
+      </c>
+      <c r="B3416" t="str">
+        <v>مستندات العملية</v>
+      </c>
+      <c r="C3416" t="str">
+        <v>Procesa dokumenti</v>
+      </c>
+    </row>
+    <row r="3417">
+      <c r="A3417" t="str">
+        <v>Process Flow</v>
+      </c>
+      <c r="B3417" t="str">
+        <v>سير العملية</v>
+      </c>
+      <c r="C3417" t="str">
+        <v>Procesa plūsma</v>
+      </c>
+    </row>
+    <row r="3418">
+      <c r="A3418" t="str">
+        <v>Process RACI</v>
+      </c>
+      <c r="B3418" t="str">
+        <v>مصفوفة راسي للعملية</v>
+      </c>
+      <c r="C3418" t="str">
+        <v>Procesa RACI</v>
+      </c>
+    </row>
+    <row r="3419">
+      <c r="A3419" t="str">
+        <v>Process characteristics</v>
+      </c>
+      <c r="B3419" t="str">
+        <v>خصائص العملية</v>
+      </c>
+      <c r="C3419" t="str">
+        <v>Procesa raksturlielumi</v>
+      </c>
+    </row>
+    <row r="3420">
+      <c r="A3420" t="str">
+        <v>Add files to attach to this process. Files will be uploaded when you save.</v>
+      </c>
+      <c r="B3420" t="str">
+        <v>أضف ملفات لإرفاقها بهذه العملية. سيتم رفع الملفات عند الحفظ.</v>
+      </c>
+      <c r="C3420" t="str">
+        <v>Pievienojiet failus šim procesam. Faili tiks augšupielādēti saglabājot.</v>
+      </c>
+    </row>
+    <row r="3421">
+      <c r="A3421" t="str">
+        <v>Define the RACI matrix for this process - who is Responsible, Accountable, Consulted, and Informed.</v>
+      </c>
+      <c r="B3421" t="str">
+        <v>حدد مصفوفة راسي لهذه العملية - من هو المسؤول والمساءل والمستشار والمطلع.</v>
+      </c>
+      <c r="C3421" t="str">
+        <v>Definējiet RACI matricu šim procesam - kas ir Atbildīgais, Pārskatāmais, Konsultētais un Informētais.</v>
+      </c>
+    </row>
+    <row r="3422">
+      <c r="A3422" t="str">
+        <v>Person kept up-to-date on progress</v>
+      </c>
+      <c r="B3422" t="str">
+        <v>الشخص الذي يتم إطلاعه على التقدم</v>
+      </c>
+      <c r="C3422" t="str">
+        <v>Persona, kas tiek informēta par progresu</v>
+      </c>
+    </row>
+    <row r="3423">
+      <c r="A3423" t="str">
+        <v>Person ultimately answerable</v>
+      </c>
+      <c r="B3423" t="str">
+        <v>الشخص المسؤول النهائي</v>
+      </c>
+      <c r="C3423" t="str">
+        <v>Persona, kas ir galīgi atbildīga</v>
+      </c>
+    </row>
+    <row r="3424">
+      <c r="A3424" t="str">
+        <v>Person who does the work</v>
+      </c>
+      <c r="B3424" t="str">
+        <v>الشخص الذي يقوم بالعمل</v>
+      </c>
+      <c r="C3424" t="str">
+        <v>Persona, kas veic darbu</v>
+      </c>
+    </row>
+    <row r="3425">
+      <c r="A3425" t="str">
+        <v>Person whose input is sought</v>
+      </c>
+      <c r="B3425" t="str">
+        <v>الشخص الذي يُطلب رأيه</v>
+      </c>
+      <c r="C3425" t="str">
+        <v>Persona, kuras ieguldījums tiek meklēts</v>
+      </c>
+    </row>
+    <row r="3426">
+      <c r="A3426" t="str">
+        <v>Roles and responsibilities</v>
+      </c>
+      <c r="B3426" t="str">
+        <v>الأدوار والمسؤوليات</v>
+      </c>
+      <c r="C3426" t="str">
+        <v>Lomas un pienākumi</v>
+      </c>
+    </row>
+    <row r="3427">
+      <c r="A3427" t="str">
+        <v>Upload employee onboarding documents for this process. Multiple files can be attached.</v>
+      </c>
+      <c r="B3427" t="str">
+        <v>ارفع مستندات تأهيل الموظفين لهذه العملية. يمكن إرفاق ملفات متعددة.</v>
+      </c>
+      <c r="C3427" t="str">
+        <v>Augšupielādējiet darbinieku ievadīšanas dokumentus šim procesam. Var pievienot vairākus failus.</v>
+      </c>
+    </row>
+    <row r="3428">
+      <c r="A3428" t="str">
+        <v>Onboarding Files</v>
+      </c>
+      <c r="B3428" t="str">
+        <v>ملفات التأهيل</v>
+      </c>
+      <c r="C3428" t="str">
+        <v>Ievadīšanas faili</v>
+      </c>
+    </row>
+    <row r="3429">
+      <c r="A3429" t="str">
+        <v>Onboarding Files to Upload</v>
+      </c>
+      <c r="B3429" t="str">
+        <v>ملفات التأهيل للرفع</v>
+      </c>
+      <c r="C3429" t="str">
+        <v>Augšupielādējamie ievadīšanas faili</v>
+      </c>
+    </row>
+    <row r="3430">
+      <c r="A3430" t="str">
+        <v>Add RPO Label</v>
+      </c>
+      <c r="B3430" t="str">
+        <v>إضافة تسمية نقطة الاسترداد</v>
+      </c>
+      <c r="C3430" t="str">
+        <v>Pievienot RPO apzīmējumu</v>
+      </c>
+    </row>
+    <row r="3431">
+      <c r="A3431" t="str">
+        <v>Add RTO Label</v>
+      </c>
+      <c r="B3431" t="str">
+        <v>إضافة تسمية وقت الاسترداد</v>
+      </c>
+      <c r="C3431" t="str">
+        <v>Pievienot RTO apzīmējumu</v>
+      </c>
+    </row>
+    <row r="3432">
+      <c r="A3432" t="str">
+        <v>RPO</v>
+      </c>
+      <c r="B3432" t="str">
+        <v>نقطة الاسترداد</v>
+      </c>
+      <c r="C3432" t="str">
+        <v>RPO</v>
+      </c>
+    </row>
+    <row r="3433">
+      <c r="A3433" t="str">
+        <v>RPO Labels</v>
+      </c>
+      <c r="B3433" t="str">
+        <v>تسميات نقطة الاسترداد</v>
+      </c>
+      <c r="C3433" t="str">
+        <v>RPO apzīmējumi</v>
+      </c>
+    </row>
+    <row r="3434">
+      <c r="A3434" t="str">
+        <v>RPO defines the maximum acceptable data loss measured in time. Configure labels to standardize RPO options across your organization.</v>
+      </c>
+      <c r="B3434" t="str">
+        <v>تحدد نقطة الاسترداد الحد الأقصى المقبول لفقدان البيانات المقاس بالوقت. قم بتكوين التسميات لتوحيد خيارات نقطة الاسترداد عبر مؤسستك.</v>
+      </c>
+      <c r="C3434" t="str">
+        <v>RPO nosaka maksimāli pieļaujamo datu zudumu, mērot laikā. Konfigurējiet apzīmējumus, lai standartizētu RPO opcijas visā organizācijā.</v>
+      </c>
+    </row>
+    <row r="3435">
+      <c r="A3435" t="str">
+        <v>RTO</v>
+      </c>
+      <c r="B3435" t="str">
+        <v>وقت الاسترداد</v>
+      </c>
+      <c r="C3435" t="str">
+        <v>RTO</v>
+      </c>
+    </row>
+    <row r="3436">
+      <c r="A3436" t="str">
+        <v>RTO Labels</v>
+      </c>
+      <c r="B3436" t="str">
+        <v>تسميات وقت الاسترداد</v>
+      </c>
+      <c r="C3436" t="str">
+        <v>RTO apzīmējumi</v>
+      </c>
+    </row>
+    <row r="3437">
+      <c r="A3437" t="str">
+        <v>RTO defines the maximum acceptable time to restore a process after a disruption. Configure labels to standardize RTO options across your organization.</v>
+      </c>
+      <c r="B3437" t="str">
+        <v>يحدد وقت الاسترداد الحد الأقصى المقبول لاستعادة العملية بعد الانقطاع. قم بتكوين التسميات لتوحيد خيارات وقت الاسترداد عبر مؤسستك.</v>
+      </c>
+      <c r="C3437" t="str">
+        <v>RTO nosaka maksimāli pieļaujamo laiku procesa atjaunošanai pēc traucējuma. Konfigurējiet apzīmējumus, lai standartizētu RTO opcijas visā organizācijā.</v>
+      </c>
+    </row>
+    <row r="3438">
+      <c r="A3438" t="str">
+        <v>Recovery Point Objective (RPO)</v>
+      </c>
+      <c r="B3438" t="str">
+        <v>هدف نقطة الاسترداد (RPO)</v>
+      </c>
+      <c r="C3438" t="str">
+        <v>Atjaunošanas punkta mērķis (RPO)</v>
+      </c>
+    </row>
+    <row r="3439">
+      <c r="A3439" t="str">
+        <v>Recovery Time Objective (RTO)</v>
+      </c>
+      <c r="B3439" t="str">
+        <v>هدف وقت الاسترداد (RTO)</v>
+      </c>
+      <c r="C3439" t="str">
+        <v>Atjaunošanas laika mērķis (RTO)</v>
+      </c>
+    </row>
+    <row r="3440">
+      <c r="A3440" t="str">
+        <v>Create a new Recovery Point Objective label</v>
+      </c>
+      <c r="B3440" t="str">
+        <v>إنشاء تسمية جديدة لهدف نقطة الاسترداد</v>
+      </c>
+      <c r="C3440" t="str">
+        <v>Izveidot jaunu RPO apzīmējumu</v>
+      </c>
+    </row>
+    <row r="3441">
+      <c r="A3441" t="str">
+        <v>Create a new Recovery Time Objective label</v>
+      </c>
+      <c r="B3441" t="str">
+        <v>إنشاء تسمية جديدة لهدف وقت الاسترداد</v>
+      </c>
+      <c r="C3441" t="str">
+        <v>Izveidot jaunu RTO apzīmējumu</v>
+      </c>
+    </row>
+    <row r="3442">
+      <c r="A3442" t="str">
+        <v>Time Value</v>
+      </c>
+      <c r="B3442" t="str">
+        <v>قيمة الوقت</v>
+      </c>
+      <c r="C3442" t="str">
+        <v>Laika vērtība</v>
+      </c>
+    </row>
+    <row r="3443">
+      <c r="A3443" t="str">
+        <v>Time Value (in hours)</v>
+      </c>
+      <c r="B3443" t="str">
+        <v>قيمة الوقت (بالساعات)</v>
+      </c>
+      <c r="C3443" t="str">
+        <v>Laika vērtība (stundās)</v>
+      </c>
+    </row>
+    <row r="3444">
+      <c r="A3444" t="str">
+        <v>Enter value in hours. Use 0.5 for 30 minutes, 0.25 for 15 minutes, etc.</v>
+      </c>
+      <c r="B3444" t="str">
+        <v>أدخل القيمة بالساعات. استخدم 0.5 لـ 30 دقيقة، 0.25 لـ 15 دقيقة، إلخ.</v>
+      </c>
+      <c r="C3444" t="str">
+        <v>Ievadiet vērtību stundās. Izmantojiet 0.5 par 30 minūtēm, 0.25 par 15 minūtēm utt.</v>
+      </c>
+    </row>
+    <row r="3445">
+      <c r="A3445" t="str">
+        <v>Add Range</v>
+      </c>
+      <c r="B3445" t="str">
+        <v>إضافة نطاق</v>
+      </c>
+      <c r="C3445" t="str">
+        <v>Pievienot diapazonu</v>
+      </c>
+    </row>
+    <row r="3446">
+      <c r="A3446" t="str">
+        <v>Add Rating</v>
+      </c>
+      <c r="B3446" t="str">
+        <v>إضافة تقييم</v>
+      </c>
+      <c r="C3446" t="str">
+        <v>Pievienot vērtējumu</v>
+      </c>
+    </row>
+    <row r="3447">
+      <c r="A3447" t="str">
+        <v>Criticality Label</v>
+      </c>
+      <c r="B3447" t="str">
+        <v>تسمية الحرجية</v>
+      </c>
+      <c r="C3447" t="str">
+        <v>Kritiskuma apzīmējums</v>
+      </c>
+    </row>
+    <row r="3448">
+      <c r="A3448" t="str">
+        <v>Criticality Ranges</v>
+      </c>
+      <c r="B3448" t="str">
+        <v>نطاقات الحرجية</v>
+      </c>
+      <c r="C3448" t="str">
+        <v>Kritiskuma diapazoni</v>
+      </c>
+    </row>
+    <row r="3449">
+      <c r="A3449" t="str">
+        <v>Edit Scoring Range</v>
+      </c>
+      <c r="B3449" t="str">
+        <v>تعديل نطاق التقييم</v>
+      </c>
+      <c r="C3449" t="str">
+        <v>Rediģēt vērtēšanas diapazonu</v>
+      </c>
+    </row>
+    <row r="3450">
+      <c r="A3450" t="str">
+        <v>Max Score</v>
+      </c>
+      <c r="B3450" t="str">
+        <v>الحد الأقصى للنقاط</v>
+      </c>
+      <c r="C3450" t="str">
+        <v>Maksimālais punktu skaits</v>
+      </c>
+    </row>
+    <row r="3451">
+      <c r="A3451" t="str">
+        <v>Min Score</v>
+      </c>
+      <c r="B3451" t="str">
+        <v>الحد الأدنى للنقاط</v>
+      </c>
+      <c r="C3451" t="str">
+        <v>Minimālais punktu skaits</v>
+      </c>
+    </row>
+    <row r="3452">
+      <c r="A3452" t="str">
+        <v>Range</v>
+      </c>
+      <c r="B3452" t="str">
+        <v>نطاق</v>
+      </c>
+      <c r="C3452" t="str">
+        <v>Diapazons</v>
+      </c>
+    </row>
+    <row r="3453">
+      <c r="A3453" t="str">
+        <v>Rating Label</v>
+      </c>
+      <c r="B3453" t="str">
+        <v>تسمية التقييم</v>
+      </c>
+      <c r="C3453" t="str">
+        <v>Vērtējuma apzīmējums</v>
+      </c>
+    </row>
+    <row r="3454">
+      <c r="A3454" t="str">
+        <v>Rating Methodology</v>
+      </c>
+      <c r="B3454" t="str">
+        <v>منهجية التقييم</v>
+      </c>
+      <c r="C3454" t="str">
+        <v>Vērtēšanas metodoloģija</v>
+      </c>
+    </row>
+    <row r="3455">
+      <c r="A3455" t="str">
+        <v>Score Value</v>
+      </c>
+      <c r="B3455" t="str">
+        <v>قيمة النقاط</v>
+      </c>
+      <c r="C3455" t="str">
+        <v>Punktu vērtība</v>
+      </c>
+    </row>
+    <row r="3456">
+      <c r="A3456" t="str">
+        <v>Sort Order</v>
+      </c>
+      <c r="B3456" t="str">
+        <v>ترتيب الفرز</v>
+      </c>
+      <c r="C3456" t="str">
+        <v>Kārtošanas secība</v>
+      </c>
+    </row>
+    <row r="3457">
+      <c r="A3457" t="str">
+        <v>Define a criticality level based on score range</v>
+      </c>
+      <c r="B3457" t="str">
+        <v>تحديد مستوى حرجية بناءً على نطاق النقاط</v>
+      </c>
+      <c r="C3457" t="str">
+        <v>Definēt kritiskuma līmeni, pamatojoties uz punktu diapazonu</v>
+      </c>
+    </row>
+    <row r="3458">
+      <c r="A3458" t="str">
+        <v>Define score ranges to determine process criticality levels</v>
+      </c>
+      <c r="B3458" t="str">
+        <v>تحديد نطاقات النقاط لتحديد مستويات حرجية العملية</v>
+      </c>
+      <c r="C3458" t="str">
+        <v>Definēt punktu diapazonus procesu kritiskuma līmeņu noteikšanai</v>
+      </c>
+    </row>
+    <row r="3459">
+      <c r="A3459" t="str">
+        <v>Impact description for this rating</v>
+      </c>
+      <c r="B3459" t="str">
+        <v>وصف التأثير لهذا التقييم</v>
+      </c>
+      <c r="C3459" t="str">
+        <v>Ietekmes apraksts šim vērtējumam</v>
+      </c>
+    </row>
+    <row r="3460">
+      <c r="A3460" t="str">
+        <v>Addition of all (Sum)</v>
+      </c>
+      <c r="B3460" t="str">
+        <v>مجموع الكل (جمع)</v>
+      </c>
+      <c r="C3460" t="str">
+        <v>Visu saskaitīšana (summa)</v>
+      </c>
+    </row>
+    <row r="3461">
+      <c r="A3461" t="str">
+        <v>All category scores will be added together for the impact rating.</v>
+      </c>
+      <c r="B3461" t="str">
+        <v>سيتم جمع جميع درجات الفئات معاً لتقييم التأثير.</v>
+      </c>
+      <c r="C3461" t="str">
+        <v>Visi kategoriju punkti tiks saskaitīti ietekmes vērtējumam.</v>
+      </c>
+    </row>
+    <row r="3462">
+      <c r="A3462" t="str">
+        <v>All category scores will be multiplied together for the impact rating.</v>
+      </c>
+      <c r="B3462" t="str">
+        <v>سيتم ضرب جميع درجات الفئات معاً لتقييم التأثير.</v>
+      </c>
+      <c r="C3462" t="str">
+        <v>Visi kategoriju punkti tiks reizināti ietekmes vērtējumam.</v>
+      </c>
+    </row>
+    <row r="3463">
+      <c r="A3463" t="str">
+        <v>High of all (Maximum)</v>
+      </c>
+      <c r="B3463" t="str">
+        <v>الأعلى من الكل (الحد الأقصى)</v>
+      </c>
+      <c r="C3463" t="str">
+        <v>Augstākais no visiem (Maksimums)</v>
+      </c>
+    </row>
+    <row r="3464">
+      <c r="A3464" t="str">
+        <v>Note: Product of all ratings will be calculated</v>
+      </c>
+      <c r="B3464" t="str">
+        <v>ملاحظة: سيتم حساب حاصل ضرب جميع التقييمات</v>
+      </c>
+      <c r="C3464" t="str">
+        <v>Piezīme: tiks aprēķināts visu vērtējumu reizinājums</v>
+      </c>
+    </row>
+    <row r="3465">
+      <c r="A3465" t="str">
+        <v>Note: Sum of all ratings will be calculated</v>
+      </c>
+      <c r="B3465" t="str">
+        <v>ملاحظة: سيتم حساب مجموع جميع التقييمات</v>
+      </c>
+      <c r="C3465" t="str">
+        <v>Piezīme: tiks aprēķināta visu vērtējumu summa</v>
+      </c>
+    </row>
+    <row r="3466">
+      <c r="A3466" t="str">
+        <v>Product of all (Multiply)</v>
+      </c>
+      <c r="B3466" t="str">
+        <v>حاصل ضرب الكل (ضرب)</v>
+      </c>
+      <c r="C3466" t="str">
+        <v>Visu reizinājums (reizināšana)</v>
+      </c>
+    </row>
+    <row r="3467">
+      <c r="A3467" t="str">
+        <v>The highest score among all categories will be used as the impact rating.</v>
+      </c>
+      <c r="B3467" t="str">
+        <v>سيتم استخدام أعلى درجة بين جميع الفئات كتقييم للتأثير.</v>
+      </c>
+      <c r="C3467" t="str">
+        <v>Augstākais punktu skaits starp visām kategorijām tiks izmantots kā ietekmes vērtējums.</v>
+      </c>
+    </row>
+    <row r="3468">
+      <c r="A3468" t="str">
+        <v>Select calculation type</v>
+      </c>
+      <c r="B3468" t="str">
+        <v>اختر نوع الحساب</v>
+      </c>
+      <c r="C3468" t="str">
+        <v>Atlasīt aprēķina veidu</v>
+      </c>
+    </row>
+    <row r="3469">
+      <c r="A3469" t="str">
+        <v>CMM Maturity Level Descriptions</v>
+      </c>
+      <c r="B3469" t="str">
+        <v>أوصاف مستويات نضج CMM</v>
+      </c>
+      <c r="C3469" t="str">
+        <v>CMM brieduma līmeņu apraksti</v>
+      </c>
+    </row>
+    <row r="3470">
+      <c r="A3470" t="str">
+        <v>Level 0 - Not Performed</v>
+      </c>
+      <c r="B3470" t="str">
+        <v>المستوى 0 - لم يُنفذ</v>
+      </c>
+      <c r="C3470" t="str">
+        <v>0. līmenis - Nav izpildīts</v>
+      </c>
+    </row>
+    <row r="3471">
+      <c r="A3471" t="str">
+        <v>Level 1 - Performed Informally</v>
+      </c>
+      <c r="B3471" t="str">
+        <v>المستوى 1 - نُفذ بشكل غير رسمي</v>
+      </c>
+      <c r="C3471" t="str">
+        <v>1. līmenis - Izpildīts neformāli</v>
+      </c>
+    </row>
+    <row r="3472">
+      <c r="A3472" t="str">
+        <v>Level 2 - Planned and Tracked</v>
+      </c>
+      <c r="B3472" t="str">
+        <v>المستوى 2 - مخطط ومتابع</v>
+      </c>
+      <c r="C3472" t="str">
+        <v>2. līmenis - Plānots un izsekots</v>
+      </c>
+    </row>
+    <row r="3473">
+      <c r="A3473" t="str">
+        <v>Level 3 - Well Defined</v>
+      </c>
+      <c r="B3473" t="str">
+        <v>المستوى 3 - محدد بشكل جيد</v>
+      </c>
+      <c r="C3473" t="str">
+        <v>3. līmenis - Labi definēts</v>
+      </c>
+    </row>
+    <row r="3474">
+      <c r="A3474" t="str">
+        <v>Level 4 - Quantitatively Controlled</v>
+      </c>
+      <c r="B3474" t="str">
+        <v>المستوى 4 - مُسيطر عليه كمياً</v>
+      </c>
+      <c r="C3474" t="str">
+        <v>4. līmenis - Kvantitatīvi kontrolēts</v>
+      </c>
+    </row>
+    <row r="3475">
+      <c r="A3475" t="str">
+        <v>Level 5 - Continuously Improving</v>
+      </c>
+      <c r="B3475" t="str">
+        <v>المستوى 5 - تحسين مستمر</v>
+      </c>
+      <c r="C3475" t="str">
+        <v>5. līmenis - Nepārtraukti uzlabojas</v>
+      </c>
+    </row>
+    <row r="3476">
+      <c r="A3476" t="str">
+        <v>Add New Control</v>
+      </c>
+      <c r="B3476" t="str">
+        <v>إضافة ضابط جديد</v>
+      </c>
+      <c r="C3476" t="str">
+        <v>Pievienot jaunu kontroli</v>
+      </c>
+    </row>
+    <row r="3477">
+      <c r="A3477" t="str">
+        <v>Choose Control</v>
+      </c>
+      <c r="B3477" t="str">
+        <v>اختر ضابطاً</v>
+      </c>
+      <c r="C3477" t="str">
+        <v>Izvēlieties kontroli</v>
+      </c>
+    </row>
+    <row r="3478">
+      <c r="A3478" t="str">
+        <v>Control Compliance</v>
+      </c>
+      <c r="B3478" t="str">
+        <v>امتثال الضوابط</v>
+      </c>
+      <c r="C3478" t="str">
+        <v>Kontroles atbilstība</v>
+      </c>
+    </row>
+    <row r="3479">
+      <c r="A3479" t="str">
+        <v>Control Not Found</v>
+      </c>
+      <c r="B3479" t="str">
+        <v>لم يتم العثور على الضابط</v>
+      </c>
+      <c r="C3479" t="str">
+        <v>Kontrole nav atrasta</v>
+      </c>
+    </row>
+    <row r="3480">
+      <c r="A3480" t="str">
+        <v>Create Exception</v>
+      </c>
+      <c r="B3480" t="str">
+        <v>إنشاء استثناء</v>
+      </c>
+      <c r="C3480" t="str">
+        <v>Izveidot izņēmumu</v>
+      </c>
+    </row>
+    <row r="3481">
+      <c r="A3481" t="str">
+        <v>Create Framework</v>
+      </c>
+      <c r="B3481" t="str">
+        <v>إنشاء إطار عمل</v>
+      </c>
+      <c r="C3481" t="str">
+        <v>Izveidot ietvaru</v>
+      </c>
+    </row>
+    <row r="3482">
+      <c r="A3482" t="str">
+        <v>Edit Framework</v>
+      </c>
+      <c r="B3482" t="str">
+        <v>تعديل إطار العمل</v>
+      </c>
+      <c r="C3482" t="str">
+        <v>Rediģēt ietvaru</v>
+      </c>
+    </row>
+    <row r="3483">
+      <c r="A3483" t="str">
+        <v>Edit SOA Entry</v>
+      </c>
+      <c r="B3483" t="str">
+        <v>تعديل إدخال بيان التطبيق</v>
+      </c>
+      <c r="C3483" t="str">
+        <v>Rediģēt SOA ierakstu</v>
+      </c>
+    </row>
+    <row r="3484">
+      <c r="A3484" t="str">
+        <v>Exception Details</v>
+      </c>
+      <c r="B3484" t="str">
+        <v>تفاصيل الاستثناء</v>
+      </c>
+      <c r="C3484" t="str">
+        <v>Izņēmuma detaļas</v>
+      </c>
+    </row>
+    <row r="3485">
+      <c r="A3485" t="str">
+        <v>Export SOA</v>
+      </c>
+      <c r="B3485" t="str">
+        <v>تصدير بيان التطبيق</v>
+      </c>
+      <c r="C3485" t="str">
+        <v>Eksportēt SOA</v>
+      </c>
+    </row>
+    <row r="3486">
+      <c r="A3486" t="str">
+        <v>Implementation Status</v>
+      </c>
+      <c r="B3486" t="str">
+        <v>حالة التنفيذ</v>
+      </c>
+      <c r="C3486" t="str">
+        <v>Ieviešanas statuss</v>
+      </c>
+    </row>
+    <row r="3487">
+      <c r="A3487" t="str">
+        <v>Import Requirements</v>
+      </c>
+      <c r="B3487" t="str">
+        <v>استيراد المتطلبات</v>
+      </c>
+      <c r="C3487" t="str">
+        <v>Importēt prasības</v>
+      </c>
+    </row>
+    <row r="3488">
+      <c r="A3488" t="str">
+        <v>Manage framework requirements and controls</v>
+      </c>
+      <c r="B3488" t="str">
+        <v>إدارة متطلبات وضوابط الإطار</v>
+      </c>
+      <c r="C3488" t="str">
+        <v>Pārvaldīt ietvara prasības un kontroles</v>
+      </c>
+    </row>
+    <row r="3489">
+      <c r="A3489" t="str">
+        <v>Manage requirement applicability and implementation status</v>
+      </c>
+      <c r="B3489" t="str">
+        <v>إدارة تطبيقية المتطلبات وحالة التنفيذ</v>
+      </c>
+      <c r="C3489" t="str">
+        <v>Pārvaldīt prasību piemērojamību un ieviešanas statusu</v>
+      </c>
+    </row>
+    <row r="3490">
+      <c r="A3490" t="str">
+        <v>Not Implemented</v>
+      </c>
+      <c r="B3490" t="str">
+        <v>غير منفذ</v>
+      </c>
+      <c r="C3490" t="str">
+        <v>Nav ieviests</v>
+      </c>
+    </row>
+    <row r="3491">
+      <c r="A3491" t="str">
+        <v>Overall Control Rating</v>
+      </c>
+      <c r="B3491" t="str">
+        <v>التقييم العام للضوابط</v>
+      </c>
+      <c r="C3491" t="str">
+        <v>Kopējais kontroles vērtējums</v>
+      </c>
+    </row>
+    <row r="3492">
+      <c r="A3492" t="str">
+        <v>Partially Applicable</v>
+      </c>
+      <c r="B3492" t="str">
+        <v>قابل للتطبيق جزئياً</v>
+      </c>
+      <c r="C3492" t="str">
+        <v>Daļēji piemērojams</v>
+      </c>
+    </row>
+    <row r="3493">
+      <c r="A3493" t="str">
+        <v>Partially Implemented</v>
+      </c>
+      <c r="B3493" t="str">
+        <v>منفذ جزئياً</v>
+      </c>
+      <c r="C3493" t="str">
+        <v>Daļēji ieviests</v>
+      </c>
+    </row>
+    <row r="3494">
+      <c r="A3494" t="str">
+        <v>Please provide the following details to create a new compliance framework.</v>
+      </c>
+      <c r="B3494" t="str">
+        <v>يرجى تقديم التفاصيل التالية لإنشاء إطار امتثال جديد.</v>
+      </c>
+      <c r="C3494" t="str">
+        <v>Lūdzu, norādiet šādu informāciju, lai izveidotu jaunu atbilstības ietvaru.</v>
+      </c>
+    </row>
+    <row r="3495">
+      <c r="A3495" t="str">
+        <v>Provide justification for applicability decision</v>
+      </c>
+      <c r="B3495" t="str">
+        <v>قدم مبرراً لقرار التطبيقية</v>
+      </c>
+      <c r="C3495" t="str">
+        <v>Norādiet pamatojumu piemērojamības lēmumam</v>
+      </c>
+    </row>
+    <row r="3496">
+      <c r="A3496" t="str">
+        <v>Select applicability</v>
+      </c>
+      <c r="B3496" t="str">
+        <v>اختر التطبيقية</v>
+      </c>
+      <c r="C3496" t="str">
+        <v>Atlasīt piemērojamību</v>
+      </c>
+    </row>
+    <row r="3497">
+      <c r="A3497" t="str">
+        <v>Statement of Applicability</v>
+      </c>
+      <c r="B3497" t="str">
+        <v>بيان التطبيق</v>
+      </c>
+      <c r="C3497" t="str">
+        <v>Piemērojamības paziņojums</v>
+      </c>
+    </row>
+    <row r="3498">
+      <c r="A3498" t="str">
+        <v>This framework has no requirements. Import requirements to enable SOA editing.</v>
+      </c>
+      <c r="B3498" t="str">
+        <v>لا يحتوي هذا الإطار على متطلبات. استورد المتطلبات لتمكين تحرير بيان التطبيق.</v>
+      </c>
+      <c r="C3498" t="str">
+        <v>Šim ietvaram nav prasību. Importējiet prasības, lai iespējotu SOA rediģēšanu.</v>
+      </c>
+    </row>
+    <row r="3499">
+      <c r="A3499" t="str">
+        <v>Total Requirements</v>
+      </c>
+      <c r="B3499" t="str">
+        <v>إجمالي المتطلبات</v>
+      </c>
+      <c r="C3499" t="str">
+        <v>Kopējās prasības</v>
+      </c>
+    </row>
+    <row r="3500">
+      <c r="A3500" t="str">
+        <v>All frameworks</v>
+      </c>
+      <c r="B3500" t="str">
+        <v>جميع الأطر</v>
+      </c>
+      <c r="C3500" t="str">
+        <v>Visi ietvari</v>
+      </c>
+    </row>
+    <row r="3501">
+      <c r="A3501" t="str">
+        <v>No requirements</v>
+      </c>
+      <c r="B3501" t="str">
+        <v>لا توجد متطلبات</v>
+      </c>
+      <c r="C3501" t="str">
+        <v>Nav prasību</v>
+      </c>
+    </row>
+    <row r="3502">
+      <c r="A3502" t="str">
+        <v>No requirements available</v>
+      </c>
+      <c r="B3502" t="str">
+        <v>لا تتوفر متطلبات</v>
+      </c>
+      <c r="C3502" t="str">
+        <v>Nav pieejamu prasību</v>
+      </c>
+    </row>
+    <row r="3503">
+      <c r="A3503" t="str">
+        <v>No requirements found</v>
+      </c>
+      <c r="B3503" t="str">
+        <v>لم يتم العثور على متطلبات</v>
+      </c>
+      <c r="C3503" t="str">
+        <v>Prasības nav atrastas</v>
+      </c>
+    </row>
+    <row r="3504">
+      <c r="A3504" t="str">
+        <v>No frameworks found.</v>
+      </c>
+      <c r="B3504" t="str">
+        <v>لم يتم العثور على أطر.</v>
+      </c>
+      <c r="C3504" t="str">
+        <v>Ietvari nav atrasti.</v>
+      </c>
+    </row>
+    <row r="3505">
+      <c r="A3505" t="str">
+        <v>Add controls to plan risk mitigation</v>
+      </c>
+      <c r="B3505" t="str">
+        <v>أضف ضوابط لتخطيط تخفيف المخاطر</v>
+      </c>
+      <c r="C3505" t="str">
+        <v>Pievienojiet kontroles risku mazināšanas plānošanai</v>
+      </c>
+    </row>
+    <row r="3506">
+      <c r="A3506" t="str">
+        <v>Adding risks to your library...</v>
+      </c>
+      <c r="B3506" t="str">
+        <v>جاري إضافة المخاطر إلى مكتبتك...</v>
+      </c>
+      <c r="C3506" t="str">
+        <v>Pievieno riskus jūsu bibliotēkai...</v>
+      </c>
+    </row>
+    <row r="3507">
+      <c r="A3507" t="str">
+        <v>Click 'Confirm &amp; Register' to add these risks to your library.</v>
+      </c>
+      <c r="B3507" t="str">
+        <v>انقر "تأكيد وتسجيل" لإضافة هذه المخاطر إلى مكتبتك.</v>
+      </c>
+      <c r="C3507" t="str">
+        <v>Noklikšķiniet "Apstiprināt un reģistrēt", lai pievienotu šos riskus jūsu bibliotēkai.</v>
+      </c>
+    </row>
+    <row r="3508">
+      <c r="A3508" t="str">
+        <v>Comparing with existing risk library...</v>
+      </c>
+      <c r="B3508" t="str">
+        <v>جاري المقارنة مع مكتبة المخاطر الحالية...</v>
+      </c>
+      <c r="C3508" t="str">
+        <v>Salīdzina ar esošo risku bibliotēku...</v>
+      </c>
+    </row>
+    <row r="3509">
+      <c r="A3509" t="str">
+        <v>Confirm &amp; Register</v>
+      </c>
+      <c r="B3509" t="str">
+        <v>تأكيد وتسجيل</v>
+      </c>
+      <c r="C3509" t="str">
+        <v>Apstiprināt un reģistrēt</v>
+      </c>
+    </row>
+    <row r="3510">
+      <c r="A3510" t="str">
+        <v>Existing Matches</v>
+      </c>
+      <c r="B3510" t="str">
+        <v>التطابقات الحالية</v>
+      </c>
+      <c r="C3510" t="str">
+        <v>Esošās atbilstības</v>
+      </c>
+    </row>
+    <row r="3511">
+      <c r="A3511" t="str">
+        <v>Impact (1-5)</v>
+      </c>
+      <c r="B3511" t="str">
+        <v>التأثير (1-5)</v>
+      </c>
+      <c r="C3511" t="str">
+        <v>Ietekme (1-5)</v>
+      </c>
+    </row>
+    <row r="3512">
+      <c r="A3512" t="str">
+        <v>Likelihood (1-5)</v>
+      </c>
+      <c r="B3512" t="str">
+        <v>الاحتمالية (1-5)</v>
+      </c>
+      <c r="C3512" t="str">
+        <v>Iespējamība (1-5)</v>
+      </c>
+    </row>
+    <row r="3513">
+      <c r="A3513" t="str">
+        <v>Likely</v>
+      </c>
+      <c r="B3513" t="str">
+        <v>محتمل</v>
+      </c>
+      <c r="C3513" t="str">
+        <v>Ticams</v>
+      </c>
+    </row>
+    <row r="3514">
+      <c r="A3514" t="str">
+        <v>Match Preview</v>
+      </c>
+      <c r="B3514" t="str">
+        <v>معاينة التطابق</v>
+      </c>
+      <c r="C3514" t="str">
+        <v>Atbilstības priekšskatījums</v>
+      </c>
+    </row>
+    <row r="3515">
+      <c r="A3515" t="str">
+        <v>Match with Library</v>
+      </c>
+      <c r="B3515" t="str">
+        <v>مطابقة مع المكتبة</v>
+      </c>
+      <c r="C3515" t="str">
+        <v>Saskaņot ar bibliotēku</v>
+      </c>
+    </row>
+    <row r="3516">
+      <c r="A3516" t="str">
+        <v>Matched</v>
+      </c>
+      <c r="B3516" t="str">
+        <v>متطابق</v>
+      </c>
+      <c r="C3516" t="str">
+        <v>Saskaņots</v>
+      </c>
+    </row>
+    <row r="3517">
+      <c r="A3517" t="str">
+        <v>Matching Complete</v>
+      </c>
+      <c r="B3517" t="str">
+        <v>اكتملت المطابقة</v>
+      </c>
+      <c r="C3517" t="str">
+        <v>Saskaņošana pabeigta</v>
+      </c>
+    </row>
+    <row r="3518">
+      <c r="A3518" t="str">
+        <v>Matching...</v>
+      </c>
+      <c r="B3518" t="str">
+        <v>جاري المطابقة...</v>
+      </c>
+      <c r="C3518" t="str">
+        <v>Saskaņo...</v>
+      </c>
+    </row>
+    <row r="3519">
+      <c r="A3519" t="str">
+        <v>New Controls</v>
+      </c>
+      <c r="B3519" t="str">
+        <v>ضوابط جديدة</v>
+      </c>
+      <c r="C3519" t="str">
+        <v>Jaunas kontroles</v>
+      </c>
+    </row>
+    <row r="3520">
+      <c r="A3520" t="str">
+        <v>New Risks</v>
+      </c>
+      <c r="B3520" t="str">
+        <v>مخاطر جديدة</v>
+      </c>
+      <c r="C3520" t="str">
+        <v>Jauni riski</v>
+      </c>
+    </row>
+    <row r="3521">
+      <c r="A3521" t="str">
+        <v>New Threats</v>
+      </c>
+      <c r="B3521" t="str">
+        <v>تهديدات جديدة</v>
+      </c>
+      <c r="C3521" t="str">
+        <v>Jauni draudi</v>
+      </c>
+    </row>
+    <row r="3522">
+      <c r="A3522" t="str">
+        <v>Planned Residual Risk Rating</v>
+      </c>
+      <c r="B3522" t="str">
+        <v>تقييم المخاطر المتبقية المخطط لها</v>
+      </c>
+      <c r="C3522" t="str">
+        <v>Plānotais atlikušā riska vērtējums</v>
+      </c>
+    </row>
+    <row r="3523">
+      <c r="A3523" t="str">
+        <v>Position in Risk Matrix</v>
+      </c>
+      <c r="B3523" t="str">
+        <v>الموقع في مصفوفة المخاطر</v>
+      </c>
+      <c r="C3523" t="str">
+        <v>Pozīcija risku matricā</v>
+      </c>
+    </row>
+    <row r="3524">
+      <c r="A3524" t="str">
+        <v>Possible</v>
+      </c>
+      <c r="B3524" t="str">
+        <v>ممكن</v>
+      </c>
+      <c r="C3524" t="str">
+        <v>Iespējams</v>
+      </c>
+    </row>
+    <row r="3525">
+      <c r="A3525" t="str">
+        <v>Rare</v>
+      </c>
+      <c r="B3525" t="str">
+        <v>نادر</v>
+      </c>
+      <c r="C3525" t="str">
+        <v>Reti</v>
+      </c>
+    </row>
+    <row r="3526">
+      <c r="A3526" t="str">
+        <v>Unlikely</v>
+      </c>
+      <c r="B3526" t="str">
+        <v>غير محتمل</v>
+      </c>
+      <c r="C3526" t="str">
+        <v>Maz ticams</v>
+      </c>
+    </row>
+    <row r="3527">
+      <c r="A3527" t="str">
+        <v>Insignificant</v>
+      </c>
+      <c r="B3527" t="str">
+        <v>غير مهم</v>
+      </c>
+      <c r="C3527" t="str">
+        <v>Nenozīmīgs</v>
+      </c>
+    </row>
+    <row r="3528">
+      <c r="A3528" t="str">
+        <v>Almost Certain</v>
+      </c>
+      <c r="B3528" t="str">
+        <v>شبه مؤكد</v>
+      </c>
+      <c r="C3528" t="str">
+        <v>Gandrīz noteikts</v>
+      </c>
+    </row>
+    <row r="3529">
+      <c r="A3529" t="str">
+        <v>Registering Risks</v>
+      </c>
+      <c r="B3529" t="str">
+        <v>تسجيل المخاطر</v>
+      </c>
+      <c r="C3529" t="str">
+        <v>Reģistrē riskus</v>
+      </c>
+    </row>
+    <row r="3530">
+      <c r="A3530" t="str">
+        <v>Registering...</v>
+      </c>
+      <c r="B3530" t="str">
+        <v>جاري التسجيل...</v>
+      </c>
+      <c r="C3530" t="str">
+        <v>Reģistrē...</v>
+      </c>
+    </row>
+    <row r="3531">
+      <c r="A3531" t="str">
+        <v>Remove this control</v>
+      </c>
+      <c r="B3531" t="str">
+        <v>إزالة هذا الضابط</v>
+      </c>
+      <c r="C3531" t="str">
+        <v>Noņemt šo kontroli</v>
+      </c>
+    </row>
+    <row r="3532">
+      <c r="A3532" t="str">
+        <v>Remove this risk</v>
+      </c>
+      <c r="B3532" t="str">
+        <v>إزالة هذه المخاطرة</v>
+      </c>
+      <c r="C3532" t="str">
+        <v>Noņemt šo risku</v>
+      </c>
+    </row>
+    <row r="3533">
+      <c r="A3533" t="str">
+        <v>Remove this threat</v>
+      </c>
+      <c r="B3533" t="str">
+        <v>إزالة هذا التهديد</v>
+      </c>
+      <c r="C3533" t="str">
+        <v>Noņemt šo draudu</v>
+      </c>
+    </row>
+    <row r="3534">
+      <c r="A3534" t="str">
+        <v>Remove this vulnerability</v>
+      </c>
+      <c r="B3534" t="str">
+        <v>إزالة هذه الثغرة</v>
+      </c>
+      <c r="C3534" t="str">
+        <v>Noņemt šo ievainojamību</v>
+      </c>
+    </row>
+    <row r="3535">
+      <c r="A3535" t="str">
+        <v>Residual Impact (1-5)</v>
+      </c>
+      <c r="B3535" t="str">
+        <v>التأثير المتبقي (1-5)</v>
+      </c>
+      <c r="C3535" t="str">
+        <v>Atlikusī ietekme (1-5)</v>
+      </c>
+    </row>
+    <row r="3536">
+      <c r="A3536" t="str">
+        <v>Residual Likelihood (1-5)</v>
+      </c>
+      <c r="B3536" t="str">
+        <v>الاحتمالية المتبقية (1-5)</v>
+      </c>
+      <c r="C3536" t="str">
+        <v>Atlikusī iespējamība (1-5)</v>
+      </c>
+    </row>
+    <row r="3537">
+      <c r="A3537" t="str">
+        <v>Residual Risk Rating</v>
+      </c>
+      <c r="B3537" t="str">
+        <v>تقييم المخاطر المتبقية</v>
+      </c>
+      <c r="C3537" t="str">
+        <v>Atlikušā riska vērtējums</v>
+      </c>
+    </row>
+    <row r="3538">
+      <c r="A3538" t="str">
+        <v>Resubmit Exception</v>
+      </c>
+      <c r="B3538" t="str">
+        <v>إعادة تقديم الاستثناء</v>
+      </c>
+      <c r="C3538" t="str">
+        <v>Atkārtoti iesniegt izņēmumu</v>
+      </c>
+    </row>
+    <row r="3539">
+      <c r="A3539" t="str">
+        <v>Review and remove unwanted risks before proceeding.</v>
+      </c>
+      <c r="B3539" t="str">
+        <v>راجع وأزل المخاطر غير المرغوب فيها قبل المتابعة.</v>
+      </c>
+      <c r="C3539" t="str">
+        <v>Pārskatiet un noņemiet nevēlamus riskus pirms turpināšanas.</v>
+      </c>
+    </row>
+    <row r="3540">
+      <c r="A3540" t="str">
+        <v>Review the AI-identified risks below. Remove any unwanted risks, then click 'Match with Library' to find duplicates.</v>
+      </c>
+      <c r="B3540" t="str">
+        <v>راجع المخاطر المحددة بالذكاء الاصطناعي أدناه. أزل أي مخاطر غير مرغوب فيها، ثم انقر "مطابقة مع المكتبة" للعثور على التكرارات.</v>
+      </c>
+      <c r="C3540" t="str">
+        <v>Pārskatiet AI identificētos riskus zemāk. Noņemiet nevēlamus riskus, pēc tam noklikšķiniet "Saskaņot ar bibliotēku", lai atrastu dublikātus.</v>
+      </c>
+    </row>
+    <row r="3541">
+      <c r="A3541" t="str">
+        <v>Review the matched results below before registering.</v>
+      </c>
+      <c r="B3541" t="str">
+        <v>راجع نتائج المطابقة أدناه قبل التسجيل.</v>
+      </c>
+      <c r="C3541" t="str">
+        <v>Pārskatiet saskaņotos rezultātus zemāk pirms reģistrēšanas.</v>
+      </c>
+    </row>
+    <row r="3542">
+      <c r="A3542" t="str">
+        <v>Review the matching results above. Click 'Confirm &amp; Register' to add new risks to your library.</v>
+      </c>
+      <c r="B3542" t="str">
+        <v>راجع نتائج المطابقة أعلاه. انقر "تأكيد وتسجيل" لإضافة مخاطر جديدة إلى مكتبتك.</v>
+      </c>
+      <c r="C3542" t="str">
+        <v>Pārskatiet saskaņošanas rezultātus augstāk. Noklikšķiniet "Apstiprināt un reģistrēt", lai pievienotu jaunus riskus jūsu bibliotēkai.</v>
+      </c>
+    </row>
+    <row r="3543">
+      <c r="A3543" t="str">
+        <v>Reviewing...</v>
+      </c>
+      <c r="B3543" t="str">
+        <v>جاري المراجعة...</v>
+      </c>
+      <c r="C3543" t="str">
+        <v>Pārskata...</v>
+      </c>
+    </row>
+    <row r="3544">
+      <c r="A3544" t="str">
+        <v>Risk Not Found</v>
+      </c>
+      <c r="B3544" t="str">
+        <v>لم يتم العثور على المخاطرة</v>
+      </c>
+      <c r="C3544" t="str">
+        <v>Risks nav atrasts</v>
+      </c>
+    </row>
+    <row r="3545">
+      <c r="A3545" t="str">
+        <v>Risk Reference</v>
+      </c>
+      <c r="B3545" t="str">
+        <v>مرجع المخاطرة</v>
+      </c>
+      <c r="C3545" t="str">
+        <v>Riska atsauce</v>
+      </c>
+    </row>
+    <row r="3546">
+      <c r="A3546" t="str">
+        <v>Risk Score = Likelihood * Impact * Vulnerability</v>
+      </c>
+      <c r="B3546" t="str">
+        <v>درجة المخاطرة = الاحتمالية × التأثير × الثغرة</v>
+      </c>
+      <c r="C3546" t="str">
+        <v>Riska rezultāts = Iespējamība × Ietekme × Ievainojamība</v>
+      </c>
+    </row>
+    <row r="3547">
+      <c r="A3547" t="str">
+        <v>Risk Summary</v>
+      </c>
+      <c r="B3547" t="str">
+        <v>ملخص المخاطر</v>
+      </c>
+      <c r="C3547" t="str">
+        <v>Risku kopsavilkums</v>
+      </c>
+    </row>
+    <row r="3548">
+      <c r="A3548" t="str">
+        <v>Risk Treatment</v>
+      </c>
+      <c r="B3548" t="str">
+        <v>معالجة المخاطر</v>
+      </c>
+      <c r="C3548" t="str">
+        <v>Risku apstrāde</v>
+      </c>
+    </row>
+    <row r="3549">
+      <c r="A3549" t="str">
+        <v>Risk View</v>
+      </c>
+      <c r="B3549" t="str">
+        <v>عرض المخاطر</v>
+      </c>
+      <c r="C3549" t="str">
+        <v>Risku skats</v>
+      </c>
+    </row>
+    <row r="3550">
+      <c r="A3550" t="str">
+        <v>Risk description, Department, Risk sources, Risk category, Potential threat, Associated vulnerabilities</v>
+      </c>
+      <c r="B3550" t="str">
+        <v>وصف المخاطرة، القسم، مصادر المخاطر، فئة المخاطر، التهديد المحتمل، الثغرات المرتبطة</v>
+      </c>
+      <c r="C3550" t="str">
+        <v>Riska apraksts, Nodaļa, Risku avoti, Riska kategorija, Potenciālais drauds, Saistītās ievainojamības</v>
+      </c>
+    </row>
+    <row r="3551">
+      <c r="A3551" t="str">
+        <v>Risk name is required. Missing in row(s): {rows}</v>
+      </c>
+      <c r="B3551" t="str">
+        <v>اسم المخاطرة مطلوب. غير موجود في الصف(الصفوف): {rows}</v>
+      </c>
+      <c r="C3551" t="str">
+        <v>Riska nosaukums ir obligāts. Trūkst rindā(-ās): {rows}</v>
+      </c>
+    </row>
+    <row r="3552">
+      <c r="A3552" t="str">
+        <v>These risks have been compared with your existing library. Only new risks were added to the Risk Register.</v>
+      </c>
+      <c r="B3552" t="str">
+        <v>تمت مقارنة هذه المخاطر مع مكتبتك الحالية. تمت إضافة المخاطر الجديدة فقط إلى سجل المخاطر.</v>
+      </c>
+      <c r="C3552" t="str">
+        <v>Šie riski ir salīdzināti ar jūsu esošo bibliotēku. Tikai jauni riski tika pievienoti risku reģistram.</v>
+      </c>
+    </row>
+    <row r="3553">
+      <c r="A3553" t="str">
+        <v>The risk has been removed from the review list.</v>
+      </c>
+      <c r="B3553" t="str">
+        <v>تمت إزالة المخاطرة من قائمة المراجعة.</v>
+      </c>
+      <c r="C3553" t="str">
+        <v>Risks ir noņemts no pārskata saraksta.</v>
+      </c>
+    </row>
+    <row r="3554">
+      <c r="A3554" t="str">
+        <v>Link controls first to generate</v>
+      </c>
+      <c r="B3554" t="str">
+        <v>اربط الضوابط أولاً للإنشاء</v>
+      </c>
+      <c r="C3554" t="str">
+        <v>Vispirms saistiet kontroles, lai ģenerētu</v>
+      </c>
+    </row>
+    <row r="3555">
+      <c r="A3555" t="str">
+        <v>Link controls from the risk register to see them here</v>
+      </c>
+      <c r="B3555" t="str">
+        <v>اربط الضوابط من سجل المخاطر لرؤيتها هنا</v>
+      </c>
+      <c r="C3555" t="str">
+        <v>Saistiet kontroles no risku reģistra, lai tās redzētu šeit</v>
+      </c>
+    </row>
+    <row r="3556">
+      <c r="A3556" t="str">
+        <v>Link controls to track compliance</v>
+      </c>
+      <c r="B3556" t="str">
+        <v>اربط الضوابط لتتبع الامتثال</v>
+      </c>
+      <c r="C3556" t="str">
+        <v>Saistiet kontroles atbilstības izsekošanai</v>
+      </c>
+    </row>
+    <row r="3557">
+      <c r="A3557" t="str">
+        <v>No controls are currently linked to this risk</v>
+      </c>
+      <c r="B3557" t="str">
+        <v>لا توجد ضوابط مرتبطة حالياً بهذه المخاطرة</v>
+      </c>
+      <c r="C3557" t="str">
+        <v>Pašlaik nav kontroles, kas saistītas ar šo risku</v>
+      </c>
+    </row>
+    <row r="3558">
+      <c r="A3558" t="str">
+        <v>No controls linked to this</v>
+      </c>
+      <c r="B3558" t="str">
+        <v>لا توجد ضوابط مرتبطة بهذا</v>
+      </c>
+      <c r="C3558" t="str">
+        <v>Nav saistītu kontroles</v>
+      </c>
+    </row>
+    <row r="3559">
+      <c r="A3559" t="str">
+        <v>No controls linked to this policy</v>
+      </c>
+      <c r="B3559" t="str">
+        <v>لا توجد ضوابط مرتبطة بهذه السياسة</v>
+      </c>
+      <c r="C3559" t="str">
+        <v>Nav kontroles, kas saistītas ar šo politiku</v>
+      </c>
+    </row>
+    <row r="3560">
+      <c r="A3560" t="str">
+        <v>No controls match your filters</v>
+      </c>
+      <c r="B3560" t="str">
+        <v>لا توجد ضوابط تطابق عوامل التصفية</v>
+      </c>
+      <c r="C3560" t="str">
+        <v>Neviena kontrole neatbilst filtriem</v>
+      </c>
+    </row>
+    <row r="3561">
+      <c r="A3561" t="str">
+        <v>No existing controls found</v>
+      </c>
+      <c r="B3561" t="str">
+        <v>لم يتم العثور على ضوابط حالية</v>
+      </c>
+      <c r="C3561" t="str">
+        <v>Nav atrastas esošas kontroles</v>
+      </c>
+    </row>
+    <row r="3562">
+      <c r="A3562" t="str">
+        <v>No planned controls found</v>
+      </c>
+      <c r="B3562" t="str">
+        <v>لم يتم العثور على ضوابط مخطط لها</v>
+      </c>
+      <c r="C3562" t="str">
+        <v>Nav atrastas plānotas kontroles</v>
+      </c>
+    </row>
+    <row r="3563">
+      <c r="A3563" t="str">
+        <v>No risks available</v>
+      </c>
+      <c r="B3563" t="str">
+        <v>لا تتوفر مخاطر</v>
+      </c>
+      <c r="C3563" t="str">
+        <v>Nav pieejamu risku</v>
+      </c>
+    </row>
+    <row r="3564">
+      <c r="A3564" t="str">
+        <v>High impact</v>
+      </c>
+      <c r="B3564" t="str">
+        <v>تأثير عالي</v>
+      </c>
+      <c r="C3564" t="str">
+        <v>Augsta ietekme</v>
+      </c>
+    </row>
+    <row r="3565">
+      <c r="A3565" t="str">
+        <v>Evidence Not Found</v>
+      </c>
+      <c r="B3565" t="str">
+        <v>لم يتم العثور على الدليل</v>
+      </c>
+      <c r="C3565" t="str">
+        <v>Pierādījums nav atrasts</v>
+      </c>
+    </row>
+    <row r="3566">
+      <c r="A3566" t="str">
+        <v>Evidence request with this title already exists</v>
+      </c>
+      <c r="B3566" t="str">
+        <v>طلب دليل بهذا العنوان موجود بالفعل</v>
+      </c>
+      <c r="C3566" t="str">
+        <v>Pierādījumu pieprasījums ar šo nosaukumu jau pastāv</v>
+      </c>
+    </row>
+    <row r="3567">
+      <c r="A3567" t="str">
+        <v>Governance document not found</v>
+      </c>
+      <c r="B3567" t="str">
+        <v>لم يتم العثور على مستند الحوكمة</v>
+      </c>
+      <c r="C3567" t="str">
+        <v>Pārvaldības dokuments nav atrasts</v>
+      </c>
+    </row>
+    <row r="3568">
+      <c r="A3568" t="str">
+        <v>Linked Evidence</v>
+      </c>
+      <c r="B3568" t="str">
+        <v>الأدلة المرتبطة</v>
+      </c>
+      <c r="C3568" t="str">
+        <v>Saistītie pierādījumi</v>
+      </c>
+    </row>
+    <row r="3569">
+      <c r="A3569" t="str">
+        <v>Linked Governance</v>
+      </c>
+      <c r="B3569" t="str">
+        <v>الحوكمة المرتبطة</v>
+      </c>
+      <c r="C3569" t="str">
+        <v>Saistītā pārvaldība</v>
+      </c>
+    </row>
+    <row r="3570">
+      <c r="A3570" t="str">
+        <v>Linked Risk</v>
+      </c>
+      <c r="B3570" t="str">
+        <v>المخاطر المرتبطة</v>
+      </c>
+      <c r="C3570" t="str">
+        <v>Saistītais risks</v>
+      </c>
+    </row>
+    <row r="3571">
+      <c r="A3571" t="str">
+        <v>Policy Reference</v>
+      </c>
+      <c r="B3571" t="str">
+        <v>مرجع السياسة</v>
+      </c>
+      <c r="C3571" t="str">
+        <v>Politikas atsauce</v>
+      </c>
+    </row>
+    <row r="3572">
+      <c r="A3572" t="str">
+        <v>Published Document</v>
+      </c>
+      <c r="B3572" t="str">
+        <v>المستند المنشور</v>
+      </c>
+      <c r="C3572" t="str">
+        <v>Publicētais dokuments</v>
+      </c>
+    </row>
+    <row r="3573">
+      <c r="A3573" t="str">
+        <v>Published On</v>
+      </c>
+      <c r="B3573" t="str">
+        <v>نُشر في</v>
+      </c>
+      <c r="C3573" t="str">
+        <v>Publicēts</v>
+      </c>
+    </row>
+    <row r="3574">
+      <c r="A3574" t="str">
+        <v>Generate Policy</v>
+      </c>
+      <c r="B3574" t="str">
+        <v>إنشاء سياسة</v>
+      </c>
+      <c r="C3574" t="str">
+        <v>Ģenerēt politiku</v>
+      </c>
+    </row>
+    <row r="3575">
+      <c r="A3575" t="str">
+        <v>The AI will use the selected template and linked controls to generate a comprehensive policy document.</v>
+      </c>
+      <c r="B3575" t="str">
+        <v>سيستخدم الذكاء الاصطناعي القالب المحدد والضوابط المرتبطة لإنشاء وثيقة سياسة شاملة.</v>
+      </c>
+      <c r="C3575" t="str">
+        <v>AI izmantos atlasīto veidni un saistītās kontroles, lai ģenerētu visaptverošu politikas dokumentu.</v>
+      </c>
+    </row>
+    <row r="3576">
+      <c r="A3576" t="str">
+        <v>Select Template</v>
+      </c>
+      <c r="B3576" t="str">
+        <v>اختر القالب</v>
+      </c>
+      <c r="C3576" t="str">
+        <v>Atlasīt veidni</v>
+      </c>
+    </row>
+    <row r="3577">
+      <c r="A3577" t="str">
+        <v>Or upload a new template</v>
+      </c>
+      <c r="B3577" t="str">
+        <v>أو ارفع قالباً جديداً</v>
+      </c>
+      <c r="C3577" t="str">
+        <v>Vai augšupielādējiet jaunu veidni</v>
+      </c>
+    </row>
+    <row r="3578">
+      <c r="A3578" t="str">
+        <v>Upload a .docx template below</v>
+      </c>
+      <c r="B3578" t="str">
+        <v>ارفع قالب .docx أدناه</v>
+      </c>
+      <c r="C3578" t="str">
+        <v>Augšupielādējiet .docx veidni zemāk</v>
+      </c>
+    </row>
+    <row r="3579">
+      <c r="A3579" t="str">
+        <v>No templates available</v>
+      </c>
+      <c r="B3579" t="str">
+        <v>لا تتوفر قوالب</v>
+      </c>
+      <c r="C3579" t="str">
+        <v>Nav pieejamu veidņu</v>
+      </c>
+    </row>
+    <row r="3580">
+      <c r="A3580" t="str">
+        <v>This will revert the status from Published to Approved. The document will need to be published again after any changes.</v>
+      </c>
+      <c r="B3580" t="str">
+        <v>سيؤدي هذا إلى إرجاع الحالة من منشور إلى معتمد. سيحتاج المستند إلى إعادة نشره بعد أي تغييرات.</v>
+      </c>
+      <c r="C3580" t="str">
+        <v>Tas atgriezīs statusu no Publicēts uz Apstiprināts. Dokuments būs jāpublicē atkārtoti pēc jebkādām izmaiņām.</v>
+      </c>
+    </row>
+    <row r="3581">
+      <c r="A3581" t="str">
+        <v>Drag and drop a file here, or</v>
+      </c>
+      <c r="B3581" t="str">
+        <v>اسحب وأسقط ملفاً هنا، أو</v>
+      </c>
+      <c r="C3581" t="str">
+        <v>Velciet un nometiet failu šeit, vai</v>
+      </c>
+    </row>
+    <row r="3582">
+      <c r="A3582" t="str">
+        <v>Drag and drop your file here, or</v>
+      </c>
+      <c r="B3582" t="str">
+        <v>اسحب وأسقط ملفك هنا، أو</v>
+      </c>
+      <c r="C3582" t="str">
+        <v>Velciet un nometiet savu failu šeit, vai</v>
+      </c>
+    </row>
+    <row r="3583">
+      <c r="A3583" t="str">
+        <v>Drop file here or click to upload</v>
+      </c>
+      <c r="B3583" t="str">
+        <v>أسقط الملف هنا أو انقر للرفع</v>
+      </c>
+      <c r="C3583" t="str">
+        <v>Nometiet failu šeit vai noklikšķiniet, lai augšupielādētu</v>
+      </c>
+    </row>
+    <row r="3584">
+      <c r="A3584" t="str">
+        <v>Existing Files</v>
+      </c>
+      <c r="B3584" t="str">
+        <v>الملفات الحالية</v>
+      </c>
+      <c r="C3584" t="str">
+        <v>Esošie faili</v>
+      </c>
+    </row>
+    <row r="3585">
+      <c r="A3585" t="str">
+        <v>Files to Upload</v>
+      </c>
+      <c r="B3585" t="str">
+        <v>ملفات للرفع</v>
+      </c>
+      <c r="C3585" t="str">
+        <v>Augšupielādējamie faili</v>
+      </c>
+    </row>
+    <row r="3586">
+      <c r="A3586" t="str">
+        <v>New Files to Upload</v>
+      </c>
+      <c r="B3586" t="str">
+        <v>ملفات جديدة للرفع</v>
+      </c>
+      <c r="C3586" t="str">
+        <v>Jauni augšupielādējamie faili</v>
+      </c>
+    </row>
+    <row r="3587">
+      <c r="A3587" t="str">
+        <v>Supported formats: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
+      </c>
+      <c r="B3587" t="str">
+        <v>التنسيقات المدعومة: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
+      </c>
+      <c r="C3587" t="str">
+        <v>Atbalstītie formāti: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
+      </c>
+    </row>
+    <row r="3588">
+      <c r="A3588" t="str">
+        <v>Upload a CSV or Excel file to import</v>
+      </c>
+      <c r="B3588" t="str">
+        <v>ارفع ملف CSV أو Excel للاستيراد</v>
+      </c>
+      <c r="C3588" t="str">
+        <v>Augšupielādējiet CSV vai Excel failu importēšanai</v>
+      </c>
+    </row>
+    <row r="3589">
+      <c r="A3589" t="str">
+        <v>Upload an Excel file (.xlsx) containing your framework requirements. You can download the sample template to see the required format.</v>
+      </c>
+      <c r="B3589" t="str">
+        <v>ارفع ملف Excel (.xlsx) يحتوي على متطلبات الإطار الخاص بك. يمكنك تنزيل القالب النموذجي لمعرفة التنسيق المطلوب.</v>
+      </c>
+      <c r="C3589" t="str">
+        <v>Augšupielādējiet Excel failu (.xlsx) ar ietvara prasībām. Varat lejupielādēt parauga veidni, lai redzētu nepieciešamo formātu.</v>
+      </c>
+    </row>
+    <row r="3590">
+      <c r="A3590" t="str">
+        <v>Upload documents to the vault first</v>
+      </c>
+      <c r="B3590" t="str">
+        <v>ارفع المستندات إلى الخزنة أولاً</v>
+      </c>
+      <c r="C3590" t="str">
+        <v>Vispirms augšupielādējiet dokumentus glabātuvē</v>
+      </c>
+    </row>
+    <row r="3591">
+      <c r="A3591" t="str">
+        <v>Upload or link documents to get started</v>
+      </c>
+      <c r="B3591" t="str">
+        <v>ارفع أو اربط المستندات للبدء</v>
+      </c>
+      <c r="C3591" t="str">
+        <v>Augšupielādējiet vai saistiet dokumentus, lai sāktu</v>
+      </c>
+    </row>
+    <row r="3592">
+      <c r="A3592" t="str">
+        <v>Uploaded by</v>
+      </c>
+      <c r="B3592" t="str">
+        <v>رُفع بواسطة</v>
+      </c>
+      <c r="C3592" t="str">
+        <v>Augšupielādēja</v>
+      </c>
+    </row>
+    <row r="3593">
+      <c r="A3593" t="str">
+        <v>Uploading document...</v>
+      </c>
+      <c r="B3593" t="str">
+        <v>جاري رفع المستند...</v>
+      </c>
+      <c r="C3593" t="str">
+        <v>Augšupielādē dokumentu...</v>
+      </c>
+    </row>
+    <row r="3594">
+      <c r="A3594" t="str">
+        <v>Delete existing file to link</v>
+      </c>
+      <c r="B3594" t="str">
+        <v>احذف الملف الحالي للربط</v>
+      </c>
+      <c r="C3594" t="str">
+        <v>Dzēsiet esošo failu, lai saistītu</v>
+      </c>
+    </row>
+    <row r="3595">
+      <c r="A3595" t="str">
+        <v>Delete existing file to upload new</v>
+      </c>
+      <c r="B3595" t="str">
+        <v>احذف الملف الحالي لرفع ملف جديد</v>
+      </c>
+      <c r="C3595" t="str">
+        <v>Dzēsiet esošo failu, lai augšupielādētu jaunu</v>
+      </c>
+    </row>
+    <row r="3596">
+      <c r="A3596" t="str">
+        <v>Delete existing file to use AI</v>
+      </c>
+      <c r="B3596" t="str">
+        <v>احذف الملف الحالي لاستخدام الذكاء الاصطناعي</v>
+      </c>
+      <c r="C3596" t="str">
+        <v>Dzēsiet esošo failu, lai izmantotu AI</v>
+      </c>
+    </row>
+    <row r="3597">
+      <c r="A3597" t="str">
+        <v>Template columns:</v>
+      </c>
+      <c r="B3597" t="str">
+        <v>أعمدة القالب:</v>
+      </c>
+      <c r="C3597" t="str">
+        <v>Veidnes kolonnas:</v>
+      </c>
+    </row>
+    <row r="3598">
+      <c r="A3598" t="str">
+        <v>Excel file is empty</v>
+      </c>
+      <c r="B3598" t="str">
+        <v>ملف Excel فارغ</v>
+      </c>
+      <c r="C3598" t="str">
+        <v>Excel fails ir tukšs</v>
+      </c>
+    </row>
+    <row r="3599">
+      <c r="A3599" t="str">
+        <v>Content-Disposition</v>
+      </c>
+      <c r="B3599" t="str">
+        <v>ترتيب المحتوى</v>
+      </c>
+      <c r="C3599" t="str">
+        <v>Satura izvietojums</v>
+      </c>
+    </row>
+    <row r="3600">
+      <c r="A3600" t="str">
+        <v>Connection Error</v>
+      </c>
+      <c r="B3600" t="str">
+        <v>خطأ في الاتصال</v>
+      </c>
+      <c r="C3600" t="str">
+        <v>Savienojuma kļūda</v>
+      </c>
+    </row>
+    <row r="3601">
+      <c r="A3601" t="str">
+        <v>Error Details</v>
+      </c>
+      <c r="B3601" t="str">
+        <v>تفاصيل الخطأ</v>
+      </c>
+      <c r="C3601" t="str">
+        <v>Kļūdas detaļas</v>
+      </c>
+    </row>
+    <row r="3602">
+      <c r="A3602" t="str">
+        <v>Error importing data. Please check the file format.</v>
+      </c>
+      <c r="B3602" t="str">
+        <v>خطأ في استيراد البيانات. يرجى التحقق من تنسيق الملف.</v>
+      </c>
+      <c r="C3602" t="str">
+        <v>Kļūda importējot datus. Lūdzu, pārbaudiet faila formātu.</v>
+      </c>
+    </row>
+    <row r="3603">
+      <c r="A3603" t="str">
+        <v>Error uploading file. Please try again.</v>
+      </c>
+      <c r="B3603" t="str">
+        <v>خطأ في رفع الملف. يرجى المحاولة مرة أخرى.</v>
+      </c>
+      <c r="C3603" t="str">
+        <v>Kļūda augšupielādējot failu. Lūdzu, mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="3604">
+      <c r="A3604" t="str">
+        <v>Exception not found</v>
+      </c>
+      <c r="B3604" t="str">
+        <v>لم يتم العثور على الاستثناء</v>
+      </c>
+      <c r="C3604" t="str">
+        <v>Izņēmums nav atrasts</v>
+      </c>
+    </row>
+    <row r="3605">
+      <c r="A3605" t="str">
+        <v>Failed to add department</v>
+      </c>
+      <c r="B3605" t="str">
+        <v>فشل في إضافة القسم</v>
+      </c>
+      <c r="C3605" t="str">
+        <v>Neizdevās pievienot nodaļu</v>
+      </c>
+    </row>
+    <row r="3606">
+      <c r="A3606" t="str">
+        <v>Failed to add item</v>
+      </c>
+      <c r="B3606" t="str">
+        <v>فشل في إضافة العنصر</v>
+      </c>
+      <c r="C3606" t="str">
+        <v>Neizdevās pievienot vienību</v>
+      </c>
+    </row>
+    <row r="3607">
+      <c r="A3607" t="str">
+        <v>Failed to approve BIA</v>
+      </c>
+      <c r="B3607" t="str">
+        <v>فشل في الموافقة على تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3607" t="str">
+        <v>Neizdevās apstiprināt BIA</v>
+      </c>
+    </row>
+    <row r="3608">
+      <c r="A3608" t="str">
+        <v>Failed to approve exception</v>
+      </c>
+      <c r="B3608" t="str">
+        <v>فشل في الموافقة على الاستثناء</v>
+      </c>
+      <c r="C3608" t="str">
+        <v>Neizdevās apstiprināt izņēmumu</v>
+      </c>
+    </row>
+    <row r="3609">
+      <c r="A3609" t="str">
+        <v>Failed to create control</v>
+      </c>
+      <c r="B3609" t="str">
+        <v>فشل في إنشاء الضابط</v>
+      </c>
+      <c r="C3609" t="str">
+        <v>Neizdevās izveidot kontroli</v>
+      </c>
+    </row>
+    <row r="3610">
+      <c r="A3610" t="str">
+        <v>Failed to create label</v>
+      </c>
+      <c r="B3610" t="str">
+        <v>فشل في إنشاء التسمية</v>
+      </c>
+      <c r="C3610" t="str">
+        <v>Neizdevās izveidot apzīmējumu</v>
+      </c>
+    </row>
+    <row r="3611">
+      <c r="A3611" t="str">
+        <v>Failed to create range</v>
+      </c>
+      <c r="B3611" t="str">
+        <v>فشل في إنشاء النطاق</v>
+      </c>
+      <c r="C3611" t="str">
+        <v>Neizdevās izveidot diapazonu</v>
+      </c>
+    </row>
+    <row r="3612">
+      <c r="A3612" t="str">
+        <v>Failed to create range. Please try again.</v>
+      </c>
+      <c r="B3612" t="str">
+        <v>فشل في إنشاء النطاق. يرجى المحاولة مرة أخرى.</v>
+      </c>
+      <c r="C3612" t="str">
+        <v>Neizdevās izveidot diapazonu. Lūdzu, mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="3613">
+      <c r="A3613" t="str">
+        <v>Failed to create rating</v>
+      </c>
+      <c r="B3613" t="str">
+        <v>فشل في إنشاء التقييم</v>
+      </c>
+      <c r="C3613" t="str">
+        <v>Neizdevās izveidot vērtējumu</v>
+      </c>
+    </row>
+    <row r="3614">
+      <c r="A3614" t="str">
+        <v>Failed to create user. Please try again.</v>
+      </c>
+      <c r="B3614" t="str">
+        <v>فشل في إنشاء المستخدم. يرجى المحاولة مرة أخرى.</v>
+      </c>
+      <c r="C3614" t="str">
+        <v>Neizdevās izveidot lietotāju. Lūdzu, mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="3615">
+      <c r="A3615" t="str">
+        <v>Failed to delete framework</v>
+      </c>
+      <c r="B3615" t="str">
+        <v>فشل في حذف الإطار</v>
+      </c>
+      <c r="C3615" t="str">
+        <v>Neizdevās dzēst ietvaru</v>
+      </c>
+    </row>
+    <row r="3616">
+      <c r="A3616" t="str">
+        <v>Failed to export audit logs</v>
+      </c>
+      <c r="B3616" t="str">
+        <v>فشل في تصدير سجلات التدقيق</v>
+      </c>
+      <c r="C3616" t="str">
+        <v>Neizdevās eksportēt audita žurnālus</v>
+      </c>
+    </row>
+    <row r="3617">
+      <c r="A3617" t="str">
+        <v>Failed to import controls</v>
+      </c>
+      <c r="B3617" t="str">
+        <v>فشل في استيراد الضوابط</v>
+      </c>
+      <c r="C3617" t="str">
+        <v>Neizdevās importēt kontroles</v>
+      </c>
+    </row>
+    <row r="3618">
+      <c r="A3618" t="str">
+        <v>Failed to import processes</v>
+      </c>
+      <c r="B3618" t="str">
+        <v>فشل في استيراد العمليات</v>
+      </c>
+      <c r="C3618" t="str">
+        <v>Neizdevās importēt procesus</v>
+      </c>
+    </row>
+    <row r="3619">
+      <c r="A3619" t="str">
+        <v>Failed to import requirements. Please check the file format.</v>
+      </c>
+      <c r="B3619" t="str">
+        <v>فشل في استيراد المتطلبات. يرجى التحقق من تنسيق الملف.</v>
+      </c>
+      <c r="C3619" t="str">
+        <v>Neizdevās importēt prasības. Lūdzu, pārbaudiet faila formātu.</v>
+      </c>
+    </row>
+    <row r="3620">
+      <c r="A3620" t="str">
+        <v>Failed to import requirements. Please try again.</v>
+      </c>
+      <c r="B3620" t="str">
+        <v>فشل في استيراد المتطلبات. يرجى المحاولة مرة أخرى.</v>
+      </c>
+      <c r="C3620" t="str">
+        <v>Neizdevās importēt prasības. Lūdzu, mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="3621">
+      <c r="A3621" t="str">
+        <v>Failed to import risks</v>
+      </c>
+      <c r="B3621" t="str">
+        <v>فشل في استيراد المخاطر</v>
+      </c>
+      <c r="C3621" t="str">
+        <v>Neizdevās importēt riskus</v>
+      </c>
+    </row>
+    <row r="3622">
+      <c r="A3622" t="str">
+        <v>Failed to load process data</v>
+      </c>
+      <c r="B3622" t="str">
+        <v>فشل في تحميل بيانات العملية</v>
+      </c>
+      <c r="C3622" t="str">
+        <v>Neizdevās ielādēt procesa datus</v>
+      </c>
+    </row>
+    <row r="3623">
+      <c r="A3623" t="str">
+        <v>Failed to load profile</v>
+      </c>
+      <c r="B3623" t="str">
+        <v>فشل في تحميل الملف الشخصي</v>
+      </c>
+      <c r="C3623" t="str">
+        <v>Neizdevās ielādēt profilu</v>
+      </c>
+    </row>
+    <row r="3624">
+      <c r="A3624" t="str">
+        <v>Failed to perform AI Review</v>
+      </c>
+      <c r="B3624" t="str">
+        <v>فشل في إجراء مراجعة الذكاء الاصطناعي</v>
+      </c>
+      <c r="C3624" t="str">
+        <v>Neizdevās veikt AI pārskatu</v>
+      </c>
+    </row>
+    <row r="3625">
+      <c r="A3625" t="str">
+        <v>Failed to resubmit exception</v>
+      </c>
+      <c r="B3625" t="str">
+        <v>فشل في إعادة تقديم الاستثناء</v>
+      </c>
+      <c r="C3625" t="str">
+        <v>Neizdevās atkārtoti iesniegt izņēmumu</v>
+      </c>
+    </row>
+    <row r="3626">
+      <c r="A3626" t="str">
+        <v>Failed to save BIA</v>
+      </c>
+      <c r="B3626" t="str">
+        <v>فشل في حفظ تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3626" t="str">
+        <v>Neizdevās saglabāt BIA</v>
+      </c>
+    </row>
+    <row r="3627">
+      <c r="A3627" t="str">
+        <v>Failed to save BIA data</v>
+      </c>
+      <c r="B3627" t="str">
+        <v>فشل في حفظ بيانات تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3627" t="str">
+        <v>Neizdevās saglabāt BIA datus</v>
+      </c>
+    </row>
+    <row r="3628">
+      <c r="A3628" t="str">
+        <v>Failed to save KPI configuration</v>
+      </c>
+      <c r="B3628" t="str">
+        <v>فشل في حفظ إعدادات مؤشرات الأداء</v>
+      </c>
+      <c r="C3628" t="str">
+        <v>Neizdevās saglabāt KPI konfigurāciju</v>
+      </c>
+    </row>
+    <row r="3629">
+      <c r="A3629" t="str">
+        <v>Failed to save SOA changes.</v>
+      </c>
+      <c r="B3629" t="str">
+        <v>فشل في حفظ تغييرات بيان التطبيق.</v>
+      </c>
+      <c r="C3629" t="str">
+        <v>Neizdevās saglabāt SOA izmaiņas.</v>
+      </c>
+    </row>
+    <row r="3630">
+      <c r="A3630" t="str">
+        <v>Failed to save framework</v>
+      </c>
+      <c r="B3630" t="str">
+        <v>فشل في حفظ الإطار</v>
+      </c>
+      <c r="C3630" t="str">
+        <v>Neizdevās saglabāt ietvaru</v>
+      </c>
+    </row>
+    <row r="3631">
+      <c r="A3631" t="str">
+        <v>Failed to save profile</v>
+      </c>
+      <c r="B3631" t="str">
+        <v>فشل في حفظ الملف الشخصي</v>
+      </c>
+      <c r="C3631" t="str">
+        <v>Neizdevās saglabāt profilu</v>
+      </c>
+    </row>
+    <row r="3632">
+      <c r="A3632" t="str">
+        <v>Failed to send back BIA</v>
+      </c>
+      <c r="B3632" t="str">
+        <v>فشل في إرجاع تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3632" t="str">
+        <v>Neizdevās nosūtīt atpakaļ BIA</v>
+      </c>
+    </row>
+    <row r="3633">
+      <c r="A3633" t="str">
+        <v>Failed to send back exception</v>
+      </c>
+      <c r="B3633" t="str">
+        <v>فشل في إرجاع الاستثناء</v>
+      </c>
+      <c r="C3633" t="str">
+        <v>Neizdevās nosūtīt atpakaļ izņēmumu</v>
+      </c>
+    </row>
+    <row r="3634">
+      <c r="A3634" t="str">
+        <v>Failed to submit BIA</v>
+      </c>
+      <c r="B3634" t="str">
+        <v>فشل في تقديم تحليل تأثير الأعمال</v>
+      </c>
+      <c r="C3634" t="str">
+        <v>Neizdevās iesniegt BIA</v>
+      </c>
+    </row>
+    <row r="3635">
+      <c r="A3635" t="str">
+        <v>Failed to submit BIA for approval</v>
+      </c>
+      <c r="B3635" t="str">
+        <v>فشل في تقديم تحليل تأثير الأعمال للموافقة</v>
+      </c>
+      <c r="C3635" t="str">
+        <v>Neizdevās iesniegt BIA apstiprināšanai</v>
+      </c>
+    </row>
+    <row r="3636">
+      <c r="A3636" t="str">
+        <v>Failed to update department</v>
+      </c>
+      <c r="B3636" t="str">
+        <v>فشل في تحديث القسم</v>
+      </c>
+      <c r="C3636" t="str">
+        <v>Neizdevās atjaunināt nodaļu</v>
+      </c>
+    </row>
+    <row r="3637">
+      <c r="A3637" t="str">
+        <v>Failed to update email notifications setting</v>
+      </c>
+      <c r="B3637" t="str">
+        <v>فشل في تحديث إعدادات إشعارات البريد الإلكتروني</v>
+      </c>
+      <c r="C3637" t="str">
+        <v>Neizdevās atjaunināt e-pasta paziņojumu iestatījumus</v>
+      </c>
+    </row>
+    <row r="3638">
+      <c r="A3638" t="str">
+        <v>Failed to update item</v>
+      </c>
+      <c r="B3638" t="str">
+        <v>فشل في تحديث العنصر</v>
+      </c>
+      <c r="C3638" t="str">
+        <v>Neizdevās atjaunināt vienību</v>
+      </c>
+    </row>
+    <row r="3639">
+      <c r="A3639" t="str">
+        <v>Failed to update label</v>
+      </c>
+      <c r="B3639" t="str">
+        <v>فشل في تحديث التسمية</v>
+      </c>
+      <c r="C3639" t="str">
+        <v>Neizdevās atjaunināt apzīmējumu</v>
+      </c>
+    </row>
+    <row r="3640">
+      <c r="A3640" t="str">
+        <v>Failed to update profile</v>
+      </c>
+      <c r="B3640" t="str">
+        <v>فشل في تحديث الملف الشخصي</v>
+      </c>
+      <c r="C3640" t="str">
+        <v>Neizdevās atjaunināt profilu</v>
+      </c>
+    </row>
+    <row r="3641">
+      <c r="A3641" t="str">
+        <v>Failed to update range</v>
+      </c>
+      <c r="B3641" t="str">
+        <v>فشل في تحديث النطاق</v>
+      </c>
+      <c r="C3641" t="str">
+        <v>Neizdevās atjaunināt diapazonu</v>
+      </c>
+    </row>
+    <row r="3642">
+      <c r="A3642" t="str">
+        <v>Failed to update range. Please try again.</v>
+      </c>
+      <c r="B3642" t="str">
+        <v>فشل في تحديث النطاق. يرجى المحاولة مرة أخرى.</v>
+      </c>
+      <c r="C3642" t="str">
+        <v>Neizdevās atjaunināt diapazonu. Lūdzu, mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="3643">
+      <c r="A3643" t="str">
+        <v>Failed to update rating</v>
+      </c>
+      <c r="B3643" t="str">
+        <v>فشل في تحديث التقييم</v>
+      </c>
+      <c r="C3643" t="str">
+        <v>Neizdevās atjaunināt vērtējumu</v>
+      </c>
+    </row>
+    <row r="3644">
+      <c r="A3644" t="str">
+        <v>Failed to update user</v>
+      </c>
+      <c r="B3644" t="str">
+        <v>فشل في تحديث المستخدم</v>
+      </c>
+      <c r="C3644" t="str">
+        <v>Neizdevās atjaunināt lietotāju</v>
+      </c>
+    </row>
+    <row r="3645">
+      <c r="A3645" t="str">
+        <v>Failed to upload artifact</v>
+      </c>
+      <c r="B3645" t="str">
+        <v>فشل في رفع القطعة</v>
+      </c>
+      <c r="C3645" t="str">
+        <v>Neizdevās augšupielādēt artefaktu</v>
+      </c>
+    </row>
+    <row r="3646">
+      <c r="A3646" t="str">
+        <v>Network error: Failed to respond</v>
+      </c>
+      <c r="B3646" t="str">
+        <v>خطأ في الشبكة: فشل في الاستجابة</v>
+      </c>
+      <c r="C3646" t="str">
+        <v>Tīkla kļūda: neizdevās atbildēt</v>
+      </c>
+    </row>
+    <row r="3647">
+      <c r="A3647" t="str">
+        <v>Operation Failed</v>
+      </c>
+      <c r="B3647" t="str">
+        <v>فشلت العملية</v>
+      </c>
+      <c r="C3647" t="str">
+        <v>Darbība neizdevās</v>
+      </c>
+    </row>
+    <row r="3648">
+      <c r="A3648" t="str">
+        <v>Unable to reach the AI service. Please check your connection and try again.</v>
+      </c>
+      <c r="B3648" t="str">
+        <v>يتعذر الوصول إلى خدمة الذكاء الاصطناعي. يرجى التحقق من اتصالك والمحاولة مرة أخرى.</v>
+      </c>
+      <c r="C3648" t="str">
+        <v>Nevar sasniegt AI pakalpojumu. Lūdzu, pārbaudiet savienojumu un mēģiniet vēlreiz.</v>
+      </c>
+    </row>
+    <row r="3649">
+      <c r="A3649" t="str">
+        <v>Are you sure you want to delete all</v>
+      </c>
+      <c r="B3649" t="str">
+        <v>هل أنت متأكد من حذف الكل</v>
+      </c>
+      <c r="C3649" t="str">
+        <v>Vai tiešām vēlaties dzēst visu</v>
+      </c>
+    </row>
+    <row r="3650">
+      <c r="A3650" t="str">
+        <v>Are you sure you want to delete this category? This action cannot be undone.</v>
+      </c>
+      <c r="B3650" t="str">
+        <v>هل أنت متأكد من حذف هذه الفئة؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C3650" t="str">
+        <v>Vai tiešām vēlaties dzēst šo kategoriju? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="3651">
+      <c r="A3651" t="str">
+        <v>Are you sure you want to delete this exception? This action cannot be undone.</v>
+      </c>
+      <c r="B3651" t="str">
+        <v>هل أنت متأكد من حذف هذا الاستثناء؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C3651" t="str">
+        <v>Vai tiešām vēlaties dzēst šo izņēmumu? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="3652">
+      <c r="A3652" t="str">
+        <v>Are you sure you want to delete this framework? This action cannot be undone.</v>
+      </c>
+      <c r="B3652" t="str">
+        <v>هل أنت متأكد من حذف هذا الإطار؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C3652" t="str">
+        <v>Vai tiešām vēlaties dzēst šo ietvaru? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="3653">
+      <c r="A3653" t="str">
+        <v>Are you sure you want to delete this label? This action cannot be undone.</v>
+      </c>
+      <c r="B3653" t="str">
+        <v>هل أنت متأكد من حذف هذه التسمية؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C3653" t="str">
+        <v>Vai tiešām vēlaties dzēst šo apzīmējumu? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="3654">
+      <c r="A3654" t="str">
+        <v>Are you sure you want to delete this scoring range? This action cannot be undone.</v>
+      </c>
+      <c r="B3654" t="str">
+        <v>هل أنت متأكد من حذف نطاق التقييم هذا؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C3654" t="str">
+        <v>Vai tiešām vēlaties dzēst šo vērtēšanas diapazonu? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="3655">
+      <c r="A3655" t="str">
+        <v>Allocated</v>
+      </c>
+      <c r="B3655" t="str">
+        <v>مخصص</v>
+      </c>
+      <c r="C3655" t="str">
+        <v>Piešķirts</v>
+      </c>
+    </row>
+    <row r="3656">
+      <c r="A3656" t="str">
+        <v>Already Linked</v>
+      </c>
+      <c r="B3656" t="str">
+        <v>مرتبط بالفعل</v>
+      </c>
+      <c r="C3656" t="str">
+        <v>Jau saistīts</v>
+      </c>
+    </row>
+    <row r="3657">
+      <c r="A3657" t="str">
+        <v>Answer</v>
+      </c>
+      <c r="B3657" t="str">
+        <v>إجابة</v>
+      </c>
+      <c r="C3657" t="str">
+        <v>Atbilde</v>
+      </c>
+    </row>
+    <row r="3658">
+      <c r="A3658" t="str">
+        <v>Approval Information</v>
+      </c>
+      <c r="B3658" t="str">
+        <v>معلومات الموافقة</v>
+      </c>
+      <c r="C3658" t="str">
+        <v>Apstiprinājuma informācija</v>
+      </c>
+    </row>
+    <row r="3659">
+      <c r="A3659" t="str">
+        <v>Approved By</v>
+      </c>
+      <c r="B3659" t="str">
+        <v>تمت الموافقة بواسطة</v>
+      </c>
+      <c r="C3659" t="str">
+        <v>Apstiprināja</v>
+      </c>
+    </row>
+    <row r="3660">
+      <c r="A3660" t="str">
+        <v>Approved Date</v>
+      </c>
+      <c r="B3660" t="str">
+        <v>تاريخ الموافقة</v>
+      </c>
+      <c r="C3660" t="str">
+        <v>Apstiprināšanas datums</v>
+      </c>
+    </row>
+    <row r="3661">
+      <c r="A3661" t="str">
+        <v>Approved by</v>
+      </c>
+      <c r="B3661" t="str">
+        <v>تمت الموافقة بواسطة</v>
+      </c>
+      <c r="C3661" t="str">
+        <v>Apstiprināja</v>
+      </c>
+    </row>
+    <row r="3662">
+      <c r="A3662" t="str">
+        <v>Archived</v>
+      </c>
+      <c r="B3662" t="str">
+        <v>مؤرشف</v>
+      </c>
+      <c r="C3662" t="str">
+        <v>Arhivēts</v>
+      </c>
+    </row>
+    <row r="3663">
+      <c r="A3663" t="str">
+        <v>Assessment Date</v>
+      </c>
+      <c r="B3663" t="str">
+        <v>تاريخ التقييم</v>
+      </c>
+      <c r="C3663" t="str">
+        <v>Novērtēšanas datums</v>
+      </c>
+    </row>
+    <row r="3664">
+      <c r="A3664" t="str">
+        <v>Checking status...</v>
+      </c>
+      <c r="B3664" t="str">
+        <v>جاري التحقق من الحالة...</v>
+      </c>
+      <c r="C3664" t="str">
+        <v>Pārbauda statusu...</v>
+      </c>
+    </row>
+    <row r="3665">
+      <c r="A3665" t="str">
+        <v>Clear Filters</v>
+      </c>
+      <c r="B3665" t="str">
+        <v>مسح عوامل التصفية</v>
+      </c>
+      <c r="C3665" t="str">
+        <v>Notīrīt filtrus</v>
+      </c>
+    </row>
+    <row r="3666">
+      <c r="A3666" t="str">
+        <v>Clear Signature</v>
+      </c>
+      <c r="B3666" t="str">
+        <v>مسح التوقيع</v>
+      </c>
+      <c r="C3666" t="str">
+        <v>Notīrīt parakstu</v>
+      </c>
+    </row>
+    <row r="3667">
+      <c r="A3667" t="str">
+        <v>Created By</v>
+      </c>
+      <c r="B3667" t="str">
+        <v>أنشئ بواسطة</v>
+      </c>
+      <c r="C3667" t="str">
+        <v>Izveidoja</v>
+      </c>
+    </row>
+    <row r="3668">
+      <c r="A3668" t="str">
+        <v>Days Remaining</v>
+      </c>
+      <c r="B3668" t="str">
+        <v>الأيام المتبقية</v>
+      </c>
+      <c r="C3668" t="str">
+        <v>Atlikušās dienas</v>
+      </c>
+    </row>
+    <row r="3669">
+      <c r="A3669" t="str">
+        <v>Description is required</v>
+      </c>
+      <c r="B3669" t="str">
+        <v>الوصف مطلوب</v>
+      </c>
+      <c r="C3669" t="str">
+        <v>Apraksts ir obligāts</v>
+      </c>
+    </row>
+    <row r="3670">
+      <c r="A3670" t="str">
+        <v>Draw your signature above</v>
+      </c>
+      <c r="B3670" t="str">
+        <v>ارسم توقيعك أعلاه</v>
+      </c>
+      <c r="C3670" t="str">
+        <v>Zīmējiet savu parakstu augstāk</v>
+      </c>
+    </row>
+    <row r="3671">
+      <c r="A3671" t="str">
+        <v>Edit KPI Record</v>
+      </c>
+      <c r="B3671" t="str">
+        <v>تعديل سجل مؤشر الأداء</v>
+      </c>
+      <c r="C3671" t="str">
+        <v>Rediģēt KPI ierakstu</v>
+      </c>
+    </row>
+    <row r="3672">
+      <c r="A3672" t="str">
+        <v>Effective Date</v>
+      </c>
+      <c r="B3672" t="str">
+        <v>تاريخ السريان</v>
+      </c>
+      <c r="C3672" t="str">
+        <v>Spēkā stāšanās datums</v>
+      </c>
+    </row>
+    <row r="3673">
+      <c r="A3673" t="str">
+        <v>Email notifications disabled</v>
+      </c>
+      <c r="B3673" t="str">
+        <v>إشعارات البريد الإلكتروني معطلة</v>
+      </c>
+      <c r="C3673" t="str">
+        <v>E-pasta paziņojumi atspējoti</v>
+      </c>
+    </row>
+    <row r="3674">
+      <c r="A3674" t="str">
+        <v>Email notifications enabled</v>
+      </c>
+      <c r="B3674" t="str">
+        <v>إشعارات البريد الإلكتروني مفعلة</v>
+      </c>
+      <c r="C3674" t="str">
+        <v>E-pasta paziņojumi iespējoti</v>
+      </c>
+    </row>
+    <row r="3675">
+      <c r="A3675" t="str">
+        <v>End date is required</v>
+      </c>
+      <c r="B3675" t="str">
+        <v>تاريخ الانتهاء مطلوب</v>
+      </c>
+      <c r="C3675" t="str">
+        <v>Beigu datums ir obligāts</v>
+      </c>
+    </row>
+    <row r="3676">
+      <c r="A3676" t="str">
+        <v>Enter description or justification</v>
+      </c>
+      <c r="B3676" t="str">
+        <v>أدخل الوصف أو المبرر</v>
+      </c>
+      <c r="C3676" t="str">
+        <v>Ievadiet aprakstu vai pamatojumu</v>
+      </c>
+    </row>
+    <row r="3677">
+      <c r="A3677" t="str">
+        <v>Enter justification</v>
+      </c>
+      <c r="B3677" t="str">
+        <v>أدخل المبرر</v>
+      </c>
+      <c r="C3677" t="str">
+        <v>Ievadiet pamatojumu</v>
+      </c>
+    </row>
+    <row r="3678">
+      <c r="A3678" t="str">
+        <v>Enter reason for sending back...</v>
+      </c>
+      <c r="B3678" t="str">
+        <v>أدخل سبب الإرجاع...</v>
+      </c>
+      <c r="C3678" t="str">
+        <v>Ievadiet atpakaļnosūtīšanas iemeslu...</v>
+      </c>
+    </row>
+    <row r="3679">
+      <c r="A3679" t="str">
+        <v>Filters</v>
+      </c>
+      <c r="B3679" t="str">
+        <v>عوامل التصفية</v>
+      </c>
+      <c r="C3679" t="str">
+        <v>Filtri</v>
+      </c>
+    </row>
+    <row r="3680">
+      <c r="A3680" t="str">
+        <v>Half-Yearly</v>
+      </c>
+      <c r="B3680" t="str">
+        <v>نصف سنوي</v>
+      </c>
+      <c r="C3680" t="str">
+        <v>Pusgada</v>
+      </c>
+    </row>
+    <row r="3681">
+      <c r="A3681" t="str">
+        <v>KPI Recurrence</v>
+      </c>
+      <c r="B3681" t="str">
+        <v>تكرار مؤشرات الأداء</v>
+      </c>
+      <c r="C3681" t="str">
+        <v>KPI periodiskums</v>
+      </c>
+    </row>
+    <row r="3682">
+      <c r="A3682" t="str">
+        <v>Label Name</v>
+      </c>
+      <c r="B3682" t="str">
+        <v>اسم التسمية</v>
+      </c>
+      <c r="C3682" t="str">
+        <v>Apzīmējuma nosaukums</v>
+      </c>
+    </row>
+    <row r="3683">
+      <c r="A3683" t="str">
+        <v>Link Artifact</v>
+      </c>
+      <c r="B3683" t="str">
+        <v>ربط القطعة</v>
+      </c>
+      <c r="C3683" t="str">
+        <v>Saistīt artefaktu</v>
+      </c>
+    </row>
+    <row r="3684">
+      <c r="A3684" t="str">
+        <v>Linked from Vault</v>
+      </c>
+      <c r="B3684" t="str">
+        <v>مرتبط من الخزنة</v>
+      </c>
+      <c r="C3684" t="str">
+        <v>Saistīts no glabātuves</v>
+      </c>
+    </row>
+    <row r="3685">
+      <c r="A3685" t="str">
+        <v>No Data</v>
+      </c>
+      <c r="B3685" t="str">
+        <v>لا توجد بيانات</v>
+      </c>
+      <c r="C3685" t="str">
+        <v>Nav datu</v>
+      </c>
+    </row>
+    <row r="3686">
+      <c r="A3686" t="str">
+        <v>No Framework</v>
+      </c>
+      <c r="B3686" t="str">
+        <v>لا يوجد إطار</v>
+      </c>
+      <c r="C3686" t="str">
+        <v>Nav ietvara</v>
+      </c>
+    </row>
+    <row r="3687">
+      <c r="A3687" t="str">
+        <v>No Risks Found</v>
+      </c>
+      <c r="B3687" t="str">
+        <v>لم يتم العثور على مخاطر</v>
+      </c>
+      <c r="C3687" t="str">
+        <v>Riski nav atrasti</v>
+      </c>
+    </row>
+    <row r="3688">
+      <c r="A3688" t="str">
+        <v>No Users</v>
+      </c>
+      <c r="B3688" t="str">
+        <v>لا يوجد مستخدمون</v>
+      </c>
+      <c r="C3688" t="str">
+        <v>Nav lietotāju</v>
+      </c>
+    </row>
+    <row r="3689">
+      <c r="A3689" t="str">
+        <v>No changes</v>
+      </c>
+      <c r="B3689" t="str">
+        <v>لا توجد تغييرات</v>
+      </c>
+      <c r="C3689" t="str">
+        <v>Nav izmaiņu</v>
+      </c>
+    </row>
+    <row r="3690">
+      <c r="A3690" t="str">
+        <v>No changes to save.</v>
+      </c>
+      <c r="B3690" t="str">
+        <v>لا توجد تغييرات للحفظ.</v>
+      </c>
+      <c r="C3690" t="str">
+        <v>Nav izmaiņu, ko saglabāt.</v>
+      </c>
+    </row>
+    <row r="3691">
+      <c r="A3691" t="str">
+        <v>No description provided</v>
+      </c>
+      <c r="B3691" t="str">
+        <v>لم يتم تقديم وصف</v>
+      </c>
+      <c r="C3691" t="str">
+        <v>Apraksts nav norādīts</v>
+      </c>
+    </row>
+    <row r="3692">
+      <c r="A3692" t="str">
+        <v>No detailed review data available</v>
+      </c>
+      <c r="B3692" t="str">
+        <v>لا تتوفر بيانات مراجعة تفصيلية</v>
+      </c>
+      <c r="C3692" t="str">
+        <v>Nav pieejami detalizēti pārskata dati</v>
+      </c>
+    </row>
+    <row r="3693">
+      <c r="A3693" t="str">
+        <v>No document attached</v>
+      </c>
+      <c r="B3693" t="str">
+        <v>لم يتم إرفاق مستند</v>
+      </c>
+      <c r="C3693" t="str">
+        <v>Dokuments nav pievienots</v>
+      </c>
+    </row>
+    <row r="3694">
+      <c r="A3694" t="str">
+        <v>No documents found in vault</v>
+      </c>
+      <c r="B3694" t="str">
+        <v>لم يتم العثور على مستندات في الخزنة</v>
+      </c>
+      <c r="C3694" t="str">
+        <v>Glabātuvē nav atrasti dokumenti</v>
+      </c>
+    </row>
+    <row r="3695">
+      <c r="A3695" t="str">
+        <v>No limit</v>
+      </c>
+      <c r="B3695" t="str">
+        <v>بلا حدود</v>
+      </c>
+      <c r="C3695" t="str">
+        <v>Nav ierobežojuma</v>
+      </c>
+    </row>
+    <row r="3696">
+      <c r="A3696" t="str">
+        <v>No processes to export</v>
+      </c>
+      <c r="B3696" t="str">
+        <v>لا توجد عمليات للتصدير</v>
+      </c>
+      <c r="C3696" t="str">
+        <v>Nav procesu eksportēšanai</v>
+      </c>
+    </row>
+    <row r="3697">
+      <c r="A3697" t="str">
+        <v>No processes were imported</v>
+      </c>
+      <c r="B3697" t="str">
+        <v>لم يتم استيراد أي عمليات</v>
+      </c>
+      <c r="C3697" t="str">
+        <v>Neviens process netika importēts</v>
+      </c>
+    </row>
+    <row r="3698">
+      <c r="A3698" t="str">
+        <v>Not Found</v>
+      </c>
+      <c r="B3698" t="str">
+        <v>غير موجود</v>
+      </c>
+      <c r="C3698" t="str">
+        <v>Nav atrasts</v>
+      </c>
+    </row>
+    <row r="3699">
+      <c r="A3699" t="str">
+        <v>Not Set</v>
+      </c>
+      <c r="B3699" t="str">
+        <v>غير محدد</v>
+      </c>
+      <c r="C3699" t="str">
+        <v>Nav iestatīts</v>
+      </c>
+    </row>
+    <row r="3700">
+      <c r="A3700" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="B3700" t="str">
+        <v>مستمر</v>
+      </c>
+      <c r="C3700" t="str">
+        <v>Notiekošs</v>
+      </c>
+    </row>
+    <row r="3701">
+      <c r="A3701" t="str">
+        <v>Only letters, numbers, spaces, hyphens, and colons are allowed</v>
+      </c>
+      <c r="B3701" t="str">
+        <v>يُسمح فقط بالأحرف والأرقام والمسافات والشرطات والنقطتين</v>
+      </c>
+      <c r="C3701" t="str">
+        <v>Atļauti tikai burti, cipari, atstarpes, defises un koli</v>
+      </c>
+    </row>
+    <row r="3702">
+      <c r="A3702" t="str">
+        <v>Please Select the Function</v>
+      </c>
+      <c r="B3702" t="str">
+        <v>يرجى اختيار الوظيفة</v>
+      </c>
+      <c r="C3702" t="str">
+        <v>Lūdzu, atlasiet funkciju</v>
+      </c>
+    </row>
+    <row r="3703">
+      <c r="A3703" t="str">
+        <v>Please enter the Process Name</v>
+      </c>
+      <c r="B3703" t="str">
+        <v>يرجى إدخال اسم العملية</v>
+      </c>
+      <c r="C3703" t="str">
+        <v>Lūdzu, ievadiet procesa nosaukumu</v>
+      </c>
+    </row>
+    <row r="3704">
+      <c r="A3704" t="str">
+        <v>Please provide a comment explaining the changes made before resubmitting for approval.</v>
+      </c>
+      <c r="B3704" t="str">
+        <v>يرجى تقديم تعليق يوضح التغييرات التي تم إجراؤها قبل إعادة التقديم للموافقة.</v>
+      </c>
+      <c r="C3704" t="str">
+        <v>Lūdzu, norādiet komentāru, kas paskaidro veiktās izmaiņas pirms atkārtotas iesniegšanas apstiprināšanai.</v>
+      </c>
+    </row>
+    <row r="3705">
+      <c r="A3705" t="str">
+        <v>Please provide a reason for sending back this exception request.</v>
+      </c>
+      <c r="B3705" t="str">
+        <v>يرجى تقديم سبب لإرجاع طلب الاستثناء هذا.</v>
+      </c>
+      <c r="C3705" t="str">
+        <v>Lūdzu, norādiet iemeslu šī izņēmuma pieprasījuma atpakaļnosūtīšanai.</v>
+      </c>
+    </row>
+    <row r="3706">
+      <c r="A3706" t="str">
+        <v>Please select an approver</v>
+      </c>
+      <c r="B3706" t="str">
+        <v>يرجى اختيار مُعتمد</v>
+      </c>
+      <c r="C3706" t="str">
+        <v>Lūdzu, atlasiet apstiprinātāju</v>
+      </c>
+    </row>
+    <row r="3707">
+      <c r="A3707" t="str">
+        <v>Please select service user</v>
+      </c>
+      <c r="B3707" t="str">
+        <v>يرجى اختيار مستخدم الخدمة</v>
+      </c>
+      <c r="C3707" t="str">
+        <v>Lūdzu, atlasiet pakalpojuma lietotāju</v>
+      </c>
+    </row>
+    <row r="3708">
+      <c r="A3708" t="str">
+        <v>Please select the service title</v>
+      </c>
+      <c r="B3708" t="str">
+        <v>يرجى اختيار عنوان الخدمة</v>
+      </c>
+      <c r="C3708" t="str">
+        <v>Lūdzu, atlasiet pakalpojuma nosaukumu</v>
+      </c>
+    </row>
+    <row r="3709">
+      <c r="A3709" t="str">
+        <v>Please sign below to publish this</v>
+      </c>
+      <c r="B3709" t="str">
+        <v>يرجى التوقيع أدناه لنشر هذا</v>
+      </c>
+      <c r="C3709" t="str">
+        <v>Lūdzu, parakstieties zemāk, lai publicētu šo</v>
+      </c>
+    </row>
+    <row r="3710">
+      <c r="A3710" t="str">
+        <v>Processing document...</v>
+      </c>
+      <c r="B3710" t="str">
+        <v>جاري معالجة المستند...</v>
+      </c>
+      <c r="C3710" t="str">
+        <v>Apstrādā dokumentu...</v>
+      </c>
+    </row>
+    <row r="3711">
+      <c r="A3711" t="str">
+        <v>Processing...</v>
+      </c>
+      <c r="B3711" t="str">
+        <v>جاري المعالجة...</v>
+      </c>
+      <c r="C3711" t="str">
+        <v>Apstrādā...</v>
+      </c>
+    </row>
+    <row r="3712">
+      <c r="A3712" t="str">
+        <v>Question</v>
+      </c>
+      <c r="B3712" t="str">
+        <v>سؤال</v>
+      </c>
+      <c r="C3712" t="str">
+        <v>Jautājums</v>
+      </c>
+    </row>
+    <row r="3713">
+      <c r="A3713" t="str">
+        <v>Queued for processing...</v>
+      </c>
+      <c r="B3713" t="str">
+        <v>في قائمة الانتظار للمعالجة...</v>
+      </c>
+      <c r="C3713" t="str">
+        <v>Ierindots apstrādei...</v>
+      </c>
+    </row>
+    <row r="3714">
+      <c r="A3714" t="str">
+        <v>Remaining</v>
+      </c>
+      <c r="B3714" t="str">
+        <v>المتبقي</v>
+      </c>
+      <c r="C3714" t="str">
+        <v>Atlicis</v>
+      </c>
+    </row>
+    <row r="3715">
+      <c r="A3715" t="str">
+        <v>Report Not Found</v>
+      </c>
+      <c r="B3715" t="str">
+        <v>لم يتم العثور على التقرير</v>
+      </c>
+      <c r="C3715" t="str">
+        <v>Atskaite nav atrasta</v>
+      </c>
+    </row>
+    <row r="3716">
+      <c r="A3716" t="str">
+        <v>Saved</v>
+      </c>
+      <c r="B3716" t="str">
+        <v>تم الحفظ</v>
+      </c>
+      <c r="C3716" t="str">
+        <v>Saglabāts</v>
+      </c>
+    </row>
+    <row r="3717">
+      <c r="A3717" t="str">
+        <v>Search audit logs...</v>
+      </c>
+      <c r="B3717" t="str">
+        <v>بحث في سجلات التدقيق...</v>
+      </c>
+      <c r="C3717" t="str">
+        <v>Meklēt audita žurnālos...</v>
+      </c>
+    </row>
+    <row r="3718">
+      <c r="A3718" t="str">
+        <v>Search by requirement code, name, control code...</v>
+      </c>
+      <c r="B3718" t="str">
+        <v>بحث حسب رمز المتطلب، الاسم، رمز الضابط...</v>
+      </c>
+      <c r="C3718" t="str">
+        <v>Meklēt pēc prasības koda, nosaukuma, kontroles koda...</v>
+      </c>
+    </row>
+    <row r="3719">
+      <c r="A3719" t="str">
+        <v>Search documents...</v>
+      </c>
+      <c r="B3719" t="str">
+        <v>بحث في المستندات...</v>
+      </c>
+      <c r="C3719" t="str">
+        <v>Meklēt dokumentos...</v>
+      </c>
+    </row>
+    <row r="3720">
+      <c r="A3720" t="str">
+        <v>Search labels...</v>
+      </c>
+      <c r="B3720" t="str">
+        <v>بحث في التسميات...</v>
+      </c>
+      <c r="C3720" t="str">
+        <v>Meklēt apzīmējumos...</v>
+      </c>
+    </row>
+    <row r="3721">
+      <c r="A3721" t="str">
+        <v>Search records...</v>
+      </c>
+      <c r="B3721" t="str">
+        <v>بحث في السجلات...</v>
+      </c>
+      <c r="C3721" t="str">
+        <v>Meklēt ierakstos...</v>
+      </c>
+    </row>
+    <row r="3722">
+      <c r="A3722" t="str">
+        <v>Select Department First</v>
+      </c>
+      <c r="B3722" t="str">
+        <v>اختر القسم أولاً</v>
+      </c>
+      <c r="C3722" t="str">
+        <v>Vispirms atlasiet nodaļu</v>
+      </c>
+    </row>
+    <row r="3723">
+      <c r="A3723" t="str">
+        <v>Select Exception</v>
+      </c>
+      <c r="B3723" t="str">
+        <v>اختر الاستثناء</v>
+      </c>
+      <c r="C3723" t="str">
+        <v>Atlasīt izņēmumu</v>
+      </c>
+    </row>
+    <row r="3724">
+      <c r="A3724" t="str">
+        <v>Select Frequency</v>
+      </c>
+      <c r="B3724" t="str">
+        <v>اختر التكرار</v>
+      </c>
+      <c r="C3724" t="str">
+        <v>Atlasīt biežumu</v>
+      </c>
+    </row>
+    <row r="3725">
+      <c r="A3725" t="str">
+        <v>Select Nature</v>
+      </c>
+      <c r="B3725" t="str">
+        <v>اختر الطبيعة</v>
+      </c>
+      <c r="C3725" t="str">
+        <v>Atlasīt veidu</v>
+      </c>
+    </row>
+    <row r="3726">
+      <c r="A3726" t="str">
+        <v>Select Process Type</v>
+      </c>
+      <c r="B3726" t="str">
+        <v>اختر نوع العملية</v>
+      </c>
+      <c r="C3726" t="str">
+        <v>Atlasīt procesa tipu</v>
+      </c>
+    </row>
+    <row r="3727">
+      <c r="A3727" t="str">
+        <v>Select an asset</v>
+      </c>
+      <c r="B3727" t="str">
+        <v>اختر أصلاً</v>
+      </c>
+      <c r="C3727" t="str">
+        <v>Atlasīt aktīvu</v>
+      </c>
+    </row>
+    <row r="3728">
+      <c r="A3728" t="str">
+        <v>Select an exception</v>
+      </c>
+      <c r="B3728" t="str">
+        <v>اختر استثناءً</v>
+      </c>
+      <c r="C3728" t="str">
+        <v>Atlasīt izņēmumu</v>
+      </c>
+    </row>
+    <row r="3729">
+      <c r="A3729" t="str">
+        <v>Select compliance</v>
+      </c>
+      <c r="B3729" t="str">
+        <v>اختر الامتثال</v>
+      </c>
+      <c r="C3729" t="str">
+        <v>Atlasīt atbilstību</v>
+      </c>
+    </row>
+    <row r="3730">
+      <c r="A3730" t="str">
+        <v>Select target audiences</v>
+      </c>
+      <c r="B3730" t="str">
+        <v>اختر الجماهير المستهدفة</v>
+      </c>
+      <c r="C3730" t="str">
+        <v>Atlasīt mērķa auditorijas</v>
+      </c>
+    </row>
+    <row r="3731">
+      <c r="A3731" t="str">
+        <v>Select user</v>
+      </c>
+      <c r="B3731" t="str">
+        <v>اختر المستخدم</v>
+      </c>
+      <c r="C3731" t="str">
+        <v>Atlasīt lietotāju</v>
+      </c>
+    </row>
+    <row r="3732">
+      <c r="A3732" t="str">
+        <v>Send Back Exception</v>
+      </c>
+      <c r="B3732" t="str">
+        <v>إرجاع الاستثناء</v>
+      </c>
+      <c r="C3732" t="str">
+        <v>Nosūtīt atpakaļ izņēmumu</v>
+      </c>
+    </row>
+    <row r="3733">
+      <c r="A3733" t="str">
+        <v>Send Back for Revision</v>
+      </c>
+      <c r="B3733" t="str">
+        <v>إرجاع للمراجعة</v>
+      </c>
+      <c r="C3733" t="str">
+        <v>Nosūtīt atpakaļ pārskatīšanai</v>
+      </c>
+    </row>
+    <row r="3734">
+      <c r="A3734" t="str">
+        <v>Signature</v>
+      </c>
+      <c r="B3734" t="str">
+        <v>التوقيع</v>
+      </c>
+      <c r="C3734" t="str">
+        <v>Paraksts</v>
+      </c>
+    </row>
+    <row r="3735">
+      <c r="A3735" t="str">
+        <v>Signature not available</v>
+      </c>
+      <c r="B3735" t="str">
+        <v>التوقيع غير متاح</v>
+      </c>
+      <c r="C3735" t="str">
+        <v>Paraksts nav pieejams</v>
+      </c>
+    </row>
+    <row r="3736">
+      <c r="A3736" t="str">
+        <v>Skipped</v>
+      </c>
+      <c r="B3736" t="str">
+        <v>تم تخطيه</v>
+      </c>
+      <c r="C3736" t="str">
+        <v>Izlaists</v>
+      </c>
+    </row>
+    <row r="3737">
+      <c r="A3737" t="str">
+        <v>Some changes failed to save.</v>
+      </c>
+      <c r="B3737" t="str">
+        <v>فشل حفظ بعض التغييرات.</v>
+      </c>
+      <c r="C3737" t="str">
+        <v>Dažas izmaiņas neizdevās saglabāt.</v>
+      </c>
+    </row>
+    <row r="3738">
+      <c r="A3738" t="str">
+        <v>Special characters are not allowed</v>
+      </c>
+      <c r="B3738" t="str">
+        <v>الأحرف الخاصة غير مسموح بها</v>
+      </c>
+      <c r="C3738" t="str">
+        <v>Speciālās rakstzīmes nav atļautas</v>
+      </c>
+    </row>
+    <row r="3739">
+      <c r="A3739" t="str">
+        <v>Stakeholder Information</v>
+      </c>
+      <c r="B3739" t="str">
+        <v>معلومات أصحاب المصلحة</v>
+      </c>
+      <c r="C3739" t="str">
+        <v>Ieinteresēto personu informācija</v>
+      </c>
+    </row>
+    <row r="3740">
+      <c r="A3740" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B3740" t="str">
+        <v>اشتراك</v>
+      </c>
+      <c r="C3740" t="str">
+        <v>Abonēt</v>
+      </c>
+    </row>
+    <row r="3741">
+      <c r="A3741" t="str">
+        <v>Task Progress</v>
+      </c>
+      <c r="B3741" t="str">
+        <v>تقدم المهمة</v>
+      </c>
+      <c r="C3741" t="str">
+        <v>Uzdevuma progress</v>
+      </c>
+    </row>
+    <row r="3742">
+      <c r="A3742" t="str">
+        <v>Timeframe</v>
+      </c>
+      <c r="B3742" t="str">
+        <v>الإطار الزمني</v>
+      </c>
+      <c r="C3742" t="str">
+        <v>Laika periods</v>
+      </c>
+    </row>
+    <row r="3743">
+      <c r="A3743" t="str">
+        <v>Toggle Columns</v>
+      </c>
+      <c r="B3743" t="str">
+        <v>تبديل الأعمدة</v>
+      </c>
+      <c r="C3743" t="str">
+        <v>Pārslēgt kolonnas</v>
+      </c>
+    </row>
+    <row r="3744">
+      <c r="A3744" t="str">
+        <v>Unlink Artifact</v>
+      </c>
+      <c r="B3744" t="str">
+        <v>إلغاء ربط القطعة</v>
+      </c>
+      <c r="C3744" t="str">
+        <v>Atsaistīt artefaktu</v>
+      </c>
+    </row>
+    <row r="3745">
+      <c r="A3745" t="str">
+        <v>Unsaved changes</v>
+      </c>
+      <c r="B3745" t="str">
+        <v>تغييرات غير محفوظة</v>
+      </c>
+      <c r="C3745" t="str">
+        <v>Nesaglabātas izmaiņas</v>
+      </c>
+    </row>
+    <row r="3746">
+      <c r="A3746" t="str">
+        <v>User Details</v>
+      </c>
+      <c r="B3746" t="str">
+        <v>تفاصيل المستخدم</v>
+      </c>
+      <c r="C3746" t="str">
+        <v>Lietotāja detaļas</v>
+      </c>
+    </row>
+    <row r="3747">
+      <c r="A3747" t="str">
+        <v>View More</v>
+      </c>
+      <c r="B3747" t="str">
+        <v>عرض المزيد</v>
+      </c>
+      <c r="C3747" t="str">
+        <v>Skatīt vairāk</v>
+      </c>
+    </row>
+    <row r="3748">
+      <c r="A3748" t="str">
+        <v>You don't have permission to access Evidence.</v>
+      </c>
+      <c r="B3748" t="str">
+        <v>ليس لديك صلاحية للوصول إلى الأدلة.</v>
+      </c>
+      <c r="C3748" t="str">
+        <v>Jums nav atļaujas piekļūt pierādījumiem.</v>
+      </c>
+    </row>
+    <row r="3749">
+      <c r="A3749" t="str">
+        <v>You don't have permission to access Risk Assessment.</v>
+      </c>
+      <c r="B3749" t="str">
+        <v>ليس لديك صلاحية للوصول إلى تقييم المخاطر.</v>
+      </c>
+      <c r="C3749" t="str">
+        <v>Jums nav atļaujas piekļūt risku novērtējumam.</v>
+      </c>
+    </row>
+    <row r="3750">
+      <c r="A3750" t="str">
+        <v>You don't have permission to access Risk Control Matrix.</v>
+      </c>
+      <c r="B3750" t="str">
+        <v>ليس لديك صلاحية للوصول إلى مصفوفة ضوابط المخاطر.</v>
+      </c>
+      <c r="C3750" t="str">
+        <v>Jums nav atļaujas piekļūt risku kontroles matricai.</v>
+      </c>
+    </row>
+    <row r="3751">
+      <c r="A3751" t="str">
+        <v>No artifacts linked to evidences. Please link artifacts first.</v>
+      </c>
+      <c r="B3751" t="str">
+        <v>لا توجد قطع مرتبطة بالأدلة. يرجى ربط القطع أولاً.</v>
+      </c>
+      <c r="C3751" t="str">
+        <v>Nav artefaktu, kas saistīti ar pierādījumiem. Lūdzu, vispirms saistiet artefaktus.</v>
+      </c>
+    </row>
+    <row r="3752">
+      <c r="A3752" t="str">
+        <v>No attachments uploaded</v>
+      </c>
+      <c r="B3752" t="str">
+        <v>لم يتم رفع مرفقات</v>
+      </c>
+      <c r="C3752" t="str">
+        <v>Nav augšupielādētu pielikumu</v>
+      </c>
+    </row>
+    <row r="3753">
+      <c r="A3753" t="str">
+        <v>No audit logs found.</v>
+      </c>
+      <c r="B3753" t="str">
+        <v>لم يتم العثور على سجلات تدقيق.</v>
+      </c>
+      <c r="C3753" t="str">
+        <v>Audita žurnāli nav atrasti.</v>
+      </c>
+    </row>
+    <row r="3754">
+      <c r="A3754" t="str">
+        <v>No departments match your search.</v>
+      </c>
+      <c r="B3754" t="str">
+        <v>لا توجد أقسام تطابق بحثك.</v>
+      </c>
+      <c r="C3754" t="str">
+        <v>Neviena nodaļa neatbilst meklēšanai.</v>
+      </c>
+    </row>
+    <row r="3755">
+      <c r="A3755" t="str">
+        <v>No eligible users found in this department</v>
+      </c>
+      <c r="B3755" t="str">
+        <v>لم يتم العثور على مستخدمين مؤهلين في هذا القسم</v>
+      </c>
+      <c r="C3755" t="str">
+        <v>Šajā nodaļā nav atrasti piemēroti lietotāji</v>
+      </c>
+    </row>
+    <row r="3756">
+      <c r="A3756" t="str">
+        <v>No issues match your search.</v>
+      </c>
+      <c r="B3756" t="str">
+        <v>لا توجد مشكلات تطابق بحثك.</v>
+      </c>
+      <c r="C3756" t="str">
+        <v>Neviena problēma neatbilst meklēšanai.</v>
+      </c>
+    </row>
+    <row r="3757">
+      <c r="A3757" t="str">
+        <v>No regulations match your search.</v>
+      </c>
+      <c r="B3757" t="str">
+        <v>لا توجد لوائح تطابق بحثك.</v>
+      </c>
+      <c r="C3757" t="str">
+        <v>Neviens noteikums neatbilst meklēšanai.</v>
+      </c>
+    </row>
+    <row r="3758">
+      <c r="A3758" t="str">
+        <v>No services match your search.</v>
+      </c>
+      <c r="B3758" t="str">
+        <v>لا توجد خدمات تطابق بحثك.</v>
+      </c>
+      <c r="C3758" t="str">
+        <v>Neviens pakalpojums neatbilst meklēšanai.</v>
+      </c>
+    </row>
+    <row r="3759">
+      <c r="A3759" t="str">
+        <v>No stakeholders have been added yet.</v>
+      </c>
+      <c r="B3759" t="str">
+        <v>لم تتم إضافة أصحاب مصلحة بعد.</v>
+      </c>
+      <c r="C3759" t="str">
+        <v>Vēl nav pievienota neviena ieinteresētā persona.</v>
+      </c>
+    </row>
+    <row r="3760">
+      <c r="A3760" t="str">
+        <v>No stakeholders match your search.</v>
+      </c>
+      <c r="B3760" t="str">
+        <v>لا يوجد أصحاب مصلحة يطابقون بحثك.</v>
+      </c>
+      <c r="C3760" t="str">
+        <v>Neviena ieinteresētā persona neatbilst meklēšanai.</v>
+      </c>
+    </row>
+    <row r="3761">
+      <c r="A3761" t="str">
+        <v>No Department Reviewers found in this department</v>
+      </c>
+      <c r="B3761" t="str">
+        <v>لم يتم العثور على مراجعين في هذا القسم</v>
+      </c>
+      <c r="C3761" t="str">
+        <v>Šajā nodaļā nav atrasti nodaļas pārskatītāji</v>
+      </c>
+    </row>
+    <row r="3762">
+      <c r="A3762" t="str">
+        <v>All Assignees</v>
+      </c>
+      <c r="B3762" t="str">
+        <v>جميع المكلفين</v>
+      </c>
+      <c r="C3762" t="str">
+        <v>Visi atbildīgie</v>
+      </c>
+    </row>
+    <row r="3763">
+      <c r="A3763" t="str">
+        <v>Imported {count} processes</v>
+      </c>
+      <c r="B3763" t="str">
+        <v>تم استيراد {count} عملية</v>
+      </c>
+      <c r="C3763" t="str">
+        <v>Importēti {count} procesi</v>
+      </c>
+    </row>
+    <row r="3764">
+      <c r="A3764" t="str">
+        <v>Successfully imported {count} issues</v>
+      </c>
+      <c r="B3764" t="str">
+        <v>تم استيراد {count} مشكلة بنجاح</v>
+      </c>
+      <c r="C3764" t="str">
+        <v>Veiksmīgi importētas {count} problēmas</v>
+      </c>
+    </row>
+    <row r="3765">
+      <c r="A3765" t="str">
+        <v>Successfully imported {count} stakeholders</v>
+      </c>
+      <c r="B3765" t="str">
+        <v>تم استيراد {count} من أصحاب المصلحة بنجاح</v>
+      </c>
+      <c r="C3765" t="str">
+        <v>Veiksmīgi importētas {count} ieinteresētās personas</v>
+      </c>
+    </row>
+    <row r="3766">
+      <c r="A3766" t="str">
+        <v>Save Issue</v>
+      </c>
+      <c r="B3766" t="str">
+        <v>حفظ المشكلة</v>
+      </c>
+      <c r="C3766" t="str">
+        <v>Saglabāt problēmu</v>
+      </c>
+    </row>
+    <row r="3767">
+      <c r="A3767" t="str">
+        <v>Update Issue</v>
+      </c>
+      <c r="B3767" t="str">
+        <v>تحديث المشكلة</v>
+      </c>
+      <c r="C3767" t="str">
+        <v>Atjaunināt problēmu</v>
+      </c>
+    </row>
+    <row r="3768">
+      <c r="A3768" t="str">
+        <v>action</v>
+      </c>
+      <c r="B3768" t="str">
+        <v>إجراء</v>
+      </c>
+      <c r="C3768" t="str">
+        <v>darbība</v>
+      </c>
+    </row>
+    <row r="3769">
+      <c r="A3769" t="str">
+        <v>artifacts</v>
+      </c>
+      <c r="B3769" t="str">
+        <v>القطع</v>
+      </c>
+      <c r="C3769" t="str">
+        <v>artefakti</v>
+      </c>
+    </row>
+    <row r="3770">
+      <c r="A3770" t="str">
+        <v>associatedVulnerabilities</v>
+      </c>
+      <c r="B3770" t="str">
+        <v>الثغرات المرتبطة</v>
+      </c>
+      <c r="C3770" t="str">
+        <v>saistītās ievainojamības</v>
+      </c>
+    </row>
+    <row r="3771">
+      <c r="A3771" t="str">
+        <v>basicRiskInformation</v>
+      </c>
+      <c r="B3771" t="str">
+        <v>معلومات المخاطر الأساسية</v>
+      </c>
+      <c r="C3771" t="str">
+        <v>pamata riska informācija</v>
+      </c>
+    </row>
+    <row r="3772">
+      <c r="A3772" t="str">
+        <v>cancel</v>
+      </c>
+      <c r="B3772" t="str">
+        <v>إلغاء</v>
+      </c>
+      <c r="C3772" t="str">
+        <v>atcelt</v>
+      </c>
+    </row>
+    <row r="3773">
+      <c r="A3773" t="str">
+        <v>cause</v>
+      </c>
+      <c r="B3773" t="str">
+        <v>السبب</v>
+      </c>
+      <c r="C3773" t="str">
+        <v>cēlonis</v>
+      </c>
+    </row>
+    <row r="3774">
+      <c r="A3774" t="str">
+        <v>causeCreatedSuccessfully</v>
+      </c>
+      <c r="B3774" t="str">
+        <v>تم إنشاء السبب بنجاح</v>
+      </c>
+      <c r="C3774" t="str">
+        <v>cēlonis veiksmīgi izveidots</v>
+      </c>
+    </row>
+    <row r="3775">
+      <c r="A3775" t="str">
+        <v>causeNameRequired</v>
+      </c>
+      <c r="B3775" t="str">
+        <v>اسم السبب مطلوب</v>
+      </c>
+      <c r="C3775" t="str">
+        <v>cēloņa nosaukums ir obligāts</v>
+      </c>
+    </row>
+    <row r="3776">
+      <c r="A3776" t="str">
+        <v>clickLinkControlToAssociate</v>
+      </c>
+      <c r="B3776" t="str">
+        <v>انقر لربط ضابط للربط</v>
+      </c>
+      <c r="C3776" t="str">
+        <v>noklikšķiniet saistīt kontroli</v>
+      </c>
+    </row>
+    <row r="3777">
+      <c r="A3777" t="str">
+        <v>code</v>
+      </c>
+      <c r="B3777" t="str">
+        <v>الرمز</v>
+      </c>
+      <c r="C3777" t="str">
+        <v>kods</v>
+      </c>
+    </row>
+    <row r="3778">
+      <c r="A3778" t="str">
+        <v>common.action</v>
+      </c>
+      <c r="B3778" t="str">
+        <v>إجراء</v>
+      </c>
+      <c r="C3778" t="str">
+        <v>darbība</v>
+      </c>
+    </row>
+    <row r="3779">
+      <c r="A3779" t="str">
+        <v>common.loadMore</v>
+      </c>
+      <c r="B3779" t="str">
+        <v>تحميل المزيد</v>
+      </c>
+      <c r="C3779" t="str">
+        <v>ielādēt vairāk</v>
+      </c>
+    </row>
+    <row r="3780">
+      <c r="A3780" t="str">
+        <v>common.noItemsFound</v>
+      </c>
+      <c r="B3780" t="str">
+        <v>لم يتم العثور على عناصر</v>
+      </c>
+      <c r="C3780" t="str">
+        <v>vienības nav atrastas</v>
+      </c>
+    </row>
+    <row r="3781">
+      <c r="A3781" t="str">
+        <v>complianceIssues</v>
+      </c>
+      <c r="B3781" t="str">
+        <v>مشكلات الامتثال</v>
+      </c>
+      <c r="C3781" t="str">
+        <v>atbilstības problēmas</v>
+      </c>
+    </row>
+    <row r="3782">
+      <c r="A3782" t="str">
+        <v>complianceRequirementsExceptions</v>
+      </c>
+      <c r="B3782" t="str">
+        <v>استثناءات متطلبات الامتثال</v>
+      </c>
+      <c r="C3782" t="str">
+        <v>atbilstības prasību izņēmumi</v>
+      </c>
+    </row>
+    <row r="3783">
+      <c r="A3783" t="str">
+        <v>controlCode</v>
+      </c>
+      <c r="B3783" t="str">
+        <v>رمز الضابط</v>
+      </c>
+      <c r="C3783" t="str">
+        <v>kontroles kods</v>
+      </c>
+    </row>
+    <row r="3784">
+      <c r="A3784" t="str">
+        <v>controlExceptions</v>
+      </c>
+      <c r="B3784" t="str">
+        <v>استثناءات الضوابط</v>
+      </c>
+      <c r="C3784" t="str">
+        <v>kontroles izņēmumi</v>
+      </c>
+    </row>
+    <row r="3785">
+      <c r="A3785" t="str">
+        <v>controlImplementationsByFramework</v>
+      </c>
+      <c r="B3785" t="str">
+        <v>تطبيقات الضوابط حسب الإطار</v>
+      </c>
+      <c r="C3785" t="str">
+        <v>kontroles ieviešanas pēc ietvara</v>
+      </c>
+    </row>
+    <row r="3786">
+      <c r="A3786" t="str">
+        <v>controlRequirementsByFramework</v>
+      </c>
+      <c r="B3786" t="str">
+        <v>متطلبات الضوابط حسب الإطار</v>
+      </c>
+      <c r="C3786" t="str">
+        <v>kontroles prasības pēc ietvara</v>
+      </c>
+    </row>
+    <row r="3787">
+      <c r="A3787" t="str">
+        <v>controlsSelected</v>
+      </c>
+      <c r="B3787" t="str">
+        <v>الضوابط المختارة</v>
+      </c>
+      <c r="C3787" t="str">
+        <v>atlasītās kontroles</v>
+      </c>
+    </row>
+    <row r="3788">
+      <c r="A3788" t="str">
+        <v>create</v>
+      </c>
+      <c r="B3788" t="str">
+        <v>إنشاء</v>
+      </c>
+      <c r="C3788" t="str">
+        <v>izveidot</v>
+      </c>
+    </row>
+    <row r="3789">
+      <c r="A3789" t="str">
+        <v>createNewCause</v>
+      </c>
+      <c r="B3789" t="str">
+        <v>إنشاء سبب جديد</v>
+      </c>
+      <c r="C3789" t="str">
+        <v>izveidot jaunu cēloni</v>
+      </c>
+    </row>
+    <row r="3790">
+      <c r="A3790" t="str">
+        <v>creating</v>
+      </c>
+      <c r="B3790" t="str">
+        <v>جاري الإنشاء</v>
+      </c>
+      <c r="C3790" t="str">
+        <v>izveido</v>
+      </c>
+    </row>
+    <row r="3791">
+      <c r="A3791" t="str">
+        <v>day</v>
+      </c>
+      <c r="B3791" t="str">
+        <v>يوم</v>
+      </c>
+      <c r="C3791" t="str">
+        <v>diena</v>
+      </c>
+    </row>
+    <row r="3792">
+      <c r="A3792" t="str">
+        <v>department</v>
+      </c>
+      <c r="B3792" t="str">
+        <v>القسم</v>
+      </c>
+      <c r="C3792" t="str">
+        <v>nodaļa</v>
+      </c>
+    </row>
+    <row r="3793">
+      <c r="A3793" t="str">
+        <v>description</v>
+      </c>
+      <c r="B3793" t="str">
+        <v>الوصف</v>
+      </c>
+      <c r="C3793" t="str">
+        <v>apraksts</v>
+      </c>
+    </row>
+    <row r="3794">
+      <c r="A3794" t="str">
+        <v>document(s) selected</v>
+      </c>
+      <c r="B3794" t="str">
+        <v>مستند(ات) مختارة</v>
+      </c>
+      <c r="C3794" t="str">
+        <v>dokuments(-i) atlasīts(-i)</v>
+      </c>
+    </row>
+    <row r="3795">
+      <c r="A3795" t="str">
+        <v>domain</v>
+      </c>
+      <c r="B3795" t="str">
+        <v>المجال</v>
+      </c>
+      <c r="C3795" t="str">
+        <v>domēns</v>
+      </c>
+    </row>
+    <row r="3796">
+      <c r="A3796" t="str">
+        <v>domainBasedProgressCompliance</v>
+      </c>
+      <c r="B3796" t="str">
+        <v>تقدم الامتثال حسب المجال</v>
+      </c>
+      <c r="C3796" t="str">
+        <v>uz domēnu balstīta atbilstības progresa</v>
+      </c>
+    </row>
+    <row r="3797">
+      <c r="A3797" t="str">
+        <v>done</v>
+      </c>
+      <c r="B3797" t="str">
+        <v>تم</v>
+      </c>
+      <c r="C3797" t="str">
+        <v>pabeigts</v>
+      </c>
+    </row>
+    <row r="3798">
+      <c r="A3798" t="str">
+        <v>e.g., 1.0</v>
+      </c>
+      <c r="B3798" t="str">
+        <v>مثال: 1.0</v>
+      </c>
+      <c r="C3798" t="str">
+        <v>piem., 1.0</v>
+      </c>
+    </row>
+    <row r="3799">
+      <c r="A3799" t="str">
+        <v>e.g., Financial, Reputational</v>
+      </c>
+      <c r="B3799" t="str">
+        <v>مثال: مالي، سمعة</v>
+      </c>
+      <c r="C3799" t="str">
+        <v>piem., Finansiāla, Reputācija</v>
+      </c>
+    </row>
+    <row r="3800">
+      <c r="A3800" t="str">
+        <v>e.g., Immediate, 4 Hours, 24 Hours</v>
+      </c>
+      <c r="B3800" t="str">
+        <v>مثال: فوري، 4 ساعات، 24 ساعة</v>
+      </c>
+      <c r="C3800" t="str">
+        <v>piem., Nekavējoties, 4 stundas, 24 stundas</v>
+      </c>
+    </row>
+    <row r="3801">
+      <c r="A3801" t="str">
+        <v>edit</v>
+      </c>
+      <c r="B3801" t="str">
+        <v>تعديل</v>
+      </c>
+      <c r="C3801" t="str">
+        <v>rediģēt</v>
+      </c>
+    </row>
+    <row r="3802">
+      <c r="A3802" t="str">
+        <v>editRisk</v>
+      </c>
+      <c r="B3802" t="str">
+        <v>تعديل المخاطرة</v>
+      </c>
+      <c r="C3802" t="str">
+        <v>rediģēt risku</v>
+      </c>
+    </row>
+    <row r="3803">
+      <c r="A3803" t="str">
+        <v>endDate</v>
+      </c>
+      <c r="B3803" t="str">
+        <v>تاريخ الانتهاء</v>
+      </c>
+      <c r="C3803" t="str">
+        <v>beigu datums</v>
+      </c>
+    </row>
+    <row r="3804">
+      <c r="A3804" t="str">
+        <v>enterCauseDescription</v>
+      </c>
+      <c r="B3804" t="str">
+        <v>أدخل وصف السبب</v>
+      </c>
+      <c r="C3804" t="str">
+        <v>ievadiet cēloņa aprakstu</v>
+      </c>
+    </row>
+    <row r="3805">
+      <c r="A3805" t="str">
+        <v>enterCauseName</v>
+      </c>
+      <c r="B3805" t="str">
+        <v>أدخل اسم السبب</v>
+      </c>
+      <c r="C3805" t="str">
+        <v>ievadiet cēloņa nosaukumu</v>
+      </c>
+    </row>
+    <row r="3806">
+      <c r="A3806" t="str">
+        <v>enterDescription</v>
+      </c>
+      <c r="B3806" t="str">
+        <v>أدخل الوصف</v>
+      </c>
+      <c r="C3806" t="str">
+        <v>ievadiet aprakstu</v>
+      </c>
+    </row>
+    <row r="3807">
+      <c r="A3807" t="str">
+        <v>enterRiskName</v>
+      </c>
+      <c r="B3807" t="str">
+        <v>أدخل اسم المخاطرة</v>
+      </c>
+      <c r="C3807" t="str">
+        <v>ievadiet riska nosaukumu</v>
+      </c>
+    </row>
+    <row r="3808">
+      <c r="A3808" t="str">
+        <v>enterRiskSources</v>
+      </c>
+      <c r="B3808" t="str">
+        <v>أدخل مصادر المخاطر</v>
+      </c>
+      <c r="C3808" t="str">
+        <v>ievadiet risku avotus</v>
+      </c>
+    </row>
+    <row r="3809">
+      <c r="A3809" t="str">
+        <v>evidences?</v>
+      </c>
+      <c r="B3809" t="str">
+        <v>أدلة؟</v>
+      </c>
+      <c r="C3809" t="str">
+        <v>pierādījumi?</v>
+      </c>
+    </row>
+    <row r="3810">
+      <c r="A3810" t="str">
+        <v>failedToLoadRisk</v>
+      </c>
+      <c r="B3810" t="str">
+        <v>فشل في تحميل المخاطرة</v>
+      </c>
+      <c r="C3810" t="str">
+        <v>neizdevās ielādēt risku</v>
+      </c>
+    </row>
+    <row r="3811">
+      <c r="A3811" t="str">
+        <v>failedToUpdateRisk</v>
+      </c>
+      <c r="B3811" t="str">
+        <v>فشل في تحديث المخاطرة</v>
+      </c>
+      <c r="C3811" t="str">
+        <v>neizdevās atjaunināt risku</v>
+      </c>
+    </row>
+    <row r="3812">
+      <c r="A3812" t="str">
+        <v>filterType</v>
+      </c>
+      <c r="B3812" t="str">
+        <v>نوع التصفية</v>
+      </c>
+      <c r="C3812" t="str">
+        <v>filtra tips</v>
+      </c>
+    </row>
+    <row r="3813">
+      <c r="A3813" t="str">
+        <v>frameworkCompliance</v>
+      </c>
+      <c r="B3813" t="str">
+        <v>امتثال الإطار</v>
+      </c>
+      <c r="C3813" t="str">
+        <v>ietvara atbilstība</v>
+      </c>
+    </row>
+    <row r="3814">
+      <c r="A3814" t="str">
+        <v>frameworkId</v>
+      </c>
+      <c r="B3814" t="str">
+        <v>معرف الإطار</v>
+      </c>
+      <c r="C3814" t="str">
+        <v>ietvara ID</v>
+      </c>
+    </row>
+    <row r="3815">
+      <c r="A3815" t="str">
+        <v>frameworkName</v>
+      </c>
+      <c r="B3815" t="str">
+        <v>اسم الإطار</v>
+      </c>
+      <c r="C3815" t="str">
+        <v>ietvara nosaukums</v>
+      </c>
+    </row>
+    <row r="3816">
+      <c r="A3816" t="str">
+        <v>frameworkWithGovernanceData</v>
+      </c>
+      <c r="B3816" t="str">
+        <v>الإطار مع بيانات الحوكمة</v>
+      </c>
+      <c r="C3816" t="str">
+        <v>ietvars ar pārvaldības datiem</v>
+      </c>
+    </row>
+    <row r="3817">
+      <c r="A3817" t="str">
+        <v>from</v>
+      </c>
+      <c r="B3817" t="str">
+        <v>من</v>
+      </c>
+      <c r="C3817" t="str">
+        <v>no</v>
+      </c>
+    </row>
+    <row r="3818">
+      <c r="A3818" t="str">
+        <v>functionalGrouping</v>
+      </c>
+      <c r="B3818" t="str">
+        <v>التجميع الوظيفي</v>
+      </c>
+      <c r="C3818" t="str">
+        <v>funkcionālā grupēšana</v>
+      </c>
+    </row>
+    <row r="3819">
+      <c r="A3819" t="str">
+        <v>hour</v>
+      </c>
+      <c r="B3819" t="str">
+        <v>ساعة</v>
+      </c>
+      <c r="C3819" t="str">
+        <v>stunda</v>
+      </c>
+    </row>
+    <row r="3820">
+      <c r="A3820" t="str">
+        <v>hours</v>
+      </c>
+      <c r="B3820" t="str">
+        <v>ساعات</v>
+      </c>
+      <c r="C3820" t="str">
+        <v>stundas</v>
+      </c>
+    </row>
+    <row r="3821">
+      <c r="A3821" t="str">
+        <v>impactedAsset</v>
+      </c>
+      <c r="B3821" t="str">
+        <v>الأصل المتأثر</v>
+      </c>
+      <c r="C3821" t="str">
+        <v>ietekmētais aktīvs</v>
+      </c>
+    </row>
+    <row r="3822">
+      <c r="A3822" t="str">
+        <v>impactedAssetProcess</v>
+      </c>
+      <c r="B3822" t="str">
+        <v>الأصل/العملية المتأثرة</v>
+      </c>
+      <c r="C3822" t="str">
+        <v>ietekmētais aktīvs/process</v>
+      </c>
+    </row>
+    <row r="3823">
+      <c r="A3823" t="str">
+        <v>impactedProcess</v>
+      </c>
+      <c r="B3823" t="str">
+        <v>العملية المتأثرة</v>
+      </c>
+      <c r="C3823" t="str">
+        <v>ietekmētais process</v>
+      </c>
+    </row>
+    <row r="3824">
+      <c r="A3824" t="str">
+        <v>input</v>
+      </c>
+      <c r="B3824" t="str">
+        <v>إدخال</v>
+      </c>
+      <c r="C3824" t="str">
+        <v>ievade</v>
+      </c>
+    </row>
+    <row r="3825">
+      <c r="A3825" t="str">
+        <v>linkControl</v>
+      </c>
+      <c r="B3825" t="str">
+        <v>ربط ضابط</v>
+      </c>
+      <c r="C3825" t="str">
+        <v>saistīt kontroli</v>
+      </c>
+    </row>
+    <row r="3826">
+      <c r="A3826" t="str">
+        <v>linkControls</v>
+      </c>
+      <c r="B3826" t="str">
+        <v>ربط الضوابط</v>
+      </c>
+      <c r="C3826" t="str">
+        <v>saistīt kontroles</v>
+      </c>
+    </row>
+    <row r="3827">
+      <c r="A3827" t="str">
+        <v>linkControlsToRisk</v>
+      </c>
+      <c r="B3827" t="str">
+        <v>ربط الضوابط بالمخاطرة</v>
+      </c>
+      <c r="C3827" t="str">
+        <v>saistīt kontroles ar risku</v>
+      </c>
+    </row>
+    <row r="3828">
+      <c r="A3828" t="str">
+        <v>minutes</v>
+      </c>
+      <c r="B3828" t="str">
+        <v>دقائق</v>
+      </c>
+      <c r="C3828" t="str">
+        <v>minūtes</v>
+      </c>
+    </row>
+    <row r="3829">
+      <c r="A3829" t="str">
+        <v>mode</v>
+      </c>
+      <c r="B3829" t="str">
+        <v>الوضع</v>
+      </c>
+      <c r="C3829" t="str">
+        <v>režīms</v>
+      </c>
+    </row>
+    <row r="3830">
+      <c r="A3830" t="str">
+        <v>name</v>
+      </c>
+      <c r="B3830" t="str">
+        <v>الاسم</v>
+      </c>
+      <c r="C3830" t="str">
+        <v>nosaukums</v>
+      </c>
+    </row>
+    <row r="3831">
+      <c r="A3831" t="str">
+        <v>next</v>
+      </c>
+      <c r="B3831" t="str">
+        <v>التالي</v>
+      </c>
+      <c r="C3831" t="str">
+        <v>nākamais</v>
+      </c>
+    </row>
+    <row r="3832">
+      <c r="A3832" t="str">
+        <v>noControlsLinkedYet</v>
+      </c>
+      <c r="B3832" t="str">
+        <v>لا توجد ضوابط مرتبطة بعد</v>
+      </c>
+      <c r="C3832" t="str">
+        <v>vēl nav saistītu kontroles</v>
+      </c>
+    </row>
+    <row r="3833">
+      <c r="A3833" t="str">
+        <v>noDepartmentReviewersFound</v>
+      </c>
+      <c r="B3833" t="str">
+        <v>لم يتم العثور على مراجعي القسم</v>
+      </c>
+      <c r="C3833" t="str">
+        <v>nodaļas pārskatītāji nav atrasti</v>
+      </c>
+    </row>
+    <row r="3834">
+      <c r="A3834" t="str">
+        <v>noPermissionToEditRisks</v>
+      </c>
+      <c r="B3834" t="str">
+        <v>ليس لديك صلاحية لتعديل المخاطر</v>
+      </c>
+      <c r="C3834" t="str">
+        <v>nav atļaujas rediģēt riskus</v>
+      </c>
+    </row>
+    <row r="3835">
+      <c r="A3835" t="str">
+        <v>options</v>
+      </c>
+      <c r="B3835" t="str">
+        <v>الخيارات</v>
+      </c>
+      <c r="C3835" t="str">
+        <v>opcijas</v>
+      </c>
+    </row>
+    <row r="3836">
+      <c r="A3836" t="str">
+        <v>overallCompliance</v>
+      </c>
+      <c r="B3836" t="str">
+        <v>الامتثال العام</v>
+      </c>
+      <c r="C3836" t="str">
+        <v>kopējā atbilstība</v>
+      </c>
+    </row>
+    <row r="3837">
+      <c r="A3837" t="str">
+        <v>overlaps with</v>
+      </c>
+      <c r="B3837" t="str">
+        <v>يتداخل مع</v>
+      </c>
+      <c r="C3837" t="str">
+        <v>pārklājas ar</v>
+      </c>
+    </row>
+    <row r="3838">
+      <c r="A3838" t="str">
+        <v>partially effective</v>
+      </c>
+      <c r="B3838" t="str">
+        <v>فعال جزئياً</v>
+      </c>
+      <c r="C3838" t="str">
+        <v>daļēji efektīvs</v>
+      </c>
+    </row>
+    <row r="3839">
+      <c r="A3839" t="str">
+        <v>pending</v>
+      </c>
+      <c r="B3839" t="str">
+        <v>معلق</v>
+      </c>
+      <c r="C3839" t="str">
+        <v>gaidošs</v>
+      </c>
+    </row>
+    <row r="3840">
+      <c r="A3840" t="str">
+        <v>potentialThreats</v>
+      </c>
+      <c r="B3840" t="str">
+        <v>التهديدات المحتملة</v>
+      </c>
+      <c r="C3840" t="str">
+        <v>potenciālie draudi</v>
+      </c>
+    </row>
+    <row r="3841">
+      <c r="A3841" t="str">
+        <v>previous</v>
+      </c>
+      <c r="B3841" t="str">
+        <v>السابق</v>
+      </c>
+      <c r="C3841" t="str">
+        <v>iepriekšējais</v>
+      </c>
+    </row>
+    <row r="3842">
+      <c r="A3842" t="str">
+        <v>riskCategory</v>
+      </c>
+      <c r="B3842" t="str">
+        <v>فئة المخاطر</v>
+      </c>
+      <c r="C3842" t="str">
+        <v>riska kategorija</v>
+      </c>
+    </row>
+    <row r="3843">
+      <c r="A3843" t="str">
+        <v>riskComplianceMatrix.controlCode</v>
+      </c>
+      <c r="B3843" t="str">
+        <v>رمز الضابط</v>
+      </c>
+      <c r="C3843" t="str">
+        <v>kontroles kods</v>
+      </c>
+    </row>
+    <row r="3844">
+      <c r="A3844" t="str">
+        <v>riskComplianceMatrix.controlName</v>
+      </c>
+      <c r="B3844" t="str">
+        <v>اسم الضابط</v>
+      </c>
+      <c r="C3844" t="str">
+        <v>kontroles nosaukums</v>
+      </c>
+    </row>
+    <row r="3845">
+      <c r="A3845" t="str">
+        <v>riskComplianceMatrix.description</v>
+      </c>
+      <c r="B3845" t="str">
+        <v>الوصف</v>
+      </c>
+      <c r="C3845" t="str">
+        <v>apraksts</v>
+      </c>
+    </row>
+    <row r="3846">
+      <c r="A3846" t="str">
+        <v>riskComplianceMatrix.inherentRiskRating</v>
+      </c>
+      <c r="B3846" t="str">
+        <v>تقييم المخاطر الأصلية</v>
+      </c>
+      <c r="C3846" t="str">
+        <v>piemītošā riska vērtējums</v>
+      </c>
+    </row>
+    <row r="3847">
+      <c r="A3847" t="str">
+        <v>riskComplianceMatrix.linkedControls</v>
+      </c>
+      <c r="B3847" t="str">
+        <v>الضوابط المرتبطة</v>
+      </c>
+      <c r="C3847" t="str">
+        <v>saistītās kontroles</v>
+      </c>
+    </row>
+    <row r="3848">
+      <c r="A3848" t="str">
+        <v>riskComplianceMatrix.noLinkedControls</v>
+      </c>
+      <c r="B3848" t="str">
+        <v>لا توجد ضوابط مرتبطة</v>
+      </c>
+      <c r="C3848" t="str">
+        <v>nav saistītu kontroles</v>
+      </c>
+    </row>
+    <row r="3849">
+      <c r="A3849" t="str">
+        <v>riskComplianceMatrix.noRisksFound</v>
+      </c>
+      <c r="B3849" t="str">
+        <v>لم يتم العثور على مخاطر</v>
+      </c>
+      <c r="C3849" t="str">
+        <v>riski nav atrasti</v>
+      </c>
+    </row>
+    <row r="3850">
+      <c r="A3850" t="str">
+        <v>riskComplianceMatrix.residualRiskRating</v>
+      </c>
+      <c r="B3850" t="str">
+        <v>تقييم المخاطر المتبقية</v>
+      </c>
+      <c r="C3850" t="str">
+        <v>atlikušā riska vērtējums</v>
+      </c>
+    </row>
+    <row r="3851">
+      <c r="A3851" t="str">
+        <v>riskComplianceMatrix.riskOwner</v>
+      </c>
+      <c r="B3851" t="str">
+        <v>مالك المخاطرة</v>
+      </c>
+      <c r="C3851" t="str">
+        <v>riska īpašnieks</v>
+      </c>
+    </row>
+    <row r="3852">
+      <c r="A3852" t="str">
+        <v>riskComplianceMatrix.status</v>
+      </c>
+      <c r="B3852" t="str">
+        <v>الحالة</v>
+      </c>
+      <c r="C3852" t="str">
+        <v>statuss</v>
+      </c>
+    </row>
+    <row r="3853">
+      <c r="A3853" t="str">
+        <v>riskComplianceMatrix.subtitle</v>
+      </c>
+      <c r="B3853" t="str">
+        <v>العنوان الفرعي</v>
+      </c>
+      <c r="C3853" t="str">
+        <v>apakšvirsraksts</v>
+      </c>
+    </row>
+    <row r="3854">
+      <c r="A3854" t="str">
+        <v>riskComplianceMatrix.title</v>
+      </c>
+      <c r="B3854" t="str">
+        <v>مصفوفة ضوابط المخاطر</v>
+      </c>
+      <c r="C3854" t="str">
+        <v>risku kontroles matrica</v>
+      </c>
+    </row>
+    <row r="3855">
+      <c r="A3855" t="str">
+        <v>riskDescription</v>
+      </c>
+      <c r="B3855" t="str">
+        <v>وصف المخاطرة</v>
+      </c>
+      <c r="C3855" t="str">
+        <v>riska apraksts</v>
+      </c>
+    </row>
+    <row r="3856">
+      <c r="A3856" t="str">
+        <v>riskDetails</v>
+      </c>
+      <c r="B3856" t="str">
+        <v>تفاصيل المخاطرة</v>
+      </c>
+      <c r="C3856" t="str">
+        <v>riska detaļas</v>
+      </c>
+    </row>
+    <row r="3857">
+      <c r="A3857" t="str">
+        <v>riskId</v>
+      </c>
+      <c r="B3857" t="str">
+        <v>معرف المخاطرة</v>
+      </c>
+      <c r="C3857" t="str">
+        <v>riska ID</v>
+      </c>
+    </row>
+    <row r="3858">
+      <c r="A3858" t="str">
+        <v>riskMapping</v>
+      </c>
+      <c r="B3858" t="str">
+        <v>خريطة المخاطر</v>
+      </c>
+      <c r="C3858" t="str">
+        <v>risku kartēšana</v>
+      </c>
+    </row>
+    <row r="3859">
+      <c r="A3859" t="str">
+        <v>riskName</v>
+      </c>
+      <c r="B3859" t="str">
+        <v>اسم المخاطرة</v>
+      </c>
+      <c r="C3859" t="str">
+        <v>riska nosaukums</v>
+      </c>
+    </row>
+    <row r="3860">
+      <c r="A3860" t="str">
+        <v>riskNotFound</v>
+      </c>
+      <c r="B3860" t="str">
+        <v>المخاطرة غير موجودة</v>
+      </c>
+      <c r="C3860" t="str">
+        <v>risks nav atrasts</v>
+      </c>
+    </row>
+    <row r="3861">
+      <c r="A3861" t="str">
+        <v>riskOwner</v>
+      </c>
+      <c r="B3861" t="str">
+        <v>مالك المخاطرة</v>
+      </c>
+      <c r="C3861" t="str">
+        <v>riska īpašnieks</v>
+      </c>
+    </row>
+    <row r="3862">
+      <c r="A3862" t="str">
+        <v>riskRating</v>
+      </c>
+      <c r="B3862" t="str">
+        <v>تقييم المخاطرة</v>
+      </c>
+      <c r="C3862" t="str">
+        <v>riska vērtējums</v>
+      </c>
+    </row>
+    <row r="3863">
+      <c r="A3863" t="str">
+        <v>riskSources</v>
+      </c>
+      <c r="B3863" t="str">
+        <v>مصادر المخاطر</v>
+      </c>
+      <c r="C3863" t="str">
+        <v>risku avoti</v>
+      </c>
+    </row>
+    <row r="3864">
+      <c r="A3864" t="str">
+        <v>riskType</v>
+      </c>
+      <c r="B3864" t="str">
+        <v>نوع المخاطرة</v>
+      </c>
+      <c r="C3864" t="str">
+        <v>riska tips</v>
+      </c>
+    </row>
+    <row r="3865">
+      <c r="A3865" t="str">
+        <v>riskUpdatedSuccessfully</v>
+      </c>
+      <c r="B3865" t="str">
+        <v>تم تحديث المخاطرة بنجاح</v>
+      </c>
+      <c r="C3865" t="str">
+        <v>risks veiksmīgi atjaunināts</v>
+      </c>
+    </row>
+    <row r="3866">
+      <c r="A3866" t="str">
+        <v>saving</v>
+      </c>
+      <c r="B3866" t="str">
+        <v>جاري الحفظ</v>
+      </c>
+      <c r="C3866" t="str">
+        <v>saglabā</v>
+      </c>
+    </row>
+    <row r="3867">
+      <c r="A3867" t="str">
+        <v>searchControls</v>
+      </c>
+      <c r="B3867" t="str">
+        <v>بحث في الضوابط</v>
+      </c>
+      <c r="C3867" t="str">
+        <v>meklēt kontroles</v>
+      </c>
+    </row>
+    <row r="3868">
+      <c r="A3868" t="str">
+        <v>selectCategory</v>
+      </c>
+      <c r="B3868" t="str">
+        <v>اختر الفئة</v>
+      </c>
+      <c r="C3868" t="str">
+        <v>atlasīt kategoriju</v>
+      </c>
+    </row>
+    <row r="3869">
+      <c r="A3869" t="str">
+        <v>selectCause</v>
+      </c>
+      <c r="B3869" t="str">
+        <v>اختر السبب</v>
+      </c>
+      <c r="C3869" t="str">
+        <v>atlasīt cēloni</v>
+      </c>
+    </row>
+    <row r="3870">
+      <c r="A3870" t="str">
+        <v>selectDepartment</v>
+      </c>
+      <c r="B3870" t="str">
+        <v>اختر القسم</v>
+      </c>
+      <c r="C3870" t="str">
+        <v>atlasīt nodaļu</v>
+      </c>
+    </row>
+    <row r="3871">
+      <c r="A3871" t="str">
+        <v>selectDepartmentFirst</v>
+      </c>
+      <c r="B3871" t="str">
+        <v>اختر القسم أولاً</v>
+      </c>
+      <c r="C3871" t="str">
+        <v>vispirms atlasiet nodaļu</v>
+      </c>
+    </row>
+    <row r="3872">
+      <c r="A3872" t="str">
+        <v>selectImpactedAsset</v>
+      </c>
+      <c r="B3872" t="str">
+        <v>اختر الأصل المتأثر</v>
+      </c>
+      <c r="C3872" t="str">
+        <v>atlasīt ietekmēto aktīvu</v>
+      </c>
+    </row>
+    <row r="3873">
+      <c r="A3873" t="str">
+        <v>selectImpactedProcess</v>
+      </c>
+      <c r="B3873" t="str">
+        <v>اختر العملية المتأثرة</v>
+      </c>
+      <c r="C3873" t="str">
+        <v>atlasīt ietekmēto procesu</v>
+      </c>
+    </row>
+    <row r="3874">
+      <c r="A3874" t="str">
+        <v>selectOwner</v>
+      </c>
+      <c r="B3874" t="str">
+        <v>اختر المالك</v>
+      </c>
+      <c r="C3874" t="str">
+        <v>atlasīt īpašnieku</v>
+      </c>
+    </row>
+    <row r="3875">
+      <c r="A3875" t="str">
+        <v>selectRiskTypeFirst</v>
+      </c>
+      <c r="B3875" t="str">
+        <v>اختر نوع المخاطرة أولاً</v>
+      </c>
+      <c r="C3875" t="str">
+        <v>vispirms atlasiet riska tipu</v>
+      </c>
+    </row>
+    <row r="3876">
+      <c r="A3876" t="str">
+        <v>selectThreats</v>
+      </c>
+      <c r="B3876" t="str">
+        <v>اختر التهديدات</v>
+      </c>
+      <c r="C3876" t="str">
+        <v>atlasīt draudus</v>
+      </c>
+    </row>
+    <row r="3877">
+      <c r="A3877" t="str">
+        <v>selectVulnerabilities</v>
+      </c>
+      <c r="B3877" t="str">
+        <v>اختر الثغرات</v>
+      </c>
+      <c r="C3877" t="str">
+        <v>atlasīt ievainojamības</v>
+      </c>
+    </row>
+    <row r="3878">
+      <c r="A3878" t="str">
+        <v>signature Publish</v>
+      </c>
+      <c r="B3878" t="str">
+        <v>توقيع النشر</v>
+      </c>
+      <c r="C3878" t="str">
+        <v>paraksta publicēšana</v>
+      </c>
+    </row>
+    <row r="3879">
+      <c r="A3879" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="B3879" t="str">
+        <v>تم تخطيه</v>
+      </c>
+      <c r="C3879" t="str">
+        <v>izlaists</v>
+      </c>
+    </row>
+    <row r="3880">
+      <c r="A3880" t="str">
+        <v>stakeholders found</v>
+      </c>
+      <c r="B3880" t="str">
+        <v>تم العثور على أصحاب مصلحة</v>
+      </c>
+      <c r="C3880" t="str">
+        <v>ieinteresētās personas atrastas</v>
+      </c>
+    </row>
+    <row r="3881">
+      <c r="A3881" t="str">
+        <v>startDate</v>
+      </c>
+      <c r="B3881" t="str">
+        <v>تاريخ البدء</v>
+      </c>
+      <c r="C3881" t="str">
+        <v>sākuma datums</v>
+      </c>
+    </row>
+    <row r="3882">
+      <c r="A3882" t="str">
+        <v>status</v>
+      </c>
+      <c r="B3882" t="str">
+        <v>الحالة</v>
+      </c>
+      <c r="C3882" t="str">
+        <v>statuss</v>
+      </c>
+    </row>
+    <row r="3883">
+      <c r="A3883" t="str">
+        <v>tab</v>
+      </c>
+      <c r="B3883" t="str">
+        <v>تبويب</v>
+      </c>
+      <c r="C3883" t="str">
+        <v>cilne</v>
+      </c>
+    </row>
+    <row r="3884">
+      <c r="A3884" t="str">
+        <v>updateRisk</v>
+      </c>
+      <c r="B3884" t="str">
+        <v>تحديث المخاطرة</v>
+      </c>
+      <c r="C3884" t="str">
+        <v>atjaunināt risku</v>
+      </c>
+    </row>
+    <row r="3885">
+      <c r="A3885" t="str">
+        <v>uploaded</v>
+      </c>
+      <c r="B3885" t="str">
+        <v>تم الرفع</v>
+      </c>
+      <c r="C3885" t="str">
+        <v>augšupielādēts</v>
+      </c>
+    </row>
+    <row r="3886">
+      <c r="A3886" t="str">
+        <v>users imported</v>
+      </c>
+      <c r="B3886" t="str">
+        <v>تم استيراد المستخدمين</v>
+      </c>
+      <c r="C3886" t="str">
+        <v>lietotāji importēti</v>
+      </c>
+    </row>
+    <row r="3887">
+      <c r="A3887" t="str">
+        <v>xlsx</v>
+      </c>
+      <c r="B3887" t="str">
+        <v>xlsx</v>
+      </c>
+      <c r="C3887" t="str">
+        <v>xlsx</v>
+      </c>
+    </row>
+    <row r="3888">
+      <c r="A3888" t="str">
+        <v>year</v>
+      </c>
+      <c r="B3888" t="str">
+        <v>سنة</v>
+      </c>
+      <c r="C3888" t="str">
+        <v>gads</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3323"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3888"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3888"/>
+  <dimension ref="A1:C3891"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -37476,5705 +37476,5738 @@
     </row>
     <row r="3371">
       <c r="A3371" t="str">
-        <v>Add BIA Category</v>
+        <v>Subscription</v>
       </c>
       <c r="B3371" t="str">
-        <v>إضافة فئة تحليل تأثير الأعمال</v>
+        <v>الاشتراك</v>
       </c>
       <c r="C3371" t="str">
-        <v>Pievienot BIA kategoriju</v>
+        <v>Abonements</v>
       </c>
     </row>
     <row r="3372">
       <c r="A3372" t="str">
-        <v>Add BIA Rating</v>
+        <v>All Subscriptions</v>
       </c>
       <c r="B3372" t="str">
-        <v>إضافة تقييم تحليل تأثير الأعمال</v>
+        <v>جميع الاشتراكات</v>
       </c>
       <c r="C3372" t="str">
-        <v>Pievienot BIA vērtējumu</v>
+        <v>Visi abonamenti</v>
       </c>
     </row>
     <row r="3373">
       <c r="A3373" t="str">
-        <v>BIA Categories</v>
+        <v>Not Subscribed</v>
       </c>
       <c r="B3373" t="str">
-        <v>فئات تحليل تأثير الأعمال</v>
+        <v>غير مشترك</v>
       </c>
       <c r="C3373" t="str">
-        <v>BIA kategorijas</v>
+        <v>Nav abonēts</v>
       </c>
     </row>
     <row r="3374">
       <c r="A3374" t="str">
-        <v>BIA Comments</v>
+        <v>Add BIA Category</v>
       </c>
       <c r="B3374" t="str">
-        <v>تعليقات تحليل تأثير الأعمال</v>
+        <v>إضافة فئة تحليل تأثير الأعمال</v>
       </c>
       <c r="C3374" t="str">
-        <v>BIA komentāri</v>
+        <v>Pievienot BIA kategoriju</v>
       </c>
     </row>
     <row r="3375">
       <c r="A3375" t="str">
-        <v>BIA approved</v>
+        <v>Add BIA Rating</v>
       </c>
       <c r="B3375" t="str">
-        <v>تمت الموافقة على تحليل تأثير الأعمال</v>
+        <v>إضافة تقييم تحليل تأثير الأعمال</v>
       </c>
       <c r="C3375" t="str">
-        <v>BIA apstiprināts</v>
+        <v>Pievienot BIA vērtējumu</v>
       </c>
     </row>
     <row r="3376">
       <c r="A3376" t="str">
-        <v>BIA data has been saved</v>
+        <v>BIA Categories</v>
       </c>
       <c r="B3376" t="str">
-        <v>تم حفظ بيانات تحليل تأثير الأعمال</v>
+        <v>فئات تحليل تأثير الأعمال</v>
       </c>
       <c r="C3376" t="str">
-        <v>BIA dati ir saglabāti</v>
+        <v>BIA kategorijas</v>
       </c>
     </row>
     <row r="3377">
       <c r="A3377" t="str">
-        <v>BIA data has been saved successfully</v>
+        <v>BIA Comments</v>
       </c>
       <c r="B3377" t="str">
-        <v>تم حفظ بيانات تحليل تأثير الأعمال بنجاح</v>
+        <v>تعليقات تحليل تأثير الأعمال</v>
       </c>
       <c r="C3377" t="str">
-        <v>BIA dati veiksmīgi saglabāti</v>
+        <v>BIA komentāri</v>
       </c>
     </row>
     <row r="3378">
       <c r="A3378" t="str">
-        <v>BIA has been approved</v>
+        <v>BIA approved</v>
       </c>
       <c r="B3378" t="str">
         <v>تمت الموافقة على تحليل تأثير الأعمال</v>
       </c>
       <c r="C3378" t="str">
-        <v>BIA ir apstiprināts</v>
+        <v>BIA apstiprināts</v>
       </c>
     </row>
     <row r="3379">
       <c r="A3379" t="str">
-        <v>BIA has been sent back for revision</v>
+        <v>BIA data has been saved</v>
       </c>
       <c r="B3379" t="str">
-        <v>تم إرجاع تحليل تأثير الأعمال للمراجعة</v>
+        <v>تم حفظ بيانات تحليل تأثير الأعمال</v>
       </c>
       <c r="C3379" t="str">
-        <v>BIA nosūtīts atpakaļ pārskatīšanai</v>
+        <v>BIA dati ir saglabāti</v>
       </c>
     </row>
     <row r="3380">
       <c r="A3380" t="str">
-        <v>BIA has been submitted for approval</v>
+        <v>BIA data has been saved successfully</v>
       </c>
       <c r="B3380" t="str">
-        <v>تم تقديم تحليل تأثير الأعمال للموافقة</v>
+        <v>تم حفظ بيانات تحليل تأثير الأعمال بنجاح</v>
       </c>
       <c r="C3380" t="str">
-        <v>BIA iesniegts apstiprināšanai</v>
+        <v>BIA dati veiksmīgi saglabāti</v>
       </c>
     </row>
     <row r="3381">
       <c r="A3381" t="str">
-        <v>BIA submitted for approval</v>
+        <v>BIA has been approved</v>
       </c>
       <c r="B3381" t="str">
-        <v>تم تقديم تحليل تأثير الأعمال للموافقة</v>
+        <v>تمت الموافقة على تحليل تأثير الأعمال</v>
       </c>
       <c r="C3381" t="str">
-        <v>BIA iesniegts apstiprināšanai</v>
+        <v>BIA ir apstiprināts</v>
       </c>
     </row>
     <row r="3382">
       <c r="A3382" t="str">
-        <v>Edit BIA Category</v>
+        <v>BIA has been sent back for revision</v>
       </c>
       <c r="B3382" t="str">
-        <v>تعديل فئة تحليل تأثير الأعمال</v>
+        <v>تم إرجاع تحليل تأثير الأعمال للمراجعة</v>
       </c>
       <c r="C3382" t="str">
-        <v>Rediģēt BIA kategoriju</v>
+        <v>BIA nosūtīts atpakaļ pārskatīšanai</v>
       </c>
     </row>
     <row r="3383">
       <c r="A3383" t="str">
-        <v>Edit BIA Rating</v>
+        <v>BIA has been submitted for approval</v>
       </c>
       <c r="B3383" t="str">
-        <v>تعديل تقييم تحليل تأثير الأعمال</v>
+        <v>تم تقديم تحليل تأثير الأعمال للموافقة</v>
       </c>
       <c r="C3383" t="str">
-        <v>Rediģēt BIA vērtējumu</v>
+        <v>BIA iesniegts apstiprināšanai</v>
       </c>
     </row>
     <row r="3384">
       <c r="A3384" t="str">
-        <v>Add a new impact category for Business Impact Analysis</v>
+        <v>BIA submitted for approval</v>
       </c>
       <c r="B3384" t="str">
-        <v>إضافة فئة تأثير جديدة لتحليل تأثير الأعمال</v>
+        <v>تم تقديم تحليل تأثير الأعمال للموافقة</v>
       </c>
       <c r="C3384" t="str">
-        <v>Pievienot jaunu ietekmes kategoriju biznesa ietekmes analīzei</v>
+        <v>BIA iesniegts apstiprināšanai</v>
       </c>
     </row>
     <row r="3385">
       <c r="A3385" t="str">
-        <v>Configure how the BIA impact rating is calculated from individual category scores</v>
+        <v>Edit BIA Category</v>
       </c>
       <c r="B3385" t="str">
-        <v>تكوين كيفية حساب تقييم تأثير تحليل الأعمال من درجات الفئات الفردية</v>
+        <v>تعديل فئة تحليل تأثير الأعمال</v>
       </c>
       <c r="C3385" t="str">
-        <v>Konfigurēt, kā BIA ietekmes vērtējums tiek aprēķināts no kategoriju punktiem</v>
+        <v>Rediģēt BIA kategoriju</v>
       </c>
     </row>
     <row r="3386">
       <c r="A3386" t="str">
-        <v>Define a new rating level for BIA assessments</v>
+        <v>Edit BIA Rating</v>
       </c>
       <c r="B3386" t="str">
-        <v>تحديد مستوى تقييم جديد لتقييمات تحليل تأثير الأعمال</v>
+        <v>تعديل تقييم تحليل تأثير الأعمال</v>
       </c>
       <c r="C3386" t="str">
-        <v>Definēt jaunu vērtējuma līmeni BIA novērtējumiem</v>
+        <v>Rediģēt BIA vērtējumu</v>
       </c>
     </row>
     <row r="3387">
       <c r="A3387" t="str">
-        <v>Enable KPI Measurement Required when adding a process to see it here</v>
+        <v>Add a new impact category for Business Impact Analysis</v>
       </c>
       <c r="B3387" t="str">
-        <v>فعّل قياس مؤشرات الأداء المطلوبة عند إضافة عملية لرؤيتها هنا</v>
+        <v>إضافة فئة تأثير جديدة لتحليل تأثير الأعمال</v>
       </c>
       <c r="C3387" t="str">
-        <v>Iespējojiet KPI mērījumu, pievienojot procesu, lai to redzētu šeit</v>
+        <v>Pievienot jaunu ietekmes kategoriju biznesa ietekmes analīzei</v>
       </c>
     </row>
     <row r="3388">
       <c r="A3388" t="str">
-        <v>Add Organisation Profile</v>
+        <v>Configure how the BIA impact rating is calculated from individual category scores</v>
       </c>
       <c r="B3388" t="str">
-        <v>إضافة ملف المنظمة</v>
+        <v>تكوين كيفية حساب تقييم تأثير تحليل الأعمال من درجات الفئات الفردية</v>
       </c>
       <c r="C3388" t="str">
-        <v>Pievienot organizācijas profilu</v>
+        <v>Konfigurēt, kā BIA ietekmes vērtējums tiek aprēķināts no kategoriju punktiem</v>
       </c>
     </row>
     <row r="3389">
       <c r="A3389" t="str">
-        <v>Edit Organisation Profile</v>
+        <v>Define a new rating level for BIA assessments</v>
       </c>
       <c r="B3389" t="str">
-        <v>تعديل ملف المنظمة</v>
+        <v>تحديد مستوى تقييم جديد لتقييمات تحليل تأثير الأعمال</v>
       </c>
       <c r="C3389" t="str">
-        <v>Rediģēt organizācijas profilu</v>
+        <v>Definēt jaunu vērtējuma līmeni BIA novērtējumiem</v>
       </c>
     </row>
     <row r="3390">
       <c r="A3390" t="str">
-        <v>Branch Size</v>
+        <v>Enable KPI Measurement Required when adding a process to see it here</v>
       </c>
       <c r="B3390" t="str">
-        <v>حجم الفرع</v>
+        <v>فعّل قياس مؤشرات الأداء المطلوبة عند إضافة عملية لرؤيتها هنا</v>
       </c>
       <c r="C3390" t="str">
-        <v>Filiāles lielums</v>
+        <v>Iespējojiet KPI mērījumu, pievienojot procesu, lai to redzētu šeit</v>
       </c>
     </row>
     <row r="3391">
       <c r="A3391" t="str">
-        <v>Budget Allocation Vs Used</v>
+        <v>Add Organisation Profile</v>
       </c>
       <c r="B3391" t="str">
-        <v>تخصيص الميزانية مقابل المستخدم</v>
+        <v>إضافة ملف المنظمة</v>
       </c>
       <c r="C3391" t="str">
-        <v>Budžeta piešķīrums pret izlietoto</v>
+        <v>Pievienot organizācijas profilu</v>
       </c>
     </row>
     <row r="3392">
       <c r="A3392" t="str">
-        <v>Employee Size</v>
+        <v>Edit Organisation Profile</v>
       </c>
       <c r="B3392" t="str">
-        <v>حجم الموظفين</v>
+        <v>تعديل ملف المنظمة</v>
       </c>
       <c r="C3392" t="str">
-        <v>Darbinieku skaits</v>
+        <v>Rediģēt organizācijas profilu</v>
       </c>
     </row>
     <row r="3393">
       <c r="A3393" t="str">
-        <v>Full Legal Entity Name</v>
+        <v>Branch Size</v>
       </c>
       <c r="B3393" t="str">
-        <v>الاسم القانوني الكامل للكيان</v>
+        <v>حجم الفرع</v>
       </c>
       <c r="C3393" t="str">
-        <v>Pilns juridiskās personas nosaukums</v>
+        <v>Filiāles lielums</v>
       </c>
     </row>
     <row r="3394">
       <c r="A3394" t="str">
-        <v>Define your organisation's regulatory context and business details</v>
+        <v>Budget Allocation Vs Used</v>
       </c>
       <c r="B3394" t="str">
-        <v>حدد السياق التنظيمي وتفاصيل الأعمال لمنظمتك</v>
+        <v>تخصيص الميزانية مقابل المستخدم</v>
       </c>
       <c r="C3394" t="str">
-        <v>Definējiet savas organizācijas regulatīvo kontekstu un biznesa detaļas</v>
+        <v>Budžeta piešķīrums pret izlietoto</v>
       </c>
     </row>
     <row r="3395">
       <c r="A3395" t="str">
-        <v>Update your organisation's regulatory context and business details</v>
+        <v>Employee Size</v>
       </c>
       <c r="B3395" t="str">
-        <v>تحديث السياق التنظيمي وتفاصيل الأعمال لمنظمتك</v>
+        <v>حجم الموظفين</v>
       </c>
       <c r="C3395" t="str">
-        <v>Atjauniniet savas organizācijas regulatīvo kontekstu un biznesa detaļas</v>
+        <v>Darbinieku skaits</v>
       </c>
     </row>
     <row r="3396">
       <c r="A3396" t="str">
-        <v>Enter admin contact email</v>
+        <v>Full Legal Entity Name</v>
       </c>
       <c r="B3396" t="str">
-        <v>أدخل البريد الإلكتروني لجهة الاتصال الإدارية</v>
+        <v>الاسم القانوني الكامل للكيان</v>
       </c>
       <c r="C3396" t="str">
-        <v>Ievadiet administratora kontakta e-pastu</v>
+        <v>Pilns juridiskās personas nosaukums</v>
       </c>
     </row>
     <row r="3397">
       <c r="A3397" t="str">
-        <v>Enter full legal entity name</v>
+        <v>Define your organisation's regulatory context and business details</v>
       </c>
       <c r="B3397" t="str">
-        <v>أدخل الاسم القانوني الكامل للكيان</v>
+        <v>حدد السياق التنظيمي وتفاصيل الأعمال لمنظمتك</v>
       </c>
       <c r="C3397" t="str">
-        <v>Ievadiet pilnu juridiskās personas nosaukumu</v>
+        <v>Definējiet savas organizācijas regulatīvo kontekstu un biznesa detaļas</v>
       </c>
     </row>
     <row r="3398">
       <c r="A3398" t="str">
-        <v>Enter headquarter address</v>
+        <v>Update your organisation's regulatory context and business details</v>
       </c>
       <c r="B3398" t="str">
-        <v>أدخل عنوان المقر الرئيسي</v>
+        <v>تحديث السياق التنظيمي وتفاصيل الأعمال لمنظمتك</v>
       </c>
       <c r="C3398" t="str">
-        <v>Ievadiet galvenā biroja adresi</v>
+        <v>Atjauniniet savas organizācijas regulatīvo kontekstu un biznesa detaļas</v>
       </c>
     </row>
     <row r="3399">
       <c r="A3399" t="str">
-        <v>Enter registration number</v>
+        <v>Enter admin contact email</v>
       </c>
       <c r="B3399" t="str">
-        <v>أدخل رقم التسجيل</v>
+        <v>أدخل البريد الإلكتروني لجهة الاتصال الإدارية</v>
       </c>
       <c r="C3399" t="str">
-        <v>Ievadiet reģistrācijas numuru</v>
+        <v>Ievadiet administratora kontakta e-pastu</v>
       </c>
     </row>
     <row r="3400">
       <c r="A3400" t="str">
-        <v>Save Profile</v>
+        <v>Enter full legal entity name</v>
       </c>
       <c r="B3400" t="str">
-        <v>حفظ الملف الشخصي</v>
+        <v>أدخل الاسم القانوني الكامل للكيان</v>
       </c>
       <c r="C3400" t="str">
-        <v>Saglabāt profilu</v>
+        <v>Ievadiet pilnu juridiskās personas nosaukumu</v>
       </c>
     </row>
     <row r="3401">
       <c r="A3401" t="str">
-        <v>Update Profile</v>
+        <v>Enter headquarter address</v>
       </c>
       <c r="B3401" t="str">
-        <v>تحديث الملف الشخصي</v>
+        <v>أدخل عنوان المقر الرئيسي</v>
       </c>
       <c r="C3401" t="str">
-        <v>Atjaunināt profilu</v>
+        <v>Ievadiet galvenā biroja adresi</v>
       </c>
     </row>
     <row r="3402">
       <c r="A3402" t="str">
-        <v>Select business model</v>
+        <v>Enter registration number</v>
       </c>
       <c r="B3402" t="str">
-        <v>اختر نموذج الأعمال</v>
+        <v>أدخل رقم التسجيل</v>
       </c>
       <c r="C3402" t="str">
-        <v>Atlasīt biznesa modeli</v>
+        <v>Ievadiet reģistrācijas numuru</v>
       </c>
     </row>
     <row r="3403">
       <c r="A3403" t="str">
-        <v>Select countries</v>
+        <v>Save Profile</v>
       </c>
       <c r="B3403" t="str">
-        <v>اختر الدول</v>
+        <v>حفظ الملف الشخصي</v>
       </c>
       <c r="C3403" t="str">
-        <v>Atlasīt valstis</v>
+        <v>Saglabāt profilu</v>
       </c>
     </row>
     <row r="3404">
       <c r="A3404" t="str">
-        <v>Select country</v>
+        <v>Update Profile</v>
       </c>
       <c r="B3404" t="str">
-        <v>اختر الدولة</v>
+        <v>تحديث الملف الشخصي</v>
       </c>
       <c r="C3404" t="str">
-        <v>Atlasīt valsti</v>
+        <v>Atjaunināt profilu</v>
       </c>
     </row>
     <row r="3405">
       <c r="A3405" t="str">
-        <v>Select entity</v>
+        <v>Select business model</v>
       </c>
       <c r="B3405" t="str">
-        <v>اختر الكيان</v>
+        <v>اختر نموذج الأعمال</v>
       </c>
       <c r="C3405" t="str">
-        <v>Atlasīt entītiju</v>
+        <v>Atlasīt biznesa modeli</v>
       </c>
     </row>
     <row r="3406">
       <c r="A3406" t="str">
-        <v>Select industries</v>
+        <v>Select countries</v>
       </c>
       <c r="B3406" t="str">
-        <v>اختر الصناعات</v>
+        <v>اختر الدول</v>
       </c>
       <c r="C3406" t="str">
-        <v>Atlasīt nozares</v>
+        <v>Atlasīt valstis</v>
       </c>
     </row>
     <row r="3407">
       <c r="A3407" t="str">
-        <v>Select organisation type</v>
+        <v>Select country</v>
       </c>
       <c r="B3407" t="str">
-        <v>اختر نوع المنظمة</v>
+        <v>اختر الدولة</v>
       </c>
       <c r="C3407" t="str">
-        <v>Atlasīt organizācijas tipu</v>
+        <v>Atlasīt valsti</v>
       </c>
     </row>
     <row r="3408">
       <c r="A3408" t="str">
-        <v>Select regulations related to this issue (optional)</v>
+        <v>Select entity</v>
       </c>
       <c r="B3408" t="str">
-        <v>اختر اللوائح المتعلقة بهذه المشكلة (اختياري)</v>
+        <v>اختر الكيان</v>
       </c>
       <c r="C3408" t="str">
-        <v>Atlasīt ar šo problēmu saistītos noteikumus (neobligāti)</v>
+        <v>Atlasīt entītiju</v>
       </c>
     </row>
     <row r="3409">
       <c r="A3409" t="str">
-        <v>Select scope</v>
+        <v>Select industries</v>
       </c>
       <c r="B3409" t="str">
-        <v>اختر النطاق</v>
+        <v>اختر الصناعات</v>
       </c>
       <c r="C3409" t="str">
-        <v>Atlasīt darbības jomu</v>
+        <v>Atlasīt nozares</v>
       </c>
     </row>
     <row r="3410">
       <c r="A3410" t="str">
-        <v>Select technologies</v>
+        <v>Select organisation type</v>
       </c>
       <c r="B3410" t="str">
-        <v>اختر التقنيات</v>
+        <v>اختر نوع المنظمة</v>
       </c>
       <c r="C3410" t="str">
-        <v>Atlasīt tehnoloģijas</v>
+        <v>Atlasīt organizācijas tipu</v>
       </c>
     </row>
     <row r="3411">
       <c r="A3411" t="str">
-        <v>Select time zone</v>
+        <v>Select regulations related to this issue (optional)</v>
       </c>
       <c r="B3411" t="str">
-        <v>اختر المنطقة الزمنية</v>
+        <v>اختر اللوائح المتعلقة بهذه المشكلة (اختياري)</v>
       </c>
       <c r="C3411" t="str">
-        <v>Atlasīt laika joslu</v>
+        <v>Atlasīt ar šo problēmu saistītos noteikumus (neobligāti)</v>
       </c>
     </row>
     <row r="3412">
       <c r="A3412" t="str">
-        <v>Specify other industry</v>
+        <v>Select scope</v>
       </c>
       <c r="B3412" t="str">
-        <v>حدد صناعة أخرى</v>
+        <v>اختر النطاق</v>
       </c>
       <c r="C3412" t="str">
-        <v>Norādiet citu nozari</v>
+        <v>Atlasīt darbības jomu</v>
       </c>
     </row>
     <row r="3413">
       <c r="A3413" t="str">
-        <v>Timezone</v>
+        <v>Select technologies</v>
       </c>
       <c r="B3413" t="str">
-        <v>المنطقة الزمنية</v>
+        <v>اختر التقنيات</v>
       </c>
       <c r="C3413" t="str">
-        <v>Laika josla</v>
+        <v>Atlasīt tehnoloģijas</v>
       </c>
     </row>
     <row r="3414">
       <c r="A3414" t="str">
-        <v>Basic process information</v>
+        <v>Select time zone</v>
       </c>
       <c r="B3414" t="str">
-        <v>معلومات العملية الأساسية</v>
+        <v>اختر المنطقة الزمنية</v>
       </c>
       <c r="C3414" t="str">
-        <v>Pamatinformācija par procesu</v>
+        <v>Atlasīt laika joslu</v>
       </c>
     </row>
     <row r="3415">
       <c r="A3415" t="str">
-        <v>Complete the form to create a new process</v>
+        <v>Specify other industry</v>
       </c>
       <c r="B3415" t="str">
-        <v>أكمل النموذج لإنشاء عملية جديدة</v>
+        <v>حدد صناعة أخرى</v>
       </c>
       <c r="C3415" t="str">
-        <v>Aizpildiet formu, lai izveidotu jaunu procesu</v>
+        <v>Norādiet citu nozari</v>
       </c>
     </row>
     <row r="3416">
       <c r="A3416" t="str">
-        <v>Process Documents</v>
+        <v>Timezone</v>
       </c>
       <c r="B3416" t="str">
-        <v>مستندات العملية</v>
+        <v>المنطقة الزمنية</v>
       </c>
       <c r="C3416" t="str">
-        <v>Procesa dokumenti</v>
+        <v>Laika josla</v>
       </c>
     </row>
     <row r="3417">
       <c r="A3417" t="str">
-        <v>Process Flow</v>
+        <v>Basic process information</v>
       </c>
       <c r="B3417" t="str">
-        <v>سير العملية</v>
+        <v>معلومات العملية الأساسية</v>
       </c>
       <c r="C3417" t="str">
-        <v>Procesa plūsma</v>
+        <v>Pamatinformācija par procesu</v>
       </c>
     </row>
     <row r="3418">
       <c r="A3418" t="str">
-        <v>Process RACI</v>
+        <v>Complete the form to create a new process</v>
       </c>
       <c r="B3418" t="str">
-        <v>مصفوفة راسي للعملية</v>
+        <v>أكمل النموذج لإنشاء عملية جديدة</v>
       </c>
       <c r="C3418" t="str">
-        <v>Procesa RACI</v>
+        <v>Aizpildiet formu, lai izveidotu jaunu procesu</v>
       </c>
     </row>
     <row r="3419">
       <c r="A3419" t="str">
-        <v>Process characteristics</v>
+        <v>Process Documents</v>
       </c>
       <c r="B3419" t="str">
-        <v>خصائص العملية</v>
+        <v>مستندات العملية</v>
       </c>
       <c r="C3419" t="str">
-        <v>Procesa raksturlielumi</v>
+        <v>Procesa dokumenti</v>
       </c>
     </row>
     <row r="3420">
       <c r="A3420" t="str">
-        <v>Add files to attach to this process. Files will be uploaded when you save.</v>
+        <v>Process Flow</v>
       </c>
       <c r="B3420" t="str">
-        <v>أضف ملفات لإرفاقها بهذه العملية. سيتم رفع الملفات عند الحفظ.</v>
+        <v>سير العملية</v>
       </c>
       <c r="C3420" t="str">
-        <v>Pievienojiet failus šim procesam. Faili tiks augšupielādēti saglabājot.</v>
+        <v>Procesa plūsma</v>
       </c>
     </row>
     <row r="3421">
       <c r="A3421" t="str">
-        <v>Define the RACI matrix for this process - who is Responsible, Accountable, Consulted, and Informed.</v>
+        <v>Process RACI</v>
       </c>
       <c r="B3421" t="str">
-        <v>حدد مصفوفة راسي لهذه العملية - من هو المسؤول والمساءل والمستشار والمطلع.</v>
+        <v>مصفوفة راسي للعملية</v>
       </c>
       <c r="C3421" t="str">
-        <v>Definējiet RACI matricu šim procesam - kas ir Atbildīgais, Pārskatāmais, Konsultētais un Informētais.</v>
+        <v>Procesa RACI</v>
       </c>
     </row>
     <row r="3422">
       <c r="A3422" t="str">
-        <v>Person kept up-to-date on progress</v>
+        <v>Process characteristics</v>
       </c>
       <c r="B3422" t="str">
-        <v>الشخص الذي يتم إطلاعه على التقدم</v>
+        <v>خصائص العملية</v>
       </c>
       <c r="C3422" t="str">
-        <v>Persona, kas tiek informēta par progresu</v>
+        <v>Procesa raksturlielumi</v>
       </c>
     </row>
     <row r="3423">
       <c r="A3423" t="str">
-        <v>Person ultimately answerable</v>
+        <v>Add files to attach to this process. Files will be uploaded when you save.</v>
       </c>
       <c r="B3423" t="str">
-        <v>الشخص المسؤول النهائي</v>
+        <v>أضف ملفات لإرفاقها بهذه العملية. سيتم رفع الملفات عند الحفظ.</v>
       </c>
       <c r="C3423" t="str">
-        <v>Persona, kas ir galīgi atbildīga</v>
+        <v>Pievienojiet failus šim procesam. Faili tiks augšupielādēti saglabājot.</v>
       </c>
     </row>
     <row r="3424">
       <c r="A3424" t="str">
-        <v>Person who does the work</v>
+        <v>Define the RACI matrix for this process - who is Responsible, Accountable, Consulted, and Informed.</v>
       </c>
       <c r="B3424" t="str">
-        <v>الشخص الذي يقوم بالعمل</v>
+        <v>حدد مصفوفة راسي لهذه العملية - من هو المسؤول والمساءل والمستشار والمطلع.</v>
       </c>
       <c r="C3424" t="str">
-        <v>Persona, kas veic darbu</v>
+        <v>Definējiet RACI matricu šim procesam - kas ir Atbildīgais, Pārskatāmais, Konsultētais un Informētais.</v>
       </c>
     </row>
     <row r="3425">
       <c r="A3425" t="str">
-        <v>Person whose input is sought</v>
+        <v>Person kept up-to-date on progress</v>
       </c>
       <c r="B3425" t="str">
-        <v>الشخص الذي يُطلب رأيه</v>
+        <v>الشخص الذي يتم إطلاعه على التقدم</v>
       </c>
       <c r="C3425" t="str">
-        <v>Persona, kuras ieguldījums tiek meklēts</v>
+        <v>Persona, kas tiek informēta par progresu</v>
       </c>
     </row>
     <row r="3426">
       <c r="A3426" t="str">
-        <v>Roles and responsibilities</v>
+        <v>Person ultimately answerable</v>
       </c>
       <c r="B3426" t="str">
-        <v>الأدوار والمسؤوليات</v>
+        <v>الشخص المسؤول النهائي</v>
       </c>
       <c r="C3426" t="str">
-        <v>Lomas un pienākumi</v>
+        <v>Persona, kas ir galīgi atbildīga</v>
       </c>
     </row>
     <row r="3427">
       <c r="A3427" t="str">
-        <v>Upload employee onboarding documents for this process. Multiple files can be attached.</v>
+        <v>Person who does the work</v>
       </c>
       <c r="B3427" t="str">
-        <v>ارفع مستندات تأهيل الموظفين لهذه العملية. يمكن إرفاق ملفات متعددة.</v>
+        <v>الشخص الذي يقوم بالعمل</v>
       </c>
       <c r="C3427" t="str">
-        <v>Augšupielādējiet darbinieku ievadīšanas dokumentus šim procesam. Var pievienot vairākus failus.</v>
+        <v>Persona, kas veic darbu</v>
       </c>
     </row>
     <row r="3428">
       <c r="A3428" t="str">
-        <v>Onboarding Files</v>
+        <v>Person whose input is sought</v>
       </c>
       <c r="B3428" t="str">
-        <v>ملفات التأهيل</v>
+        <v>الشخص الذي يُطلب رأيه</v>
       </c>
       <c r="C3428" t="str">
-        <v>Ievadīšanas faili</v>
+        <v>Persona, kuras ieguldījums tiek meklēts</v>
       </c>
     </row>
     <row r="3429">
       <c r="A3429" t="str">
-        <v>Onboarding Files to Upload</v>
+        <v>Roles and responsibilities</v>
       </c>
       <c r="B3429" t="str">
-        <v>ملفات التأهيل للرفع</v>
+        <v>الأدوار والمسؤوليات</v>
       </c>
       <c r="C3429" t="str">
-        <v>Augšupielādējamie ievadīšanas faili</v>
+        <v>Lomas un pienākumi</v>
       </c>
     </row>
     <row r="3430">
       <c r="A3430" t="str">
-        <v>Add RPO Label</v>
+        <v>Upload employee onboarding documents for this process. Multiple files can be attached.</v>
       </c>
       <c r="B3430" t="str">
-        <v>إضافة تسمية نقطة الاسترداد</v>
+        <v>ارفع مستندات تأهيل الموظفين لهذه العملية. يمكن إرفاق ملفات متعددة.</v>
       </c>
       <c r="C3430" t="str">
-        <v>Pievienot RPO apzīmējumu</v>
+        <v>Augšupielādējiet darbinieku ievadīšanas dokumentus šim procesam. Var pievienot vairākus failus.</v>
       </c>
     </row>
     <row r="3431">
       <c r="A3431" t="str">
-        <v>Add RTO Label</v>
+        <v>Onboarding Files</v>
       </c>
       <c r="B3431" t="str">
-        <v>إضافة تسمية وقت الاسترداد</v>
+        <v>ملفات التأهيل</v>
       </c>
       <c r="C3431" t="str">
-        <v>Pievienot RTO apzīmējumu</v>
+        <v>Ievadīšanas faili</v>
       </c>
     </row>
     <row r="3432">
       <c r="A3432" t="str">
-        <v>RPO</v>
+        <v>Onboarding Files to Upload</v>
       </c>
       <c r="B3432" t="str">
-        <v>نقطة الاسترداد</v>
+        <v>ملفات التأهيل للرفع</v>
       </c>
       <c r="C3432" t="str">
-        <v>RPO</v>
+        <v>Augšupielādējamie ievadīšanas faili</v>
       </c>
     </row>
     <row r="3433">
       <c r="A3433" t="str">
-        <v>RPO Labels</v>
+        <v>Add RPO Label</v>
       </c>
       <c r="B3433" t="str">
-        <v>تسميات نقطة الاسترداد</v>
+        <v>إضافة تسمية نقطة الاسترداد</v>
       </c>
       <c r="C3433" t="str">
-        <v>RPO apzīmējumi</v>
+        <v>Pievienot RPO apzīmējumu</v>
       </c>
     </row>
     <row r="3434">
       <c r="A3434" t="str">
-        <v>RPO defines the maximum acceptable data loss measured in time. Configure labels to standardize RPO options across your organization.</v>
+        <v>Add RTO Label</v>
       </c>
       <c r="B3434" t="str">
-        <v>تحدد نقطة الاسترداد الحد الأقصى المقبول لفقدان البيانات المقاس بالوقت. قم بتكوين التسميات لتوحيد خيارات نقطة الاسترداد عبر مؤسستك.</v>
+        <v>إضافة تسمية وقت الاسترداد</v>
       </c>
       <c r="C3434" t="str">
-        <v>RPO nosaka maksimāli pieļaujamo datu zudumu, mērot laikā. Konfigurējiet apzīmējumus, lai standartizētu RPO opcijas visā organizācijā.</v>
+        <v>Pievienot RTO apzīmējumu</v>
       </c>
     </row>
     <row r="3435">
       <c r="A3435" t="str">
-        <v>RTO</v>
+        <v>RPO</v>
       </c>
       <c r="B3435" t="str">
-        <v>وقت الاسترداد</v>
+        <v>نقطة الاسترداد</v>
       </c>
       <c r="C3435" t="str">
-        <v>RTO</v>
+        <v>RPO</v>
       </c>
     </row>
     <row r="3436">
       <c r="A3436" t="str">
-        <v>RTO Labels</v>
+        <v>RPO Labels</v>
       </c>
       <c r="B3436" t="str">
-        <v>تسميات وقت الاسترداد</v>
+        <v>تسميات نقطة الاسترداد</v>
       </c>
       <c r="C3436" t="str">
-        <v>RTO apzīmējumi</v>
+        <v>RPO apzīmējumi</v>
       </c>
     </row>
     <row r="3437">
       <c r="A3437" t="str">
-        <v>RTO defines the maximum acceptable time to restore a process after a disruption. Configure labels to standardize RTO options across your organization.</v>
+        <v>RPO defines the maximum acceptable data loss measured in time. Configure labels to standardize RPO options across your organization.</v>
       </c>
       <c r="B3437" t="str">
-        <v>يحدد وقت الاسترداد الحد الأقصى المقبول لاستعادة العملية بعد الانقطاع. قم بتكوين التسميات لتوحيد خيارات وقت الاسترداد عبر مؤسستك.</v>
+        <v>تحدد نقطة الاسترداد الحد الأقصى المقبول لفقدان البيانات المقاس بالوقت. قم بتكوين التسميات لتوحيد خيارات نقطة الاسترداد عبر مؤسستك.</v>
       </c>
       <c r="C3437" t="str">
-        <v>RTO nosaka maksimāli pieļaujamo laiku procesa atjaunošanai pēc traucējuma. Konfigurējiet apzīmējumus, lai standartizētu RTO opcijas visā organizācijā.</v>
+        <v>RPO nosaka maksimāli pieļaujamo datu zudumu, mērot laikā. Konfigurējiet apzīmējumus, lai standartizētu RPO opcijas visā organizācijā.</v>
       </c>
     </row>
     <row r="3438">
       <c r="A3438" t="str">
-        <v>Recovery Point Objective (RPO)</v>
+        <v>RTO</v>
       </c>
       <c r="B3438" t="str">
-        <v>هدف نقطة الاسترداد (RPO)</v>
+        <v>وقت الاسترداد</v>
       </c>
       <c r="C3438" t="str">
-        <v>Atjaunošanas punkta mērķis (RPO)</v>
+        <v>RTO</v>
       </c>
     </row>
     <row r="3439">
       <c r="A3439" t="str">
-        <v>Recovery Time Objective (RTO)</v>
+        <v>RTO Labels</v>
       </c>
       <c r="B3439" t="str">
-        <v>هدف وقت الاسترداد (RTO)</v>
+        <v>تسميات وقت الاسترداد</v>
       </c>
       <c r="C3439" t="str">
-        <v>Atjaunošanas laika mērķis (RTO)</v>
+        <v>RTO apzīmējumi</v>
       </c>
     </row>
     <row r="3440">
       <c r="A3440" t="str">
-        <v>Create a new Recovery Point Objective label</v>
+        <v>RTO defines the maximum acceptable time to restore a process after a disruption. Configure labels to standardize RTO options across your organization.</v>
       </c>
       <c r="B3440" t="str">
-        <v>إنشاء تسمية جديدة لهدف نقطة الاسترداد</v>
+        <v>يحدد وقت الاسترداد الحد الأقصى المقبول لاستعادة العملية بعد الانقطاع. قم بتكوين التسميات لتوحيد خيارات وقت الاسترداد عبر مؤسستك.</v>
       </c>
       <c r="C3440" t="str">
-        <v>Izveidot jaunu RPO apzīmējumu</v>
+        <v>RTO nosaka maksimāli pieļaujamo laiku procesa atjaunošanai pēc traucējuma. Konfigurējiet apzīmējumus, lai standartizētu RTO opcijas visā organizācijā.</v>
       </c>
     </row>
     <row r="3441">
       <c r="A3441" t="str">
-        <v>Create a new Recovery Time Objective label</v>
+        <v>Recovery Point Objective (RPO)</v>
       </c>
       <c r="B3441" t="str">
-        <v>إنشاء تسمية جديدة لهدف وقت الاسترداد</v>
+        <v>هدف نقطة الاسترداد (RPO)</v>
       </c>
       <c r="C3441" t="str">
-        <v>Izveidot jaunu RTO apzīmējumu</v>
+        <v>Atjaunošanas punkta mērķis (RPO)</v>
       </c>
     </row>
     <row r="3442">
       <c r="A3442" t="str">
-        <v>Time Value</v>
+        <v>Recovery Time Objective (RTO)</v>
       </c>
       <c r="B3442" t="str">
-        <v>قيمة الوقت</v>
+        <v>هدف وقت الاسترداد (RTO)</v>
       </c>
       <c r="C3442" t="str">
-        <v>Laika vērtība</v>
+        <v>Atjaunošanas laika mērķis (RTO)</v>
       </c>
     </row>
     <row r="3443">
       <c r="A3443" t="str">
-        <v>Time Value (in hours)</v>
+        <v>Create a new Recovery Point Objective label</v>
       </c>
       <c r="B3443" t="str">
-        <v>قيمة الوقت (بالساعات)</v>
+        <v>إنشاء تسمية جديدة لهدف نقطة الاسترداد</v>
       </c>
       <c r="C3443" t="str">
-        <v>Laika vērtība (stundās)</v>
+        <v>Izveidot jaunu RPO apzīmējumu</v>
       </c>
     </row>
     <row r="3444">
       <c r="A3444" t="str">
-        <v>Enter value in hours. Use 0.5 for 30 minutes, 0.25 for 15 minutes, etc.</v>
+        <v>Create a new Recovery Time Objective label</v>
       </c>
       <c r="B3444" t="str">
-        <v>أدخل القيمة بالساعات. استخدم 0.5 لـ 30 دقيقة، 0.25 لـ 15 دقيقة، إلخ.</v>
+        <v>إنشاء تسمية جديدة لهدف وقت الاسترداد</v>
       </c>
       <c r="C3444" t="str">
-        <v>Ievadiet vērtību stundās. Izmantojiet 0.5 par 30 minūtēm, 0.25 par 15 minūtēm utt.</v>
+        <v>Izveidot jaunu RTO apzīmējumu</v>
       </c>
     </row>
     <row r="3445">
       <c r="A3445" t="str">
-        <v>Add Range</v>
+        <v>Time Value</v>
       </c>
       <c r="B3445" t="str">
-        <v>إضافة نطاق</v>
+        <v>قيمة الوقت</v>
       </c>
       <c r="C3445" t="str">
-        <v>Pievienot diapazonu</v>
+        <v>Laika vērtība</v>
       </c>
     </row>
     <row r="3446">
       <c r="A3446" t="str">
-        <v>Add Rating</v>
+        <v>Time Value (in hours)</v>
       </c>
       <c r="B3446" t="str">
-        <v>إضافة تقييم</v>
+        <v>قيمة الوقت (بالساعات)</v>
       </c>
       <c r="C3446" t="str">
-        <v>Pievienot vērtējumu</v>
+        <v>Laika vērtība (stundās)</v>
       </c>
     </row>
     <row r="3447">
       <c r="A3447" t="str">
-        <v>Criticality Label</v>
+        <v>Enter value in hours. Use 0.5 for 30 minutes, 0.25 for 15 minutes, etc.</v>
       </c>
       <c r="B3447" t="str">
-        <v>تسمية الحرجية</v>
+        <v>أدخل القيمة بالساعات. استخدم 0.5 لـ 30 دقيقة، 0.25 لـ 15 دقيقة، إلخ.</v>
       </c>
       <c r="C3447" t="str">
-        <v>Kritiskuma apzīmējums</v>
+        <v>Ievadiet vērtību stundās. Izmantojiet 0.5 par 30 minūtēm, 0.25 par 15 minūtēm utt.</v>
       </c>
     </row>
     <row r="3448">
       <c r="A3448" t="str">
-        <v>Criticality Ranges</v>
+        <v>Add Range</v>
       </c>
       <c r="B3448" t="str">
-        <v>نطاقات الحرجية</v>
+        <v>إضافة نطاق</v>
       </c>
       <c r="C3448" t="str">
-        <v>Kritiskuma diapazoni</v>
+        <v>Pievienot diapazonu</v>
       </c>
     </row>
     <row r="3449">
       <c r="A3449" t="str">
-        <v>Edit Scoring Range</v>
+        <v>Add Rating</v>
       </c>
       <c r="B3449" t="str">
-        <v>تعديل نطاق التقييم</v>
+        <v>إضافة تقييم</v>
       </c>
       <c r="C3449" t="str">
-        <v>Rediģēt vērtēšanas diapazonu</v>
+        <v>Pievienot vērtējumu</v>
       </c>
     </row>
     <row r="3450">
       <c r="A3450" t="str">
-        <v>Max Score</v>
+        <v>Criticality Label</v>
       </c>
       <c r="B3450" t="str">
-        <v>الحد الأقصى للنقاط</v>
+        <v>تسمية الحرجية</v>
       </c>
       <c r="C3450" t="str">
-        <v>Maksimālais punktu skaits</v>
+        <v>Kritiskuma apzīmējums</v>
       </c>
     </row>
     <row r="3451">
       <c r="A3451" t="str">
-        <v>Min Score</v>
+        <v>Criticality Ranges</v>
       </c>
       <c r="B3451" t="str">
-        <v>الحد الأدنى للنقاط</v>
+        <v>نطاقات الحرجية</v>
       </c>
       <c r="C3451" t="str">
-        <v>Minimālais punktu skaits</v>
+        <v>Kritiskuma diapazoni</v>
       </c>
     </row>
     <row r="3452">
       <c r="A3452" t="str">
-        <v>Range</v>
+        <v>Edit Scoring Range</v>
       </c>
       <c r="B3452" t="str">
-        <v>نطاق</v>
+        <v>تعديل نطاق التقييم</v>
       </c>
       <c r="C3452" t="str">
-        <v>Diapazons</v>
+        <v>Rediģēt vērtēšanas diapazonu</v>
       </c>
     </row>
     <row r="3453">
       <c r="A3453" t="str">
-        <v>Rating Label</v>
+        <v>Max Score</v>
       </c>
       <c r="B3453" t="str">
-        <v>تسمية التقييم</v>
+        <v>الحد الأقصى للنقاط</v>
       </c>
       <c r="C3453" t="str">
-        <v>Vērtējuma apzīmējums</v>
+        <v>Maksimālais punktu skaits</v>
       </c>
     </row>
     <row r="3454">
       <c r="A3454" t="str">
-        <v>Rating Methodology</v>
+        <v>Min Score</v>
       </c>
       <c r="B3454" t="str">
-        <v>منهجية التقييم</v>
+        <v>الحد الأدنى للنقاط</v>
       </c>
       <c r="C3454" t="str">
-        <v>Vērtēšanas metodoloģija</v>
+        <v>Minimālais punktu skaits</v>
       </c>
     </row>
     <row r="3455">
       <c r="A3455" t="str">
-        <v>Score Value</v>
+        <v>Range</v>
       </c>
       <c r="B3455" t="str">
-        <v>قيمة النقاط</v>
+        <v>نطاق</v>
       </c>
       <c r="C3455" t="str">
-        <v>Punktu vērtība</v>
+        <v>Diapazons</v>
       </c>
     </row>
     <row r="3456">
       <c r="A3456" t="str">
-        <v>Sort Order</v>
+        <v>Rating Label</v>
       </c>
       <c r="B3456" t="str">
-        <v>ترتيب الفرز</v>
+        <v>تسمية التقييم</v>
       </c>
       <c r="C3456" t="str">
-        <v>Kārtošanas secība</v>
+        <v>Vērtējuma apzīmējums</v>
       </c>
     </row>
     <row r="3457">
       <c r="A3457" t="str">
-        <v>Define a criticality level based on score range</v>
+        <v>Rating Methodology</v>
       </c>
       <c r="B3457" t="str">
-        <v>تحديد مستوى حرجية بناءً على نطاق النقاط</v>
+        <v>منهجية التقييم</v>
       </c>
       <c r="C3457" t="str">
-        <v>Definēt kritiskuma līmeni, pamatojoties uz punktu diapazonu</v>
+        <v>Vērtēšanas metodoloģija</v>
       </c>
     </row>
     <row r="3458">
       <c r="A3458" t="str">
-        <v>Define score ranges to determine process criticality levels</v>
+        <v>Score Value</v>
       </c>
       <c r="B3458" t="str">
-        <v>تحديد نطاقات النقاط لتحديد مستويات حرجية العملية</v>
+        <v>قيمة النقاط</v>
       </c>
       <c r="C3458" t="str">
-        <v>Definēt punktu diapazonus procesu kritiskuma līmeņu noteikšanai</v>
+        <v>Punktu vērtība</v>
       </c>
     </row>
     <row r="3459">
       <c r="A3459" t="str">
-        <v>Impact description for this rating</v>
+        <v>Sort Order</v>
       </c>
       <c r="B3459" t="str">
-        <v>وصف التأثير لهذا التقييم</v>
+        <v>ترتيب الفرز</v>
       </c>
       <c r="C3459" t="str">
-        <v>Ietekmes apraksts šim vērtējumam</v>
+        <v>Kārtošanas secība</v>
       </c>
     </row>
     <row r="3460">
       <c r="A3460" t="str">
-        <v>Addition of all (Sum)</v>
+        <v>Define a criticality level based on score range</v>
       </c>
       <c r="B3460" t="str">
-        <v>مجموع الكل (جمع)</v>
+        <v>تحديد مستوى حرجية بناءً على نطاق النقاط</v>
       </c>
       <c r="C3460" t="str">
-        <v>Visu saskaitīšana (summa)</v>
+        <v>Definēt kritiskuma līmeni, pamatojoties uz punktu diapazonu</v>
       </c>
     </row>
     <row r="3461">
       <c r="A3461" t="str">
-        <v>All category scores will be added together for the impact rating.</v>
+        <v>Define score ranges to determine process criticality levels</v>
       </c>
       <c r="B3461" t="str">
-        <v>سيتم جمع جميع درجات الفئات معاً لتقييم التأثير.</v>
+        <v>تحديد نطاقات النقاط لتحديد مستويات حرجية العملية</v>
       </c>
       <c r="C3461" t="str">
-        <v>Visi kategoriju punkti tiks saskaitīti ietekmes vērtējumam.</v>
+        <v>Definēt punktu diapazonus procesu kritiskuma līmeņu noteikšanai</v>
       </c>
     </row>
     <row r="3462">
       <c r="A3462" t="str">
-        <v>All category scores will be multiplied together for the impact rating.</v>
+        <v>Impact description for this rating</v>
       </c>
       <c r="B3462" t="str">
-        <v>سيتم ضرب جميع درجات الفئات معاً لتقييم التأثير.</v>
+        <v>وصف التأثير لهذا التقييم</v>
       </c>
       <c r="C3462" t="str">
-        <v>Visi kategoriju punkti tiks reizināti ietekmes vērtējumam.</v>
+        <v>Ietekmes apraksts šim vērtējumam</v>
       </c>
     </row>
     <row r="3463">
       <c r="A3463" t="str">
-        <v>High of all (Maximum)</v>
+        <v>Addition of all (Sum)</v>
       </c>
       <c r="B3463" t="str">
-        <v>الأعلى من الكل (الحد الأقصى)</v>
+        <v>مجموع الكل (جمع)</v>
       </c>
       <c r="C3463" t="str">
-        <v>Augstākais no visiem (Maksimums)</v>
+        <v>Visu saskaitīšana (summa)</v>
       </c>
     </row>
     <row r="3464">
       <c r="A3464" t="str">
-        <v>Note: Product of all ratings will be calculated</v>
+        <v>All category scores will be added together for the impact rating.</v>
       </c>
       <c r="B3464" t="str">
-        <v>ملاحظة: سيتم حساب حاصل ضرب جميع التقييمات</v>
+        <v>سيتم جمع جميع درجات الفئات معاً لتقييم التأثير.</v>
       </c>
       <c r="C3464" t="str">
-        <v>Piezīme: tiks aprēķināts visu vērtējumu reizinājums</v>
+        <v>Visi kategoriju punkti tiks saskaitīti ietekmes vērtējumam.</v>
       </c>
     </row>
     <row r="3465">
       <c r="A3465" t="str">
-        <v>Note: Sum of all ratings will be calculated</v>
+        <v>All category scores will be multiplied together for the impact rating.</v>
       </c>
       <c r="B3465" t="str">
-        <v>ملاحظة: سيتم حساب مجموع جميع التقييمات</v>
+        <v>سيتم ضرب جميع درجات الفئات معاً لتقييم التأثير.</v>
       </c>
       <c r="C3465" t="str">
-        <v>Piezīme: tiks aprēķināta visu vērtējumu summa</v>
+        <v>Visi kategoriju punkti tiks reizināti ietekmes vērtējumam.</v>
       </c>
     </row>
     <row r="3466">
       <c r="A3466" t="str">
-        <v>Product of all (Multiply)</v>
+        <v>High of all (Maximum)</v>
       </c>
       <c r="B3466" t="str">
-        <v>حاصل ضرب الكل (ضرب)</v>
+        <v>الأعلى من الكل (الحد الأقصى)</v>
       </c>
       <c r="C3466" t="str">
-        <v>Visu reizinājums (reizināšana)</v>
+        <v>Augstākais no visiem (Maksimums)</v>
       </c>
     </row>
     <row r="3467">
       <c r="A3467" t="str">
-        <v>The highest score among all categories will be used as the impact rating.</v>
+        <v>Note: Product of all ratings will be calculated</v>
       </c>
       <c r="B3467" t="str">
-        <v>سيتم استخدام أعلى درجة بين جميع الفئات كتقييم للتأثير.</v>
+        <v>ملاحظة: سيتم حساب حاصل ضرب جميع التقييمات</v>
       </c>
       <c r="C3467" t="str">
-        <v>Augstākais punktu skaits starp visām kategorijām tiks izmantots kā ietekmes vērtējums.</v>
+        <v>Piezīme: tiks aprēķināts visu vērtējumu reizinājums</v>
       </c>
     </row>
     <row r="3468">
       <c r="A3468" t="str">
-        <v>Select calculation type</v>
+        <v>Note: Sum of all ratings will be calculated</v>
       </c>
       <c r="B3468" t="str">
-        <v>اختر نوع الحساب</v>
+        <v>ملاحظة: سيتم حساب مجموع جميع التقييمات</v>
       </c>
       <c r="C3468" t="str">
-        <v>Atlasīt aprēķina veidu</v>
+        <v>Piezīme: tiks aprēķināta visu vērtējumu summa</v>
       </c>
     </row>
     <row r="3469">
       <c r="A3469" t="str">
-        <v>CMM Maturity Level Descriptions</v>
+        <v>Product of all (Multiply)</v>
       </c>
       <c r="B3469" t="str">
-        <v>أوصاف مستويات نضج CMM</v>
+        <v>حاصل ضرب الكل (ضرب)</v>
       </c>
       <c r="C3469" t="str">
-        <v>CMM brieduma līmeņu apraksti</v>
+        <v>Visu reizinājums (reizināšana)</v>
       </c>
     </row>
     <row r="3470">
       <c r="A3470" t="str">
-        <v>Level 0 - Not Performed</v>
+        <v>The highest score among all categories will be used as the impact rating.</v>
       </c>
       <c r="B3470" t="str">
-        <v>المستوى 0 - لم يُنفذ</v>
+        <v>سيتم استخدام أعلى درجة بين جميع الفئات كتقييم للتأثير.</v>
       </c>
       <c r="C3470" t="str">
-        <v>0. līmenis - Nav izpildīts</v>
+        <v>Augstākais punktu skaits starp visām kategorijām tiks izmantots kā ietekmes vērtējums.</v>
       </c>
     </row>
     <row r="3471">
       <c r="A3471" t="str">
-        <v>Level 1 - Performed Informally</v>
+        <v>Select calculation type</v>
       </c>
       <c r="B3471" t="str">
-        <v>المستوى 1 - نُفذ بشكل غير رسمي</v>
+        <v>اختر نوع الحساب</v>
       </c>
       <c r="C3471" t="str">
-        <v>1. līmenis - Izpildīts neformāli</v>
+        <v>Atlasīt aprēķina veidu</v>
       </c>
     </row>
     <row r="3472">
       <c r="A3472" t="str">
-        <v>Level 2 - Planned and Tracked</v>
+        <v>CMM Maturity Level Descriptions</v>
       </c>
       <c r="B3472" t="str">
-        <v>المستوى 2 - مخطط ومتابع</v>
+        <v>أوصاف مستويات نضج CMM</v>
       </c>
       <c r="C3472" t="str">
-        <v>2. līmenis - Plānots un izsekots</v>
+        <v>CMM brieduma līmeņu apraksti</v>
       </c>
     </row>
     <row r="3473">
       <c r="A3473" t="str">
-        <v>Level 3 - Well Defined</v>
+        <v>Level 0 - Not Performed</v>
       </c>
       <c r="B3473" t="str">
-        <v>المستوى 3 - محدد بشكل جيد</v>
+        <v>المستوى 0 - لم يُنفذ</v>
       </c>
       <c r="C3473" t="str">
-        <v>3. līmenis - Labi definēts</v>
+        <v>0. līmenis - Nav izpildīts</v>
       </c>
     </row>
     <row r="3474">
       <c r="A3474" t="str">
-        <v>Level 4 - Quantitatively Controlled</v>
+        <v>Level 1 - Performed Informally</v>
       </c>
       <c r="B3474" t="str">
-        <v>المستوى 4 - مُسيطر عليه كمياً</v>
+        <v>المستوى 1 - نُفذ بشكل غير رسمي</v>
       </c>
       <c r="C3474" t="str">
-        <v>4. līmenis - Kvantitatīvi kontrolēts</v>
+        <v>1. līmenis - Izpildīts neformāli</v>
       </c>
     </row>
     <row r="3475">
       <c r="A3475" t="str">
-        <v>Level 5 - Continuously Improving</v>
+        <v>Level 2 - Planned and Tracked</v>
       </c>
       <c r="B3475" t="str">
-        <v>المستوى 5 - تحسين مستمر</v>
+        <v>المستوى 2 - مخطط ومتابع</v>
       </c>
       <c r="C3475" t="str">
-        <v>5. līmenis - Nepārtraukti uzlabojas</v>
+        <v>2. līmenis - Plānots un izsekots</v>
       </c>
     </row>
     <row r="3476">
       <c r="A3476" t="str">
-        <v>Add New Control</v>
+        <v>Level 3 - Well Defined</v>
       </c>
       <c r="B3476" t="str">
-        <v>إضافة ضابط جديد</v>
+        <v>المستوى 3 - محدد بشكل جيد</v>
       </c>
       <c r="C3476" t="str">
-        <v>Pievienot jaunu kontroli</v>
+        <v>3. līmenis - Labi definēts</v>
       </c>
     </row>
     <row r="3477">
       <c r="A3477" t="str">
-        <v>Choose Control</v>
+        <v>Level 4 - Quantitatively Controlled</v>
       </c>
       <c r="B3477" t="str">
-        <v>اختر ضابطاً</v>
+        <v>المستوى 4 - مُسيطر عليه كمياً</v>
       </c>
       <c r="C3477" t="str">
-        <v>Izvēlieties kontroli</v>
+        <v>4. līmenis - Kvantitatīvi kontrolēts</v>
       </c>
     </row>
     <row r="3478">
       <c r="A3478" t="str">
-        <v>Control Compliance</v>
+        <v>Level 5 - Continuously Improving</v>
       </c>
       <c r="B3478" t="str">
-        <v>امتثال الضوابط</v>
+        <v>المستوى 5 - تحسين مستمر</v>
       </c>
       <c r="C3478" t="str">
-        <v>Kontroles atbilstība</v>
+        <v>5. līmenis - Nepārtraukti uzlabojas</v>
       </c>
     </row>
     <row r="3479">
       <c r="A3479" t="str">
-        <v>Control Not Found</v>
+        <v>Add New Control</v>
       </c>
       <c r="B3479" t="str">
-        <v>لم يتم العثور على الضابط</v>
+        <v>إضافة ضابط جديد</v>
       </c>
       <c r="C3479" t="str">
-        <v>Kontrole nav atrasta</v>
+        <v>Pievienot jaunu kontroli</v>
       </c>
     </row>
     <row r="3480">
       <c r="A3480" t="str">
-        <v>Create Exception</v>
+        <v>Choose Control</v>
       </c>
       <c r="B3480" t="str">
-        <v>إنشاء استثناء</v>
+        <v>اختر ضابطاً</v>
       </c>
       <c r="C3480" t="str">
-        <v>Izveidot izņēmumu</v>
+        <v>Izvēlieties kontroli</v>
       </c>
     </row>
     <row r="3481">
       <c r="A3481" t="str">
-        <v>Create Framework</v>
+        <v>Control Compliance</v>
       </c>
       <c r="B3481" t="str">
-        <v>إنشاء إطار عمل</v>
+        <v>امتثال الضوابط</v>
       </c>
       <c r="C3481" t="str">
-        <v>Izveidot ietvaru</v>
+        <v>Kontroles atbilstība</v>
       </c>
     </row>
     <row r="3482">
       <c r="A3482" t="str">
-        <v>Edit Framework</v>
+        <v>Control Not Found</v>
       </c>
       <c r="B3482" t="str">
-        <v>تعديل إطار العمل</v>
+        <v>لم يتم العثور على الضابط</v>
       </c>
       <c r="C3482" t="str">
-        <v>Rediģēt ietvaru</v>
+        <v>Kontrole nav atrasta</v>
       </c>
     </row>
     <row r="3483">
       <c r="A3483" t="str">
-        <v>Edit SOA Entry</v>
+        <v>Create Exception</v>
       </c>
       <c r="B3483" t="str">
-        <v>تعديل إدخال بيان التطبيق</v>
+        <v>إنشاء استثناء</v>
       </c>
       <c r="C3483" t="str">
-        <v>Rediģēt SOA ierakstu</v>
+        <v>Izveidot izņēmumu</v>
       </c>
     </row>
     <row r="3484">
       <c r="A3484" t="str">
-        <v>Exception Details</v>
+        <v>Create Framework</v>
       </c>
       <c r="B3484" t="str">
-        <v>تفاصيل الاستثناء</v>
+        <v>إنشاء إطار عمل</v>
       </c>
       <c r="C3484" t="str">
-        <v>Izņēmuma detaļas</v>
+        <v>Izveidot ietvaru</v>
       </c>
     </row>
     <row r="3485">
       <c r="A3485" t="str">
-        <v>Export SOA</v>
+        <v>Edit Framework</v>
       </c>
       <c r="B3485" t="str">
-        <v>تصدير بيان التطبيق</v>
+        <v>تعديل إطار العمل</v>
       </c>
       <c r="C3485" t="str">
-        <v>Eksportēt SOA</v>
+        <v>Rediģēt ietvaru</v>
       </c>
     </row>
     <row r="3486">
       <c r="A3486" t="str">
-        <v>Implementation Status</v>
+        <v>Edit SOA Entry</v>
       </c>
       <c r="B3486" t="str">
-        <v>حالة التنفيذ</v>
+        <v>تعديل إدخال بيان التطبيق</v>
       </c>
       <c r="C3486" t="str">
-        <v>Ieviešanas statuss</v>
+        <v>Rediģēt SOA ierakstu</v>
       </c>
     </row>
     <row r="3487">
       <c r="A3487" t="str">
-        <v>Import Requirements</v>
+        <v>Exception Details</v>
       </c>
       <c r="B3487" t="str">
-        <v>استيراد المتطلبات</v>
+        <v>تفاصيل الاستثناء</v>
       </c>
       <c r="C3487" t="str">
-        <v>Importēt prasības</v>
+        <v>Izņēmuma detaļas</v>
       </c>
     </row>
     <row r="3488">
       <c r="A3488" t="str">
-        <v>Manage framework requirements and controls</v>
+        <v>Export SOA</v>
       </c>
       <c r="B3488" t="str">
-        <v>إدارة متطلبات وضوابط الإطار</v>
+        <v>تصدير بيان التطبيق</v>
       </c>
       <c r="C3488" t="str">
-        <v>Pārvaldīt ietvara prasības un kontroles</v>
+        <v>Eksportēt SOA</v>
       </c>
     </row>
     <row r="3489">
       <c r="A3489" t="str">
-        <v>Manage requirement applicability and implementation status</v>
+        <v>Implementation Status</v>
       </c>
       <c r="B3489" t="str">
-        <v>إدارة تطبيقية المتطلبات وحالة التنفيذ</v>
+        <v>حالة التنفيذ</v>
       </c>
       <c r="C3489" t="str">
-        <v>Pārvaldīt prasību piemērojamību un ieviešanas statusu</v>
+        <v>Ieviešanas statuss</v>
       </c>
     </row>
     <row r="3490">
       <c r="A3490" t="str">
-        <v>Not Implemented</v>
+        <v>Import Requirements</v>
       </c>
       <c r="B3490" t="str">
-        <v>غير منفذ</v>
+        <v>استيراد المتطلبات</v>
       </c>
       <c r="C3490" t="str">
-        <v>Nav ieviests</v>
+        <v>Importēt prasības</v>
       </c>
     </row>
     <row r="3491">
       <c r="A3491" t="str">
-        <v>Overall Control Rating</v>
+        <v>Manage framework requirements and controls</v>
       </c>
       <c r="B3491" t="str">
-        <v>التقييم العام للضوابط</v>
+        <v>إدارة متطلبات وضوابط الإطار</v>
       </c>
       <c r="C3491" t="str">
-        <v>Kopējais kontroles vērtējums</v>
+        <v>Pārvaldīt ietvara prasības un kontroles</v>
       </c>
     </row>
     <row r="3492">
       <c r="A3492" t="str">
-        <v>Partially Applicable</v>
+        <v>Manage requirement applicability and implementation status</v>
       </c>
       <c r="B3492" t="str">
-        <v>قابل للتطبيق جزئياً</v>
+        <v>إدارة تطبيقية المتطلبات وحالة التنفيذ</v>
       </c>
       <c r="C3492" t="str">
-        <v>Daļēji piemērojams</v>
+        <v>Pārvaldīt prasību piemērojamību un ieviešanas statusu</v>
       </c>
     </row>
     <row r="3493">
       <c r="A3493" t="str">
-        <v>Partially Implemented</v>
+        <v>Not Implemented</v>
       </c>
       <c r="B3493" t="str">
-        <v>منفذ جزئياً</v>
+        <v>غير منفذ</v>
       </c>
       <c r="C3493" t="str">
-        <v>Daļēji ieviests</v>
+        <v>Nav ieviests</v>
       </c>
     </row>
     <row r="3494">
       <c r="A3494" t="str">
-        <v>Please provide the following details to create a new compliance framework.</v>
+        <v>Overall Control Rating</v>
       </c>
       <c r="B3494" t="str">
-        <v>يرجى تقديم التفاصيل التالية لإنشاء إطار امتثال جديد.</v>
+        <v>التقييم العام للضوابط</v>
       </c>
       <c r="C3494" t="str">
-        <v>Lūdzu, norādiet šādu informāciju, lai izveidotu jaunu atbilstības ietvaru.</v>
+        <v>Kopējais kontroles vērtējums</v>
       </c>
     </row>
     <row r="3495">
       <c r="A3495" t="str">
-        <v>Provide justification for applicability decision</v>
+        <v>Partially Applicable</v>
       </c>
       <c r="B3495" t="str">
-        <v>قدم مبرراً لقرار التطبيقية</v>
+        <v>قابل للتطبيق جزئياً</v>
       </c>
       <c r="C3495" t="str">
-        <v>Norādiet pamatojumu piemērojamības lēmumam</v>
+        <v>Daļēji piemērojams</v>
       </c>
     </row>
     <row r="3496">
       <c r="A3496" t="str">
-        <v>Select applicability</v>
+        <v>Partially Implemented</v>
       </c>
       <c r="B3496" t="str">
-        <v>اختر التطبيقية</v>
+        <v>منفذ جزئياً</v>
       </c>
       <c r="C3496" t="str">
-        <v>Atlasīt piemērojamību</v>
+        <v>Daļēji ieviests</v>
       </c>
     </row>
     <row r="3497">
       <c r="A3497" t="str">
-        <v>Statement of Applicability</v>
+        <v>Please provide the following details to create a new compliance framework.</v>
       </c>
       <c r="B3497" t="str">
-        <v>بيان التطبيق</v>
+        <v>يرجى تقديم التفاصيل التالية لإنشاء إطار امتثال جديد.</v>
       </c>
       <c r="C3497" t="str">
-        <v>Piemērojamības paziņojums</v>
+        <v>Lūdzu, norādiet šādu informāciju, lai izveidotu jaunu atbilstības ietvaru.</v>
       </c>
     </row>
     <row r="3498">
       <c r="A3498" t="str">
-        <v>This framework has no requirements. Import requirements to enable SOA editing.</v>
+        <v>Provide justification for applicability decision</v>
       </c>
       <c r="B3498" t="str">
-        <v>لا يحتوي هذا الإطار على متطلبات. استورد المتطلبات لتمكين تحرير بيان التطبيق.</v>
+        <v>قدم مبرراً لقرار التطبيقية</v>
       </c>
       <c r="C3498" t="str">
-        <v>Šim ietvaram nav prasību. Importējiet prasības, lai iespējotu SOA rediģēšanu.</v>
+        <v>Norādiet pamatojumu piemērojamības lēmumam</v>
       </c>
     </row>
     <row r="3499">
       <c r="A3499" t="str">
-        <v>Total Requirements</v>
+        <v>Select applicability</v>
       </c>
       <c r="B3499" t="str">
-        <v>إجمالي المتطلبات</v>
+        <v>اختر التطبيقية</v>
       </c>
       <c r="C3499" t="str">
-        <v>Kopējās prasības</v>
+        <v>Atlasīt piemērojamību</v>
       </c>
     </row>
     <row r="3500">
       <c r="A3500" t="str">
-        <v>All frameworks</v>
+        <v>Statement of Applicability</v>
       </c>
       <c r="B3500" t="str">
-        <v>جميع الأطر</v>
+        <v>بيان التطبيق</v>
       </c>
       <c r="C3500" t="str">
-        <v>Visi ietvari</v>
+        <v>Piemērojamības paziņojums</v>
       </c>
     </row>
     <row r="3501">
       <c r="A3501" t="str">
-        <v>No requirements</v>
+        <v>This framework has no requirements. Import requirements to enable SOA editing.</v>
       </c>
       <c r="B3501" t="str">
-        <v>لا توجد متطلبات</v>
+        <v>لا يحتوي هذا الإطار على متطلبات. استورد المتطلبات لتمكين تحرير بيان التطبيق.</v>
       </c>
       <c r="C3501" t="str">
-        <v>Nav prasību</v>
+        <v>Šim ietvaram nav prasību. Importējiet prasības, lai iespējotu SOA rediģēšanu.</v>
       </c>
     </row>
     <row r="3502">
       <c r="A3502" t="str">
-        <v>No requirements available</v>
+        <v>Total Requirements</v>
       </c>
       <c r="B3502" t="str">
-        <v>لا تتوفر متطلبات</v>
+        <v>إجمالي المتطلبات</v>
       </c>
       <c r="C3502" t="str">
-        <v>Nav pieejamu prasību</v>
+        <v>Kopējās prasības</v>
       </c>
     </row>
     <row r="3503">
       <c r="A3503" t="str">
-        <v>No requirements found</v>
+        <v>All frameworks</v>
       </c>
       <c r="B3503" t="str">
-        <v>لم يتم العثور على متطلبات</v>
+        <v>جميع الأطر</v>
       </c>
       <c r="C3503" t="str">
-        <v>Prasības nav atrastas</v>
+        <v>Visi ietvari</v>
       </c>
     </row>
     <row r="3504">
       <c r="A3504" t="str">
-        <v>No frameworks found.</v>
+        <v>No requirements</v>
       </c>
       <c r="B3504" t="str">
-        <v>لم يتم العثور على أطر.</v>
+        <v>لا توجد متطلبات</v>
       </c>
       <c r="C3504" t="str">
-        <v>Ietvari nav atrasti.</v>
+        <v>Nav prasību</v>
       </c>
     </row>
     <row r="3505">
       <c r="A3505" t="str">
-        <v>Add controls to plan risk mitigation</v>
+        <v>No requirements available</v>
       </c>
       <c r="B3505" t="str">
-        <v>أضف ضوابط لتخطيط تخفيف المخاطر</v>
+        <v>لا تتوفر متطلبات</v>
       </c>
       <c r="C3505" t="str">
-        <v>Pievienojiet kontroles risku mazināšanas plānošanai</v>
+        <v>Nav pieejamu prasību</v>
       </c>
     </row>
     <row r="3506">
       <c r="A3506" t="str">
-        <v>Adding risks to your library...</v>
+        <v>No requirements found</v>
       </c>
       <c r="B3506" t="str">
-        <v>جاري إضافة المخاطر إلى مكتبتك...</v>
+        <v>لم يتم العثور على متطلبات</v>
       </c>
       <c r="C3506" t="str">
-        <v>Pievieno riskus jūsu bibliotēkai...</v>
+        <v>Prasības nav atrastas</v>
       </c>
     </row>
     <row r="3507">
       <c r="A3507" t="str">
-        <v>Click 'Confirm &amp; Register' to add these risks to your library.</v>
+        <v>No frameworks found.</v>
       </c>
       <c r="B3507" t="str">
-        <v>انقر "تأكيد وتسجيل" لإضافة هذه المخاطر إلى مكتبتك.</v>
+        <v>لم يتم العثور على أطر.</v>
       </c>
       <c r="C3507" t="str">
-        <v>Noklikšķiniet "Apstiprināt un reģistrēt", lai pievienotu šos riskus jūsu bibliotēkai.</v>
+        <v>Ietvari nav atrasti.</v>
       </c>
     </row>
     <row r="3508">
       <c r="A3508" t="str">
-        <v>Comparing with existing risk library...</v>
+        <v>Add controls to plan risk mitigation</v>
       </c>
       <c r="B3508" t="str">
-        <v>جاري المقارنة مع مكتبة المخاطر الحالية...</v>
+        <v>أضف ضوابط لتخطيط تخفيف المخاطر</v>
       </c>
       <c r="C3508" t="str">
-        <v>Salīdzina ar esošo risku bibliotēku...</v>
+        <v>Pievienojiet kontroles risku mazināšanas plānošanai</v>
       </c>
     </row>
     <row r="3509">
       <c r="A3509" t="str">
-        <v>Confirm &amp; Register</v>
+        <v>Adding risks to your library...</v>
       </c>
       <c r="B3509" t="str">
-        <v>تأكيد وتسجيل</v>
+        <v>جاري إضافة المخاطر إلى مكتبتك...</v>
       </c>
       <c r="C3509" t="str">
-        <v>Apstiprināt un reģistrēt</v>
+        <v>Pievieno riskus jūsu bibliotēkai...</v>
       </c>
     </row>
     <row r="3510">
       <c r="A3510" t="str">
-        <v>Existing Matches</v>
+        <v>Click 'Confirm &amp; Register' to add these risks to your library.</v>
       </c>
       <c r="B3510" t="str">
-        <v>التطابقات الحالية</v>
+        <v>انقر "تأكيد وتسجيل" لإضافة هذه المخاطر إلى مكتبتك.</v>
       </c>
       <c r="C3510" t="str">
-        <v>Esošās atbilstības</v>
+        <v>Noklikšķiniet "Apstiprināt un reģistrēt", lai pievienotu šos riskus jūsu bibliotēkai.</v>
       </c>
     </row>
     <row r="3511">
       <c r="A3511" t="str">
-        <v>Impact (1-5)</v>
+        <v>Comparing with existing risk library...</v>
       </c>
       <c r="B3511" t="str">
-        <v>التأثير (1-5)</v>
+        <v>جاري المقارنة مع مكتبة المخاطر الحالية...</v>
       </c>
       <c r="C3511" t="str">
-        <v>Ietekme (1-5)</v>
+        <v>Salīdzina ar esošo risku bibliotēku...</v>
       </c>
     </row>
     <row r="3512">
       <c r="A3512" t="str">
-        <v>Likelihood (1-5)</v>
+        <v>Confirm &amp; Register</v>
       </c>
       <c r="B3512" t="str">
-        <v>الاحتمالية (1-5)</v>
+        <v>تأكيد وتسجيل</v>
       </c>
       <c r="C3512" t="str">
-        <v>Iespējamība (1-5)</v>
+        <v>Apstiprināt un reģistrēt</v>
       </c>
     </row>
     <row r="3513">
       <c r="A3513" t="str">
-        <v>Likely</v>
+        <v>Existing Matches</v>
       </c>
       <c r="B3513" t="str">
-        <v>محتمل</v>
+        <v>التطابقات الحالية</v>
       </c>
       <c r="C3513" t="str">
-        <v>Ticams</v>
+        <v>Esošās atbilstības</v>
       </c>
     </row>
     <row r="3514">
       <c r="A3514" t="str">
-        <v>Match Preview</v>
+        <v>Impact (1-5)</v>
       </c>
       <c r="B3514" t="str">
-        <v>معاينة التطابق</v>
+        <v>التأثير (1-5)</v>
       </c>
       <c r="C3514" t="str">
-        <v>Atbilstības priekšskatījums</v>
+        <v>Ietekme (1-5)</v>
       </c>
     </row>
     <row r="3515">
       <c r="A3515" t="str">
-        <v>Match with Library</v>
+        <v>Likelihood (1-5)</v>
       </c>
       <c r="B3515" t="str">
-        <v>مطابقة مع المكتبة</v>
+        <v>الاحتمالية (1-5)</v>
       </c>
       <c r="C3515" t="str">
-        <v>Saskaņot ar bibliotēku</v>
+        <v>Iespējamība (1-5)</v>
       </c>
     </row>
     <row r="3516">
       <c r="A3516" t="str">
-        <v>Matched</v>
+        <v>Likely</v>
       </c>
       <c r="B3516" t="str">
-        <v>متطابق</v>
+        <v>محتمل</v>
       </c>
       <c r="C3516" t="str">
-        <v>Saskaņots</v>
+        <v>Ticams</v>
       </c>
     </row>
     <row r="3517">
       <c r="A3517" t="str">
-        <v>Matching Complete</v>
+        <v>Match Preview</v>
       </c>
       <c r="B3517" t="str">
-        <v>اكتملت المطابقة</v>
+        <v>معاينة التطابق</v>
       </c>
       <c r="C3517" t="str">
-        <v>Saskaņošana pabeigta</v>
+        <v>Atbilstības priekšskatījums</v>
       </c>
     </row>
     <row r="3518">
       <c r="A3518" t="str">
-        <v>Matching...</v>
+        <v>Match with Library</v>
       </c>
       <c r="B3518" t="str">
-        <v>جاري المطابقة...</v>
+        <v>مطابقة مع المكتبة</v>
       </c>
       <c r="C3518" t="str">
-        <v>Saskaņo...</v>
+        <v>Saskaņot ar bibliotēku</v>
       </c>
     </row>
     <row r="3519">
       <c r="A3519" t="str">
-        <v>New Controls</v>
+        <v>Matched</v>
       </c>
       <c r="B3519" t="str">
-        <v>ضوابط جديدة</v>
+        <v>متطابق</v>
       </c>
       <c r="C3519" t="str">
-        <v>Jaunas kontroles</v>
+        <v>Saskaņots</v>
       </c>
     </row>
     <row r="3520">
       <c r="A3520" t="str">
-        <v>New Risks</v>
+        <v>Matching Complete</v>
       </c>
       <c r="B3520" t="str">
-        <v>مخاطر جديدة</v>
+        <v>اكتملت المطابقة</v>
       </c>
       <c r="C3520" t="str">
-        <v>Jauni riski</v>
+        <v>Saskaņošana pabeigta</v>
       </c>
     </row>
     <row r="3521">
       <c r="A3521" t="str">
-        <v>New Threats</v>
+        <v>Matching...</v>
       </c>
       <c r="B3521" t="str">
-        <v>تهديدات جديدة</v>
+        <v>جاري المطابقة...</v>
       </c>
       <c r="C3521" t="str">
-        <v>Jauni draudi</v>
+        <v>Saskaņo...</v>
       </c>
     </row>
     <row r="3522">
       <c r="A3522" t="str">
-        <v>Planned Residual Risk Rating</v>
+        <v>New Controls</v>
       </c>
       <c r="B3522" t="str">
-        <v>تقييم المخاطر المتبقية المخطط لها</v>
+        <v>ضوابط جديدة</v>
       </c>
       <c r="C3522" t="str">
-        <v>Plānotais atlikušā riska vērtējums</v>
+        <v>Jaunas kontroles</v>
       </c>
     </row>
     <row r="3523">
       <c r="A3523" t="str">
-        <v>Position in Risk Matrix</v>
+        <v>New Risks</v>
       </c>
       <c r="B3523" t="str">
-        <v>الموقع في مصفوفة المخاطر</v>
+        <v>مخاطر جديدة</v>
       </c>
       <c r="C3523" t="str">
-        <v>Pozīcija risku matricā</v>
+        <v>Jauni riski</v>
       </c>
     </row>
     <row r="3524">
       <c r="A3524" t="str">
-        <v>Possible</v>
+        <v>New Threats</v>
       </c>
       <c r="B3524" t="str">
-        <v>ممكن</v>
+        <v>تهديدات جديدة</v>
       </c>
       <c r="C3524" t="str">
-        <v>Iespējams</v>
+        <v>Jauni draudi</v>
       </c>
     </row>
     <row r="3525">
       <c r="A3525" t="str">
-        <v>Rare</v>
+        <v>Planned Residual Risk Rating</v>
       </c>
       <c r="B3525" t="str">
-        <v>نادر</v>
+        <v>تقييم المخاطر المتبقية المخطط لها</v>
       </c>
       <c r="C3525" t="str">
-        <v>Reti</v>
+        <v>Plānotais atlikušā riska vērtējums</v>
       </c>
     </row>
     <row r="3526">
       <c r="A3526" t="str">
-        <v>Unlikely</v>
+        <v>Position in Risk Matrix</v>
       </c>
       <c r="B3526" t="str">
-        <v>غير محتمل</v>
+        <v>الموقع في مصفوفة المخاطر</v>
       </c>
       <c r="C3526" t="str">
-        <v>Maz ticams</v>
+        <v>Pozīcija risku matricā</v>
       </c>
     </row>
     <row r="3527">
       <c r="A3527" t="str">
-        <v>Insignificant</v>
+        <v>Possible</v>
       </c>
       <c r="B3527" t="str">
-        <v>غير مهم</v>
+        <v>ممكن</v>
       </c>
       <c r="C3527" t="str">
-        <v>Nenozīmīgs</v>
+        <v>Iespējams</v>
       </c>
     </row>
     <row r="3528">
       <c r="A3528" t="str">
-        <v>Almost Certain</v>
+        <v>Rare</v>
       </c>
       <c r="B3528" t="str">
-        <v>شبه مؤكد</v>
+        <v>نادر</v>
       </c>
       <c r="C3528" t="str">
-        <v>Gandrīz noteikts</v>
+        <v>Reti</v>
       </c>
     </row>
     <row r="3529">
       <c r="A3529" t="str">
-        <v>Registering Risks</v>
+        <v>Unlikely</v>
       </c>
       <c r="B3529" t="str">
-        <v>تسجيل المخاطر</v>
+        <v>غير محتمل</v>
       </c>
       <c r="C3529" t="str">
-        <v>Reģistrē riskus</v>
+        <v>Maz ticams</v>
       </c>
     </row>
     <row r="3530">
       <c r="A3530" t="str">
-        <v>Registering...</v>
+        <v>Insignificant</v>
       </c>
       <c r="B3530" t="str">
-        <v>جاري التسجيل...</v>
+        <v>غير مهم</v>
       </c>
       <c r="C3530" t="str">
-        <v>Reģistrē...</v>
+        <v>Nenozīmīgs</v>
       </c>
     </row>
     <row r="3531">
       <c r="A3531" t="str">
-        <v>Remove this control</v>
+        <v>Almost Certain</v>
       </c>
       <c r="B3531" t="str">
-        <v>إزالة هذا الضابط</v>
+        <v>شبه مؤكد</v>
       </c>
       <c r="C3531" t="str">
-        <v>Noņemt šo kontroli</v>
+        <v>Gandrīz noteikts</v>
       </c>
     </row>
     <row r="3532">
       <c r="A3532" t="str">
-        <v>Remove this risk</v>
+        <v>Registering Risks</v>
       </c>
       <c r="B3532" t="str">
-        <v>إزالة هذه المخاطرة</v>
+        <v>تسجيل المخاطر</v>
       </c>
       <c r="C3532" t="str">
-        <v>Noņemt šo risku</v>
+        <v>Reģistrē riskus</v>
       </c>
     </row>
     <row r="3533">
       <c r="A3533" t="str">
-        <v>Remove this threat</v>
+        <v>Registering...</v>
       </c>
       <c r="B3533" t="str">
-        <v>إزالة هذا التهديد</v>
+        <v>جاري التسجيل...</v>
       </c>
       <c r="C3533" t="str">
-        <v>Noņemt šo draudu</v>
+        <v>Reģistrē...</v>
       </c>
     </row>
     <row r="3534">
       <c r="A3534" t="str">
-        <v>Remove this vulnerability</v>
+        <v>Remove this control</v>
       </c>
       <c r="B3534" t="str">
-        <v>إزالة هذه الثغرة</v>
+        <v>إزالة هذا الضابط</v>
       </c>
       <c r="C3534" t="str">
-        <v>Noņemt šo ievainojamību</v>
+        <v>Noņemt šo kontroli</v>
       </c>
     </row>
     <row r="3535">
       <c r="A3535" t="str">
-        <v>Residual Impact (1-5)</v>
+        <v>Remove this risk</v>
       </c>
       <c r="B3535" t="str">
-        <v>التأثير المتبقي (1-5)</v>
+        <v>إزالة هذه المخاطرة</v>
       </c>
       <c r="C3535" t="str">
-        <v>Atlikusī ietekme (1-5)</v>
+        <v>Noņemt šo risku</v>
       </c>
     </row>
     <row r="3536">
       <c r="A3536" t="str">
-        <v>Residual Likelihood (1-5)</v>
+        <v>Remove this threat</v>
       </c>
       <c r="B3536" t="str">
-        <v>الاحتمالية المتبقية (1-5)</v>
+        <v>إزالة هذا التهديد</v>
       </c>
       <c r="C3536" t="str">
-        <v>Atlikusī iespējamība (1-5)</v>
+        <v>Noņemt šo draudu</v>
       </c>
     </row>
     <row r="3537">
       <c r="A3537" t="str">
-        <v>Residual Risk Rating</v>
+        <v>Remove this vulnerability</v>
       </c>
       <c r="B3537" t="str">
-        <v>تقييم المخاطر المتبقية</v>
+        <v>إزالة هذه الثغرة</v>
       </c>
       <c r="C3537" t="str">
-        <v>Atlikušā riska vērtējums</v>
+        <v>Noņemt šo ievainojamību</v>
       </c>
     </row>
     <row r="3538">
       <c r="A3538" t="str">
-        <v>Resubmit Exception</v>
+        <v>Residual Impact (1-5)</v>
       </c>
       <c r="B3538" t="str">
-        <v>إعادة تقديم الاستثناء</v>
+        <v>التأثير المتبقي (1-5)</v>
       </c>
       <c r="C3538" t="str">
-        <v>Atkārtoti iesniegt izņēmumu</v>
+        <v>Atlikusī ietekme (1-5)</v>
       </c>
     </row>
     <row r="3539">
       <c r="A3539" t="str">
-        <v>Review and remove unwanted risks before proceeding.</v>
+        <v>Residual Likelihood (1-5)</v>
       </c>
       <c r="B3539" t="str">
-        <v>راجع وأزل المخاطر غير المرغوب فيها قبل المتابعة.</v>
+        <v>الاحتمالية المتبقية (1-5)</v>
       </c>
       <c r="C3539" t="str">
-        <v>Pārskatiet un noņemiet nevēlamus riskus pirms turpināšanas.</v>
+        <v>Atlikusī iespējamība (1-5)</v>
       </c>
     </row>
     <row r="3540">
       <c r="A3540" t="str">
-        <v>Review the AI-identified risks below. Remove any unwanted risks, then click 'Match with Library' to find duplicates.</v>
+        <v>Residual Risk Rating</v>
       </c>
       <c r="B3540" t="str">
-        <v>راجع المخاطر المحددة بالذكاء الاصطناعي أدناه. أزل أي مخاطر غير مرغوب فيها، ثم انقر "مطابقة مع المكتبة" للعثور على التكرارات.</v>
+        <v>تقييم المخاطر المتبقية</v>
       </c>
       <c r="C3540" t="str">
-        <v>Pārskatiet AI identificētos riskus zemāk. Noņemiet nevēlamus riskus, pēc tam noklikšķiniet "Saskaņot ar bibliotēku", lai atrastu dublikātus.</v>
+        <v>Atlikušā riska vērtējums</v>
       </c>
     </row>
     <row r="3541">
       <c r="A3541" t="str">
-        <v>Review the matched results below before registering.</v>
+        <v>Resubmit Exception</v>
       </c>
       <c r="B3541" t="str">
-        <v>راجع نتائج المطابقة أدناه قبل التسجيل.</v>
+        <v>إعادة تقديم الاستثناء</v>
       </c>
       <c r="C3541" t="str">
-        <v>Pārskatiet saskaņotos rezultātus zemāk pirms reģistrēšanas.</v>
+        <v>Atkārtoti iesniegt izņēmumu</v>
       </c>
     </row>
     <row r="3542">
       <c r="A3542" t="str">
-        <v>Review the matching results above. Click 'Confirm &amp; Register' to add new risks to your library.</v>
+        <v>Review and remove unwanted risks before proceeding.</v>
       </c>
       <c r="B3542" t="str">
-        <v>راجع نتائج المطابقة أعلاه. انقر "تأكيد وتسجيل" لإضافة مخاطر جديدة إلى مكتبتك.</v>
+        <v>راجع وأزل المخاطر غير المرغوب فيها قبل المتابعة.</v>
       </c>
       <c r="C3542" t="str">
-        <v>Pārskatiet saskaņošanas rezultātus augstāk. Noklikšķiniet "Apstiprināt un reģistrēt", lai pievienotu jaunus riskus jūsu bibliotēkai.</v>
+        <v>Pārskatiet un noņemiet nevēlamus riskus pirms turpināšanas.</v>
       </c>
     </row>
     <row r="3543">
       <c r="A3543" t="str">
-        <v>Reviewing...</v>
+        <v>Review the AI-identified risks below. Remove any unwanted risks, then click 'Match with Library' to find duplicates.</v>
       </c>
       <c r="B3543" t="str">
-        <v>جاري المراجعة...</v>
+        <v>راجع المخاطر المحددة بالذكاء الاصطناعي أدناه. أزل أي مخاطر غير مرغوب فيها، ثم انقر "مطابقة مع المكتبة" للعثور على التكرارات.</v>
       </c>
       <c r="C3543" t="str">
-        <v>Pārskata...</v>
+        <v>Pārskatiet AI identificētos riskus zemāk. Noņemiet nevēlamus riskus, pēc tam noklikšķiniet "Saskaņot ar bibliotēku", lai atrastu dublikātus.</v>
       </c>
     </row>
     <row r="3544">
       <c r="A3544" t="str">
-        <v>Risk Not Found</v>
+        <v>Review the matched results below before registering.</v>
       </c>
       <c r="B3544" t="str">
-        <v>لم يتم العثور على المخاطرة</v>
+        <v>راجع نتائج المطابقة أدناه قبل التسجيل.</v>
       </c>
       <c r="C3544" t="str">
-        <v>Risks nav atrasts</v>
+        <v>Pārskatiet saskaņotos rezultātus zemāk pirms reģistrēšanas.</v>
       </c>
     </row>
     <row r="3545">
       <c r="A3545" t="str">
-        <v>Risk Reference</v>
+        <v>Review the matching results above. Click 'Confirm &amp; Register' to add new risks to your library.</v>
       </c>
       <c r="B3545" t="str">
-        <v>مرجع المخاطرة</v>
+        <v>راجع نتائج المطابقة أعلاه. انقر "تأكيد وتسجيل" لإضافة مخاطر جديدة إلى مكتبتك.</v>
       </c>
       <c r="C3545" t="str">
-        <v>Riska atsauce</v>
+        <v>Pārskatiet saskaņošanas rezultātus augstāk. Noklikšķiniet "Apstiprināt un reģistrēt", lai pievienotu jaunus riskus jūsu bibliotēkai.</v>
       </c>
     </row>
     <row r="3546">
       <c r="A3546" t="str">
-        <v>Risk Score = Likelihood * Impact * Vulnerability</v>
+        <v>Reviewing...</v>
       </c>
       <c r="B3546" t="str">
-        <v>درجة المخاطرة = الاحتمالية × التأثير × الثغرة</v>
+        <v>جاري المراجعة...</v>
       </c>
       <c r="C3546" t="str">
-        <v>Riska rezultāts = Iespējamība × Ietekme × Ievainojamība</v>
+        <v>Pārskata...</v>
       </c>
     </row>
     <row r="3547">
       <c r="A3547" t="str">
-        <v>Risk Summary</v>
+        <v>Risk Not Found</v>
       </c>
       <c r="B3547" t="str">
-        <v>ملخص المخاطر</v>
+        <v>لم يتم العثور على المخاطرة</v>
       </c>
       <c r="C3547" t="str">
-        <v>Risku kopsavilkums</v>
+        <v>Risks nav atrasts</v>
       </c>
     </row>
     <row r="3548">
       <c r="A3548" t="str">
-        <v>Risk Treatment</v>
+        <v>Risk Reference</v>
       </c>
       <c r="B3548" t="str">
-        <v>معالجة المخاطر</v>
+        <v>مرجع المخاطرة</v>
       </c>
       <c r="C3548" t="str">
-        <v>Risku apstrāde</v>
+        <v>Riska atsauce</v>
       </c>
     </row>
     <row r="3549">
       <c r="A3549" t="str">
-        <v>Risk View</v>
+        <v>Risk Score = Likelihood * Impact * Vulnerability</v>
       </c>
       <c r="B3549" t="str">
-        <v>عرض المخاطر</v>
+        <v>درجة المخاطرة = الاحتمالية × التأثير × الثغرة</v>
       </c>
       <c r="C3549" t="str">
-        <v>Risku skats</v>
+        <v>Riska rezultāts = Iespējamība × Ietekme × Ievainojamība</v>
       </c>
     </row>
     <row r="3550">
       <c r="A3550" t="str">
-        <v>Risk description, Department, Risk sources, Risk category, Potential threat, Associated vulnerabilities</v>
+        <v>Risk Summary</v>
       </c>
       <c r="B3550" t="str">
-        <v>وصف المخاطرة، القسم، مصادر المخاطر، فئة المخاطر، التهديد المحتمل، الثغرات المرتبطة</v>
+        <v>ملخص المخاطر</v>
       </c>
       <c r="C3550" t="str">
-        <v>Riska apraksts, Nodaļa, Risku avoti, Riska kategorija, Potenciālais drauds, Saistītās ievainojamības</v>
+        <v>Risku kopsavilkums</v>
       </c>
     </row>
     <row r="3551">
       <c r="A3551" t="str">
-        <v>Risk name is required. Missing in row(s): {rows}</v>
+        <v>Risk Treatment</v>
       </c>
       <c r="B3551" t="str">
-        <v>اسم المخاطرة مطلوب. غير موجود في الصف(الصفوف): {rows}</v>
+        <v>معالجة المخاطر</v>
       </c>
       <c r="C3551" t="str">
-        <v>Riska nosaukums ir obligāts. Trūkst rindā(-ās): {rows}</v>
+        <v>Risku apstrāde</v>
       </c>
     </row>
     <row r="3552">
       <c r="A3552" t="str">
-        <v>These risks have been compared with your existing library. Only new risks were added to the Risk Register.</v>
+        <v>Risk View</v>
       </c>
       <c r="B3552" t="str">
-        <v>تمت مقارنة هذه المخاطر مع مكتبتك الحالية. تمت إضافة المخاطر الجديدة فقط إلى سجل المخاطر.</v>
+        <v>عرض المخاطر</v>
       </c>
       <c r="C3552" t="str">
-        <v>Šie riski ir salīdzināti ar jūsu esošo bibliotēku. Tikai jauni riski tika pievienoti risku reģistram.</v>
+        <v>Risku skats</v>
       </c>
     </row>
     <row r="3553">
       <c r="A3553" t="str">
-        <v>The risk has been removed from the review list.</v>
+        <v>Risk description, Department, Risk sources, Risk category, Potential threat, Associated vulnerabilities</v>
       </c>
       <c r="B3553" t="str">
-        <v>تمت إزالة المخاطرة من قائمة المراجعة.</v>
+        <v>وصف المخاطرة، القسم، مصادر المخاطر، فئة المخاطر، التهديد المحتمل، الثغرات المرتبطة</v>
       </c>
       <c r="C3553" t="str">
-        <v>Risks ir noņemts no pārskata saraksta.</v>
+        <v>Riska apraksts, Nodaļa, Risku avoti, Riska kategorija, Potenciālais drauds, Saistītās ievainojamības</v>
       </c>
     </row>
     <row r="3554">
       <c r="A3554" t="str">
-        <v>Link controls first to generate</v>
+        <v>Risk name is required. Missing in row(s): {rows}</v>
       </c>
       <c r="B3554" t="str">
-        <v>اربط الضوابط أولاً للإنشاء</v>
+        <v>اسم المخاطرة مطلوب. غير موجود في الصف(الصفوف): {rows}</v>
       </c>
       <c r="C3554" t="str">
-        <v>Vispirms saistiet kontroles, lai ģenerētu</v>
+        <v>Riska nosaukums ir obligāts. Trūkst rindā(-ās): {rows}</v>
       </c>
     </row>
     <row r="3555">
       <c r="A3555" t="str">
-        <v>Link controls from the risk register to see them here</v>
+        <v>These risks have been compared with your existing library. Only new risks were added to the Risk Register.</v>
       </c>
       <c r="B3555" t="str">
-        <v>اربط الضوابط من سجل المخاطر لرؤيتها هنا</v>
+        <v>تمت مقارنة هذه المخاطر مع مكتبتك الحالية. تمت إضافة المخاطر الجديدة فقط إلى سجل المخاطر.</v>
       </c>
       <c r="C3555" t="str">
-        <v>Saistiet kontroles no risku reģistra, lai tās redzētu šeit</v>
+        <v>Šie riski ir salīdzināti ar jūsu esošo bibliotēku. Tikai jauni riski tika pievienoti risku reģistram.</v>
       </c>
     </row>
     <row r="3556">
       <c r="A3556" t="str">
-        <v>Link controls to track compliance</v>
+        <v>The risk has been removed from the review list.</v>
       </c>
       <c r="B3556" t="str">
-        <v>اربط الضوابط لتتبع الامتثال</v>
+        <v>تمت إزالة المخاطرة من قائمة المراجعة.</v>
       </c>
       <c r="C3556" t="str">
-        <v>Saistiet kontroles atbilstības izsekošanai</v>
+        <v>Risks ir noņemts no pārskata saraksta.</v>
       </c>
     </row>
     <row r="3557">
       <c r="A3557" t="str">
-        <v>No controls are currently linked to this risk</v>
+        <v>Link controls first to generate</v>
       </c>
       <c r="B3557" t="str">
-        <v>لا توجد ضوابط مرتبطة حالياً بهذه المخاطرة</v>
+        <v>اربط الضوابط أولاً للإنشاء</v>
       </c>
       <c r="C3557" t="str">
-        <v>Pašlaik nav kontroles, kas saistītas ar šo risku</v>
+        <v>Vispirms saistiet kontroles, lai ģenerētu</v>
       </c>
     </row>
     <row r="3558">
       <c r="A3558" t="str">
-        <v>No controls linked to this</v>
+        <v>Link controls from the risk register to see them here</v>
       </c>
       <c r="B3558" t="str">
-        <v>لا توجد ضوابط مرتبطة بهذا</v>
+        <v>اربط الضوابط من سجل المخاطر لرؤيتها هنا</v>
       </c>
       <c r="C3558" t="str">
-        <v>Nav saistītu kontroles</v>
+        <v>Saistiet kontroles no risku reģistra, lai tās redzētu šeit</v>
       </c>
     </row>
     <row r="3559">
       <c r="A3559" t="str">
-        <v>No controls linked to this policy</v>
+        <v>Link controls to track compliance</v>
       </c>
       <c r="B3559" t="str">
-        <v>لا توجد ضوابط مرتبطة بهذه السياسة</v>
+        <v>اربط الضوابط لتتبع الامتثال</v>
       </c>
       <c r="C3559" t="str">
-        <v>Nav kontroles, kas saistītas ar šo politiku</v>
+        <v>Saistiet kontroles atbilstības izsekošanai</v>
       </c>
     </row>
     <row r="3560">
       <c r="A3560" t="str">
-        <v>No controls match your filters</v>
+        <v>No controls are currently linked to this risk</v>
       </c>
       <c r="B3560" t="str">
-        <v>لا توجد ضوابط تطابق عوامل التصفية</v>
+        <v>لا توجد ضوابط مرتبطة حالياً بهذه المخاطرة</v>
       </c>
       <c r="C3560" t="str">
-        <v>Neviena kontrole neatbilst filtriem</v>
+        <v>Pašlaik nav kontroles, kas saistītas ar šo risku</v>
       </c>
     </row>
     <row r="3561">
       <c r="A3561" t="str">
-        <v>No existing controls found</v>
+        <v>No controls linked to this</v>
       </c>
       <c r="B3561" t="str">
-        <v>لم يتم العثور على ضوابط حالية</v>
+        <v>لا توجد ضوابط مرتبطة بهذا</v>
       </c>
       <c r="C3561" t="str">
-        <v>Nav atrastas esošas kontroles</v>
+        <v>Nav saistītu kontroles</v>
       </c>
     </row>
     <row r="3562">
       <c r="A3562" t="str">
-        <v>No planned controls found</v>
+        <v>No controls linked to this policy</v>
       </c>
       <c r="B3562" t="str">
-        <v>لم يتم العثور على ضوابط مخطط لها</v>
+        <v>لا توجد ضوابط مرتبطة بهذه السياسة</v>
       </c>
       <c r="C3562" t="str">
-        <v>Nav atrastas plānotas kontroles</v>
+        <v>Nav kontroles, kas saistītas ar šo politiku</v>
       </c>
     </row>
     <row r="3563">
       <c r="A3563" t="str">
-        <v>No risks available</v>
+        <v>No controls match your filters</v>
       </c>
       <c r="B3563" t="str">
-        <v>لا تتوفر مخاطر</v>
+        <v>لا توجد ضوابط تطابق عوامل التصفية</v>
       </c>
       <c r="C3563" t="str">
-        <v>Nav pieejamu risku</v>
+        <v>Neviena kontrole neatbilst filtriem</v>
       </c>
     </row>
     <row r="3564">
       <c r="A3564" t="str">
-        <v>High impact</v>
+        <v>No existing controls found</v>
       </c>
       <c r="B3564" t="str">
-        <v>تأثير عالي</v>
+        <v>لم يتم العثور على ضوابط حالية</v>
       </c>
       <c r="C3564" t="str">
-        <v>Augsta ietekme</v>
+        <v>Nav atrastas esošas kontroles</v>
       </c>
     </row>
     <row r="3565">
       <c r="A3565" t="str">
-        <v>Evidence Not Found</v>
+        <v>No planned controls found</v>
       </c>
       <c r="B3565" t="str">
-        <v>لم يتم العثور على الدليل</v>
+        <v>لم يتم العثور على ضوابط مخطط لها</v>
       </c>
       <c r="C3565" t="str">
-        <v>Pierādījums nav atrasts</v>
+        <v>Nav atrastas plānotas kontroles</v>
       </c>
     </row>
     <row r="3566">
       <c r="A3566" t="str">
-        <v>Evidence request with this title already exists</v>
+        <v>No risks available</v>
       </c>
       <c r="B3566" t="str">
-        <v>طلب دليل بهذا العنوان موجود بالفعل</v>
+        <v>لا تتوفر مخاطر</v>
       </c>
       <c r="C3566" t="str">
-        <v>Pierādījumu pieprasījums ar šo nosaukumu jau pastāv</v>
+        <v>Nav pieejamu risku</v>
       </c>
     </row>
     <row r="3567">
       <c r="A3567" t="str">
-        <v>Governance document not found</v>
+        <v>High impact</v>
       </c>
       <c r="B3567" t="str">
-        <v>لم يتم العثور على مستند الحوكمة</v>
+        <v>تأثير عالي</v>
       </c>
       <c r="C3567" t="str">
-        <v>Pārvaldības dokuments nav atrasts</v>
+        <v>Augsta ietekme</v>
       </c>
     </row>
     <row r="3568">
       <c r="A3568" t="str">
-        <v>Linked Evidence</v>
+        <v>Evidence Not Found</v>
       </c>
       <c r="B3568" t="str">
-        <v>الأدلة المرتبطة</v>
+        <v>لم يتم العثور على الدليل</v>
       </c>
       <c r="C3568" t="str">
-        <v>Saistītie pierādījumi</v>
+        <v>Pierādījums nav atrasts</v>
       </c>
     </row>
     <row r="3569">
       <c r="A3569" t="str">
-        <v>Linked Governance</v>
+        <v>Evidence request with this title already exists</v>
       </c>
       <c r="B3569" t="str">
-        <v>الحوكمة المرتبطة</v>
+        <v>طلب دليل بهذا العنوان موجود بالفعل</v>
       </c>
       <c r="C3569" t="str">
-        <v>Saistītā pārvaldība</v>
+        <v>Pierādījumu pieprasījums ar šo nosaukumu jau pastāv</v>
       </c>
     </row>
     <row r="3570">
       <c r="A3570" t="str">
-        <v>Linked Risk</v>
+        <v>Governance document not found</v>
       </c>
       <c r="B3570" t="str">
-        <v>المخاطر المرتبطة</v>
+        <v>لم يتم العثور على مستند الحوكمة</v>
       </c>
       <c r="C3570" t="str">
-        <v>Saistītais risks</v>
+        <v>Pārvaldības dokuments nav atrasts</v>
       </c>
     </row>
     <row r="3571">
       <c r="A3571" t="str">
-        <v>Policy Reference</v>
+        <v>Linked Evidence</v>
       </c>
       <c r="B3571" t="str">
-        <v>مرجع السياسة</v>
+        <v>الأدلة المرتبطة</v>
       </c>
       <c r="C3571" t="str">
-        <v>Politikas atsauce</v>
+        <v>Saistītie pierādījumi</v>
       </c>
     </row>
     <row r="3572">
       <c r="A3572" t="str">
-        <v>Published Document</v>
+        <v>Linked Governance</v>
       </c>
       <c r="B3572" t="str">
-        <v>المستند المنشور</v>
+        <v>الحوكمة المرتبطة</v>
       </c>
       <c r="C3572" t="str">
-        <v>Publicētais dokuments</v>
+        <v>Saistītā pārvaldība</v>
       </c>
     </row>
     <row r="3573">
       <c r="A3573" t="str">
-        <v>Published On</v>
+        <v>Linked Risk</v>
       </c>
       <c r="B3573" t="str">
-        <v>نُشر في</v>
+        <v>المخاطر المرتبطة</v>
       </c>
       <c r="C3573" t="str">
-        <v>Publicēts</v>
+        <v>Saistītais risks</v>
       </c>
     </row>
     <row r="3574">
       <c r="A3574" t="str">
-        <v>Generate Policy</v>
+        <v>Policy Reference</v>
       </c>
       <c r="B3574" t="str">
-        <v>إنشاء سياسة</v>
+        <v>مرجع السياسة</v>
       </c>
       <c r="C3574" t="str">
-        <v>Ģenerēt politiku</v>
+        <v>Politikas atsauce</v>
       </c>
     </row>
     <row r="3575">
       <c r="A3575" t="str">
-        <v>The AI will use the selected template and linked controls to generate a comprehensive policy document.</v>
+        <v>Published Document</v>
       </c>
       <c r="B3575" t="str">
-        <v>سيستخدم الذكاء الاصطناعي القالب المحدد والضوابط المرتبطة لإنشاء وثيقة سياسة شاملة.</v>
+        <v>المستند المنشور</v>
       </c>
       <c r="C3575" t="str">
-        <v>AI izmantos atlasīto veidni un saistītās kontroles, lai ģenerētu visaptverošu politikas dokumentu.</v>
+        <v>Publicētais dokuments</v>
       </c>
     </row>
     <row r="3576">
       <c r="A3576" t="str">
-        <v>Select Template</v>
+        <v>Published On</v>
       </c>
       <c r="B3576" t="str">
-        <v>اختر القالب</v>
+        <v>نُشر في</v>
       </c>
       <c r="C3576" t="str">
-        <v>Atlasīt veidni</v>
+        <v>Publicēts</v>
       </c>
     </row>
     <row r="3577">
       <c r="A3577" t="str">
-        <v>Or upload a new template</v>
+        <v>Generate Policy</v>
       </c>
       <c r="B3577" t="str">
-        <v>أو ارفع قالباً جديداً</v>
+        <v>إنشاء سياسة</v>
       </c>
       <c r="C3577" t="str">
-        <v>Vai augšupielādējiet jaunu veidni</v>
+        <v>Ģenerēt politiku</v>
       </c>
     </row>
     <row r="3578">
       <c r="A3578" t="str">
-        <v>Upload a .docx template below</v>
+        <v>The AI will use the selected template and linked controls to generate a comprehensive policy document.</v>
       </c>
       <c r="B3578" t="str">
-        <v>ارفع قالب .docx أدناه</v>
+        <v>سيستخدم الذكاء الاصطناعي القالب المحدد والضوابط المرتبطة لإنشاء وثيقة سياسة شاملة.</v>
       </c>
       <c r="C3578" t="str">
-        <v>Augšupielādējiet .docx veidni zemāk</v>
+        <v>AI izmantos atlasīto veidni un saistītās kontroles, lai ģenerētu visaptverošu politikas dokumentu.</v>
       </c>
     </row>
     <row r="3579">
       <c r="A3579" t="str">
-        <v>No templates available</v>
+        <v>Select Template</v>
       </c>
       <c r="B3579" t="str">
-        <v>لا تتوفر قوالب</v>
+        <v>اختر القالب</v>
       </c>
       <c r="C3579" t="str">
-        <v>Nav pieejamu veidņu</v>
+        <v>Atlasīt veidni</v>
       </c>
     </row>
     <row r="3580">
       <c r="A3580" t="str">
-        <v>This will revert the status from Published to Approved. The document will need to be published again after any changes.</v>
+        <v>Or upload a new template</v>
       </c>
       <c r="B3580" t="str">
-        <v>سيؤدي هذا إلى إرجاع الحالة من منشور إلى معتمد. سيحتاج المستند إلى إعادة نشره بعد أي تغييرات.</v>
+        <v>أو ارفع قالباً جديداً</v>
       </c>
       <c r="C3580" t="str">
-        <v>Tas atgriezīs statusu no Publicēts uz Apstiprināts. Dokuments būs jāpublicē atkārtoti pēc jebkādām izmaiņām.</v>
+        <v>Vai augšupielādējiet jaunu veidni</v>
       </c>
     </row>
     <row r="3581">
       <c r="A3581" t="str">
-        <v>Drag and drop a file here, or</v>
+        <v>Upload a .docx template below</v>
       </c>
       <c r="B3581" t="str">
-        <v>اسحب وأسقط ملفاً هنا، أو</v>
+        <v>ارفع قالب .docx أدناه</v>
       </c>
       <c r="C3581" t="str">
-        <v>Velciet un nometiet failu šeit, vai</v>
+        <v>Augšupielādējiet .docx veidni zemāk</v>
       </c>
     </row>
     <row r="3582">
       <c r="A3582" t="str">
-        <v>Drag and drop your file here, or</v>
+        <v>No templates available</v>
       </c>
       <c r="B3582" t="str">
-        <v>اسحب وأسقط ملفك هنا، أو</v>
+        <v>لا تتوفر قوالب</v>
       </c>
       <c r="C3582" t="str">
-        <v>Velciet un nometiet savu failu šeit, vai</v>
+        <v>Nav pieejamu veidņu</v>
       </c>
     </row>
     <row r="3583">
       <c r="A3583" t="str">
-        <v>Drop file here or click to upload</v>
+        <v>This will revert the status from Published to Approved. The document will need to be published again after any changes.</v>
       </c>
       <c r="B3583" t="str">
-        <v>أسقط الملف هنا أو انقر للرفع</v>
+        <v>سيؤدي هذا إلى إرجاع الحالة من منشور إلى معتمد. سيحتاج المستند إلى إعادة نشره بعد أي تغييرات.</v>
       </c>
       <c r="C3583" t="str">
-        <v>Nometiet failu šeit vai noklikšķiniet, lai augšupielādētu</v>
+        <v>Tas atgriezīs statusu no Publicēts uz Apstiprināts. Dokuments būs jāpublicē atkārtoti pēc jebkādām izmaiņām.</v>
       </c>
     </row>
     <row r="3584">
       <c r="A3584" t="str">
-        <v>Existing Files</v>
+        <v>Drag and drop a file here, or</v>
       </c>
       <c r="B3584" t="str">
-        <v>الملفات الحالية</v>
+        <v>اسحب وأسقط ملفاً هنا، أو</v>
       </c>
       <c r="C3584" t="str">
-        <v>Esošie faili</v>
+        <v>Velciet un nometiet failu šeit, vai</v>
       </c>
     </row>
     <row r="3585">
       <c r="A3585" t="str">
-        <v>Files to Upload</v>
+        <v>Drag and drop your file here, or</v>
       </c>
       <c r="B3585" t="str">
-        <v>ملفات للرفع</v>
+        <v>اسحب وأسقط ملفك هنا، أو</v>
       </c>
       <c r="C3585" t="str">
-        <v>Augšupielādējamie faili</v>
+        <v>Velciet un nometiet savu failu šeit, vai</v>
       </c>
     </row>
     <row r="3586">
       <c r="A3586" t="str">
-        <v>New Files to Upload</v>
+        <v>Drop file here or click to upload</v>
       </c>
       <c r="B3586" t="str">
-        <v>ملفات جديدة للرفع</v>
+        <v>أسقط الملف هنا أو انقر للرفع</v>
       </c>
       <c r="C3586" t="str">
-        <v>Jauni augšupielādējamie faili</v>
+        <v>Nometiet failu šeit vai noklikšķiniet, lai augšupielādētu</v>
       </c>
     </row>
     <row r="3587">
       <c r="A3587" t="str">
-        <v>Supported formats: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
+        <v>Existing Files</v>
       </c>
       <c r="B3587" t="str">
-        <v>التنسيقات المدعومة: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
+        <v>الملفات الحالية</v>
       </c>
       <c r="C3587" t="str">
-        <v>Atbalstītie formāti: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
+        <v>Esošie faili</v>
       </c>
     </row>
     <row r="3588">
       <c r="A3588" t="str">
-        <v>Upload a CSV or Excel file to import</v>
+        <v>Files to Upload</v>
       </c>
       <c r="B3588" t="str">
-        <v>ارفع ملف CSV أو Excel للاستيراد</v>
+        <v>ملفات للرفع</v>
       </c>
       <c r="C3588" t="str">
-        <v>Augšupielādējiet CSV vai Excel failu importēšanai</v>
+        <v>Augšupielādējamie faili</v>
       </c>
     </row>
     <row r="3589">
       <c r="A3589" t="str">
-        <v>Upload an Excel file (.xlsx) containing your framework requirements. You can download the sample template to see the required format.</v>
+        <v>New Files to Upload</v>
       </c>
       <c r="B3589" t="str">
-        <v>ارفع ملف Excel (.xlsx) يحتوي على متطلبات الإطار الخاص بك. يمكنك تنزيل القالب النموذجي لمعرفة التنسيق المطلوب.</v>
+        <v>ملفات جديدة للرفع</v>
       </c>
       <c r="C3589" t="str">
-        <v>Augšupielādējiet Excel failu (.xlsx) ar ietvara prasībām. Varat lejupielādēt parauga veidni, lai redzētu nepieciešamo formātu.</v>
+        <v>Jauni augšupielādējamie faili</v>
       </c>
     </row>
     <row r="3590">
       <c r="A3590" t="str">
-        <v>Upload documents to the vault first</v>
+        <v>Supported formats: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
       </c>
       <c r="B3590" t="str">
-        <v>ارفع المستندات إلى الخزنة أولاً</v>
+        <v>التنسيقات المدعومة: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
       </c>
       <c r="C3590" t="str">
-        <v>Vispirms augšupielādējiet dokumentus glabātuvē</v>
+        <v>Atbalstītie formāti: PDF, DOC, DOCX, XLS, XLSX, PPT, PPTX, TXT</v>
       </c>
     </row>
     <row r="3591">
       <c r="A3591" t="str">
-        <v>Upload or link documents to get started</v>
+        <v>Upload a CSV or Excel file to import</v>
       </c>
       <c r="B3591" t="str">
-        <v>ارفع أو اربط المستندات للبدء</v>
+        <v>ارفع ملف CSV أو Excel للاستيراد</v>
       </c>
       <c r="C3591" t="str">
-        <v>Augšupielādējiet vai saistiet dokumentus, lai sāktu</v>
+        <v>Augšupielādējiet CSV vai Excel failu importēšanai</v>
       </c>
     </row>
     <row r="3592">
       <c r="A3592" t="str">
-        <v>Uploaded by</v>
+        <v>Upload an Excel file (.xlsx) containing your framework requirements. You can download the sample template to see the required format.</v>
       </c>
       <c r="B3592" t="str">
-        <v>رُفع بواسطة</v>
+        <v>ارفع ملف Excel (.xlsx) يحتوي على متطلبات الإطار الخاص بك. يمكنك تنزيل القالب النموذجي لمعرفة التنسيق المطلوب.</v>
       </c>
       <c r="C3592" t="str">
-        <v>Augšupielādēja</v>
+        <v>Augšupielādējiet Excel failu (.xlsx) ar ietvara prasībām. Varat lejupielādēt parauga veidni, lai redzētu nepieciešamo formātu.</v>
       </c>
     </row>
     <row r="3593">
       <c r="A3593" t="str">
-        <v>Uploading document...</v>
+        <v>Upload documents to the vault first</v>
       </c>
       <c r="B3593" t="str">
-        <v>جاري رفع المستند...</v>
+        <v>ارفع المستندات إلى الخزنة أولاً</v>
       </c>
       <c r="C3593" t="str">
-        <v>Augšupielādē dokumentu...</v>
+        <v>Vispirms augšupielādējiet dokumentus glabātuvē</v>
       </c>
     </row>
     <row r="3594">
       <c r="A3594" t="str">
-        <v>Delete existing file to link</v>
+        <v>Upload or link documents to get started</v>
       </c>
       <c r="B3594" t="str">
-        <v>احذف الملف الحالي للربط</v>
+        <v>ارفع أو اربط المستندات للبدء</v>
       </c>
       <c r="C3594" t="str">
-        <v>Dzēsiet esošo failu, lai saistītu</v>
+        <v>Augšupielādējiet vai saistiet dokumentus, lai sāktu</v>
       </c>
     </row>
     <row r="3595">
       <c r="A3595" t="str">
-        <v>Delete existing file to upload new</v>
+        <v>Uploaded by</v>
       </c>
       <c r="B3595" t="str">
-        <v>احذف الملف الحالي لرفع ملف جديد</v>
+        <v>رُفع بواسطة</v>
       </c>
       <c r="C3595" t="str">
-        <v>Dzēsiet esošo failu, lai augšupielādētu jaunu</v>
+        <v>Augšupielādēja</v>
       </c>
     </row>
     <row r="3596">
       <c r="A3596" t="str">
-        <v>Delete existing file to use AI</v>
+        <v>Uploading document...</v>
       </c>
       <c r="B3596" t="str">
-        <v>احذف الملف الحالي لاستخدام الذكاء الاصطناعي</v>
+        <v>جاري رفع المستند...</v>
       </c>
       <c r="C3596" t="str">
-        <v>Dzēsiet esošo failu, lai izmantotu AI</v>
+        <v>Augšupielādē dokumentu...</v>
       </c>
     </row>
     <row r="3597">
       <c r="A3597" t="str">
-        <v>Template columns:</v>
+        <v>Delete existing file to link</v>
       </c>
       <c r="B3597" t="str">
-        <v>أعمدة القالب:</v>
+        <v>احذف الملف الحالي للربط</v>
       </c>
       <c r="C3597" t="str">
-        <v>Veidnes kolonnas:</v>
+        <v>Dzēsiet esošo failu, lai saistītu</v>
       </c>
     </row>
     <row r="3598">
       <c r="A3598" t="str">
-        <v>Excel file is empty</v>
+        <v>Delete existing file to upload new</v>
       </c>
       <c r="B3598" t="str">
-        <v>ملف Excel فارغ</v>
+        <v>احذف الملف الحالي لرفع ملف جديد</v>
       </c>
       <c r="C3598" t="str">
-        <v>Excel fails ir tukšs</v>
+        <v>Dzēsiet esošo failu, lai augšupielādētu jaunu</v>
       </c>
     </row>
     <row r="3599">
       <c r="A3599" t="str">
-        <v>Content-Disposition</v>
+        <v>Delete existing file to use AI</v>
       </c>
       <c r="B3599" t="str">
-        <v>ترتيب المحتوى</v>
+        <v>احذف الملف الحالي لاستخدام الذكاء الاصطناعي</v>
       </c>
       <c r="C3599" t="str">
-        <v>Satura izvietojums</v>
+        <v>Dzēsiet esošo failu, lai izmantotu AI</v>
       </c>
     </row>
     <row r="3600">
       <c r="A3600" t="str">
-        <v>Connection Error</v>
+        <v>Template columns:</v>
       </c>
       <c r="B3600" t="str">
-        <v>خطأ في الاتصال</v>
+        <v>أعمدة القالب:</v>
       </c>
       <c r="C3600" t="str">
-        <v>Savienojuma kļūda</v>
+        <v>Veidnes kolonnas:</v>
       </c>
     </row>
     <row r="3601">
       <c r="A3601" t="str">
-        <v>Error Details</v>
+        <v>Excel file is empty</v>
       </c>
       <c r="B3601" t="str">
-        <v>تفاصيل الخطأ</v>
+        <v>ملف Excel فارغ</v>
       </c>
       <c r="C3601" t="str">
-        <v>Kļūdas detaļas</v>
+        <v>Excel fails ir tukšs</v>
       </c>
     </row>
     <row r="3602">
       <c r="A3602" t="str">
-        <v>Error importing data. Please check the file format.</v>
+        <v>Content-Disposition</v>
       </c>
       <c r="B3602" t="str">
-        <v>خطأ في استيراد البيانات. يرجى التحقق من تنسيق الملف.</v>
+        <v>ترتيب المحتوى</v>
       </c>
       <c r="C3602" t="str">
-        <v>Kļūda importējot datus. Lūdzu, pārbaudiet faila formātu.</v>
+        <v>Satura izvietojums</v>
       </c>
     </row>
     <row r="3603">
       <c r="A3603" t="str">
-        <v>Error uploading file. Please try again.</v>
+        <v>Connection Error</v>
       </c>
       <c r="B3603" t="str">
-        <v>خطأ في رفع الملف. يرجى المحاولة مرة أخرى.</v>
+        <v>خطأ في الاتصال</v>
       </c>
       <c r="C3603" t="str">
-        <v>Kļūda augšupielādējot failu. Lūdzu, mēģiniet vēlreiz.</v>
+        <v>Savienojuma kļūda</v>
       </c>
     </row>
     <row r="3604">
       <c r="A3604" t="str">
-        <v>Exception not found</v>
+        <v>Error Details</v>
       </c>
       <c r="B3604" t="str">
-        <v>لم يتم العثور على الاستثناء</v>
+        <v>تفاصيل الخطأ</v>
       </c>
       <c r="C3604" t="str">
-        <v>Izņēmums nav atrasts</v>
+        <v>Kļūdas detaļas</v>
       </c>
     </row>
     <row r="3605">
       <c r="A3605" t="str">
-        <v>Failed to add department</v>
+        <v>Error importing data. Please check the file format.</v>
       </c>
       <c r="B3605" t="str">
-        <v>فشل في إضافة القسم</v>
+        <v>خطأ في استيراد البيانات. يرجى التحقق من تنسيق الملف.</v>
       </c>
       <c r="C3605" t="str">
-        <v>Neizdevās pievienot nodaļu</v>
+        <v>Kļūda importējot datus. Lūdzu, pārbaudiet faila formātu.</v>
       </c>
     </row>
     <row r="3606">
       <c r="A3606" t="str">
-        <v>Failed to add item</v>
+        <v>Error uploading file. Please try again.</v>
       </c>
       <c r="B3606" t="str">
-        <v>فشل في إضافة العنصر</v>
+        <v>خطأ في رفع الملف. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C3606" t="str">
-        <v>Neizdevās pievienot vienību</v>
+        <v>Kļūda augšupielādējot failu. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="3607">
       <c r="A3607" t="str">
-        <v>Failed to approve BIA</v>
+        <v>Exception not found</v>
       </c>
       <c r="B3607" t="str">
-        <v>فشل في الموافقة على تحليل تأثير الأعمال</v>
+        <v>لم يتم العثور على الاستثناء</v>
       </c>
       <c r="C3607" t="str">
-        <v>Neizdevās apstiprināt BIA</v>
+        <v>Izņēmums nav atrasts</v>
       </c>
     </row>
     <row r="3608">
       <c r="A3608" t="str">
-        <v>Failed to approve exception</v>
+        <v>Failed to add department</v>
       </c>
       <c r="B3608" t="str">
-        <v>فشل في الموافقة على الاستثناء</v>
+        <v>فشل في إضافة القسم</v>
       </c>
       <c r="C3608" t="str">
-        <v>Neizdevās apstiprināt izņēmumu</v>
+        <v>Neizdevās pievienot nodaļu</v>
       </c>
     </row>
     <row r="3609">
       <c r="A3609" t="str">
-        <v>Failed to create control</v>
+        <v>Failed to add item</v>
       </c>
       <c r="B3609" t="str">
-        <v>فشل في إنشاء الضابط</v>
+        <v>فشل في إضافة العنصر</v>
       </c>
       <c r="C3609" t="str">
-        <v>Neizdevās izveidot kontroli</v>
+        <v>Neizdevās pievienot vienību</v>
       </c>
     </row>
     <row r="3610">
       <c r="A3610" t="str">
-        <v>Failed to create label</v>
+        <v>Failed to approve BIA</v>
       </c>
       <c r="B3610" t="str">
-        <v>فشل في إنشاء التسمية</v>
+        <v>فشل في الموافقة على تحليل تأثير الأعمال</v>
       </c>
       <c r="C3610" t="str">
-        <v>Neizdevās izveidot apzīmējumu</v>
+        <v>Neizdevās apstiprināt BIA</v>
       </c>
     </row>
     <row r="3611">
       <c r="A3611" t="str">
-        <v>Failed to create range</v>
+        <v>Failed to approve exception</v>
       </c>
       <c r="B3611" t="str">
-        <v>فشل في إنشاء النطاق</v>
+        <v>فشل في الموافقة على الاستثناء</v>
       </c>
       <c r="C3611" t="str">
-        <v>Neizdevās izveidot diapazonu</v>
+        <v>Neizdevās apstiprināt izņēmumu</v>
       </c>
     </row>
     <row r="3612">
       <c r="A3612" t="str">
-        <v>Failed to create range. Please try again.</v>
+        <v>Failed to create control</v>
       </c>
       <c r="B3612" t="str">
-        <v>فشل في إنشاء النطاق. يرجى المحاولة مرة أخرى.</v>
+        <v>فشل في إنشاء الضابط</v>
       </c>
       <c r="C3612" t="str">
-        <v>Neizdevās izveidot diapazonu. Lūdzu, mēģiniet vēlreiz.</v>
+        <v>Neizdevās izveidot kontroli</v>
       </c>
     </row>
     <row r="3613">
       <c r="A3613" t="str">
-        <v>Failed to create rating</v>
+        <v>Failed to create label</v>
       </c>
       <c r="B3613" t="str">
-        <v>فشل في إنشاء التقييم</v>
+        <v>فشل في إنشاء التسمية</v>
       </c>
       <c r="C3613" t="str">
-        <v>Neizdevās izveidot vērtējumu</v>
+        <v>Neizdevās izveidot apzīmējumu</v>
       </c>
     </row>
     <row r="3614">
       <c r="A3614" t="str">
-        <v>Failed to create user. Please try again.</v>
+        <v>Failed to create range</v>
       </c>
       <c r="B3614" t="str">
-        <v>فشل في إنشاء المستخدم. يرجى المحاولة مرة أخرى.</v>
+        <v>فشل في إنشاء النطاق</v>
       </c>
       <c r="C3614" t="str">
-        <v>Neizdevās izveidot lietotāju. Lūdzu, mēģiniet vēlreiz.</v>
+        <v>Neizdevās izveidot diapazonu</v>
       </c>
     </row>
     <row r="3615">
       <c r="A3615" t="str">
-        <v>Failed to delete framework</v>
+        <v>Failed to create range. Please try again.</v>
       </c>
       <c r="B3615" t="str">
-        <v>فشل في حذف الإطار</v>
+        <v>فشل في إنشاء النطاق. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C3615" t="str">
-        <v>Neizdevās dzēst ietvaru</v>
+        <v>Neizdevās izveidot diapazonu. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="3616">
       <c r="A3616" t="str">
-        <v>Failed to export audit logs</v>
+        <v>Failed to create rating</v>
       </c>
       <c r="B3616" t="str">
-        <v>فشل في تصدير سجلات التدقيق</v>
+        <v>فشل في إنشاء التقييم</v>
       </c>
       <c r="C3616" t="str">
-        <v>Neizdevās eksportēt audita žurnālus</v>
+        <v>Neizdevās izveidot vērtējumu</v>
       </c>
     </row>
     <row r="3617">
       <c r="A3617" t="str">
-        <v>Failed to import controls</v>
+        <v>Failed to create user. Please try again.</v>
       </c>
       <c r="B3617" t="str">
-        <v>فشل في استيراد الضوابط</v>
+        <v>فشل في إنشاء المستخدم. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C3617" t="str">
-        <v>Neizdevās importēt kontroles</v>
+        <v>Neizdevās izveidot lietotāju. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="3618">
       <c r="A3618" t="str">
-        <v>Failed to import processes</v>
+        <v>Failed to delete framework</v>
       </c>
       <c r="B3618" t="str">
-        <v>فشل في استيراد العمليات</v>
+        <v>فشل في حذف الإطار</v>
       </c>
       <c r="C3618" t="str">
-        <v>Neizdevās importēt procesus</v>
+        <v>Neizdevās dzēst ietvaru</v>
       </c>
     </row>
     <row r="3619">
       <c r="A3619" t="str">
-        <v>Failed to import requirements. Please check the file format.</v>
+        <v>Failed to export audit logs</v>
       </c>
       <c r="B3619" t="str">
-        <v>فشل في استيراد المتطلبات. يرجى التحقق من تنسيق الملف.</v>
+        <v>فشل في تصدير سجلات التدقيق</v>
       </c>
       <c r="C3619" t="str">
-        <v>Neizdevās importēt prasības. Lūdzu, pārbaudiet faila formātu.</v>
+        <v>Neizdevās eksportēt audita žurnālus</v>
       </c>
     </row>
     <row r="3620">
       <c r="A3620" t="str">
-        <v>Failed to import requirements. Please try again.</v>
+        <v>Failed to import controls</v>
       </c>
       <c r="B3620" t="str">
-        <v>فشل في استيراد المتطلبات. يرجى المحاولة مرة أخرى.</v>
+        <v>فشل في استيراد الضوابط</v>
       </c>
       <c r="C3620" t="str">
-        <v>Neizdevās importēt prasības. Lūdzu, mēģiniet vēlreiz.</v>
+        <v>Neizdevās importēt kontroles</v>
       </c>
     </row>
     <row r="3621">
       <c r="A3621" t="str">
-        <v>Failed to import risks</v>
+        <v>Failed to import processes</v>
       </c>
       <c r="B3621" t="str">
-        <v>فشل في استيراد المخاطر</v>
+        <v>فشل في استيراد العمليات</v>
       </c>
       <c r="C3621" t="str">
-        <v>Neizdevās importēt riskus</v>
+        <v>Neizdevās importēt procesus</v>
       </c>
     </row>
     <row r="3622">
       <c r="A3622" t="str">
-        <v>Failed to load process data</v>
+        <v>Failed to import requirements. Please check the file format.</v>
       </c>
       <c r="B3622" t="str">
-        <v>فشل في تحميل بيانات العملية</v>
+        <v>فشل في استيراد المتطلبات. يرجى التحقق من تنسيق الملف.</v>
       </c>
       <c r="C3622" t="str">
-        <v>Neizdevās ielādēt procesa datus</v>
+        <v>Neizdevās importēt prasības. Lūdzu, pārbaudiet faila formātu.</v>
       </c>
     </row>
     <row r="3623">
       <c r="A3623" t="str">
-        <v>Failed to load profile</v>
+        <v>Failed to import requirements. Please try again.</v>
       </c>
       <c r="B3623" t="str">
-        <v>فشل في تحميل الملف الشخصي</v>
+        <v>فشل في استيراد المتطلبات. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C3623" t="str">
-        <v>Neizdevās ielādēt profilu</v>
+        <v>Neizdevās importēt prasības. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="3624">
       <c r="A3624" t="str">
-        <v>Failed to perform AI Review</v>
+        <v>Failed to import risks</v>
       </c>
       <c r="B3624" t="str">
-        <v>فشل في إجراء مراجعة الذكاء الاصطناعي</v>
+        <v>فشل في استيراد المخاطر</v>
       </c>
       <c r="C3624" t="str">
-        <v>Neizdevās veikt AI pārskatu</v>
+        <v>Neizdevās importēt riskus</v>
       </c>
     </row>
     <row r="3625">
       <c r="A3625" t="str">
-        <v>Failed to resubmit exception</v>
+        <v>Failed to load process data</v>
       </c>
       <c r="B3625" t="str">
-        <v>فشل في إعادة تقديم الاستثناء</v>
+        <v>فشل في تحميل بيانات العملية</v>
       </c>
       <c r="C3625" t="str">
-        <v>Neizdevās atkārtoti iesniegt izņēmumu</v>
+        <v>Neizdevās ielādēt procesa datus</v>
       </c>
     </row>
     <row r="3626">
       <c r="A3626" t="str">
-        <v>Failed to save BIA</v>
+        <v>Failed to load profile</v>
       </c>
       <c r="B3626" t="str">
-        <v>فشل في حفظ تحليل تأثير الأعمال</v>
+        <v>فشل في تحميل الملف الشخصي</v>
       </c>
       <c r="C3626" t="str">
-        <v>Neizdevās saglabāt BIA</v>
+        <v>Neizdevās ielādēt profilu</v>
       </c>
     </row>
     <row r="3627">
       <c r="A3627" t="str">
-        <v>Failed to save BIA data</v>
+        <v>Failed to perform AI Review</v>
       </c>
       <c r="B3627" t="str">
-        <v>فشل في حفظ بيانات تحليل تأثير الأعمال</v>
+        <v>فشل في إجراء مراجعة الذكاء الاصطناعي</v>
       </c>
       <c r="C3627" t="str">
-        <v>Neizdevās saglabāt BIA datus</v>
+        <v>Neizdevās veikt AI pārskatu</v>
       </c>
     </row>
     <row r="3628">
       <c r="A3628" t="str">
-        <v>Failed to save KPI configuration</v>
+        <v>Failed to resubmit exception</v>
       </c>
       <c r="B3628" t="str">
-        <v>فشل في حفظ إعدادات مؤشرات الأداء</v>
+        <v>فشل في إعادة تقديم الاستثناء</v>
       </c>
       <c r="C3628" t="str">
-        <v>Neizdevās saglabāt KPI konfigurāciju</v>
+        <v>Neizdevās atkārtoti iesniegt izņēmumu</v>
       </c>
     </row>
     <row r="3629">
       <c r="A3629" t="str">
-        <v>Failed to save SOA changes.</v>
+        <v>Failed to save BIA</v>
       </c>
       <c r="B3629" t="str">
-        <v>فشل في حفظ تغييرات بيان التطبيق.</v>
+        <v>فشل في حفظ تحليل تأثير الأعمال</v>
       </c>
       <c r="C3629" t="str">
-        <v>Neizdevās saglabāt SOA izmaiņas.</v>
+        <v>Neizdevās saglabāt BIA</v>
       </c>
     </row>
     <row r="3630">
       <c r="A3630" t="str">
-        <v>Failed to save framework</v>
+        <v>Failed to save BIA data</v>
       </c>
       <c r="B3630" t="str">
-        <v>فشل في حفظ الإطار</v>
+        <v>فشل في حفظ بيانات تحليل تأثير الأعمال</v>
       </c>
       <c r="C3630" t="str">
-        <v>Neizdevās saglabāt ietvaru</v>
+        <v>Neizdevās saglabāt BIA datus</v>
       </c>
     </row>
     <row r="3631">
       <c r="A3631" t="str">
-        <v>Failed to save profile</v>
+        <v>Failed to save KPI configuration</v>
       </c>
       <c r="B3631" t="str">
-        <v>فشل في حفظ الملف الشخصي</v>
+        <v>فشل في حفظ إعدادات مؤشرات الأداء</v>
       </c>
       <c r="C3631" t="str">
-        <v>Neizdevās saglabāt profilu</v>
+        <v>Neizdevās saglabāt KPI konfigurāciju</v>
       </c>
     </row>
     <row r="3632">
       <c r="A3632" t="str">
-        <v>Failed to send back BIA</v>
+        <v>Failed to save SOA changes.</v>
       </c>
       <c r="B3632" t="str">
-        <v>فشل في إرجاع تحليل تأثير الأعمال</v>
+        <v>فشل في حفظ تغييرات بيان التطبيق.</v>
       </c>
       <c r="C3632" t="str">
-        <v>Neizdevās nosūtīt atpakaļ BIA</v>
+        <v>Neizdevās saglabāt SOA izmaiņas.</v>
       </c>
     </row>
     <row r="3633">
       <c r="A3633" t="str">
-        <v>Failed to send back exception</v>
+        <v>Failed to save framework</v>
       </c>
       <c r="B3633" t="str">
-        <v>فشل في إرجاع الاستثناء</v>
+        <v>فشل في حفظ الإطار</v>
       </c>
       <c r="C3633" t="str">
-        <v>Neizdevās nosūtīt atpakaļ izņēmumu</v>
+        <v>Neizdevās saglabāt ietvaru</v>
       </c>
     </row>
     <row r="3634">
       <c r="A3634" t="str">
-        <v>Failed to submit BIA</v>
+        <v>Failed to save profile</v>
       </c>
       <c r="B3634" t="str">
-        <v>فشل في تقديم تحليل تأثير الأعمال</v>
+        <v>فشل في حفظ الملف الشخصي</v>
       </c>
       <c r="C3634" t="str">
-        <v>Neizdevās iesniegt BIA</v>
+        <v>Neizdevās saglabāt profilu</v>
       </c>
     </row>
     <row r="3635">
       <c r="A3635" t="str">
-        <v>Failed to submit BIA for approval</v>
+        <v>Failed to send back BIA</v>
       </c>
       <c r="B3635" t="str">
-        <v>فشل في تقديم تحليل تأثير الأعمال للموافقة</v>
+        <v>فشل في إرجاع تحليل تأثير الأعمال</v>
       </c>
       <c r="C3635" t="str">
-        <v>Neizdevās iesniegt BIA apstiprināšanai</v>
+        <v>Neizdevās nosūtīt atpakaļ BIA</v>
       </c>
     </row>
     <row r="3636">
       <c r="A3636" t="str">
-        <v>Failed to update department</v>
+        <v>Failed to send back exception</v>
       </c>
       <c r="B3636" t="str">
-        <v>فشل في تحديث القسم</v>
+        <v>فشل في إرجاع الاستثناء</v>
       </c>
       <c r="C3636" t="str">
-        <v>Neizdevās atjaunināt nodaļu</v>
+        <v>Neizdevās nosūtīt atpakaļ izņēmumu</v>
       </c>
     </row>
     <row r="3637">
       <c r="A3637" t="str">
-        <v>Failed to update email notifications setting</v>
+        <v>Failed to submit BIA</v>
       </c>
       <c r="B3637" t="str">
-        <v>فشل في تحديث إعدادات إشعارات البريد الإلكتروني</v>
+        <v>فشل في تقديم تحليل تأثير الأعمال</v>
       </c>
       <c r="C3637" t="str">
-        <v>Neizdevās atjaunināt e-pasta paziņojumu iestatījumus</v>
+        <v>Neizdevās iesniegt BIA</v>
       </c>
     </row>
     <row r="3638">
       <c r="A3638" t="str">
-        <v>Failed to update item</v>
+        <v>Failed to submit BIA for approval</v>
       </c>
       <c r="B3638" t="str">
-        <v>فشل في تحديث العنصر</v>
+        <v>فشل في تقديم تحليل تأثير الأعمال للموافقة</v>
       </c>
       <c r="C3638" t="str">
-        <v>Neizdevās atjaunināt vienību</v>
+        <v>Neizdevās iesniegt BIA apstiprināšanai</v>
       </c>
     </row>
     <row r="3639">
       <c r="A3639" t="str">
-        <v>Failed to update label</v>
+        <v>Failed to update department</v>
       </c>
       <c r="B3639" t="str">
-        <v>فشل في تحديث التسمية</v>
+        <v>فشل في تحديث القسم</v>
       </c>
       <c r="C3639" t="str">
-        <v>Neizdevās atjaunināt apzīmējumu</v>
+        <v>Neizdevās atjaunināt nodaļu</v>
       </c>
     </row>
     <row r="3640">
       <c r="A3640" t="str">
-        <v>Failed to update profile</v>
+        <v>Failed to update email notifications setting</v>
       </c>
       <c r="B3640" t="str">
-        <v>فشل في تحديث الملف الشخصي</v>
+        <v>فشل في تحديث إعدادات إشعارات البريد الإلكتروني</v>
       </c>
       <c r="C3640" t="str">
-        <v>Neizdevās atjaunināt profilu</v>
+        <v>Neizdevās atjaunināt e-pasta paziņojumu iestatījumus</v>
       </c>
     </row>
     <row r="3641">
       <c r="A3641" t="str">
-        <v>Failed to update range</v>
+        <v>Failed to update item</v>
       </c>
       <c r="B3641" t="str">
-        <v>فشل في تحديث النطاق</v>
+        <v>فشل في تحديث العنصر</v>
       </c>
       <c r="C3641" t="str">
-        <v>Neizdevās atjaunināt diapazonu</v>
+        <v>Neizdevās atjaunināt vienību</v>
       </c>
     </row>
     <row r="3642">
       <c r="A3642" t="str">
-        <v>Failed to update range. Please try again.</v>
+        <v>Failed to update label</v>
       </c>
       <c r="B3642" t="str">
-        <v>فشل في تحديث النطاق. يرجى المحاولة مرة أخرى.</v>
+        <v>فشل في تحديث التسمية</v>
       </c>
       <c r="C3642" t="str">
-        <v>Neizdevās atjaunināt diapazonu. Lūdzu, mēģiniet vēlreiz.</v>
+        <v>Neizdevās atjaunināt apzīmējumu</v>
       </c>
     </row>
     <row r="3643">
       <c r="A3643" t="str">
-        <v>Failed to update rating</v>
+        <v>Failed to update profile</v>
       </c>
       <c r="B3643" t="str">
-        <v>فشل في تحديث التقييم</v>
+        <v>فشل في تحديث الملف الشخصي</v>
       </c>
       <c r="C3643" t="str">
-        <v>Neizdevās atjaunināt vērtējumu</v>
+        <v>Neizdevās atjaunināt profilu</v>
       </c>
     </row>
     <row r="3644">
       <c r="A3644" t="str">
-        <v>Failed to update user</v>
+        <v>Failed to update range</v>
       </c>
       <c r="B3644" t="str">
-        <v>فشل في تحديث المستخدم</v>
+        <v>فشل في تحديث النطاق</v>
       </c>
       <c r="C3644" t="str">
-        <v>Neizdevās atjaunināt lietotāju</v>
+        <v>Neizdevās atjaunināt diapazonu</v>
       </c>
     </row>
     <row r="3645">
       <c r="A3645" t="str">
-        <v>Failed to upload artifact</v>
+        <v>Failed to update range. Please try again.</v>
       </c>
       <c r="B3645" t="str">
-        <v>فشل في رفع القطعة</v>
+        <v>فشل في تحديث النطاق. يرجى المحاولة مرة أخرى.</v>
       </c>
       <c r="C3645" t="str">
-        <v>Neizdevās augšupielādēt artefaktu</v>
+        <v>Neizdevās atjaunināt diapazonu. Lūdzu, mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="3646">
       <c r="A3646" t="str">
-        <v>Network error: Failed to respond</v>
+        <v>Failed to update rating</v>
       </c>
       <c r="B3646" t="str">
-        <v>خطأ في الشبكة: فشل في الاستجابة</v>
+        <v>فشل في تحديث التقييم</v>
       </c>
       <c r="C3646" t="str">
-        <v>Tīkla kļūda: neizdevās atbildēt</v>
+        <v>Neizdevās atjaunināt vērtējumu</v>
       </c>
     </row>
     <row r="3647">
       <c r="A3647" t="str">
-        <v>Operation Failed</v>
+        <v>Failed to update user</v>
       </c>
       <c r="B3647" t="str">
-        <v>فشلت العملية</v>
+        <v>فشل في تحديث المستخدم</v>
       </c>
       <c r="C3647" t="str">
-        <v>Darbība neizdevās</v>
+        <v>Neizdevās atjaunināt lietotāju</v>
       </c>
     </row>
     <row r="3648">
       <c r="A3648" t="str">
-        <v>Unable to reach the AI service. Please check your connection and try again.</v>
+        <v>Failed to upload artifact</v>
       </c>
       <c r="B3648" t="str">
-        <v>يتعذر الوصول إلى خدمة الذكاء الاصطناعي. يرجى التحقق من اتصالك والمحاولة مرة أخرى.</v>
+        <v>فشل في رفع القطعة</v>
       </c>
       <c r="C3648" t="str">
-        <v>Nevar sasniegt AI pakalpojumu. Lūdzu, pārbaudiet savienojumu un mēģiniet vēlreiz.</v>
+        <v>Neizdevās augšupielādēt artefaktu</v>
       </c>
     </row>
     <row r="3649">
       <c r="A3649" t="str">
-        <v>Are you sure you want to delete all</v>
+        <v>Network error: Failed to respond</v>
       </c>
       <c r="B3649" t="str">
-        <v>هل أنت متأكد من حذف الكل</v>
+        <v>خطأ في الشبكة: فشل في الاستجابة</v>
       </c>
       <c r="C3649" t="str">
-        <v>Vai tiešām vēlaties dzēst visu</v>
+        <v>Tīkla kļūda: neizdevās atbildēt</v>
       </c>
     </row>
     <row r="3650">
       <c r="A3650" t="str">
-        <v>Are you sure you want to delete this category? This action cannot be undone.</v>
+        <v>Operation Failed</v>
       </c>
       <c r="B3650" t="str">
-        <v>هل أنت متأكد من حذف هذه الفئة؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>فشلت العملية</v>
       </c>
       <c r="C3650" t="str">
-        <v>Vai tiešām vēlaties dzēst šo kategoriju? Šo darbību nevar atsaukt.</v>
+        <v>Darbība neizdevās</v>
       </c>
     </row>
     <row r="3651">
       <c r="A3651" t="str">
-        <v>Are you sure you want to delete this exception? This action cannot be undone.</v>
+        <v>Unable to reach the AI service. Please check your connection and try again.</v>
       </c>
       <c r="B3651" t="str">
-        <v>هل أنت متأكد من حذف هذا الاستثناء؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>يتعذر الوصول إلى خدمة الذكاء الاصطناعي. يرجى التحقق من اتصالك والمحاولة مرة أخرى.</v>
       </c>
       <c r="C3651" t="str">
-        <v>Vai tiešām vēlaties dzēst šo izņēmumu? Šo darbību nevar atsaukt.</v>
+        <v>Nevar sasniegt AI pakalpojumu. Lūdzu, pārbaudiet savienojumu un mēģiniet vēlreiz.</v>
       </c>
     </row>
     <row r="3652">
       <c r="A3652" t="str">
-        <v>Are you sure you want to delete this framework? This action cannot be undone.</v>
+        <v>Are you sure you want to delete all</v>
       </c>
       <c r="B3652" t="str">
-        <v>هل أنت متأكد من حذف هذا الإطار؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>هل أنت متأكد من حذف الكل</v>
       </c>
       <c r="C3652" t="str">
-        <v>Vai tiešām vēlaties dzēst šo ietvaru? Šo darbību nevar atsaukt.</v>
+        <v>Vai tiešām vēlaties dzēst visu</v>
       </c>
     </row>
     <row r="3653">
       <c r="A3653" t="str">
-        <v>Are you sure you want to delete this label? This action cannot be undone.</v>
+        <v>Are you sure you want to delete this category? This action cannot be undone.</v>
       </c>
       <c r="B3653" t="str">
-        <v>هل أنت متأكد من حذف هذه التسمية؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>هل أنت متأكد من حذف هذه الفئة؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C3653" t="str">
-        <v>Vai tiešām vēlaties dzēst šo apzīmējumu? Šo darbību nevar atsaukt.</v>
+        <v>Vai tiešām vēlaties dzēst šo kategoriju? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="3654">
       <c r="A3654" t="str">
-        <v>Are you sure you want to delete this scoring range? This action cannot be undone.</v>
+        <v>Are you sure you want to delete this exception? This action cannot be undone.</v>
       </c>
       <c r="B3654" t="str">
-        <v>هل أنت متأكد من حذف نطاق التقييم هذا؟ لا يمكن التراجع عن هذا الإجراء.</v>
+        <v>هل أنت متأكد من حذف هذا الاستثناء؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C3654" t="str">
-        <v>Vai tiešām vēlaties dzēst šo vērtēšanas diapazonu? Šo darbību nevar atsaukt.</v>
+        <v>Vai tiešām vēlaties dzēst šo izņēmumu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="3655">
       <c r="A3655" t="str">
-        <v>Allocated</v>
+        <v>Are you sure you want to delete this framework? This action cannot be undone.</v>
       </c>
       <c r="B3655" t="str">
-        <v>مخصص</v>
+        <v>هل أنت متأكد من حذف هذا الإطار؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C3655" t="str">
-        <v>Piešķirts</v>
+        <v>Vai tiešām vēlaties dzēst šo ietvaru? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="3656">
       <c r="A3656" t="str">
-        <v>Already Linked</v>
+        <v>Are you sure you want to delete this label? This action cannot be undone.</v>
       </c>
       <c r="B3656" t="str">
-        <v>مرتبط بالفعل</v>
+        <v>هل أنت متأكد من حذف هذه التسمية؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C3656" t="str">
-        <v>Jau saistīts</v>
+        <v>Vai tiešām vēlaties dzēst šo apzīmējumu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="3657">
       <c r="A3657" t="str">
-        <v>Answer</v>
+        <v>Are you sure you want to delete this scoring range? This action cannot be undone.</v>
       </c>
       <c r="B3657" t="str">
-        <v>إجابة</v>
+        <v>هل أنت متأكد من حذف نطاق التقييم هذا؟ لا يمكن التراجع عن هذا الإجراء.</v>
       </c>
       <c r="C3657" t="str">
-        <v>Atbilde</v>
+        <v>Vai tiešām vēlaties dzēst šo vērtēšanas diapazonu? Šo darbību nevar atsaukt.</v>
       </c>
     </row>
     <row r="3658">
       <c r="A3658" t="str">
-        <v>Approval Information</v>
+        <v>Allocated</v>
       </c>
       <c r="B3658" t="str">
-        <v>معلومات الموافقة</v>
+        <v>مخصص</v>
       </c>
       <c r="C3658" t="str">
-        <v>Apstiprinājuma informācija</v>
+        <v>Piešķirts</v>
       </c>
     </row>
     <row r="3659">
       <c r="A3659" t="str">
-        <v>Approved By</v>
+        <v>Already Linked</v>
       </c>
       <c r="B3659" t="str">
-        <v>تمت الموافقة بواسطة</v>
+        <v>مرتبط بالفعل</v>
       </c>
       <c r="C3659" t="str">
-        <v>Apstiprināja</v>
+        <v>Jau saistīts</v>
       </c>
     </row>
     <row r="3660">
       <c r="A3660" t="str">
-        <v>Approved Date</v>
+        <v>Answer</v>
       </c>
       <c r="B3660" t="str">
-        <v>تاريخ الموافقة</v>
+        <v>إجابة</v>
       </c>
       <c r="C3660" t="str">
-        <v>Apstiprināšanas datums</v>
+        <v>Atbilde</v>
       </c>
     </row>
     <row r="3661">
       <c r="A3661" t="str">
-        <v>Approved by</v>
+        <v>Approval Information</v>
       </c>
       <c r="B3661" t="str">
-        <v>تمت الموافقة بواسطة</v>
+        <v>معلومات الموافقة</v>
       </c>
       <c r="C3661" t="str">
-        <v>Apstiprināja</v>
+        <v>Apstiprinājuma informācija</v>
       </c>
     </row>
     <row r="3662">
       <c r="A3662" t="str">
-        <v>Archived</v>
+        <v>Approved By</v>
       </c>
       <c r="B3662" t="str">
-        <v>مؤرشف</v>
+        <v>تمت الموافقة بواسطة</v>
       </c>
       <c r="C3662" t="str">
-        <v>Arhivēts</v>
+        <v>Apstiprināja</v>
       </c>
     </row>
     <row r="3663">
       <c r="A3663" t="str">
-        <v>Assessment Date</v>
+        <v>Approved Date</v>
       </c>
       <c r="B3663" t="str">
-        <v>تاريخ التقييم</v>
+        <v>تاريخ الموافقة</v>
       </c>
       <c r="C3663" t="str">
-        <v>Novērtēšanas datums</v>
+        <v>Apstiprināšanas datums</v>
       </c>
     </row>
     <row r="3664">
       <c r="A3664" t="str">
-        <v>Checking status...</v>
+        <v>Approved by</v>
       </c>
       <c r="B3664" t="str">
-        <v>جاري التحقق من الحالة...</v>
+        <v>تمت الموافقة بواسطة</v>
       </c>
       <c r="C3664" t="str">
-        <v>Pārbauda statusu...</v>
+        <v>Apstiprināja</v>
       </c>
     </row>
     <row r="3665">
       <c r="A3665" t="str">
-        <v>Clear Filters</v>
+        <v>Archived</v>
       </c>
       <c r="B3665" t="str">
-        <v>مسح عوامل التصفية</v>
+        <v>مؤرشف</v>
       </c>
       <c r="C3665" t="str">
-        <v>Notīrīt filtrus</v>
+        <v>Arhivēts</v>
       </c>
     </row>
     <row r="3666">
       <c r="A3666" t="str">
-        <v>Clear Signature</v>
+        <v>Assessment Date</v>
       </c>
       <c r="B3666" t="str">
-        <v>مسح التوقيع</v>
+        <v>تاريخ التقييم</v>
       </c>
       <c r="C3666" t="str">
-        <v>Notīrīt parakstu</v>
+        <v>Novērtēšanas datums</v>
       </c>
     </row>
     <row r="3667">
       <c r="A3667" t="str">
-        <v>Created By</v>
+        <v>Checking status...</v>
       </c>
       <c r="B3667" t="str">
-        <v>أنشئ بواسطة</v>
+        <v>جاري التحقق من الحالة...</v>
       </c>
       <c r="C3667" t="str">
-        <v>Izveidoja</v>
+        <v>Pārbauda statusu...</v>
       </c>
     </row>
     <row r="3668">
       <c r="A3668" t="str">
-        <v>Days Remaining</v>
+        <v>Clear Filters</v>
       </c>
       <c r="B3668" t="str">
-        <v>الأيام المتبقية</v>
+        <v>مسح عوامل التصفية</v>
       </c>
       <c r="C3668" t="str">
-        <v>Atlikušās dienas</v>
+        <v>Notīrīt filtrus</v>
       </c>
     </row>
     <row r="3669">
       <c r="A3669" t="str">
-        <v>Description is required</v>
+        <v>Clear Signature</v>
       </c>
       <c r="B3669" t="str">
-        <v>الوصف مطلوب</v>
+        <v>مسح التوقيع</v>
       </c>
       <c r="C3669" t="str">
-        <v>Apraksts ir obligāts</v>
+        <v>Notīrīt parakstu</v>
       </c>
     </row>
     <row r="3670">
       <c r="A3670" t="str">
-        <v>Draw your signature above</v>
+        <v>Created By</v>
       </c>
       <c r="B3670" t="str">
-        <v>ارسم توقيعك أعلاه</v>
+        <v>أنشئ بواسطة</v>
       </c>
       <c r="C3670" t="str">
-        <v>Zīmējiet savu parakstu augstāk</v>
+        <v>Izveidoja</v>
       </c>
     </row>
     <row r="3671">
       <c r="A3671" t="str">
-        <v>Edit KPI Record</v>
+        <v>Days Remaining</v>
       </c>
       <c r="B3671" t="str">
-        <v>تعديل سجل مؤشر الأداء</v>
+        <v>الأيام المتبقية</v>
       </c>
       <c r="C3671" t="str">
-        <v>Rediģēt KPI ierakstu</v>
+        <v>Atlikušās dienas</v>
       </c>
     </row>
     <row r="3672">
       <c r="A3672" t="str">
-        <v>Effective Date</v>
+        <v>Description is required</v>
       </c>
       <c r="B3672" t="str">
-        <v>تاريخ السريان</v>
+        <v>الوصف مطلوب</v>
       </c>
       <c r="C3672" t="str">
-        <v>Spēkā stāšanās datums</v>
+        <v>Apraksts ir obligāts</v>
       </c>
     </row>
     <row r="3673">
       <c r="A3673" t="str">
-        <v>Email notifications disabled</v>
+        <v>Draw your signature above</v>
       </c>
       <c r="B3673" t="str">
-        <v>إشعارات البريد الإلكتروني معطلة</v>
+        <v>ارسم توقيعك أعلاه</v>
       </c>
       <c r="C3673" t="str">
-        <v>E-pasta paziņojumi atspējoti</v>
+        <v>Zīmējiet savu parakstu augstāk</v>
       </c>
     </row>
     <row r="3674">
       <c r="A3674" t="str">
-        <v>Email notifications enabled</v>
+        <v>Edit KPI Record</v>
       </c>
       <c r="B3674" t="str">
-        <v>إشعارات البريد الإلكتروني مفعلة</v>
+        <v>تعديل سجل مؤشر الأداء</v>
       </c>
       <c r="C3674" t="str">
-        <v>E-pasta paziņojumi iespējoti</v>
+        <v>Rediģēt KPI ierakstu</v>
       </c>
     </row>
     <row r="3675">
       <c r="A3675" t="str">
-        <v>End date is required</v>
+        <v>Effective Date</v>
       </c>
       <c r="B3675" t="str">
-        <v>تاريخ الانتهاء مطلوب</v>
+        <v>تاريخ السريان</v>
       </c>
       <c r="C3675" t="str">
-        <v>Beigu datums ir obligāts</v>
+        <v>Spēkā stāšanās datums</v>
       </c>
     </row>
     <row r="3676">
       <c r="A3676" t="str">
-        <v>Enter description or justification</v>
+        <v>Email notifications disabled</v>
       </c>
       <c r="B3676" t="str">
-        <v>أدخل الوصف أو المبرر</v>
+        <v>إشعارات البريد الإلكتروني معطلة</v>
       </c>
       <c r="C3676" t="str">
-        <v>Ievadiet aprakstu vai pamatojumu</v>
+        <v>E-pasta paziņojumi atspējoti</v>
       </c>
     </row>
     <row r="3677">
       <c r="A3677" t="str">
-        <v>Enter justification</v>
+        <v>Email notifications enabled</v>
       </c>
       <c r="B3677" t="str">
-        <v>أدخل المبرر</v>
+        <v>إشعارات البريد الإلكتروني مفعلة</v>
       </c>
       <c r="C3677" t="str">
-        <v>Ievadiet pamatojumu</v>
+        <v>E-pasta paziņojumi iespējoti</v>
       </c>
     </row>
     <row r="3678">
       <c r="A3678" t="str">
-        <v>Enter reason for sending back...</v>
+        <v>End date is required</v>
       </c>
       <c r="B3678" t="str">
-        <v>أدخل سبب الإرجاع...</v>
+        <v>تاريخ الانتهاء مطلوب</v>
       </c>
       <c r="C3678" t="str">
-        <v>Ievadiet atpakaļnosūtīšanas iemeslu...</v>
+        <v>Beigu datums ir obligāts</v>
       </c>
     </row>
     <row r="3679">
       <c r="A3679" t="str">
-        <v>Filters</v>
+        <v>Enter description or justification</v>
       </c>
       <c r="B3679" t="str">
-        <v>عوامل التصفية</v>
+        <v>أدخل الوصف أو المبرر</v>
       </c>
       <c r="C3679" t="str">
-        <v>Filtri</v>
+        <v>Ievadiet aprakstu vai pamatojumu</v>
       </c>
     </row>
     <row r="3680">
       <c r="A3680" t="str">
-        <v>Half-Yearly</v>
+        <v>Enter justification</v>
       </c>
       <c r="B3680" t="str">
-        <v>نصف سنوي</v>
+        <v>أدخل المبرر</v>
       </c>
       <c r="C3680" t="str">
-        <v>Pusgada</v>
+        <v>Ievadiet pamatojumu</v>
       </c>
     </row>
     <row r="3681">
       <c r="A3681" t="str">
-        <v>KPI Recurrence</v>
+        <v>Enter reason for sending back...</v>
       </c>
       <c r="B3681" t="str">
-        <v>تكرار مؤشرات الأداء</v>
+        <v>أدخل سبب الإرجاع...</v>
       </c>
       <c r="C3681" t="str">
-        <v>KPI periodiskums</v>
+        <v>Ievadiet atpakaļnosūtīšanas iemeslu...</v>
       </c>
     </row>
     <row r="3682">
       <c r="A3682" t="str">
-        <v>Label Name</v>
+        <v>Filters</v>
       </c>
       <c r="B3682" t="str">
-        <v>اسم التسمية</v>
+        <v>عوامل التصفية</v>
       </c>
       <c r="C3682" t="str">
-        <v>Apzīmējuma nosaukums</v>
+        <v>Filtri</v>
       </c>
     </row>
     <row r="3683">
       <c r="A3683" t="str">
-        <v>Link Artifact</v>
+        <v>Half-Yearly</v>
       </c>
       <c r="B3683" t="str">
-        <v>ربط القطعة</v>
+        <v>نصف سنوي</v>
       </c>
       <c r="C3683" t="str">
-        <v>Saistīt artefaktu</v>
+        <v>Pusgada</v>
       </c>
     </row>
     <row r="3684">
       <c r="A3684" t="str">
-        <v>Linked from Vault</v>
+        <v>KPI Recurrence</v>
       </c>
       <c r="B3684" t="str">
-        <v>مرتبط من الخزنة</v>
+        <v>تكرار مؤشرات الأداء</v>
       </c>
       <c r="C3684" t="str">
-        <v>Saistīts no glabātuves</v>
+        <v>KPI periodiskums</v>
       </c>
     </row>
     <row r="3685">
       <c r="A3685" t="str">
-        <v>No Data</v>
+        <v>Label Name</v>
       </c>
       <c r="B3685" t="str">
-        <v>لا توجد بيانات</v>
+        <v>اسم التسمية</v>
       </c>
       <c r="C3685" t="str">
-        <v>Nav datu</v>
+        <v>Apzīmējuma nosaukums</v>
       </c>
     </row>
     <row r="3686">
       <c r="A3686" t="str">
-        <v>No Framework</v>
+        <v>Link Artifact</v>
       </c>
       <c r="B3686" t="str">
-        <v>لا يوجد إطار</v>
+        <v>ربط القطعة</v>
       </c>
       <c r="C3686" t="str">
-        <v>Nav ietvara</v>
+        <v>Saistīt artefaktu</v>
       </c>
     </row>
     <row r="3687">
       <c r="A3687" t="str">
-        <v>No Risks Found</v>
+        <v>Linked from Vault</v>
       </c>
       <c r="B3687" t="str">
-        <v>لم يتم العثور على مخاطر</v>
+        <v>مرتبط من الخزنة</v>
       </c>
       <c r="C3687" t="str">
-        <v>Riski nav atrasti</v>
+        <v>Saistīts no glabātuves</v>
       </c>
     </row>
     <row r="3688">
       <c r="A3688" t="str">
-        <v>No Users</v>
+        <v>No Data</v>
       </c>
       <c r="B3688" t="str">
-        <v>لا يوجد مستخدمون</v>
+        <v>لا توجد بيانات</v>
       </c>
       <c r="C3688" t="str">
-        <v>Nav lietotāju</v>
+        <v>Nav datu</v>
       </c>
     </row>
     <row r="3689">
       <c r="A3689" t="str">
-        <v>No changes</v>
+        <v>No Framework</v>
       </c>
       <c r="B3689" t="str">
-        <v>لا توجد تغييرات</v>
+        <v>لا يوجد إطار</v>
       </c>
       <c r="C3689" t="str">
-        <v>Nav izmaiņu</v>
+        <v>Nav ietvara</v>
       </c>
     </row>
     <row r="3690">
       <c r="A3690" t="str">
-        <v>No changes to save.</v>
+        <v>No Risks Found</v>
       </c>
       <c r="B3690" t="str">
-        <v>لا توجد تغييرات للحفظ.</v>
+        <v>لم يتم العثور على مخاطر</v>
       </c>
       <c r="C3690" t="str">
-        <v>Nav izmaiņu, ko saglabāt.</v>
+        <v>Riski nav atrasti</v>
       </c>
     </row>
     <row r="3691">
       <c r="A3691" t="str">
-        <v>No description provided</v>
+        <v>No Users</v>
       </c>
       <c r="B3691" t="str">
-        <v>لم يتم تقديم وصف</v>
+        <v>لا يوجد مستخدمون</v>
       </c>
       <c r="C3691" t="str">
-        <v>Apraksts nav norādīts</v>
+        <v>Nav lietotāju</v>
       </c>
     </row>
     <row r="3692">
       <c r="A3692" t="str">
-        <v>No detailed review data available</v>
+        <v>No changes</v>
       </c>
       <c r="B3692" t="str">
-        <v>لا تتوفر بيانات مراجعة تفصيلية</v>
+        <v>لا توجد تغييرات</v>
       </c>
       <c r="C3692" t="str">
-        <v>Nav pieejami detalizēti pārskata dati</v>
+        <v>Nav izmaiņu</v>
       </c>
     </row>
     <row r="3693">
       <c r="A3693" t="str">
-        <v>No document attached</v>
+        <v>No changes to save.</v>
       </c>
       <c r="B3693" t="str">
-        <v>لم يتم إرفاق مستند</v>
+        <v>لا توجد تغييرات للحفظ.</v>
       </c>
       <c r="C3693" t="str">
-        <v>Dokuments nav pievienots</v>
+        <v>Nav izmaiņu, ko saglabāt.</v>
       </c>
     </row>
     <row r="3694">
       <c r="A3694" t="str">
-        <v>No documents found in vault</v>
+        <v>No description provided</v>
       </c>
       <c r="B3694" t="str">
-        <v>لم يتم العثور على مستندات في الخزنة</v>
+        <v>لم يتم تقديم وصف</v>
       </c>
       <c r="C3694" t="str">
-        <v>Glabātuvē nav atrasti dokumenti</v>
+        <v>Apraksts nav norādīts</v>
       </c>
     </row>
     <row r="3695">
       <c r="A3695" t="str">
-        <v>No limit</v>
+        <v>No detailed review data available</v>
       </c>
       <c r="B3695" t="str">
-        <v>بلا حدود</v>
+        <v>لا تتوفر بيانات مراجعة تفصيلية</v>
       </c>
       <c r="C3695" t="str">
-        <v>Nav ierobežojuma</v>
+        <v>Nav pieejami detalizēti pārskata dati</v>
       </c>
     </row>
     <row r="3696">
       <c r="A3696" t="str">
-        <v>No processes to export</v>
+        <v>No document attached</v>
       </c>
       <c r="B3696" t="str">
-        <v>لا توجد عمليات للتصدير</v>
+        <v>لم يتم إرفاق مستند</v>
       </c>
       <c r="C3696" t="str">
-        <v>Nav procesu eksportēšanai</v>
+        <v>Dokuments nav pievienots</v>
       </c>
     </row>
     <row r="3697">
       <c r="A3697" t="str">
-        <v>No processes were imported</v>
+        <v>No documents found in vault</v>
       </c>
       <c r="B3697" t="str">
-        <v>لم يتم استيراد أي عمليات</v>
+        <v>لم يتم العثور على مستندات في الخزنة</v>
       </c>
       <c r="C3697" t="str">
-        <v>Neviens process netika importēts</v>
+        <v>Glabātuvē nav atrasti dokumenti</v>
       </c>
     </row>
     <row r="3698">
       <c r="A3698" t="str">
-        <v>Not Found</v>
+        <v>No limit</v>
       </c>
       <c r="B3698" t="str">
-        <v>غير موجود</v>
+        <v>بلا حدود</v>
       </c>
       <c r="C3698" t="str">
-        <v>Nav atrasts</v>
+        <v>Nav ierobežojuma</v>
       </c>
     </row>
     <row r="3699">
       <c r="A3699" t="str">
-        <v>Not Set</v>
+        <v>No processes to export</v>
       </c>
       <c r="B3699" t="str">
-        <v>غير محدد</v>
+        <v>لا توجد عمليات للتصدير</v>
       </c>
       <c r="C3699" t="str">
-        <v>Nav iestatīts</v>
+        <v>Nav procesu eksportēšanai</v>
       </c>
     </row>
     <row r="3700">
       <c r="A3700" t="str">
-        <v>Ongoing</v>
+        <v>No processes were imported</v>
       </c>
       <c r="B3700" t="str">
-        <v>مستمر</v>
+        <v>لم يتم استيراد أي عمليات</v>
       </c>
       <c r="C3700" t="str">
-        <v>Notiekošs</v>
+        <v>Neviens process netika importēts</v>
       </c>
     </row>
     <row r="3701">
       <c r="A3701" t="str">
-        <v>Only letters, numbers, spaces, hyphens, and colons are allowed</v>
+        <v>Not Found</v>
       </c>
       <c r="B3701" t="str">
-        <v>يُسمح فقط بالأحرف والأرقام والمسافات والشرطات والنقطتين</v>
+        <v>غير موجود</v>
       </c>
       <c r="C3701" t="str">
-        <v>Atļauti tikai burti, cipari, atstarpes, defises un koli</v>
+        <v>Nav atrasts</v>
       </c>
     </row>
     <row r="3702">
       <c r="A3702" t="str">
-        <v>Please Select the Function</v>
+        <v>Not Set</v>
       </c>
       <c r="B3702" t="str">
-        <v>يرجى اختيار الوظيفة</v>
+        <v>غير محدد</v>
       </c>
       <c r="C3702" t="str">
-        <v>Lūdzu, atlasiet funkciju</v>
+        <v>Nav iestatīts</v>
       </c>
     </row>
     <row r="3703">
       <c r="A3703" t="str">
-        <v>Please enter the Process Name</v>
+        <v>Ongoing</v>
       </c>
       <c r="B3703" t="str">
-        <v>يرجى إدخال اسم العملية</v>
+        <v>مستمر</v>
       </c>
       <c r="C3703" t="str">
-        <v>Lūdzu, ievadiet procesa nosaukumu</v>
+        <v>Notiekošs</v>
       </c>
     </row>
     <row r="3704">
       <c r="A3704" t="str">
-        <v>Please provide a comment explaining the changes made before resubmitting for approval.</v>
+        <v>Only letters, numbers, spaces, hyphens, and colons are allowed</v>
       </c>
       <c r="B3704" t="str">
-        <v>يرجى تقديم تعليق يوضح التغييرات التي تم إجراؤها قبل إعادة التقديم للموافقة.</v>
+        <v>يُسمح فقط بالأحرف والأرقام والمسافات والشرطات والنقطتين</v>
       </c>
       <c r="C3704" t="str">
-        <v>Lūdzu, norādiet komentāru, kas paskaidro veiktās izmaiņas pirms atkārtotas iesniegšanas apstiprināšanai.</v>
+        <v>Atļauti tikai burti, cipari, atstarpes, defises un koli</v>
       </c>
     </row>
     <row r="3705">
       <c r="A3705" t="str">
-        <v>Please provide a reason for sending back this exception request.</v>
+        <v>Please Select the Function</v>
       </c>
       <c r="B3705" t="str">
-        <v>يرجى تقديم سبب لإرجاع طلب الاستثناء هذا.</v>
+        <v>يرجى اختيار الوظيفة</v>
       </c>
       <c r="C3705" t="str">
-        <v>Lūdzu, norādiet iemeslu šī izņēmuma pieprasījuma atpakaļnosūtīšanai.</v>
+        <v>Lūdzu, atlasiet funkciju</v>
       </c>
     </row>
     <row r="3706">
       <c r="A3706" t="str">
-        <v>Please select an approver</v>
+        <v>Please enter the Process Name</v>
       </c>
       <c r="B3706" t="str">
-        <v>يرجى اختيار مُعتمد</v>
+        <v>يرجى إدخال اسم العملية</v>
       </c>
       <c r="C3706" t="str">
-        <v>Lūdzu, atlasiet apstiprinātāju</v>
+        <v>Lūdzu, ievadiet procesa nosaukumu</v>
       </c>
     </row>
     <row r="3707">
       <c r="A3707" t="str">
-        <v>Please select service user</v>
+        <v>Please provide a comment explaining the changes made before resubmitting for approval.</v>
       </c>
       <c r="B3707" t="str">
-        <v>يرجى اختيار مستخدم الخدمة</v>
+        <v>يرجى تقديم تعليق يوضح التغييرات التي تم إجراؤها قبل إعادة التقديم للموافقة.</v>
       </c>
       <c r="C3707" t="str">
-        <v>Lūdzu, atlasiet pakalpojuma lietotāju</v>
+        <v>Lūdzu, norādiet komentāru, kas paskaidro veiktās izmaiņas pirms atkārtotas iesniegšanas apstiprināšanai.</v>
       </c>
     </row>
     <row r="3708">
       <c r="A3708" t="str">
-        <v>Please select the service title</v>
+        <v>Please provide a reason for sending back this exception request.</v>
       </c>
       <c r="B3708" t="str">
-        <v>يرجى اختيار عنوان الخدمة</v>
+        <v>يرجى تقديم سبب لإرجاع طلب الاستثناء هذا.</v>
       </c>
       <c r="C3708" t="str">
-        <v>Lūdzu, atlasiet pakalpojuma nosaukumu</v>
+        <v>Lūdzu, norādiet iemeslu šī izņēmuma pieprasījuma atpakaļnosūtīšanai.</v>
       </c>
     </row>
     <row r="3709">
       <c r="A3709" t="str">
-        <v>Please sign below to publish this</v>
+        <v>Please select an approver</v>
       </c>
       <c r="B3709" t="str">
-        <v>يرجى التوقيع أدناه لنشر هذا</v>
+        <v>يرجى اختيار مُعتمد</v>
       </c>
       <c r="C3709" t="str">
-        <v>Lūdzu, parakstieties zemāk, lai publicētu šo</v>
+        <v>Lūdzu, atlasiet apstiprinātāju</v>
       </c>
     </row>
     <row r="3710">
       <c r="A3710" t="str">
-        <v>Processing document...</v>
+        <v>Please select service user</v>
       </c>
       <c r="B3710" t="str">
-        <v>جاري معالجة المستند...</v>
+        <v>يرجى اختيار مستخدم الخدمة</v>
       </c>
       <c r="C3710" t="str">
-        <v>Apstrādā dokumentu...</v>
+        <v>Lūdzu, atlasiet pakalpojuma lietotāju</v>
       </c>
     </row>
     <row r="3711">
       <c r="A3711" t="str">
-        <v>Processing...</v>
+        <v>Please select the service title</v>
       </c>
       <c r="B3711" t="str">
-        <v>جاري المعالجة...</v>
+        <v>يرجى اختيار عنوان الخدمة</v>
       </c>
       <c r="C3711" t="str">
-        <v>Apstrādā...</v>
+        <v>Lūdzu, atlasiet pakalpojuma nosaukumu</v>
       </c>
     </row>
     <row r="3712">
       <c r="A3712" t="str">
-        <v>Question</v>
+        <v>Please sign below to publish this</v>
       </c>
       <c r="B3712" t="str">
-        <v>سؤال</v>
+        <v>يرجى التوقيع أدناه لنشر هذا</v>
       </c>
       <c r="C3712" t="str">
-        <v>Jautājums</v>
+        <v>Lūdzu, parakstieties zemāk, lai publicētu šo</v>
       </c>
     </row>
     <row r="3713">
       <c r="A3713" t="str">
-        <v>Queued for processing...</v>
+        <v>Processing document...</v>
       </c>
       <c r="B3713" t="str">
-        <v>في قائمة الانتظار للمعالجة...</v>
+        <v>جاري معالجة المستند...</v>
       </c>
       <c r="C3713" t="str">
-        <v>Ierindots apstrādei...</v>
+        <v>Apstrādā dokumentu...</v>
       </c>
     </row>
     <row r="3714">
       <c r="A3714" t="str">
-        <v>Remaining</v>
+        <v>Processing...</v>
       </c>
       <c r="B3714" t="str">
-        <v>المتبقي</v>
+        <v>جاري المعالجة...</v>
       </c>
       <c r="C3714" t="str">
-        <v>Atlicis</v>
+        <v>Apstrādā...</v>
       </c>
     </row>
     <row r="3715">
       <c r="A3715" t="str">
-        <v>Report Not Found</v>
+        <v>Question</v>
       </c>
       <c r="B3715" t="str">
-        <v>لم يتم العثور على التقرير</v>
+        <v>سؤال</v>
       </c>
       <c r="C3715" t="str">
-        <v>Atskaite nav atrasta</v>
+        <v>Jautājums</v>
       </c>
     </row>
     <row r="3716">
       <c r="A3716" t="str">
-        <v>Saved</v>
+        <v>Queued for processing...</v>
       </c>
       <c r="B3716" t="str">
-        <v>تم الحفظ</v>
+        <v>في قائمة الانتظار للمعالجة...</v>
       </c>
       <c r="C3716" t="str">
-        <v>Saglabāts</v>
+        <v>Ierindots apstrādei...</v>
       </c>
     </row>
     <row r="3717">
       <c r="A3717" t="str">
-        <v>Search audit logs...</v>
+        <v>Remaining</v>
       </c>
       <c r="B3717" t="str">
-        <v>بحث في سجلات التدقيق...</v>
+        <v>المتبقي</v>
       </c>
       <c r="C3717" t="str">
-        <v>Meklēt audita žurnālos...</v>
+        <v>Atlicis</v>
       </c>
     </row>
     <row r="3718">
       <c r="A3718" t="str">
-        <v>Search by requirement code, name, control code...</v>
+        <v>Report Not Found</v>
       </c>
       <c r="B3718" t="str">
-        <v>بحث حسب رمز المتطلب، الاسم، رمز الضابط...</v>
+        <v>لم يتم العثور على التقرير</v>
       </c>
       <c r="C3718" t="str">
-        <v>Meklēt pēc prasības koda, nosaukuma, kontroles koda...</v>
+        <v>Atskaite nav atrasta</v>
       </c>
     </row>
     <row r="3719">
       <c r="A3719" t="str">
-        <v>Search documents...</v>
+        <v>Saved</v>
       </c>
       <c r="B3719" t="str">
-        <v>بحث في المستندات...</v>
+        <v>تم الحفظ</v>
       </c>
       <c r="C3719" t="str">
-        <v>Meklēt dokumentos...</v>
+        <v>Saglabāts</v>
       </c>
     </row>
     <row r="3720">
       <c r="A3720" t="str">
-        <v>Search labels...</v>
+        <v>Search audit logs...</v>
       </c>
       <c r="B3720" t="str">
-        <v>بحث في التسميات...</v>
+        <v>بحث في سجلات التدقيق...</v>
       </c>
       <c r="C3720" t="str">
-        <v>Meklēt apzīmējumos...</v>
+        <v>Meklēt audita žurnālos...</v>
       </c>
     </row>
     <row r="3721">
       <c r="A3721" t="str">
-        <v>Search records...</v>
+        <v>Search by requirement code, name, control code...</v>
       </c>
       <c r="B3721" t="str">
-        <v>بحث في السجلات...</v>
+        <v>بحث حسب رمز المتطلب، الاسم، رمز الضابط...</v>
       </c>
       <c r="C3721" t="str">
-        <v>Meklēt ierakstos...</v>
+        <v>Meklēt pēc prasības koda, nosaukuma, kontroles koda...</v>
       </c>
     </row>
     <row r="3722">
       <c r="A3722" t="str">
-        <v>Select Department First</v>
+        <v>Search documents...</v>
       </c>
       <c r="B3722" t="str">
-        <v>اختر القسم أولاً</v>
+        <v>بحث في المستندات...</v>
       </c>
       <c r="C3722" t="str">
-        <v>Vispirms atlasiet nodaļu</v>
+        <v>Meklēt dokumentos...</v>
       </c>
     </row>
     <row r="3723">
       <c r="A3723" t="str">
-        <v>Select Exception</v>
+        <v>Search labels...</v>
       </c>
       <c r="B3723" t="str">
-        <v>اختر الاستثناء</v>
+        <v>بحث في التسميات...</v>
       </c>
       <c r="C3723" t="str">
-        <v>Atlasīt izņēmumu</v>
+        <v>Meklēt apzīmējumos...</v>
       </c>
     </row>
     <row r="3724">
       <c r="A3724" t="str">
-        <v>Select Frequency</v>
+        <v>Search records...</v>
       </c>
       <c r="B3724" t="str">
-        <v>اختر التكرار</v>
+        <v>بحث في السجلات...</v>
       </c>
       <c r="C3724" t="str">
-        <v>Atlasīt biežumu</v>
+        <v>Meklēt ierakstos...</v>
       </c>
     </row>
     <row r="3725">
       <c r="A3725" t="str">
-        <v>Select Nature</v>
+        <v>Select Department First</v>
       </c>
       <c r="B3725" t="str">
-        <v>اختر الطبيعة</v>
+        <v>اختر القسم أولاً</v>
       </c>
       <c r="C3725" t="str">
-        <v>Atlasīt veidu</v>
+        <v>Vispirms atlasiet nodaļu</v>
       </c>
     </row>
     <row r="3726">
       <c r="A3726" t="str">
-        <v>Select Process Type</v>
+        <v>Select Exception</v>
       </c>
       <c r="B3726" t="str">
-        <v>اختر نوع العملية</v>
+        <v>اختر الاستثناء</v>
       </c>
       <c r="C3726" t="str">
-        <v>Atlasīt procesa tipu</v>
+        <v>Atlasīt izņēmumu</v>
       </c>
     </row>
     <row r="3727">
       <c r="A3727" t="str">
-        <v>Select an asset</v>
+        <v>Select Frequency</v>
       </c>
       <c r="B3727" t="str">
-        <v>اختر أصلاً</v>
+        <v>اختر التكرار</v>
       </c>
       <c r="C3727" t="str">
-        <v>Atlasīt aktīvu</v>
+        <v>Atlasīt biežumu</v>
       </c>
     </row>
     <row r="3728">
       <c r="A3728" t="str">
-        <v>Select an exception</v>
+        <v>Select Nature</v>
       </c>
       <c r="B3728" t="str">
-        <v>اختر استثناءً</v>
+        <v>اختر الطبيعة</v>
       </c>
       <c r="C3728" t="str">
-        <v>Atlasīt izņēmumu</v>
+        <v>Atlasīt veidu</v>
       </c>
     </row>
     <row r="3729">
       <c r="A3729" t="str">
-        <v>Select compliance</v>
+        <v>Select Process Type</v>
       </c>
       <c r="B3729" t="str">
-        <v>اختر الامتثال</v>
+        <v>اختر نوع العملية</v>
       </c>
       <c r="C3729" t="str">
-        <v>Atlasīt atbilstību</v>
+        <v>Atlasīt procesa tipu</v>
       </c>
     </row>
     <row r="3730">
       <c r="A3730" t="str">
-        <v>Select target audiences</v>
+        <v>Select an asset</v>
       </c>
       <c r="B3730" t="str">
-        <v>اختر الجماهير المستهدفة</v>
+        <v>اختر أصلاً</v>
       </c>
       <c r="C3730" t="str">
-        <v>Atlasīt mērķa auditorijas</v>
+        <v>Atlasīt aktīvu</v>
       </c>
     </row>
     <row r="3731">
       <c r="A3731" t="str">
-        <v>Select user</v>
+        <v>Select an exception</v>
       </c>
       <c r="B3731" t="str">
-        <v>اختر المستخدم</v>
+        <v>اختر استثناءً</v>
       </c>
       <c r="C3731" t="str">
-        <v>Atlasīt lietotāju</v>
+        <v>Atlasīt izņēmumu</v>
       </c>
     </row>
     <row r="3732">
       <c r="A3732" t="str">
-        <v>Send Back Exception</v>
+        <v>Select compliance</v>
       </c>
       <c r="B3732" t="str">
-        <v>إرجاع الاستثناء</v>
+        <v>اختر الامتثال</v>
       </c>
       <c r="C3732" t="str">
-        <v>Nosūtīt atpakaļ izņēmumu</v>
+        <v>Atlasīt atbilstību</v>
       </c>
     </row>
     <row r="3733">
       <c r="A3733" t="str">
-        <v>Send Back for Revision</v>
+        <v>Select target audiences</v>
       </c>
       <c r="B3733" t="str">
-        <v>إرجاع للمراجعة</v>
+        <v>اختر الجماهير المستهدفة</v>
       </c>
       <c r="C3733" t="str">
-        <v>Nosūtīt atpakaļ pārskatīšanai</v>
+        <v>Atlasīt mērķa auditorijas</v>
       </c>
     </row>
     <row r="3734">
       <c r="A3734" t="str">
-        <v>Signature</v>
+        <v>Select user</v>
       </c>
       <c r="B3734" t="str">
-        <v>التوقيع</v>
+        <v>اختر المستخدم</v>
       </c>
       <c r="C3734" t="str">
-        <v>Paraksts</v>
+        <v>Atlasīt lietotāju</v>
       </c>
     </row>
     <row r="3735">
       <c r="A3735" t="str">
-        <v>Signature not available</v>
+        <v>Send Back Exception</v>
       </c>
       <c r="B3735" t="str">
-        <v>التوقيع غير متاح</v>
+        <v>إرجاع الاستثناء</v>
       </c>
       <c r="C3735" t="str">
-        <v>Paraksts nav pieejams</v>
+        <v>Nosūtīt atpakaļ izņēmumu</v>
       </c>
     </row>
     <row r="3736">
       <c r="A3736" t="str">
-        <v>Skipped</v>
+        <v>Send Back for Revision</v>
       </c>
       <c r="B3736" t="str">
-        <v>تم تخطيه</v>
+        <v>إرجاع للمراجعة</v>
       </c>
       <c r="C3736" t="str">
-        <v>Izlaists</v>
+        <v>Nosūtīt atpakaļ pārskatīšanai</v>
       </c>
     </row>
     <row r="3737">
       <c r="A3737" t="str">
-        <v>Some changes failed to save.</v>
+        <v>Signature</v>
       </c>
       <c r="B3737" t="str">
-        <v>فشل حفظ بعض التغييرات.</v>
+        <v>التوقيع</v>
       </c>
       <c r="C3737" t="str">
-        <v>Dažas izmaiņas neizdevās saglabāt.</v>
+        <v>Paraksts</v>
       </c>
     </row>
     <row r="3738">
       <c r="A3738" t="str">
-        <v>Special characters are not allowed</v>
+        <v>Signature not available</v>
       </c>
       <c r="B3738" t="str">
-        <v>الأحرف الخاصة غير مسموح بها</v>
+        <v>التوقيع غير متاح</v>
       </c>
       <c r="C3738" t="str">
-        <v>Speciālās rakstzīmes nav atļautas</v>
+        <v>Paraksts nav pieejams</v>
       </c>
     </row>
     <row r="3739">
       <c r="A3739" t="str">
-        <v>Stakeholder Information</v>
+        <v>Skipped</v>
       </c>
       <c r="B3739" t="str">
-        <v>معلومات أصحاب المصلحة</v>
+        <v>تم تخطيه</v>
       </c>
       <c r="C3739" t="str">
-        <v>Ieinteresēto personu informācija</v>
+        <v>Izlaists</v>
       </c>
     </row>
     <row r="3740">
       <c r="A3740" t="str">
-        <v>Subscribe</v>
+        <v>Some changes failed to save.</v>
       </c>
       <c r="B3740" t="str">
-        <v>اشتراك</v>
+        <v>فشل حفظ بعض التغييرات.</v>
       </c>
       <c r="C3740" t="str">
-        <v>Abonēt</v>
+        <v>Dažas izmaiņas neizdevās saglabāt.</v>
       </c>
     </row>
     <row r="3741">
       <c r="A3741" t="str">
-        <v>Task Progress</v>
+        <v>Special characters are not allowed</v>
       </c>
       <c r="B3741" t="str">
-        <v>تقدم المهمة</v>
+        <v>الأحرف الخاصة غير مسموح بها</v>
       </c>
       <c r="C3741" t="str">
-        <v>Uzdevuma progress</v>
+        <v>Speciālās rakstzīmes nav atļautas</v>
       </c>
     </row>
     <row r="3742">
       <c r="A3742" t="str">
-        <v>Timeframe</v>
+        <v>Stakeholder Information</v>
       </c>
       <c r="B3742" t="str">
-        <v>الإطار الزمني</v>
+        <v>معلومات أصحاب المصلحة</v>
       </c>
       <c r="C3742" t="str">
-        <v>Laika periods</v>
+        <v>Ieinteresēto personu informācija</v>
       </c>
     </row>
     <row r="3743">
       <c r="A3743" t="str">
-        <v>Toggle Columns</v>
+        <v>Subscribe</v>
       </c>
       <c r="B3743" t="str">
-        <v>تبديل الأعمدة</v>
+        <v>اشتراك</v>
       </c>
       <c r="C3743" t="str">
-        <v>Pārslēgt kolonnas</v>
+        <v>Abonēt</v>
       </c>
     </row>
     <row r="3744">
       <c r="A3744" t="str">
-        <v>Unlink Artifact</v>
+        <v>Task Progress</v>
       </c>
       <c r="B3744" t="str">
-        <v>إلغاء ربط القطعة</v>
+        <v>تقدم المهمة</v>
       </c>
       <c r="C3744" t="str">
-        <v>Atsaistīt artefaktu</v>
+        <v>Uzdevuma progress</v>
       </c>
     </row>
     <row r="3745">
       <c r="A3745" t="str">
-        <v>Unsaved changes</v>
+        <v>Timeframe</v>
       </c>
       <c r="B3745" t="str">
-        <v>تغييرات غير محفوظة</v>
+        <v>الإطار الزمني</v>
       </c>
       <c r="C3745" t="str">
-        <v>Nesaglabātas izmaiņas</v>
+        <v>Laika periods</v>
       </c>
     </row>
     <row r="3746">
       <c r="A3746" t="str">
-        <v>User Details</v>
+        <v>Toggle Columns</v>
       </c>
       <c r="B3746" t="str">
-        <v>تفاصيل المستخدم</v>
+        <v>تبديل الأعمدة</v>
       </c>
       <c r="C3746" t="str">
-        <v>Lietotāja detaļas</v>
+        <v>Pārslēgt kolonnas</v>
       </c>
     </row>
     <row r="3747">
       <c r="A3747" t="str">
-        <v>View More</v>
+        <v>Unlink Artifact</v>
       </c>
       <c r="B3747" t="str">
-        <v>عرض المزيد</v>
+        <v>إلغاء ربط القطعة</v>
       </c>
       <c r="C3747" t="str">
-        <v>Skatīt vairāk</v>
+        <v>Atsaistīt artefaktu</v>
       </c>
     </row>
     <row r="3748">
       <c r="A3748" t="str">
-        <v>You don't have permission to access Evidence.</v>
+        <v>Unsaved changes</v>
       </c>
       <c r="B3748" t="str">
-        <v>ليس لديك صلاحية للوصول إلى الأدلة.</v>
+        <v>تغييرات غير محفوظة</v>
       </c>
       <c r="C3748" t="str">
-        <v>Jums nav atļaujas piekļūt pierādījumiem.</v>
+        <v>Nesaglabātas izmaiņas</v>
       </c>
     </row>
     <row r="3749">
       <c r="A3749" t="str">
-        <v>You don't have permission to access Risk Assessment.</v>
+        <v>User Details</v>
       </c>
       <c r="B3749" t="str">
-        <v>ليس لديك صلاحية للوصول إلى تقييم المخاطر.</v>
+        <v>تفاصيل المستخدم</v>
       </c>
       <c r="C3749" t="str">
-        <v>Jums nav atļaujas piekļūt risku novērtējumam.</v>
+        <v>Lietotāja detaļas</v>
       </c>
     </row>
     <row r="3750">
       <c r="A3750" t="str">
-        <v>You don't have permission to access Risk Control Matrix.</v>
+        <v>View More</v>
       </c>
       <c r="B3750" t="str">
-        <v>ليس لديك صلاحية للوصول إلى مصفوفة ضوابط المخاطر.</v>
+        <v>عرض المزيد</v>
       </c>
       <c r="C3750" t="str">
-        <v>Jums nav atļaujas piekļūt risku kontroles matricai.</v>
+        <v>Skatīt vairāk</v>
       </c>
     </row>
     <row r="3751">
       <c r="A3751" t="str">
-        <v>No artifacts linked to evidences. Please link artifacts first.</v>
+        <v>You don't have permission to access Evidence.</v>
       </c>
       <c r="B3751" t="str">
-        <v>لا توجد قطع مرتبطة بالأدلة. يرجى ربط القطع أولاً.</v>
+        <v>ليس لديك صلاحية للوصول إلى الأدلة.</v>
       </c>
       <c r="C3751" t="str">
-        <v>Nav artefaktu, kas saistīti ar pierādījumiem. Lūdzu, vispirms saistiet artefaktus.</v>
+        <v>Jums nav atļaujas piekļūt pierādījumiem.</v>
       </c>
     </row>
     <row r="3752">
       <c r="A3752" t="str">
-        <v>No attachments uploaded</v>
+        <v>You don't have permission to access Risk Assessment.</v>
       </c>
       <c r="B3752" t="str">
-        <v>لم يتم رفع مرفقات</v>
+        <v>ليس لديك صلاحية للوصول إلى تقييم المخاطر.</v>
       </c>
       <c r="C3752" t="str">
-        <v>Nav augšupielādētu pielikumu</v>
+        <v>Jums nav atļaujas piekļūt risku novērtējumam.</v>
       </c>
     </row>
     <row r="3753">
       <c r="A3753" t="str">
-        <v>No audit logs found.</v>
+        <v>You don't have permission to access Risk Control Matrix.</v>
       </c>
       <c r="B3753" t="str">
-        <v>لم يتم العثور على سجلات تدقيق.</v>
+        <v>ليس لديك صلاحية للوصول إلى مصفوفة ضوابط المخاطر.</v>
       </c>
       <c r="C3753" t="str">
-        <v>Audita žurnāli nav atrasti.</v>
+        <v>Jums nav atļaujas piekļūt risku kontroles matricai.</v>
       </c>
     </row>
     <row r="3754">
       <c r="A3754" t="str">
-        <v>No departments match your search.</v>
+        <v>No artifacts linked to evidences. Please link artifacts first.</v>
       </c>
       <c r="B3754" t="str">
-        <v>لا توجد أقسام تطابق بحثك.</v>
+        <v>لا توجد قطع مرتبطة بالأدلة. يرجى ربط القطع أولاً.</v>
       </c>
       <c r="C3754" t="str">
-        <v>Neviena nodaļa neatbilst meklēšanai.</v>
+        <v>Nav artefaktu, kas saistīti ar pierādījumiem. Lūdzu, vispirms saistiet artefaktus.</v>
       </c>
     </row>
     <row r="3755">
       <c r="A3755" t="str">
-        <v>No eligible users found in this department</v>
+        <v>No attachments uploaded</v>
       </c>
       <c r="B3755" t="str">
-        <v>لم يتم العثور على مستخدمين مؤهلين في هذا القسم</v>
+        <v>لم يتم رفع مرفقات</v>
       </c>
       <c r="C3755" t="str">
-        <v>Šajā nodaļā nav atrasti piemēroti lietotāji</v>
+        <v>Nav augšupielādētu pielikumu</v>
       </c>
     </row>
     <row r="3756">
       <c r="A3756" t="str">
-        <v>No issues match your search.</v>
+        <v>No audit logs found.</v>
       </c>
       <c r="B3756" t="str">
-        <v>لا توجد مشكلات تطابق بحثك.</v>
+        <v>لم يتم العثور على سجلات تدقيق.</v>
       </c>
       <c r="C3756" t="str">
-        <v>Neviena problēma neatbilst meklēšanai.</v>
+        <v>Audita žurnāli nav atrasti.</v>
       </c>
     </row>
     <row r="3757">
       <c r="A3757" t="str">
-        <v>No regulations match your search.</v>
+        <v>No departments match your search.</v>
       </c>
       <c r="B3757" t="str">
-        <v>لا توجد لوائح تطابق بحثك.</v>
+        <v>لا توجد أقسام تطابق بحثك.</v>
       </c>
       <c r="C3757" t="str">
-        <v>Neviens noteikums neatbilst meklēšanai.</v>
+        <v>Neviena nodaļa neatbilst meklēšanai.</v>
       </c>
     </row>
     <row r="3758">
       <c r="A3758" t="str">
-        <v>No services match your search.</v>
+        <v>No eligible users found in this department</v>
       </c>
       <c r="B3758" t="str">
-        <v>لا توجد خدمات تطابق بحثك.</v>
+        <v>لم يتم العثور على مستخدمين مؤهلين في هذا القسم</v>
       </c>
       <c r="C3758" t="str">
-        <v>Neviens pakalpojums neatbilst meklēšanai.</v>
+        <v>Šajā nodaļā nav atrasti piemēroti lietotāji</v>
       </c>
     </row>
     <row r="3759">
       <c r="A3759" t="str">
-        <v>No stakeholders have been added yet.</v>
+        <v>No issues match your search.</v>
       </c>
       <c r="B3759" t="str">
-        <v>لم تتم إضافة أصحاب مصلحة بعد.</v>
+        <v>لا توجد مشكلات تطابق بحثك.</v>
       </c>
       <c r="C3759" t="str">
-        <v>Vēl nav pievienota neviena ieinteresētā persona.</v>
+        <v>Neviena problēma neatbilst meklēšanai.</v>
       </c>
     </row>
     <row r="3760">
       <c r="A3760" t="str">
-        <v>No stakeholders match your search.</v>
+        <v>No regulations match your search.</v>
       </c>
       <c r="B3760" t="str">
-        <v>لا يوجد أصحاب مصلحة يطابقون بحثك.</v>
+        <v>لا توجد لوائح تطابق بحثك.</v>
       </c>
       <c r="C3760" t="str">
-        <v>Neviena ieinteresētā persona neatbilst meklēšanai.</v>
+        <v>Neviens noteikums neatbilst meklēšanai.</v>
       </c>
     </row>
     <row r="3761">
       <c r="A3761" t="str">
-        <v>No Department Reviewers found in this department</v>
+        <v>No services match your search.</v>
       </c>
       <c r="B3761" t="str">
-        <v>لم يتم العثور على مراجعين في هذا القسم</v>
+        <v>لا توجد خدمات تطابق بحثك.</v>
       </c>
       <c r="C3761" t="str">
-        <v>Šajā nodaļā nav atrasti nodaļas pārskatītāji</v>
+        <v>Neviens pakalpojums neatbilst meklēšanai.</v>
       </c>
     </row>
     <row r="3762">
       <c r="A3762" t="str">
-        <v>All Assignees</v>
+        <v>No stakeholders have been added yet.</v>
       </c>
       <c r="B3762" t="str">
-        <v>جميع المكلفين</v>
+        <v>لم تتم إضافة أصحاب مصلحة بعد.</v>
       </c>
       <c r="C3762" t="str">
-        <v>Visi atbildīgie</v>
+        <v>Vēl nav pievienota neviena ieinteresētā persona.</v>
       </c>
     </row>
     <row r="3763">
       <c r="A3763" t="str">
-        <v>Imported {count} processes</v>
+        <v>No stakeholders match your search.</v>
       </c>
       <c r="B3763" t="str">
-        <v>تم استيراد {count} عملية</v>
+        <v>لا يوجد أصحاب مصلحة يطابقون بحثك.</v>
       </c>
       <c r="C3763" t="str">
-        <v>Importēti {count} procesi</v>
+        <v>Neviena ieinteresētā persona neatbilst meklēšanai.</v>
       </c>
     </row>
     <row r="3764">
       <c r="A3764" t="str">
-        <v>Successfully imported {count} issues</v>
+        <v>No Department Reviewers found in this department</v>
       </c>
       <c r="B3764" t="str">
-        <v>تم استيراد {count} مشكلة بنجاح</v>
+        <v>لم يتم العثور على مراجعين في هذا القسم</v>
       </c>
       <c r="C3764" t="str">
-        <v>Veiksmīgi importētas {count} problēmas</v>
+        <v>Šajā nodaļā nav atrasti nodaļas pārskatītāji</v>
       </c>
     </row>
     <row r="3765">
       <c r="A3765" t="str">
-        <v>Successfully imported {count} stakeholders</v>
+        <v>All Assignees</v>
       </c>
       <c r="B3765" t="str">
-        <v>تم استيراد {count} من أصحاب المصلحة بنجاح</v>
+        <v>جميع المكلفين</v>
       </c>
       <c r="C3765" t="str">
-        <v>Veiksmīgi importētas {count} ieinteresētās personas</v>
+        <v>Visi atbildīgie</v>
       </c>
     </row>
     <row r="3766">
       <c r="A3766" t="str">
-        <v>Save Issue</v>
+        <v>Imported {count} processes</v>
       </c>
       <c r="B3766" t="str">
-        <v>حفظ المشكلة</v>
+        <v>تم استيراد {count} عملية</v>
       </c>
       <c r="C3766" t="str">
-        <v>Saglabāt problēmu</v>
+        <v>Importēti {count} procesi</v>
       </c>
     </row>
     <row r="3767">
       <c r="A3767" t="str">
-        <v>Update Issue</v>
+        <v>Successfully imported {count} issues</v>
       </c>
       <c r="B3767" t="str">
-        <v>تحديث المشكلة</v>
+        <v>تم استيراد {count} مشكلة بنجاح</v>
       </c>
       <c r="C3767" t="str">
-        <v>Atjaunināt problēmu</v>
+        <v>Veiksmīgi importētas {count} problēmas</v>
       </c>
     </row>
     <row r="3768">
       <c r="A3768" t="str">
-        <v>action</v>
+        <v>Successfully imported {count} stakeholders</v>
       </c>
       <c r="B3768" t="str">
-        <v>إجراء</v>
+        <v>تم استيراد {count} من أصحاب المصلحة بنجاح</v>
       </c>
       <c r="C3768" t="str">
-        <v>darbība</v>
+        <v>Veiksmīgi importētas {count} ieinteresētās personas</v>
       </c>
     </row>
     <row r="3769">
       <c r="A3769" t="str">
-        <v>artifacts</v>
+        <v>Save Issue</v>
       </c>
       <c r="B3769" t="str">
-        <v>القطع</v>
+        <v>حفظ المشكلة</v>
       </c>
       <c r="C3769" t="str">
-        <v>artefakti</v>
+        <v>Saglabāt problēmu</v>
       </c>
     </row>
     <row r="3770">
       <c r="A3770" t="str">
-        <v>associatedVulnerabilities</v>
+        <v>Update Issue</v>
       </c>
       <c r="B3770" t="str">
-        <v>الثغرات المرتبطة</v>
+        <v>تحديث المشكلة</v>
       </c>
       <c r="C3770" t="str">
-        <v>saistītās ievainojamības</v>
+        <v>Atjaunināt problēmu</v>
       </c>
     </row>
     <row r="3771">
       <c r="A3771" t="str">
-        <v>basicRiskInformation</v>
+        <v>action</v>
       </c>
       <c r="B3771" t="str">
-        <v>معلومات المخاطر الأساسية</v>
+        <v>إجراء</v>
       </c>
       <c r="C3771" t="str">
-        <v>pamata riska informācija</v>
+        <v>darbība</v>
       </c>
     </row>
     <row r="3772">
       <c r="A3772" t="str">
-        <v>cancel</v>
+        <v>artifacts</v>
       </c>
       <c r="B3772" t="str">
-        <v>إلغاء</v>
+        <v>القطع</v>
       </c>
       <c r="C3772" t="str">
-        <v>atcelt</v>
+        <v>artefakti</v>
       </c>
     </row>
     <row r="3773">
       <c r="A3773" t="str">
-        <v>cause</v>
+        <v>associatedVulnerabilities</v>
       </c>
       <c r="B3773" t="str">
-        <v>السبب</v>
+        <v>الثغرات المرتبطة</v>
       </c>
       <c r="C3773" t="str">
-        <v>cēlonis</v>
+        <v>saistītās ievainojamības</v>
       </c>
     </row>
     <row r="3774">
       <c r="A3774" t="str">
-        <v>causeCreatedSuccessfully</v>
+        <v>basicRiskInformation</v>
       </c>
       <c r="B3774" t="str">
-        <v>تم إنشاء السبب بنجاح</v>
+        <v>معلومات المخاطر الأساسية</v>
       </c>
       <c r="C3774" t="str">
-        <v>cēlonis veiksmīgi izveidots</v>
+        <v>pamata riska informācija</v>
       </c>
     </row>
     <row r="3775">
       <c r="A3775" t="str">
-        <v>causeNameRequired</v>
+        <v>cancel</v>
       </c>
       <c r="B3775" t="str">
-        <v>اسم السبب مطلوب</v>
+        <v>إلغاء</v>
       </c>
       <c r="C3775" t="str">
-        <v>cēloņa nosaukums ir obligāts</v>
+        <v>atcelt</v>
       </c>
     </row>
     <row r="3776">
       <c r="A3776" t="str">
-        <v>clickLinkControlToAssociate</v>
+        <v>cause</v>
       </c>
       <c r="B3776" t="str">
-        <v>انقر لربط ضابط للربط</v>
+        <v>السبب</v>
       </c>
       <c r="C3776" t="str">
-        <v>noklikšķiniet saistīt kontroli</v>
+        <v>cēlonis</v>
       </c>
     </row>
     <row r="3777">
       <c r="A3777" t="str">
-        <v>code</v>
+        <v>causeCreatedSuccessfully</v>
       </c>
       <c r="B3777" t="str">
-        <v>الرمز</v>
+        <v>تم إنشاء السبب بنجاح</v>
       </c>
       <c r="C3777" t="str">
-        <v>kods</v>
+        <v>cēlonis veiksmīgi izveidots</v>
       </c>
     </row>
     <row r="3778">
       <c r="A3778" t="str">
-        <v>common.action</v>
+        <v>causeNameRequired</v>
       </c>
       <c r="B3778" t="str">
-        <v>إجراء</v>
+        <v>اسم السبب مطلوب</v>
       </c>
       <c r="C3778" t="str">
-        <v>darbība</v>
+        <v>cēloņa nosaukums ir obligāts</v>
       </c>
     </row>
     <row r="3779">
       <c r="A3779" t="str">
-        <v>common.loadMore</v>
+        <v>clickLinkControlToAssociate</v>
       </c>
       <c r="B3779" t="str">
-        <v>تحميل المزيد</v>
+        <v>انقر لربط ضابط للربط</v>
       </c>
       <c r="C3779" t="str">
-        <v>ielādēt vairāk</v>
+        <v>noklikšķiniet saistīt kontroli</v>
       </c>
     </row>
     <row r="3780">
       <c r="A3780" t="str">
-        <v>common.noItemsFound</v>
+        <v>code</v>
       </c>
       <c r="B3780" t="str">
-        <v>لم يتم العثور على عناصر</v>
+        <v>الرمز</v>
       </c>
       <c r="C3780" t="str">
-        <v>vienības nav atrastas</v>
+        <v>kods</v>
       </c>
     </row>
     <row r="3781">
       <c r="A3781" t="str">
-        <v>complianceIssues</v>
+        <v>common.action</v>
       </c>
       <c r="B3781" t="str">
-        <v>مشكلات الامتثال</v>
+        <v>إجراء</v>
       </c>
       <c r="C3781" t="str">
-        <v>atbilstības problēmas</v>
+        <v>darbība</v>
       </c>
     </row>
     <row r="3782">
       <c r="A3782" t="str">
-        <v>complianceRequirementsExceptions</v>
+        <v>common.loadMore</v>
       </c>
       <c r="B3782" t="str">
-        <v>استثناءات متطلبات الامتثال</v>
+        <v>تحميل المزيد</v>
       </c>
       <c r="C3782" t="str">
-        <v>atbilstības prasību izņēmumi</v>
+        <v>ielādēt vairāk</v>
       </c>
     </row>
     <row r="3783">
       <c r="A3783" t="str">
-        <v>controlCode</v>
+        <v>common.noItemsFound</v>
       </c>
       <c r="B3783" t="str">
-        <v>رمز الضابط</v>
+        <v>لم يتم العثور على عناصر</v>
       </c>
       <c r="C3783" t="str">
-        <v>kontroles kods</v>
+        <v>vienības nav atrastas</v>
       </c>
     </row>
     <row r="3784">
       <c r="A3784" t="str">
-        <v>controlExceptions</v>
+        <v>complianceIssues</v>
       </c>
       <c r="B3784" t="str">
-        <v>استثناءات الضوابط</v>
+        <v>مشكلات الامتثال</v>
       </c>
       <c r="C3784" t="str">
-        <v>kontroles izņēmumi</v>
+        <v>atbilstības problēmas</v>
       </c>
     </row>
     <row r="3785">
       <c r="A3785" t="str">
-        <v>controlImplementationsByFramework</v>
+        <v>complianceRequirementsExceptions</v>
       </c>
       <c r="B3785" t="str">
-        <v>تطبيقات الضوابط حسب الإطار</v>
+        <v>استثناءات متطلبات الامتثال</v>
       </c>
       <c r="C3785" t="str">
-        <v>kontroles ieviešanas pēc ietvara</v>
+        <v>atbilstības prasību izņēmumi</v>
       </c>
     </row>
     <row r="3786">
       <c r="A3786" t="str">
-        <v>controlRequirementsByFramework</v>
+        <v>controlCode</v>
       </c>
       <c r="B3786" t="str">
-        <v>متطلبات الضوابط حسب الإطار</v>
+        <v>رمز الضابط</v>
       </c>
       <c r="C3786" t="str">
-        <v>kontroles prasības pēc ietvara</v>
+        <v>kontroles kods</v>
       </c>
     </row>
     <row r="3787">
       <c r="A3787" t="str">
-        <v>controlsSelected</v>
+        <v>controlExceptions</v>
       </c>
       <c r="B3787" t="str">
-        <v>الضوابط المختارة</v>
+        <v>استثناءات الضوابط</v>
       </c>
       <c r="C3787" t="str">
-        <v>atlasītās kontroles</v>
+        <v>kontroles izņēmumi</v>
       </c>
     </row>
     <row r="3788">
       <c r="A3788" t="str">
-        <v>create</v>
+        <v>controlImplementationsByFramework</v>
       </c>
       <c r="B3788" t="str">
-        <v>إنشاء</v>
+        <v>تطبيقات الضوابط حسب الإطار</v>
       </c>
       <c r="C3788" t="str">
-        <v>izveidot</v>
+        <v>kontroles ieviešanas pēc ietvara</v>
       </c>
     </row>
     <row r="3789">
       <c r="A3789" t="str">
-        <v>createNewCause</v>
+        <v>controlRequirementsByFramework</v>
       </c>
       <c r="B3789" t="str">
-        <v>إنشاء سبب جديد</v>
+        <v>متطلبات الضوابط حسب الإطار</v>
       </c>
       <c r="C3789" t="str">
-        <v>izveidot jaunu cēloni</v>
+        <v>kontroles prasības pēc ietvara</v>
       </c>
     </row>
     <row r="3790">
       <c r="A3790" t="str">
-        <v>creating</v>
+        <v>controlsSelected</v>
       </c>
       <c r="B3790" t="str">
-        <v>جاري الإنشاء</v>
+        <v>الضوابط المختارة</v>
       </c>
       <c r="C3790" t="str">
-        <v>izveido</v>
+        <v>atlasītās kontroles</v>
       </c>
     </row>
     <row r="3791">
       <c r="A3791" t="str">
-        <v>day</v>
+        <v>create</v>
       </c>
       <c r="B3791" t="str">
-        <v>يوم</v>
+        <v>إنشاء</v>
       </c>
       <c r="C3791" t="str">
-        <v>diena</v>
+        <v>izveidot</v>
       </c>
     </row>
     <row r="3792">
       <c r="A3792" t="str">
-        <v>department</v>
+        <v>createNewCause</v>
       </c>
       <c r="B3792" t="str">
-        <v>القسم</v>
+        <v>إنشاء سبب جديد</v>
       </c>
       <c r="C3792" t="str">
-        <v>nodaļa</v>
+        <v>izveidot jaunu cēloni</v>
       </c>
     </row>
     <row r="3793">
       <c r="A3793" t="str">
-        <v>description</v>
+        <v>creating</v>
       </c>
       <c r="B3793" t="str">
-        <v>الوصف</v>
+        <v>جاري الإنشاء</v>
       </c>
       <c r="C3793" t="str">
-        <v>apraksts</v>
+        <v>izveido</v>
       </c>
     </row>
     <row r="3794">
       <c r="A3794" t="str">
-        <v>document(s) selected</v>
+        <v>day</v>
       </c>
       <c r="B3794" t="str">
-        <v>مستند(ات) مختارة</v>
+        <v>يوم</v>
       </c>
       <c r="C3794" t="str">
-        <v>dokuments(-i) atlasīts(-i)</v>
+        <v>diena</v>
       </c>
     </row>
     <row r="3795">
       <c r="A3795" t="str">
-        <v>domain</v>
+        <v>department</v>
       </c>
       <c r="B3795" t="str">
-        <v>المجال</v>
+        <v>القسم</v>
       </c>
       <c r="C3795" t="str">
-        <v>domēns</v>
+        <v>nodaļa</v>
       </c>
     </row>
     <row r="3796">
       <c r="A3796" t="str">
-        <v>domainBasedProgressCompliance</v>
+        <v>description</v>
       </c>
       <c r="B3796" t="str">
-        <v>تقدم الامتثال حسب المجال</v>
+        <v>الوصف</v>
       </c>
       <c r="C3796" t="str">
-        <v>uz domēnu balstīta atbilstības progresa</v>
+        <v>apraksts</v>
       </c>
     </row>
     <row r="3797">
       <c r="A3797" t="str">
-        <v>done</v>
+        <v>document(s) selected</v>
       </c>
       <c r="B3797" t="str">
-        <v>تم</v>
+        <v>مستند(ات) مختارة</v>
       </c>
       <c r="C3797" t="str">
-        <v>pabeigts</v>
+        <v>dokuments(-i) atlasīts(-i)</v>
       </c>
     </row>
     <row r="3798">
       <c r="A3798" t="str">
-        <v>e.g., 1.0</v>
+        <v>domain</v>
       </c>
       <c r="B3798" t="str">
-        <v>مثال: 1.0</v>
+        <v>المجال</v>
       </c>
       <c r="C3798" t="str">
-        <v>piem., 1.0</v>
+        <v>domēns</v>
       </c>
     </row>
     <row r="3799">
       <c r="A3799" t="str">
-        <v>e.g., Financial, Reputational</v>
+        <v>domainBasedProgressCompliance</v>
       </c>
       <c r="B3799" t="str">
-        <v>مثال: مالي، سمعة</v>
+        <v>تقدم الامتثال حسب المجال</v>
       </c>
       <c r="C3799" t="str">
-        <v>piem., Finansiāla, Reputācija</v>
+        <v>uz domēnu balstīta atbilstības progresa</v>
       </c>
     </row>
     <row r="3800">
       <c r="A3800" t="str">
-        <v>e.g., Immediate, 4 Hours, 24 Hours</v>
+        <v>done</v>
       </c>
       <c r="B3800" t="str">
-        <v>مثال: فوري، 4 ساعات، 24 ساعة</v>
+        <v>تم</v>
       </c>
       <c r="C3800" t="str">
-        <v>piem., Nekavējoties, 4 stundas, 24 stundas</v>
+        <v>pabeigts</v>
       </c>
     </row>
     <row r="3801">
       <c r="A3801" t="str">
-        <v>edit</v>
+        <v>e.g., 1.0</v>
       </c>
       <c r="B3801" t="str">
-        <v>تعديل</v>
+        <v>مثال: 1.0</v>
       </c>
       <c r="C3801" t="str">
-        <v>rediģēt</v>
+        <v>piem., 1.0</v>
       </c>
     </row>
     <row r="3802">
       <c r="A3802" t="str">
-        <v>editRisk</v>
+        <v>e.g., Financial, Reputational</v>
       </c>
       <c r="B3802" t="str">
-        <v>تعديل المخاطرة</v>
+        <v>مثال: مالي، سمعة</v>
       </c>
       <c r="C3802" t="str">
-        <v>rediģēt risku</v>
+        <v>piem., Finansiāla, Reputācija</v>
       </c>
     </row>
     <row r="3803">
       <c r="A3803" t="str">
-        <v>endDate</v>
+        <v>e.g., Immediate, 4 Hours, 24 Hours</v>
       </c>
       <c r="B3803" t="str">
-        <v>تاريخ الانتهاء</v>
+        <v>مثال: فوري، 4 ساعات، 24 ساعة</v>
       </c>
       <c r="C3803" t="str">
-        <v>beigu datums</v>
+        <v>piem., Nekavējoties, 4 stundas, 24 stundas</v>
       </c>
     </row>
     <row r="3804">
       <c r="A3804" t="str">
-        <v>enterCauseDescription</v>
+        <v>edit</v>
       </c>
       <c r="B3804" t="str">
-        <v>أدخل وصف السبب</v>
+        <v>تعديل</v>
       </c>
       <c r="C3804" t="str">
-        <v>ievadiet cēloņa aprakstu</v>
+        <v>rediģēt</v>
       </c>
     </row>
     <row r="3805">
       <c r="A3805" t="str">
-        <v>enterCauseName</v>
+        <v>editRisk</v>
       </c>
       <c r="B3805" t="str">
-        <v>أدخل اسم السبب</v>
+        <v>تعديل المخاطرة</v>
       </c>
       <c r="C3805" t="str">
-        <v>ievadiet cēloņa nosaukumu</v>
+        <v>rediģēt risku</v>
       </c>
     </row>
     <row r="3806">
       <c r="A3806" t="str">
-        <v>enterDescription</v>
+        <v>endDate</v>
       </c>
       <c r="B3806" t="str">
-        <v>أدخل الوصف</v>
+        <v>تاريخ الانتهاء</v>
       </c>
       <c r="C3806" t="str">
-        <v>ievadiet aprakstu</v>
+        <v>beigu datums</v>
       </c>
     </row>
     <row r="3807">
       <c r="A3807" t="str">
-        <v>enterRiskName</v>
+        <v>enterCauseDescription</v>
       </c>
       <c r="B3807" t="str">
-        <v>أدخل اسم المخاطرة</v>
+        <v>أدخل وصف السبب</v>
       </c>
       <c r="C3807" t="str">
-        <v>ievadiet riska nosaukumu</v>
+        <v>ievadiet cēloņa aprakstu</v>
       </c>
     </row>
     <row r="3808">
       <c r="A3808" t="str">
-        <v>enterRiskSources</v>
+        <v>enterCauseName</v>
       </c>
       <c r="B3808" t="str">
-        <v>أدخل مصادر المخاطر</v>
+        <v>أدخل اسم السبب</v>
       </c>
       <c r="C3808" t="str">
-        <v>ievadiet risku avotus</v>
+        <v>ievadiet cēloņa nosaukumu</v>
       </c>
     </row>
     <row r="3809">
       <c r="A3809" t="str">
-        <v>evidences?</v>
+        <v>enterDescription</v>
       </c>
       <c r="B3809" t="str">
-        <v>أدلة؟</v>
+        <v>أدخل الوصف</v>
       </c>
       <c r="C3809" t="str">
-        <v>pierādījumi?</v>
+        <v>ievadiet aprakstu</v>
       </c>
     </row>
     <row r="3810">
       <c r="A3810" t="str">
-        <v>failedToLoadRisk</v>
+        <v>enterRiskName</v>
       </c>
       <c r="B3810" t="str">
-        <v>فشل في تحميل المخاطرة</v>
+        <v>أدخل اسم المخاطرة</v>
       </c>
       <c r="C3810" t="str">
-        <v>neizdevās ielādēt risku</v>
+        <v>ievadiet riska nosaukumu</v>
       </c>
     </row>
     <row r="3811">
       <c r="A3811" t="str">
-        <v>failedToUpdateRisk</v>
+        <v>enterRiskSources</v>
       </c>
       <c r="B3811" t="str">
-        <v>فشل في تحديث المخاطرة</v>
+        <v>أدخل مصادر المخاطر</v>
       </c>
       <c r="C3811" t="str">
-        <v>neizdevās atjaunināt risku</v>
+        <v>ievadiet risku avotus</v>
       </c>
     </row>
     <row r="3812">
       <c r="A3812" t="str">
-        <v>filterType</v>
+        <v>evidences?</v>
       </c>
       <c r="B3812" t="str">
-        <v>نوع التصفية</v>
+        <v>أدلة؟</v>
       </c>
       <c r="C3812" t="str">
-        <v>filtra tips</v>
+        <v>pierādījumi?</v>
       </c>
     </row>
     <row r="3813">
       <c r="A3813" t="str">
-        <v>frameworkCompliance</v>
+        <v>failedToLoadRisk</v>
       </c>
       <c r="B3813" t="str">
-        <v>امتثال الإطار</v>
+        <v>فشل في تحميل المخاطرة</v>
       </c>
       <c r="C3813" t="str">
-        <v>ietvara atbilstība</v>
+        <v>neizdevās ielādēt risku</v>
       </c>
     </row>
     <row r="3814">
       <c r="A3814" t="str">
-        <v>frameworkId</v>
+        <v>failedToUpdateRisk</v>
       </c>
       <c r="B3814" t="str">
-        <v>معرف الإطار</v>
+        <v>فشل في تحديث المخاطرة</v>
       </c>
       <c r="C3814" t="str">
-        <v>ietvara ID</v>
+        <v>neizdevās atjaunināt risku</v>
       </c>
     </row>
     <row r="3815">
       <c r="A3815" t="str">
-        <v>frameworkName</v>
+        <v>filterType</v>
       </c>
       <c r="B3815" t="str">
-        <v>اسم الإطار</v>
+        <v>نوع التصفية</v>
       </c>
       <c r="C3815" t="str">
-        <v>ietvara nosaukums</v>
+        <v>filtra tips</v>
       </c>
     </row>
     <row r="3816">
       <c r="A3816" t="str">
-        <v>frameworkWithGovernanceData</v>
+        <v>frameworkCompliance</v>
       </c>
       <c r="B3816" t="str">
-        <v>الإطار مع بيانات الحوكمة</v>
+        <v>امتثال الإطار</v>
       </c>
       <c r="C3816" t="str">
-        <v>ietvars ar pārvaldības datiem</v>
+        <v>ietvara atbilstība</v>
       </c>
     </row>
     <row r="3817">
       <c r="A3817" t="str">
-        <v>from</v>
+        <v>frameworkId</v>
       </c>
       <c r="B3817" t="str">
-        <v>من</v>
+        <v>معرف الإطار</v>
       </c>
       <c r="C3817" t="str">
-        <v>no</v>
+        <v>ietvara ID</v>
       </c>
     </row>
     <row r="3818">
       <c r="A3818" t="str">
-        <v>functionalGrouping</v>
+        <v>frameworkName</v>
       </c>
       <c r="B3818" t="str">
-        <v>التجميع الوظيفي</v>
+        <v>اسم الإطار</v>
       </c>
       <c r="C3818" t="str">
-        <v>funkcionālā grupēšana</v>
+        <v>ietvara nosaukums</v>
       </c>
     </row>
     <row r="3819">
       <c r="A3819" t="str">
-        <v>hour</v>
+        <v>frameworkWithGovernanceData</v>
       </c>
       <c r="B3819" t="str">
-        <v>ساعة</v>
+        <v>الإطار مع بيانات الحوكمة</v>
       </c>
       <c r="C3819" t="str">
-        <v>stunda</v>
+        <v>ietvars ar pārvaldības datiem</v>
       </c>
     </row>
     <row r="3820">
       <c r="A3820" t="str">
-        <v>hours</v>
+        <v>from</v>
       </c>
       <c r="B3820" t="str">
-        <v>ساعات</v>
+        <v>من</v>
       </c>
       <c r="C3820" t="str">
-        <v>stundas</v>
+        <v>no</v>
       </c>
     </row>
     <row r="3821">
       <c r="A3821" t="str">
-        <v>impactedAsset</v>
+        <v>functionalGrouping</v>
       </c>
       <c r="B3821" t="str">
-        <v>الأصل المتأثر</v>
+        <v>التجميع الوظيفي</v>
       </c>
       <c r="C3821" t="str">
-        <v>ietekmētais aktīvs</v>
+        <v>funkcionālā grupēšana</v>
       </c>
     </row>
     <row r="3822">
       <c r="A3822" t="str">
-        <v>impactedAssetProcess</v>
+        <v>hour</v>
       </c>
       <c r="B3822" t="str">
-        <v>الأصل/العملية المتأثرة</v>
+        <v>ساعة</v>
       </c>
       <c r="C3822" t="str">
-        <v>ietekmētais aktīvs/process</v>
+        <v>stunda</v>
       </c>
     </row>
     <row r="3823">
       <c r="A3823" t="str">
-        <v>impactedProcess</v>
+        <v>hours</v>
       </c>
       <c r="B3823" t="str">
-        <v>العملية المتأثرة</v>
+        <v>ساعات</v>
       </c>
       <c r="C3823" t="str">
-        <v>ietekmētais process</v>
+        <v>stundas</v>
       </c>
     </row>
     <row r="3824">
       <c r="A3824" t="str">
-        <v>input</v>
+        <v>impactedAsset</v>
       </c>
       <c r="B3824" t="str">
-        <v>إدخال</v>
+        <v>الأصل المتأثر</v>
       </c>
       <c r="C3824" t="str">
-        <v>ievade</v>
+        <v>ietekmētais aktīvs</v>
       </c>
     </row>
     <row r="3825">
       <c r="A3825" t="str">
-        <v>linkControl</v>
+        <v>impactedAssetProcess</v>
       </c>
       <c r="B3825" t="str">
-        <v>ربط ضابط</v>
+        <v>الأصل/العملية المتأثرة</v>
       </c>
       <c r="C3825" t="str">
-        <v>saistīt kontroli</v>
+        <v>ietekmētais aktīvs/process</v>
       </c>
     </row>
     <row r="3826">
       <c r="A3826" t="str">
-        <v>linkControls</v>
+        <v>impactedProcess</v>
       </c>
       <c r="B3826" t="str">
-        <v>ربط الضوابط</v>
+        <v>العملية المتأثرة</v>
       </c>
       <c r="C3826" t="str">
-        <v>saistīt kontroles</v>
+        <v>ietekmētais process</v>
       </c>
     </row>
     <row r="3827">
       <c r="A3827" t="str">
-        <v>linkControlsToRisk</v>
+        <v>input</v>
       </c>
       <c r="B3827" t="str">
-        <v>ربط الضوابط بالمخاطرة</v>
+        <v>إدخال</v>
       </c>
       <c r="C3827" t="str">
-        <v>saistīt kontroles ar risku</v>
+        <v>ievade</v>
       </c>
     </row>
     <row r="3828">
       <c r="A3828" t="str">
-        <v>minutes</v>
+        <v>linkControl</v>
       </c>
       <c r="B3828" t="str">
-        <v>دقائق</v>
+        <v>ربط ضابط</v>
       </c>
       <c r="C3828" t="str">
-        <v>minūtes</v>
+        <v>saistīt kontroli</v>
       </c>
     </row>
     <row r="3829">
       <c r="A3829" t="str">
-        <v>mode</v>
+        <v>linkControls</v>
       </c>
       <c r="B3829" t="str">
-        <v>الوضع</v>
+        <v>ربط الضوابط</v>
       </c>
       <c r="C3829" t="str">
-        <v>režīms</v>
+        <v>saistīt kontroles</v>
       </c>
     </row>
     <row r="3830">
       <c r="A3830" t="str">
-        <v>name</v>
+        <v>linkControlsToRisk</v>
       </c>
       <c r="B3830" t="str">
-        <v>الاسم</v>
+        <v>ربط الضوابط بالمخاطرة</v>
       </c>
       <c r="C3830" t="str">
-        <v>nosaukums</v>
+        <v>saistīt kontroles ar risku</v>
       </c>
     </row>
     <row r="3831">
       <c r="A3831" t="str">
-        <v>next</v>
+        <v>minutes</v>
       </c>
       <c r="B3831" t="str">
-        <v>التالي</v>
+        <v>دقائق</v>
       </c>
       <c r="C3831" t="str">
-        <v>nākamais</v>
+        <v>minūtes</v>
       </c>
     </row>
     <row r="3832">
       <c r="A3832" t="str">
-        <v>noControlsLinkedYet</v>
+        <v>mode</v>
       </c>
       <c r="B3832" t="str">
-        <v>لا توجد ضوابط مرتبطة بعد</v>
+        <v>الوضع</v>
       </c>
       <c r="C3832" t="str">
-        <v>vēl nav saistītu kontroles</v>
+        <v>režīms</v>
       </c>
     </row>
     <row r="3833">
       <c r="A3833" t="str">
-        <v>noDepartmentReviewersFound</v>
+        <v>name</v>
       </c>
       <c r="B3833" t="str">
-        <v>لم يتم العثور على مراجعي القسم</v>
+        <v>الاسم</v>
       </c>
       <c r="C3833" t="str">
-        <v>nodaļas pārskatītāji nav atrasti</v>
+        <v>nosaukums</v>
       </c>
     </row>
     <row r="3834">
       <c r="A3834" t="str">
-        <v>noPermissionToEditRisks</v>
+        <v>next</v>
       </c>
       <c r="B3834" t="str">
-        <v>ليس لديك صلاحية لتعديل المخاطر</v>
+        <v>التالي</v>
       </c>
       <c r="C3834" t="str">
-        <v>nav atļaujas rediģēt riskus</v>
+        <v>nākamais</v>
       </c>
     </row>
     <row r="3835">
       <c r="A3835" t="str">
-        <v>options</v>
+        <v>noControlsLinkedYet</v>
       </c>
       <c r="B3835" t="str">
-        <v>الخيارات</v>
+        <v>لا توجد ضوابط مرتبطة بعد</v>
       </c>
       <c r="C3835" t="str">
-        <v>opcijas</v>
+        <v>vēl nav saistītu kontroles</v>
       </c>
     </row>
     <row r="3836">
       <c r="A3836" t="str">
-        <v>overallCompliance</v>
+        <v>noDepartmentReviewersFound</v>
       </c>
       <c r="B3836" t="str">
-        <v>الامتثال العام</v>
+        <v>لم يتم العثور على مراجعي القسم</v>
       </c>
       <c r="C3836" t="str">
-        <v>kopējā atbilstība</v>
+        <v>nodaļas pārskatītāji nav atrasti</v>
       </c>
     </row>
     <row r="3837">
       <c r="A3837" t="str">
-        <v>overlaps with</v>
+        <v>noPermissionToEditRisks</v>
       </c>
       <c r="B3837" t="str">
-        <v>يتداخل مع</v>
+        <v>ليس لديك صلاحية لتعديل المخاطر</v>
       </c>
       <c r="C3837" t="str">
-        <v>pārklājas ar</v>
+        <v>nav atļaujas rediģēt riskus</v>
       </c>
     </row>
     <row r="3838">
       <c r="A3838" t="str">
-        <v>partially effective</v>
+        <v>options</v>
       </c>
       <c r="B3838" t="str">
-        <v>فعال جزئياً</v>
+        <v>الخيارات</v>
       </c>
       <c r="C3838" t="str">
-        <v>daļēji efektīvs</v>
+        <v>opcijas</v>
       </c>
     </row>
     <row r="3839">
       <c r="A3839" t="str">
-        <v>pending</v>
+        <v>overallCompliance</v>
       </c>
       <c r="B3839" t="str">
-        <v>معلق</v>
+        <v>الامتثال العام</v>
       </c>
       <c r="C3839" t="str">
-        <v>gaidošs</v>
+        <v>kopējā atbilstība</v>
       </c>
     </row>
     <row r="3840">
       <c r="A3840" t="str">
-        <v>potentialThreats</v>
+        <v>overlaps with</v>
       </c>
       <c r="B3840" t="str">
-        <v>التهديدات المحتملة</v>
+        <v>يتداخل مع</v>
       </c>
       <c r="C3840" t="str">
-        <v>potenciālie draudi</v>
+        <v>pārklājas ar</v>
       </c>
     </row>
     <row r="3841">
       <c r="A3841" t="str">
-        <v>previous</v>
+        <v>partially effective</v>
       </c>
       <c r="B3841" t="str">
-        <v>السابق</v>
+        <v>فعال جزئياً</v>
       </c>
       <c r="C3841" t="str">
-        <v>iepriekšējais</v>
+        <v>daļēji efektīvs</v>
       </c>
     </row>
     <row r="3842">
       <c r="A3842" t="str">
-        <v>riskCategory</v>
+        <v>pending</v>
       </c>
       <c r="B3842" t="str">
-        <v>فئة المخاطر</v>
+        <v>معلق</v>
       </c>
       <c r="C3842" t="str">
-        <v>riska kategorija</v>
+        <v>gaidošs</v>
       </c>
     </row>
     <row r="3843">
       <c r="A3843" t="str">
-        <v>riskComplianceMatrix.controlCode</v>
+        <v>potentialThreats</v>
       </c>
       <c r="B3843" t="str">
-        <v>رمز الضابط</v>
+        <v>التهديدات المحتملة</v>
       </c>
       <c r="C3843" t="str">
-        <v>kontroles kods</v>
+        <v>potenciālie draudi</v>
       </c>
     </row>
     <row r="3844">
       <c r="A3844" t="str">
-        <v>riskComplianceMatrix.controlName</v>
+        <v>previous</v>
       </c>
       <c r="B3844" t="str">
-        <v>اسم الضابط</v>
+        <v>السابق</v>
       </c>
       <c r="C3844" t="str">
-        <v>kontroles nosaukums</v>
+        <v>iepriekšējais</v>
       </c>
     </row>
     <row r="3845">
       <c r="A3845" t="str">
-        <v>riskComplianceMatrix.description</v>
+        <v>riskCategory</v>
       </c>
       <c r="B3845" t="str">
-        <v>الوصف</v>
+        <v>فئة المخاطر</v>
       </c>
       <c r="C3845" t="str">
-        <v>apraksts</v>
+        <v>riska kategorija</v>
       </c>
     </row>
     <row r="3846">
       <c r="A3846" t="str">
-        <v>riskComplianceMatrix.inherentRiskRating</v>
+        <v>riskComplianceMatrix.controlCode</v>
       </c>
       <c r="B3846" t="str">
-        <v>تقييم المخاطر الأصلية</v>
+        <v>رمز الضابط</v>
       </c>
       <c r="C3846" t="str">
-        <v>piemītošā riska vērtējums</v>
+        <v>kontroles kods</v>
       </c>
     </row>
     <row r="3847">
       <c r="A3847" t="str">
-        <v>riskComplianceMatrix.linkedControls</v>
+        <v>riskComplianceMatrix.controlName</v>
       </c>
       <c r="B3847" t="str">
-        <v>الضوابط المرتبطة</v>
+        <v>اسم الضابط</v>
       </c>
       <c r="C3847" t="str">
-        <v>saistītās kontroles</v>
+        <v>kontroles nosaukums</v>
       </c>
     </row>
     <row r="3848">
       <c r="A3848" t="str">
-        <v>riskComplianceMatrix.noLinkedControls</v>
+        <v>riskComplianceMatrix.description</v>
       </c>
       <c r="B3848" t="str">
-        <v>لا توجد ضوابط مرتبطة</v>
+        <v>الوصف</v>
       </c>
       <c r="C3848" t="str">
-        <v>nav saistītu kontroles</v>
+        <v>apraksts</v>
       </c>
     </row>
     <row r="3849">
       <c r="A3849" t="str">
-        <v>riskComplianceMatrix.noRisksFound</v>
+        <v>riskComplianceMatrix.inherentRiskRating</v>
       </c>
       <c r="B3849" t="str">
-        <v>لم يتم العثور على مخاطر</v>
+        <v>تقييم المخاطر الأصلية</v>
       </c>
       <c r="C3849" t="str">
-        <v>riski nav atrasti</v>
+        <v>piemītošā riska vērtējums</v>
       </c>
     </row>
     <row r="3850">
       <c r="A3850" t="str">
-        <v>riskComplianceMatrix.residualRiskRating</v>
+        <v>riskComplianceMatrix.linkedControls</v>
       </c>
       <c r="B3850" t="str">
-        <v>تقييم المخاطر المتبقية</v>
+        <v>الضوابط المرتبطة</v>
       </c>
       <c r="C3850" t="str">
-        <v>atlikušā riska vērtējums</v>
+        <v>saistītās kontroles</v>
       </c>
     </row>
     <row r="3851">
       <c r="A3851" t="str">
-        <v>riskComplianceMatrix.riskOwner</v>
+        <v>riskComplianceMatrix.noLinkedControls</v>
       </c>
       <c r="B3851" t="str">
-        <v>مالك المخاطرة</v>
+        <v>لا توجد ضوابط مرتبطة</v>
       </c>
       <c r="C3851" t="str">
-        <v>riska īpašnieks</v>
+        <v>nav saistītu kontroles</v>
       </c>
     </row>
     <row r="3852">
       <c r="A3852" t="str">
-        <v>riskComplianceMatrix.status</v>
+        <v>riskComplianceMatrix.noRisksFound</v>
       </c>
       <c r="B3852" t="str">
-        <v>الحالة</v>
+        <v>لم يتم العثور على مخاطر</v>
       </c>
       <c r="C3852" t="str">
-        <v>statuss</v>
+        <v>riski nav atrasti</v>
       </c>
     </row>
     <row r="3853">
       <c r="A3853" t="str">
-        <v>riskComplianceMatrix.subtitle</v>
+        <v>riskComplianceMatrix.residualRiskRating</v>
       </c>
       <c r="B3853" t="str">
-        <v>العنوان الفرعي</v>
+        <v>تقييم المخاطر المتبقية</v>
       </c>
       <c r="C3853" t="str">
-        <v>apakšvirsraksts</v>
+        <v>atlikušā riska vērtējums</v>
       </c>
     </row>
     <row r="3854">
       <c r="A3854" t="str">
-        <v>riskComplianceMatrix.title</v>
+        <v>riskComplianceMatrix.riskOwner</v>
       </c>
       <c r="B3854" t="str">
-        <v>مصفوفة ضوابط المخاطر</v>
+        <v>مالك المخاطرة</v>
       </c>
       <c r="C3854" t="str">
-        <v>risku kontroles matrica</v>
+        <v>riska īpašnieks</v>
       </c>
     </row>
     <row r="3855">
       <c r="A3855" t="str">
-        <v>riskDescription</v>
+        <v>riskComplianceMatrix.status</v>
       </c>
       <c r="B3855" t="str">
-        <v>وصف المخاطرة</v>
+        <v>الحالة</v>
       </c>
       <c r="C3855" t="str">
-        <v>riska apraksts</v>
+        <v>statuss</v>
       </c>
     </row>
     <row r="3856">
       <c r="A3856" t="str">
-        <v>riskDetails</v>
+        <v>riskComplianceMatrix.subtitle</v>
       </c>
       <c r="B3856" t="str">
-        <v>تفاصيل المخاطرة</v>
+        <v>العنوان الفرعي</v>
       </c>
       <c r="C3856" t="str">
-        <v>riska detaļas</v>
+        <v>apakšvirsraksts</v>
       </c>
     </row>
     <row r="3857">
       <c r="A3857" t="str">
-        <v>riskId</v>
+        <v>riskComplianceMatrix.title</v>
       </c>
       <c r="B3857" t="str">
-        <v>معرف المخاطرة</v>
+        <v>مصفوفة ضوابط المخاطر</v>
       </c>
       <c r="C3857" t="str">
-        <v>riska ID</v>
+        <v>risku kontroles matrica</v>
       </c>
     </row>
     <row r="3858">
       <c r="A3858" t="str">
-        <v>riskMapping</v>
+        <v>riskDescription</v>
       </c>
       <c r="B3858" t="str">
-        <v>خريطة المخاطر</v>
+        <v>وصف المخاطرة</v>
       </c>
       <c r="C3858" t="str">
-        <v>risku kartēšana</v>
+        <v>riska apraksts</v>
       </c>
     </row>
     <row r="3859">
       <c r="A3859" t="str">
-        <v>riskName</v>
+        <v>riskDetails</v>
       </c>
       <c r="B3859" t="str">
-        <v>اسم المخاطرة</v>
+        <v>تفاصيل المخاطرة</v>
       </c>
       <c r="C3859" t="str">
-        <v>riska nosaukums</v>
+        <v>riska detaļas</v>
       </c>
     </row>
     <row r="3860">
       <c r="A3860" t="str">
-        <v>riskNotFound</v>
+        <v>riskId</v>
       </c>
       <c r="B3860" t="str">
-        <v>المخاطرة غير موجودة</v>
+        <v>معرف المخاطرة</v>
       </c>
       <c r="C3860" t="str">
-        <v>risks nav atrasts</v>
+        <v>riska ID</v>
       </c>
     </row>
     <row r="3861">
       <c r="A3861" t="str">
-        <v>riskOwner</v>
+        <v>riskMapping</v>
       </c>
       <c r="B3861" t="str">
-        <v>مالك المخاطرة</v>
+        <v>خريطة المخاطر</v>
       </c>
       <c r="C3861" t="str">
-        <v>riska īpašnieks</v>
+        <v>risku kartēšana</v>
       </c>
     </row>
     <row r="3862">
       <c r="A3862" t="str">
-        <v>riskRating</v>
+        <v>riskName</v>
       </c>
       <c r="B3862" t="str">
-        <v>تقييم المخاطرة</v>
+        <v>اسم المخاطرة</v>
       </c>
       <c r="C3862" t="str">
-        <v>riska vērtējums</v>
+        <v>riska nosaukums</v>
       </c>
     </row>
     <row r="3863">
       <c r="A3863" t="str">
-        <v>riskSources</v>
+        <v>riskNotFound</v>
       </c>
       <c r="B3863" t="str">
-        <v>مصادر المخاطر</v>
+        <v>المخاطرة غير موجودة</v>
       </c>
       <c r="C3863" t="str">
-        <v>risku avoti</v>
+        <v>risks nav atrasts</v>
       </c>
     </row>
     <row r="3864">
       <c r="A3864" t="str">
-        <v>riskType</v>
+        <v>riskOwner</v>
       </c>
       <c r="B3864" t="str">
-        <v>نوع المخاطرة</v>
+        <v>مالك المخاطرة</v>
       </c>
       <c r="C3864" t="str">
-        <v>riska tips</v>
+        <v>riska īpašnieks</v>
       </c>
     </row>
     <row r="3865">
       <c r="A3865" t="str">
-        <v>riskUpdatedSuccessfully</v>
+        <v>riskRating</v>
       </c>
       <c r="B3865" t="str">
-        <v>تم تحديث المخاطرة بنجاح</v>
+        <v>تقييم المخاطرة</v>
       </c>
       <c r="C3865" t="str">
-        <v>risks veiksmīgi atjaunināts</v>
+        <v>riska vērtējums</v>
       </c>
     </row>
     <row r="3866">
       <c r="A3866" t="str">
-        <v>saving</v>
+        <v>riskSources</v>
       </c>
       <c r="B3866" t="str">
-        <v>جاري الحفظ</v>
+        <v>مصادر المخاطر</v>
       </c>
       <c r="C3866" t="str">
-        <v>saglabā</v>
+        <v>risku avoti</v>
       </c>
     </row>
     <row r="3867">
       <c r="A3867" t="str">
-        <v>searchControls</v>
+        <v>riskType</v>
       </c>
       <c r="B3867" t="str">
-        <v>بحث في الضوابط</v>
+        <v>نوع المخاطرة</v>
       </c>
       <c r="C3867" t="str">
-        <v>meklēt kontroles</v>
+        <v>riska tips</v>
       </c>
     </row>
     <row r="3868">
       <c r="A3868" t="str">
-        <v>selectCategory</v>
+        <v>riskUpdatedSuccessfully</v>
       </c>
       <c r="B3868" t="str">
-        <v>اختر الفئة</v>
+        <v>تم تحديث المخاطرة بنجاح</v>
       </c>
       <c r="C3868" t="str">
-        <v>atlasīt kategoriju</v>
+        <v>risks veiksmīgi atjaunināts</v>
       </c>
     </row>
     <row r="3869">
       <c r="A3869" t="str">
-        <v>selectCause</v>
+        <v>saving</v>
       </c>
       <c r="B3869" t="str">
-        <v>اختر السبب</v>
+        <v>جاري الحفظ</v>
       </c>
       <c r="C3869" t="str">
-        <v>atlasīt cēloni</v>
+        <v>saglabā</v>
       </c>
     </row>
     <row r="3870">
       <c r="A3870" t="str">
-        <v>selectDepartment</v>
+        <v>searchControls</v>
       </c>
       <c r="B3870" t="str">
-        <v>اختر القسم</v>
+        <v>بحث في الضوابط</v>
       </c>
       <c r="C3870" t="str">
-        <v>atlasīt nodaļu</v>
+        <v>meklēt kontroles</v>
       </c>
     </row>
     <row r="3871">
       <c r="A3871" t="str">
-        <v>selectDepartmentFirst</v>
+        <v>selectCategory</v>
       </c>
       <c r="B3871" t="str">
-        <v>اختر القسم أولاً</v>
+        <v>اختر الفئة</v>
       </c>
       <c r="C3871" t="str">
-        <v>vispirms atlasiet nodaļu</v>
+        <v>atlasīt kategoriju</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" t="str">
-        <v>selectImpactedAsset</v>
+        <v>selectCause</v>
       </c>
       <c r="B3872" t="str">
-        <v>اختر الأصل المتأثر</v>
+        <v>اختر السبب</v>
       </c>
       <c r="C3872" t="str">
-        <v>atlasīt ietekmēto aktīvu</v>
+        <v>atlasīt cēloni</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" t="str">
-        <v>selectImpactedProcess</v>
+        <v>selectDepartment</v>
       </c>
       <c r="B3873" t="str">
-        <v>اختر العملية المتأثرة</v>
+        <v>اختر القسم</v>
       </c>
       <c r="C3873" t="str">
-        <v>atlasīt ietekmēto procesu</v>
+        <v>atlasīt nodaļu</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" t="str">
-        <v>selectOwner</v>
+        <v>selectDepartmentFirst</v>
       </c>
       <c r="B3874" t="str">
-        <v>اختر المالك</v>
+        <v>اختر القسم أولاً</v>
       </c>
       <c r="C3874" t="str">
-        <v>atlasīt īpašnieku</v>
+        <v>vispirms atlasiet nodaļu</v>
       </c>
     </row>
     <row r="3875">
       <c r="A3875" t="str">
-        <v>selectRiskTypeFirst</v>
+        <v>selectImpactedAsset</v>
       </c>
       <c r="B3875" t="str">
-        <v>اختر نوع المخاطرة أولاً</v>
+        <v>اختر الأصل المتأثر</v>
       </c>
       <c r="C3875" t="str">
-        <v>vispirms atlasiet riska tipu</v>
+        <v>atlasīt ietekmēto aktīvu</v>
       </c>
     </row>
     <row r="3876">
       <c r="A3876" t="str">
-        <v>selectThreats</v>
+        <v>selectImpactedProcess</v>
       </c>
       <c r="B3876" t="str">
-        <v>اختر التهديدات</v>
+        <v>اختر العملية المتأثرة</v>
       </c>
       <c r="C3876" t="str">
-        <v>atlasīt draudus</v>
+        <v>atlasīt ietekmēto procesu</v>
       </c>
     </row>
     <row r="3877">
       <c r="A3877" t="str">
-        <v>selectVulnerabilities</v>
+        <v>selectOwner</v>
       </c>
       <c r="B3877" t="str">
-        <v>اختر الثغرات</v>
+        <v>اختر المالك</v>
       </c>
       <c r="C3877" t="str">
-        <v>atlasīt ievainojamības</v>
+        <v>atlasīt īpašnieku</v>
       </c>
     </row>
     <row r="3878">
       <c r="A3878" t="str">
-        <v>signature Publish</v>
+        <v>selectRiskTypeFirst</v>
       </c>
       <c r="B3878" t="str">
-        <v>توقيع النشر</v>
+        <v>اختر نوع المخاطرة أولاً</v>
       </c>
       <c r="C3878" t="str">
-        <v>paraksta publicēšana</v>
+        <v>vispirms atlasiet riska tipu</v>
       </c>
     </row>
     <row r="3879">
       <c r="A3879" t="str">
-        <v>skipped</v>
+        <v>selectThreats</v>
       </c>
       <c r="B3879" t="str">
-        <v>تم تخطيه</v>
+        <v>اختر التهديدات</v>
       </c>
       <c r="C3879" t="str">
-        <v>izlaists</v>
+        <v>atlasīt draudus</v>
       </c>
     </row>
     <row r="3880">
       <c r="A3880" t="str">
-        <v>stakeholders found</v>
+        <v>selectVulnerabilities</v>
       </c>
       <c r="B3880" t="str">
-        <v>تم العثور على أصحاب مصلحة</v>
+        <v>اختر الثغرات</v>
       </c>
       <c r="C3880" t="str">
-        <v>ieinteresētās personas atrastas</v>
+        <v>atlasīt ievainojamības</v>
       </c>
     </row>
     <row r="3881">
       <c r="A3881" t="str">
-        <v>startDate</v>
+        <v>signature Publish</v>
       </c>
       <c r="B3881" t="str">
-        <v>تاريخ البدء</v>
+        <v>توقيع النشر</v>
       </c>
       <c r="C3881" t="str">
-        <v>sākuma datums</v>
+        <v>paraksta publicēšana</v>
       </c>
     </row>
     <row r="3882">
       <c r="A3882" t="str">
-        <v>status</v>
+        <v>skipped</v>
       </c>
       <c r="B3882" t="str">
-        <v>الحالة</v>
+        <v>تم تخطيه</v>
       </c>
       <c r="C3882" t="str">
-        <v>statuss</v>
+        <v>izlaists</v>
       </c>
     </row>
     <row r="3883">
       <c r="A3883" t="str">
-        <v>tab</v>
+        <v>stakeholders found</v>
       </c>
       <c r="B3883" t="str">
-        <v>تبويب</v>
+        <v>تم العثور على أصحاب مصلحة</v>
       </c>
       <c r="C3883" t="str">
-        <v>cilne</v>
+        <v>ieinteresētās personas atrastas</v>
       </c>
     </row>
     <row r="3884">
       <c r="A3884" t="str">
-        <v>updateRisk</v>
+        <v>startDate</v>
       </c>
       <c r="B3884" t="str">
-        <v>تحديث المخاطرة</v>
+        <v>تاريخ البدء</v>
       </c>
       <c r="C3884" t="str">
-        <v>atjaunināt risku</v>
+        <v>sākuma datums</v>
       </c>
     </row>
     <row r="3885">
       <c r="A3885" t="str">
-        <v>uploaded</v>
+        <v>status</v>
       </c>
       <c r="B3885" t="str">
-        <v>تم الرفع</v>
+        <v>الحالة</v>
       </c>
       <c r="C3885" t="str">
-        <v>augšupielādēts</v>
+        <v>statuss</v>
       </c>
     </row>
     <row r="3886">
       <c r="A3886" t="str">
-        <v>users imported</v>
+        <v>tab</v>
       </c>
       <c r="B3886" t="str">
-        <v>تم استيراد المستخدمين</v>
+        <v>تبويب</v>
       </c>
       <c r="C3886" t="str">
-        <v>lietotāji importēti</v>
+        <v>cilne</v>
       </c>
     </row>
     <row r="3887">
       <c r="A3887" t="str">
-        <v>xlsx</v>
+        <v>updateRisk</v>
       </c>
       <c r="B3887" t="str">
-        <v>xlsx</v>
+        <v>تحديث المخاطرة</v>
       </c>
       <c r="C3887" t="str">
-        <v>xlsx</v>
+        <v>atjaunināt risku</v>
       </c>
     </row>
     <row r="3888">
       <c r="A3888" t="str">
+        <v>uploaded</v>
+      </c>
+      <c r="B3888" t="str">
+        <v>تم الرفع</v>
+      </c>
+      <c r="C3888" t="str">
+        <v>augšupielādēts</v>
+      </c>
+    </row>
+    <row r="3889">
+      <c r="A3889" t="str">
+        <v>users imported</v>
+      </c>
+      <c r="B3889" t="str">
+        <v>تم استيراد المستخدمين</v>
+      </c>
+      <c r="C3889" t="str">
+        <v>lietotāji importēti</v>
+      </c>
+    </row>
+    <row r="3890">
+      <c r="A3890" t="str">
+        <v>xlsx</v>
+      </c>
+      <c r="B3890" t="str">
+        <v>xlsx</v>
+      </c>
+      <c r="C3890" t="str">
+        <v>xlsx</v>
+      </c>
+    </row>
+    <row r="3891">
+      <c r="A3891" t="str">
         <v>year</v>
       </c>
-      <c r="B3888" t="str">
+      <c r="B3891" t="str">
         <v>سنة</v>
       </c>
-      <c r="C3888" t="str">
+      <c r="C3891" t="str">
         <v>gads</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3888"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3891"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3891"/>
+  <dimension ref="A1:C3908"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -43205,9 +43205,196 @@
         <v>gads</v>
       </c>
     </row>
+    <row r="3892">
+      <c r="A3892" t="str">
+        <v>Help Assistant</v>
+      </c>
+      <c r="B3892" t="str">
+        <v>مساعد المساعدة</v>
+      </c>
+      <c r="C3892" t="str">
+        <v>Palīdzības asistents</v>
+      </c>
+    </row>
+    <row r="3893">
+      <c r="A3893" t="str">
+        <v>Need help?</v>
+      </c>
+      <c r="B3893" t="str">
+        <v>هل تحتاج مساعدة؟</v>
+      </c>
+      <c r="C3893" t="str">
+        <v>Vajadzīga palīdzība?</v>
+      </c>
+    </row>
+    <row r="3894">
+      <c r="A3894" t="str">
+        <v>Ask anything about the application</v>
+      </c>
+      <c r="B3894" t="str">
+        <v>اسأل أي شيء عن التطبيق</v>
+      </c>
+      <c r="C3894" t="str">
+        <v>Jautājiet jebko par lietojumprogrammu</v>
+      </c>
+    </row>
+    <row r="3895">
+      <c r="A3895" t="str">
+        <v>Type your question...</v>
+      </c>
+      <c r="B3895" t="str">
+        <v>اكتب سؤالك...</v>
+      </c>
+      <c r="C3895" t="str">
+        <v>Ierakstiet savu jautājumu...</v>
+      </c>
+    </row>
+    <row r="3896">
+      <c r="A3896" t="str">
+        <v>Clear chat</v>
+      </c>
+      <c r="B3896" t="str">
+        <v>مسح المحادثة</v>
+      </c>
+      <c r="C3896" t="str">
+        <v>Notīrīt sarunu</v>
+      </c>
+    </row>
+    <row r="3897">
+      <c r="A3897" t="str">
+        <v>Browse by Module</v>
+      </c>
+      <c r="B3897" t="str">
+        <v>تصفح حسب الوحدة</v>
+      </c>
+      <c r="C3897" t="str">
+        <v>Pārlūkot pēc moduļa</v>
+      </c>
+    </row>
+    <row r="3898">
+      <c r="A3898" t="str">
+        <v>Suggested for this page</v>
+      </c>
+      <c r="B3898" t="str">
+        <v>مقترح لهذه الصفحة</v>
+      </c>
+      <c r="C3898" t="str">
+        <v>Ieteikts šai lapai</v>
+      </c>
+    </row>
+    <row r="3899">
+      <c r="A3899" t="str">
+        <v>topics</v>
+      </c>
+      <c r="B3899" t="str">
+        <v>مواضيع</v>
+      </c>
+      <c r="C3899" t="str">
+        <v>tēmas</v>
+      </c>
+    </row>
+    <row r="3900">
+      <c r="A3900" t="str">
+        <v>Back to modules</v>
+      </c>
+      <c r="B3900" t="str">
+        <v>العودة للوحدات</v>
+      </c>
+      <c r="C3900" t="str">
+        <v>Atpakaļ uz moduļiem</v>
+      </c>
+    </row>
+    <row r="3901">
+      <c r="A3901" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="B3901" t="str">
+        <v>ملاحظات</v>
+      </c>
+      <c r="C3901" t="str">
+        <v>Piezīmes</v>
+      </c>
+    </row>
+    <row r="3902">
+      <c r="A3902" t="str">
+        <v>Related</v>
+      </c>
+      <c r="B3902" t="str">
+        <v>ذو صلة</v>
+      </c>
+      <c r="C3902" t="str">
+        <v>Saistītais</v>
+      </c>
+    </row>
+    <row r="3903">
+      <c r="A3903" t="str">
+        <v>Related Questions</v>
+      </c>
+      <c r="B3903" t="str">
+        <v>أسئلة ذات صلة</v>
+      </c>
+      <c r="C3903" t="str">
+        <v>Saistītie jautājumi</v>
+      </c>
+    </row>
+    <row r="3904">
+      <c r="A3904" t="str">
+        <v>Press</v>
+      </c>
+      <c r="B3904" t="str">
+        <v>اضغط</v>
+      </c>
+      <c r="C3904" t="str">
+        <v>Nospiediet</v>
+      </c>
+    </row>
+    <row r="3905">
+      <c r="A3905" t="str">
+        <v>to toggle help</v>
+      </c>
+      <c r="B3905" t="str">
+        <v>لفتح/إغلاق المساعدة</v>
+      </c>
+      <c r="C3905" t="str">
+        <v>lai pārslēgtu palīdzību</v>
+      </c>
+    </row>
+    <row r="3906">
+      <c r="A3906" t="str">
+        <v>General</v>
+      </c>
+      <c r="B3906" t="str">
+        <v>عام</v>
+      </c>
+      <c r="C3906" t="str">
+        <v>Vispārīgi</v>
+      </c>
+    </row>
+    <row r="3907">
+      <c r="A3907" t="str">
+        <v>TPRM</v>
+      </c>
+      <c r="B3907" t="str">
+        <v>إدارة مخاطر الطرف الثالث</v>
+      </c>
+      <c r="C3907" t="str">
+        <v>TPRM</v>
+      </c>
+    </row>
+    <row r="3908">
+      <c r="A3908" t="str">
+        <v>GRC Administration</v>
+      </c>
+      <c r="B3908" t="str">
+        <v>إدارة الحوكمة والمخاطر والامتثال</v>
+      </c>
+      <c r="C3908" t="str">
+        <v>GRC administrēšana</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3891"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3908"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,12 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4446"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C4460"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -49310,9 +49305,163 @@
         <v>Izvēlnes</v>
       </c>
     </row>
+    <row r="4447">
+      <c r="A4447" t="str">
+        <v>Export/Import</v>
+      </c>
+      <c r="B4447" t="str">
+        <v>تصدير/استيراد</v>
+      </c>
+      <c r="C4447" t="str">
+        <v>Eksportēt/Importēt</v>
+      </c>
+    </row>
+    <row r="4448">
+      <c r="A4448" t="str">
+        <v>Download Vendor Profile Template</v>
+      </c>
+      <c r="B4448" t="str">
+        <v>تحميل نموذج ملف المورد</v>
+      </c>
+      <c r="C4448" t="str">
+        <v>Lejupielādēt piegādātāja profila veidni</v>
+      </c>
+    </row>
+    <row r="4449">
+      <c r="A4449" t="str">
+        <v>Import Vendor Profile</v>
+      </c>
+      <c r="B4449" t="str">
+        <v>استيراد ملف المورد</v>
+      </c>
+      <c r="C4449" t="str">
+        <v>Importēt piegādātāja profilu</v>
+      </c>
+    </row>
+    <row r="4450">
+      <c r="A4450" t="str">
+        <v>Export Vendor Risk Rating Questions</v>
+      </c>
+      <c r="B4450" t="str">
+        <v>تصدير أسئلة تصنيف مخاطر المورد</v>
+      </c>
+      <c r="C4450" t="str">
+        <v>Eksportēt piegādātāja riska vērtējuma jautājumus</v>
+      </c>
+    </row>
+    <row r="4451">
+      <c r="A4451" t="str">
+        <v>Import Responses for Questions</v>
+      </c>
+      <c r="B4451" t="str">
+        <v>استيراد ردود الأسئلة</v>
+      </c>
+      <c r="C4451" t="str">
+        <v>Importēt atbildes uz jautājumiem</v>
+      </c>
+    </row>
+    <row r="4452">
+      <c r="A4452" t="str">
+        <v>Import Complete</v>
+      </c>
+      <c r="B4452" t="str">
+        <v>اكتمل الاستيراد</v>
+      </c>
+      <c r="C4452" t="str">
+        <v>Importēšana pabeigta</v>
+      </c>
+    </row>
+    <row r="4453">
+      <c r="A4453" t="str">
+        <v>vendors created</v>
+      </c>
+      <c r="B4453" t="str">
+        <v>تم إنشاء الموردين</v>
+      </c>
+      <c r="C4453" t="str">
+        <v>piegādātāji izveidoti</v>
+      </c>
+    </row>
+    <row r="4454">
+      <c r="A4454" t="str">
+        <v>responses updated</v>
+      </c>
+      <c r="B4454" t="str">
+        <v>تم تحديث الردود</v>
+      </c>
+      <c r="C4454" t="str">
+        <v>atbildes atjauninātas</v>
+      </c>
+    </row>
+    <row r="4455">
+      <c r="A4455" t="str">
+        <v>ratings updated</v>
+      </c>
+      <c r="B4455" t="str">
+        <v>تم تحديث التصنيفات</v>
+      </c>
+      <c r="C4455" t="str">
+        <v>vērtējumi atjaunināti</v>
+      </c>
+    </row>
+    <row r="4456">
+      <c r="A4456" t="str">
+        <v>Failed to export questions</v>
+      </c>
+      <c r="B4456" t="str">
+        <v>فشل تصدير الأسئلة</v>
+      </c>
+      <c r="C4456" t="str">
+        <v>Neizdevās eksportēt jautājumus</v>
+      </c>
+    </row>
+    <row r="4457">
+      <c r="A4457" t="str">
+        <v>Failed to import vendors</v>
+      </c>
+      <c r="B4457" t="str">
+        <v>فشل استيراد الموردين</v>
+      </c>
+      <c r="C4457" t="str">
+        <v>Neizdevās importēt piegādātājus</v>
+      </c>
+    </row>
+    <row r="4458">
+      <c r="A4458" t="str">
+        <v>Failed to import responses</v>
+      </c>
+      <c r="B4458" t="str">
+        <v>فشل استيراد الردود</v>
+      </c>
+      <c r="C4458" t="str">
+        <v>Neizdevās importēt atbildes</v>
+      </c>
+    </row>
+    <row r="4459">
+      <c r="A4459" t="str">
+        <v>Upload the filled vendor profile template (.xlsx or .xls)</v>
+      </c>
+      <c r="B4459" t="str">
+        <v>ارفع نموذج ملف المورد المعبأ (.xlsx أو .xls)</v>
+      </c>
+      <c r="C4459" t="str">
+        <v>Augšupielādēt aizpildīto piegādātāja profila veidni (.xlsx vai .xls)</v>
+      </c>
+    </row>
+    <row r="4460">
+      <c r="A4460" t="str">
+        <v>Upload the filled vendor questionnaire with responses (.xlsx or .xls)</v>
+      </c>
+      <c r="B4460" t="str">
+        <v>ارفع استبيان المورد المعبأ بالردود (.xlsx أو .xls)</v>
+      </c>
+      <c r="C4460" t="str">
+        <v>Augšupielādēt aizpildīto piegādātāja anketu ar atbildēm (.xlsx vai .xls)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4446"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4460"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,12 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5218"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C5306"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -57802,9 +57797,977 @@
         <v>Dodieties uz Pamatdatu pārvaldība &gt; Jomas.</v>
       </c>
     </row>
+    <row r="5219">
+      <c r="A5219" t="str">
+        <v>Technical Evidence</v>
+      </c>
+      <c r="B5219" t="str">
+        <v>الأدلة التقنية</v>
+      </c>
+      <c r="C5219" t="str">
+        <v>Tehniskie pierādījumi</v>
+      </c>
+    </row>
+    <row r="5220">
+      <c r="A5220" t="str">
+        <v>Credential Vault</v>
+      </c>
+      <c r="B5220" t="str">
+        <v>خزنة بيانات الاعتماد</v>
+      </c>
+      <c r="C5220" t="str">
+        <v>Akreditācijas datu glabātuve</v>
+      </c>
+    </row>
+    <row r="5221">
+      <c r="A5221" t="str">
+        <v>Configure Credentials</v>
+      </c>
+      <c r="B5221" t="str">
+        <v>تكوين بيانات الاعتماد</v>
+      </c>
+      <c r="C5221" t="str">
+        <v>Konfigurēt akreditācijas datus</v>
+      </c>
+    </row>
+    <row r="5222">
+      <c r="A5222" t="str">
+        <v>Connect to live systems to pull real-time evidence. This data can be used to support automated checks and provide up-to-the-minute status for audits. Ensure your integrations are configured on the Settings page.</v>
+      </c>
+      <c r="B5222" t="str">
+        <v>الاتصال بالأنظمة المباشرة لسحب الأدلة في الوقت الفعلي. يمكن استخدام هذه البيانات لدعم عمليات التحقق الآلية وتوفير حالة محدثة للتدقيق.</v>
+      </c>
+      <c r="C5222" t="str">
+        <v>Savienojieties ar reāllaika sistēmām, lai iegūtu pierādījumus. Šos datus var izmantot automatizētu pārbaužu atbalstam.</v>
+      </c>
+    </row>
+    <row r="5223">
+      <c r="A5223" t="str">
+        <v>Microsoft Azure &amp; Defender</v>
+      </c>
+      <c r="B5223" t="str">
+        <v>مايكروسوفت أزور والمدافع</v>
+      </c>
+      <c r="C5223" t="str">
+        <v>Microsoft Azure un Defender</v>
+      </c>
+    </row>
+    <row r="5224">
+      <c r="A5224" t="str">
+        <v>Tenable</v>
+      </c>
+      <c r="B5224" t="str">
+        <v>تينابل</v>
+      </c>
+      <c r="C5224" t="str">
+        <v>Tenable</v>
+      </c>
+    </row>
+    <row r="5225">
+      <c r="A5225" t="str">
+        <v>Acunetix</v>
+      </c>
+      <c r="B5225" t="str">
+        <v>أكيونتكس</v>
+      </c>
+      <c r="C5225" t="str">
+        <v>Acunetix</v>
+      </c>
+    </row>
+    <row r="5226">
+      <c r="A5226" t="str">
+        <v>Service Desk</v>
+      </c>
+      <c r="B5226" t="str">
+        <v>مكتب الخدمة</v>
+      </c>
+      <c r="C5226" t="str">
+        <v>Pakalpojumu dienests</v>
+      </c>
+    </row>
+    <row r="5227">
+      <c r="A5227" t="str">
+        <v>Google Cloud Platform</v>
+      </c>
+      <c r="B5227" t="str">
+        <v>منصة جوجل السحابية</v>
+      </c>
+      <c r="C5227" t="str">
+        <v>Google mākoņa platforma</v>
+      </c>
+    </row>
+    <row r="5228">
+      <c r="A5228" t="str">
+        <v>No data sources configured</v>
+      </c>
+      <c r="B5228" t="str">
+        <v>لم يتم تكوين مصادر البيانات</v>
+      </c>
+      <c r="C5228" t="str">
+        <v>Nav konfigurēti datu avoti</v>
+      </c>
+    </row>
+    <row r="5229">
+      <c r="A5229" t="str">
+        <v>Configure credentials in Settings to enable data collection for this platform.</v>
+      </c>
+      <c r="B5229" t="str">
+        <v>قم بتكوين بيانات الاعتماد في الإعدادات لتمكين جمع البيانات لهذه المنصة.</v>
+      </c>
+      <c r="C5229" t="str">
+        <v>Konfigurējiet akreditācijas datus iestatījumos, lai iespējotu datu vākšanu šai platformai.</v>
+      </c>
+    </row>
+    <row r="5230">
+      <c r="A5230" t="str">
+        <v>Last Collected</v>
+      </c>
+      <c r="B5230" t="str">
+        <v>آخر جمع</v>
+      </c>
+      <c r="C5230" t="str">
+        <v>Pēdējoreiz savākts</v>
+      </c>
+    </row>
+    <row r="5231">
+      <c r="A5231" t="str">
+        <v>Never</v>
+      </c>
+      <c r="B5231" t="str">
+        <v>أبداً</v>
+      </c>
+      <c r="C5231" t="str">
+        <v>Nekad</v>
+      </c>
+    </row>
+    <row r="5232">
+      <c r="A5232" t="str">
+        <v>Collect</v>
+      </c>
+      <c r="B5232" t="str">
+        <v>جمع</v>
+      </c>
+      <c r="C5232" t="str">
+        <v>Savākt</v>
+      </c>
+    </row>
+    <row r="5233">
+      <c r="A5233" t="str">
+        <v>Recollect</v>
+      </c>
+      <c r="B5233" t="str">
+        <v>إعادة الجمع</v>
+      </c>
+      <c r="C5233" t="str">
+        <v>Atkārtoti savākt</v>
+      </c>
+    </row>
+    <row r="5234">
+      <c r="A5234" t="str">
+        <v>Record Count</v>
+      </c>
+      <c r="B5234" t="str">
+        <v>عدد السجلات</v>
+      </c>
+      <c r="C5234" t="str">
+        <v>Ierakstu skaits</v>
+      </c>
+    </row>
+    <row r="5235">
+      <c r="A5235" t="str">
+        <v>Collection failed</v>
+      </c>
+      <c r="B5235" t="str">
+        <v>فشل الجمع</v>
+      </c>
+      <c r="C5235" t="str">
+        <v>Savākšana neizdevās</v>
+      </c>
+    </row>
+    <row r="5236">
+      <c r="A5236" t="str">
+        <v>View Data</v>
+      </c>
+      <c r="B5236" t="str">
+        <v>عرض البيانات</v>
+      </c>
+      <c r="C5236" t="str">
+        <v>Skatīt datus</v>
+      </c>
+    </row>
+    <row r="5237">
+      <c r="A5237" t="str">
+        <v>Collecting...</v>
+      </c>
+      <c r="B5237" t="str">
+        <v>جاري الجمع...</v>
+      </c>
+      <c r="C5237" t="str">
+        <v>Savāc...</v>
+      </c>
+    </row>
+    <row r="5238">
+      <c r="A5238" t="str">
+        <v>Manage credentials for connecting to external platforms. Credentials are encrypted and stored securely.</v>
+      </c>
+      <c r="B5238" t="str">
+        <v>إدارة بيانات الاعتماد للاتصال بالمنصات الخارجية. يتم تشفير بيانات الاعتماد وتخزينها بأمان.</v>
+      </c>
+      <c r="C5238" t="str">
+        <v>Pārvaldiet akreditācijas datus savienojumam ar ārējām platformām. Akreditācijas dati tiek šifrēti un droši glabāti.</v>
+      </c>
+    </row>
+    <row r="5239">
+      <c r="A5239" t="str">
+        <v>Connected</v>
+      </c>
+      <c r="B5239" t="str">
+        <v>متصل</v>
+      </c>
+      <c r="C5239" t="str">
+        <v>Savienots</v>
+      </c>
+    </row>
+    <row r="5240">
+      <c r="A5240" t="str">
+        <v>Disconnected</v>
+      </c>
+      <c r="B5240" t="str">
+        <v>غير متصل</v>
+      </c>
+      <c r="C5240" t="str">
+        <v>Atvienots</v>
+      </c>
+    </row>
+    <row r="5241">
+      <c r="A5241" t="str">
+        <v>Not Configured</v>
+      </c>
+      <c r="B5241" t="str">
+        <v>غير مكوّن</v>
+      </c>
+      <c r="C5241" t="str">
+        <v>Nav konfigurēts</v>
+      </c>
+    </row>
+    <row r="5242">
+      <c r="A5242" t="str">
+        <v>Azure Entra (AD)</v>
+      </c>
+      <c r="B5242" t="str">
+        <v>أزور إنترا (AD)</v>
+      </c>
+      <c r="C5242" t="str">
+        <v>Azure Entra (AD)</v>
+      </c>
+    </row>
+    <row r="5243">
+      <c r="A5243" t="str">
+        <v>Azure Security</v>
+      </c>
+      <c r="B5243" t="str">
+        <v>أمن أزور</v>
+      </c>
+      <c r="C5243" t="str">
+        <v>Azure drošība</v>
+      </c>
+    </row>
+    <row r="5244">
+      <c r="A5244" t="str">
+        <v>Cisco</v>
+      </c>
+      <c r="B5244" t="str">
+        <v>سيسكو</v>
+      </c>
+      <c r="C5244" t="str">
+        <v>Cisco</v>
+      </c>
+    </row>
+    <row r="5245">
+      <c r="A5245" t="str">
+        <v>Palo Alto Networks</v>
+      </c>
+      <c r="B5245" t="str">
+        <v>شبكات بالو ألتو</v>
+      </c>
+      <c r="C5245" t="str">
+        <v>Palo Alto Networks</v>
+      </c>
+    </row>
+    <row r="5246">
+      <c r="A5246" t="str">
+        <v>FortiGate</v>
+      </c>
+      <c r="B5246" t="str">
+        <v>فورتي جيت</v>
+      </c>
+      <c r="C5246" t="str">
+        <v>FortiGate</v>
+      </c>
+    </row>
+    <row r="5247">
+      <c r="A5247" t="str">
+        <v>ServiceNow</v>
+      </c>
+      <c r="B5247" t="str">
+        <v>سيرفس ناو</v>
+      </c>
+      <c r="C5247" t="str">
+        <v>ServiceNow</v>
+      </c>
+    </row>
+    <row r="5248">
+      <c r="A5248" t="str">
+        <v>Connect to Azure Active Directory for user accounts, MFA status, dormant users, and password policies.</v>
+      </c>
+      <c r="B5248" t="str">
+        <v>الاتصال بـ Azure Active Directory للحصول على حسابات المستخدمين وحالة MFA والمستخدمين الخاملين وسياسات كلمات المرور.</v>
+      </c>
+      <c r="C5248" t="str">
+        <v>Savienojieties ar Azure Active Directory lietotāju kontiem, MFA statusam, neaktīviem lietotājiem un paroļu politikām.</v>
+      </c>
+    </row>
+    <row r="5249">
+      <c r="A5249" t="str">
+        <v>Connect to Azure Defender, Sentinel, Secure Score, and Cloud Security Posture Management.</v>
+      </c>
+      <c r="B5249" t="str">
+        <v>الاتصال بـ Azure Defender و Sentinel و Secure Score وإدارة وضع أمان السحابة.</v>
+      </c>
+      <c r="C5249" t="str">
+        <v>Savienojieties ar Azure Defender, Sentinel, Secure Score un mākoņa drošības pārvaldību.</v>
+      </c>
+    </row>
+    <row r="5250">
+      <c r="A5250" t="str">
+        <v>Connect to GCP Security Command Center for posture, findings, IAM, and cloud inventory.</v>
+      </c>
+      <c r="B5250" t="str">
+        <v>الاتصال بمركز أوامر أمان GCP للوضع الأمني والنتائج وIAM ومخزون السحابة.</v>
+      </c>
+      <c r="C5250" t="str">
+        <v>Savienojieties ar GCP drošības komandu centru.</v>
+      </c>
+    </row>
+    <row r="5251">
+      <c r="A5251" t="str">
+        <v>Connect to Cisco ASA/FTD firewalls for configuration analysis and compliance checks.</v>
+      </c>
+      <c r="B5251" t="str">
+        <v>الاتصال بجدران حماية Cisco ASA/FTD لتحليل التكوين وفحوصات الامتثال.</v>
+      </c>
+      <c r="C5251" t="str">
+        <v>Savienojieties ar Cisco ASA/FTD ugunsmūriem konfigurācijas analīzei.</v>
+      </c>
+    </row>
+    <row r="5252">
+      <c r="A5252" t="str">
+        <v>Connect to Palo Alto firewalls for security policy and configuration evidence.</v>
+      </c>
+      <c r="B5252" t="str">
+        <v>الاتصال بجدران حماية Palo Alto لأدلة سياسة الأمان والتكوين.</v>
+      </c>
+      <c r="C5252" t="str">
+        <v>Savienojieties ar Palo Alto ugunsmūriem drošības politikas pierādījumiem.</v>
+      </c>
+    </row>
+    <row r="5253">
+      <c r="A5253" t="str">
+        <v>Connect to FortiGate firewalls for network security compliance evidence.</v>
+      </c>
+      <c r="B5253" t="str">
+        <v>الاتصال بجدران حماية FortiGate لأدلة امتثال أمان الشبكة.</v>
+      </c>
+      <c r="C5253" t="str">
+        <v>Savienojieties ar FortiGate ugunsmūriem tīkla drošības pierādījumiem.</v>
+      </c>
+    </row>
+    <row r="5254">
+      <c r="A5254" t="str">
+        <v>Connect to ServiceNow for incidents, change requests, and service desk evidence.</v>
+      </c>
+      <c r="B5254" t="str">
+        <v>الاتصال بـ ServiceNow للحوادث وطلبات التغيير وأدلة مكتب الخدمة.</v>
+      </c>
+      <c r="C5254" t="str">
+        <v>Savienojieties ar ServiceNow incidentiem un izmaiņu pieprasījumiem.</v>
+      </c>
+    </row>
+    <row r="5255">
+      <c r="A5255" t="str">
+        <v>Connect to Tenable for vulnerability scan results and security assessment data.</v>
+      </c>
+      <c r="B5255" t="str">
+        <v>الاتصال بـ Tenable لنتائج فحص الثغرات وبيانات تقييم الأمان.</v>
+      </c>
+      <c r="C5255" t="str">
+        <v>Savienojieties ar Tenable ievainojamību skenēšanas rezultātiem.</v>
+      </c>
+    </row>
+    <row r="5256">
+      <c r="A5256" t="str">
+        <v>Connect to Acunetix for web application vulnerability scanning evidence.</v>
+      </c>
+      <c r="B5256" t="str">
+        <v>الاتصال بـ Acunetix لأدلة فحص ثغرات تطبيقات الويب.</v>
+      </c>
+      <c r="C5256" t="str">
+        <v>Savienojieties ar Acunetix tīmekļa ievainojamību skenēšanas pierādījumiem.</v>
+      </c>
+    </row>
+    <row r="5257">
+      <c r="A5257" t="str">
+        <v>Credential Name</v>
+      </c>
+      <c r="B5257" t="str">
+        <v>اسم بيانات الاعتماد</v>
+      </c>
+      <c r="C5257" t="str">
+        <v>Akreditācijas datu nosaukums</v>
+      </c>
+    </row>
+    <row r="5258">
+      <c r="A5258" t="str">
+        <v>Tenant ID</v>
+      </c>
+      <c r="B5258" t="str">
+        <v>معرف المستأجر</v>
+      </c>
+      <c r="C5258" t="str">
+        <v>Īrnieka ID</v>
+      </c>
+    </row>
+    <row r="5259">
+      <c r="A5259" t="str">
+        <v>Client ID</v>
+      </c>
+      <c r="B5259" t="str">
+        <v>معرف العميل</v>
+      </c>
+      <c r="C5259" t="str">
+        <v>Klienta ID</v>
+      </c>
+    </row>
+    <row r="5260">
+      <c r="A5260" t="str">
+        <v>Client Secret</v>
+      </c>
+      <c r="B5260" t="str">
+        <v>سر العميل</v>
+      </c>
+      <c r="C5260" t="str">
+        <v>Klienta noslēpums</v>
+      </c>
+    </row>
+    <row r="5261">
+      <c r="A5261" t="str">
+        <v>API Key</v>
+      </c>
+      <c r="B5261" t="str">
+        <v>مفتاح API</v>
+      </c>
+      <c r="C5261" t="str">
+        <v>API atslēga</v>
+      </c>
+    </row>
+    <row r="5262">
+      <c r="A5262" t="str">
+        <v>API Token</v>
+      </c>
+      <c r="B5262" t="str">
+        <v>رمز API</v>
+      </c>
+      <c r="C5262" t="str">
+        <v>API žetons</v>
+      </c>
+    </row>
+    <row r="5263">
+      <c r="A5263" t="str">
+        <v>Instance URL</v>
+      </c>
+      <c r="B5263" t="str">
+        <v>رابط المثيل</v>
+      </c>
+      <c r="C5263" t="str">
+        <v>Instances URL</v>
+      </c>
+    </row>
+    <row r="5264">
+      <c r="A5264" t="str">
+        <v>Access Key</v>
+      </c>
+      <c r="B5264" t="str">
+        <v>مفتاح الوصول</v>
+      </c>
+      <c r="C5264" t="str">
+        <v>Piekļuves atslēga</v>
+      </c>
+    </row>
+    <row r="5265">
+      <c r="A5265" t="str">
+        <v>Secret Key</v>
+      </c>
+      <c r="B5265" t="str">
+        <v>المفتاح السري</v>
+      </c>
+      <c r="C5265" t="str">
+        <v>Slepenā atslēga</v>
+      </c>
+    </row>
+    <row r="5266">
+      <c r="A5266" t="str">
+        <v>Host URL</v>
+      </c>
+      <c r="B5266" t="str">
+        <v>رابط المضيف</v>
+      </c>
+      <c r="C5266" t="str">
+        <v>Resursdatora URL</v>
+      </c>
+    </row>
+    <row r="5267">
+      <c r="A5267" t="str">
+        <v>Project ID</v>
+      </c>
+      <c r="B5267" t="str">
+        <v>معرف المشروع</v>
+      </c>
+      <c r="C5267" t="str">
+        <v>Projekta ID</v>
+      </c>
+    </row>
+    <row r="5268">
+      <c r="A5268" t="str">
+        <v>Service Account JSON</v>
+      </c>
+      <c r="B5268" t="str">
+        <v>ملف حساب الخدمة JSON</v>
+      </c>
+      <c r="C5268" t="str">
+        <v>Pakalpojuma konta JSON</v>
+      </c>
+    </row>
+    <row r="5269">
+      <c r="A5269" t="str">
+        <v>Save Credential</v>
+      </c>
+      <c r="B5269" t="str">
+        <v>حفظ بيانات الاعتماد</v>
+      </c>
+      <c r="C5269" t="str">
+        <v>Saglabāt akreditācijas datus</v>
+      </c>
+    </row>
+    <row r="5270">
+      <c r="A5270" t="str">
+        <v>Update Credential</v>
+      </c>
+      <c r="B5270" t="str">
+        <v>تحديث بيانات الاعتماد</v>
+      </c>
+      <c r="C5270" t="str">
+        <v>Atjaunināt akreditācijas datus</v>
+      </c>
+    </row>
+    <row r="5271">
+      <c r="A5271" t="str">
+        <v>Test Connection</v>
+      </c>
+      <c r="B5271" t="str">
+        <v>اختبار الاتصال</v>
+      </c>
+      <c r="C5271" t="str">
+        <v>Testēt savienojumu</v>
+      </c>
+    </row>
+    <row r="5272">
+      <c r="A5272" t="str">
+        <v>Connection successful</v>
+      </c>
+      <c r="B5272" t="str">
+        <v>الاتصال ناجح</v>
+      </c>
+      <c r="C5272" t="str">
+        <v>Savienojums veiksmīgs</v>
+      </c>
+    </row>
+    <row r="5273">
+      <c r="A5273" t="str">
+        <v>Connection Failed</v>
+      </c>
+      <c r="B5273" t="str">
+        <v>فشل الاتصال</v>
+      </c>
+      <c r="C5273" t="str">
+        <v>Savienojums neizdevās</v>
+      </c>
+    </row>
+    <row r="5274">
+      <c r="A5274" t="str">
+        <v>Credential saved and data sources initialized</v>
+      </c>
+      <c r="B5274" t="str">
+        <v>تم حفظ بيانات الاعتماد وتهيئة مصادر البيانات</v>
+      </c>
+      <c r="C5274" t="str">
+        <v>Akreditācijas dati saglabāti un datu avoti inicializēti</v>
+      </c>
+    </row>
+    <row r="5275">
+      <c r="A5275" t="str">
+        <v>Credential updated</v>
+      </c>
+      <c r="B5275" t="str">
+        <v>تم تحديث بيانات الاعتماد</v>
+      </c>
+      <c r="C5275" t="str">
+        <v>Akreditācijas dati atjaunināti</v>
+      </c>
+    </row>
+    <row r="5276">
+      <c r="A5276" t="str">
+        <v>Credential deleted</v>
+      </c>
+      <c r="B5276" t="str">
+        <v>تم حذف بيانات الاعتماد</v>
+      </c>
+      <c r="C5276" t="str">
+        <v>Akreditācijas dati dzēsti</v>
+      </c>
+    </row>
+    <row r="5277">
+      <c r="A5277" t="str">
+        <v>Are you sure you want to delete this credential? All associated collections and data will be removed.</v>
+      </c>
+      <c r="B5277" t="str">
+        <v>هل أنت متأكد من حذف بيانات الاعتماد هذه؟ سيتم إزالة جميع المجموعات والبيانات المرتبطة.</v>
+      </c>
+      <c r="C5277" t="str">
+        <v>Vai tiešām vēlaties dzēst šos akreditācijas datus? Visas saistītās kolekcijas un dati tiks noņemti.</v>
+      </c>
+    </row>
+    <row r="5278">
+      <c r="A5278" t="str">
+        <v>Missing required fields</v>
+      </c>
+      <c r="B5278" t="str">
+        <v>حقول مطلوبة مفقودة</v>
+      </c>
+      <c r="C5278" t="str">
+        <v>Trūkst obligāto lauku</v>
+      </c>
+    </row>
+    <row r="5279">
+      <c r="A5279" t="str">
+        <v>Leave empty to keep current value</v>
+      </c>
+      <c r="B5279" t="str">
+        <v>اتركه فارغاً للاحتفاظ بالقيمة الحالية</v>
+      </c>
+      <c r="C5279" t="str">
+        <v>Atstājiet tukšu, lai saglabātu pašreizējo vērtību</v>
+      </c>
+    </row>
+    <row r="5280">
+      <c r="A5280" t="str">
+        <v>Paste service account JSON here</v>
+      </c>
+      <c r="B5280" t="str">
+        <v>الصق ملف JSON لحساب الخدمة هنا</v>
+      </c>
+      <c r="C5280" t="str">
+        <v>Ielīmējiet pakalpojuma konta JSON šeit</v>
+      </c>
+    </row>
+    <row r="5281">
+      <c r="A5281" t="str">
+        <v>Unknown platform</v>
+      </c>
+      <c r="B5281" t="str">
+        <v>منصة غير معروفة</v>
+      </c>
+      <c r="C5281" t="str">
+        <v>Nezināma platforma</v>
+      </c>
+    </row>
+    <row r="5282">
+      <c r="A5282" t="str">
+        <v>No records collected yet</v>
+      </c>
+      <c r="B5282" t="str">
+        <v>لم يتم جمع سجلات بعد</v>
+      </c>
+      <c r="C5282" t="str">
+        <v>Vēl nav savākti ieraksti</v>
+      </c>
+    </row>
+    <row r="5283">
+      <c r="A5283" t="str">
+        <v>Click Recollect to fetch data from the source.</v>
+      </c>
+      <c r="B5283" t="str">
+        <v>انقر على إعادة الجمع لجلب البيانات من المصدر.</v>
+      </c>
+      <c r="C5283" t="str">
+        <v>Noklikšķiniet Atkārtoti savākt, lai iegūtu datus no avota.</v>
+      </c>
+    </row>
+    <row r="5284">
+      <c r="A5284" t="str">
+        <v>Control Mappings</v>
+      </c>
+      <c r="B5284" t="str">
+        <v>تعيينات الضوابط</v>
+      </c>
+      <c r="C5284" t="str">
+        <v>Kontroles kartējumi</v>
+      </c>
+    </row>
+    <row r="5285">
+      <c r="A5285" t="str">
+        <v>AI Suggest Controls</v>
+      </c>
+      <c r="B5285" t="str">
+        <v>اقتراح ضوابط بالذكاء الاصطناعي</v>
+      </c>
+      <c r="C5285" t="str">
+        <v>AI ieteikt kontroles</v>
+      </c>
+    </row>
+    <row r="5286">
+      <c r="A5286" t="str">
+        <v>No control mappings yet. Use AI Suggest to auto-map controls.</v>
+      </c>
+      <c r="B5286" t="str">
+        <v>لا توجد تعيينات ضوابط بعد. استخدم اقتراح AI لتعيين الضوابط تلقائياً.</v>
+      </c>
+      <c r="C5286" t="str">
+        <v>Vēl nav kontroles kartējumu. Izmantojiet AI ieteikumu automātiskai kartēšanai.</v>
+      </c>
+    </row>
+    <row r="5287">
+      <c r="A5287" t="str">
+        <v>Pending Confirmation</v>
+      </c>
+      <c r="B5287" t="str">
+        <v>في انتظار التأكيد</v>
+      </c>
+      <c r="C5287" t="str">
+        <v>Gaida apstiprinājumu</v>
+      </c>
+    </row>
+    <row r="5288">
+      <c r="A5288" t="str">
+        <v>Confirmed</v>
+      </c>
+      <c r="B5288" t="str">
+        <v>مؤكد</v>
+      </c>
+      <c r="C5288" t="str">
+        <v>Apstiprināts</v>
+      </c>
+    </row>
+    <row r="5289">
+      <c r="A5289" t="str">
+        <v>confidence</v>
+      </c>
+      <c r="B5289" t="str">
+        <v>الثقة</v>
+      </c>
+      <c r="C5289" t="str">
+        <v>pārliecība</v>
+      </c>
+    </row>
+    <row r="5290">
+      <c r="A5290" t="str">
+        <v>Reject</v>
+      </c>
+      <c r="B5290" t="str">
+        <v>رفض</v>
+      </c>
+      <c r="C5290" t="str">
+        <v>Noraidīt</v>
+      </c>
+    </row>
+    <row r="5291">
+      <c r="A5291" t="str">
+        <v>Mapping confirmed</v>
+      </c>
+      <c r="B5291" t="str">
+        <v>تم تأكيد التعيين</v>
+      </c>
+      <c r="C5291" t="str">
+        <v>Kartējums apstiprināts</v>
+      </c>
+    </row>
+    <row r="5292">
+      <c r="A5292" t="str">
+        <v>Mapping rejected</v>
+      </c>
+      <c r="B5292" t="str">
+        <v>تم رفض التعيين</v>
+      </c>
+      <c r="C5292" t="str">
+        <v>Kartējums noraidīts</v>
+      </c>
+    </row>
+    <row r="5293">
+      <c r="A5293" t="str">
+        <v>AI suggestion failed</v>
+      </c>
+      <c r="B5293" t="str">
+        <v>فشل اقتراح الذكاء الاصطناعي</v>
+      </c>
+      <c r="C5293" t="str">
+        <v>AI ieteikums neizdevās</v>
+      </c>
+    </row>
+    <row r="5294">
+      <c r="A5294" t="str">
+        <v>AI suggestions generated</v>
+      </c>
+      <c r="B5294" t="str">
+        <v>تم إنشاء اقتراحات الذكاء الاصطناعي</v>
+      </c>
+      <c r="C5294" t="str">
+        <v>AI ieteikumi ģenerēti</v>
+      </c>
+    </row>
+    <row r="5295">
+      <c r="A5295" t="str">
+        <v>Failed to confirm mapping</v>
+      </c>
+      <c r="B5295" t="str">
+        <v>فشل تأكيد التعيين</v>
+      </c>
+      <c r="C5295" t="str">
+        <v>Neizdevās apstiprināt kartējumu</v>
+      </c>
+    </row>
+    <row r="5296">
+      <c r="A5296" t="str">
+        <v>Failed to reject mapping</v>
+      </c>
+      <c r="B5296" t="str">
+        <v>فشل رفض التعيين</v>
+      </c>
+      <c r="C5296" t="str">
+        <v>Neizdevās noraidīt kartējumu</v>
+      </c>
+    </row>
+    <row r="5297">
+      <c r="A5297" t="str">
+        <v>You don't have permission to access Technical Evidence.</v>
+      </c>
+      <c r="B5297" t="str">
+        <v>ليس لديك صلاحية للوصول إلى الأدلة التقنية.</v>
+      </c>
+      <c r="C5297" t="str">
+        <v>Jums nav atļaujas piekļūt tehniskajiem pierādījumiem.</v>
+      </c>
+    </row>
+    <row r="5298">
+      <c r="A5298" t="str">
+        <v>You don't have permission to manage integration credentials.</v>
+      </c>
+      <c r="B5298" t="str">
+        <v>ليس لديك صلاحية لإدارة بيانات اعتماد التكامل.</v>
+      </c>
+      <c r="C5298" t="str">
+        <v>Jums nav atļaujas pārvaldīt integrācijas akreditācijas datus.</v>
+      </c>
+    </row>
+    <row r="5299">
+      <c r="A5299" t="str">
+        <v>You don't have permission to manage credentials.</v>
+      </c>
+      <c r="B5299" t="str">
+        <v>ليس لديك صلاحية لإدارة بيانات الاعتماد.</v>
+      </c>
+      <c r="C5299" t="str">
+        <v>Jums nav atļaujas pārvaldīt akreditācijas datus.</v>
+      </c>
+    </row>
+    <row r="5300">
+      <c r="A5300" t="str">
+        <v>You don't have permission to view this data.</v>
+      </c>
+      <c r="B5300" t="str">
+        <v>ليس لديك صلاحية لعرض هذه البيانات.</v>
+      </c>
+      <c r="C5300" t="str">
+        <v>Jums nav atļaujas skatīt šos datus.</v>
+      </c>
+    </row>
+    <row r="5301">
+      <c r="A5301" t="str">
+        <v>Configure Credential</v>
+      </c>
+      <c r="B5301" t="str">
+        <v>تكوين بيانات الاعتماد</v>
+      </c>
+      <c r="C5301" t="str">
+        <v>Konfigurēt akreditācijas datus</v>
+      </c>
+    </row>
+    <row r="5302">
+      <c r="A5302" t="str">
+        <v>Save the credential first before testing</v>
+      </c>
+      <c r="B5302" t="str">
+        <v>احفظ بيانات الاعتماد أولاً قبل الاختبار</v>
+      </c>
+      <c r="C5302" t="str">
+        <v>Vispirms saglabājiet akreditācijas datus pirms testēšanas</v>
+      </c>
+    </row>
+    <row r="5303">
+      <c r="A5303" t="str">
+        <v>Failed to save credential</v>
+      </c>
+      <c r="B5303" t="str">
+        <v>فشل حفظ بيانات الاعتماد</v>
+      </c>
+      <c r="C5303" t="str">
+        <v>Neizdevās saglabāt akreditācijas datus</v>
+      </c>
+    </row>
+    <row r="5304">
+      <c r="A5304" t="str">
+        <v>Failed to update</v>
+      </c>
+      <c r="B5304" t="str">
+        <v>فشل التحديث</v>
+      </c>
+      <c r="C5304" t="str">
+        <v>Neizdevās atjaunināt</v>
+      </c>
+    </row>
+    <row r="5305">
+      <c r="A5305" t="str">
+        <v>Failed to delete credential</v>
+      </c>
+      <c r="B5305" t="str">
+        <v>فشل حذف بيانات الاعتماد</v>
+      </c>
+      <c r="C5305" t="str">
+        <v>Neizdevās dzēst akreditācijas datus</v>
+      </c>
+    </row>
+    <row r="5306">
+      <c r="A5306" t="str">
+        <v>Connection test failed</v>
+      </c>
+      <c r="B5306" t="str">
+        <v>فشل اختبار الاتصال</v>
+      </c>
+      <c r="C5306" t="str">
+        <v>Savienojuma tests neizdevās</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5218"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5306"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5306"/>
+  <dimension ref="A1:C5391"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -58765,9 +58765,944 @@
         <v>Savienojuma tests neizdevās</v>
       </c>
     </row>
+    <row r="5307">
+      <c r="A5307" t="str">
+        <v>Add Minutes</v>
+      </c>
+      <c r="B5307" t="str">
+        <v>إضافة محضر</v>
+      </c>
+      <c r="C5307" t="str">
+        <v>Pievienot protokolu</v>
+      </c>
+    </row>
+    <row r="5308">
+      <c r="A5308" t="str">
+        <v>Agenda</v>
+      </c>
+      <c r="B5308" t="str">
+        <v>جدول الأعمال</v>
+      </c>
+      <c r="C5308" t="str">
+        <v>Darba kārtība</v>
+      </c>
+    </row>
+    <row r="5309">
+      <c r="A5309" t="str">
+        <v>Announcement</v>
+      </c>
+      <c r="B5309" t="str">
+        <v>الإعلان</v>
+      </c>
+      <c r="C5309" t="str">
+        <v>Paziņojums</v>
+      </c>
+    </row>
+    <row r="5310">
+      <c r="A5310" t="str">
+        <v>Announcement message</v>
+      </c>
+      <c r="B5310" t="str">
+        <v>نص الإعلان</v>
+      </c>
+      <c r="C5310" t="str">
+        <v>Paziņojuma teksts</v>
+      </c>
+    </row>
+    <row r="5311">
+      <c r="A5311" t="str">
+        <v>Announcement saved</v>
+      </c>
+      <c r="B5311" t="str">
+        <v>تم حفظ الإعلان</v>
+      </c>
+      <c r="C5311" t="str">
+        <v>Paziņojums saglabāts</v>
+      </c>
+    </row>
+    <row r="5312">
+      <c r="A5312" t="str">
+        <v>Announcement sent</v>
+      </c>
+      <c r="B5312" t="str">
+        <v>تم إرسال الإعلان</v>
+      </c>
+      <c r="C5312" t="str">
+        <v>Paziņojums nosūtīts</v>
+      </c>
+    </row>
+    <row r="5313">
+      <c r="A5313" t="str">
+        <v>Announcement subject</v>
+      </c>
+      <c r="B5313" t="str">
+        <v>موضوع الإعلان</v>
+      </c>
+      <c r="C5313" t="str">
+        <v>Paziņojuma temats</v>
+      </c>
+    </row>
+    <row r="5314">
+      <c r="A5314" t="str">
+        <v>Are you sure you want to delete these minutes?</v>
+      </c>
+      <c r="B5314" t="str">
+        <v>هل أنت متأكد أنك تريد حذف هذا المحضر؟</v>
+      </c>
+      <c r="C5314" t="str">
+        <v>Vai tiešām vēlaties dzēst šo protokolu?</v>
+      </c>
+    </row>
+    <row r="5315">
+      <c r="A5315" t="str">
+        <v>Are you sure you want to delete this document?</v>
+      </c>
+      <c r="B5315" t="str">
+        <v>هل أنت متأكد أنك تريد حذف هذا المستند؟</v>
+      </c>
+      <c r="C5315" t="str">
+        <v>Vai tiešām vēlaties dzēst šo dokumentu?</v>
+      </c>
+    </row>
+    <row r="5316">
+      <c r="A5316" t="str">
+        <v>Attendees</v>
+      </c>
+      <c r="B5316" t="str">
+        <v>الحضور</v>
+      </c>
+      <c r="C5316" t="str">
+        <v>Dalībnieki</v>
+      </c>
+    </row>
+    <row r="5317">
+      <c r="A5317" t="str">
+        <v>Audit Announcement</v>
+      </c>
+      <c r="B5317" t="str">
+        <v>إعلان التدقيق</v>
+      </c>
+      <c r="C5317" t="str">
+        <v>Audita paziņojums</v>
+      </c>
+    </row>
+    <row r="5318">
+      <c r="A5318" t="str">
+        <v>audit engagement(s) generated from this plan</v>
+      </c>
+      <c r="B5318" t="str">
+        <v>مهمة (مهام) تدقيق تم إنشاؤها من هذه الخطة</v>
+      </c>
+      <c r="C5318" t="str">
+        <v>no šī plāna izveidotie audita uzdevumi</v>
+      </c>
+    </row>
+    <row r="5319">
+      <c r="A5319" t="str">
+        <v>Audit methodology</v>
+      </c>
+      <c r="B5319" t="str">
+        <v>منهجية التدقيق</v>
+      </c>
+      <c r="C5319" t="str">
+        <v>Audita metodoloģija</v>
+      </c>
+    </row>
+    <row r="5320">
+      <c r="A5320" t="str">
+        <v>Audit objectives</v>
+      </c>
+      <c r="B5320" t="str">
+        <v>أهداف التدقيق</v>
+      </c>
+      <c r="C5320" t="str">
+        <v>Audita mērķi</v>
+      </c>
+    </row>
+    <row r="5321">
+      <c r="A5321" t="str">
+        <v>Audit Planning Memorandum</v>
+      </c>
+      <c r="B5321" t="str">
+        <v>مذكرة تخطيط التدقيق</v>
+      </c>
+      <c r="C5321" t="str">
+        <v>Audita plānošanas memorands</v>
+      </c>
+    </row>
+    <row r="5322">
+      <c r="A5322" t="str">
+        <v>Audit planning memorandum saved</v>
+      </c>
+      <c r="B5322" t="str">
+        <v>تم حفظ مذكرة تخطيط التدقيق</v>
+      </c>
+      <c r="C5322" t="str">
+        <v>Audita plānošanas memorands saglabāts</v>
+      </c>
+    </row>
+    <row r="5323">
+      <c r="A5323" t="str">
+        <v>Audit Program</v>
+      </c>
+      <c r="B5323" t="str">
+        <v>برنامج التدقيق</v>
+      </c>
+      <c r="C5323" t="str">
+        <v>Audita programma</v>
+      </c>
+    </row>
+    <row r="5324">
+      <c r="A5324" t="str">
+        <v>Audit Program Documents</v>
+      </c>
+      <c r="B5324" t="str">
+        <v>مستندات برنامج التدقيق</v>
+      </c>
+      <c r="C5324" t="str">
+        <v>Audita programmas dokumenti</v>
+      </c>
+    </row>
+    <row r="5325">
+      <c r="A5325" t="str">
+        <v>Audit scope</v>
+      </c>
+      <c r="B5325" t="str">
+        <v>نطاق التدقيق</v>
+      </c>
+      <c r="C5325" t="str">
+        <v>Audita tvērums</v>
+      </c>
+    </row>
+    <row r="5326">
+      <c r="A5326" t="str">
+        <v>Audit timeline</v>
+      </c>
+      <c r="B5326" t="str">
+        <v>الجدول الزمني للتدقيق</v>
+      </c>
+      <c r="C5326" t="str">
+        <v>Audita laika grafiks</v>
+      </c>
+    </row>
+    <row r="5327">
+      <c r="A5327" t="str">
+        <v>Closing Meeting</v>
+      </c>
+      <c r="B5327" t="str">
+        <v>اجتماع الإغلاق</v>
+      </c>
+      <c r="C5327" t="str">
+        <v>Noslēguma sanāksme</v>
+      </c>
+    </row>
+    <row r="5328">
+      <c r="A5328" t="str">
+        <v>Commence Date</v>
+      </c>
+      <c r="B5328" t="str">
+        <v>تاريخ البدء</v>
+      </c>
+      <c r="C5328" t="str">
+        <v>Sākuma datums</v>
+      </c>
+    </row>
+    <row r="5329">
+      <c r="A5329" t="str">
+        <v>Current</v>
+      </c>
+      <c r="B5329" t="str">
+        <v>الحالي</v>
+      </c>
+      <c r="C5329" t="str">
+        <v>Pašreizējais</v>
+      </c>
+    </row>
+    <row r="5330">
+      <c r="A5330" t="str">
+        <v>Current step updated</v>
+      </c>
+      <c r="B5330" t="str">
+        <v>تم تحديث الخطوة الحالية</v>
+      </c>
+      <c r="C5330" t="str">
+        <v>Pašreizējais solis atjaunināts</v>
+      </c>
+    </row>
+    <row r="5331">
+      <c r="A5331" t="str">
+        <v>Decisions &amp; Action Plans</v>
+      </c>
+      <c r="B5331" t="str">
+        <v>القرارات وخطط العمل</v>
+      </c>
+      <c r="C5331" t="str">
+        <v>Lēmumi un rīcības plāni</v>
+      </c>
+    </row>
+    <row r="5332">
+      <c r="A5332" t="str">
+        <v>Delete Minutes</v>
+      </c>
+      <c r="B5332" t="str">
+        <v>حذف المحضر</v>
+      </c>
+      <c r="C5332" t="str">
+        <v>Dzēst protokolu</v>
+      </c>
+    </row>
+    <row r="5333">
+      <c r="A5333" t="str">
+        <v>Document deleted</v>
+      </c>
+      <c r="B5333" t="str">
+        <v>تم حذف المستند</v>
+      </c>
+      <c r="C5333" t="str">
+        <v>Dokuments dzēsts</v>
+      </c>
+    </row>
+    <row r="5334">
+      <c r="A5334" t="str">
+        <v>Documents uploaded</v>
+      </c>
+      <c r="B5334" t="str">
+        <v>تم رفع المستندات</v>
+      </c>
+      <c r="C5334" t="str">
+        <v>Dokumenti augšupielādēti</v>
+      </c>
+    </row>
+    <row r="5335">
+      <c r="A5335" t="str">
+        <v>Edit Minutes</v>
+      </c>
+      <c r="B5335" t="str">
+        <v>تعديل المحضر</v>
+      </c>
+      <c r="C5335" t="str">
+        <v>Rediģēt protokolu</v>
+      </c>
+    </row>
+    <row r="5336">
+      <c r="A5336" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B5336" t="str">
+        <v>البريد الإلكتروني</v>
+      </c>
+      <c r="C5336" t="str">
+        <v>E-pasta adrese</v>
+      </c>
+    </row>
+    <row r="5337">
+      <c r="A5337" t="str">
+        <v>Failed to delete minutes</v>
+      </c>
+      <c r="B5337" t="str">
+        <v>فشل حذف المحضر</v>
+      </c>
+      <c r="C5337" t="str">
+        <v>Neizdevās dzēst protokolu</v>
+      </c>
+    </row>
+    <row r="5338">
+      <c r="A5338" t="str">
+        <v>Failed to load announcement</v>
+      </c>
+      <c r="B5338" t="str">
+        <v>فشل تحميل الإعلان</v>
+      </c>
+      <c r="C5338" t="str">
+        <v>Neizdevās ielādēt paziņojumu</v>
+      </c>
+    </row>
+    <row r="5339">
+      <c r="A5339" t="str">
+        <v>Failed to load audit planning memorandum</v>
+      </c>
+      <c r="B5339" t="str">
+        <v>فشل تحميل مذكرة تخطيط التدقيق</v>
+      </c>
+      <c r="C5339" t="str">
+        <v>Neizdevās ielādēt audita plānošanas memorandu</v>
+      </c>
+    </row>
+    <row r="5340">
+      <c r="A5340" t="str">
+        <v>Failed to load documents</v>
+      </c>
+      <c r="B5340" t="str">
+        <v>فشل تحميل المستندات</v>
+      </c>
+      <c r="C5340" t="str">
+        <v>Neizdevās ielādēt dokumentus</v>
+      </c>
+    </row>
+    <row r="5341">
+      <c r="A5341" t="str">
+        <v>Failed to load meeting minutes</v>
+      </c>
+      <c r="B5341" t="str">
+        <v>فشل تحميل محضر الاجتماع</v>
+      </c>
+      <c r="C5341" t="str">
+        <v>Neizdevās ielādēt sanāksmes protokolu</v>
+      </c>
+    </row>
+    <row r="5342">
+      <c r="A5342" t="str">
+        <v>Failed to save announcement</v>
+      </c>
+      <c r="B5342" t="str">
+        <v>فشل حفظ الإعلان</v>
+      </c>
+      <c r="C5342" t="str">
+        <v>Neizdevās saglabāt paziņojumu</v>
+      </c>
+    </row>
+    <row r="5343">
+      <c r="A5343" t="str">
+        <v>Failed to save audit planning memorandum</v>
+      </c>
+      <c r="B5343" t="str">
+        <v>فشل حفظ مذكرة تخطيط التدقيق</v>
+      </c>
+      <c r="C5343" t="str">
+        <v>Neizdevās saglabāt audita plānošanas memorandu</v>
+      </c>
+    </row>
+    <row r="5344">
+      <c r="A5344" t="str">
+        <v>Failed to save minutes</v>
+      </c>
+      <c r="B5344" t="str">
+        <v>فشل حفظ المحضر</v>
+      </c>
+      <c r="C5344" t="str">
+        <v>Neizdevās saglabāt protokolu</v>
+      </c>
+    </row>
+    <row r="5345">
+      <c r="A5345" t="str">
+        <v>Failed to send announcement</v>
+      </c>
+      <c r="B5345" t="str">
+        <v>فشل إرسال الإعلان</v>
+      </c>
+      <c r="C5345" t="str">
+        <v>Neizdevās nosūtīt paziņojumu</v>
+      </c>
+    </row>
+    <row r="5346">
+      <c r="A5346" t="str">
+        <v>Failed to update workflow</v>
+      </c>
+      <c r="B5346" t="str">
+        <v>فشل تحديث سير العمل</v>
+      </c>
+      <c r="C5346" t="str">
+        <v>Neizdevās atjaunināt darbplūsmu</v>
+      </c>
+    </row>
+    <row r="5347">
+      <c r="A5347" t="str">
+        <v>Failed to upload documents</v>
+      </c>
+      <c r="B5347" t="str">
+        <v>فشل رفع المستندات</v>
+      </c>
+      <c r="C5347" t="str">
+        <v>Neizdevās augšupielādēt dokumentus</v>
+      </c>
+    </row>
+    <row r="5348">
+      <c r="A5348" t="str">
+        <v>Finalized</v>
+      </c>
+      <c r="B5348" t="str">
+        <v>نهائي</v>
+      </c>
+      <c r="C5348" t="str">
+        <v>Pabeigts</v>
+      </c>
+    </row>
+    <row r="5349">
+      <c r="A5349" t="str">
+        <v>Findings Discussion</v>
+      </c>
+      <c r="B5349" t="str">
+        <v>مناقشة الملاحظات</v>
+      </c>
+      <c r="C5349" t="str">
+        <v>Konstatējumu apspriešana</v>
+      </c>
+    </row>
+    <row r="5350">
+      <c r="A5350" t="str">
+        <v>Follow-up</v>
+      </c>
+      <c r="B5350" t="str">
+        <v>المتابعة</v>
+      </c>
+      <c r="C5350" t="str">
+        <v>Turpmākā uzraudzība</v>
+      </c>
+    </row>
+    <row r="5351">
+      <c r="A5351" t="str">
+        <v>List of attendees</v>
+      </c>
+      <c r="B5351" t="str">
+        <v>قائمة الحضور</v>
+      </c>
+      <c r="C5351" t="str">
+        <v>Dalībnieku saraksts</v>
+      </c>
+    </row>
+    <row r="5352">
+      <c r="A5352" t="str">
+        <v>Management contact</v>
+      </c>
+      <c r="B5352" t="str">
+        <v>جهة اتصال الإدارة</v>
+      </c>
+      <c r="C5352" t="str">
+        <v>Vadības kontaktpersona</v>
+      </c>
+    </row>
+    <row r="5353">
+      <c r="A5353" t="str">
+        <v>Mark complete &amp; continue</v>
+      </c>
+      <c r="B5353" t="str">
+        <v>وضع علامة كمكتمل والمتابعة</v>
+      </c>
+      <c r="C5353" t="str">
+        <v>Atzīmēt kā pabeigtu un turpināt</v>
+      </c>
+    </row>
+    <row r="5354">
+      <c r="A5354" t="str">
+        <v>Meeting</v>
+      </c>
+      <c r="B5354" t="str">
+        <v>اجتماع</v>
+      </c>
+      <c r="C5354" t="str">
+        <v>Sanāksme</v>
+      </c>
+    </row>
+    <row r="5355">
+      <c r="A5355" t="str">
+        <v>Meeting Date</v>
+      </c>
+      <c r="B5355" t="str">
+        <v>تاريخ الاجتماع</v>
+      </c>
+      <c r="C5355" t="str">
+        <v>Sanāksmes datums</v>
+      </c>
+    </row>
+    <row r="5356">
+      <c r="A5356" t="str">
+        <v>Meeting title</v>
+      </c>
+      <c r="B5356" t="str">
+        <v>عنوان الاجتماع</v>
+      </c>
+      <c r="C5356" t="str">
+        <v>Sanāksmes nosaukums</v>
+      </c>
+    </row>
+    <row r="5357">
+      <c r="A5357" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B5357" t="str">
+        <v>الرسالة</v>
+      </c>
+      <c r="C5357" t="str">
+        <v>Ziņojums</v>
+      </c>
+    </row>
+    <row r="5358">
+      <c r="A5358" t="str">
+        <v>Methodology</v>
+      </c>
+      <c r="B5358" t="str">
+        <v>المنهجية</v>
+      </c>
+      <c r="C5358" t="str">
+        <v>Metodoloģija</v>
+      </c>
+    </row>
+    <row r="5359">
+      <c r="A5359" t="str">
+        <v>Minutes</v>
+      </c>
+      <c r="B5359" t="str">
+        <v>المحضر</v>
+      </c>
+      <c r="C5359" t="str">
+        <v>Protokols</v>
+      </c>
+    </row>
+    <row r="5360">
+      <c r="A5360" t="str">
+        <v>Minutes added</v>
+      </c>
+      <c r="B5360" t="str">
+        <v>تمت إضافة المحضر</v>
+      </c>
+      <c r="C5360" t="str">
+        <v>Protokols pievienots</v>
+      </c>
+    </row>
+    <row r="5361">
+      <c r="A5361" t="str">
+        <v>Minutes deleted</v>
+      </c>
+      <c r="B5361" t="str">
+        <v>تم حذف المحضر</v>
+      </c>
+      <c r="C5361" t="str">
+        <v>Protokols dzēsts</v>
+      </c>
+    </row>
+    <row r="5362">
+      <c r="A5362" t="str">
+        <v>Minutes updated</v>
+      </c>
+      <c r="B5362" t="str">
+        <v>تم تحديث المحضر</v>
+      </c>
+      <c r="C5362" t="str">
+        <v>Protokols atjaunināts</v>
+      </c>
+    </row>
+    <row r="5363">
+      <c r="A5363" t="str">
+        <v>No documents uploaded yet</v>
+      </c>
+      <c r="B5363" t="str">
+        <v>لم يتم رفع أي مستندات بعد</v>
+      </c>
+      <c r="C5363" t="str">
+        <v>Vēl nav augšupielādēts neviens dokuments</v>
+      </c>
+    </row>
+    <row r="5364">
+      <c r="A5364" t="str">
+        <v>No memorandum yet</v>
+      </c>
+      <c r="B5364" t="str">
+        <v>لا توجد مذكرة بعد</v>
+      </c>
+      <c r="C5364" t="str">
+        <v>Vēl nav memoranda</v>
+      </c>
+    </row>
+    <row r="5365">
+      <c r="A5365" t="str">
+        <v>No minutes recorded yet</v>
+      </c>
+      <c r="B5365" t="str">
+        <v>لم يتم تسجيل أي محضر بعد</v>
+      </c>
+      <c r="C5365" t="str">
+        <v>Vēl nav reģistrēts neviens protokols</v>
+      </c>
+    </row>
+    <row r="5366">
+      <c r="A5366" t="str">
+        <v>on</v>
+      </c>
+      <c r="B5366" t="str">
+        <v>بتاريخ</v>
+      </c>
+      <c r="C5366" t="str">
+        <v>datumā</v>
+      </c>
+    </row>
+    <row r="5367">
+      <c r="A5367" t="str">
+        <v>Opening Meeting</v>
+      </c>
+      <c r="B5367" t="str">
+        <v>اجتماع الافتتاح</v>
+      </c>
+      <c r="C5367" t="str">
+        <v>Atklāšanas sanāksme</v>
+      </c>
+    </row>
+    <row r="5368">
+      <c r="A5368" t="str">
+        <v>Recipient Email</v>
+      </c>
+      <c r="B5368" t="str">
+        <v>بريد المستلم الإلكتروني</v>
+      </c>
+      <c r="C5368" t="str">
+        <v>Saņēmēja e-pasts</v>
+      </c>
+    </row>
+    <row r="5369">
+      <c r="A5369" t="str">
+        <v>Recipient Name</v>
+      </c>
+      <c r="B5369" t="str">
+        <v>اسم المستلم</v>
+      </c>
+      <c r="C5369" t="str">
+        <v>Saņēmēja vārds</v>
+      </c>
+    </row>
+    <row r="5370">
+      <c r="A5370" t="str">
+        <v>Recorded by</v>
+      </c>
+      <c r="B5370" t="str">
+        <v>سُجِّل بواسطة</v>
+      </c>
+      <c r="C5370" t="str">
+        <v>Reģistrēja</v>
+      </c>
+    </row>
+    <row r="5371">
+      <c r="A5371" t="str">
+        <v>Save Draft</v>
+      </c>
+      <c r="B5371" t="str">
+        <v>حفظ المسودة</v>
+      </c>
+      <c r="C5371" t="str">
+        <v>Saglabāt melnrakstu</v>
+      </c>
+    </row>
+    <row r="5372">
+      <c r="A5372" t="str">
+        <v>Send Announcement</v>
+      </c>
+      <c r="B5372" t="str">
+        <v>إرسال الإعلان</v>
+      </c>
+      <c r="C5372" t="str">
+        <v>Nosūtīt paziņojumu</v>
+      </c>
+    </row>
+    <row r="5373">
+      <c r="A5373" t="str">
+        <v>Send this announcement to the auditee?</v>
+      </c>
+      <c r="B5373" t="str">
+        <v>إرسال هذا الإعلان إلى الجهة الخاضعة للتدقيق؟</v>
+      </c>
+      <c r="C5373" t="str">
+        <v>Nosūtīt šo paziņojumu auditējamai pusei?</v>
+      </c>
+    </row>
+    <row r="5374">
+      <c r="A5374" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="B5374" t="str">
+        <v>تم الإرسال</v>
+      </c>
+      <c r="C5374" t="str">
+        <v>Nosūtīts</v>
+      </c>
+    </row>
+    <row r="5375">
+      <c r="A5375" t="str">
+        <v>Sent by</v>
+      </c>
+      <c r="B5375" t="str">
+        <v>أُرسل بواسطة</v>
+      </c>
+      <c r="C5375" t="str">
+        <v>Nosūtīja</v>
+      </c>
+    </row>
+    <row r="5376">
+      <c r="A5376" t="str">
+        <v>Set as current step</v>
+      </c>
+      <c r="B5376" t="str">
+        <v>تعيين كخطوة حالية</v>
+      </c>
+      <c r="C5376" t="str">
+        <v>Iestatīt kā pašreizējo soli</v>
+      </c>
+    </row>
+    <row r="5377">
+      <c r="A5377" t="str">
+        <v>Step marked complete</v>
+      </c>
+      <c r="B5377" t="str">
+        <v>تم وضع علامة على الخطوة كمكتملة</v>
+      </c>
+      <c r="C5377" t="str">
+        <v>Solis atzīmēts kā pabeigts</v>
+      </c>
+    </row>
+    <row r="5378">
+      <c r="A5378" t="str">
+        <v>steps complete</v>
+      </c>
+      <c r="B5378" t="str">
+        <v>خطوات مكتملة</v>
+      </c>
+      <c r="C5378" t="str">
+        <v>soļi pabeigti</v>
+      </c>
+    </row>
+    <row r="5379">
+      <c r="A5379" t="str">
+        <v>Subject</v>
+      </c>
+      <c r="B5379" t="str">
+        <v>الموضوع</v>
+      </c>
+      <c r="C5379" t="str">
+        <v>Temats</v>
+      </c>
+    </row>
+    <row r="5380">
+      <c r="A5380" t="str">
+        <v>This step will be available in a future update.</v>
+      </c>
+      <c r="B5380" t="str">
+        <v>ستتوفر هذه الخطوة في تحديث مستقبلي.</v>
+      </c>
+      <c r="C5380" t="str">
+        <v>Šis solis būs pieejams nākamajā atjauninājumā.</v>
+      </c>
+    </row>
+    <row r="5381">
+      <c r="A5381" t="str">
+        <v>Workflow</v>
+      </c>
+      <c r="B5381" t="str">
+        <v>سير العمل</v>
+      </c>
+      <c r="C5381" t="str">
+        <v>Darbplūsma</v>
+      </c>
+    </row>
+    <row r="5382">
+      <c r="A5382" t="str">
+        <v>Send the formal audit announcement to management with the preliminary information request (PBC) list.</v>
+      </c>
+      <c r="B5382" t="str">
+        <v>إرسال إعلان التدقيق الرسمي إلى الإدارة مع قائمة طلب المعلومات الأولية (PBC).</v>
+      </c>
+      <c r="C5382" t="str">
+        <v>Nosūtīt vadībai oficiālu audita paziņojumu kopā ar sākotnējo informācijas pieprasījuma (PBC) sarakstu.</v>
+      </c>
+    </row>
+    <row r="5383">
+      <c r="A5383" t="str">
+        <v>Define audit scope, objectives, methodology and timeline; attach detailed audit program documents.</v>
+      </c>
+      <c r="B5383" t="str">
+        <v>تحديد نطاق التدقيق وأهدافه ومنهجيته وجدوله الزمني؛ وإرفاق مستندات برنامج التدقيق التفصيلية.</v>
+      </c>
+      <c r="C5383" t="str">
+        <v>Definēt audita tvērumu, mērķus, metodoloģiju un laika grafiku; pievienot detalizētus audita programmas dokumentus.</v>
+      </c>
+    </row>
+    <row r="5384">
+      <c r="A5384" t="str">
+        <v>Walk through objectives, scope, timeline and key contacts; capture the Minutes of Meeting.</v>
+      </c>
+      <c r="B5384" t="str">
+        <v>استعراض الأهداف والنطاق والجدول الزمني وجهات الاتصال الرئيسية؛ وتسجيل محضر الاجتماع.</v>
+      </c>
+      <c r="C5384" t="str">
+        <v>Pārrunāt mērķus, tvērumu, laika grafiku un galvenās kontaktpersonas; reģistrēt sanāksmes protokolu.</v>
+      </c>
+    </row>
+    <row r="5385">
+      <c r="A5385" t="str">
+        <v>Review the audit program overview and prepare workpapers before fieldwork begins.</v>
+      </c>
+      <c r="B5385" t="str">
+        <v>مراجعة نظرة عامة على برنامج التدقيق وإعداد أوراق العمل قبل بدء العمل الميداني.</v>
+      </c>
+      <c r="C5385" t="str">
+        <v>Pārskatīt audita programmas kopsavilkumu un sagatavot darba dokumentus pirms lauka darba sākuma.</v>
+      </c>
+    </row>
+    <row r="5386">
+      <c r="A5386" t="str">
+        <v>Run walkthroughs and control testing, manage workpapers, and collect evidence.</v>
+      </c>
+      <c r="B5386" t="str">
+        <v>إجراء الاستعراضات واختبار الضوابط وإدارة أوراق العمل وجمع الأدلة.</v>
+      </c>
+      <c r="C5386" t="str">
+        <v>Veikt caurskates un kontroļu testēšanu, pārvaldīt darba dokumentus un vākt pierādījumus.</v>
+      </c>
+    </row>
+    <row r="5387">
+      <c r="A5387" t="str">
+        <v>Record audit findings with criteria, condition, cause, effect and recommendations.</v>
+      </c>
+      <c r="B5387" t="str">
+        <v>تسجيل ملاحظات التدقيق مع المعايير والحالة والسبب والأثر والتوصيات.</v>
+      </c>
+      <c r="C5387" t="str">
+        <v>Reģistrēt audita konstatējumus ar kritērijiem, stāvokli, cēloni, sekām un ieteikumiem.</v>
+      </c>
+    </row>
+    <row r="5388">
+      <c r="A5388" t="str">
+        <v>Validate facts, agree on action plans and finalize management responses; capture the Minutes of Meeting.</v>
+      </c>
+      <c r="B5388" t="str">
+        <v>التحقق من الحقائق والاتفاق على خطط العمل ووضع اللمسات النهائية على ردود الإدارة؛ وتسجيل محضر الاجتماع.</v>
+      </c>
+      <c r="C5388" t="str">
+        <v>Pārbaudīt faktus, vienoties par rīcības plāniem un pabeigt vadības atbildes; reģistrēt sanāksmes protokolu.</v>
+      </c>
+    </row>
+    <row r="5389">
+      <c r="A5389" t="str">
+        <v>Generate the draft and final audit reports and capture auditee responses.</v>
+      </c>
+      <c r="B5389" t="str">
+        <v>إنشاء مسودة تقارير التدقيق والتقارير النهائية وتسجيل ردود الجهة الخاضعة للتدقيق.</v>
+      </c>
+      <c r="C5389" t="str">
+        <v>Izveidot audita ziņojumu melnrakstus un galīgos ziņojumus un fiksēt auditējamās puses atbildes.</v>
+      </c>
+    </row>
+    <row r="5390">
+      <c r="A5390" t="str">
+        <v>Discuss final observations and action plans; capture the Minutes of Meeting.</v>
+      </c>
+      <c r="B5390" t="str">
+        <v>مناقشة الملاحظات النهائية وخطط العمل؛ وتسجيل محضر الاجتماع.</v>
+      </c>
+      <c r="C5390" t="str">
+        <v>Apspriest galīgos novērojumus un rīcības plānus; reģistrēt sanāksmes protokolu.</v>
+      </c>
+    </row>
+    <row r="5391">
+      <c r="A5391" t="str">
+        <v>Track implementation of recommendations, due dates and remediation progress.</v>
+      </c>
+      <c r="B5391" t="str">
+        <v>تتبع تنفيذ التوصيات وتواريخ الاستحقاق وتقدم المعالجة.</v>
+      </c>
+      <c r="C5391" t="str">
+        <v>Sekot līdzi ieteikumu ieviešanai, termiņiem un novēršanas progresam.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5306"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5391"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5391"/>
+  <dimension ref="A1:C5410"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -59700,9 +59700,218 @@
         <v>Sekot līdzi ieteikumu ieviešanai, termiņiem un novēršanas progresam.</v>
       </c>
     </row>
+    <row r="5392">
+      <c r="A5392" t="str">
+        <v>Add findings in Fieldwork to communicate them here.</v>
+      </c>
+      <c r="B5392" t="str">
+        <v>أضف الملاحظات في العمل الميداني لإبلاغها هنا.</v>
+      </c>
+      <c r="C5392" t="str">
+        <v>Pievienojiet konstatējumus lauka darbā, lai tos šeit paziņotu.</v>
+      </c>
+    </row>
+    <row r="5393">
+      <c r="A5393" t="str">
+        <v>Aggregated</v>
+      </c>
+      <c r="B5393" t="str">
+        <v>مجمّع</v>
+      </c>
+      <c r="C5393" t="str">
+        <v>Apkopots</v>
+      </c>
+    </row>
+    <row r="5394">
+      <c r="A5394" t="str">
+        <v>Communication Mode</v>
+      </c>
+      <c r="B5394" t="str">
+        <v>وضع الإبلاغ</v>
+      </c>
+      <c r="C5394" t="str">
+        <v>Saziņas režīms</v>
+      </c>
+    </row>
+    <row r="5395">
+      <c r="A5395" t="str">
+        <v>Communication mode updated</v>
+      </c>
+      <c r="B5395" t="str">
+        <v>تم تحديث وضع الإبلاغ</v>
+      </c>
+      <c r="C5395" t="str">
+        <v>Saziņas režīms atjaunināts</v>
+      </c>
+    </row>
+    <row r="5396">
+      <c r="A5396" t="str">
+        <v>Continuous</v>
+      </c>
+      <c r="B5396" t="str">
+        <v>مستمر</v>
+      </c>
+      <c r="C5396" t="str">
+        <v>Nepārtraukts</v>
+      </c>
+    </row>
+    <row r="5397">
+      <c r="A5397" t="str">
+        <v>Failed to load findings</v>
+      </c>
+      <c r="B5397" t="str">
+        <v>فشل تحميل الملاحظات</v>
+      </c>
+      <c r="C5397" t="str">
+        <v>Neizdevās ielādēt konstatējumus</v>
+      </c>
+    </row>
+    <row r="5398">
+      <c r="A5398" t="str">
+        <v>Failed to share finding</v>
+      </c>
+      <c r="B5398" t="str">
+        <v>فشل مشاركة الملاحظة</v>
+      </c>
+      <c r="C5398" t="str">
+        <v>Neizdevās kopīgot konstatējumu</v>
+      </c>
+    </row>
+    <row r="5399">
+      <c r="A5399" t="str">
+        <v>Failed to unshare finding</v>
+      </c>
+      <c r="B5399" t="str">
+        <v>فشل إلغاء مشاركة الملاحظة</v>
+      </c>
+      <c r="C5399" t="str">
+        <v>Neizdevās atcelt konstatējuma kopīgošanu</v>
+      </c>
+    </row>
+    <row r="5400">
+      <c r="A5400" t="str">
+        <v>Failed to update communication mode</v>
+      </c>
+      <c r="B5400" t="str">
+        <v>فشل تحديث وضع الإبلاغ</v>
+      </c>
+      <c r="C5400" t="str">
+        <v>Neizdevās atjaunināt saziņas režīmu</v>
+      </c>
+    </row>
+    <row r="5401">
+      <c r="A5401" t="str">
+        <v>Finding shared with auditee</v>
+      </c>
+      <c r="B5401" t="str">
+        <v>تمت مشاركة الملاحظة مع الجهة الخاضعة للتدقيق</v>
+      </c>
+      <c r="C5401" t="str">
+        <v>Konstatējums kopīgots ar auditējamo pusi</v>
+      </c>
+    </row>
+    <row r="5402">
+      <c r="A5402" t="str">
+        <v>Finding unshared</v>
+      </c>
+      <c r="B5402" t="str">
+        <v>تم إلغاء مشاركة الملاحظة</v>
+      </c>
+      <c r="C5402" t="str">
+        <v>Konstatējuma kopīgošana atcelta</v>
+      </c>
+    </row>
+    <row r="5403">
+      <c r="A5403" t="str">
+        <v>Findings are consolidated into the draft detailed report.</v>
+      </c>
+      <c r="B5403" t="str">
+        <v>يتم تجميع الملاحظات في مسودة التقرير التفصيلي.</v>
+      </c>
+      <c r="C5403" t="str">
+        <v>Konstatējumi tiek apkopoti detalizētā ziņojuma melnrakstā.</v>
+      </c>
+    </row>
+    <row r="5404">
+      <c r="A5404" t="str">
+        <v>Findings are shared with the auditee individually as they are identified.</v>
+      </c>
+      <c r="B5404" t="str">
+        <v>تتم مشاركة الملاحظات مع الجهة الخاضعة للتدقيق بشكل فردي عند تحديدها.</v>
+      </c>
+      <c r="C5404" t="str">
+        <v>Konstatējumi tiek individuāli kopīgoti ar auditējamo pusi, tiklīdz tie tiek identificēti.</v>
+      </c>
+    </row>
+    <row r="5405">
+      <c r="A5405" t="str">
+        <v>Findings Communication</v>
+      </c>
+      <c r="B5405" t="str">
+        <v>إبلاغ الملاحظات</v>
+      </c>
+      <c r="C5405" t="str">
+        <v>Konstatējumu paziņošana</v>
+      </c>
+    </row>
+    <row r="5406">
+      <c r="A5406" t="str">
+        <v>No findings recorded yet.</v>
+      </c>
+      <c r="B5406" t="str">
+        <v>لم يتم تسجيل أي ملاحظات بعد.</v>
+      </c>
+      <c r="C5406" t="str">
+        <v>Vēl nav reģistrēts neviens konstatējums.</v>
+      </c>
+    </row>
+    <row r="5407">
+      <c r="A5407" t="str">
+        <v>Open in Fieldwork</v>
+      </c>
+      <c r="B5407" t="str">
+        <v>فتح في العمل الميداني</v>
+      </c>
+      <c r="C5407" t="str">
+        <v>Atvērt lauka darbā</v>
+      </c>
+    </row>
+    <row r="5408">
+      <c r="A5408" t="str">
+        <v>Share with auditee</v>
+      </c>
+      <c r="B5408" t="str">
+        <v>مشاركة مع الجهة الخاضعة للتدقيق</v>
+      </c>
+      <c r="C5408" t="str">
+        <v>Kopīgot ar auditējamo pusi</v>
+      </c>
+    </row>
+    <row r="5409">
+      <c r="A5409" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="B5409" t="str">
+        <v>تمت المشاركة</v>
+      </c>
+      <c r="C5409" t="str">
+        <v>Kopīgots</v>
+      </c>
+    </row>
+    <row r="5410">
+      <c r="A5410" t="str">
+        <v>Unshare</v>
+      </c>
+      <c r="B5410" t="str">
+        <v>إلغاء المشاركة</v>
+      </c>
+      <c r="C5410" t="str">
+        <v>Atcelt kopīgošanu</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5391"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5410"/>
+  <dimension ref="A1:C5415"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -59909,9 +59909,64 @@
         <v>Atcelt kopīgošanu</v>
       </c>
     </row>
+    <row r="5411">
+      <c r="A5411" t="str">
+        <v>Audit Program Overview</v>
+      </c>
+      <c r="B5411" t="str">
+        <v>نظرة عامة على برنامج التدقيق</v>
+      </c>
+      <c r="C5411" t="str">
+        <v>Audita programmas pārskats</v>
+      </c>
+    </row>
+    <row r="5412">
+      <c r="A5412" t="str">
+        <v>Download Audit Program</v>
+      </c>
+      <c r="B5412" t="str">
+        <v>تنزيل برنامج التدقيق</v>
+      </c>
+      <c r="C5412" t="str">
+        <v>Lejupielādēt audita programmu</v>
+      </c>
+    </row>
+    <row r="5413">
+      <c r="A5413" t="str">
+        <v>Implementation Recommendation Document</v>
+      </c>
+      <c r="B5413" t="str">
+        <v>وثيقة توصيات التنفيذ</v>
+      </c>
+      <c r="C5413" t="str">
+        <v>Ieviešanas ieteikumu dokuments</v>
+      </c>
+    </row>
+    <row r="5414">
+      <c r="A5414" t="str">
+        <v>procedure</v>
+      </c>
+      <c r="B5414" t="str">
+        <v>إجراء</v>
+      </c>
+      <c r="C5414" t="str">
+        <v>procedūra</v>
+      </c>
+    </row>
+    <row r="5415">
+      <c r="A5415" t="str">
+        <v>procedures</v>
+      </c>
+      <c r="B5415" t="str">
+        <v>إجراءات</v>
+      </c>
+      <c r="C5415" t="str">
+        <v>procedūras</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5415"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5415"/>
+  <dimension ref="A1:C5422"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -59964,9 +59964,86 @@
         <v>procedūras</v>
       </c>
     </row>
+    <row r="5416">
+      <c r="A5416" t="str">
+        <v>Failed to submit strategic plan</v>
+      </c>
+      <c r="B5416" t="str">
+        <v>فشل إرسال الخطة الاستراتيجية</v>
+      </c>
+      <c r="C5416" t="str">
+        <v>Neizdevās iesniegt stratēģisko plānu</v>
+      </c>
+    </row>
+    <row r="5417">
+      <c r="A5417" t="str">
+        <v>Failed to withdraw submission</v>
+      </c>
+      <c r="B5417" t="str">
+        <v>فشل سحب الطلب</v>
+      </c>
+      <c r="C5417" t="str">
+        <v>Neizdevās atsaukt iesniegumu</v>
+      </c>
+    </row>
+    <row r="5418">
+      <c r="A5418" t="str">
+        <v>Strategic plan submitted for approval</v>
+      </c>
+      <c r="B5418" t="str">
+        <v>تم إرسال الخطة الاستراتيجية للموافقة</v>
+      </c>
+      <c r="C5418" t="str">
+        <v>Stratēģiskais plāns iesniegts apstiprināšanai</v>
+      </c>
+    </row>
+    <row r="5419">
+      <c r="A5419" t="str">
+        <v>Submission withdrawn</v>
+      </c>
+      <c r="B5419" t="str">
+        <v>تم سحب الطلب</v>
+      </c>
+      <c r="C5419" t="str">
+        <v>Iesniegums atsaukts</v>
+      </c>
+    </row>
+    <row r="5420">
+      <c r="A5420" t="str">
+        <v>Submit this strategic plan for approval by the approving authority.</v>
+      </c>
+      <c r="B5420" t="str">
+        <v>إرسال هذه الخطة الاستراتيجية للموافقة من قبل الجهة المعتمِدة.</v>
+      </c>
+      <c r="C5420" t="str">
+        <v>Iesniegt šo stratēģisko plānu apstiprināšanai apstiprinātājinstitūcijā.</v>
+      </c>
+    </row>
+    <row r="5421">
+      <c r="A5421" t="str">
+        <v>This strategic plan is awaiting approval.</v>
+      </c>
+      <c r="B5421" t="str">
+        <v>هذه الخطة الاستراتيجية في انتظار الموافقة.</v>
+      </c>
+      <c r="C5421" t="str">
+        <v>Šis stratēģiskais plāns gaida apstiprinājumu.</v>
+      </c>
+    </row>
+    <row r="5422">
+      <c r="A5422" t="str">
+        <v>Withdraw to Draft</v>
+      </c>
+      <c r="B5422" t="str">
+        <v>إعادة إلى المسودة</v>
+      </c>
+      <c r="C5422" t="str">
+        <v>Atsaukt uz melnrakstu</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5415"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5422"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,12 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5353"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C5374"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -59287,9 +59282,240 @@
         <v>Izmaiņas regulējuma vidē vai izpildes prasībās</v>
       </c>
     </row>
+    <row r="5354">
+      <c r="A5354" t="str">
+        <v>Auditor Comment</v>
+      </c>
+      <c r="B5354" t="str">
+        <v>تعليق المدقق</v>
+      </c>
+      <c r="C5354" t="str">
+        <v>Auditora komentārs</v>
+      </c>
+    </row>
+    <row r="5355">
+      <c r="A5355" t="str">
+        <v>Auditor comment saved successfully</v>
+      </c>
+      <c r="B5355" t="str">
+        <v>تم حفظ تعليق المدقق بنجاح</v>
+      </c>
+      <c r="C5355" t="str">
+        <v>Auditora komentārs veiksmīgi saglabāts</v>
+      </c>
+    </row>
+    <row r="5356">
+      <c r="A5356" t="str">
+        <v>Failed to save auditor comment</v>
+      </c>
+      <c r="B5356" t="str">
+        <v>فشل في حفظ تعليق المدقق</v>
+      </c>
+      <c r="C5356" t="str">
+        <v>Neizdevās saglabāt auditora komentāru</v>
+      </c>
+    </row>
+    <row r="5357">
+      <c r="A5357" t="str">
+        <v>Assign to Auditor</v>
+      </c>
+      <c r="B5357" t="str">
+        <v>تعيين للمدقق</v>
+      </c>
+      <c r="C5357" t="str">
+        <v>Piešķirt auditoram</v>
+      </c>
+    </row>
+    <row r="5358">
+      <c r="A5358" t="str">
+        <v>Internal Notes (Not visible to Auditor)</v>
+      </c>
+      <c r="B5358" t="str">
+        <v>ملاحظات داخلية (غير مرئية للمدقق)</v>
+      </c>
+      <c r="C5358" t="str">
+        <v>Iekšējās piezīmes (Nav redzamas auditoram)</v>
+      </c>
+    </row>
+    <row r="5359">
+      <c r="A5359" t="str">
+        <v>Finding shared with auditor</v>
+      </c>
+      <c r="B5359" t="str">
+        <v>تمت مشاركة الملاحظة مع المدقق</v>
+      </c>
+      <c r="C5359" t="str">
+        <v>Konstatējums kopīgots ar auditoru</v>
+      </c>
+    </row>
+    <row r="5360">
+      <c r="A5360" t="str">
+        <v>Consolidated draft shared with auditor</v>
+      </c>
+      <c r="B5360" t="str">
+        <v>تمت مشاركة المسودة المجمّعة مع المدقق</v>
+      </c>
+      <c r="C5360" t="str">
+        <v>Kopsavilkuma melnraksts kopīgots ar auditoru</v>
+      </c>
+    </row>
+    <row r="5361">
+      <c r="A5361" t="str">
+        <v>All findings consolidated and shared with the auditor.</v>
+      </c>
+      <c r="B5361" t="str">
+        <v>تم دمج جميع الملاحظات ومشاركتها مع المدقق.</v>
+      </c>
+      <c r="C5361" t="str">
+        <v>Visi konstatējumi apvienoti un kopīgoti ar auditoru.</v>
+      </c>
+    </row>
+    <row r="5362">
+      <c r="A5362" t="str">
+        <v>Share consolidated draft with auditor</v>
+      </c>
+      <c r="B5362" t="str">
+        <v>مشاركة المسودة المجمّعة مع المدقق</v>
+      </c>
+      <c r="C5362" t="str">
+        <v>Kopsavilkuma melnrakstu kopīgot ar auditoru</v>
+      </c>
+    </row>
+    <row r="5363">
+      <c r="A5363" t="str">
+        <v>Share with auditor</v>
+      </c>
+      <c r="B5363" t="str">
+        <v>مشاركة مع المدقق</v>
+      </c>
+      <c r="C5363" t="str">
+        <v>Kopīgot ar auditoru</v>
+      </c>
+    </row>
+    <row r="5364">
+      <c r="A5364" t="str">
+        <v>Send this announcement to the auditor?</v>
+      </c>
+      <c r="B5364" t="str">
+        <v>إرسال هذا الإعلان إلى المدقق؟</v>
+      </c>
+      <c r="C5364" t="str">
+        <v>Nosūtīt šo paziņojumu auditoram?</v>
+      </c>
+    </row>
+    <row r="5365">
+      <c r="A5365" t="str">
+        <v>Describe what evidence is expected from the auditor...</v>
+      </c>
+      <c r="B5365" t="str">
+        <v>وصف الأدلة المتوقعة من المدقق...</v>
+      </c>
+      <c r="C5365" t="str">
+        <v>Aprakstiet, kādi pierādījumi tiek sagaidīti no auditora...</v>
+      </c>
+    </row>
+    <row r="5366">
+      <c r="A5366" t="str">
+        <v>Select Audit Manager</v>
+      </c>
+      <c r="B5366" t="str">
+        <v>اختر مدير التدقيق</v>
+      </c>
+      <c r="C5366" t="str">
+        <v>Atlasīt audita vadītāju</v>
+      </c>
+    </row>
+    <row r="5367">
+      <c r="A5367" t="str">
+        <v>Assigned Audit Manager</v>
+      </c>
+      <c r="B5367" t="str">
+        <v>مدير التدقيق المعيّن</v>
+      </c>
+      <c r="C5367" t="str">
+        <v>Norīkotais audita vadītājs</v>
+      </c>
+    </row>
+    <row r="5368">
+      <c r="A5368" t="str">
+        <v>Assigned Audit Managers</v>
+      </c>
+      <c r="B5368" t="str">
+        <v>مدراء التدقيق المعيّنون</v>
+      </c>
+      <c r="C5368" t="str">
+        <v>Norīkotie audita vadītāji</v>
+      </c>
+    </row>
+    <row r="5369">
+      <c r="A5369" t="str">
+        <v>Assign Audit Managers</v>
+      </c>
+      <c r="B5369" t="str">
+        <v>تعيين مدراء التدقيق</v>
+      </c>
+      <c r="C5369" t="str">
+        <v>Piešķirt audita vadītājus</v>
+      </c>
+    </row>
+    <row r="5370">
+      <c r="A5370" t="str">
+        <v>All Levels</v>
+      </c>
+      <c r="B5370" t="str">
+        <v>كل المستويات</v>
+      </c>
+      <c r="C5370" t="str">
+        <v>Visi līmeņi</v>
+      </c>
+    </row>
+    <row r="5371">
+      <c r="A5371" t="str">
+        <v>No risks match the selected risk level.</v>
+      </c>
+      <c r="B5371" t="str">
+        <v>لا توجد مخاطر تطابق مستوى المخاطر المحدد.</v>
+      </c>
+      <c r="C5371" t="str">
+        <v>Neviens risks neatbilst atlasītajam riska līmenim.</v>
+      </c>
+    </row>
+    <row r="5372">
+      <c r="A5372" t="str">
+        <v>Additional Recipients</v>
+      </c>
+      <c r="B5372" t="str">
+        <v>مستلمون إضافيون</v>
+      </c>
+      <c r="C5372" t="str">
+        <v>Papildu saņēmēji</v>
+      </c>
+    </row>
+    <row r="5373">
+      <c r="A5373" t="str">
+        <v>Add Recipient</v>
+      </c>
+      <c r="B5373" t="str">
+        <v>إضافة مستلم</v>
+      </c>
+      <c r="C5373" t="str">
+        <v>Pievienot saņēmēju</v>
+      </c>
+    </row>
+    <row r="5374">
+      <c r="A5374" t="str">
+        <v>Add more people to receive this announcement (CC).</v>
+      </c>
+      <c r="B5374" t="str">
+        <v>أضف المزيد من الأشخاص لتلقي هذا الإعلان (نسخة).</v>
+      </c>
+      <c r="C5374" t="str">
+        <v>Pievienojiet vairāk personu, kas saņems šo paziņojumu (CC).</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5353"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5374"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5374"/>
+  <dimension ref="A1:C5376"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -59513,9 +59513,31 @@
         <v>Pievienojiet vairāk personu, kas saņems šo paziņojumu (CC).</v>
       </c>
     </row>
+    <row r="5375">
+      <c r="A5375" t="str">
+        <v>Risk Heat Map</v>
+      </c>
+      <c r="B5375" t="str">
+        <v>خريطة حرارة المخاطر</v>
+      </c>
+      <c r="C5375" t="str">
+        <v>Risku siltuma karte</v>
+      </c>
+    </row>
+    <row r="5376">
+      <c r="A5376" t="str">
+        <v>Complete the risk assessment to view the heat map.</v>
+      </c>
+      <c r="B5376" t="str">
+        <v>أكمل تقييم المخاطر لعرض خريطة الحرارة.</v>
+      </c>
+      <c r="C5376" t="str">
+        <v>Pabeidziet riska novērtējumu, lai skatītu siltuma karti.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5374"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5376"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5376"/>
+  <dimension ref="A1:C5411"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -59535,9 +59535,394 @@
         <v>Pabeidziet riska novērtējumu, lai skatītu siltuma karti.</v>
       </c>
     </row>
+    <row r="5377">
+      <c r="A5377" t="str">
+        <v>Internal Audit Report</v>
+      </c>
+      <c r="B5377" t="str">
+        <v>تقرير التدقيق الداخلي</v>
+      </c>
+      <c r="C5377" t="str">
+        <v>Iekšējā audita ziņojums</v>
+      </c>
+    </row>
+    <row r="5378">
+      <c r="A5378" t="str">
+        <v>Opinion</v>
+      </c>
+      <c r="B5378" t="str">
+        <v>الرأي</v>
+      </c>
+      <c r="C5378" t="str">
+        <v>Atzinums</v>
+      </c>
+    </row>
+    <row r="5379">
+      <c r="A5379" t="str">
+        <v>Overall Audit Opinion</v>
+      </c>
+      <c r="B5379" t="str">
+        <v>الرأي العام للتدقيق</v>
+      </c>
+      <c r="C5379" t="str">
+        <v>Kopējais audita atzinums</v>
+      </c>
+    </row>
+    <row r="5380">
+      <c r="A5380" t="str">
+        <v>Needs Improvement</v>
+      </c>
+      <c r="B5380" t="str">
+        <v>يحتاج إلى تحسين</v>
+      </c>
+      <c r="C5380" t="str">
+        <v>Nepieciešami uzlabojumi</v>
+      </c>
+    </row>
+    <row r="5381">
+      <c r="A5381" t="str">
+        <v>Total Observations</v>
+      </c>
+      <c r="B5381" t="str">
+        <v>إجمالي الملاحظات</v>
+      </c>
+      <c r="C5381" t="str">
+        <v>Kopā novērojumi</v>
+      </c>
+    </row>
+    <row r="5382">
+      <c r="A5382" t="str">
+        <v>Areas Requiring Management's Attention</v>
+      </c>
+      <c r="B5382" t="str">
+        <v>المجالات التي تتطلب اهتمام الإدارة</v>
+      </c>
+      <c r="C5382" t="str">
+        <v>Jomas, kurām nepieciešama vadības uzmanība</v>
+      </c>
+    </row>
+    <row r="5383">
+      <c r="A5383" t="str">
+        <v>Immediate Action</v>
+      </c>
+      <c r="B5383" t="str">
+        <v>إجراء فوري</v>
+      </c>
+      <c r="C5383" t="str">
+        <v>Tūlītēja rīcība</v>
+      </c>
+    </row>
+    <row r="5384">
+      <c r="A5384" t="str">
+        <v>Medium-Term Improvement</v>
+      </c>
+      <c r="B5384" t="str">
+        <v>تحسين متوسط المدى</v>
+      </c>
+      <c r="C5384" t="str">
+        <v>Vidēja termiņa uzlabojums</v>
+      </c>
+    </row>
+    <row r="5385">
+      <c r="A5385" t="str">
+        <v>Detailed Report</v>
+      </c>
+      <c r="B5385" t="str">
+        <v>التقرير التفصيلي</v>
+      </c>
+      <c r="C5385" t="str">
+        <v>Detalizēts ziņojums</v>
+      </c>
+    </row>
+    <row r="5386">
+      <c r="A5386" t="str">
+        <v>Priorities for the Implementation of Audit Recommendations</v>
+      </c>
+      <c r="B5386" t="str">
+        <v>أولويات تنفيذ توصيات التدقيق</v>
+      </c>
+      <c r="C5386" t="str">
+        <v>Audita ieteikumu īstenošanas prioritātes</v>
+      </c>
+    </row>
+    <row r="5387">
+      <c r="A5387" t="str">
+        <v>Definition of Finding Types</v>
+      </c>
+      <c r="B5387" t="str">
+        <v>تعريف أنواع الملاحظات</v>
+      </c>
+      <c r="C5387" t="str">
+        <v>Konstatējumu veidu definīcija</v>
+      </c>
+    </row>
+    <row r="5388">
+      <c r="A5388" t="str">
+        <v>Definition</v>
+      </c>
+      <c r="B5388" t="str">
+        <v>التعريف</v>
+      </c>
+      <c r="C5388" t="str">
+        <v>Definīcija</v>
+      </c>
+    </row>
+    <row r="5389">
+      <c r="A5389" t="str">
+        <v>Summary of Audit Findings</v>
+      </c>
+      <c r="B5389" t="str">
+        <v>ملخص ملاحظات التدقيق</v>
+      </c>
+      <c r="C5389" t="str">
+        <v>Audita konstatējumu kopsavilkums</v>
+      </c>
+    </row>
+    <row r="5390">
+      <c r="A5390" t="str">
+        <v>Index of Audit Notes</v>
+      </c>
+      <c r="B5390" t="str">
+        <v>فهرس ملاحظات التدقيق</v>
+      </c>
+      <c r="C5390" t="str">
+        <v>Audita piezīmju rādītājs</v>
+      </c>
+    </row>
+    <row r="5391">
+      <c r="A5391" t="str">
+        <v>Summary of Findings</v>
+      </c>
+      <c r="B5391" t="str">
+        <v>ملخص الملاحظات</v>
+      </c>
+      <c r="C5391" t="str">
+        <v>Konstatējumu kopsavilkums</v>
+      </c>
+    </row>
+    <row r="5392">
+      <c r="A5392" t="str">
+        <v>Number</v>
+      </c>
+      <c r="B5392" t="str">
+        <v>الرقم</v>
+      </c>
+      <c r="C5392" t="str">
+        <v>Numurs</v>
+      </c>
+    </row>
+    <row r="5393">
+      <c r="A5393" t="str">
+        <v>Detailed Notes</v>
+      </c>
+      <c r="B5393" t="str">
+        <v>الملاحظات التفصيلية</v>
+      </c>
+      <c r="C5393" t="str">
+        <v>Detalizētas piezīmes</v>
+      </c>
+    </row>
+    <row r="5394">
+      <c r="A5394" t="str">
+        <v>Not provided</v>
+      </c>
+      <c r="B5394" t="str">
+        <v>غير متوفر</v>
+      </c>
+      <c r="C5394" t="str">
+        <v>Nav norādīts</v>
+      </c>
+    </row>
+    <row r="5395">
+      <c r="A5395" t="str">
+        <v>Finding Type</v>
+      </c>
+      <c r="B5395" t="str">
+        <v>نوع الملاحظة</v>
+      </c>
+      <c r="C5395" t="str">
+        <v>Konstatējuma veids</v>
+      </c>
+    </row>
+    <row r="5396">
+      <c r="A5396" t="str">
+        <v>Select finding type</v>
+      </c>
+      <c r="B5396" t="str">
+        <v>اختر نوع الملاحظة</v>
+      </c>
+      <c r="C5396" t="str">
+        <v>Atlasiet konstatējuma veidu</v>
+      </c>
+    </row>
+    <row r="5397">
+      <c r="A5397" t="str">
+        <v>Absence of Control</v>
+      </c>
+      <c r="B5397" t="str">
+        <v>غياب الرقابة</v>
+      </c>
+      <c r="C5397" t="str">
+        <v>Kontroles trūkums</v>
+      </c>
+    </row>
+    <row r="5398">
+      <c r="A5398" t="str">
+        <v>Lack of Operational Effectiveness</v>
+      </c>
+      <c r="B5398" t="str">
+        <v>ضعف الفاعلية التشغيلية</v>
+      </c>
+      <c r="C5398" t="str">
+        <v>Operacionālās efektivitātes trūkums</v>
+      </c>
+    </row>
+    <row r="5399">
+      <c r="A5399" t="str">
+        <v>Best Practices</v>
+      </c>
+      <c r="B5399" t="str">
+        <v>أفضل الممارسات</v>
+      </c>
+      <c r="C5399" t="str">
+        <v>Labākā prakse</v>
+      </c>
+    </row>
+    <row r="5400">
+      <c r="A5400" t="str">
+        <v>Non-Compliance</v>
+      </c>
+      <c r="B5400" t="str">
+        <v>عدم الامتثال</v>
+      </c>
+      <c r="C5400" t="str">
+        <v>Neatbilstība</v>
+      </c>
+    </row>
+    <row r="5401">
+      <c r="A5401" t="str">
+        <v>Select the overall audit opinion for</v>
+      </c>
+      <c r="B5401" t="str">
+        <v>اختر الرأي العام للتدقيق لـ</v>
+      </c>
+      <c r="C5401" t="str">
+        <v>Atlasiet kopējo audita atzinumu priekš</v>
+      </c>
+    </row>
+    <row r="5402">
+      <c r="A5402" t="str">
+        <v>You can refine the opinion and all report sections after generating.</v>
+      </c>
+      <c r="B5402" t="str">
+        <v>يمكنك تحسين الرأي وجميع أقسام التقرير بعد الإنشاء.</v>
+      </c>
+      <c r="C5402" t="str">
+        <v>Pēc ģenerēšanas varat precizēt atzinumu un visas ziņojuma sadaļas.</v>
+      </c>
+    </row>
+    <row r="5403">
+      <c r="A5403" t="str">
+        <v>High-priority audit observations are given precedence for implementation to assist management in directing resources toward the timely execution of corrective actions and mitigation of significant risks.</v>
+      </c>
+      <c r="B5403" t="str">
+        <v>تُعطى ملاحظات التدقيق ذات الأولوية العالية الأسبقية في التنفيذ لمساعدة الإدارة على توجيه الموارد نحو التنفيذ الفوري للإجراءات التصحيحية وتخفيف المخاطر الجوهرية.</v>
+      </c>
+      <c r="C5403" t="str">
+        <v>Augstas prioritātes audita novērojumiem tiek dota priekšroka īstenošanā, lai palīdzētu vadībai novirzīt resursus savlaicīgai korektīvo darbību izpildei un būtisku risku mazināšanai.</v>
+      </c>
+    </row>
+    <row r="5404">
+      <c r="A5404" t="str">
+        <v>It needs to be constantly reviewed and monitored, and the process of evaluating control systems must be completed. Senior management should be informed consistently.</v>
+      </c>
+      <c r="B5404" t="str">
+        <v>يجب مراجعته ومراقبته باستمرار، ويجب إكمال عملية تقييم أنظمة الرقابة. ويجب إبلاغ الإدارة العليا باستمرار.</v>
+      </c>
+      <c r="C5404" t="str">
+        <v>Tas pastāvīgi jāpārskata un jāuzrauga, un jāpabeidz kontroles sistēmu novērtēšanas process. Augstākā vadība regulāri jāinformē.</v>
+      </c>
+    </row>
+    <row r="5405">
+      <c r="A5405" t="str">
+        <v>You need to review regularly to ensure the adequacy and effectiveness of the control systems. Senior management should be informed regularly.</v>
+      </c>
+      <c r="B5405" t="str">
+        <v>تحتاج إلى المراجعة بانتظام لضمان كفاية وفعالية أنظمة الرقابة. ويجب إبلاغ الإدارة العليا بانتظام.</v>
+      </c>
+      <c r="C5405" t="str">
+        <v>Regulāri jāpārskata, lai nodrošinātu kontroles sistēmu pietiekamību un efektivitāti. Augstākā vadība regulāri jāinformē.</v>
+      </c>
+    </row>
+    <row r="5406">
+      <c r="A5406" t="str">
+        <v>You need to review periodically, keeping in mind monitoring the results of the risk to ensure it doesn't increase over time.</v>
+      </c>
+      <c r="B5406" t="str">
+        <v>تحتاج إلى المراجعة دوريًا، مع مراعاة مراقبة نتائج المخاطر لضمان عدم زيادتها بمرور الوقت.</v>
+      </c>
+      <c r="C5406" t="str">
+        <v>Periodiski jāpārskata, ņemot vērā riska rezultātu uzraudzību, lai nodrošinātu, ka tas laika gaitā nepalielinās.</v>
+      </c>
+    </row>
+    <row r="5407">
+      <c r="A5407" t="str">
+        <v>Inspection of the control systems required is not specific, and control measures are evaluated when appropriate. No need for reporting.</v>
+      </c>
+      <c r="B5407" t="str">
+        <v>فحص أنظمة الرقابة المطلوبة غير محدد، وتُقيَّم تدابير الرقابة عند الاقتضاء. لا حاجة لإعداد التقارير.</v>
+      </c>
+      <c r="C5407" t="str">
+        <v>Nepieciešamo kontroles sistēmu pārbaude nav specifiska, un kontroles pasākumi tiek novērtēti pēc vajadzības. Ziņošana nav nepieciešama.</v>
+      </c>
+    </row>
+    <row r="5408">
+      <c r="A5408" t="str">
+        <v>Absence of control or errors in the design of the existing control procedure.</v>
+      </c>
+      <c r="B5408" t="str">
+        <v>غياب الرقابة أو أخطاء في تصميم إجراء الرقابة القائم.</v>
+      </c>
+      <c r="C5408" t="str">
+        <v>Kontroles trūkums vai kļūdas esošās kontroles procedūras izstrādē.</v>
+      </c>
+    </row>
+    <row r="5409">
+      <c r="A5409" t="str">
+        <v>The control procedure does not work as required although it is appropriately designed, or the person responsible does not have the competence and authority to implement the control effectively.</v>
+      </c>
+      <c r="B5409" t="str">
+        <v>لا يعمل إجراء الرقابة كما هو مطلوب رغم تصميمه بشكل مناسب، أو أن الشخص المسؤول لا يملك الكفاءة والصلاحية لتنفيذ الرقابة بفعالية.</v>
+      </c>
+      <c r="C5409" t="str">
+        <v>Kontroles procedūra nedarbojas, kā paredzēts, lai gan tā ir atbilstoši izstrādāta, vai atbildīgajai personai nav kompetences un pilnvaru efektīvi īstenot kontroli.</v>
+      </c>
+    </row>
+    <row r="5410">
+      <c r="A5410" t="str">
+        <v>Note to strengthen the internal control environment based on best practices.</v>
+      </c>
+      <c r="B5410" t="str">
+        <v>ملاحظة لتعزيز بيئة الرقابة الداخلية بناءً على أفضل الممارسات.</v>
+      </c>
+      <c r="C5410" t="str">
+        <v>Piezīme iekšējās kontroles vides stiprināšanai, pamatojoties uz labāko praksi.</v>
+      </c>
+    </row>
+    <row r="5411">
+      <c r="A5411" t="str">
+        <v>Findings resulting from non-compliance with legislation, regulations and laws.</v>
+      </c>
+      <c r="B5411" t="str">
+        <v>ملاحظات ناتجة عن عدم الامتثال للتشريعات واللوائح والقوانين.</v>
+      </c>
+      <c r="C5411" t="str">
+        <v>Konstatējumi, kas izriet no neatbilstības tiesību aktiem, noteikumiem un likumiem.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5376"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5411"/>
+  <dimension ref="A1:C5423"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -59920,9 +59920,141 @@
         <v>Konstatējumi, kas izriet no neatbilstības tiesību aktiem, noteikumiem un likumiem.</v>
       </c>
     </row>
+    <row r="5412">
+      <c r="A5412" t="str">
+        <v>Finish &amp; Generate Report</v>
+      </c>
+      <c r="B5412" t="str">
+        <v>إنهاء وإنشاء التقرير</v>
+      </c>
+      <c r="C5412" t="str">
+        <v>Pabeigt un ģenerēt ziņojumu</v>
+      </c>
+    </row>
+    <row r="5413">
+      <c r="A5413" t="str">
+        <v>Complete all previous steps to finish the audit and generate the report.</v>
+      </c>
+      <c r="B5413" t="str">
+        <v>أكمل جميع الخطوات السابقة لإنهاء التدقيق وإنشاء التقرير.</v>
+      </c>
+      <c r="C5413" t="str">
+        <v>Pabeidziet visus iepriekšējos soļus, lai pabeigtu auditu un ģenerētu ziņojumu.</v>
+      </c>
+    </row>
+    <row r="5414">
+      <c r="A5414" t="str">
+        <v>Audit completed and report generated</v>
+      </c>
+      <c r="B5414" t="str">
+        <v>تم إكمال التدقيق وإنشاء التقرير</v>
+      </c>
+      <c r="C5414" t="str">
+        <v>Audits pabeigts un ziņojums ģenerēts</v>
+      </c>
+    </row>
+    <row r="5415">
+      <c r="A5415" t="str">
+        <v>Failed to finish audit and generate report</v>
+      </c>
+      <c r="B5415" t="str">
+        <v>فشل إنهاء التدقيق وإنشاء التقرير</v>
+      </c>
+      <c r="C5415" t="str">
+        <v>Neizdevās pabeigt auditu un ģenerēt ziņojumu</v>
+      </c>
+    </row>
+    <row r="5416">
+      <c r="A5416" t="str">
+        <v>View Report</v>
+      </c>
+      <c r="B5416" t="str">
+        <v>عرض التقرير</v>
+      </c>
+      <c r="C5416" t="str">
+        <v>Skatīt ziņojumu</v>
+      </c>
+    </row>
+    <row r="5417">
+      <c r="A5417" t="str">
+        <v>Add Findings</v>
+      </c>
+      <c r="B5417" t="str">
+        <v>إضافة ملاحظات</v>
+      </c>
+      <c r="C5417" t="str">
+        <v>Pievienot konstatējumus</v>
+      </c>
+    </row>
+    <row r="5418">
+      <c r="A5418" t="str">
+        <v>Save Findings</v>
+      </c>
+      <c r="B5418" t="str">
+        <v>حفظ الملاحظات</v>
+      </c>
+      <c r="C5418" t="str">
+        <v>Saglabāt konstatējumus</v>
+      </c>
+    </row>
+    <row r="5419">
+      <c r="A5419" t="str">
+        <v>Use Add Row to record multiple findings, then Save Findings.</v>
+      </c>
+      <c r="B5419" t="str">
+        <v>استخدم "إضافة صف" لتسجيل عدة ملاحظات، ثم احفظ الملاحظات.</v>
+      </c>
+      <c r="C5419" t="str">
+        <v>Izmantojiet "Pievienot rindu", lai reģistrētu vairākus konstatējumus, pēc tam saglabājiet.</v>
+      </c>
+    </row>
+    <row r="5420">
+      <c r="A5420" t="str">
+        <v>Recipients</v>
+      </c>
+      <c r="B5420" t="str">
+        <v>المستلمون</v>
+      </c>
+      <c r="C5420" t="str">
+        <v>Saņēmēji</v>
+      </c>
+    </row>
+    <row r="5421">
+      <c r="A5421" t="str">
+        <v>Select recipient</v>
+      </c>
+      <c r="B5421" t="str">
+        <v>اختر مستلمًا</v>
+      </c>
+      <c r="C5421" t="str">
+        <v>Atlasiet saņēmēju</v>
+      </c>
+    </row>
+    <row r="5422">
+      <c r="A5422" t="str">
+        <v>Select one or more recipients; their email is added automatically.</v>
+      </c>
+      <c r="B5422" t="str">
+        <v>اختر مستلمًا واحدًا أو أكثر؛ تتم إضافة بريدهم الإلكتروني تلقائيًا.</v>
+      </c>
+      <c r="C5422" t="str">
+        <v>Atlasiet vienu vai vairākus saņēmējus; viņu e-pasts tiek pievienots automātiski.</v>
+      </c>
+    </row>
+    <row r="5423">
+      <c r="A5423" t="str">
+        <v>All users already added</v>
+      </c>
+      <c r="B5423" t="str">
+        <v>تمت إضافة جميع المستخدمين بالفعل</v>
+      </c>
+      <c r="C5423" t="str">
+        <v>Visi lietotāji jau pievienoti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5423"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/i18n/translations.xlsx
+++ b/i18n/translations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5423"/>
+  <dimension ref="A1:C5481"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -60052,9 +60052,647 @@
         <v>Visi lietotāji jau pievienoti</v>
       </c>
     </row>
+    <row r="5424">
+      <c r="A5424" t="str">
+        <v>Independence &amp; Objectivity</v>
+      </c>
+      <c r="B5424" t="str">
+        <v>الاستقلالية والموضوعية</v>
+      </c>
+      <c r="C5424" t="str">
+        <v>Neatkarība un objektivitāte</v>
+      </c>
+    </row>
+    <row r="5425">
+      <c r="A5425" t="str">
+        <v>Independence</v>
+      </c>
+      <c r="B5425" t="str">
+        <v>الاستقلالية</v>
+      </c>
+      <c r="C5425" t="str">
+        <v>Neatkarība</v>
+      </c>
+    </row>
+    <row r="5426">
+      <c r="A5426" t="str">
+        <v>Objectivity</v>
+      </c>
+      <c r="B5426" t="str">
+        <v>الموضوعية</v>
+      </c>
+      <c r="C5426" t="str">
+        <v>Objektivitāte</v>
+      </c>
+    </row>
+    <row r="5427">
+      <c r="A5427" t="str">
+        <v>Independence Declaration</v>
+      </c>
+      <c r="B5427" t="str">
+        <v>إقرار الاستقلالية</v>
+      </c>
+      <c r="C5427" t="str">
+        <v>Neatkarības deklarācija</v>
+      </c>
+    </row>
+    <row r="5428">
+      <c r="A5428" t="str">
+        <v>Objectivity Declaration</v>
+      </c>
+      <c r="B5428" t="str">
+        <v>إقرار الموضوعية</v>
+      </c>
+      <c r="C5428" t="str">
+        <v>Objektivitātes deklarācija</v>
+      </c>
+    </row>
+    <row r="5429">
+      <c r="A5429" t="str">
+        <v>New Declaration</v>
+      </c>
+      <c r="B5429" t="str">
+        <v>إقرار جديد</v>
+      </c>
+      <c r="C5429" t="str">
+        <v>Jauna deklarācija</v>
+      </c>
+    </row>
+    <row r="5430">
+      <c r="A5430" t="str">
+        <v>View Declaration</v>
+      </c>
+      <c r="B5430" t="str">
+        <v>عرض الإقرار</v>
+      </c>
+      <c r="C5430" t="str">
+        <v>Skatīt deklarāciju</v>
+      </c>
+    </row>
+    <row r="5431">
+      <c r="A5431" t="str">
+        <v>Edit Declaration</v>
+      </c>
+      <c r="B5431" t="str">
+        <v>تعديل الإقرار</v>
+      </c>
+      <c r="C5431" t="str">
+        <v>Rediģēt deklarāciju</v>
+      </c>
+    </row>
+    <row r="5432">
+      <c r="A5432" t="str">
+        <v>Delete Declaration</v>
+      </c>
+      <c r="B5432" t="str">
+        <v>حذف الإقرار</v>
+      </c>
+      <c r="C5432" t="str">
+        <v>Dzēst deklarāciju</v>
+      </c>
+    </row>
+    <row r="5433">
+      <c r="A5433" t="str">
+        <v>Declaration Type</v>
+      </c>
+      <c r="B5433" t="str">
+        <v>نوع الإقرار</v>
+      </c>
+      <c r="C5433" t="str">
+        <v>Deklarācijas veids</v>
+      </c>
+    </row>
+    <row r="5434">
+      <c r="A5434" t="str">
+        <v>Declaration Result</v>
+      </c>
+      <c r="B5434" t="str">
+        <v>نتيجة الإقرار</v>
+      </c>
+      <c r="C5434" t="str">
+        <v>Deklarācijas rezultāts</v>
+      </c>
+    </row>
+    <row r="5435">
+      <c r="A5435" t="str">
+        <v>Objectivity Assessment</v>
+      </c>
+      <c r="B5435" t="str">
+        <v>تقييم الموضوعية</v>
+      </c>
+      <c r="C5435" t="str">
+        <v>Objektivitātes novērtējums</v>
+      </c>
+    </row>
+    <row r="5436">
+      <c r="A5436" t="str">
+        <v>Declaration saved</v>
+      </c>
+      <c r="B5436" t="str">
+        <v>تم حفظ الإقرار</v>
+      </c>
+      <c r="C5436" t="str">
+        <v>Deklarācija saglabāta</v>
+      </c>
+    </row>
+    <row r="5437">
+      <c r="A5437" t="str">
+        <v>Declaration deleted</v>
+      </c>
+      <c r="B5437" t="str">
+        <v>تم حذف الإقرار</v>
+      </c>
+      <c r="C5437" t="str">
+        <v>Deklarācija dzēsta</v>
+      </c>
+    </row>
+    <row r="5438">
+      <c r="A5438" t="str">
+        <v>Failed to load declarations</v>
+      </c>
+      <c r="B5438" t="str">
+        <v>فشل تحميل الإقرارات</v>
+      </c>
+      <c r="C5438" t="str">
+        <v>Neizdevās ielādēt deklarācijas</v>
+      </c>
+    </row>
+    <row r="5439">
+      <c r="A5439" t="str">
+        <v>Failed to save declaration</v>
+      </c>
+      <c r="B5439" t="str">
+        <v>فشل حفظ الإقرار</v>
+      </c>
+      <c r="C5439" t="str">
+        <v>Neizdevās saglabāt deklarāciju</v>
+      </c>
+    </row>
+    <row r="5440">
+      <c r="A5440" t="str">
+        <v>Failed to delete declaration</v>
+      </c>
+      <c r="B5440" t="str">
+        <v>فشل حذف الإقرار</v>
+      </c>
+      <c r="C5440" t="str">
+        <v>Neizdevās dzēst deklarāciju</v>
+      </c>
+    </row>
+    <row r="5441">
+      <c r="A5441" t="str">
+        <v>No declarations yet</v>
+      </c>
+      <c r="B5441" t="str">
+        <v>لا توجد إقرارات بعد</v>
+      </c>
+      <c r="C5441" t="str">
+        <v>Vēl nav deklarāciju</v>
+      </c>
+    </row>
+    <row r="5442">
+      <c r="A5442" t="str">
+        <v>Use New Declaration to add one.</v>
+      </c>
+      <c r="B5442" t="str">
+        <v>استخدم "إقرار جديد" لإضافة واحد.</v>
+      </c>
+      <c r="C5442" t="str">
+        <v>Izmantojiet "Jauna deklarācija", lai pievienotu.</v>
+      </c>
+    </row>
+    <row r="5443">
+      <c r="A5443" t="str">
+        <v>Auditor independence and objectivity declarations per the Global Internal Audit Standards.</v>
+      </c>
+      <c r="B5443" t="str">
+        <v>إقرارات استقلالية وموضوعية المدقق وفقًا للمعايير العالمية للتدقيق الداخلي.</v>
+      </c>
+      <c r="C5443" t="str">
+        <v>Auditora neatkarības un objektivitātes deklarācijas saskaņā ar Globālajiem iekšējā audita standartiem.</v>
+      </c>
+    </row>
+    <row r="5444">
+      <c r="A5444" t="str">
+        <v>Position</v>
+      </c>
+      <c r="B5444" t="str">
+        <v>المنصب</v>
+      </c>
+      <c r="C5444" t="str">
+        <v>Amats</v>
+      </c>
+    </row>
+    <row r="5445">
+      <c r="A5445" t="str">
+        <v>Project</v>
+      </c>
+      <c r="B5445" t="str">
+        <v>المشروع</v>
+      </c>
+      <c r="C5445" t="str">
+        <v>Projekts</v>
+      </c>
+    </row>
+    <row r="5446">
+      <c r="A5446" t="str">
+        <v>Result</v>
+      </c>
+      <c r="B5446" t="str">
+        <v>النتيجة</v>
+      </c>
+      <c r="C5446" t="str">
+        <v>Rezultāts</v>
+      </c>
+    </row>
+    <row r="5447">
+      <c r="A5447" t="str">
+        <v>Explanation</v>
+      </c>
+      <c r="B5447" t="str">
+        <v>التوضيح</v>
+      </c>
+      <c r="C5447" t="str">
+        <v>Skaidrojums</v>
+      </c>
+    </row>
+    <row r="5448">
+      <c r="A5448" t="str">
+        <v>Employee Signature</v>
+      </c>
+      <c r="B5448" t="str">
+        <v>توقيع الموظف</v>
+      </c>
+      <c r="C5448" t="str">
+        <v>Darbinieka paraksts</v>
+      </c>
+    </row>
+    <row r="5449">
+      <c r="A5449" t="str">
+        <v>Internal Auditor Signature</v>
+      </c>
+      <c r="B5449" t="str">
+        <v>توقيع المدقق الداخلي</v>
+      </c>
+      <c r="C5449" t="str">
+        <v>Iekšējā auditora paraksts</v>
+      </c>
+    </row>
+    <row r="5450">
+      <c r="A5450" t="str">
+        <v>Type your full name</v>
+      </c>
+      <c r="B5450" t="str">
+        <v>اكتب اسمك الكامل</v>
+      </c>
+      <c r="C5450" t="str">
+        <v>Ierakstiet savu pilnu vārdu</v>
+      </c>
+    </row>
+    <row r="5451">
+      <c r="A5451" t="str">
+        <v>Save Draft</v>
+      </c>
+      <c r="B5451" t="str">
+        <v>حفظ كمسودة</v>
+      </c>
+      <c r="C5451" t="str">
+        <v>Saglabāt melnrakstu</v>
+      </c>
+    </row>
+    <row r="5452">
+      <c r="A5452" t="str">
+        <v>Mark Reviewed</v>
+      </c>
+      <c r="B5452" t="str">
+        <v>وضع علامة تمت المراجعة</v>
+      </c>
+      <c r="C5452" t="str">
+        <v>Atzīmēt kā pārskatītu</v>
+      </c>
+    </row>
+    <row r="5453">
+      <c r="A5453" t="str">
+        <v>Reviewer Name</v>
+      </c>
+      <c r="B5453" t="str">
+        <v>اسم المراجع</v>
+      </c>
+      <c r="C5453" t="str">
+        <v>Pārskatītāja vārds</v>
+      </c>
+    </row>
+    <row r="5454">
+      <c r="A5454" t="str">
+        <v>Reviewer Signature</v>
+      </c>
+      <c r="B5454" t="str">
+        <v>توقيع المراجع</v>
+      </c>
+      <c r="C5454" t="str">
+        <v>Pārskatītāja paraksts</v>
+      </c>
+    </row>
+    <row r="5455">
+      <c r="A5455" t="str">
+        <v>Reviewer name is required</v>
+      </c>
+      <c r="B5455" t="str">
+        <v>اسم المراجع مطلوب</v>
+      </c>
+      <c r="C5455" t="str">
+        <v>Pārskatītāja vārds ir obligāts</v>
+      </c>
+    </row>
+    <row r="5456">
+      <c r="A5456" t="str">
+        <v>Please select a declaration result</v>
+      </c>
+      <c r="B5456" t="str">
+        <v>يرجى اختيار نتيجة الإقرار</v>
+      </c>
+      <c r="C5456" t="str">
+        <v>Lūdzu, atlasiet deklarācijas rezultātu</v>
+      </c>
+    </row>
+    <row r="5457">
+      <c r="A5457" t="str">
+        <v>Reviewed by (Chief Audit Executive / Audit Manager)</v>
+      </c>
+      <c r="B5457" t="str">
+        <v>تمت المراجعة بواسطة (الرئيس التنفيذي للتدقيق / مدير التدقيق)</v>
+      </c>
+      <c r="C5457" t="str">
+        <v>Pārskatīja (Galvenais audita vadītājs / Audita vadītājs)</v>
+      </c>
+    </row>
+    <row r="5458">
+      <c r="A5458" t="str">
+        <v>Approved by (Audit Manager)</v>
+      </c>
+      <c r="B5458" t="str">
+        <v>تمت الموافقة بواسطة (مدير التدقيق)</v>
+      </c>
+      <c r="C5458" t="str">
+        <v>Apstiprināja (Audita vadītājs)</v>
+      </c>
+    </row>
+    <row r="5459">
+      <c r="A5459" t="str">
+        <v>Are you sure you want to delete this declaration? This action cannot be undone.</v>
+      </c>
+      <c r="B5459" t="str">
+        <v>هل أنت متأكد أنك تريد حذف هذا الإقرار؟ لا يمكن التراجع عن هذا الإجراء.</v>
+      </c>
+      <c r="C5459" t="str">
+        <v>Vai tiešām vēlaties dzēst šo deklarāciju? Šo darbību nevar atsaukt.</v>
+      </c>
+    </row>
+    <row r="5460">
+      <c r="A5460" t="str">
+        <v>I confirm full independence</v>
+      </c>
+      <c r="B5460" t="str">
+        <v>أؤكد الاستقلالية الكاملة</v>
+      </c>
+      <c r="C5460" t="str">
+        <v>Apstiprinu pilnīgu neatkarību</v>
+      </c>
+    </row>
+    <row r="5461">
+      <c r="A5461" t="str">
+        <v>Potential impairment exists</v>
+      </c>
+      <c r="B5461" t="str">
+        <v>يوجد ضعف محتمل</v>
+      </c>
+      <c r="C5461" t="str">
+        <v>Pastāv iespējama ietekme</v>
+      </c>
+    </row>
+    <row r="5462">
+      <c r="A5462" t="str">
+        <v>No threats to objectivity identified</v>
+      </c>
+      <c r="B5462" t="str">
+        <v>لم يتم تحديد أي تهديدات للموضوعية</v>
+      </c>
+      <c r="C5462" t="str">
+        <v>Objektivitātes apdraudējumi nav konstatēti</v>
+      </c>
+    </row>
+    <row r="5463">
+      <c r="A5463" t="str">
+        <v>Potential threat identified</v>
+      </c>
+      <c r="B5463" t="str">
+        <v>تم تحديد تهديد محتمل</v>
+      </c>
+      <c r="C5463" t="str">
+        <v>Konstatēts iespējams apdraudējums</v>
+      </c>
+    </row>
+    <row r="5464">
+      <c r="A5464" t="str">
+        <v>I hereby declare that I am independent with respect to the activities, departments, and processes subject to this audit engagement. I confirm that:</v>
+      </c>
+      <c r="B5464" t="str">
+        <v>أقر بموجب هذا بأنني مستقل فيما يتعلق بالأنشطة والإدارات والعمليات الخاضعة لمهمة التدقيق هذه. وأؤكد أنني:</v>
+      </c>
+      <c r="C5464" t="str">
+        <v>Ar šo apliecinu, ka esmu neatkarīgs attiecībā uz darbībām, nodaļām un procesiem, uz kuriem attiecas šis audita uzdevums. Apstiprinu, ka:</v>
+      </c>
+    </row>
+    <row r="5465">
+      <c r="A5465" t="str">
+        <v>I confirm that I will perform this audit engagement with full objectivity and professional judgment. I declare that:</v>
+      </c>
+      <c r="B5465" t="str">
+        <v>أؤكد أنني سأؤدي مهمة التدقيق هذه بموضوعية كاملة وحكم مهني. وأقر بأنني:</v>
+      </c>
+      <c r="C5465" t="str">
+        <v>Apstiprinu, ka veikšu šo audita uzdevumu ar pilnīgu objektivitāti un profesionālu spriedumu. Apliecinu, ka:</v>
+      </c>
+    </row>
+    <row r="5466">
+      <c r="A5466" t="str">
+        <v>I have no personal, financial, or professional interests that could impair my independence.</v>
+      </c>
+      <c r="B5466" t="str">
+        <v>ليس لدي أي مصالح شخصية أو مالية أو مهنية قد تضعف استقلاليتي.</v>
+      </c>
+      <c r="C5466" t="str">
+        <v>Man nav personisku, finansiālu vai profesionālu interešu, kas varētu ietekmēt manu neatkarību.</v>
+      </c>
+    </row>
+    <row r="5467">
+      <c r="A5467" t="str">
+        <v>I have not been involved in operational responsibilities related to the audited area during the past 12 months.</v>
+      </c>
+      <c r="B5467" t="str">
+        <v>لم أشارك في مسؤوليات تشغيلية تتعلق بالمجال الخاضع للتدقيق خلال الأشهر الـ12 الماضية.</v>
+      </c>
+      <c r="C5467" t="str">
+        <v>Pēdējo 12 mēnešu laikā neesmu bijis iesaistīts ar auditējamo jomu saistītos operacionālos pienākumos.</v>
+      </c>
+    </row>
+    <row r="5468">
+      <c r="A5468" t="str">
+        <v>I have no close relationships with personnel working in the audited department that may affect my impartiality.</v>
+      </c>
+      <c r="B5468" t="str">
+        <v>ليس لدي علاقات وثيقة مع العاملين في الإدارة الخاضعة للتدقيق قد تؤثر على حيادي.</v>
+      </c>
+      <c r="C5468" t="str">
+        <v>Man nav ciešu attiecību ar auditējamās nodaļas darbiniekiem, kas varētu ietekmēt manu objektivitāti.</v>
+      </c>
+    </row>
+    <row r="5469">
+      <c r="A5469" t="str">
+        <v>I will immediately disclose any situation that may arise which could affect my independence.</v>
+      </c>
+      <c r="B5469" t="str">
+        <v>سأفصح فورًا عن أي موقف قد ينشأ ويؤثر على استقلاليتي.</v>
+      </c>
+      <c r="C5469" t="str">
+        <v>Es nekavējoties atklāšu jebkuru situāciju, kas varētu ietekmēt manu neatkarību.</v>
+      </c>
+    </row>
+    <row r="5470">
+      <c r="A5470" t="str">
+        <v>I will conduct the audit without bias, conflict of interest, or undue influence.</v>
+      </c>
+      <c r="B5470" t="str">
+        <v>سأجري التدقيق دون تحيز أو تضارب في المصالح أو تأثير غير مبرر.</v>
+      </c>
+      <c r="C5470" t="str">
+        <v>Es veikšu auditu bez aizspriedumiem, interešu konflikta vai nepamatotas ietekmes.</v>
+      </c>
+    </row>
+    <row r="5471">
+      <c r="A5471" t="str">
+        <v>My conclusions will be based solely on sufficient and appropriate audit evidence.</v>
+      </c>
+      <c r="B5471" t="str">
+        <v>ستستند استنتاجاتي فقط إلى أدلة تدقيق كافية ومناسبة.</v>
+      </c>
+      <c r="C5471" t="str">
+        <v>Mani secinājumi balstīsies tikai uz pietiekamiem un atbilstošiem audita pierādījumiem.</v>
+      </c>
+    </row>
+    <row r="5472">
+      <c r="A5472" t="str">
+        <v>I will disclose any circumstances that may affect my professional judgment.</v>
+      </c>
+      <c r="B5472" t="str">
+        <v>سأفصح عن أي ظروف قد تؤثر على حكمي المهني.</v>
+      </c>
+      <c r="C5472" t="str">
+        <v>Es atklāšu jebkurus apstākļus, kas varētu ietekmēt manu profesionālo spriedumu.</v>
+      </c>
+    </row>
+    <row r="5473">
+      <c r="A5473" t="str">
+        <v>I will adhere to the Code of Ethics and Objectivity principles established by The Institute of Internal Auditors.</v>
+      </c>
+      <c r="B5473" t="str">
+        <v>سألتزم بمدونة الأخلاقيات ومبادئ الموضوعية التي وضعها معهد المدققين الداخليين.</v>
+      </c>
+      <c r="C5473" t="str">
+        <v>Es ievērošu Ētikas kodeksu un objektivitātes principus, ko noteicis Iekšējo auditoru institūts.</v>
+      </c>
+    </row>
+    <row r="5474">
+      <c r="A5474" t="str">
+        <v>Finish and Generate Report</v>
+      </c>
+      <c r="B5474" t="str">
+        <v>إنهاء وإنشاء التقرير</v>
+      </c>
+      <c r="C5474" t="str">
+        <v>Pabeigt un ģenerēt ziņojumu</v>
+      </c>
+    </row>
+    <row r="5475">
+      <c r="A5475" t="str">
+        <v>This marks the engagement as completed and generates the audit report. The report will appear in the Report section.</v>
+      </c>
+      <c r="B5475" t="str">
+        <v>يؤدي هذا إلى وضع علامة على المهمة كمكتملة وإنشاء تقرير التدقيق. سيظهر التقرير في قسم التقارير.</v>
+      </c>
+      <c r="C5475" t="str">
+        <v>Tas atzīmē uzdevumu kā pabeigtu un ģenerē audita ziņojumu. Ziņojums parādīsies ziņojumu sadaļā.</v>
+      </c>
+    </row>
+    <row r="5476">
+      <c r="A5476" t="str">
+        <v>Report generated. Opening the Report section.</v>
+      </c>
+      <c r="B5476" t="str">
+        <v>تم إنشاء التقرير. جارٍ فتح قسم التقارير.</v>
+      </c>
+      <c r="C5476" t="str">
+        <v>Ziņojums ģenerēts. Atver ziņojumu sadaļu.</v>
+      </c>
+    </row>
+    <row r="5477">
+      <c r="A5477" t="str">
+        <v>Generate the audit report. It will appear in the Report section.</v>
+      </c>
+      <c r="B5477" t="str">
+        <v>إنشاء تقرير التدقيق. سيظهر في قسم التقارير.</v>
+      </c>
+      <c r="C5477" t="str">
+        <v>Ģenerēt audita ziņojumu. Tas parādīsies ziņojumu sadaļā.</v>
+      </c>
+    </row>
+    <row r="5478">
+      <c r="A5478" t="str">
+        <v>Report generated. It is now available in the Report section.</v>
+      </c>
+      <c r="B5478" t="str">
+        <v>تم إنشاء التقرير. أصبح متاحًا الآن في قسم التقارير.</v>
+      </c>
+      <c r="C5478" t="str">
+        <v>Ziņojums ģenerēts. Tas tagad pieejams ziņojumu sadaļā.</v>
+      </c>
+    </row>
+    <row r="5479">
+      <c r="A5479" t="str">
+        <v>Report generated</v>
+      </c>
+      <c r="B5479" t="str">
+        <v>تم إنشاء التقرير</v>
+      </c>
+      <c r="C5479" t="str">
+        <v>Ziņojums ģenerēts</v>
+      </c>
+    </row>
+    <row r="5480">
+      <c r="A5480" t="str">
+        <v>Report generated — read only</v>
+      </c>
+      <c r="B5480" t="str">
+        <v>تم إنشاء التقرير — للقراءة فقط</v>
+      </c>
+      <c r="C5480" t="str">
+        <v>Ziņojums ģenerēts — tikai lasāms</v>
+      </c>
+    </row>
+    <row r="5481">
+      <c r="A5481" t="str">
+        <v>Failed to complete engagement</v>
+      </c>
+      <c r="B5481" t="str">
+        <v>فشل إكمال المهمة</v>
+      </c>
+      <c r="C5481" t="str">
+        <v>Neizdevās pabeigt uzdevumu</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5423"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5481"/>
   </ignoredErrors>
 </worksheet>
 </file>